--- a/scraped_data.xlsx
+++ b/scraped_data.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <workbookPr codeName="ThisWorkbook"/>
   <sheets>
-    <sheet name="Scraped Data" sheetId="1" r:id="rId1"/>
+    <sheet name="Excess Stock" sheetId="1" r:id="rId1"/>
   </sheets>
 </workbook>
 </file>
@@ -397,99 +397,339 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B11"/>
+  <dimension ref="A1:B21"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>Quote</v>
+        <v>Product</v>
       </c>
       <c r="B1" t="str">
-        <v>Author</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>“The world as we have created it is a process of our thinking. It cannot be changed without changing our thinking.”</v>
-      </c>
-      <c r="B2" t="str">
-        <v>Albert Einstein</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>“It is our choices, Harry, that show what we truly are, far more than our abilities.”</v>
-      </c>
-      <c r="B3" t="str">
-        <v>J.K. Rowling</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>“There are only two ways to live your life. One is as though nothing is a miracle. The other is as though everything is a miracle.”</v>
-      </c>
-      <c r="B4" t="str">
-        <v>Albert Einstein</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>“The person, be it gentleman or lady, who has not pleasure in a good novel, must be intolerably stupid.”</v>
-      </c>
-      <c r="B5" t="str">
-        <v>Jane Austen</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>“Imperfection is beauty, madness is genius and it's better to be absolutely ridiculous than absolutely boring.”</v>
-      </c>
-      <c r="B6" t="str">
-        <v>Marilyn Monroe</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>“Try not to become a man of success. Rather become a man of value.”</v>
-      </c>
-      <c r="B7" t="str">
-        <v>Albert Einstein</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>“It is better to be hated for what you are than to be loved for what you are not.”</v>
-      </c>
-      <c r="B8" t="str">
-        <v>André Gide</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>“I have not failed. I've just found 10,000 ways that won't work.”</v>
-      </c>
-      <c r="B9" t="str">
-        <v>Thomas A. Edison</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>“A woman is like a tea bag; you never know how strong it is until it's in hot water.”</v>
-      </c>
-      <c r="B10" t="str">
-        <v>Eleanor Roosevelt</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>“A day without sunshine is like, you know, night.”</v>
-      </c>
-      <c r="B11" t="str">
-        <v>Steve Martin</v>
+        <v>FullDetails</v>
+      </c>
+    </row>
+    <row r="2" xml:space="preserve">
+      <c r="A2" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4310 301-Coil, 2B,
+0.80 x 1128.0 x coil mm</v>
+      </c>
+      <c r="B2" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4310 301-Coil, 2B,
+0.80 x 1128.0 x coil mm
+Weight (Kg):10,677
+Quality:Prime
+Help
+Location:FABRICA ALGECIRAS
+2,700.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="3" xml:space="preserve">
+      <c r="A3" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4310 301-Coil, 2B,
+0.80 x 1139.0 x coil mm</v>
+      </c>
+      <c r="B3" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4310 301-Coil, 2B,
+0.80 x 1139.0 x coil mm
+Weight (Kg):7,820
+Quality:Prime
+Help
+Location:FABRICA ALGECIRAS
+2,275.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="4" xml:space="preserve">
+      <c r="A4" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4310 301-Coil, 2B,
+0.80 x 1288.0 x coil mm</v>
+      </c>
+      <c r="B4" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4310 301-Coil, 2B,
+0.80 x 1288.0 x coil mm
+Weight (Kg):20,316
+Quality:Prime
+Help
+Location:FABRICA ALGECIRAS
+2,700.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="5" xml:space="preserve">
+      <c r="A5" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4310 301-Coil, 2B,
+1.00 x 1270.0 x coil mm</v>
+      </c>
+      <c r="B5" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4310 301-Coil, 2B,
+1.00 x 1270.0 x coil mm
+Weight (Kg):17,550
+Quality:Prime
+Help
+Location:FABRICA ALGECIRAS
+2,700.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="6" xml:space="preserve">
+      <c r="A6" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4310 301-Coil, 2B,
+1.50 x 625.0 x coil mm</v>
+      </c>
+      <c r="B6" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4310 301-Coil, 2B,
+1.50 x 625.0 x coil mm
+Weight (Kg):950
+Quality:Downgraded
+Help
+Location:FABRICA ALGECIRAS
+1,875.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="7" xml:space="preserve">
+      <c r="A7" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4310 301-Coil, 2B,
+2.00 x 1279.0 x coil mm</v>
+      </c>
+      <c r="B7" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4310 301-Coil, 2B,
+2.00 x 1279.0 x coil mm
+Weight (Kg):23,630
+Quality:Prime
+Help
+Location:FABRICA ALGECIRAS
+2,700.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="8" xml:space="preserve">
+      <c r="A8" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4310 301-Coil, 2B,
+3.00 x 160.0 x coil mm</v>
+      </c>
+      <c r="B8" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4310 301-Coil, 2B,
+3.00 x 160.0 x coil mm
+Weight (Kg):2,880
+Quality:Prime
+Help
+Location:FABRICA ALGECIRAS
+1,925.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="9" xml:space="preserve">
+      <c r="A9" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4310 301-Coil, 2B,
+3.00 x 160.0 x coil mm</v>
+      </c>
+      <c r="B9" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4310 301-Coil, 2B,
+3.00 x 160.0 x coil mm
+Weight (Kg):2,678
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+1,925.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="10" xml:space="preserve">
+      <c r="A10" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4310 301-Coil, 2B,
+3.00 x 180.9 x coil mm</v>
+      </c>
+      <c r="B10" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4310 301-Coil, 2B,
+3.00 x 180.9 x coil mm
+Weight (Kg):3,078
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+1,925.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="11" xml:space="preserve">
+      <c r="A11" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4310 301-Coil, 2D,
+0.80 x 1263.0 x coil mm</v>
+      </c>
+      <c r="B11" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4310 301-Coil, 2D,
+0.80 x 1263.0 x coil mm
+Weight (Kg):17,770
+Quality:Prime
+Help
+Location:FABRICA ALGECIRAS
+2,700.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="12" xml:space="preserve">
+      <c r="A12" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4310 301-Coil, BA,
+0.40 x 120.9 x coil mm</v>
+      </c>
+      <c r="B12" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4310 301-Coil, BA,
+0.40 x 120.9 x coil mm
+Weight (Kg):886
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+1,875.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="13" xml:space="preserve">
+      <c r="A13" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4310 301-Coil, BA,
+0.40 x 1290.0 x coil mm</v>
+      </c>
+      <c r="B13" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4310 301-Coil, BA,
+0.40 x 1290.0 x coil mm
+Weight (Kg):9,500
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,075.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="14" xml:space="preserve">
+      <c r="A14" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4310 301-Coil, BA,
+0.40 x 140.9 x coil mm</v>
+      </c>
+      <c r="B14" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4310 301-Coil, BA,
+0.40 x 140.9 x coil mm
+Weight (Kg):922
+Quality:Downgraded
+Help
+Location:FABRICA ALGECIRAS
+1,875.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="15" xml:space="preserve">
+      <c r="A15" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4310 301-Coil, BA,
+0.40 x 150.9 x coil mm</v>
+      </c>
+      <c r="B15" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4310 301-Coil, BA,
+0.40 x 150.9 x coil mm
+Weight (Kg):912
+Quality:Downgraded
+Help
+Location:FABRICA ALGECIRAS
+1,875.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="16" xml:space="preserve">
+      <c r="A16" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4310 301-Coil, BA,
+0.40 x 170.0 x coil mm</v>
+      </c>
+      <c r="B16" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4310 301-Coil, BA,
+0.40 x 170.0 x coil mm
+Weight (Kg):1,694
+Quality:Prime
+Help
+Location:FABRICA ALGECIRAS
+1,925.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="17" xml:space="preserve">
+      <c r="A17" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4310 301-Coil, BA,
+0.40 x 180.9 x coil mm</v>
+      </c>
+      <c r="B17" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4310 301-Coil, BA,
+0.40 x 180.9 x coil mm
+Weight (Kg):1,401
+Quality:Downgraded
+Help
+Location:FABRICA ALGECIRAS
+1,875.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="18" xml:space="preserve">
+      <c r="A18" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4310 301-Coil, BA,
+0.40 x 190.0 x coil mm</v>
+      </c>
+      <c r="B18" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4310 301-Coil, BA,
+0.40 x 190.0 x coil mm
+Weight (Kg):1,034
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+1,925.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="19" xml:space="preserve">
+      <c r="A19" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4310 301-Coil, BA,
+0.40 x 520.0 x coil mm</v>
+      </c>
+      <c r="B19" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4310 301-Coil, BA,
+0.40 x 520.0 x coil mm
+Weight (Kg):4,059
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+1,975.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="20" xml:space="preserve">
+      <c r="A20" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4310 301-Coil, BA,
+0.40 x 536.5 x coil mm</v>
+      </c>
+      <c r="B20" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4310 301-Coil, BA,
+0.40 x 536.5 x coil mm
+Weight (Kg):2,565
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+1,975.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="21" xml:space="preserve">
+      <c r="A21" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4310 301-Coil, BA,
+0.40 x 536.5 x coil mm</v>
+      </c>
+      <c r="B21" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4310 301-Coil, BA,
+0.40 x 536.5 x coil mm
+Weight (Kg):2,738
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+1,975.00 €/ton
+Add to cart</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B11"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B21"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/scraped_data.xlsx
+++ b/scraped_data.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B650"/>
+  <dimension ref="A1:B601"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -2313,18 +2313,18 @@
     </row>
     <row r="121" xml:space="preserve">
       <c r="A121" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4301 304-Untrimmed, Coil, 2B,
-1.80 x 1275.0 x coil mm</v>
+        <v xml:space="preserve">Acerinox Europa, 1.4301 304-Untrimmed, Coil, BA,
+0.40 x 941.0 x coil mm</v>
       </c>
       <c r="B121" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4301 304-Untrimmed, Coil, 2B,
-1.80 x 1275.0 x coil mm
-Weight (Kg):3,135
-Quality:Prime
-Help
-Location:FABRICA ALGECIRAS
-2,425.00 €/ton
-Out of Stock</v>
+        <v xml:space="preserve">Acerinox Europa, 1.4301 304-Untrimmed, Coil, BA,
+0.40 x 941.0 x coil mm
+Weight (Kg):2,375
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,225.00 €/ton
+Add to cart</v>
       </c>
     </row>
     <row r="122" xml:space="preserve">
@@ -2335,7 +2335,7 @@
       <c r="B122" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4301 304-Untrimmed, Coil, BA,
 0.40 x 941.0 x coil mm
-Weight (Kg):2,375
+Weight (Kg):2,126
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -2346,12 +2346,12 @@
     <row r="123" xml:space="preserve">
       <c r="A123" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4301 304-Untrimmed, Coil, BA,
-0.40 x 941.0 x coil mm</v>
+0.40 x 943.0 x coil mm</v>
       </c>
       <c r="B123" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4301 304-Untrimmed, Coil, BA,
-0.40 x 941.0 x coil mm
-Weight (Kg):2,126
+0.40 x 943.0 x coil mm
+Weight (Kg):3,205
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -2367,11 +2367,11 @@
       <c r="B124" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4301 304-Untrimmed, Coil, BA,
 0.40 x 943.0 x coil mm
-Weight (Kg):3,205
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-2,225.00 €/ton
+Weight (Kg):2,585
+Quality:Prime
+Help
+Location:FABRICA ALGECIRAS
+2,425.00 €/ton
 Add to cart</v>
       </c>
     </row>
@@ -2383,23 +2383,23 @@
       <c r="B125" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4301 304-Untrimmed, Coil, BA,
 0.40 x 943.0 x coil mm
-Weight (Kg):2,585
-Quality:Prime
-Help
-Location:FABRICA ALGECIRAS
-2,425.00 €/ton
+Weight (Kg):3,349
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,225.00 €/ton
 Add to cart</v>
       </c>
     </row>
     <row r="126" xml:space="preserve">
       <c r="A126" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4301 304-Untrimmed, Coil, BA,
-0.40 x 943.0 x coil mm</v>
+0.60 x 1280.0 x coil mm</v>
       </c>
       <c r="B126" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4301 304-Untrimmed, Coil, BA,
-0.40 x 943.0 x coil mm
-Weight (Kg):3,349
+0.60 x 1280.0 x coil mm
+Weight (Kg):2,150
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -2410,12 +2410,12 @@
     <row r="127" xml:space="preserve">
       <c r="A127" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4301 304-Untrimmed, Coil, BA,
-0.60 x 1280.0 x coil mm</v>
+0.60 x 938.0 x coil mm</v>
       </c>
       <c r="B127" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4301 304-Untrimmed, Coil, BA,
-0.60 x 1280.0 x coil mm
-Weight (Kg):2,150
+0.60 x 938.0 x coil mm
+Weight (Kg):1,785
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -2426,12 +2426,12 @@
     <row r="128" xml:space="preserve">
       <c r="A128" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4301 304-Untrimmed, Coil, BA,
-0.60 x 938.0 x coil mm</v>
+0.70 x 1223.0 x coil mm</v>
       </c>
       <c r="B128" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4301 304-Untrimmed, Coil, BA,
-0.60 x 938.0 x coil mm
-Weight (Kg):1,785
+0.70 x 1223.0 x coil mm
+Weight (Kg):8,790
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -2442,12 +2442,12 @@
     <row r="129" xml:space="preserve">
       <c r="A129" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4301 304-Untrimmed, Coil, BA,
-0.70 x 1223.0 x coil mm</v>
+0.70 x 1273.0 x coil mm</v>
       </c>
       <c r="B129" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4301 304-Untrimmed, Coil, BA,
-0.70 x 1223.0 x coil mm
-Weight (Kg):8,790
+0.70 x 1273.0 x coil mm
+Weight (Kg):3,323
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -2458,25 +2458,9 @@
     <row r="130" xml:space="preserve">
       <c r="A130" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4301 304-Untrimmed, Coil, BA,
-0.70 x 1273.0 x coil mm</v>
+0.90 x 1245.0 x coil mm</v>
       </c>
       <c r="B130" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4301 304-Untrimmed, Coil, BA,
-0.70 x 1273.0 x coil mm
-Weight (Kg):3,323
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-2,225.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="131" xml:space="preserve">
-      <c r="A131" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4301 304-Untrimmed, Coil, BA,
-0.90 x 1245.0 x coil mm</v>
-      </c>
-      <c r="B131" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4301 304-Untrimmed, Coil, BA,
 0.90 x 1245.0 x coil mm
 Weight (Kg):2,372
@@ -2487,12 +2471,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="132" xml:space="preserve">
-      <c r="A132" t="str" xml:space="preserve">
+    <row r="131" xml:space="preserve">
+      <c r="A131" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4301 304-Untrimmed, Coil, SB-G-400,
 1.00 x 850.0 x coil mm</v>
       </c>
-      <c r="B132" t="str" xml:space="preserve">
+      <c r="B131" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4301 304-Untrimmed, Coil, SB-G-400,
 1.00 x 850.0 x coil mm
 Weight (Kg):5,870
@@ -2503,15 +2487,31 @@
 Add to cart</v>
       </c>
     </row>
+    <row r="132" xml:space="preserve">
+      <c r="A132" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4301 304DDQ-Coil, BA,
+0.70 x 1020.0 x coil mm</v>
+      </c>
+      <c r="B132" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4301 304DDQ-Coil, BA,
+0.70 x 1020.0 x coil mm
+Weight (Kg):7,100
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,225.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
     <row r="133" xml:space="preserve">
       <c r="A133" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4301 304DDQ-Coil, BA,
-0.70 x 1020.0 x coil mm</v>
+0.70 x 943.0 x coil mm</v>
       </c>
       <c r="B133" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4301 304DDQ-Coil, BA,
-0.70 x 1020.0 x coil mm
-Weight (Kg):7,100
+0.70 x 943.0 x coil mm
+Weight (Kg):16,790
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -2527,11 +2527,11 @@
       <c r="B134" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4301 304DDQ-Coil, BA,
 0.70 x 943.0 x coil mm
-Weight (Kg):16,790
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-2,225.00 €/ton
+Weight (Kg):16,740
+Quality:Prime
+Help
+Location:FABRICA ALGECIRAS
+2,900.00 €/ton
 Add to cart</v>
       </c>
     </row>
@@ -2543,11 +2543,11 @@
       <c r="B135" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4301 304DDQ-Coil, BA,
 0.70 x 943.0 x coil mm
-Weight (Kg):16,740
-Quality:Prime
-Help
-Location:FABRICA ALGECIRAS
-2,900.00 €/ton
+Weight (Kg):16,670
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,225.00 €/ton
 Add to cart</v>
       </c>
     </row>
@@ -2559,27 +2559,27 @@
       <c r="B136" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4301 304DDQ-Coil, BA,
 0.70 x 943.0 x coil mm
-Weight (Kg):16,670
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-2,225.00 €/ton
+Weight (Kg):16,680
+Quality:Prime
+Help
+Location:FABRICA ALGECIRAS
+2,900.00 €/ton
 Add to cart</v>
       </c>
     </row>
     <row r="137" xml:space="preserve">
       <c r="A137" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4301 304DDQ-Coil, BA,
-0.70 x 943.0 x coil mm</v>
+0.70 x 951.0 x coil mm</v>
       </c>
       <c r="B137" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4301 304DDQ-Coil, BA,
-0.70 x 943.0 x coil mm
-Weight (Kg):16,680
-Quality:Prime
-Help
-Location:FABRICA ALGECIRAS
-2,900.00 €/ton
+0.70 x 951.0 x coil mm
+Weight (Kg):3,561
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,225.00 €/ton
 Add to cart</v>
       </c>
     </row>
@@ -2591,11 +2591,11 @@
       <c r="B138" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4301 304DDQ-Coil, BA,
 0.70 x 951.0 x coil mm
-Weight (Kg):3,561
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-2,225.00 €/ton
+Weight (Kg):2,860
+Quality:Prime
+Help
+Location:FABRICA ALGECIRAS
+2,425.00 €/ton
 Add to cart</v>
       </c>
     </row>
@@ -2649,13 +2649,13 @@
     </row>
     <row r="142" xml:space="preserve">
       <c r="A142" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4301 304DDQ-Coil, BA,
-0.70 x 951.0 x coil mm</v>
+        <v xml:space="preserve">Acerinox Europa, 1.4306 304L-Coil, 2B,
+0.40 x 1270.0 x coil mm</v>
       </c>
       <c r="B142" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4301 304DDQ-Coil, BA,
-0.70 x 951.0 x coil mm
-Weight (Kg):2,860
+        <v xml:space="preserve">Acerinox Europa, 1.4306 304L-Coil, 2B,
+0.40 x 1270.0 x coil mm
+Weight (Kg):3,940
 Quality:Prime
 Help
 Location:FABRICA ALGECIRAS
@@ -2666,41 +2666,25 @@
     <row r="143" xml:space="preserve">
       <c r="A143" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4306 304L-Coil, 2B,
-0.40 x 1270.0 x coil mm</v>
+0.40 x 390.0 x coil mm</v>
       </c>
       <c r="B143" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4306 304L-Coil, 2B,
-0.40 x 1270.0 x coil mm
-Weight (Kg):3,940
-Quality:Prime
-Help
-Location:FABRICA ALGECIRAS
-2,425.00 €/ton
+0.40 x 390.0 x coil mm
+Weight (Kg):1,250
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,075.00 €/ton
 Add to cart</v>
       </c>
     </row>
     <row r="144" xml:space="preserve">
       <c r="A144" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4306 304L-Coil, 2B,
-0.40 x 390.0 x coil mm</v>
+0.90 x 1271.0 x coil mm</v>
       </c>
       <c r="B144" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4306 304L-Coil, 2B,
-0.40 x 390.0 x coil mm
-Weight (Kg):1,250
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-2,075.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="145" xml:space="preserve">
-      <c r="A145" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4306 304L-Coil, 2B,
-0.90 x 1271.0 x coil mm</v>
-      </c>
-      <c r="B145" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4306 304L-Coil, 2B,
 0.90 x 1271.0 x coil mm
 Weight (Kg):3,100
@@ -2711,12 +2695,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="146" xml:space="preserve">
-      <c r="A146" t="str" xml:space="preserve">
+    <row r="145" xml:space="preserve">
+      <c r="A145" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L-Sheet, SB-G-500,
 3.00 x 1500.0 x 3000.0 mm</v>
       </c>
-      <c r="B146" t="str" xml:space="preserve">
+      <c r="B145" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L-Sheet, SB-G-500,
 3.00 x 1500.0 x 3000.0 mm
 Weight (Kg):1,466
@@ -2727,15 +2711,31 @@
 Add to cart</v>
       </c>
     </row>
+    <row r="146" xml:space="preserve">
+      <c r="A146" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Coil, 2B,
+1.40 x 101.0 x coil mm</v>
+      </c>
+      <c r="B146" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Coil, 2B,
+1.40 x 101.0 x coil mm
+Weight (Kg):504
+Quality:Prime
+Help
+Location:FABRICA ALGECIRAS
+2,075.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
     <row r="147" xml:space="preserve">
       <c r="A147" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Coil, 2B,
-1.40 x 101.0 x coil mm</v>
+1.40 x 105.0 x coil mm</v>
       </c>
       <c r="B147" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Coil, 2B,
-1.40 x 101.0 x coil mm
-Weight (Kg):504
+1.40 x 105.0 x coil mm
+Weight (Kg):530
 Quality:Prime
 Help
 Location:FABRICA ALGECIRAS
@@ -2746,12 +2746,12 @@
     <row r="148" xml:space="preserve">
       <c r="A148" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Coil, 2B,
-1.40 x 105.0 x coil mm</v>
+1.40 x 110.9 x coil mm</v>
       </c>
       <c r="B148" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Coil, 2B,
-1.40 x 105.0 x coil mm
-Weight (Kg):530
+1.40 x 110.9 x coil mm
+Weight (Kg):616
 Quality:Prime
 Help
 Location:FABRICA ALGECIRAS
@@ -2762,64 +2762,64 @@
     <row r="149" xml:space="preserve">
       <c r="A149" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Coil, 2B,
-1.40 x 110.9 x coil mm</v>
+1.50 x 1289.0 x coil mm</v>
       </c>
       <c r="B149" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Coil, 2B,
-1.40 x 110.9 x coil mm
-Weight (Kg):616
-Quality:Prime
-Help
-Location:FABRICA ALGECIRAS
-2,075.00 €/ton
+1.50 x 1289.0 x coil mm
+Weight (Kg):3,070
+Quality:Prime
+Help
+Location:FABRICA ALGECIRAS
+2,425.00 €/ton
 Add to cart</v>
       </c>
     </row>
     <row r="150" xml:space="preserve">
       <c r="A150" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Coil, 2B,
-1.50 x 1289.0 x coil mm</v>
+1.80 x 102.0 x coil mm</v>
       </c>
       <c r="B150" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Coil, 2B,
-1.50 x 1289.0 x coil mm
-Weight (Kg):3,070
-Quality:Prime
-Help
-Location:FABRICA ALGECIRAS
-2,425.00 €/ton
+1.80 x 102.0 x coil mm
+Weight (Kg):794
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,075.00 €/ton
 Add to cart</v>
       </c>
     </row>
     <row r="151" xml:space="preserve">
       <c r="A151" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Coil, 2B,
-1.80 x 102.0 x coil mm</v>
+2.00 x 1277.0 x coil mm</v>
       </c>
       <c r="B151" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Coil, 2B,
-1.80 x 102.0 x coil mm
-Weight (Kg):794
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-2,075.00 €/ton
+2.00 x 1277.0 x coil mm
+Weight (Kg):2,940
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,225.00 €/ton
 Add to cart</v>
       </c>
     </row>
     <row r="152" xml:space="preserve">
       <c r="A152" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Coil, 2B,
-2.00 x 1277.0 x coil mm</v>
+2.00 x 553.0 x coil mm</v>
       </c>
       <c r="B152" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Coil, 2B,
-2.00 x 1277.0 x coil mm
-Weight (Kg):2,940
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-2,225.00 €/ton
+2.00 x 553.0 x coil mm
+Weight (Kg):385
+Quality:Downgraded
+Help
+Location:FABRICA ALGECIRAS
+2,025.00 €/ton
 Add to cart</v>
       </c>
     </row>
@@ -2842,44 +2842,44 @@
     <row r="154" xml:space="preserve">
       <c r="A154" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Coil, 2B,
-2.00 x 553.0 x coil mm</v>
+2.50 x 1000.0 x coil mm</v>
       </c>
       <c r="B154" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Coil, 2B,
-2.00 x 553.0 x coil mm
-Weight (Kg):385
-Quality:Downgraded
-Help
-Location:FABRICA ALGECIRAS
-2,025.00 €/ton
+2.50 x 1000.0 x coil mm
+Weight (Kg):2,280
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,225.00 €/ton
 Add to cart</v>
       </c>
     </row>
     <row r="155" xml:space="preserve">
       <c r="A155" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Coil, 2B,
-2.50 x 1000.0 x coil mm</v>
+5.00 x 265.9 x coil mm</v>
       </c>
       <c r="B155" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Coil, 2B,
-2.50 x 1000.0 x coil mm
-Weight (Kg):2,280
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-2,225.00 €/ton
+5.00 x 265.9 x coil mm
+Weight (Kg):1,596
+Quality:Prime
+Help
+Location:FABRICA ALGECIRAS
+2,075.00 €/ton
 Add to cart</v>
       </c>
     </row>
     <row r="156" xml:space="preserve">
       <c r="A156" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Coil, 2B,
-5.00 x 265.9 x coil mm</v>
+5.00 x 286.0 x coil mm</v>
       </c>
       <c r="B156" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Coil, 2B,
-5.00 x 265.9 x coil mm
-Weight (Kg):1,596
+5.00 x 286.0 x coil mm
+Weight (Kg):2,451
 Quality:Prime
 Help
 Location:FABRICA ALGECIRAS
@@ -2896,7 +2896,7 @@
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Coil, 2B,
 5.00 x 286.0 x coil mm
 Weight (Kg):2,451
-Quality:Prime
+Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
 2,075.00 €/ton
@@ -2906,16 +2906,16 @@
     <row r="158" xml:space="preserve">
       <c r="A158" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Coil, 2B,
-5.00 x 286.0 x coil mm</v>
+6.00 x 1500.0 x coil mm</v>
       </c>
       <c r="B158" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Coil, 2B,
-5.00 x 286.0 x coil mm
-Weight (Kg):2,451
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-2,075.00 €/ton
+6.00 x 1500.0 x coil mm
+Weight (Kg):1,700
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,225.00 €/ton
 Add to cart</v>
       </c>
     </row>
@@ -2927,7 +2927,7 @@
       <c r="B159" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Coil, 2B,
 6.00 x 1500.0 x coil mm
-Weight (Kg):1,700
+Weight (Kg):2,355
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -2943,7 +2943,7 @@
       <c r="B160" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Coil, 2B,
 6.00 x 1500.0 x coil mm
-Weight (Kg):2,355
+Weight (Kg):2,375
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -2959,7 +2959,7 @@
       <c r="B161" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Coil, 2B,
 6.00 x 1500.0 x coil mm
-Weight (Kg):2,375
+Weight (Kg):2,204
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -2991,7 +2991,7 @@
       <c r="B163" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Coil, 2B,
 6.00 x 1500.0 x coil mm
-Weight (Kg):2,204
+Weight (Kg):2,844
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -3002,41 +3002,25 @@
     <row r="164" xml:space="preserve">
       <c r="A164" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Coil, 2B,
-6.00 x 1500.0 x coil mm</v>
+6.00 x 220.0 x coil mm</v>
       </c>
       <c r="B164" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Coil, 2B,
-6.00 x 1500.0 x coil mm
-Weight (Kg):2,844
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-2,225.00 €/ton
+6.00 x 220.0 x coil mm
+Weight (Kg):4,046
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,075.00 €/ton
 Add to cart</v>
       </c>
     </row>
     <row r="165" xml:space="preserve">
       <c r="A165" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Coil, 2B,
-6.00 x 220.0 x coil mm</v>
+6.00 x 250.0 x coil mm</v>
       </c>
       <c r="B165" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Coil, 2B,
-6.00 x 220.0 x coil mm
-Weight (Kg):4,046
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-2,075.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="166" xml:space="preserve">
-      <c r="A166" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Coil, 2B,
-6.00 x 250.0 x coil mm</v>
-      </c>
-      <c r="B166" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Coil, 2B,
 6.00 x 250.0 x coil mm
 Weight (Kg):3,086
@@ -3047,12 +3031,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="167" xml:space="preserve">
-      <c r="A167" t="str" xml:space="preserve">
+    <row r="166" xml:space="preserve">
+      <c r="A166" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Coil, BA,
 0.70 x 1268.0 x coil mm</v>
       </c>
-      <c r="B167" t="str" xml:space="preserve">
+      <c r="B166" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Coil, BA,
 0.70 x 1268.0 x coil mm
 Weight (Kg):20,010
@@ -3063,28 +3047,28 @@
 Add to cart</v>
       </c>
     </row>
+    <row r="167" xml:space="preserve">
+      <c r="A167" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Coil, Emboss Skin,
+0.50 x 1250.0 x coil mm</v>
+      </c>
+      <c r="B167" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Coil, Emboss Skin,
+0.50 x 1250.0 x coil mm
+Weight (Kg):3,950
+Quality:Prime
+Help
+Location:FABRICA ALGECIRAS
+2,425.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
     <row r="168" xml:space="preserve">
       <c r="A168" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Coil, Emboss Skin,
-0.50 x 1250.0 x coil mm</v>
+0.50 x 1261.0 x coil mm</v>
       </c>
       <c r="B168" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Coil, Emboss Skin,
-0.50 x 1250.0 x coil mm
-Weight (Kg):3,950
-Quality:Prime
-Help
-Location:FABRICA ALGECIRAS
-2,425.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="169" xml:space="preserve">
-      <c r="A169" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Coil, Emboss Skin,
-0.50 x 1261.0 x coil mm</v>
-      </c>
-      <c r="B169" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Coil, Emboss Skin,
 0.50 x 1261.0 x coil mm
 Weight (Kg):10,590
@@ -3095,19 +3079,35 @@
 Add to cart</v>
       </c>
     </row>
+    <row r="169" xml:space="preserve">
+      <c r="A169" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Coil, Nb. 1,
+4.70 x 220.0 x coil mm</v>
+      </c>
+      <c r="B169" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Coil, Nb. 1,
+4.70 x 220.0 x coil mm
+Weight (Kg):3,704
+Quality:Prime
+Help
+Location:FABRICA ALGECIRAS
+1,975.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
     <row r="170" xml:space="preserve">
       <c r="A170" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Coil, Nb. 1,
-4.70 x 220.0 x coil mm</v>
+8.00 x 1500.0 x coil mm</v>
       </c>
       <c r="B170" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Coil, Nb. 1,
-4.70 x 220.0 x coil mm
-Weight (Kg):3,704
-Quality:Prime
-Help
-Location:FABRICA ALGECIRAS
-1,975.00 €/ton
+8.00 x 1500.0 x coil mm
+Weight (Kg):4,076
+Quality:Prime
+Help
+Location:FABRICA ALGECIRAS
+2,325.00 €/ton
 Add to cart</v>
       </c>
     </row>
@@ -3119,7 +3119,7 @@
       <c r="B171" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Coil, Nb. 1,
 8.00 x 1500.0 x coil mm
-Weight (Kg):4,076
+Weight (Kg):2,749
 Quality:Prime
 Help
 Location:FABRICA ALGECIRAS
@@ -3129,26 +3129,10 @@
     </row>
     <row r="172" xml:space="preserve">
       <c r="A172" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Coil, Nb. 1,
-8.00 x 1500.0 x coil mm</v>
-      </c>
-      <c r="B172" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Coil, Nb. 1,
-8.00 x 1500.0 x coil mm
-Weight (Kg):2,749
-Quality:Prime
-Help
-Location:FABRICA ALGECIRAS
-2,325.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="173" xml:space="preserve">
-      <c r="A173" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Coil, Nb. 2 Chequered,
 6.00 x 1250.0 x coil mm</v>
       </c>
-      <c r="B173" t="str" xml:space="preserve">
+      <c r="B172" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Coil, Nb. 2 Chequered,
 6.00 x 1250.0 x coil mm
 Weight (Kg):19,244
@@ -3159,12 +3143,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="174" xml:space="preserve">
-      <c r="A174" t="str" xml:space="preserve">
+    <row r="173" xml:space="preserve">
+      <c r="A173" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Coil, Nb. 3 Chequered,
 4.00 x 1548.0 x coil mm</v>
       </c>
-      <c r="B174" t="str" xml:space="preserve">
+      <c r="B173" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Coil, Nb. 3 Chequered,
 4.00 x 1548.0 x coil mm
 Weight (Kg):3,000
@@ -3175,28 +3159,28 @@
 Add to cart</v>
       </c>
     </row>
+    <row r="174" xml:space="preserve">
+      <c r="A174" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Coil, Polished N4-G-180,
+0.90 x 190.0 x coil mm</v>
+      </c>
+      <c r="B174" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Coil, Polished N4-G-180,
+0.90 x 190.0 x coil mm
+Weight (Kg):1,424
+Quality:Prime
+Help
+Location:FABRICA ALGECIRAS
+2,075.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
     <row r="175" xml:space="preserve">
       <c r="A175" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Coil, Polished N4-G-180,
-0.90 x 190.0 x coil mm</v>
+0.90 x 205.9 x coil mm</v>
       </c>
       <c r="B175" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Coil, Polished N4-G-180,
-0.90 x 190.0 x coil mm
-Weight (Kg):1,424
-Quality:Prime
-Help
-Location:FABRICA ALGECIRAS
-2,075.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="176" xml:space="preserve">
-      <c r="A176" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Coil, Polished N4-G-180,
-0.90 x 205.9 x coil mm</v>
-      </c>
-      <c r="B176" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Coil, Polished N4-G-180,
 0.90 x 205.9 x coil mm
 Weight (Kg):802
@@ -3207,12 +3191,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="177" xml:space="preserve">
-      <c r="A177" t="str" xml:space="preserve">
+    <row r="176" xml:space="preserve">
+      <c r="A176" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Coil, SB-G-400,
 1.00 x 154.9 x coil mm</v>
       </c>
-      <c r="B177" t="str" xml:space="preserve">
+      <c r="B176" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Coil, SB-G-400,
 1.00 x 154.9 x coil mm
 Weight (Kg):1,152
@@ -3223,15 +3207,31 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="178" xml:space="preserve">
-      <c r="A178" t="str" xml:space="preserve">
+    <row r="177" xml:space="preserve">
+      <c r="A177" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Coil, SB-G-500,
 0.90 x 1250.0 x coil mm</v>
       </c>
-      <c r="B178" t="str" xml:space="preserve">
+      <c r="B177" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Coil, SB-G-500,
 0.90 x 1250.0 x coil mm
 Weight (Kg):2,329
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,225.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="178" xml:space="preserve">
+      <c r="A178" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
+0.70 x 1500.0 x 3000.0 mm</v>
+      </c>
+      <c r="B178" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
+0.70 x 1500.0 x 3000.0 mm
+Weight (Kg):612
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -3295,7 +3295,7 @@
       <c r="B182" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 0.70 x 1500.0 x 3000.0 mm
-Weight (Kg):612
+Weight (Kg):702
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -3306,12 +3306,12 @@
     <row r="183" xml:space="preserve">
       <c r="A183" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
-0.70 x 1500.0 x 3000.0 mm</v>
+0.80 x 1000.0 x 2000.0 mm</v>
       </c>
       <c r="B183" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
-0.70 x 1500.0 x 3000.0 mm
-Weight (Kg):702
+0.80 x 1000.0 x 2000.0 mm
+Weight (Kg):580
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -3322,12 +3322,12 @@
     <row r="184" xml:space="preserve">
       <c r="A184" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
-0.80 x 1000.0 x 2000.0 mm</v>
+1.00 x 1500.0 x 3000.0 mm</v>
       </c>
       <c r="B184" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
-0.80 x 1000.0 x 2000.0 mm
-Weight (Kg):580
+1.00 x 1500.0 x 3000.0 mm
+Weight (Kg):659
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -3343,7 +3343,7 @@
       <c r="B185" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 1.00 x 1500.0 x 3000.0 mm
-Weight (Kg):659
+Weight (Kg):1,508
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -3359,7 +3359,7 @@
       <c r="B186" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 1.00 x 1500.0 x 3000.0 mm
-Weight (Kg):1,508
+Weight (Kg):1,921
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -3375,7 +3375,7 @@
       <c r="B187" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 1.00 x 1500.0 x 3000.0 mm
-Weight (Kg):1,921
+Weight (Kg):894
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -3391,7 +3391,7 @@
       <c r="B188" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 1.00 x 1500.0 x 3000.0 mm
-Weight (Kg):894
+Weight (Kg):700
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -3407,7 +3407,7 @@
       <c r="B189" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 1.00 x 1500.0 x 3000.0 mm
-Weight (Kg):700
+Weight (Kg):842
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -3418,12 +3418,12 @@
     <row r="190" xml:space="preserve">
       <c r="A190" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
-1.00 x 1500.0 x 3000.0 mm</v>
+2.00 x 1000.0 x 2000.0 mm</v>
       </c>
       <c r="B190" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
-1.00 x 1500.0 x 3000.0 mm
-Weight (Kg):842
+2.00 x 1000.0 x 2000.0 mm
+Weight (Kg):512
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -3439,7 +3439,7 @@
       <c r="B191" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 2.00 x 1000.0 x 2000.0 mm
-Weight (Kg):512
+Weight (Kg):949
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -3450,12 +3450,12 @@
     <row r="192" xml:space="preserve">
       <c r="A192" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
-2.00 x 1000.0 x 2000.0 mm</v>
+2.00 x 1250.0 x 2500.0 mm</v>
       </c>
       <c r="B192" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
-2.00 x 1000.0 x 2000.0 mm
-Weight (Kg):949
+2.00 x 1250.0 x 2500.0 mm
+Weight (Kg):777
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -3471,7 +3471,7 @@
       <c r="B193" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 2.00 x 1250.0 x 2500.0 mm
-Weight (Kg):777
+Weight (Kg):576
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -3487,7 +3487,7 @@
       <c r="B194" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 2.00 x 1250.0 x 2500.0 mm
-Weight (Kg):576
+Weight (Kg):622
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -3503,7 +3503,7 @@
       <c r="B195" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 2.00 x 1250.0 x 2500.0 mm
-Weight (Kg):622
+Weight (Kg):862
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -3519,7 +3519,7 @@
       <c r="B196" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 2.00 x 1250.0 x 2500.0 mm
-Weight (Kg):862
+Weight (Kg):619
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -3535,7 +3535,7 @@
       <c r="B197" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 2.00 x 1250.0 x 2500.0 mm
-Weight (Kg):619
+Weight (Kg):867
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -3551,7 +3551,7 @@
       <c r="B198" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 2.00 x 1250.0 x 2500.0 mm
-Weight (Kg):867
+Weight (Kg):774
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -3562,12 +3562,12 @@
     <row r="199" xml:space="preserve">
       <c r="A199" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
-2.00 x 1250.0 x 2500.0 mm</v>
+2.00 x 1250.0 x 3000.0 mm</v>
       </c>
       <c r="B199" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
-2.00 x 1250.0 x 2500.0 mm
-Weight (Kg):774
+2.00 x 1250.0 x 3000.0 mm
+Weight (Kg):877
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -3578,12 +3578,12 @@
     <row r="200" xml:space="preserve">
       <c r="A200" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
-2.00 x 1250.0 x 3000.0 mm</v>
+2.50 x 1000.0 x 2000.0 mm</v>
       </c>
       <c r="B200" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
-2.00 x 1250.0 x 3000.0 mm
-Weight (Kg):877
+2.50 x 1000.0 x 2000.0 mm
+Weight (Kg):781
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -3599,7 +3599,7 @@
       <c r="B201" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 2.50 x 1000.0 x 2000.0 mm
-Weight (Kg):781
+Weight (Kg):590
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -3610,12 +3610,12 @@
     <row r="202" xml:space="preserve">
       <c r="A202" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
-2.50 x 1000.0 x 2000.0 mm</v>
+2.50 x 1250.0 x 2500.0 mm</v>
       </c>
       <c r="B202" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
-2.50 x 1000.0 x 2000.0 mm
-Weight (Kg):590
+2.50 x 1250.0 x 2500.0 mm
+Weight (Kg):660
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -3631,7 +3631,7 @@
       <c r="B203" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 2.50 x 1250.0 x 2500.0 mm
-Weight (Kg):660
+Weight (Kg):852
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -3642,12 +3642,12 @@
     <row r="204" xml:space="preserve">
       <c r="A204" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
-2.50 x 1250.0 x 2500.0 mm</v>
+2.50 x 1500.0 x 3000.0 mm</v>
       </c>
       <c r="B204" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
-2.50 x 1250.0 x 2500.0 mm
-Weight (Kg):852
+2.50 x 1500.0 x 3000.0 mm
+Weight (Kg):605
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -3663,7 +3663,7 @@
       <c r="B205" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 2.50 x 1500.0 x 3000.0 mm
-Weight (Kg):605
+Weight (Kg):521
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -3679,7 +3679,7 @@
       <c r="B206" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 2.50 x 1500.0 x 3000.0 mm
-Weight (Kg):521
+Weight (Kg):527
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -3695,7 +3695,7 @@
       <c r="B207" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 2.50 x 1500.0 x 3000.0 mm
-Weight (Kg):527
+Weight (Kg):862
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -3706,12 +3706,12 @@
     <row r="208" xml:space="preserve">
       <c r="A208" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
-2.50 x 1500.0 x 3000.0 mm</v>
+3.00 x 1000.0 x 2000.0 mm</v>
       </c>
       <c r="B208" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
-2.50 x 1500.0 x 3000.0 mm
-Weight (Kg):862
+3.00 x 1000.0 x 2000.0 mm
+Weight (Kg):1,038
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -3727,7 +3727,7 @@
       <c r="B209" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 3.00 x 1000.0 x 2000.0 mm
-Weight (Kg):1,038
+Weight (Kg):946
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -3743,7 +3743,7 @@
       <c r="B210" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 3.00 x 1000.0 x 2000.0 mm
-Weight (Kg):946
+Weight (Kg):503
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -3759,7 +3759,7 @@
       <c r="B211" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 3.00 x 1000.0 x 2000.0 mm
-Weight (Kg):503
+Weight (Kg):880
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -3775,7 +3775,7 @@
       <c r="B212" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 3.00 x 1000.0 x 2000.0 mm
-Weight (Kg):880
+Weight (Kg):796
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -3791,7 +3791,7 @@
       <c r="B213" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 3.00 x 1000.0 x 2000.0 mm
-Weight (Kg):796
+Weight (Kg):578
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -3807,7 +3807,7 @@
       <c r="B214" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 3.00 x 1000.0 x 2000.0 mm
-Weight (Kg):578
+Weight (Kg):1,506
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -3823,7 +3823,7 @@
       <c r="B215" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 3.00 x 1000.0 x 2000.0 mm
-Weight (Kg):1,506
+Weight (Kg):1,538
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -3839,7 +3839,7 @@
       <c r="B216" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 3.00 x 1000.0 x 2000.0 mm
-Weight (Kg):1,538
+Weight (Kg):520
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -3850,12 +3850,12 @@
     <row r="217" xml:space="preserve">
       <c r="A217" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
-3.00 x 1000.0 x 2000.0 mm</v>
+3.00 x 1250.0 x 2500.0 mm</v>
       </c>
       <c r="B217" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
-3.00 x 1000.0 x 2000.0 mm
-Weight (Kg):520
+3.00 x 1250.0 x 2500.0 mm
+Weight (Kg):812
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -3871,7 +3871,7 @@
       <c r="B218" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 3.00 x 1250.0 x 2500.0 mm
-Weight (Kg):812
+Weight (Kg):816
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -3887,7 +3887,7 @@
       <c r="B219" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 3.00 x 1250.0 x 2500.0 mm
-Weight (Kg):816
+Weight (Kg):1,320
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -3903,7 +3903,7 @@
       <c r="B220" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 3.00 x 1250.0 x 2500.0 mm
-Weight (Kg):1,320
+Weight (Kg):830
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -3919,7 +3919,7 @@
       <c r="B221" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 3.00 x 1250.0 x 2500.0 mm
-Weight (Kg):830
+Weight (Kg):1,446
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -3935,7 +3935,7 @@
       <c r="B222" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 3.00 x 1250.0 x 2500.0 mm
-Weight (Kg):1,446
+Weight (Kg):670
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -3951,7 +3951,7 @@
       <c r="B223" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 3.00 x 1250.0 x 2500.0 mm
-Weight (Kg):670
+Weight (Kg):884
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -3967,7 +3967,7 @@
       <c r="B224" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 3.00 x 1250.0 x 2500.0 mm
-Weight (Kg):884
+Weight (Kg):762
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -3978,12 +3978,12 @@
     <row r="225" xml:space="preserve">
       <c r="A225" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
-3.00 x 1250.0 x 2500.0 mm</v>
+5.00 x 1250.0 x 2500.0 mm</v>
       </c>
       <c r="B225" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
-3.00 x 1250.0 x 2500.0 mm
-Weight (Kg):762
+5.00 x 1250.0 x 2500.0 mm
+Weight (Kg):750
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -3994,12 +3994,12 @@
     <row r="226" xml:space="preserve">
       <c r="A226" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
-5.00 x 1250.0 x 2500.0 mm</v>
+5.00 x 1500.0 x 3000.0 mm</v>
       </c>
       <c r="B226" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
-5.00 x 1250.0 x 2500.0 mm
-Weight (Kg):750
+5.00 x 1500.0 x 3000.0 mm
+Weight (Kg):1,760
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -4015,7 +4015,7 @@
       <c r="B227" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 5.00 x 1500.0 x 3000.0 mm
-Weight (Kg):1,760
+Weight (Kg):1,976
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -4031,7 +4031,7 @@
       <c r="B228" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 5.00 x 1500.0 x 3000.0 mm
-Weight (Kg):1,976
+Weight (Kg):1,236
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -4047,7 +4047,7 @@
       <c r="B229" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 5.00 x 1500.0 x 3000.0 mm
-Weight (Kg):1,236
+Weight (Kg):1,968
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -4063,7 +4063,7 @@
       <c r="B230" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 5.00 x 1500.0 x 3000.0 mm
-Weight (Kg):1,968
+Weight (Kg):1,240
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -4079,7 +4079,7 @@
       <c r="B231" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 5.00 x 1500.0 x 3000.0 mm
-Weight (Kg):1,240
+Weight (Kg):1,070
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -4095,7 +4095,7 @@
       <c r="B232" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 5.00 x 1500.0 x 3000.0 mm
-Weight (Kg):1,070
+Weight (Kg):1,960
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -4111,7 +4111,7 @@
       <c r="B233" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 5.00 x 1500.0 x 3000.0 mm
-Weight (Kg):1,960
+Weight (Kg):1,734
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -4127,7 +4127,7 @@
       <c r="B234" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 5.00 x 1500.0 x 3000.0 mm
-Weight (Kg):1,734
+Weight (Kg):1,874
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -4143,7 +4143,7 @@
       <c r="B235" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 5.00 x 1500.0 x 3000.0 mm
-Weight (Kg):1,874
+Weight (Kg):884
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -4159,7 +4159,7 @@
       <c r="B236" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 5.00 x 1500.0 x 3000.0 mm
-Weight (Kg):884
+Weight (Kg):1,578
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -4175,7 +4175,7 @@
       <c r="B237" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 5.00 x 1500.0 x 3000.0 mm
-Weight (Kg):1,578
+Weight (Kg):852
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -4191,7 +4191,7 @@
       <c r="B238" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 5.00 x 1500.0 x 3000.0 mm
-Weight (Kg):852
+Weight (Kg):1,942
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -4202,12 +4202,12 @@
     <row r="239" xml:space="preserve">
       <c r="A239" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
-5.00 x 1500.0 x 3000.0 mm</v>
+6.00 x 1000.0 x 2000.0 mm</v>
       </c>
       <c r="B239" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
-5.00 x 1500.0 x 3000.0 mm
-Weight (Kg):1,942
+6.00 x 1000.0 x 2000.0 mm
+Weight (Kg):1,906
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -4223,7 +4223,7 @@
       <c r="B240" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 6.00 x 1000.0 x 2000.0 mm
-Weight (Kg):1,906
+Weight (Kg):1,886
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -4239,7 +4239,7 @@
       <c r="B241" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 6.00 x 1000.0 x 2000.0 mm
-Weight (Kg):1,886
+Weight (Kg):1,414
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -4255,7 +4255,7 @@
       <c r="B242" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 6.00 x 1000.0 x 2000.0 mm
-Weight (Kg):1,414
+Weight (Kg):1,620
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -4271,7 +4271,7 @@
       <c r="B243" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 6.00 x 1000.0 x 2000.0 mm
-Weight (Kg):1,620
+Weight (Kg):938
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -4287,7 +4287,7 @@
       <c r="B244" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 6.00 x 1000.0 x 2000.0 mm
-Weight (Kg):938
+Weight (Kg):1,406
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -4303,7 +4303,7 @@
       <c r="B245" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 6.00 x 1000.0 x 2000.0 mm
-Weight (Kg):1,406
+Weight (Kg):1,140
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -4314,12 +4314,12 @@
     <row r="246" xml:space="preserve">
       <c r="A246" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
-6.00 x 1000.0 x 2000.0 mm</v>
+6.00 x 1250.0 x 2500.0 mm</v>
       </c>
       <c r="B246" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
-6.00 x 1000.0 x 2000.0 mm
-Weight (Kg):1,140
+6.00 x 1250.0 x 2500.0 mm
+Weight (Kg):1,652
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -4335,7 +4335,7 @@
       <c r="B247" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 6.00 x 1250.0 x 2500.0 mm
-Weight (Kg):1,652
+Weight (Kg):1,610
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -4351,7 +4351,7 @@
       <c r="B248" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 6.00 x 1250.0 x 2500.0 mm
-Weight (Kg):1,610
+Weight (Kg):1,900
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -4367,7 +4367,7 @@
       <c r="B249" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 6.00 x 1250.0 x 2500.0 mm
-Weight (Kg):1,900
+Weight (Kg):2,346
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -4383,7 +4383,7 @@
       <c r="B250" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 6.00 x 1250.0 x 2500.0 mm
-Weight (Kg):2,346
+Weight (Kg):1,624
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -4394,12 +4394,12 @@
     <row r="251" xml:space="preserve">
       <c r="A251" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
-6.00 x 1250.0 x 2500.0 mm</v>
+6.00 x 1500.0 x 3000.0 mm</v>
       </c>
       <c r="B251" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
-6.00 x 1250.0 x 2500.0 mm
-Weight (Kg):1,624
+6.00 x 1500.0 x 3000.0 mm
+Weight (Kg):1,062
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -4415,7 +4415,7 @@
       <c r="B252" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 6.00 x 1500.0 x 3000.0 mm
-Weight (Kg):1,062
+Weight (Kg):1,966
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -4431,7 +4431,7 @@
       <c r="B253" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 6.00 x 1500.0 x 3000.0 mm
-Weight (Kg):1,966
+Weight (Kg):1,496
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -4447,7 +4447,7 @@
       <c r="B254" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 6.00 x 1500.0 x 3000.0 mm
-Weight (Kg):1,496
+Weight (Kg):1,320
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -4463,7 +4463,7 @@
       <c r="B255" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 6.00 x 1500.0 x 3000.0 mm
-Weight (Kg):1,320
+Weight (Kg):1,071
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -4479,7 +4479,7 @@
       <c r="B256" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 6.00 x 1500.0 x 3000.0 mm
-Weight (Kg):1,071
+Weight (Kg):1,264
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -4495,7 +4495,7 @@
       <c r="B257" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 6.00 x 1500.0 x 3000.0 mm
-Weight (Kg):1,264
+Weight (Kg):1,916
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -4511,7 +4511,7 @@
       <c r="B258" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 6.00 x 1500.0 x 3000.0 mm
-Weight (Kg):1,916
+Weight (Kg):1,908
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -4527,7 +4527,7 @@
       <c r="B259" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 6.00 x 1500.0 x 3000.0 mm
-Weight (Kg):1,908
+Weight (Kg):1,928
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -4543,7 +4543,7 @@
       <c r="B260" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 6.00 x 1500.0 x 3000.0 mm
-Weight (Kg):1,928
+Weight (Kg):1,290
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -4559,7 +4559,7 @@
       <c r="B261" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 6.00 x 1500.0 x 3000.0 mm
-Weight (Kg):1,290
+Weight (Kg):1,698
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -4575,7 +4575,7 @@
       <c r="B262" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 6.00 x 1500.0 x 3000.0 mm
-Weight (Kg):1,698
+Weight (Kg):1,754
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -4591,7 +4591,7 @@
       <c r="B263" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 6.00 x 1500.0 x 3000.0 mm
-Weight (Kg):1,754
+Weight (Kg):1,716
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -4607,7 +4607,7 @@
       <c r="B264" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 6.00 x 1500.0 x 3000.0 mm
-Weight (Kg):1,716
+Weight (Kg):1,548
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -4623,7 +4623,7 @@
       <c r="B265" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 6.00 x 1500.0 x 3000.0 mm
-Weight (Kg):1,548
+Weight (Kg):1,916
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -4639,7 +4639,7 @@
       <c r="B266" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 6.00 x 1500.0 x 3000.0 mm
-Weight (Kg):1,916
+Weight (Kg):1,485
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -4655,7 +4655,7 @@
       <c r="B267" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 6.00 x 1500.0 x 3000.0 mm
-Weight (Kg):1,485
+Weight (Kg):1,940
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -4671,7 +4671,7 @@
       <c r="B268" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 6.00 x 1500.0 x 3000.0 mm
-Weight (Kg):1,940
+Weight (Kg):1,762
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -4687,7 +4687,7 @@
       <c r="B269" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 6.00 x 1500.0 x 3000.0 mm
-Weight (Kg):1,762
+Weight (Kg):1,918
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -4703,7 +4703,7 @@
       <c r="B270" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 6.00 x 1500.0 x 3000.0 mm
-Weight (Kg):1,918
+Weight (Kg):1,306
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -4719,7 +4719,7 @@
       <c r="B271" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 6.00 x 1500.0 x 3000.0 mm
-Weight (Kg):1,306
+Weight (Kg):1,066
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -4735,7 +4735,7 @@
       <c r="B272" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 6.00 x 1500.0 x 3000.0 mm
-Weight (Kg):1,066
+Weight (Kg):1,936
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -4751,7 +4751,7 @@
       <c r="B273" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 6.00 x 1500.0 x 3000.0 mm
-Weight (Kg):1,936
+Weight (Kg):2,390
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -4767,7 +4767,7 @@
       <c r="B274" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 6.00 x 1500.0 x 3000.0 mm
-Weight (Kg):2,390
+Weight (Kg):1,728
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -4783,7 +4783,7 @@
       <c r="B275" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 6.00 x 1500.0 x 3000.0 mm
-Weight (Kg):1,728
+Weight (Kg):1,514
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -4799,7 +4799,7 @@
       <c r="B276" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 6.00 x 1500.0 x 3000.0 mm
-Weight (Kg):1,514
+Weight (Kg):1,922
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -4815,7 +4815,7 @@
       <c r="B277" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 6.00 x 1500.0 x 3000.0 mm
-Weight (Kg):1,922
+Weight (Kg):1,942
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -4831,7 +4831,7 @@
       <c r="B278" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 6.00 x 1500.0 x 3000.0 mm
-Weight (Kg):1,942
+Weight (Kg):2,114
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -4847,7 +4847,7 @@
       <c r="B279" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 6.00 x 1500.0 x 3000.0 mm
-Weight (Kg):2,114
+Weight (Kg):1,088
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -4863,7 +4863,7 @@
       <c r="B280" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 6.00 x 1500.0 x 3000.0 mm
-Weight (Kg):1,088
+Weight (Kg):1,274
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -4879,7 +4879,7 @@
       <c r="B281" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 6.00 x 1500.0 x 3000.0 mm
-Weight (Kg):1,274
+Weight (Kg):1,718
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -4895,7 +4895,7 @@
       <c r="B282" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 6.00 x 1500.0 x 3000.0 mm
-Weight (Kg):1,718
+Weight (Kg):1,922
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -4911,7 +4911,7 @@
       <c r="B283" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 6.00 x 1500.0 x 3000.0 mm
-Weight (Kg):1,922
+Weight (Kg):1,878
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -4927,7 +4927,7 @@
       <c r="B284" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 6.00 x 1500.0 x 3000.0 mm
-Weight (Kg):1,878
+Weight (Kg):1,714
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -4943,7 +4943,7 @@
       <c r="B285" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 6.00 x 1500.0 x 3000.0 mm
-Weight (Kg):1,714
+Weight (Kg):1,918
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -4959,7 +4959,7 @@
       <c r="B286" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 6.00 x 1500.0 x 3000.0 mm
-Weight (Kg):1,918
+Weight (Kg):1,754
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -4975,7 +4975,7 @@
       <c r="B287" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 6.00 x 1500.0 x 3000.0 mm
-Weight (Kg):1,754
+Weight (Kg):1,528
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -4991,7 +4991,7 @@
       <c r="B288" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 6.00 x 1500.0 x 3000.0 mm
-Weight (Kg):1,528
+Weight (Kg):2,136
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -5007,7 +5007,7 @@
       <c r="B289" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 6.00 x 1500.0 x 3000.0 mm
-Weight (Kg):2,136
+Weight (Kg):1,946
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -5017,13 +5017,13 @@
     </row>
     <row r="290" xml:space="preserve">
       <c r="A290" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
-6.00 x 1500.0 x 3000.0 mm</v>
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, BA,
+0.80 x 1000.0 x 2000.0 mm</v>
       </c>
       <c r="B290" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
-6.00 x 1500.0 x 3000.0 mm
-Weight (Kg):1,946
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, BA,
+0.80 x 1000.0 x 2000.0 mm
+Weight (Kg):1,633
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -5039,7 +5039,7 @@
       <c r="B291" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, BA,
 0.80 x 1000.0 x 2000.0 mm
-Weight (Kg):1,633
+Weight (Kg):1,286
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -5055,7 +5055,7 @@
       <c r="B292" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, BA,
 0.80 x 1000.0 x 2000.0 mm
-Weight (Kg):1,286
+Weight (Kg):727
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -5066,12 +5066,12 @@
     <row r="293" xml:space="preserve">
       <c r="A293" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, BA,
-0.80 x 1000.0 x 2000.0 mm</v>
+1.00 x 1000.0 x 2000.0 mm</v>
       </c>
       <c r="B293" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, BA,
-0.80 x 1000.0 x 2000.0 mm
-Weight (Kg):727
+1.00 x 1000.0 x 2000.0 mm
+Weight (Kg):650
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -5087,7 +5087,7 @@
       <c r="B294" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, BA,
 1.00 x 1000.0 x 2000.0 mm
-Weight (Kg):650
+Weight (Kg):869
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -5103,7 +5103,7 @@
       <c r="B295" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, BA,
 1.00 x 1000.0 x 2000.0 mm
-Weight (Kg):869
+Weight (Kg):885
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -5119,7 +5119,7 @@
       <c r="B296" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, BA,
 1.00 x 1000.0 x 2000.0 mm
-Weight (Kg):885
+Weight (Kg):931
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -5130,12 +5130,12 @@
     <row r="297" xml:space="preserve">
       <c r="A297" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, BA,
-1.00 x 1000.0 x 2000.0 mm</v>
+1.00 x 1250.0 x 3000.0 mm</v>
       </c>
       <c r="B297" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, BA,
-1.00 x 1000.0 x 2000.0 mm
-Weight (Kg):931
+1.00 x 1250.0 x 3000.0 mm
+Weight (Kg):766
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -5151,7 +5151,7 @@
       <c r="B298" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, BA,
 1.00 x 1250.0 x 3000.0 mm
-Weight (Kg):766
+Weight (Kg):1,417
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -5162,12 +5162,12 @@
     <row r="299" xml:space="preserve">
       <c r="A299" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, BA,
-1.00 x 1250.0 x 3000.0 mm</v>
+1.50 x 1000.0 x 2000.0 mm</v>
       </c>
       <c r="B299" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, BA,
-1.00 x 1250.0 x 3000.0 mm
-Weight (Kg):1,417
+1.50 x 1000.0 x 2000.0 mm
+Weight (Kg):1,459
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -5183,7 +5183,7 @@
       <c r="B300" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, BA,
 1.50 x 1000.0 x 2000.0 mm
-Weight (Kg):1,459
+Weight (Kg):825
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -5199,7 +5199,7 @@
       <c r="B301" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, BA,
 1.50 x 1000.0 x 2000.0 mm
-Weight (Kg):825
+Weight (Kg):738
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -5215,7 +5215,7 @@
       <c r="B302" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, BA,
 1.50 x 1000.0 x 2000.0 mm
-Weight (Kg):738
+Weight (Kg):886
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -5231,7 +5231,7 @@
       <c r="B303" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, BA,
 1.50 x 1000.0 x 2000.0 mm
-Weight (Kg):886
+Weight (Kg):1,116
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -5247,7 +5247,7 @@
       <c r="B304" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, BA,
 1.50 x 1000.0 x 2000.0 mm
-Weight (Kg):1,116
+Weight (Kg):692
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -5263,7 +5263,7 @@
       <c r="B305" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, BA,
 1.50 x 1000.0 x 2000.0 mm
-Weight (Kg):692
+Weight (Kg):1,613
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -5279,7 +5279,7 @@
       <c r="B306" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, BA,
 1.50 x 1000.0 x 2000.0 mm
-Weight (Kg):1,613
+Weight (Kg):946
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -5290,12 +5290,12 @@
     <row r="307" xml:space="preserve">
       <c r="A307" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, BA,
-1.50 x 1000.0 x 2000.0 mm</v>
+1.50 x 1250.0 x 2500.0 mm</v>
       </c>
       <c r="B307" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, BA,
-1.50 x 1000.0 x 2000.0 mm
-Weight (Kg):946
+1.50 x 1250.0 x 2500.0 mm
+Weight (Kg):1,628
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -5306,25 +5306,9 @@
     <row r="308" xml:space="preserve">
       <c r="A308" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, BA,
-1.50 x 1250.0 x 2500.0 mm</v>
+1.80 x 1000.0 x 2000.0 mm</v>
       </c>
       <c r="B308" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, BA,
-1.50 x 1250.0 x 2500.0 mm
-Weight (Kg):1,628
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-2,225.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="309" xml:space="preserve">
-      <c r="A309" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, BA,
-1.80 x 1000.0 x 2000.0 mm</v>
-      </c>
-      <c r="B309" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, BA,
 1.80 x 1000.0 x 2000.0 mm
 Weight (Kg):1,405
@@ -5332,6 +5316,22 @@
 Help
 Location:FABRICA ALGECIRAS
 2,225.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="309" xml:space="preserve">
+      <c r="A309" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, Nb. 3 Chequered,
+4.50 x 1250.0 x 3000.0 mm</v>
+      </c>
+      <c r="B309" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, Nb. 3 Chequered,
+4.50 x 1250.0 x 3000.0 mm
+Weight (Kg):1,046
+Quality:Prime
+Help
+Location:FABRICA ALGECIRAS
+2,900.00 €/ton
 Add to cart</v>
       </c>
     </row>
@@ -5343,7 +5343,7 @@
       <c r="B310" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, Nb. 3 Chequered,
 4.50 x 1250.0 x 3000.0 mm
-Weight (Kg):1,046
+Weight (Kg):1,316
 Quality:Prime
 Help
 Location:FABRICA ALGECIRAS
@@ -5353,29 +5353,29 @@
     </row>
     <row r="311" xml:space="preserve">
       <c r="A311" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, Nb. 3 Chequered,
-4.50 x 1250.0 x 3000.0 mm</v>
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, Polished N4-G-240,
+0.80 x 1500.0 x 3000.0 mm</v>
       </c>
       <c r="B311" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, Nb. 3 Chequered,
-4.50 x 1250.0 x 3000.0 mm
-Weight (Kg):1,316
-Quality:Prime
-Help
-Location:FABRICA ALGECIRAS
-2,900.00 €/ton
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, Polished N4-G-240,
+0.80 x 1500.0 x 3000.0 mm
+Weight (Kg):630
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,225.00 €/ton
 Add to cart</v>
       </c>
     </row>
     <row r="312" xml:space="preserve">
       <c r="A312" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, Polished N4-G-240,
-0.80 x 1500.0 x 3000.0 mm</v>
+0.90 x 1500.0 x 3000.0 mm</v>
       </c>
       <c r="B312" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, Polished N4-G-240,
-0.80 x 1500.0 x 3000.0 mm
-Weight (Kg):630
+0.90 x 1500.0 x 3000.0 mm
+Weight (Kg):807
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -5391,7 +5391,7 @@
       <c r="B313" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, Polished N4-G-240,
 0.90 x 1500.0 x 3000.0 mm
-Weight (Kg):807
+Weight (Kg):622
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -5401,13 +5401,13 @@
     </row>
     <row r="314" xml:space="preserve">
       <c r="A314" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, Polished N4-G-240,
-0.90 x 1500.0 x 3000.0 mm</v>
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, SB-G-400,
+1.50 x 1000.0 x 2000.0 mm</v>
       </c>
       <c r="B314" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, Polished N4-G-240,
-0.90 x 1500.0 x 3000.0 mm
-Weight (Kg):622
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, SB-G-400,
+1.50 x 1000.0 x 2000.0 mm
+Weight (Kg):674
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -5423,7 +5423,7 @@
       <c r="B315" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, SB-G-400,
 1.50 x 1000.0 x 2000.0 mm
-Weight (Kg):674
+Weight (Kg):535
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -5433,13 +5433,13 @@
     </row>
     <row r="316" xml:space="preserve">
       <c r="A316" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, SB-G-400,
-1.50 x 1000.0 x 2000.0 mm</v>
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, SB-G-500,
+0.70 x 1500.0 x 3000.0 mm</v>
       </c>
       <c r="B316" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, SB-G-400,
-1.50 x 1000.0 x 2000.0 mm
-Weight (Kg):535
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, SB-G-500,
+0.70 x 1500.0 x 3000.0 mm
+Weight (Kg):1,226
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -5455,7 +5455,7 @@
       <c r="B317" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, SB-G-500,
 0.70 x 1500.0 x 3000.0 mm
-Weight (Kg):1,226
+Weight (Kg):1,001
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -5471,7 +5471,7 @@
       <c r="B318" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, SB-G-500,
 0.70 x 1500.0 x 3000.0 mm
-Weight (Kg):1,001
+Weight (Kg):681
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -5487,7 +5487,7 @@
       <c r="B319" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, SB-G-500,
 0.70 x 1500.0 x 3000.0 mm
-Weight (Kg):681
+Weight (Kg):673
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -5503,7 +5503,7 @@
       <c r="B320" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, SB-G-500,
 0.70 x 1500.0 x 3000.0 mm
-Weight (Kg):673
+Weight (Kg):722
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -5530,12 +5530,12 @@
     <row r="322" xml:space="preserve">
       <c r="A322" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, SB-G-500,
-0.70 x 1500.0 x 3000.0 mm</v>
+0.80 x 1000.0 x 2000.0 mm</v>
       </c>
       <c r="B322" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, SB-G-500,
-0.70 x 1500.0 x 3000.0 mm
-Weight (Kg):722
+0.80 x 1000.0 x 2000.0 mm
+Weight (Kg):1,256
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -5546,12 +5546,12 @@
     <row r="323" xml:space="preserve">
       <c r="A323" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, SB-G-500,
-0.80 x 1000.0 x 2000.0 mm</v>
+0.80 x 1250.0 x 3000.0 mm</v>
       </c>
       <c r="B323" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, SB-G-500,
-0.80 x 1000.0 x 2000.0 mm
-Weight (Kg):1,256
+0.80 x 1250.0 x 3000.0 mm
+Weight (Kg):535
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -5562,25 +5562,9 @@
     <row r="324" xml:space="preserve">
       <c r="A324" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, SB-G-500,
-0.80 x 1250.0 x 3000.0 mm</v>
+3.00 x 1500.0 x 3000.0 mm</v>
       </c>
       <c r="B324" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, SB-G-500,
-0.80 x 1250.0 x 3000.0 mm
-Weight (Kg):535
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-2,225.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="325" xml:space="preserve">
-      <c r="A325" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, SB-G-500,
-3.00 x 1500.0 x 3000.0 mm</v>
-      </c>
-      <c r="B325" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, SB-G-500,
 3.00 x 1500.0 x 3000.0 mm
 Weight (Kg):839
@@ -5591,12 +5575,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="326" xml:space="preserve">
-      <c r="A326" t="str" xml:space="preserve">
+    <row r="325" xml:space="preserve">
+      <c r="A325" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Untrimmed, Coil,
 0.80 x 1271.0 x coil mm</v>
       </c>
-      <c r="B326" t="str" xml:space="preserve">
+      <c r="B325" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Untrimmed, Coil,
 0.80 x 1271.0 x coil mm
 Weight (Kg):2,950
@@ -5607,15 +5591,31 @@
 Add to cart</v>
       </c>
     </row>
+    <row r="326" xml:space="preserve">
+      <c r="A326" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Untrimmed, Coil, 2B,
+1.20 x 1277.0 x coil mm</v>
+      </c>
+      <c r="B326" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Untrimmed, Coil, 2B,
+1.20 x 1277.0 x coil mm
+Weight (Kg):2,230
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,225.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
     <row r="327" xml:space="preserve">
       <c r="A327" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Untrimmed, Coil, 2B,
-1.20 x 1277.0 x coil mm</v>
+2.00 x 1275.0 x coil mm</v>
       </c>
       <c r="B327" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Untrimmed, Coil, 2B,
-1.20 x 1277.0 x coil mm
-Weight (Kg):2,230
+2.00 x 1275.0 x coil mm
+Weight (Kg):2,619
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -5626,25 +5626,9 @@
     <row r="328" xml:space="preserve">
       <c r="A328" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Untrimmed, Coil, 2B,
-2.00 x 1275.0 x coil mm</v>
+5.00 x 1540.0 x coil mm</v>
       </c>
       <c r="B328" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Untrimmed, Coil, 2B,
-2.00 x 1275.0 x coil mm
-Weight (Kg):2,619
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-2,225.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="329" xml:space="preserve">
-      <c r="A329" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Untrimmed, Coil, 2B,
-5.00 x 1540.0 x coil mm</v>
-      </c>
-      <c r="B329" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Untrimmed, Coil, 2B,
 5.00 x 1540.0 x coil mm
 Weight (Kg):13,250
@@ -5655,12 +5639,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="330" xml:space="preserve">
-      <c r="A330" t="str" xml:space="preserve">
+    <row r="329" xml:space="preserve">
+      <c r="A329" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Untrimmed, Coil, 2D,
 1.00 x 1027.0 x coil mm</v>
       </c>
-      <c r="B330" t="str" xml:space="preserve">
+      <c r="B329" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Untrimmed, Coil, 2D,
 1.00 x 1027.0 x coil mm
 Weight (Kg):2,410
@@ -5671,44 +5655,44 @@
 Add to cart</v>
       </c>
     </row>
+    <row r="330" xml:space="preserve">
+      <c r="A330" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Untrimmed, Coil, BA,
+0.40 x 1017.0 x coil mm</v>
+      </c>
+      <c r="B330" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Untrimmed, Coil, BA,
+0.40 x 1017.0 x coil mm
+Weight (Kg):5,705
+Quality:Prime
+Help
+Location:FABRICA ALGECIRAS
+2,425.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
     <row r="331" xml:space="preserve">
       <c r="A331" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Untrimmed, Coil, BA,
-0.40 x 1017.0 x coil mm</v>
+0.90 x 1275.0 x coil mm</v>
       </c>
       <c r="B331" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Untrimmed, Coil, BA,
-0.40 x 1017.0 x coil mm
-Weight (Kg):5,705
-Quality:Prime
-Help
-Location:FABRICA ALGECIRAS
-2,425.00 €/ton
+0.90 x 1275.0 x coil mm
+Weight (Kg):2,500
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,225.00 €/ton
 Add to cart</v>
       </c>
     </row>
     <row r="332" xml:space="preserve">
       <c r="A332" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Untrimmed, Coil, BA,
-0.90 x 1275.0 x coil mm</v>
+0.90 x 1288.0 x coil mm</v>
       </c>
       <c r="B332" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Untrimmed, Coil, BA,
-0.90 x 1275.0 x coil mm
-Weight (Kg):2,500
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-2,225.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="333" xml:space="preserve">
-      <c r="A333" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Untrimmed, Coil, BA,
-0.90 x 1288.0 x coil mm</v>
-      </c>
-      <c r="B333" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Untrimmed, Coil, BA,
 0.90 x 1288.0 x coil mm
 Weight (Kg):7,960
@@ -5719,12 +5703,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="334" xml:space="preserve">
-      <c r="A334" t="str" xml:space="preserve">
+    <row r="333" xml:space="preserve">
+      <c r="A333" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Untrimmed, Coil, SB-G-400,
 1.20 x 1500.0 x coil mm</v>
       </c>
-      <c r="B334" t="str" xml:space="preserve">
+      <c r="B333" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Untrimmed, Coil, SB-G-400,
 1.20 x 1500.0 x coil mm
 Weight (Kg):2,640
@@ -5735,67 +5719,83 @@
 Add to cart</v>
       </c>
     </row>
+    <row r="334" xml:space="preserve">
+      <c r="A334" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Coil, 2B,
+1.20 x 1536.0 x coil mm</v>
+      </c>
+      <c r="B334" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Coil, 2B,
+1.20 x 1536.0 x coil mm
+Weight (Kg):1,260
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+3,395.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
     <row r="335" xml:space="preserve">
       <c r="A335" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Coil, 2B,
-1.20 x 1536.0 x coil mm</v>
+1.50 x 140.0 x coil mm</v>
       </c>
       <c r="B335" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Coil, 2B,
-1.20 x 1536.0 x coil mm
-Weight (Kg):1,260
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-3,395.00 €/ton
+1.50 x 140.0 x coil mm
+Weight (Kg):758
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+3,270.00 €/ton
 Add to cart</v>
       </c>
     </row>
     <row r="336" xml:space="preserve">
       <c r="A336" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Coil, 2B,
-1.50 x 140.0 x coil mm</v>
+2.00 x 1498.0 x coil mm</v>
       </c>
       <c r="B336" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Coil, 2B,
-1.50 x 140.0 x coil mm
-Weight (Kg):758
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-3,270.00 €/ton
+2.00 x 1498.0 x coil mm
+Weight (Kg):2,770
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+3,395.00 €/ton
 Add to cart</v>
       </c>
     </row>
     <row r="337" xml:space="preserve">
       <c r="A337" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Coil, 2B,
-2.00 x 1498.0 x coil mm</v>
+5.00 x 1250.0 x coil mm</v>
       </c>
       <c r="B337" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Coil, 2B,
-2.00 x 1498.0 x coil mm
-Weight (Kg):2,770
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-3,395.00 €/ton
+5.00 x 1250.0 x coil mm
+Weight (Kg):12,055
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+3,375.00 €/ton
 Add to cart</v>
       </c>
     </row>
     <row r="338" xml:space="preserve">
       <c r="A338" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Coil, 2B,
-5.00 x 1250.0 x coil mm</v>
+5.00 x 240.0 x coil mm</v>
       </c>
       <c r="B338" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Coil, 2B,
-5.00 x 1250.0 x coil mm
-Weight (Kg):12,055
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-3,375.00 €/ton
+5.00 x 240.0 x coil mm
+Weight (Kg):2,314
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+3,270.00 €/ton
 Add to cart</v>
       </c>
     </row>
@@ -5855,7 +5855,7 @@
       <c r="B342" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Coil, 2B,
 5.00 x 240.0 x coil mm
-Weight (Kg):2,314
+Weight (Kg):2,237
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -5866,32 +5866,32 @@
     <row r="343" xml:space="preserve">
       <c r="A343" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Coil, 2B,
-5.00 x 240.0 x coil mm</v>
+6.00 x 1500.0 x coil mm</v>
       </c>
       <c r="B343" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Coil, 2B,
-5.00 x 240.0 x coil mm
-Weight (Kg):2,237
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-3,270.00 €/ton
+6.00 x 1500.0 x coil mm
+Weight (Kg):2,016
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+3,395.00 €/ton
 Add to cart</v>
       </c>
     </row>
     <row r="344" xml:space="preserve">
       <c r="A344" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Coil, 2B,
-6.00 x 1500.0 x coil mm</v>
+6.00 x 250.9 x coil mm</v>
       </c>
       <c r="B344" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Coil, 2B,
-6.00 x 1500.0 x coil mm
-Weight (Kg):2,016
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-3,395.00 €/ton
+6.00 x 250.9 x coil mm
+Weight (Kg):548
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+3,270.00 €/ton
 Add to cart</v>
       </c>
     </row>
@@ -5903,7 +5903,7 @@
       <c r="B345" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Coil, 2B,
 6.00 x 250.9 x coil mm
-Weight (Kg):548
+Weight (Kg):1,880
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -5913,13 +5913,13 @@
     </row>
     <row r="346" xml:space="preserve">
       <c r="A346" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Coil, 2B,
-6.00 x 250.9 x coil mm</v>
+        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Coil, 2D,
+3.30 x 112.0 x coil mm</v>
       </c>
       <c r="B346" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Coil, 2B,
-6.00 x 250.9 x coil mm
-Weight (Kg):1,880
+        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Coil, 2D,
+3.30 x 112.0 x coil mm
+Weight (Kg):1,017
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -5935,8 +5935,8 @@
       <c r="B347" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Coil, 2D,
 3.30 x 112.0 x coil mm
-Weight (Kg):1,017
-Quality:Prime-2
+Weight (Kg):878
+Quality:Prime
 Help
 Location:FABRICA ALGECIRAS
 3,270.00 €/ton
@@ -5946,13 +5946,13 @@
     <row r="348" xml:space="preserve">
       <c r="A348" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Coil, 2D,
-3.30 x 112.0 x coil mm</v>
+3.30 x 449.0 x coil mm</v>
       </c>
       <c r="B348" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Coil, 2D,
-3.30 x 112.0 x coil mm
-Weight (Kg):878
-Quality:Prime
+3.30 x 449.0 x coil mm
+Weight (Kg):1,850
+Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
 3,270.00 €/ton
@@ -5967,7 +5967,7 @@
       <c r="B349" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Coil, 2D,
 3.30 x 449.0 x coil mm
-Weight (Kg):1,850
+Weight (Kg):1,854
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -5977,14 +5977,14 @@
     </row>
     <row r="350" xml:space="preserve">
       <c r="A350" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Coil, 2D,
-3.30 x 449.0 x coil mm</v>
+        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Coil, BA,
+0.40 x 295.9 x coil mm</v>
       </c>
       <c r="B350" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Coil, 2D,
-3.30 x 449.0 x coil mm
-Weight (Kg):1,854
-Quality:Prime-2
+        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Coil, BA,
+0.40 x 295.9 x coil mm
+Weight (Kg):662
+Quality:Prime
 Help
 Location:FABRICA ALGECIRAS
 3,270.00 €/ton
@@ -5999,7 +5999,7 @@
       <c r="B351" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Coil, BA,
 0.40 x 295.9 x coil mm
-Weight (Kg):662
+Weight (Kg):650
 Quality:Prime
 Help
 Location:FABRICA ALGECIRAS
@@ -6010,25 +6010,9 @@
     <row r="352" xml:space="preserve">
       <c r="A352" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Coil, BA,
-0.40 x 295.9 x coil mm</v>
+0.50 x 160.0 x coil mm</v>
       </c>
       <c r="B352" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Coil, BA,
-0.40 x 295.9 x coil mm
-Weight (Kg):650
-Quality:Prime
-Help
-Location:FABRICA ALGECIRAS
-3,270.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="353" xml:space="preserve">
-      <c r="A353" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Coil, BA,
-0.50 x 160.0 x coil mm</v>
-      </c>
-      <c r="B353" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Coil, BA,
 0.50 x 160.0 x coil mm
 Weight (Kg):1,066
@@ -6036,6 +6020,22 @@
 Help
 Location:FABRICA ALGECIRAS
 3,270.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="353" xml:space="preserve">
+      <c r="A353" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Coil, Nb. 1,
+4.10 x 150.0 x coil mm</v>
+      </c>
+      <c r="B353" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Coil, Nb. 1,
+4.10 x 150.0 x coil mm
+Weight (Kg):1,593
+Quality:Prime
+Help
+Location:FABRICA ALGECIRAS
+3,170.00 €/ton
 Add to cart</v>
       </c>
     </row>
@@ -6047,7 +6047,7 @@
       <c r="B354" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Coil, Nb. 1,
 4.10 x 150.0 x coil mm
-Weight (Kg):1,593
+Weight (Kg):1,438
 Quality:Prime
 Help
 Location:FABRICA ALGECIRAS
@@ -6058,25 +6058,9 @@
     <row r="355" xml:space="preserve">
       <c r="A355" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Coil, Nb. 1,
-4.10 x 150.0 x coil mm</v>
+4.50 x 220.0 x coil mm</v>
       </c>
       <c r="B355" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Coil, Nb. 1,
-4.10 x 150.0 x coil mm
-Weight (Kg):1,438
-Quality:Prime
-Help
-Location:FABRICA ALGECIRAS
-3,170.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="356" xml:space="preserve">
-      <c r="A356" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Coil, Nb. 1,
-4.50 x 220.0 x coil mm</v>
-      </c>
-      <c r="B356" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Coil, Nb. 1,
 4.50 x 220.0 x coil mm
 Weight (Kg):3,869
@@ -6087,12 +6071,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="357" xml:space="preserve">
-      <c r="A357" t="str" xml:space="preserve">
+    <row r="356" xml:space="preserve">
+      <c r="A356" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Coil, SB-G-400,
 1.00 x 250.9 x coil mm</v>
       </c>
-      <c r="B357" t="str" xml:space="preserve">
+      <c r="B356" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Coil, SB-G-400,
 1.00 x 250.9 x coil mm
 Weight (Kg):1,428
@@ -6103,15 +6087,31 @@
 Add to cart</v>
       </c>
     </row>
+    <row r="357" xml:space="preserve">
+      <c r="A357" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
+0.70 x 1250.0 x 2500.0 mm</v>
+      </c>
+      <c r="B357" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
+0.70 x 1250.0 x 2500.0 mm
+Weight (Kg):1,756
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+3,395.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
     <row r="358" xml:space="preserve">
       <c r="A358" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
-0.70 x 1250.0 x 2500.0 mm</v>
+0.80 x 1250.0 x 3000.0 mm</v>
       </c>
       <c r="B358" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
-0.70 x 1250.0 x 2500.0 mm
-Weight (Kg):1,756
+0.80 x 1250.0 x 3000.0 mm
+Weight (Kg):695
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -6122,12 +6122,12 @@
     <row r="359" xml:space="preserve">
       <c r="A359" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
-0.80 x 1250.0 x 3000.0 mm</v>
+0.80 x 1500.0 x 3000.0 mm</v>
       </c>
       <c r="B359" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
-0.80 x 1250.0 x 3000.0 mm
-Weight (Kg):695
+0.80 x 1500.0 x 3000.0 mm
+Weight (Kg):978
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -6143,7 +6143,7 @@
       <c r="B360" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
 0.80 x 1500.0 x 3000.0 mm
-Weight (Kg):978
+Weight (Kg):1,741
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -6159,7 +6159,7 @@
       <c r="B361" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
 0.80 x 1500.0 x 3000.0 mm
-Weight (Kg):1,741
+Weight (Kg):803
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -6175,7 +6175,7 @@
       <c r="B362" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
 0.80 x 1500.0 x 3000.0 mm
-Weight (Kg):803
+Weight (Kg):1,136
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -6186,12 +6186,12 @@
     <row r="363" xml:space="preserve">
       <c r="A363" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
-0.80 x 1500.0 x 3000.0 mm</v>
+0.90 x 1000.0 x 2000.0 mm</v>
       </c>
       <c r="B363" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
-0.80 x 1500.0 x 3000.0 mm
-Weight (Kg):1,136
+0.90 x 1000.0 x 2000.0 mm
+Weight (Kg):576
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -6202,12 +6202,12 @@
     <row r="364" xml:space="preserve">
       <c r="A364" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
-0.90 x 1000.0 x 2000.0 mm</v>
+0.90 x 1500.0 x 3000.0 mm</v>
       </c>
       <c r="B364" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
-0.90 x 1000.0 x 2000.0 mm
-Weight (Kg):576
+0.90 x 1500.0 x 3000.0 mm
+Weight (Kg):553
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -6218,12 +6218,12 @@
     <row r="365" xml:space="preserve">
       <c r="A365" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
-0.90 x 1500.0 x 3000.0 mm</v>
+1.10 x 1500.0 x 3000.0 mm</v>
       </c>
       <c r="B365" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
-0.90 x 1500.0 x 3000.0 mm
-Weight (Kg):553
+1.10 x 1500.0 x 3000.0 mm
+Weight (Kg):1,233
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -6234,12 +6234,12 @@
     <row r="366" xml:space="preserve">
       <c r="A366" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
-1.10 x 1500.0 x 3000.0 mm</v>
+1.20 x 1250.0 x 2500.0 mm</v>
       </c>
       <c r="B366" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
-1.10 x 1500.0 x 3000.0 mm
-Weight (Kg):1,233
+1.20 x 1250.0 x 2500.0 mm
+Weight (Kg):685
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -6250,12 +6250,12 @@
     <row r="367" xml:space="preserve">
       <c r="A367" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
-1.20 x 1250.0 x 2500.0 mm</v>
+1.50 x 1000.0 x 2000.0 mm</v>
       </c>
       <c r="B367" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
-1.20 x 1250.0 x 2500.0 mm
-Weight (Kg):685
+1.50 x 1000.0 x 2000.0 mm
+Weight (Kg):598
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -6266,12 +6266,12 @@
     <row r="368" xml:space="preserve">
       <c r="A368" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
-1.50 x 1000.0 x 2000.0 mm</v>
+2.00 x 1000.0 x 2000.0 mm</v>
       </c>
       <c r="B368" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
-1.50 x 1000.0 x 2000.0 mm
-Weight (Kg):598
+2.00 x 1000.0 x 2000.0 mm
+Weight (Kg):2,359
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -6287,7 +6287,7 @@
       <c r="B369" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
 2.00 x 1000.0 x 2000.0 mm
-Weight (Kg):2,359
+Weight (Kg):529
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -6303,7 +6303,7 @@
       <c r="B370" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
 2.00 x 1000.0 x 2000.0 mm
-Weight (Kg):529
+Weight (Kg):889
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -6319,7 +6319,7 @@
       <c r="B371" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
 2.00 x 1000.0 x 2000.0 mm
-Weight (Kg):889
+Weight (Kg):628
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -6335,7 +6335,7 @@
       <c r="B372" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
 2.00 x 1000.0 x 2000.0 mm
-Weight (Kg):628
+Weight (Kg):1,968
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -6346,12 +6346,12 @@
     <row r="373" xml:space="preserve">
       <c r="A373" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
-2.00 x 1000.0 x 2000.0 mm</v>
+2.00 x 1250.0 x 2500.0 mm</v>
       </c>
       <c r="B373" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
-2.00 x 1000.0 x 2000.0 mm
-Weight (Kg):1,968
+2.00 x 1250.0 x 2500.0 mm
+Weight (Kg):928
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -6367,7 +6367,7 @@
       <c r="B374" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
 2.00 x 1250.0 x 2500.0 mm
-Weight (Kg):928
+Weight (Kg):816
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -6383,7 +6383,7 @@
       <c r="B375" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
 2.00 x 1250.0 x 2500.0 mm
-Weight (Kg):816
+Weight (Kg):976
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -6399,7 +6399,7 @@
       <c r="B376" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
 2.00 x 1250.0 x 2500.0 mm
-Weight (Kg):976
+Weight (Kg):585
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -6415,7 +6415,7 @@
       <c r="B377" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
 2.00 x 1250.0 x 2500.0 mm
-Weight (Kg):585
+Weight (Kg):1,956
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -6431,7 +6431,7 @@
       <c r="B378" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
 2.00 x 1250.0 x 2500.0 mm
-Weight (Kg):1,956
+Weight (Kg):1,779
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -6442,12 +6442,12 @@
     <row r="379" xml:space="preserve">
       <c r="A379" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
-2.00 x 1250.0 x 2500.0 mm</v>
+2.00 x 1500.0 x 3000.0 mm</v>
       </c>
       <c r="B379" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
-2.00 x 1250.0 x 2500.0 mm
-Weight (Kg):1,779
+2.00 x 1500.0 x 3000.0 mm
+Weight (Kg):693
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -6463,7 +6463,7 @@
       <c r="B380" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
 2.00 x 1500.0 x 3000.0 mm
-Weight (Kg):693
+Weight (Kg):1,122
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -6479,7 +6479,7 @@
       <c r="B381" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
 2.00 x 1500.0 x 3000.0 mm
-Weight (Kg):1,122
+Weight (Kg):1,108
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -6495,7 +6495,7 @@
       <c r="B382" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
 2.00 x 1500.0 x 3000.0 mm
-Weight (Kg):1,108
+Weight (Kg):1,836
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -6511,7 +6511,7 @@
       <c r="B383" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
 2.00 x 1500.0 x 3000.0 mm
-Weight (Kg):1,836
+Weight (Kg):630
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -6527,7 +6527,7 @@
       <c r="B384" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
 2.00 x 1500.0 x 3000.0 mm
-Weight (Kg):630
+Weight (Kg):726
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -6543,7 +6543,7 @@
       <c r="B385" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
 2.00 x 1500.0 x 3000.0 mm
-Weight (Kg):726
+Weight (Kg):565
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -6559,7 +6559,7 @@
       <c r="B386" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
 2.00 x 1500.0 x 3000.0 mm
-Weight (Kg):565
+Weight (Kg):729
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -6575,7 +6575,7 @@
       <c r="B387" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
 2.00 x 1500.0 x 3000.0 mm
-Weight (Kg):729
+Weight (Kg):792
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -6591,7 +6591,7 @@
       <c r="B388" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
 2.00 x 1500.0 x 3000.0 mm
-Weight (Kg):792
+Weight (Kg):637
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -6607,7 +6607,7 @@
       <c r="B389" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
 2.00 x 1500.0 x 3000.0 mm
-Weight (Kg):637
+Weight (Kg):1,289
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -6618,12 +6618,12 @@
     <row r="390" xml:space="preserve">
       <c r="A390" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
-2.00 x 1500.0 x 3000.0 mm</v>
+2.50 x 1500.0 x 3000.0 mm</v>
       </c>
       <c r="B390" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
-2.00 x 1500.0 x 3000.0 mm
-Weight (Kg):1,289
+2.50 x 1500.0 x 3000.0 mm
+Weight (Kg):1,826
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -6639,7 +6639,7 @@
       <c r="B391" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
 2.50 x 1500.0 x 3000.0 mm
-Weight (Kg):1,826
+Weight (Kg):1,040
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -6655,7 +6655,7 @@
       <c r="B392" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
 2.50 x 1500.0 x 3000.0 mm
-Weight (Kg):1,040
+Weight (Kg):1,328
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -6666,12 +6666,12 @@
     <row r="393" xml:space="preserve">
       <c r="A393" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
-2.50 x 1500.0 x 3000.0 mm</v>
+3.00 x 1000.0 x 2000.0 mm</v>
       </c>
       <c r="B393" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
-2.50 x 1500.0 x 3000.0 mm
-Weight (Kg):1,328
+3.00 x 1000.0 x 2000.0 mm
+Weight (Kg):940
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -6682,12 +6682,12 @@
     <row r="394" xml:space="preserve">
       <c r="A394" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
-3.00 x 1000.0 x 2000.0 mm</v>
+3.00 x 1250.0 x 2500.0 mm</v>
       </c>
       <c r="B394" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
-3.00 x 1000.0 x 2000.0 mm
-Weight (Kg):940
+3.00 x 1250.0 x 2500.0 mm
+Weight (Kg):1,396
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -6703,7 +6703,7 @@
       <c r="B395" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
 3.00 x 1250.0 x 2500.0 mm
-Weight (Kg):1,396
+Weight (Kg):2,318
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -6719,7 +6719,7 @@
       <c r="B396" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
 3.00 x 1250.0 x 2500.0 mm
-Weight (Kg):2,318
+Weight (Kg):1,074
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -6735,7 +6735,7 @@
       <c r="B397" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
 3.00 x 1250.0 x 2500.0 mm
-Weight (Kg):1,074
+Weight (Kg):1,584
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -6751,7 +6751,7 @@
       <c r="B398" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
 3.00 x 1250.0 x 2500.0 mm
-Weight (Kg):1,584
+Weight (Kg):1,028
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -6767,7 +6767,7 @@
       <c r="B399" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
 3.00 x 1250.0 x 2500.0 mm
-Weight (Kg):1,028
+Weight (Kg):598
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -6778,12 +6778,12 @@
     <row r="400" xml:space="preserve">
       <c r="A400" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
-3.00 x 1250.0 x 2500.0 mm</v>
+3.00 x 1340.0 x 2480.0 mm</v>
       </c>
       <c r="B400" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
-3.00 x 1250.0 x 2500.0 mm
-Weight (Kg):598
+3.00 x 1340.0 x 2480.0 mm
+Weight (Kg):1,174
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -6799,7 +6799,7 @@
       <c r="B401" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
 3.00 x 1340.0 x 2480.0 mm
-Weight (Kg):1,174
+Weight (Kg):1,020
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -6815,7 +6815,7 @@
       <c r="B402" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
 3.00 x 1340.0 x 2480.0 mm
-Weight (Kg):1,020
+Weight (Kg):1,169
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -6831,7 +6831,7 @@
       <c r="B403" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
 3.00 x 1340.0 x 2480.0 mm
-Weight (Kg):1,169
+Weight (Kg):1,951
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -6842,12 +6842,12 @@
     <row r="404" xml:space="preserve">
       <c r="A404" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
-3.00 x 1340.0 x 2480.0 mm</v>
+5.00 x 1000.0 x 2000.0 mm</v>
       </c>
       <c r="B404" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
-3.00 x 1340.0 x 2480.0 mm
-Weight (Kg):1,951
+5.00 x 1000.0 x 2000.0 mm
+Weight (Kg):1,588
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -6858,12 +6858,12 @@
     <row r="405" xml:space="preserve">
       <c r="A405" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
-5.00 x 1000.0 x 2000.0 mm</v>
+5.00 x 1250.0 x 2500.0 mm</v>
       </c>
       <c r="B405" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
-5.00 x 1000.0 x 2000.0 mm
-Weight (Kg):1,588
+5.00 x 1250.0 x 2500.0 mm
+Weight (Kg):742
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -6874,12 +6874,12 @@
     <row r="406" xml:space="preserve">
       <c r="A406" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
-5.00 x 1250.0 x 2500.0 mm</v>
+6.00 x 1000.0 x 2000.0 mm</v>
       </c>
       <c r="B406" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
-5.00 x 1250.0 x 2500.0 mm
-Weight (Kg):742
+6.00 x 1000.0 x 2000.0 mm
+Weight (Kg):1,624
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -6895,7 +6895,7 @@
       <c r="B407" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
 6.00 x 1000.0 x 2000.0 mm
-Weight (Kg):1,624
+Weight (Kg):1,434
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -6911,7 +6911,7 @@
       <c r="B408" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
 6.00 x 1000.0 x 2000.0 mm
-Weight (Kg):1,434
+Weight (Kg):580
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -6927,7 +6927,7 @@
       <c r="B409" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
 6.00 x 1000.0 x 2000.0 mm
-Weight (Kg):580
+Weight (Kg):1,054
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -6943,7 +6943,7 @@
       <c r="B410" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
 6.00 x 1000.0 x 2000.0 mm
-Weight (Kg):1,054
+Weight (Kg):1,716
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -6959,7 +6959,7 @@
       <c r="B411" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
 6.00 x 1000.0 x 2000.0 mm
-Weight (Kg):1,716
+Weight (Kg):1,148
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -6975,7 +6975,7 @@
       <c r="B412" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
 6.00 x 1000.0 x 2000.0 mm
-Weight (Kg):1,148
+Weight (Kg):960
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -6991,7 +6991,7 @@
       <c r="B413" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
 6.00 x 1000.0 x 2000.0 mm
-Weight (Kg):960
+Weight (Kg):772
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -7002,12 +7002,12 @@
     <row r="414" xml:space="preserve">
       <c r="A414" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
-6.00 x 1000.0 x 2000.0 mm</v>
+6.00 x 1500.0 x 3000.0 mm</v>
       </c>
       <c r="B414" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
-6.00 x 1000.0 x 2000.0 mm
-Weight (Kg):772
+6.00 x 1500.0 x 3000.0 mm
+Weight (Kg):2,146
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -7023,7 +7023,7 @@
       <c r="B415" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
 6.00 x 1500.0 x 3000.0 mm
-Weight (Kg):2,146
+Weight (Kg):1,994
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -7039,7 +7039,7 @@
       <c r="B416" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
 6.00 x 1500.0 x 3000.0 mm
-Weight (Kg):1,994
+Weight (Kg):1,488
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -7055,7 +7055,7 @@
       <c r="B417" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
 6.00 x 1500.0 x 3000.0 mm
-Weight (Kg):1,488
+Weight (Kg):1,278
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -7071,7 +7071,7 @@
       <c r="B418" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
 6.00 x 1500.0 x 3000.0 mm
-Weight (Kg):1,278
+Weight (Kg):1,062
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -7087,7 +7087,7 @@
       <c r="B419" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
 6.00 x 1500.0 x 3000.0 mm
-Weight (Kg):1,062
+Weight (Kg):1,526
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -7103,7 +7103,7 @@
       <c r="B420" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
 6.00 x 1500.0 x 3000.0 mm
-Weight (Kg):1,526
+Weight (Kg):1,280
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -7114,12 +7114,12 @@
     <row r="421" xml:space="preserve">
       <c r="A421" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
-6.00 x 1500.0 x 3000.0 mm</v>
+6.00 x 1510.0 x 3010.0 mm</v>
       </c>
       <c r="B421" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
-6.00 x 1500.0 x 3000.0 mm
-Weight (Kg):1,280
+6.00 x 1510.0 x 3010.0 mm
+Weight (Kg):1,986
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -7135,7 +7135,7 @@
       <c r="B422" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
 6.00 x 1510.0 x 3010.0 mm
-Weight (Kg):1,986
+Weight (Kg):1,784
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -7145,26 +7145,10 @@
     </row>
     <row r="423" xml:space="preserve">
       <c r="A423" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
-6.00 x 1510.0 x 3010.0 mm</v>
-      </c>
-      <c r="B423" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
-6.00 x 1510.0 x 3010.0 mm
-Weight (Kg):1,784
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-3,395.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="424" xml:space="preserve">
-      <c r="A424" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, Nb. 1,
 6.00 x 1000.0 x 2000.0 mm</v>
       </c>
-      <c r="B424" t="str" xml:space="preserve">
+      <c r="B423" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, Nb. 1,
 6.00 x 1000.0 x 2000.0 mm
 Weight (Kg):570
@@ -7175,15 +7159,31 @@
 Add to cart</v>
       </c>
     </row>
+    <row r="424" xml:space="preserve">
+      <c r="A424" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, SB-G-400,
+1.50 x 1500.0 x 3000.0 mm</v>
+      </c>
+      <c r="B424" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, SB-G-400,
+1.50 x 1500.0 x 3000.0 mm
+Weight (Kg):723
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+3,395.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
     <row r="425" xml:space="preserve">
       <c r="A425" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, SB-G-400,
-1.50 x 1500.0 x 3000.0 mm</v>
+2.00 x 1500.0 x 3000.0 mm</v>
       </c>
       <c r="B425" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, SB-G-400,
-1.50 x 1500.0 x 3000.0 mm
-Weight (Kg):723
+2.00 x 1500.0 x 3000.0 mm
+Weight (Kg):819
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -7199,7 +7199,7 @@
       <c r="B426" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, SB-G-400,
 2.00 x 1500.0 x 3000.0 mm
-Weight (Kg):819
+Weight (Kg):1,935
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -7209,13 +7209,13 @@
     </row>
     <row r="427" xml:space="preserve">
       <c r="A427" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, SB-G-400,
-2.00 x 1500.0 x 3000.0 mm</v>
+        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Untrimmed, Coil, 2B,
+1.20 x 1537.0 x coil mm</v>
       </c>
       <c r="B427" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, SB-G-400,
-2.00 x 1500.0 x 3000.0 mm
-Weight (Kg):1,935
+        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Untrimmed, Coil, 2B,
+1.20 x 1537.0 x coil mm
+Weight (Kg):2,125
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -7226,12 +7226,12 @@
     <row r="428" xml:space="preserve">
       <c r="A428" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Untrimmed, Coil, 2B,
-1.20 x 1537.0 x coil mm</v>
+1.80 x 1530.0 x coil mm</v>
       </c>
       <c r="B428" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Untrimmed, Coil, 2B,
-1.20 x 1537.0 x coil mm
-Weight (Kg):2,125
+1.80 x 1530.0 x coil mm
+Weight (Kg):5,263
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -7242,12 +7242,12 @@
     <row r="429" xml:space="preserve">
       <c r="A429" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Untrimmed, Coil, 2B,
-1.80 x 1530.0 x coil mm</v>
+1.80 x 1535.0 x coil mm</v>
       </c>
       <c r="B429" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Untrimmed, Coil, 2B,
-1.80 x 1530.0 x coil mm
-Weight (Kg):5,263
+1.80 x 1535.0 x coil mm
+Weight (Kg):2,726
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -7258,57 +7258,41 @@
     <row r="430" xml:space="preserve">
       <c r="A430" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Untrimmed, Coil, 2B,
-1.80 x 1535.0 x coil mm</v>
+2.00 x 1023.0 x coil mm</v>
       </c>
       <c r="B430" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Untrimmed, Coil, 2B,
-1.80 x 1535.0 x coil mm
-Weight (Kg):2,726
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-3,395.00 €/ton
+2.00 x 1023.0 x coil mm
+Weight (Kg):1,825
+Quality:Prime
+Help
+Location:FABRICA ALGECIRAS
+3,595.00 €/ton
 Add to cart</v>
       </c>
     </row>
     <row r="431" xml:space="preserve">
       <c r="A431" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Untrimmed, Coil, 2B,
-2.00 x 1023.0 x coil mm</v>
+3.00 x 1552.0 x coil mm</v>
       </c>
       <c r="B431" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Untrimmed, Coil, 2B,
-2.00 x 1023.0 x coil mm
-Weight (Kg):1,825
-Quality:Prime
-Help
-Location:FABRICA ALGECIRAS
-3,595.00 €/ton
+3.00 x 1552.0 x coil mm
+Weight (Kg):2,868
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+3,395.00 €/ton
 Add to cart</v>
       </c>
     </row>
     <row r="432" xml:space="preserve">
       <c r="A432" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Untrimmed, Coil, 2B,
-3.00 x 1552.0 x coil mm</v>
+6.00 x 1030.0 x coil mm</v>
       </c>
       <c r="B432" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Untrimmed, Coil, 2B,
-3.00 x 1552.0 x coil mm
-Weight (Kg):2,868
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-3,395.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="433" xml:space="preserve">
-      <c r="A433" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Untrimmed, Coil, 2B,
-6.00 x 1030.0 x coil mm</v>
-      </c>
-      <c r="B433" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Untrimmed, Coil, 2B,
 6.00 x 1030.0 x coil mm
 Weight (Kg):2,225
@@ -7319,12 +7303,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="434" xml:space="preserve">
-      <c r="A434" t="str" xml:space="preserve">
+    <row r="433" xml:space="preserve">
+      <c r="A433" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4571 316Ti-Coil, 2B,
 4.00 x 210.0 x coil mm</v>
       </c>
-      <c r="B434" t="str" xml:space="preserve">
+      <c r="B433" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4571 316Ti-Coil, 2B,
 4.00 x 210.0 x coil mm
 Weight (Kg):3,817
@@ -7332,6 +7316,22 @@
 Help
 Location:FABRICA ALGECIRAS
 3,370.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="434" xml:space="preserve">
+      <c r="A434" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4571 316Ti-Coil, Nb. 1,
+3.00 x 184.0 x coil mm</v>
+      </c>
+      <c r="B434" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4571 316Ti-Coil, Nb. 1,
+3.00 x 184.0 x coil mm
+Weight (Kg):1,794
+Quality:Prime
+Help
+Location:FABRICA ALGECIRAS
+3,270.00 €/ton
 Add to cart</v>
       </c>
     </row>
@@ -7343,7 +7343,7 @@
       <c r="B435" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4571 316Ti-Coil, Nb. 1,
 3.00 x 184.0 x coil mm
-Weight (Kg):1,794
+Weight (Kg):1,806
 Quality:Prime
 Help
 Location:FABRICA ALGECIRAS
@@ -7359,7 +7359,7 @@
       <c r="B436" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4571 316Ti-Coil, Nb. 1,
 3.00 x 184.0 x coil mm
-Weight (Kg):1,806
+Weight (Kg):1,808
 Quality:Prime
 Help
 Location:FABRICA ALGECIRAS
@@ -7370,25 +7370,9 @@
     <row r="437" xml:space="preserve">
       <c r="A437" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4571 316Ti-Coil, Nb. 1,
-3.00 x 184.0 x coil mm</v>
+4.00 x 200.0 x coil mm</v>
       </c>
       <c r="B437" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4571 316Ti-Coil, Nb. 1,
-3.00 x 184.0 x coil mm
-Weight (Kg):1,808
-Quality:Prime
-Help
-Location:FABRICA ALGECIRAS
-3,270.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="438" xml:space="preserve">
-      <c r="A438" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4571 316Ti-Coil, Nb. 1,
-4.00 x 200.0 x coil mm</v>
-      </c>
-      <c r="B438" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4571 316Ti-Coil, Nb. 1,
 4.00 x 200.0 x coil mm
 Weight (Kg):1,918
@@ -7399,12 +7383,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="439" xml:space="preserve">
-      <c r="A439" t="str" xml:space="preserve">
+    <row r="438" xml:space="preserve">
+      <c r="A438" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4571 316Ti-Plate, Nb. 1,
 45.00 x 1500.0 x 3000.0 mm</v>
       </c>
-      <c r="B439" t="str" xml:space="preserve">
+      <c r="B438" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4571 316Ti-Plate, Nb. 1,
 45.00 x 1500.0 x 3000.0 mm
 Weight (Kg):1,640
@@ -7412,6 +7396,22 @@
 Help
 Location:FABRICA ALGECIRAS
 4,600.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="439" xml:space="preserve">
+      <c r="A439" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4571 316Ti-Sheet, 2B,
+3.00 x 1000.0 x 2000.0 mm</v>
+      </c>
+      <c r="B439" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4571 316Ti-Sheet, 2B,
+3.00 x 1000.0 x 2000.0 mm
+Weight (Kg):918
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+3,495.00 €/ton
 Add to cart</v>
       </c>
     </row>
@@ -7423,7 +7423,7 @@
       <c r="B440" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4571 316Ti-Sheet, 2B,
 3.00 x 1000.0 x 2000.0 mm
-Weight (Kg):918
+Weight (Kg):518
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -7455,7 +7455,7 @@
       <c r="B442" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4571 316Ti-Sheet, 2B,
 3.00 x 1000.0 x 2000.0 mm
-Weight (Kg):518
+Weight (Kg):848
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -7466,12 +7466,12 @@
     <row r="443" xml:space="preserve">
       <c r="A443" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4571 316Ti-Sheet, 2B,
-3.00 x 1000.0 x 2000.0 mm</v>
+5.00 x 1000.0 x 2000.0 mm</v>
       </c>
       <c r="B443" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4571 316Ti-Sheet, 2B,
-3.00 x 1000.0 x 2000.0 mm
-Weight (Kg):848
+5.00 x 1000.0 x 2000.0 mm
+Weight (Kg):1,102
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -7482,12 +7482,12 @@
     <row r="444" xml:space="preserve">
       <c r="A444" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4571 316Ti-Sheet, 2B,
-5.00 x 1000.0 x 2000.0 mm</v>
+6.00 x 1000.0 x 2000.0 mm</v>
       </c>
       <c r="B444" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4571 316Ti-Sheet, 2B,
-5.00 x 1000.0 x 2000.0 mm
-Weight (Kg):1,102
+6.00 x 1000.0 x 2000.0 mm
+Weight (Kg):1,050
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -7503,7 +7503,7 @@
       <c r="B445" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4571 316Ti-Sheet, 2B,
 6.00 x 1000.0 x 2000.0 mm
-Weight (Kg):1,050
+Weight (Kg):952
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -7513,26 +7513,10 @@
     </row>
     <row r="446" xml:space="preserve">
       <c r="A446" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4571 316Ti-Sheet, 2B,
-6.00 x 1000.0 x 2000.0 mm</v>
-      </c>
-      <c r="B446" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4571 316Ti-Sheet, 2B,
-6.00 x 1000.0 x 2000.0 mm
-Weight (Kg):952
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-3,495.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="447" xml:space="preserve">
-      <c r="A447" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4571 316Ti-Sheet, Nb. 1,
 8.00 x 1500.0 x 3000.0 mm</v>
       </c>
-      <c r="B447" t="str" xml:space="preserve">
+      <c r="B446" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4571 316Ti-Sheet, Nb. 1,
 8.00 x 1500.0 x 3000.0 mm
 Weight (Kg):1,136
@@ -7540,6 +7524,22 @@
 Help
 Location:FABRICA ALGECIRAS
 3,495.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="447" xml:space="preserve">
+      <c r="A447" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4541 321-Coil, 2B,
+1.90 x 217.0 x coil mm</v>
+      </c>
+      <c r="B447" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4541 321-Coil, 2B,
+1.90 x 217.0 x coil mm
+Weight (Kg):3,537
+Quality:Prime
+Help
+Location:FABRICA ALGECIRAS
+2,235.00 €/ton
 Add to cart</v>
       </c>
     </row>
@@ -7551,7 +7551,7 @@
       <c r="B448" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4541 321-Coil, 2B,
 1.90 x 217.0 x coil mm
-Weight (Kg):3,537
+Weight (Kg):3,484
 Quality:Prime
 Help
 Location:FABRICA ALGECIRAS
@@ -7567,7 +7567,7 @@
       <c r="B449" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4541 321-Coil, 2B,
 1.90 x 217.0 x coil mm
-Weight (Kg):3,484
+Weight (Kg):3,537
 Quality:Prime
 Help
 Location:FABRICA ALGECIRAS
@@ -7583,7 +7583,7 @@
       <c r="B450" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4541 321-Coil, 2B,
 1.90 x 217.0 x coil mm
-Weight (Kg):3,537
+Weight (Kg):3,490
 Quality:Prime
 Help
 Location:FABRICA ALGECIRAS
@@ -7599,7 +7599,7 @@
       <c r="B451" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4541 321-Coil, 2B,
 1.90 x 217.0 x coil mm
-Weight (Kg):3,490
+Weight (Kg):3,537
 Quality:Prime
 Help
 Location:FABRICA ALGECIRAS
@@ -7615,7 +7615,7 @@
       <c r="B452" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4541 321-Coil, 2B,
 1.90 x 217.0 x coil mm
-Weight (Kg):3,537
+Weight (Kg):3,492
 Quality:Prime
 Help
 Location:FABRICA ALGECIRAS
@@ -7631,7 +7631,7 @@
       <c r="B453" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4541 321-Coil, 2B,
 1.90 x 217.0 x coil mm
-Weight (Kg):3,492
+Weight (Kg):3,480
 Quality:Prime
 Help
 Location:FABRICA ALGECIRAS
@@ -7642,25 +7642,9 @@
     <row r="454" xml:space="preserve">
       <c r="A454" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4541 321-Coil, 2B,
-1.90 x 217.0 x coil mm</v>
+4.00 x 520.0 x coil mm</v>
       </c>
       <c r="B454" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4541 321-Coil, 2B,
-1.90 x 217.0 x coil mm
-Weight (Kg):3,480
-Quality:Prime
-Help
-Location:FABRICA ALGECIRAS
-2,235.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="455" xml:space="preserve">
-      <c r="A455" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4541 321-Coil, 2B,
-4.00 x 520.0 x coil mm</v>
-      </c>
-      <c r="B455" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4541 321-Coil, 2B,
 4.00 x 520.0 x coil mm
 Weight (Kg):7,263
@@ -7671,28 +7655,28 @@
 Add to cart</v>
       </c>
     </row>
+    <row r="455" xml:space="preserve">
+      <c r="A455" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4541 321-Coil, Nb. 1,
+5.00 x 1542.0 x coil mm</v>
+      </c>
+      <c r="B455" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4541 321-Coil, Nb. 1,
+5.00 x 1542.0 x coil mm
+Weight (Kg):4,890
+Quality:Prime
+Help
+Location:FABRICA ALGECIRAS
+2,875.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
     <row r="456" xml:space="preserve">
       <c r="A456" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4541 321-Coil, Nb. 1,
-5.00 x 1542.0 x coil mm</v>
+5.00 x 230.9 x coil mm</v>
       </c>
       <c r="B456" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4541 321-Coil, Nb. 1,
-5.00 x 1542.0 x coil mm
-Weight (Kg):4,890
-Quality:Prime
-Help
-Location:FABRICA ALGECIRAS
-2,875.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="457" xml:space="preserve">
-      <c r="A457" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4541 321-Coil, Nb. 1,
-5.00 x 230.9 x coil mm</v>
-      </c>
-      <c r="B457" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4541 321-Coil, Nb. 1,
 5.00 x 230.9 x coil mm
 Weight (Kg):4,198
@@ -7703,15 +7687,31 @@
 Add to cart</v>
       </c>
     </row>
+    <row r="457" xml:space="preserve">
+      <c r="A457" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4541 321-Sheet, 2B,
+3.00 x 1000.0 x 2000.0 mm</v>
+      </c>
+      <c r="B457" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4541 321-Sheet, 2B,
+3.00 x 1000.0 x 2000.0 mm
+Weight (Kg):1,104
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,385.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
     <row r="458" xml:space="preserve">
       <c r="A458" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4541 321-Sheet, 2B,
-3.00 x 1000.0 x 2000.0 mm</v>
+4.00 x 1000.0 x 2000.0 mm</v>
       </c>
       <c r="B458" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4541 321-Sheet, 2B,
-3.00 x 1000.0 x 2000.0 mm
-Weight (Kg):1,104
+4.00 x 1000.0 x 2000.0 mm
+Weight (Kg):1,552
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -7722,25 +7722,9 @@
     <row r="459" xml:space="preserve">
       <c r="A459" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4541 321-Sheet, 2B,
-4.00 x 1000.0 x 2000.0 mm</v>
+6.00 x 1250.0 x 2500.0 mm</v>
       </c>
       <c r="B459" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4541 321-Sheet, 2B,
-4.00 x 1000.0 x 2000.0 mm
-Weight (Kg):1,552
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-2,385.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="460" xml:space="preserve">
-      <c r="A460" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4541 321-Sheet, 2B,
-6.00 x 1250.0 x 2500.0 mm</v>
-      </c>
-      <c r="B460" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4541 321-Sheet, 2B,
 6.00 x 1250.0 x 2500.0 mm
 Weight (Kg):1,296
@@ -7751,12 +7735,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="461" xml:space="preserve">
-      <c r="A461" t="str" xml:space="preserve">
+    <row r="460" xml:space="preserve">
+      <c r="A460" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4541 321-Sheet, Nb. 1,
 8.00 x 1000.0 x 2000.0 mm</v>
       </c>
-      <c r="B461" t="str" xml:space="preserve">
+      <c r="B460" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4541 321-Sheet, Nb. 1,
 8.00 x 1000.0 x 2000.0 mm
 Weight (Kg):640
@@ -7767,28 +7751,28 @@
 Add to cart</v>
       </c>
     </row>
+    <row r="461" xml:space="preserve">
+      <c r="A461" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4512 409L-Coil, 2B,
+1.00 x 1304.0 x coil mm</v>
+      </c>
+      <c r="B461" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4512 409L-Coil, 2B,
+1.00 x 1304.0 x coil mm
+Weight (Kg):10,360
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+1,125.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
     <row r="462" xml:space="preserve">
       <c r="A462" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4512 409L-Coil, 2B,
-1.00 x 1304.0 x coil mm</v>
+1.00 x 625.0 x coil mm</v>
       </c>
       <c r="B462" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4512 409L-Coil, 2B,
-1.00 x 1304.0 x coil mm
-Weight (Kg):10,360
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-1,125.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="463" xml:space="preserve">
-      <c r="A463" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4512 409L-Coil, 2B,
-1.00 x 625.0 x coil mm</v>
-      </c>
-      <c r="B463" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4512 409L-Coil, 2B,
 1.00 x 625.0 x coil mm
 Weight (Kg):6,700
@@ -7799,12 +7783,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="464" xml:space="preserve">
-      <c r="A464" t="str" xml:space="preserve">
+    <row r="463" xml:space="preserve">
+      <c r="A463" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4512 409L-Coil, 2D,
 2.00 x 1291.0 x coil mm</v>
       </c>
-      <c r="B464" t="str" xml:space="preserve">
+      <c r="B463" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4512 409L-Coil, 2D,
 2.00 x 1291.0 x coil mm
 Weight (Kg):3,579
@@ -7815,15 +7799,31 @@
 Add to cart</v>
       </c>
     </row>
+    <row r="464" xml:space="preserve">
+      <c r="A464" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4512 409L-Coil, Nb. 1,
+4.00 x 140.0 x coil mm</v>
+      </c>
+      <c r="B464" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4512 409L-Coil, Nb. 1,
+4.00 x 140.0 x coil mm
+Weight (Kg):2,354
+Quality:Prime
+Help
+Location:FABRICA ALGECIRAS
+900.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
     <row r="465" xml:space="preserve">
       <c r="A465" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4512 409L-Coil, Nb. 1,
-4.00 x 140.0 x coil mm</v>
+5.00 x 190.0 x coil mm</v>
       </c>
       <c r="B465" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4512 409L-Coil, Nb. 1,
-4.00 x 140.0 x coil mm
-Weight (Kg):2,354
+5.00 x 190.0 x coil mm
+Weight (Kg):2,447
 Quality:Prime
 Help
 Location:FABRICA ALGECIRAS
@@ -7834,13 +7834,13 @@
     <row r="466" xml:space="preserve">
       <c r="A466" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4512 409L-Coil, Nb. 1,
-5.00 x 190.0 x coil mm</v>
+6.00 x 270.0 x coil mm</v>
       </c>
       <c r="B466" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4512 409L-Coil, Nb. 1,
-5.00 x 190.0 x coil mm
-Weight (Kg):2,447
-Quality:Prime
+6.00 x 270.0 x coil mm
+Weight (Kg):2,116
+Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
 900.00 €/ton
@@ -7855,7 +7855,7 @@
       <c r="B467" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4512 409L-Coil, Nb. 1,
 6.00 x 270.0 x coil mm
-Weight (Kg):2,116
+Weight (Kg):1,780
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -7866,13 +7866,13 @@
     <row r="468" xml:space="preserve">
       <c r="A468" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4512 409L-Coil, Nb. 1,
-6.00 x 270.0 x coil mm</v>
+8.00 x 115.9 x coil mm</v>
       </c>
       <c r="B468" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4512 409L-Coil, Nb. 1,
-6.00 x 270.0 x coil mm
-Weight (Kg):1,780
-Quality:Prime-2
+8.00 x 115.9 x coil mm
+Weight (Kg):1,238
+Quality:Prime
 Help
 Location:FABRICA ALGECIRAS
 900.00 €/ton
@@ -7882,12 +7882,12 @@
     <row r="469" xml:space="preserve">
       <c r="A469" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4512 409L-Coil, Nb. 1,
-8.00 x 115.9 x coil mm</v>
+8.00 x 125.9 x coil mm</v>
       </c>
       <c r="B469" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4512 409L-Coil, Nb. 1,
-8.00 x 115.9 x coil mm
-Weight (Kg):1,238
+8.00 x 125.9 x coil mm
+Weight (Kg):1,214
 Quality:Prime
 Help
 Location:FABRICA ALGECIRAS
@@ -7898,25 +7898,9 @@
     <row r="470" xml:space="preserve">
       <c r="A470" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4512 409L-Coil, Nb. 1,
-8.00 x 125.9 x coil mm</v>
+8.00 x 230.9 x coil mm</v>
       </c>
       <c r="B470" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4512 409L-Coil, Nb. 1,
-8.00 x 125.9 x coil mm
-Weight (Kg):1,214
-Quality:Prime
-Help
-Location:FABRICA ALGECIRAS
-900.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="471" xml:space="preserve">
-      <c r="A471" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4512 409L-Coil, Nb. 1,
-8.00 x 230.9 x coil mm</v>
-      </c>
-      <c r="B471" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4512 409L-Coil, Nb. 1,
 8.00 x 230.9 x coil mm
 Weight (Kg):2,960
@@ -7927,12 +7911,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="472" xml:space="preserve">
-      <c r="A472" t="str" xml:space="preserve">
+    <row r="471" xml:space="preserve">
+      <c r="A471" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4512 409L-Untrimmed, Coil, 2B,
 1.00 x 625.0 x coil mm</v>
       </c>
-      <c r="B472" t="str" xml:space="preserve">
+      <c r="B471" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4512 409L-Untrimmed, Coil, 2B,
 1.00 x 625.0 x coil mm
 Weight (Kg):3,441
@@ -7943,12 +7927,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="473" xml:space="preserve">
-      <c r="A473" t="str" xml:space="preserve">
+    <row r="472" xml:space="preserve">
+      <c r="A472" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4512 409L-Untrimmed, Coil, 2D,
 1.50 x 1295.0 x coil mm</v>
       </c>
-      <c r="B473" t="str" xml:space="preserve">
+      <c r="B472" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4512 409L-Untrimmed, Coil, 2D,
 1.50 x 1295.0 x coil mm
 Weight (Kg):2,445
@@ -7959,12 +7943,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="474" xml:space="preserve">
-      <c r="A474" t="str" xml:space="preserve">
+    <row r="473" xml:space="preserve">
+      <c r="A473" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, 2B,
 0.70 x 299.9 x coil mm</v>
       </c>
-      <c r="B474" t="str" xml:space="preserve">
+      <c r="B473" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, 2B,
 0.70 x 299.9 x coil mm
 Weight (Kg):2,518
@@ -7975,60 +7959,60 @@
 Add to cart</v>
       </c>
     </row>
+    <row r="474" xml:space="preserve">
+      <c r="A474" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, 2D,
+0.50 x 1518.0 x coil mm</v>
+      </c>
+      <c r="B474" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, 2D,
+0.50 x 1518.0 x coil mm
+Weight (Kg):4,480
+Quality:Prime
+Help
+Location:FABRICA ALGECIRAS
+1,325.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
     <row r="475" xml:space="preserve">
       <c r="A475" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, 2D,
-0.50 x 1518.0 x coil mm</v>
+0.70 x 1007.0 x coil mm</v>
       </c>
       <c r="B475" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, 2D,
-0.50 x 1518.0 x coil mm
-Weight (Kg):4,480
-Quality:Prime
-Help
-Location:FABRICA ALGECIRAS
-1,325.00 €/ton
+0.70 x 1007.0 x coil mm
+Weight (Kg):14,970
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+1,125.00 €/ton
 Add to cart</v>
       </c>
     </row>
     <row r="476" xml:space="preserve">
       <c r="A476" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, 2D,
-0.70 x 1007.0 x coil mm</v>
+0.70 x 1450.0 x coil mm</v>
       </c>
       <c r="B476" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, 2D,
-0.70 x 1007.0 x coil mm
-Weight (Kg):14,970
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-1,125.00 €/ton
+0.70 x 1450.0 x coil mm
+Weight (Kg):4,780
+Quality:Prime
+Help
+Location:FABRICA ALGECIRAS
+1,325.00 €/ton
 Add to cart</v>
       </c>
     </row>
     <row r="477" xml:space="preserve">
       <c r="A477" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, 2D,
-0.70 x 1450.0 x coil mm</v>
+0.70 x 869.0 x coil mm</v>
       </c>
       <c r="B477" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, 2D,
-0.70 x 1450.0 x coil mm
-Weight (Kg):4,780
-Quality:Prime
-Help
-Location:FABRICA ALGECIRAS
-1,325.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="478" xml:space="preserve">
-      <c r="A478" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, 2D,
-0.70 x 869.0 x coil mm</v>
-      </c>
-      <c r="B478" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, 2D,
 0.70 x 869.0 x coil mm
 Weight (Kg):13,570
@@ -8039,31 +8023,47 @@
 Add to cart</v>
       </c>
     </row>
+    <row r="478" xml:space="preserve">
+      <c r="A478" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, BA,
+0.60 x 310.0 x coil mm</v>
+      </c>
+      <c r="B478" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, BA,
+0.60 x 310.0 x coil mm
+Weight (Kg):786
+Quality:Prime
+Help
+Location:FABRICA ALGECIRAS
+1,000.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
     <row r="479" xml:space="preserve">
       <c r="A479" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, BA,
-0.60 x 310.0 x coil mm</v>
+0.50 x 114.0 x coil mm</v>
       </c>
       <c r="B479" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, BA,
-0.60 x 310.0 x coil mm
-Weight (Kg):786
-Quality:Prime
+0.50 x 114.0 x coil mm
+Weight (Kg):1,225
+Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
 1,000.00 €/ton
-Add to cart</v>
+Reserved</v>
       </c>
     </row>
     <row r="480" xml:space="preserve">
       <c r="A480" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, BA,
-0.50 x 114.0 x coil mm</v>
+0.60 x 340.0 x coil mm</v>
       </c>
       <c r="B480" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, BA,
-0.50 x 114.0 x coil mm
-Weight (Kg):1,225
+0.60 x 340.0 x coil mm
+Weight (Kg):4,383
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -8074,12 +8074,12 @@
     <row r="481" xml:space="preserve">
       <c r="A481" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, BA,
-0.60 x 340.0 x coil mm</v>
+0.60 x 440.0 x coil mm</v>
       </c>
       <c r="B481" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, BA,
-0.60 x 340.0 x coil mm
-Weight (Kg):4,383
+0.60 x 440.0 x coil mm
+Weight (Kg):5,670
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -8378,17 +8378,17 @@
     <row r="500" xml:space="preserve">
       <c r="A500" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, BA,
-0.60 x 440.0 x coil mm</v>
+0.70 x 870.0 x coil mm</v>
       </c>
       <c r="B500" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, BA,
-0.60 x 440.0 x coil mm
-Weight (Kg):5,670
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-1,000.00 €/ton
-Reserved</v>
+0.70 x 870.0 x coil mm
+Weight (Kg):13,910
+Quality:Prime
+Help
+Location:FABRICA ALGECIRAS
+1,900.00 €/ton
+Add to cart</v>
       </c>
     </row>
     <row r="501" xml:space="preserve">
@@ -8410,41 +8410,25 @@
     <row r="502" xml:space="preserve">
       <c r="A502" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, BA,
-0.70 x 870.0 x coil mm</v>
+0.70 x 953.0 x coil mm</v>
       </c>
       <c r="B502" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, BA,
-0.70 x 870.0 x coil mm
-Weight (Kg):13,910
-Quality:Prime
-Help
-Location:FABRICA ALGECIRAS
-1,900.00 €/ton
+0.70 x 953.0 x coil mm
+Weight (Kg):6,970
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+1,125.00 €/ton
 Add to cart</v>
       </c>
     </row>
     <row r="503" xml:space="preserve">
       <c r="A503" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, BA,
-0.70 x 953.0 x coil mm</v>
+1.00 x 530.0 x coil mm</v>
       </c>
       <c r="B503" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, BA,
-0.70 x 953.0 x coil mm
-Weight (Kg):6,970
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-1,125.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="504" xml:space="preserve">
-      <c r="A504" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, BA,
-1.00 x 530.0 x coil mm</v>
-      </c>
-      <c r="B504" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, BA,
 1.00 x 530.0 x coil mm
 Weight (Kg):880
@@ -8455,32 +8439,48 @@
 Add to cart</v>
       </c>
     </row>
+    <row r="504" xml:space="preserve">
+      <c r="A504" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, Polished N4-G-180,
+0.90 x 1250.0 x coil mm</v>
+      </c>
+      <c r="B504" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, Polished N4-G-180,
+0.90 x 1250.0 x coil mm
+Weight (Kg):2,218
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+1,125.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
     <row r="505" xml:space="preserve">
       <c r="A505" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, Polished N4-G-180,
-0.90 x 1250.0 x coil mm</v>
+1.20 x 120.0 x coil mm</v>
       </c>
       <c r="B505" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, Polished N4-G-180,
-0.90 x 1250.0 x coil mm
-Weight (Kg):2,218
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-1,125.00 €/ton
+1.20 x 120.0 x coil mm
+Weight (Kg):1,430
+Quality:Prime
+Help
+Location:FABRICA ALGECIRAS
+1,000.00 €/ton
 Add to cart</v>
       </c>
     </row>
     <row r="506" xml:space="preserve">
       <c r="A506" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, Polished N4-G-180,
-1.20 x 120.0 x coil mm</v>
+1.20 x 250.0 x coil mm</v>
       </c>
       <c r="B506" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, Polished N4-G-180,
-1.20 x 120.0 x coil mm
-Weight (Kg):1,430
-Quality:Prime
+1.20 x 250.0 x coil mm
+Weight (Kg):1,902
+Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
 1,000.00 €/ton
@@ -8490,13 +8490,13 @@
     <row r="507" xml:space="preserve">
       <c r="A507" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, Polished N4-G-180,
-1.20 x 250.0 x coil mm</v>
+1.20 x 250.9 x coil mm</v>
       </c>
       <c r="B507" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, Polished N4-G-180,
-1.20 x 250.0 x coil mm
-Weight (Kg):1,902
-Quality:Prime-2
+1.20 x 250.9 x coil mm
+Weight (Kg):1,960
+Quality:Prime
 Help
 Location:FABRICA ALGECIRAS
 1,000.00 €/ton
@@ -8511,8 +8511,8 @@
       <c r="B508" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, Polished N4-G-180,
 1.20 x 250.9 x coil mm
-Weight (Kg):1,960
-Quality:Prime
+Weight (Kg):1,918
+Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
 1,000.00 €/ton
@@ -8522,12 +8522,12 @@
     <row r="509" xml:space="preserve">
       <c r="A509" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, Polished N4-G-180,
-1.20 x 250.9 x coil mm</v>
+1.20 x 260.9 x coil mm</v>
       </c>
       <c r="B509" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, Polished N4-G-180,
-1.20 x 250.9 x coil mm
-Weight (Kg):1,918
+1.20 x 260.9 x coil mm
+Weight (Kg):1,524
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -8543,7 +8543,7 @@
       <c r="B510" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, Polished N4-G-180,
 1.20 x 260.9 x coil mm
-Weight (Kg):1,524
+Weight (Kg):1,934
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -8553,13 +8553,13 @@
     </row>
     <row r="511" xml:space="preserve">
       <c r="A511" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, Polished N4-G-180,
-1.20 x 260.9 x coil mm</v>
+        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, SB-G-400,
+0.60 x 134.9 x coil mm</v>
       </c>
       <c r="B511" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, Polished N4-G-180,
-1.20 x 260.9 x coil mm
-Weight (Kg):1,934
+        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, SB-G-400,
+0.60 x 134.9 x coil mm
+Weight (Kg):1,134
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -8575,7 +8575,7 @@
       <c r="B512" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, SB-G-400,
 0.60 x 134.9 x coil mm
-Weight (Kg):1,134
+Weight (Kg):962
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -8586,12 +8586,12 @@
     <row r="513" xml:space="preserve">
       <c r="A513" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, SB-G-400,
-0.60 x 134.9 x coil mm</v>
+0.60 x 245.9 x coil mm</v>
       </c>
       <c r="B513" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, SB-G-400,
-0.60 x 134.9 x coil mm
-Weight (Kg):962
+0.60 x 245.9 x coil mm
+Weight (Kg):1,778
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -8602,12 +8602,12 @@
     <row r="514" xml:space="preserve">
       <c r="A514" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, SB-G-400,
-0.60 x 245.9 x coil mm</v>
+1.00 x 118.9 x coil mm</v>
       </c>
       <c r="B514" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, SB-G-400,
-0.60 x 245.9 x coil mm
-Weight (Kg):1,778
+1.00 x 118.9 x coil mm
+Weight (Kg):754
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -8623,7 +8623,7 @@
       <c r="B515" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, SB-G-400,
 1.00 x 118.9 x coil mm
-Weight (Kg):754
+Weight (Kg):802
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -8634,25 +8634,9 @@
     <row r="516" xml:space="preserve">
       <c r="A516" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, SB-G-400,
-1.00 x 118.9 x coil mm</v>
+1.00 x 266.9 x coil mm</v>
       </c>
       <c r="B516" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, SB-G-400,
-1.00 x 118.9 x coil mm
-Weight (Kg):802
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-1,000.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="517" xml:space="preserve">
-      <c r="A517" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, SB-G-400,
-1.00 x 266.9 x coil mm</v>
-      </c>
-      <c r="B517" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, SB-G-400,
 1.00 x 266.9 x coil mm
 Weight (Kg):1,322
@@ -8663,12 +8647,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="518" xml:space="preserve">
-      <c r="A518" t="str" xml:space="preserve">
+    <row r="517" xml:space="preserve">
+      <c r="A517" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, SB-G-500,
 0.70 x 245.9 x coil mm</v>
       </c>
-      <c r="B518" t="str" xml:space="preserve">
+      <c r="B517" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, SB-G-500,
 0.70 x 245.9 x coil mm
 Weight (Kg):1,496
@@ -8679,32 +8663,48 @@
 Add to cart</v>
       </c>
     </row>
+    <row r="518" xml:space="preserve">
+      <c r="A518" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, SBA,
+0.70 x 1056.0 x coil mm</v>
+      </c>
+      <c r="B518" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, SBA,
+0.70 x 1056.0 x coil mm
+Weight (Kg):15,197
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+1,125.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
     <row r="519" xml:space="preserve">
       <c r="A519" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, SBA,
-0.70 x 1056.0 x coil mm</v>
+0.70 x 150.9 x coil mm</v>
       </c>
       <c r="B519" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, SBA,
-0.70 x 1056.0 x coil mm
-Weight (Kg):15,197
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-1,125.00 €/ton
+0.70 x 150.9 x coil mm
+Weight (Kg):1,268
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+1,000.00 €/ton
 Add to cart</v>
       </c>
     </row>
     <row r="520" xml:space="preserve">
       <c r="A520" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, SBA,
-0.70 x 150.9 x coil mm</v>
+0.70 x 173.0 x coil mm</v>
       </c>
       <c r="B520" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, SBA,
-0.70 x 150.9 x coil mm
-Weight (Kg):1,268
-Quality:Prime-2
+0.70 x 173.0 x coil mm
+Weight (Kg):890
+Quality:Prime
 Help
 Location:FABRICA ALGECIRAS
 1,000.00 €/ton
@@ -8714,13 +8714,13 @@
     <row r="521" xml:space="preserve">
       <c r="A521" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, SBA,
-0.70 x 173.0 x coil mm</v>
+0.70 x 195.9 x coil mm</v>
       </c>
       <c r="B521" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, SBA,
-0.70 x 173.0 x coil mm
-Weight (Kg):890
-Quality:Prime
+0.70 x 195.9 x coil mm
+Weight (Kg):962
+Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
 1,000.00 €/ton
@@ -8730,44 +8730,44 @@
     <row r="522" xml:space="preserve">
       <c r="A522" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, SBA,
-0.70 x 195.9 x coil mm</v>
+0.70 x 682.0 x coil mm</v>
       </c>
       <c r="B522" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, SBA,
-0.70 x 195.9 x coil mm
-Weight (Kg):962
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-1,000.00 €/ton
+0.70 x 682.0 x coil mm
+Weight (Kg):3,870
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+1,025.00 €/ton
 Add to cart</v>
       </c>
     </row>
     <row r="523" xml:space="preserve">
       <c r="A523" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, SBA,
-0.70 x 682.0 x coil mm</v>
+0.70 x 825.0 x coil mm</v>
       </c>
       <c r="B523" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, SBA,
-0.70 x 682.0 x coil mm
-Weight (Kg):3,870
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-1,025.00 €/ton
+0.70 x 825.0 x coil mm
+Weight (Kg):6,448
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+1,125.00 €/ton
 Add to cart</v>
       </c>
     </row>
     <row r="524" xml:space="preserve">
       <c r="A524" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, SBA,
-0.70 x 825.0 x coil mm</v>
+0.70 x 942.0 x coil mm</v>
       </c>
       <c r="B524" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, SBA,
-0.70 x 825.0 x coil mm
-Weight (Kg):6,448
+0.70 x 942.0 x coil mm
+Weight (Kg):1,810
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -8778,12 +8778,12 @@
     <row r="525" xml:space="preserve">
       <c r="A525" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, SBA,
-0.70 x 942.0 x coil mm</v>
+0.70 x 948.0 x coil mm</v>
       </c>
       <c r="B525" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, SBA,
-0.70 x 942.0 x coil mm
-Weight (Kg):1,810
+0.70 x 948.0 x coil mm
+Weight (Kg):3,410
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -8794,12 +8794,12 @@
     <row r="526" xml:space="preserve">
       <c r="A526" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, SBA,
-0.70 x 948.0 x coil mm</v>
+0.70 x 960.0 x coil mm</v>
       </c>
       <c r="B526" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, SBA,
-0.70 x 948.0 x coil mm
-Weight (Kg):3,410
+0.70 x 960.0 x coil mm
+Weight (Kg):2,780
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -8810,25 +8810,9 @@
     <row r="527" xml:space="preserve">
       <c r="A527" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, SBA,
-0.70 x 960.0 x coil mm</v>
+0.70 x 963.0 x coil mm</v>
       </c>
       <c r="B527" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, SBA,
-0.70 x 960.0 x coil mm
-Weight (Kg):2,780
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-1,125.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="528" xml:space="preserve">
-      <c r="A528" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, SBA,
-0.70 x 963.0 x coil mm</v>
-      </c>
-      <c r="B528" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, SBA,
 0.70 x 963.0 x coil mm
 Weight (Kg):4,570
@@ -8836,6 +8820,22 @@
 Help
 Location:FABRICA ALGECIRAS
 1,325.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="528" xml:space="preserve">
+      <c r="A528" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Disk, BA,
+0.60 x 550.0 x 0.0 mm</v>
+      </c>
+      <c r="B528" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Disk, BA,
+0.60 x 550.0 x 0.0 mm
+Weight (Kg):578
+Quality:Prime
+Help
+Location:FABRICA ALGECIRAS
+1,900.00 €/ton
 Add to cart</v>
       </c>
     </row>
@@ -8847,7 +8847,7 @@
       <c r="B529" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Disk, BA,
 0.60 x 550.0 x 0.0 mm
-Weight (Kg):578
+Weight (Kg):572
 Quality:Prime
 Help
 Location:FABRICA ALGECIRAS
@@ -8863,7 +8863,7 @@
       <c r="B530" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Disk, BA,
 0.60 x 550.0 x 0.0 mm
-Weight (Kg):572
+Weight (Kg):576
 Quality:Prime
 Help
 Location:FABRICA ALGECIRAS
@@ -8879,7 +8879,7 @@
       <c r="B531" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Disk, BA,
 0.60 x 550.0 x 0.0 mm
-Weight (Kg):576
+Weight (Kg):578
 Quality:Prime
 Help
 Location:FABRICA ALGECIRAS
@@ -8895,7 +8895,7 @@
       <c r="B532" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Disk, BA,
 0.60 x 550.0 x 0.0 mm
-Weight (Kg):578
+Weight (Kg):582
 Quality:Prime
 Help
 Location:FABRICA ALGECIRAS
@@ -8905,29 +8905,29 @@
     </row>
     <row r="533" xml:space="preserve">
       <c r="A533" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Disk, BA,
-0.60 x 550.0 x 0.0 mm</v>
+        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Sheet, 2B,
+0.80 x 1500.0 x 3000.0 mm</v>
       </c>
       <c r="B533" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Disk, BA,
-0.60 x 550.0 x 0.0 mm
-Weight (Kg):582
-Quality:Prime
-Help
-Location:FABRICA ALGECIRAS
-1,900.00 €/ton
+        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Sheet, 2B,
+0.80 x 1500.0 x 3000.0 mm
+Weight (Kg):1,744
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+1,125.00 €/ton
 Add to cart</v>
       </c>
     </row>
     <row r="534" xml:space="preserve">
       <c r="A534" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Sheet, 2B,
-0.80 x 1500.0 x 3000.0 mm</v>
+2.00 x 1250.0 x 2500.0 mm</v>
       </c>
       <c r="B534" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Sheet, 2B,
-0.80 x 1500.0 x 3000.0 mm
-Weight (Kg):1,744
+2.00 x 1250.0 x 2500.0 mm
+Weight (Kg):619
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -8938,12 +8938,12 @@
     <row r="535" xml:space="preserve">
       <c r="A535" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Sheet, 2B,
-2.00 x 1250.0 x 2500.0 mm</v>
+3.00 x 1250.0 x 2500.0 mm</v>
       </c>
       <c r="B535" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Sheet, 2B,
-2.00 x 1250.0 x 2500.0 mm
-Weight (Kg):619
+3.00 x 1250.0 x 2500.0 mm
+Weight (Kg):566
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -8959,7 +8959,7 @@
       <c r="B536" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Sheet, 2B,
 3.00 x 1250.0 x 2500.0 mm
-Weight (Kg):566
+Weight (Kg):640
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -8969,26 +8969,10 @@
     </row>
     <row r="537" xml:space="preserve">
       <c r="A537" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Sheet, 2B,
-3.00 x 1250.0 x 2500.0 mm</v>
-      </c>
-      <c r="B537" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Sheet, 2B,
-3.00 x 1250.0 x 2500.0 mm
-Weight (Kg):640
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-1,125.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="538" xml:space="preserve">
-      <c r="A538" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Sheet, BA,
 0.70 x 1250.0 x 2500.0 mm</v>
       </c>
-      <c r="B538" t="str" xml:space="preserve">
+      <c r="B537" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Sheet, BA,
 0.70 x 1250.0 x 2500.0 mm
 Weight (Kg):766
@@ -8999,12 +8983,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="539" xml:space="preserve">
-      <c r="A539" t="str" xml:space="preserve">
+    <row r="538" xml:space="preserve">
+      <c r="A538" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Sheet, SB-G-400,
 1.00 x 1500.0 x 3000.0 mm</v>
       </c>
-      <c r="B539" t="str" xml:space="preserve">
+      <c r="B538" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Sheet, SB-G-400,
 1.00 x 1500.0 x 3000.0 mm
 Weight (Kg):1,940
@@ -9015,12 +8999,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="540" xml:space="preserve">
-      <c r="A540" t="str" xml:space="preserve">
+    <row r="539" xml:space="preserve">
+      <c r="A539" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Untrimmed, Coil, 1/4 HT,
 3.00 x 1292.0 x coil mm</v>
       </c>
-      <c r="B540" t="str" xml:space="preserve">
+      <c r="B539" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Untrimmed, Coil, 1/4 HT,
 3.00 x 1292.0 x coil mm
 Weight (Kg):3,641
@@ -9028,6 +9012,22 @@
 Help
 Location:FABRICA ALGECIRAS
 1,125.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="540" xml:space="preserve">
+      <c r="A540" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Untrimmed, Coil, 2B,
+1.20 x 1500.0 x coil mm</v>
+      </c>
+      <c r="B540" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Untrimmed, Coil, 2B,
+1.20 x 1500.0 x coil mm
+Weight (Kg):4,750
+Quality:Downgraded
+Help
+Location:FABRICA ALGECIRAS
+1,000.00 €/ton
 Add to cart</v>
       </c>
     </row>
@@ -9049,17 +9049,17 @@
     </row>
     <row r="542" xml:space="preserve">
       <c r="A542" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Untrimmed, Coil, 2B,
-1.20 x 1500.0 x coil mm</v>
+        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Untrimmed, Coil, 2D, ET-100
+0.50 x 1250.0 x coil mm</v>
       </c>
       <c r="B542" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Untrimmed, Coil, 2B,
-1.20 x 1500.0 x coil mm
-Weight (Kg):4,750
-Quality:Downgraded
-Help
-Location:FABRICA ALGECIRAS
-1,000.00 €/ton
+        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Untrimmed, Coil, 2D, ET-100
+0.50 x 1250.0 x coil mm
+Weight (Kg):5,160
+Quality:Prime
+Help
+Location:FABRICA ALGECIRAS
+1,325.00 €/ton
 Add to cart</v>
       </c>
     </row>
@@ -9071,7 +9071,7 @@
       <c r="B543" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Untrimmed, Coil, 2D, ET-100
 0.50 x 1250.0 x coil mm
-Weight (Kg):5,160
+Weight (Kg):3,695
 Quality:Prime
 Help
 Location:FABRICA ALGECIRAS
@@ -9081,29 +9081,29 @@
     </row>
     <row r="544" xml:space="preserve">
       <c r="A544" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Untrimmed, Coil, 2D, ET-100
-0.50 x 1250.0 x coil mm</v>
+        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Untrimmed, Coil, BA,
+0.60 x 1246.0 x coil mm</v>
       </c>
       <c r="B544" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Untrimmed, Coil, 2D, ET-100
-0.50 x 1250.0 x coil mm
-Weight (Kg):3,695
-Quality:Prime
-Help
-Location:FABRICA ALGECIRAS
-1,325.00 €/ton
+        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Untrimmed, Coil, BA,
+0.60 x 1246.0 x coil mm
+Weight (Kg):2,585
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+1,125.00 €/ton
 Add to cart</v>
       </c>
     </row>
     <row r="545" xml:space="preserve">
       <c r="A545" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Untrimmed, Coil, BA,
-0.60 x 1246.0 x coil mm</v>
+1.00 x 1028.0 x coil mm</v>
       </c>
       <c r="B545" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Untrimmed, Coil, BA,
-0.60 x 1246.0 x coil mm
-Weight (Kg):2,585
+1.00 x 1028.0 x coil mm
+Weight (Kg):2,430
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -9114,25 +9114,9 @@
     <row r="546" xml:space="preserve">
       <c r="A546" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Untrimmed, Coil, BA,
-1.00 x 1028.0 x coil mm</v>
+1.00 x 1285.0 x coil mm</v>
       </c>
       <c r="B546" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Untrimmed, Coil, BA,
-1.00 x 1028.0 x coil mm
-Weight (Kg):2,430
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-1,125.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="547" xml:space="preserve">
-      <c r="A547" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Untrimmed, Coil, BA,
-1.00 x 1285.0 x coil mm</v>
-      </c>
-      <c r="B547" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Untrimmed, Coil, BA,
 1.00 x 1285.0 x coil mm
 Weight (Kg):5,491
@@ -9143,28 +9127,28 @@
 Add to cart</v>
       </c>
     </row>
+    <row r="547" xml:space="preserve">
+      <c r="A547" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Untrimmed, Coil, SBA,
+0.70 x 825.0 x coil mm</v>
+      </c>
+      <c r="B547" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Untrimmed, Coil, SBA,
+0.70 x 825.0 x coil mm
+Weight (Kg):7,260
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+1,125.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
     <row r="548" xml:space="preserve">
       <c r="A548" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Untrimmed, Coil, SBA,
-0.70 x 825.0 x coil mm</v>
+0.70 x 873.0 x coil mm</v>
       </c>
       <c r="B548" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Untrimmed, Coil, SBA,
-0.70 x 825.0 x coil mm
-Weight (Kg):7,260
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-1,125.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="549" xml:space="preserve">
-      <c r="A549" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Untrimmed, Coil, SBA,
-0.70 x 873.0 x coil mm</v>
-      </c>
-      <c r="B549" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Untrimmed, Coil, SBA,
 0.70 x 873.0 x coil mm
 Weight (Kg):4,020
@@ -9175,12 +9159,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="550" xml:space="preserve">
-      <c r="A550" t="str" xml:space="preserve">
+    <row r="549" xml:space="preserve">
+      <c r="A549" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4510 430Ti-Coil, 2B,
 2.00 x 100.9 x coil mm</v>
       </c>
-      <c r="B550" t="str" xml:space="preserve">
+      <c r="B549" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4510 430Ti-Coil, 2B,
 2.00 x 100.9 x coil mm
 Weight (Kg):1,710
@@ -9191,51 +9175,67 @@
 Add to cart</v>
       </c>
     </row>
+    <row r="550" xml:space="preserve">
+      <c r="A550" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4510 430Ti-Coil, BA,
+0.40 x 180.0 x coil mm</v>
+      </c>
+      <c r="B550" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4510 430Ti-Coil, BA,
+0.40 x 180.0 x coil mm
+Weight (Kg):1,188
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+1,000.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
     <row r="551" xml:space="preserve">
       <c r="A551" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4510 430Ti-Coil, BA,
-0.40 x 180.0 x coil mm</v>
+0.40 x 508.0 x coil mm</v>
       </c>
       <c r="B551" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4510 430Ti-Coil, BA,
-0.40 x 180.0 x coil mm
-Weight (Kg):1,188
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-1,000.00 €/ton
+0.40 x 508.0 x coil mm
+Weight (Kg):3,364
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+1,025.00 €/ton
 Add to cart</v>
       </c>
     </row>
     <row r="552" xml:space="preserve">
       <c r="A552" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4510 430Ti-Coil, BA,
-0.40 x 508.0 x coil mm</v>
+0.70 x 325.0 x coil mm</v>
       </c>
       <c r="B552" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4510 430Ti-Coil, BA,
-0.40 x 508.0 x coil mm
-Weight (Kg):3,364
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-1,025.00 €/ton
+0.70 x 325.0 x coil mm
+Weight (Kg):4,156
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+1,000.00 €/ton
 Add to cart</v>
       </c>
     </row>
     <row r="553" xml:space="preserve">
       <c r="A553" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4510 430Ti-Coil, BA,
-0.70 x 325.0 x coil mm</v>
+0.70 x 900.0 x coil mm</v>
       </c>
       <c r="B553" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4510 430Ti-Coil, BA,
-0.70 x 325.0 x coil mm
-Weight (Kg):4,156
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-1,000.00 €/ton
+0.70 x 900.0 x coil mm
+Weight (Kg):2,800
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+1,125.00 €/ton
 Add to cart</v>
       </c>
     </row>
@@ -9247,7 +9247,7 @@
       <c r="B554" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4510 430Ti-Coil, BA,
 0.70 x 900.0 x coil mm
-Weight (Kg):2,800
+Weight (Kg):6,570
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -9258,12 +9258,12 @@
     <row r="555" xml:space="preserve">
       <c r="A555" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4510 430Ti-Coil, BA,
-0.70 x 900.0 x coil mm</v>
+0.70 x 905.0 x coil mm</v>
       </c>
       <c r="B555" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4510 430Ti-Coil, BA,
-0.70 x 900.0 x coil mm
-Weight (Kg):6,570
+0.70 x 905.0 x coil mm
+Weight (Kg):9,410
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -9274,12 +9274,12 @@
     <row r="556" xml:space="preserve">
       <c r="A556" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4510 430Ti-Coil, BA,
-0.70 x 905.0 x coil mm</v>
+0.70 x 932.0 x coil mm</v>
       </c>
       <c r="B556" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4510 430Ti-Coil, BA,
-0.70 x 905.0 x coil mm
-Weight (Kg):9,410
+0.70 x 932.0 x coil mm
+Weight (Kg):2,270
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -9290,12 +9290,12 @@
     <row r="557" xml:space="preserve">
       <c r="A557" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4510 430Ti-Coil, BA,
-0.70 x 932.0 x coil mm</v>
+0.70 x 940.0 x coil mm</v>
       </c>
       <c r="B557" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4510 430Ti-Coil, BA,
-0.70 x 932.0 x coil mm
-Weight (Kg):2,270
+0.70 x 940.0 x coil mm
+Weight (Kg):14,920
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -9369,13 +9369,13 @@
     </row>
     <row r="562" xml:space="preserve">
       <c r="A562" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4510 430Ti-Coil, BA,
-0.70 x 940.0 x coil mm</v>
+        <v xml:space="preserve">Acerinox Europa, 1.4510 430Ti-Untrimmed, Coil, BA,
+0.50 x 1275.0 x coil mm</v>
       </c>
       <c r="B562" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4510 430Ti-Coil, BA,
-0.70 x 940.0 x coil mm
-Weight (Kg):14,920
+        <v xml:space="preserve">Acerinox Europa, 1.4510 430Ti-Untrimmed, Coil, BA,
+0.50 x 1275.0 x coil mm
+Weight (Kg):2,258
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -9386,25 +9386,9 @@
     <row r="563" xml:space="preserve">
       <c r="A563" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4510 430Ti-Untrimmed, Coil, BA,
-0.50 x 1275.0 x coil mm</v>
+0.70 x 928.0 x coil mm</v>
       </c>
       <c r="B563" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4510 430Ti-Untrimmed, Coil, BA,
-0.50 x 1275.0 x coil mm
-Weight (Kg):2,258
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-1,125.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="564" xml:space="preserve">
-      <c r="A564" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4510 430Ti-Untrimmed, Coil, BA,
-0.70 x 928.0 x coil mm</v>
-      </c>
-      <c r="B564" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4510 430Ti-Untrimmed, Coil, BA,
 0.70 x 928.0 x coil mm
 Weight (Kg):4,257
@@ -9415,12 +9399,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="565" xml:space="preserve">
-      <c r="A565" t="str" xml:space="preserve">
+    <row r="564" xml:space="preserve">
+      <c r="A564" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4509 441-Coil, 2B,
 1.20 x 275.9 x coil mm</v>
       </c>
-      <c r="B565" t="str" xml:space="preserve">
+      <c r="B564" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4509 441-Coil, 2B,
 1.20 x 275.9 x coil mm
 Weight (Kg):2,416
@@ -9431,15 +9415,31 @@
 Add to cart</v>
       </c>
     </row>
+    <row r="565" xml:space="preserve">
+      <c r="A565" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4509 441-Coil, 2D,
+1.20 x 196.0 x coil mm</v>
+      </c>
+      <c r="B565" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4509 441-Coil, 2D,
+1.20 x 196.0 x coil mm
+Weight (Kg):2,970
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+1,100.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
     <row r="566" xml:space="preserve">
       <c r="A566" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4509 441-Coil, 2D,
-1.20 x 196.0 x coil mm</v>
+1.20 x 200.0 x coil mm</v>
       </c>
       <c r="B566" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4509 441-Coil, 2D,
-1.20 x 196.0 x coil mm
-Weight (Kg):2,970
+1.20 x 200.0 x coil mm
+Weight (Kg):3,310
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -9450,12 +9450,12 @@
     <row r="567" xml:space="preserve">
       <c r="A567" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4509 441-Coil, 2D,
-1.20 x 200.0 x coil mm</v>
+1.20 x 214.9 x coil mm</v>
       </c>
       <c r="B567" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4509 441-Coil, 2D,
-1.20 x 200.0 x coil mm
-Weight (Kg):3,310
+1.20 x 214.9 x coil mm
+Weight (Kg):3,220
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -9466,12 +9466,12 @@
     <row r="568" xml:space="preserve">
       <c r="A568" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4509 441-Coil, 2D,
-1.20 x 214.9 x coil mm</v>
+1.20 x 223.9 x coil mm</v>
       </c>
       <c r="B568" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4509 441-Coil, 2D,
-1.20 x 214.9 x coil mm
-Weight (Kg):3,220
+1.20 x 223.9 x coil mm
+Weight (Kg):3,798
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -9482,28 +9482,28 @@
     <row r="569" xml:space="preserve">
       <c r="A569" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4509 441-Coil, 2D,
-1.20 x 223.9 x coil mm</v>
+1.20 x 224.0 x coil mm</v>
       </c>
       <c r="B569" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4509 441-Coil, 2D,
-1.20 x 223.9 x coil mm
-Weight (Kg):3,798
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-1,100.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="570" xml:space="preserve">
-      <c r="A570" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4509 441-Coil, 2D,
-1.20 x 224.0 x coil mm</v>
-      </c>
-      <c r="B570" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4509 441-Coil, 2D,
 1.20 x 224.0 x coil mm
 Weight (Kg):3,808
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+1,100.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="570" xml:space="preserve">
+      <c r="A570" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4509 441-Coil, BA,
+0.80 x 130.9 x coil mm</v>
+      </c>
+      <c r="B570" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4509 441-Coil, BA,
+0.80 x 130.9 x coil mm
+Weight (Kg):245
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -9535,7 +9535,7 @@
       <c r="B572" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4509 441-Coil, BA,
 0.80 x 130.9 x coil mm
-Weight (Kg):245
+Weight (Kg):213
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -9551,7 +9551,7 @@
       <c r="B573" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4509 441-Coil, BA,
 0.80 x 130.9 x coil mm
-Weight (Kg):213
+Weight (Kg):244
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -9561,45 +9561,45 @@
     </row>
     <row r="574" xml:space="preserve">
       <c r="A574" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4509 441-Coil, BA,
-0.80 x 130.9 x coil mm</v>
+        <v xml:space="preserve">Acerinox Europa, 1.4509 441-Coil, SB-G-400,
+1.00 x 1000.0 x coil mm</v>
       </c>
       <c r="B574" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4509 441-Coil, BA,
-0.80 x 130.9 x coil mm
-Weight (Kg):244
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-1,100.00 €/ton
+        <v xml:space="preserve">Acerinox Europa, 1.4509 441-Coil, SB-G-400,
+1.00 x 1000.0 x coil mm
+Weight (Kg):7,550
+Quality:Prime
+Help
+Location:FABRICA ALGECIRAS
+1,625.00 €/ton
 Add to cart</v>
       </c>
     </row>
     <row r="575" xml:space="preserve">
       <c r="A575" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4509 441-Coil, SB-G-400,
-1.00 x 1000.0 x coil mm</v>
+1.00 x 255.0 x coil mm</v>
       </c>
       <c r="B575" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4509 441-Coil, SB-G-400,
-1.00 x 1000.0 x coil mm
-Weight (Kg):7,550
-Quality:Prime
-Help
-Location:FABRICA ALGECIRAS
-1,625.00 €/ton
+1.00 x 255.0 x coil mm
+Weight (Kg):2,182
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+1,100.00 €/ton
 Add to cart</v>
       </c>
     </row>
     <row r="576" xml:space="preserve">
       <c r="A576" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4509 441-Coil, SB-G-400,
-1.00 x 255.0 x coil mm</v>
+1.00 x 290.9 x coil mm</v>
       </c>
       <c r="B576" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4509 441-Coil, SB-G-400,
-1.00 x 255.0 x coil mm
-Weight (Kg):2,182
+1.00 x 290.9 x coil mm
+Weight (Kg):2,370
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -9610,12 +9610,12 @@
     <row r="577" xml:space="preserve">
       <c r="A577" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4509 441-Coil, SB-G-400,
-1.00 x 290.9 x coil mm</v>
+1.20 x 110.9 x coil mm</v>
       </c>
       <c r="B577" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4509 441-Coil, SB-G-400,
-1.00 x 290.9 x coil mm
-Weight (Kg):2,370
+1.20 x 110.9 x coil mm
+Weight (Kg):856
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -9626,12 +9626,12 @@
     <row r="578" xml:space="preserve">
       <c r="A578" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4509 441-Coil, SB-G-400,
-1.20 x 110.9 x coil mm</v>
+1.20 x 130.9 x coil mm</v>
       </c>
       <c r="B578" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4509 441-Coil, SB-G-400,
-1.20 x 110.9 x coil mm
-Weight (Kg):856
+1.20 x 130.9 x coil mm
+Weight (Kg):564
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -9647,8 +9647,8 @@
       <c r="B579" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4509 441-Coil, SB-G-400,
 1.20 x 130.9 x coil mm
-Weight (Kg):564
-Quality:Prime-2
+Weight (Kg):532
+Quality:Prime
 Help
 Location:FABRICA ALGECIRAS
 1,100.00 €/ton
@@ -9658,13 +9658,13 @@
     <row r="580" xml:space="preserve">
       <c r="A580" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4509 441-Coil, SB-G-400,
-1.20 x 130.9 x coil mm</v>
+1.50 x 130.9 x coil mm</v>
       </c>
       <c r="B580" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4509 441-Coil, SB-G-400,
-1.20 x 130.9 x coil mm
-Weight (Kg):532
-Quality:Prime
+1.50 x 130.9 x coil mm
+Weight (Kg):640
+Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
 1,100.00 €/ton
@@ -9690,25 +9690,9 @@
     <row r="582" xml:space="preserve">
       <c r="A582" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4509 441-Coil, SB-G-400,
-1.50 x 130.9 x coil mm</v>
+1.50 x 360.0 x coil mm</v>
       </c>
       <c r="B582" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4509 441-Coil, SB-G-400,
-1.50 x 130.9 x coil mm
-Weight (Kg):640
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-1,100.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="583" xml:space="preserve">
-      <c r="A583" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4509 441-Coil, SB-G-400,
-1.50 x 360.0 x coil mm</v>
-      </c>
-      <c r="B583" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4509 441-Coil, SB-G-400,
 1.50 x 360.0 x coil mm
 Weight (Kg):1,488
@@ -9719,12 +9703,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="584" xml:space="preserve">
-      <c r="A584" t="str" xml:space="preserve">
+    <row r="583" xml:space="preserve">
+      <c r="A583" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4509 441-Untrimmed, Coil, 2B,
 1.50 x 1539.0 x coil mm</v>
       </c>
-      <c r="B584" t="str" xml:space="preserve">
+      <c r="B583" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4509 441-Untrimmed, Coil, 2B,
 1.50 x 1539.0 x coil mm
 Weight (Kg):14,230
@@ -9735,12 +9719,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="585" xml:space="preserve">
-      <c r="A585" t="str" xml:space="preserve">
+    <row r="584" xml:space="preserve">
+      <c r="A584" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4509 441-Untrimmed, Coil, BA,
 0.40 x 1075.0 x coil mm</v>
       </c>
-      <c r="B585" t="str" xml:space="preserve">
+      <c r="B584" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4509 441-Untrimmed, Coil, BA,
 0.40 x 1075.0 x coil mm
 Weight (Kg):9,750
@@ -9751,12 +9735,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="586" xml:space="preserve">
-      <c r="A586" t="str" xml:space="preserve">
+    <row r="585" xml:space="preserve">
+      <c r="A585" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4509 441-Untrimmed, Coil, Nb. 1,
 5.00 x 1045.0 x coil mm</v>
       </c>
-      <c r="B586" t="str" xml:space="preserve">
+      <c r="B585" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4509 441-Untrimmed, Coil, Nb. 1,
 5.00 x 1045.0 x coil mm
 Weight (Kg):7,880
@@ -9767,12 +9751,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="587" xml:space="preserve">
-      <c r="A587" t="str" xml:space="preserve">
+    <row r="586" xml:space="preserve">
+      <c r="A586" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 441-1.4509 Coil, 2B,
 1.20 x 240.9 x coil mm</v>
       </c>
-      <c r="B587" t="str" xml:space="preserve">
+      <c r="B586" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 441-1.4509 Coil, 2B,
 1.20 x 240.9 x coil mm
 Weight (Kg):3,882
@@ -9783,12 +9767,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="588" xml:space="preserve">
-      <c r="A588" t="str" xml:space="preserve">
+    <row r="587" xml:space="preserve">
+      <c r="A587" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 304-1.4301 Coil,
 0.70 x 270.9 x coil mm</v>
       </c>
-      <c r="B588" t="str" xml:space="preserve">
+      <c r="B587" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 304-1.4301 Coil,
 0.70 x 270.9 x coil mm
 Weight (Kg):2,704
@@ -9799,12 +9783,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="589" xml:space="preserve">
-      <c r="A589" t="str" xml:space="preserve">
+    <row r="588" xml:space="preserve">
+      <c r="A588" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 316L-1.4404 Coil,
 1.20 x 136.0 x coil mm</v>
       </c>
-      <c r="B589" t="str" xml:space="preserve">
+      <c r="B588" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 316L-1.4404 Coil,
 1.20 x 136.0 x coil mm
 Weight (Kg):2,300
@@ -9815,12 +9799,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="590" xml:space="preserve">
-      <c r="A590" t="str" xml:space="preserve">
+    <row r="589" xml:space="preserve">
+      <c r="A589" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 304L/304-4301/4307 Coil, 2B,
 6.00 x 245.0 x coil mm</v>
       </c>
-      <c r="B590" t="str" xml:space="preserve">
+      <c r="B589" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 304L/304-4301/4307 Coil, 2B,
 6.00 x 245.0 x coil mm
 Weight (Kg):2,394
@@ -9831,12 +9815,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="591" xml:space="preserve">
-      <c r="A591" t="str" xml:space="preserve">
+    <row r="590" xml:space="preserve">
+      <c r="A590" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, 2B,
 0.70 x 197.5 x coil mm</v>
       </c>
-      <c r="B591" t="str" xml:space="preserve">
+      <c r="B590" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, 2B,
 0.70 x 197.5 x coil mm
 Weight (Kg):2,442
@@ -9847,12 +9831,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="592" xml:space="preserve">
-      <c r="A592" t="str" xml:space="preserve">
+    <row r="591" xml:space="preserve">
+      <c r="A591" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 441-1.4509 Coil, 2B,
 2.00 x 120.9 x coil mm</v>
       </c>
-      <c r="B592" t="str" xml:space="preserve">
+      <c r="B591" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 441-1.4509 Coil, 2B,
 2.00 x 120.9 x coil mm
 Weight (Kg):1,956
@@ -9860,6 +9844,22 @@
 Help
 Location:FABRICA ALGECIRAS
 1,100.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="592" xml:space="preserve">
+      <c r="A592" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 304-1.4301 Coil, 2B,
+1.20 x 119.9 x coil mm</v>
+      </c>
+      <c r="B592" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 304-1.4301 Coil, 2B,
+1.20 x 119.9 x coil mm
+Weight (Kg):1,500
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,075.00 €/ton
 Add to cart</v>
       </c>
     </row>
@@ -9871,7 +9871,7 @@
       <c r="B593" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 304-1.4301 Coil, 2B,
 1.20 x 119.9 x coil mm
-Weight (Kg):1,500
+Weight (Kg):1,400
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -9881,29 +9881,29 @@
     </row>
     <row r="594" xml:space="preserve">
       <c r="A594" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 304-1.4301 Coil, 2B,
-1.20 x 119.9 x coil mm</v>
+        <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, BA,
+0.70 x 125.0 x coil mm</v>
       </c>
       <c r="B594" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 304-1.4301 Coil, 2B,
-1.20 x 119.9 x coil mm
-Weight (Kg):1,400
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-2,075.00 €/ton
+        <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, BA,
+0.70 x 125.0 x coil mm
+Weight (Kg):1,764
+Quality:Prime
+Help
+Location:FABRICA ALGECIRAS
+1,000.00 €/ton
 Add to cart</v>
       </c>
     </row>
     <row r="595" xml:space="preserve">
       <c r="A595" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, BA,
-0.70 x 125.0 x coil mm</v>
+0.70 x 104.9 x coil mm</v>
       </c>
       <c r="B595" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, BA,
-0.70 x 125.0 x coil mm
-Weight (Kg):1,764
+0.70 x 104.9 x coil mm
+Weight (Kg):1,240
 Quality:Prime
 Help
 Location:FABRICA ALGECIRAS
@@ -9914,12 +9914,12 @@
     <row r="596" xml:space="preserve">
       <c r="A596" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, BA,
-0.70 x 104.9 x coil mm</v>
+0.70 x 118.9 x coil mm</v>
       </c>
       <c r="B596" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, BA,
-0.70 x 104.9 x coil mm
-Weight (Kg):1,240
+0.70 x 118.9 x coil mm
+Weight (Kg):1,802
 Quality:Prime
 Help
 Location:FABRICA ALGECIRAS
@@ -9930,12 +9930,12 @@
     <row r="597" xml:space="preserve">
       <c r="A597" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, BA,
-0.70 x 118.9 x coil mm</v>
+0.70 x 115.9 x coil mm</v>
       </c>
       <c r="B597" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, BA,
-0.70 x 118.9 x coil mm
-Weight (Kg):1,802
+0.70 x 115.9 x coil mm
+Weight (Kg):1,368
 Quality:Prime
 Help
 Location:FABRICA ALGECIRAS
@@ -9946,25 +9946,9 @@
     <row r="598" xml:space="preserve">
       <c r="A598" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, BA,
-0.70 x 115.9 x coil mm</v>
+0.70 x 119.0 x coil mm</v>
       </c>
       <c r="B598" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, BA,
-0.70 x 115.9 x coil mm
-Weight (Kg):1,368
-Quality:Prime
-Help
-Location:FABRICA ALGECIRAS
-1,000.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="599" xml:space="preserve">
-      <c r="A599" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, BA,
-0.70 x 119.0 x coil mm</v>
-      </c>
-      <c r="B599" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, BA,
 0.70 x 119.0 x coil mm
 Weight (Kg):1,622
@@ -9975,12 +9959,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="600" xml:space="preserve">
-      <c r="A600" t="str" xml:space="preserve">
+    <row r="599" xml:space="preserve">
+      <c r="A599" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 304L/304-4301/4307 Coil, 2B,
 1.40 x 110.9 x coil mm</v>
       </c>
-      <c r="B600" t="str" xml:space="preserve">
+      <c r="B599" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 304L/304-4301/4307 Coil, 2B,
 1.40 x 110.9 x coil mm
 Weight (Kg):1,240
@@ -9988,6 +9972,22 @@
 Help
 Location:FABRICA ALGECIRAS
 2,075.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="600" xml:space="preserve">
+      <c r="A600" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, BA,
+0.70 x 104.0 x coil mm</v>
+      </c>
+      <c r="B600" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, BA,
+0.70 x 104.0 x coil mm
+Weight (Kg):1,622
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+1,000.00 €/ton
 Add to cart</v>
       </c>
     </row>
@@ -9999,801 +9999,17 @@
       <c r="B601" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, BA,
 0.70 x 104.0 x coil mm
-Weight (Kg):1,622
+Weight (Kg):1,688
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
 1,000.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="602" xml:space="preserve">
-      <c r="A602" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, BA,
-0.70 x 104.0 x coil mm</v>
-      </c>
-      <c r="B602" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, BA,
-0.70 x 104.0 x coil mm
-Weight (Kg):1,688
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-1,000.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="603" xml:space="preserve">
-      <c r="A603" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 304L/304-4301/4307 Coil, 2B,
-1.40 x 110.9 x coil mm</v>
-      </c>
-      <c r="B603" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 304L/304-4301/4307 Coil, 2B,
-1.40 x 110.9 x coil mm
-Weight (Kg):1,162
-Quality:Prime
-Help
-Location:FABRICA ALGECIRAS
-2,075.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="604" xml:space="preserve">
-      <c r="A604" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 430Ti-1.4510 Coil, BA,
-0.70 x 165.9 x coil mm</v>
-      </c>
-      <c r="B604" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 430Ti-1.4510 Coil, BA,
-0.70 x 165.9 x coil mm
-Weight (Kg):2,692
-Quality:Prime
-Help
-Location:FABRICA ALGECIRAS
-1,000.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="605" xml:space="preserve">
-      <c r="A605" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 430Ti-1.4510 Coil, BA,
-0.70 x 165.9 x coil mm</v>
-      </c>
-      <c r="B605" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 430Ti-1.4510 Coil, BA,
-0.70 x 165.9 x coil mm
-Weight (Kg):2,756
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-1,000.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="606" xml:space="preserve">
-      <c r="A606" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, BA,
-0.70 x 140.9 x coil mm</v>
-      </c>
-      <c r="B606" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, BA,
-0.70 x 140.9 x coil mm
-Weight (Kg):1,676
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-1,000.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="607" xml:space="preserve">
-      <c r="A607" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, BA,
-0.70 x 100.9 x coil mm</v>
-      </c>
-      <c r="B607" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, BA,
-0.70 x 100.9 x coil mm
-Weight (Kg):1,340
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-1,000.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="608" xml:space="preserve">
-      <c r="A608" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, BA,
-0.70 x 125.0 x coil mm</v>
-      </c>
-      <c r="B608" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, BA,
-0.70 x 125.0 x coil mm
-Weight (Kg):1,550
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-1,000.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="609" xml:space="preserve">
-      <c r="A609" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, BA,
-0.70 x 125.0 x coil mm</v>
-      </c>
-      <c r="B609" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, BA,
-0.70 x 125.0 x coil mm
-Weight (Kg):1,414
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-1,000.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="610" xml:space="preserve">
-      <c r="A610" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, BA,
-0.70 x 100.9 x coil mm</v>
-      </c>
-      <c r="B610" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, BA,
-0.70 x 100.9 x coil mm
-Weight (Kg):2,188
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-1,000.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="611" xml:space="preserve">
-      <c r="A611" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 304L/304-4301/4307 Coil, Nb. 1,
-4.70 x 110.0 x coil mm</v>
-      </c>
-      <c r="B611" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 304L/304-4301/4307 Coil, Nb. 1,
-4.70 x 110.0 x coil mm
-Weight (Kg):1,796
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-1,975.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="612" xml:space="preserve">
-      <c r="A612" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 304L/304-4301/4307 Coil, Nb. 1,
-4.70 x 110.0 x coil mm</v>
-      </c>
-      <c r="B612" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 304L/304-4301/4307 Coil, Nb. 1,
-4.70 x 110.0 x coil mm
-Weight (Kg):2,038
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-1,975.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="613" xml:space="preserve">
-      <c r="A613" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, BA,
-0.70 x 165.9 x coil mm</v>
-      </c>
-      <c r="B613" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, BA,
-0.70 x 165.9 x coil mm
-Weight (Kg):2,620
-Quality:Prime
-Help
-Location:FABRICA ALGECIRAS
-1,000.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="614" xml:space="preserve">
-      <c r="A614" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 304-1.4301 Coil,
-0.70 x 260.9 x coil mm</v>
-      </c>
-      <c r="B614" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 304-1.4301 Coil,
-0.70 x 260.9 x coil mm
-Weight (Kg):1,330
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-2,075.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="615" xml:space="preserve">
-      <c r="A615" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 304-1.4301 Coil,
-0.70 x 260.9 x coil mm</v>
-      </c>
-      <c r="B615" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 304-1.4301 Coil,
-0.70 x 260.9 x coil mm
-Weight (Kg):1,264
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-2,075.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="616" xml:space="preserve">
-      <c r="A616" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, BA,
-0.70 x 110.0 x coil mm</v>
-      </c>
-      <c r="B616" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, BA,
-0.70 x 110.0 x coil mm
-Weight (Kg):1,250
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-1,000.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="617" xml:space="preserve">
-      <c r="A617" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, BA,
-0.70 x 122.9 x coil mm</v>
-      </c>
-      <c r="B617" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, BA,
-0.70 x 122.9 x coil mm
-Weight (Kg):1,460
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-1,000.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="618" xml:space="preserve">
-      <c r="A618" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 304L/304-4301/4307 Coil, 2B,
-1.40 x 110.0 x coil mm</v>
-      </c>
-      <c r="B618" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 304L/304-4301/4307 Coil, 2B,
-1.40 x 110.0 x coil mm
-Weight (Kg):1,554
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-2,075.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="619" xml:space="preserve">
-      <c r="A619" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 304L/304-4301/4307 Coil, 2B,
-1.40 x 110.0 x coil mm</v>
-      </c>
-      <c r="B619" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 304L/304-4301/4307 Coil, 2B,
-1.40 x 110.0 x coil mm
-Weight (Kg):1,586
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-2,075.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="620" xml:space="preserve">
-      <c r="A620" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 304L/304-4301/4307 Coil, 2B,
-1.40 x 104.0 x coil mm</v>
-      </c>
-      <c r="B620" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 304L/304-4301/4307 Coil, 2B,
-1.40 x 104.0 x coil mm
-Weight (Kg):1,030
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-2,075.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="621" xml:space="preserve">
-      <c r="A621" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 304DDQ-1.4301 Coil, BA,
-0.70 x 181.9 x coil mm</v>
-      </c>
-      <c r="B621" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 304DDQ-1.4301 Coil, BA,
-0.70 x 181.9 x coil mm
-Weight (Kg):2,912
-Quality:Prime
-Help
-Location:FABRICA ALGECIRAS
-2,075.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="622" xml:space="preserve">
-      <c r="A622" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 304-1.4301 Coil,
-1.50 x 136.0 x coil mm</v>
-      </c>
-      <c r="B622" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 304-1.4301 Coil,
-1.50 x 136.0 x coil mm
-Weight (Kg):3,450
-Quality:Prime
-Help
-Location:FABRICA ALGECIRAS
-2,075.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="623" xml:space="preserve">
-      <c r="A623" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 304-1.4301 Coil, BA,
-0.40 x 200.0 x coil mm</v>
-      </c>
-      <c r="B623" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 304-1.4301 Coil, BA,
-0.40 x 200.0 x coil mm
-Weight (Kg):1,964
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-2,075.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="624" xml:space="preserve">
-      <c r="A624" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 304-1.4301 Coil, BA, ET-60
-0.60 x 120.0 x coil mm</v>
-      </c>
-      <c r="B624" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 304-1.4301 Coil, BA, ET-60
-0.60 x 120.0 x coil mm
-Weight (Kg):1,302
-Quality:Prime
-Help
-Location:FABRICA ALGECIRAS
-2,075.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="625" xml:space="preserve">
-      <c r="A625" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, ET-100
-0.70 x 124.9 x coil mm</v>
-      </c>
-      <c r="B625" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, ET-100
-0.70 x 124.9 x coil mm
-Weight (Kg):2,106
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-1,000.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="626" xml:space="preserve">
-      <c r="A626" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, ET-100
-0.70 x 124.9 x coil mm</v>
-      </c>
-      <c r="B626" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, ET-100
-0.70 x 124.9 x coil mm
-Weight (Kg):1,972
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-1,000.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="627" xml:space="preserve">
-      <c r="A627" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 430Ti-1.4510 Coil, 2B,
-0.80 x 155.9 x coil mm</v>
-      </c>
-      <c r="B627" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 430Ti-1.4510 Coil, 2B,
-0.80 x 155.9 x coil mm
-Weight (Kg):1,586
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-1,000.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="628" xml:space="preserve">
-      <c r="A628" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 304-1.4301 Coil, BA,
-0.40 x 270.0 x coil mm</v>
-      </c>
-      <c r="B628" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 304-1.4301 Coil, BA,
-0.40 x 270.0 x coil mm
-Weight (Kg):2,572
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-2,075.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="629" xml:space="preserve">
-      <c r="A629" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, BA,
-0.60 x 130.0 x coil mm</v>
-      </c>
-      <c r="B629" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, BA,
-0.60 x 130.0 x coil mm
-Weight (Kg):1,490
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-1,000.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="630" xml:space="preserve">
-      <c r="A630" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 441-1.4509 Coil, BA,
-0.40 x 110.0 x coil mm</v>
-      </c>
-      <c r="B630" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 441-1.4509 Coil, BA,
-0.40 x 110.0 x coil mm
-Weight (Kg):1,870
-Quality:Prime
-Help
-Location:FABRICA ALGECIRAS
-1,100.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="631" xml:space="preserve">
-      <c r="A631" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 441-1.4509 Coil, BA,
-0.40 x 110.0 x coil mm</v>
-      </c>
-      <c r="B631" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 441-1.4509 Coil, BA,
-0.40 x 110.0 x coil mm
-Weight (Kg):1,882
-Quality:Prime
-Help
-Location:FABRICA ALGECIRAS
-1,100.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="632" xml:space="preserve">
-      <c r="A632" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 301-1.4310 Coil, BA,
-0.40 x 110.0 x coil mm</v>
-      </c>
-      <c r="B632" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 301-1.4310 Coil, BA,
-0.40 x 110.0 x coil mm
-Weight (Kg):1,934
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-1,925.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="633" xml:space="preserve">
-      <c r="A633" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 301-1.4310 Coil, BA,
-0.40 x 110.0 x coil mm</v>
-      </c>
-      <c r="B633" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 301-1.4310 Coil, BA,
-0.40 x 110.0 x coil mm
-Weight (Kg):1,860
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-1,925.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="634" xml:space="preserve">
-      <c r="A634" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 321-1.4541 Coil, 2B,
-1.90 x 104.5 x coil mm</v>
-      </c>
-      <c r="B634" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 321-1.4541 Coil, 2B,
-1.90 x 104.5 x coil mm
-Weight (Kg):2,304
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-2,235.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="635" xml:space="preserve">
-      <c r="A635" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 304L/304-4301/4307 Coil, Polished N4-G-180,
-1.20 x 255.9 x coil mm</v>
-      </c>
-      <c r="B635" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 304L/304-4301/4307 Coil, Polished N4-G-180,
-1.20 x 255.9 x coil mm
-Weight (Kg):4,298
-Quality:Prime
-Help
-Location:FABRICA ALGECIRAS
-2,075.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="636" xml:space="preserve">
-      <c r="A636" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 301-1.4310 Coil, BA,
-0.40 x 110.0 x coil mm</v>
-      </c>
-      <c r="B636" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 301-1.4310 Coil, BA,
-0.40 x 110.0 x coil mm
-Weight (Kg):1,698
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-1,925.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="637" xml:space="preserve">
-      <c r="A637" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, BA,
-0.40 x 130.0 x coil mm</v>
-      </c>
-      <c r="B637" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, BA,
-0.40 x 130.0 x coil mm
-Weight (Kg):1,916
-Quality:Prime
-Help
-Location:FABRICA ALGECIRAS
-1,000.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="638" xml:space="preserve">
-      <c r="A638" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 430Ti-1.4510 Coil, BA,
-0.50 x 140.0 x coil mm</v>
-      </c>
-      <c r="B638" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 430Ti-1.4510 Coil, BA,
-0.50 x 140.0 x coil mm
-Weight (Kg):3,054
-Quality:Prime
-Help
-Location:FABRICA ALGECIRAS
-1,000.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="639" xml:space="preserve">
-      <c r="A639" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 430Ti-1.4510 Coil, BA,
-0.50 x 140.0 x coil mm</v>
-      </c>
-      <c r="B639" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 430Ti-1.4510 Coil, BA,
-0.50 x 140.0 x coil mm
-Weight (Kg):3,060
-Quality:Prime
-Help
-Location:FABRICA ALGECIRAS
-1,000.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="640" xml:space="preserve">
-      <c r="A640" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 430Ti-1.4510 Coil, BA,
-0.50 x 140.0 x coil mm</v>
-      </c>
-      <c r="B640" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 430Ti-1.4510 Coil, BA,
-0.50 x 140.0 x coil mm
-Weight (Kg):2,220
-Quality:Prime
-Help
-Location:FABRICA ALGECIRAS
-1,000.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="641" xml:space="preserve">
-      <c r="A641" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 430Ti-1.4510 Coil, BA,
-0.50 x 140.0 x coil mm</v>
-      </c>
-      <c r="B641" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 430Ti-1.4510 Coil, BA,
-0.50 x 140.0 x coil mm
-Weight (Kg):2,224
-Quality:Prime
-Help
-Location:FABRICA ALGECIRAS
-1,000.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="642" xml:space="preserve">
-      <c r="A642" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 304L/304-4301/4307 Coil, 2B,
-1.40 x 100.9 x coil mm</v>
-      </c>
-      <c r="B642" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 304L/304-4301/4307 Coil, 2B,
-1.40 x 100.9 x coil mm
-Weight (Kg):1,612
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-2,075.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="643" xml:space="preserve">
-      <c r="A643" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 304L/304-4301/4307 Coil, 2B,
-1.40 x 100.9 x coil mm</v>
-      </c>
-      <c r="B643" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 304L/304-4301/4307 Coil, 2B,
-1.40 x 100.9 x coil mm
-Weight (Kg):1,600
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-2,075.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="644" xml:space="preserve">
-      <c r="A644" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 304-1.4301 Coil, Emboss Chequered,
-0.70 x 174.9 x coil mm</v>
-      </c>
-      <c r="B644" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 304-1.4301 Coil, Emboss Chequered,
-0.70 x 174.9 x coil mm
-Weight (Kg):1,494
-Quality:Prime
-Help
-Location:FABRICA ALGECIRAS
-2,075.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="645" xml:space="preserve">
-      <c r="A645" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 304-1.4301 Coil, Emboss Chequered,
-0.70 x 174.9 x coil mm</v>
-      </c>
-      <c r="B645" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 304-1.4301 Coil, Emboss Chequered,
-0.70 x 174.9 x coil mm
-Weight (Kg):1,472
-Quality:Prime
-Help
-Location:FABRICA ALGECIRAS
-2,075.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="646" xml:space="preserve">
-      <c r="A646" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, SB-G-240,
-0.50 x 290.9 x coil mm</v>
-      </c>
-      <c r="B646" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, SB-G-240,
-0.50 x 290.9 x coil mm
-Weight (Kg):4,408
-Quality:Prime
-Help
-Location:FABRICA ALGECIRAS
-1,000.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="647" xml:space="preserve">
-      <c r="A647" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 304-1.4301 Coil, BA,
-0.60 x 110.0 x coil mm</v>
-      </c>
-      <c r="B647" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 304-1.4301 Coil, BA,
-0.60 x 110.0 x coil mm
-Weight (Kg):1,032
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-2,075.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="648" xml:space="preserve">
-      <c r="A648" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 304-1.4301 Coil, BA,
-0.40 x 270.0 x coil mm</v>
-      </c>
-      <c r="B648" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 304-1.4301 Coil, BA,
-0.40 x 270.0 x coil mm
-Weight (Kg):3,124
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-2,075.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="649" xml:space="preserve">
-      <c r="A649" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 304-1.4301 Coil, BA,
-0.60 x 135.0 x coil mm</v>
-      </c>
-      <c r="B649" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 304-1.4301 Coil, BA,
-0.60 x 135.0 x coil mm
-Weight (Kg):2,078
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-2,075.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="650" xml:space="preserve">
-      <c r="A650" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 441-1.4509 Coil, 2B,
-2.00 x 245.9 x coil mm</v>
-      </c>
-      <c r="B650" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 441-1.4509 Coil, 2B,
-2.00 x 245.9 x coil mm
-Weight (Kg):3,492
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-1,100.00 €/ton
 Add to cart</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B650"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B601"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/scraped_data.xlsx
+++ b/scraped_data.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B601"/>
+  <dimension ref="A1:B621"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -410,73 +410,41 @@
     <row r="2" xml:space="preserve">
       <c r="A2" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4310 301-Coil, 2B,
-0.80 x 1128.0 x coil mm</v>
+0.80 x 1139.0 x coil mm</v>
       </c>
       <c r="B2" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4310 301-Coil, 2B,
-0.80 x 1128.0 x coil mm
-Weight (Kg):10,677
-Quality:Prime
-Help
-Location:FABRICA ALGECIRAS
-2,700.00 €/ton
+0.80 x 1139.0 x coil mm
+Weight (Kg):7,820
+Quality:Prime
+Help
+Location:FABRICA ALGECIRAS
+2,275.00 €/ton
 Add to cart</v>
       </c>
     </row>
     <row r="3" xml:space="preserve">
       <c r="A3" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4310 301-Coil, 2B,
-0.80 x 1139.0 x coil mm</v>
+1.00 x 1270.0 x coil mm</v>
       </c>
       <c r="B3" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4310 301-Coil, 2B,
-0.80 x 1139.0 x coil mm
-Weight (Kg):7,820
-Quality:Prime
-Help
-Location:FABRICA ALGECIRAS
-2,275.00 €/ton
+1.00 x 1270.0 x coil mm
+Weight (Kg):17,550
+Quality:Prime
+Help
+Location:FABRICA ALGECIRAS
+2,700.00 €/ton
 Add to cart</v>
       </c>
     </row>
     <row r="4" xml:space="preserve">
       <c r="A4" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4310 301-Coil, 2B,
-0.80 x 1288.0 x coil mm</v>
+1.50 x 625.0 x coil mm</v>
       </c>
       <c r="B4" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4310 301-Coil, 2B,
-0.80 x 1288.0 x coil mm
-Weight (Kg):20,316
-Quality:Prime
-Help
-Location:FABRICA ALGECIRAS
-2,700.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="5" xml:space="preserve">
-      <c r="A5" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4310 301-Coil, 2B,
-1.00 x 1270.0 x coil mm</v>
-      </c>
-      <c r="B5" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4310 301-Coil, 2B,
-1.00 x 1270.0 x coil mm
-Weight (Kg):17,550
-Quality:Prime
-Help
-Location:FABRICA ALGECIRAS
-2,700.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="6" xml:space="preserve">
-      <c r="A6" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4310 301-Coil, 2B,
-1.50 x 625.0 x coil mm</v>
-      </c>
-      <c r="B6" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4310 301-Coil, 2B,
 1.50 x 625.0 x coil mm
 Weight (Kg):950
@@ -487,60 +455,44 @@
 Add to cart</v>
       </c>
     </row>
+    <row r="5" xml:space="preserve">
+      <c r="A5" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4310 301-Coil, 2B,
+2.00 x 1279.0 x coil mm</v>
+      </c>
+      <c r="B5" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4310 301-Coil, 2B,
+2.00 x 1279.0 x coil mm
+Weight (Kg):23,630
+Quality:Prime
+Help
+Location:FABRICA ALGECIRAS
+2,700.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="6" xml:space="preserve">
+      <c r="A6" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4310 301-Coil, 2B,
+3.00 x 160.0 x coil mm</v>
+      </c>
+      <c r="B6" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4310 301-Coil, 2B,
+3.00 x 160.0 x coil mm
+Weight (Kg):2,678
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+1,925.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
     <row r="7" xml:space="preserve">
       <c r="A7" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4310 301-Coil, 2B,
-2.00 x 1279.0 x coil mm</v>
+3.00 x 180.9 x coil mm</v>
       </c>
       <c r="B7" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4310 301-Coil, 2B,
-2.00 x 1279.0 x coil mm
-Weight (Kg):23,630
-Quality:Prime
-Help
-Location:FABRICA ALGECIRAS
-2,700.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="8" xml:space="preserve">
-      <c r="A8" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4310 301-Coil, 2B,
-3.00 x 160.0 x coil mm</v>
-      </c>
-      <c r="B8" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4310 301-Coil, 2B,
-3.00 x 160.0 x coil mm
-Weight (Kg):2,880
-Quality:Prime
-Help
-Location:FABRICA ALGECIRAS
-1,925.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="9" xml:space="preserve">
-      <c r="A9" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4310 301-Coil, 2B,
-3.00 x 160.0 x coil mm</v>
-      </c>
-      <c r="B9" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4310 301-Coil, 2B,
-3.00 x 160.0 x coil mm
-Weight (Kg):2,678
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-1,925.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="10" xml:space="preserve">
-      <c r="A10" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4310 301-Coil, 2B,
-3.00 x 180.9 x coil mm</v>
-      </c>
-      <c r="B10" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4310 301-Coil, 2B,
 3.00 x 180.9 x coil mm
 Weight (Kg):3,078
@@ -551,28 +503,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="11" xml:space="preserve">
-      <c r="A11" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4310 301-Coil, 2D,
-0.80 x 1263.0 x coil mm</v>
-      </c>
-      <c r="B11" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4310 301-Coil, 2D,
-0.80 x 1263.0 x coil mm
-Weight (Kg):17,770
-Quality:Prime
-Help
-Location:FABRICA ALGECIRAS
-2,700.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="12" xml:space="preserve">
-      <c r="A12" t="str" xml:space="preserve">
+    <row r="8" xml:space="preserve">
+      <c r="A8" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4310 301-Coil, BA,
 0.40 x 120.9 x coil mm</v>
       </c>
-      <c r="B12" t="str" xml:space="preserve">
+      <c r="B8" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4310 301-Coil, BA,
 0.40 x 120.9 x coil mm
 Weight (Kg):886
@@ -583,12 +519,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="13" xml:space="preserve">
-      <c r="A13" t="str" xml:space="preserve">
+    <row r="9" xml:space="preserve">
+      <c r="A9" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4310 301-Coil, BA,
 0.40 x 1290.0 x coil mm</v>
       </c>
-      <c r="B13" t="str" xml:space="preserve">
+      <c r="B9" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4310 301-Coil, BA,
 0.40 x 1290.0 x coil mm
 Weight (Kg):9,500
@@ -599,12 +535,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="14" xml:space="preserve">
-      <c r="A14" t="str" xml:space="preserve">
+    <row r="10" xml:space="preserve">
+      <c r="A10" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4310 301-Coil, BA,
 0.40 x 140.9 x coil mm</v>
       </c>
-      <c r="B14" t="str" xml:space="preserve">
+      <c r="B10" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4310 301-Coil, BA,
 0.40 x 140.9 x coil mm
 Weight (Kg):922
@@ -615,12 +551,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="15" xml:space="preserve">
-      <c r="A15" t="str" xml:space="preserve">
+    <row r="11" xml:space="preserve">
+      <c r="A11" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4310 301-Coil, BA,
 0.40 x 150.9 x coil mm</v>
       </c>
-      <c r="B15" t="str" xml:space="preserve">
+      <c r="B11" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4310 301-Coil, BA,
 0.40 x 150.9 x coil mm
 Weight (Kg):912
@@ -631,12 +567,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="16" xml:space="preserve">
-      <c r="A16" t="str" xml:space="preserve">
+    <row r="12" xml:space="preserve">
+      <c r="A12" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4310 301-Coil, BA,
 0.40 x 170.0 x coil mm</v>
       </c>
-      <c r="B16" t="str" xml:space="preserve">
+      <c r="B12" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4310 301-Coil, BA,
 0.40 x 170.0 x coil mm
 Weight (Kg):1,694
@@ -647,12 +583,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="17" xml:space="preserve">
-      <c r="A17" t="str" xml:space="preserve">
+    <row r="13" xml:space="preserve">
+      <c r="A13" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4310 301-Coil, BA,
 0.40 x 180.9 x coil mm</v>
       </c>
-      <c r="B17" t="str" xml:space="preserve">
+      <c r="B13" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4310 301-Coil, BA,
 0.40 x 180.9 x coil mm
 Weight (Kg):1,401
@@ -663,12 +599,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="18" xml:space="preserve">
-      <c r="A18" t="str" xml:space="preserve">
+    <row r="14" xml:space="preserve">
+      <c r="A14" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4310 301-Coil, BA,
 0.40 x 190.0 x coil mm</v>
       </c>
-      <c r="B18" t="str" xml:space="preserve">
+      <c r="B14" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4310 301-Coil, BA,
 0.40 x 190.0 x coil mm
 Weight (Kg):1,034
@@ -679,12 +615,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="19" xml:space="preserve">
-      <c r="A19" t="str" xml:space="preserve">
+    <row r="15" xml:space="preserve">
+      <c r="A15" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4310 301-Coil, BA,
 0.40 x 520.0 x coil mm</v>
       </c>
-      <c r="B19" t="str" xml:space="preserve">
+      <c r="B15" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4310 301-Coil, BA,
 0.40 x 520.0 x coil mm
 Weight (Kg):4,059
@@ -695,12 +631,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="20" xml:space="preserve">
-      <c r="A20" t="str" xml:space="preserve">
+    <row r="16" xml:space="preserve">
+      <c r="A16" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4310 301-Coil, BA,
 0.40 x 536.5 x coil mm</v>
       </c>
-      <c r="B20" t="str" xml:space="preserve">
+      <c r="B16" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4310 301-Coil, BA,
 0.40 x 536.5 x coil mm
 Weight (Kg):2,565
@@ -711,12 +647,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="21" xml:space="preserve">
-      <c r="A21" t="str" xml:space="preserve">
+    <row r="17" xml:space="preserve">
+      <c r="A17" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4310 301-Coil, BA,
 0.40 x 536.5 x coil mm</v>
       </c>
-      <c r="B21" t="str" xml:space="preserve">
+      <c r="B17" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4310 301-Coil, BA,
 0.40 x 536.5 x coil mm
 Weight (Kg):2,738
@@ -725,6 +661,70 @@
 Location:FABRICA ALGECIRAS
 1,975.00 €/ton
 Add to cart</v>
+      </c>
+    </row>
+    <row r="18" xml:space="preserve">
+      <c r="A18" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4310 301-Coil, 2B,
+0.80 x 1128.0 x coil mm</v>
+      </c>
+      <c r="B18" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4310 301-Coil, 2B,
+0.80 x 1128.0 x coil mm
+Weight (Kg):10,677
+Quality:Prime
+Help
+Location:FABRICA ALGECIRAS
+2,700.00 €/ton
+Reserved</v>
+      </c>
+    </row>
+    <row r="19" xml:space="preserve">
+      <c r="A19" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4310 301-Coil, 2B,
+0.80 x 1288.0 x coil mm</v>
+      </c>
+      <c r="B19" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4310 301-Coil, 2B,
+0.80 x 1288.0 x coil mm
+Weight (Kg):20,316
+Quality:Prime
+Help
+Location:FABRICA ALGECIRAS
+2,700.00 €/ton
+Reserved</v>
+      </c>
+    </row>
+    <row r="20" xml:space="preserve">
+      <c r="A20" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4310 301-Coil, 2B,
+3.00 x 160.0 x coil mm</v>
+      </c>
+      <c r="B20" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4310 301-Coil, 2B,
+3.00 x 160.0 x coil mm
+Weight (Kg):2,880
+Quality:Prime
+Help
+Location:FABRICA ALGECIRAS
+1,925.00 €/ton
+Reserved</v>
+      </c>
+    </row>
+    <row r="21" xml:space="preserve">
+      <c r="A21" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4310 301-Coil, 2D,
+0.80 x 1263.0 x coil mm</v>
+      </c>
+      <c r="B21" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4310 301-Coil, 2D,
+0.80 x 1263.0 x coil mm
+Weight (Kg):17,770
+Quality:Prime
+Help
+Location:FABRICA ALGECIRAS
+2,700.00 €/ton
+Reserved</v>
       </c>
     </row>
     <row r="22" xml:space="preserve">
@@ -9305,10 +9305,26 @@
     </row>
     <row r="558" xml:space="preserve">
       <c r="A558" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4510 430Ti-Untrimmed, Coil, BA,
+0.50 x 1275.0 x coil mm</v>
+      </c>
+      <c r="B558" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4510 430Ti-Untrimmed, Coil, BA,
+0.50 x 1275.0 x coil mm
+Weight (Kg):2,258
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+1,125.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="559" xml:space="preserve">
+      <c r="A559" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Untrimmed, Coil, BA,
 0.50 x 1107.0 x coil mm</v>
       </c>
-      <c r="B558" t="str" xml:space="preserve">
+      <c r="B559" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Untrimmed, Coil, BA,
 0.50 x 1107.0 x coil mm
 Weight (Kg):2,230
@@ -9319,12 +9335,12 @@
 Reserved</v>
       </c>
     </row>
-    <row r="559" xml:space="preserve">
-      <c r="A559" t="str" xml:space="preserve">
+    <row r="560" xml:space="preserve">
+      <c r="A560" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Untrimmed, Coil, BA,
 0.60 x 1270.0 x coil mm</v>
       </c>
-      <c r="B559" t="str" xml:space="preserve">
+      <c r="B560" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Untrimmed, Coil, BA,
 0.60 x 1270.0 x coil mm
 Weight (Kg):3,385
@@ -9335,12 +9351,12 @@
 Reserved</v>
       </c>
     </row>
-    <row r="560" xml:space="preserve">
-      <c r="A560" t="str" xml:space="preserve">
+    <row r="561" xml:space="preserve">
+      <c r="A561" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Untrimmed, Coil, BA,
 0.60 x 1275.0 x coil mm</v>
       </c>
-      <c r="B560" t="str" xml:space="preserve">
+      <c r="B561" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Untrimmed, Coil, BA,
 0.60 x 1275.0 x coil mm
 Weight (Kg):3,535
@@ -9351,44 +9367,12 @@
 Reserved</v>
       </c>
     </row>
-    <row r="561" xml:space="preserve">
-      <c r="A561" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Untrimmed, Coil, BA,
-0.70 x 950.0 x coil mm</v>
-      </c>
-      <c r="B561" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Untrimmed, Coil, BA,
-0.70 x 950.0 x coil mm
-Weight (Kg):3,820
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-1,125.00 €/ton
-Out of Stock</v>
-      </c>
-    </row>
     <row r="562" xml:space="preserve">
       <c r="A562" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4510 430Ti-Untrimmed, Coil, BA,
-0.50 x 1275.0 x coil mm</v>
+0.70 x 928.0 x coil mm</v>
       </c>
       <c r="B562" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4510 430Ti-Untrimmed, Coil, BA,
-0.50 x 1275.0 x coil mm
-Weight (Kg):2,258
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-1,125.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="563" xml:space="preserve">
-      <c r="A563" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4510 430Ti-Untrimmed, Coil, BA,
-0.70 x 928.0 x coil mm</v>
-      </c>
-      <c r="B563" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4510 430Ti-Untrimmed, Coil, BA,
 0.70 x 928.0 x coil mm
 Weight (Kg):4,257
@@ -9399,12 +9383,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="564" xml:space="preserve">
-      <c r="A564" t="str" xml:space="preserve">
+    <row r="563" xml:space="preserve">
+      <c r="A563" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4509 441-Coil, 2B,
 1.20 x 275.9 x coil mm</v>
       </c>
-      <c r="B564" t="str" xml:space="preserve">
+      <c r="B563" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4509 441-Coil, 2B,
 1.20 x 275.9 x coil mm
 Weight (Kg):2,416
@@ -9415,15 +9399,31 @@
 Add to cart</v>
       </c>
     </row>
+    <row r="564" xml:space="preserve">
+      <c r="A564" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4509 441-Coil, 2D,
+1.20 x 196.0 x coil mm</v>
+      </c>
+      <c r="B564" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4509 441-Coil, 2D,
+1.20 x 196.0 x coil mm
+Weight (Kg):2,970
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+1,100.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
     <row r="565" xml:space="preserve">
       <c r="A565" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4509 441-Coil, 2D,
-1.20 x 196.0 x coil mm</v>
+1.20 x 200.0 x coil mm</v>
       </c>
       <c r="B565" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4509 441-Coil, 2D,
-1.20 x 196.0 x coil mm
-Weight (Kg):2,970
+1.20 x 200.0 x coil mm
+Weight (Kg):3,310
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -9434,12 +9434,12 @@
     <row r="566" xml:space="preserve">
       <c r="A566" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4509 441-Coil, 2D,
-1.20 x 200.0 x coil mm</v>
+1.20 x 214.9 x coil mm</v>
       </c>
       <c r="B566" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4509 441-Coil, 2D,
-1.20 x 200.0 x coil mm
-Weight (Kg):3,310
+1.20 x 214.9 x coil mm
+Weight (Kg):3,220
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -9450,12 +9450,12 @@
     <row r="567" xml:space="preserve">
       <c r="A567" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4509 441-Coil, 2D,
-1.20 x 214.9 x coil mm</v>
+1.20 x 223.9 x coil mm</v>
       </c>
       <c r="B567" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4509 441-Coil, 2D,
-1.20 x 214.9 x coil mm
-Weight (Kg):3,220
+1.20 x 223.9 x coil mm
+Weight (Kg):3,798
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -9466,28 +9466,28 @@
     <row r="568" xml:space="preserve">
       <c r="A568" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4509 441-Coil, 2D,
-1.20 x 223.9 x coil mm</v>
+1.20 x 224.0 x coil mm</v>
       </c>
       <c r="B568" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4509 441-Coil, 2D,
-1.20 x 223.9 x coil mm
-Weight (Kg):3,798
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-1,100.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="569" xml:space="preserve">
-      <c r="A569" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4509 441-Coil, 2D,
-1.20 x 224.0 x coil mm</v>
-      </c>
-      <c r="B569" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4509 441-Coil, 2D,
 1.20 x 224.0 x coil mm
 Weight (Kg):3,808
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+1,100.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="569" xml:space="preserve">
+      <c r="A569" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4509 441-Coil, BA,
+0.80 x 130.9 x coil mm</v>
+      </c>
+      <c r="B569" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4509 441-Coil, BA,
+0.80 x 130.9 x coil mm
+Weight (Kg):245
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -9519,7 +9519,7 @@
       <c r="B571" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4509 441-Coil, BA,
 0.80 x 130.9 x coil mm
-Weight (Kg):245
+Weight (Kg):213
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -9535,7 +9535,7 @@
       <c r="B572" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4509 441-Coil, BA,
 0.80 x 130.9 x coil mm
-Weight (Kg):213
+Weight (Kg):244
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -9545,45 +9545,45 @@
     </row>
     <row r="573" xml:space="preserve">
       <c r="A573" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4509 441-Coil, BA,
-0.80 x 130.9 x coil mm</v>
+        <v xml:space="preserve">Acerinox Europa, 1.4509 441-Coil, SB-G-400,
+1.00 x 1000.0 x coil mm</v>
       </c>
       <c r="B573" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4509 441-Coil, BA,
-0.80 x 130.9 x coil mm
-Weight (Kg):244
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-1,100.00 €/ton
+        <v xml:space="preserve">Acerinox Europa, 1.4509 441-Coil, SB-G-400,
+1.00 x 1000.0 x coil mm
+Weight (Kg):7,550
+Quality:Prime
+Help
+Location:FABRICA ALGECIRAS
+1,625.00 €/ton
 Add to cart</v>
       </c>
     </row>
     <row r="574" xml:space="preserve">
       <c r="A574" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4509 441-Coil, SB-G-400,
-1.00 x 1000.0 x coil mm</v>
+1.00 x 255.0 x coil mm</v>
       </c>
       <c r="B574" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4509 441-Coil, SB-G-400,
-1.00 x 1000.0 x coil mm
-Weight (Kg):7,550
-Quality:Prime
-Help
-Location:FABRICA ALGECIRAS
-1,625.00 €/ton
+1.00 x 255.0 x coil mm
+Weight (Kg):2,182
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+1,100.00 €/ton
 Add to cart</v>
       </c>
     </row>
     <row r="575" xml:space="preserve">
       <c r="A575" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4509 441-Coil, SB-G-400,
-1.00 x 255.0 x coil mm</v>
+1.00 x 290.9 x coil mm</v>
       </c>
       <c r="B575" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4509 441-Coil, SB-G-400,
-1.00 x 255.0 x coil mm
-Weight (Kg):2,182
+1.00 x 290.9 x coil mm
+Weight (Kg):2,370
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -9594,12 +9594,12 @@
     <row r="576" xml:space="preserve">
       <c r="A576" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4509 441-Coil, SB-G-400,
-1.00 x 290.9 x coil mm</v>
+1.20 x 110.9 x coil mm</v>
       </c>
       <c r="B576" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4509 441-Coil, SB-G-400,
-1.00 x 290.9 x coil mm
-Weight (Kg):2,370
+1.20 x 110.9 x coil mm
+Weight (Kg):856
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -9610,12 +9610,12 @@
     <row r="577" xml:space="preserve">
       <c r="A577" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4509 441-Coil, SB-G-400,
-1.20 x 110.9 x coil mm</v>
+1.20 x 130.9 x coil mm</v>
       </c>
       <c r="B577" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4509 441-Coil, SB-G-400,
-1.20 x 110.9 x coil mm
-Weight (Kg):856
+1.20 x 130.9 x coil mm
+Weight (Kg):564
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -9631,8 +9631,8 @@
       <c r="B578" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4509 441-Coil, SB-G-400,
 1.20 x 130.9 x coil mm
-Weight (Kg):564
-Quality:Prime-2
+Weight (Kg):532
+Quality:Prime
 Help
 Location:FABRICA ALGECIRAS
 1,100.00 €/ton
@@ -9642,13 +9642,13 @@
     <row r="579" xml:space="preserve">
       <c r="A579" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4509 441-Coil, SB-G-400,
-1.20 x 130.9 x coil mm</v>
+1.50 x 130.9 x coil mm</v>
       </c>
       <c r="B579" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4509 441-Coil, SB-G-400,
-1.20 x 130.9 x coil mm
-Weight (Kg):532
-Quality:Prime
+1.50 x 130.9 x coil mm
+Weight (Kg):640
+Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
 1,100.00 €/ton
@@ -9658,13 +9658,13 @@
     <row r="580" xml:space="preserve">
       <c r="A580" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4509 441-Coil, SB-G-400,
-1.50 x 130.9 x coil mm</v>
+1.50 x 360.0 x coil mm</v>
       </c>
       <c r="B580" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4509 441-Coil, SB-G-400,
-1.50 x 130.9 x coil mm
-Weight (Kg):640
-Quality:Prime-2
+1.50 x 360.0 x coil mm
+Weight (Kg):1,488
+Quality:Downgraded
 Help
 Location:FABRICA ALGECIRAS
 1,100.00 €/ton
@@ -9689,26 +9689,10 @@
     </row>
     <row r="582" xml:space="preserve">
       <c r="A582" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4509 441-Coil, SB-G-400,
-1.50 x 360.0 x coil mm</v>
-      </c>
-      <c r="B582" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4509 441-Coil, SB-G-400,
-1.50 x 360.0 x coil mm
-Weight (Kg):1,488
-Quality:Downgraded
-Help
-Location:FABRICA ALGECIRAS
-1,100.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="583" xml:space="preserve">
-      <c r="A583" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4509 441-Untrimmed, Coil, 2B,
 1.50 x 1539.0 x coil mm</v>
       </c>
-      <c r="B583" t="str" xml:space="preserve">
+      <c r="B582" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4509 441-Untrimmed, Coil, 2B,
 1.50 x 1539.0 x coil mm
 Weight (Kg):14,230
@@ -9719,12 +9703,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="584" xml:space="preserve">
-      <c r="A584" t="str" xml:space="preserve">
+    <row r="583" xml:space="preserve">
+      <c r="A583" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4509 441-Untrimmed, Coil, BA,
 0.40 x 1075.0 x coil mm</v>
       </c>
-      <c r="B584" t="str" xml:space="preserve">
+      <c r="B583" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4509 441-Untrimmed, Coil, BA,
 0.40 x 1075.0 x coil mm
 Weight (Kg):9,750
@@ -9735,12 +9719,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="585" xml:space="preserve">
-      <c r="A585" t="str" xml:space="preserve">
+    <row r="584" xml:space="preserve">
+      <c r="A584" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4509 441-Untrimmed, Coil, Nb. 1,
 5.00 x 1045.0 x coil mm</v>
       </c>
-      <c r="B585" t="str" xml:space="preserve">
+      <c r="B584" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4509 441-Untrimmed, Coil, Nb. 1,
 5.00 x 1045.0 x coil mm
 Weight (Kg):7,880
@@ -9751,12 +9735,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="586" xml:space="preserve">
-      <c r="A586" t="str" xml:space="preserve">
+    <row r="585" xml:space="preserve">
+      <c r="A585" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 441-1.4509 Coil, 2B,
 1.20 x 240.9 x coil mm</v>
       </c>
-      <c r="B586" t="str" xml:space="preserve">
+      <c r="B585" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 441-1.4509 Coil, 2B,
 1.20 x 240.9 x coil mm
 Weight (Kg):3,882
@@ -9767,12 +9751,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="587" xml:space="preserve">
-      <c r="A587" t="str" xml:space="preserve">
+    <row r="586" xml:space="preserve">
+      <c r="A586" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 304-1.4301 Coil,
 0.70 x 270.9 x coil mm</v>
       </c>
-      <c r="B587" t="str" xml:space="preserve">
+      <c r="B586" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 304-1.4301 Coil,
 0.70 x 270.9 x coil mm
 Weight (Kg):2,704
@@ -9783,12 +9767,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="588" xml:space="preserve">
-      <c r="A588" t="str" xml:space="preserve">
+    <row r="587" xml:space="preserve">
+      <c r="A587" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 316L-1.4404 Coil,
 1.20 x 136.0 x coil mm</v>
       </c>
-      <c r="B588" t="str" xml:space="preserve">
+      <c r="B587" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 316L-1.4404 Coil,
 1.20 x 136.0 x coil mm
 Weight (Kg):2,300
@@ -9799,12 +9783,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="589" xml:space="preserve">
-      <c r="A589" t="str" xml:space="preserve">
+    <row r="588" xml:space="preserve">
+      <c r="A588" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 304L/304-4301/4307 Coil, 2B,
 6.00 x 245.0 x coil mm</v>
       </c>
-      <c r="B589" t="str" xml:space="preserve">
+      <c r="B588" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 304L/304-4301/4307 Coil, 2B,
 6.00 x 245.0 x coil mm
 Weight (Kg):2,394
@@ -9815,12 +9799,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="590" xml:space="preserve">
-      <c r="A590" t="str" xml:space="preserve">
+    <row r="589" xml:space="preserve">
+      <c r="A589" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, 2B,
 0.70 x 197.5 x coil mm</v>
       </c>
-      <c r="B590" t="str" xml:space="preserve">
+      <c r="B589" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, 2B,
 0.70 x 197.5 x coil mm
 Weight (Kg):2,442
@@ -9831,12 +9815,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="591" xml:space="preserve">
-      <c r="A591" t="str" xml:space="preserve">
+    <row r="590" xml:space="preserve">
+      <c r="A590" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 441-1.4509 Coil, 2B,
 2.00 x 120.9 x coil mm</v>
       </c>
-      <c r="B591" t="str" xml:space="preserve">
+      <c r="B590" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 441-1.4509 Coil, 2B,
 2.00 x 120.9 x coil mm
 Weight (Kg):1,956
@@ -9844,6 +9828,22 @@
 Help
 Location:FABRICA ALGECIRAS
 1,100.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="591" xml:space="preserve">
+      <c r="A591" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 304-1.4301 Coil, 2B,
+1.20 x 119.9 x coil mm</v>
+      </c>
+      <c r="B591" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 304-1.4301 Coil, 2B,
+1.20 x 119.9 x coil mm
+Weight (Kg):1,500
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,075.00 €/ton
 Add to cart</v>
       </c>
     </row>
@@ -9855,7 +9855,7 @@
       <c r="B592" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 304-1.4301 Coil, 2B,
 1.20 x 119.9 x coil mm
-Weight (Kg):1,500
+Weight (Kg):1,400
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -9865,29 +9865,29 @@
     </row>
     <row r="593" xml:space="preserve">
       <c r="A593" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 304-1.4301 Coil, 2B,
-1.20 x 119.9 x coil mm</v>
+        <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, BA,
+0.70 x 125.0 x coil mm</v>
       </c>
       <c r="B593" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 304-1.4301 Coil, 2B,
-1.20 x 119.9 x coil mm
-Weight (Kg):1,400
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-2,075.00 €/ton
+        <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, BA,
+0.70 x 125.0 x coil mm
+Weight (Kg):1,764
+Quality:Prime
+Help
+Location:FABRICA ALGECIRAS
+1,000.00 €/ton
 Add to cart</v>
       </c>
     </row>
     <row r="594" xml:space="preserve">
       <c r="A594" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, BA,
-0.70 x 125.0 x coil mm</v>
+0.70 x 104.9 x coil mm</v>
       </c>
       <c r="B594" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, BA,
-0.70 x 125.0 x coil mm
-Weight (Kg):1,764
+0.70 x 104.9 x coil mm
+Weight (Kg):1,240
 Quality:Prime
 Help
 Location:FABRICA ALGECIRAS
@@ -9898,12 +9898,12 @@
     <row r="595" xml:space="preserve">
       <c r="A595" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, BA,
-0.70 x 104.9 x coil mm</v>
+0.70 x 118.9 x coil mm</v>
       </c>
       <c r="B595" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, BA,
-0.70 x 104.9 x coil mm
-Weight (Kg):1,240
+0.70 x 118.9 x coil mm
+Weight (Kg):1,802
 Quality:Prime
 Help
 Location:FABRICA ALGECIRAS
@@ -9914,12 +9914,12 @@
     <row r="596" xml:space="preserve">
       <c r="A596" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, BA,
-0.70 x 118.9 x coil mm</v>
+0.70 x 115.9 x coil mm</v>
       </c>
       <c r="B596" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, BA,
-0.70 x 118.9 x coil mm
-Weight (Kg):1,802
+0.70 x 115.9 x coil mm
+Weight (Kg):1,368
 Quality:Prime
 Help
 Location:FABRICA ALGECIRAS
@@ -9930,25 +9930,9 @@
     <row r="597" xml:space="preserve">
       <c r="A597" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, BA,
-0.70 x 115.9 x coil mm</v>
+0.70 x 119.0 x coil mm</v>
       </c>
       <c r="B597" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, BA,
-0.70 x 115.9 x coil mm
-Weight (Kg):1,368
-Quality:Prime
-Help
-Location:FABRICA ALGECIRAS
-1,000.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="598" xml:space="preserve">
-      <c r="A598" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, BA,
-0.70 x 119.0 x coil mm</v>
-      </c>
-      <c r="B598" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, BA,
 0.70 x 119.0 x coil mm
 Weight (Kg):1,622
@@ -9959,12 +9943,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="599" xml:space="preserve">
-      <c r="A599" t="str" xml:space="preserve">
+    <row r="598" xml:space="preserve">
+      <c r="A598" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 304L/304-4301/4307 Coil, 2B,
 1.40 x 110.9 x coil mm</v>
       </c>
-      <c r="B599" t="str" xml:space="preserve">
+      <c r="B598" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 304L/304-4301/4307 Coil, 2B,
 1.40 x 110.9 x coil mm
 Weight (Kg):1,240
@@ -9972,6 +9956,22 @@
 Help
 Location:FABRICA ALGECIRAS
 2,075.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="599" xml:space="preserve">
+      <c r="A599" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, BA,
+0.70 x 104.0 x coil mm</v>
+      </c>
+      <c r="B599" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, BA,
+0.70 x 104.0 x coil mm
+Weight (Kg):1,622
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+1,000.00 €/ton
 Add to cart</v>
       </c>
     </row>
@@ -9983,7 +9983,7 @@
       <c r="B600" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, BA,
 0.70 x 104.0 x coil mm
-Weight (Kg):1,622
+Weight (Kg):1,688
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -9993,23 +9993,343 @@
     </row>
     <row r="601" xml:space="preserve">
       <c r="A601" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 304L/304-4301/4307 Coil, 2B,
+1.40 x 110.9 x coil mm</v>
+      </c>
+      <c r="B601" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 304L/304-4301/4307 Coil, 2B,
+1.40 x 110.9 x coil mm
+Weight (Kg):1,162
+Quality:Prime
+Help
+Location:FABRICA ALGECIRAS
+2,075.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="602" xml:space="preserve">
+      <c r="A602" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 430Ti-1.4510 Coil, BA,
+0.70 x 165.9 x coil mm</v>
+      </c>
+      <c r="B602" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 430Ti-1.4510 Coil, BA,
+0.70 x 165.9 x coil mm
+Weight (Kg):2,692
+Quality:Prime
+Help
+Location:FABRICA ALGECIRAS
+1,000.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="603" xml:space="preserve">
+      <c r="A603" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 430Ti-1.4510 Coil, BA,
+0.70 x 165.9 x coil mm</v>
+      </c>
+      <c r="B603" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 430Ti-1.4510 Coil, BA,
+0.70 x 165.9 x coil mm
+Weight (Kg):2,756
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+1,000.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="604" xml:space="preserve">
+      <c r="A604" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, BA,
-0.70 x 104.0 x coil mm</v>
-      </c>
-      <c r="B601" t="str" xml:space="preserve">
+0.70 x 140.9 x coil mm</v>
+      </c>
+      <c r="B604" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, BA,
-0.70 x 104.0 x coil mm
-Weight (Kg):1,688
+0.70 x 140.9 x coil mm
+Weight (Kg):1,676
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
 1,000.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="605" xml:space="preserve">
+      <c r="A605" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, BA,
+0.70 x 100.9 x coil mm</v>
+      </c>
+      <c r="B605" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, BA,
+0.70 x 100.9 x coil mm
+Weight (Kg):1,340
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+1,000.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="606" xml:space="preserve">
+      <c r="A606" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, BA,
+0.70 x 125.0 x coil mm</v>
+      </c>
+      <c r="B606" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, BA,
+0.70 x 125.0 x coil mm
+Weight (Kg):1,550
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+1,000.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="607" xml:space="preserve">
+      <c r="A607" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, BA,
+0.70 x 125.0 x coil mm</v>
+      </c>
+      <c r="B607" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, BA,
+0.70 x 125.0 x coil mm
+Weight (Kg):1,414
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+1,000.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="608" xml:space="preserve">
+      <c r="A608" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, BA,
+0.70 x 100.9 x coil mm</v>
+      </c>
+      <c r="B608" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, BA,
+0.70 x 100.9 x coil mm
+Weight (Kg):2,188
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+1,000.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="609" xml:space="preserve">
+      <c r="A609" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 304L/304-4301/4307 Coil, Nb. 1,
+4.70 x 110.0 x coil mm</v>
+      </c>
+      <c r="B609" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 304L/304-4301/4307 Coil, Nb. 1,
+4.70 x 110.0 x coil mm
+Weight (Kg):1,796
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+1,975.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="610" xml:space="preserve">
+      <c r="A610" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 304L/304-4301/4307 Coil, Nb. 1,
+4.70 x 110.0 x coil mm</v>
+      </c>
+      <c r="B610" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 304L/304-4301/4307 Coil, Nb. 1,
+4.70 x 110.0 x coil mm
+Weight (Kg):2,038
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+1,975.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="611" xml:space="preserve">
+      <c r="A611" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, BA,
+0.70 x 165.9 x coil mm</v>
+      </c>
+      <c r="B611" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, BA,
+0.70 x 165.9 x coil mm
+Weight (Kg):2,620
+Quality:Prime
+Help
+Location:FABRICA ALGECIRAS
+1,000.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="612" xml:space="preserve">
+      <c r="A612" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 304-1.4301 Coil,
+0.70 x 260.9 x coil mm</v>
+      </c>
+      <c r="B612" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 304-1.4301 Coil,
+0.70 x 260.9 x coil mm
+Weight (Kg):1,330
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,075.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="613" xml:space="preserve">
+      <c r="A613" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 304-1.4301 Coil,
+0.70 x 260.9 x coil mm</v>
+      </c>
+      <c r="B613" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 304-1.4301 Coil,
+0.70 x 260.9 x coil mm
+Weight (Kg):1,264
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,075.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="614" xml:space="preserve">
+      <c r="A614" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, BA,
+0.70 x 110.0 x coil mm</v>
+      </c>
+      <c r="B614" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, BA,
+0.70 x 110.0 x coil mm
+Weight (Kg):1,250
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+1,000.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="615" xml:space="preserve">
+      <c r="A615" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, BA,
+0.70 x 122.9 x coil mm</v>
+      </c>
+      <c r="B615" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, BA,
+0.70 x 122.9 x coil mm
+Weight (Kg):1,460
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+1,000.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="616" xml:space="preserve">
+      <c r="A616" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 304L/304-4301/4307 Coil, 2B,
+1.40 x 110.0 x coil mm</v>
+      </c>
+      <c r="B616" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 304L/304-4301/4307 Coil, 2B,
+1.40 x 110.0 x coil mm
+Weight (Kg):1,554
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,075.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="617" xml:space="preserve">
+      <c r="A617" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 304L/304-4301/4307 Coil, 2B,
+1.40 x 110.0 x coil mm</v>
+      </c>
+      <c r="B617" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 304L/304-4301/4307 Coil, 2B,
+1.40 x 110.0 x coil mm
+Weight (Kg):1,586
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,075.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="618" xml:space="preserve">
+      <c r="A618" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 304L/304-4301/4307 Coil, 2B,
+1.40 x 104.0 x coil mm</v>
+      </c>
+      <c r="B618" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 304L/304-4301/4307 Coil, 2B,
+1.40 x 104.0 x coil mm
+Weight (Kg):1,030
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,075.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="619" xml:space="preserve">
+      <c r="A619" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 304DDQ-1.4301 Coil, BA,
+0.70 x 181.9 x coil mm</v>
+      </c>
+      <c r="B619" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 304DDQ-1.4301 Coil, BA,
+0.70 x 181.9 x coil mm
+Weight (Kg):2,912
+Quality:Prime
+Help
+Location:FABRICA ALGECIRAS
+2,075.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="620" xml:space="preserve">
+      <c r="A620" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 304-1.4301 Coil,
+1.50 x 136.0 x coil mm</v>
+      </c>
+      <c r="B620" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 304-1.4301 Coil,
+1.50 x 136.0 x coil mm
+Weight (Kg):3,450
+Quality:Prime
+Help
+Location:FABRICA ALGECIRAS
+2,075.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="621" xml:space="preserve">
+      <c r="A621" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 304-1.4301 Coil, BA,
+0.40 x 200.0 x coil mm</v>
+      </c>
+      <c r="B621" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 304-1.4301 Coil, BA,
+0.40 x 200.0 x coil mm
+Weight (Kg):1,964
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,075.00 €/ton
 Add to cart</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B601"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B621"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/scraped_data.xlsx
+++ b/scraped_data.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B621"/>
+  <dimension ref="A1:B648"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -10327,9 +10327,441 @@
 Add to cart</v>
       </c>
     </row>
+    <row r="622" xml:space="preserve">
+      <c r="A622" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 304-1.4301 Coil, BA, ET-60
+0.60 x 120.0 x coil mm</v>
+      </c>
+      <c r="B622" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 304-1.4301 Coil, BA, ET-60
+0.60 x 120.0 x coil mm
+Weight (Kg):1,302
+Quality:Prime
+Help
+Location:FABRICA ALGECIRAS
+2,075.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="623" xml:space="preserve">
+      <c r="A623" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, ET-100
+0.70 x 124.9 x coil mm</v>
+      </c>
+      <c r="B623" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, ET-100
+0.70 x 124.9 x coil mm
+Weight (Kg):2,106
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+1,000.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="624" xml:space="preserve">
+      <c r="A624" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, ET-100
+0.70 x 124.9 x coil mm</v>
+      </c>
+      <c r="B624" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, ET-100
+0.70 x 124.9 x coil mm
+Weight (Kg):1,972
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+1,000.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="625" xml:space="preserve">
+      <c r="A625" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 430Ti-1.4510 Coil, 2B,
+0.80 x 155.9 x coil mm</v>
+      </c>
+      <c r="B625" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 430Ti-1.4510 Coil, 2B,
+0.80 x 155.9 x coil mm
+Weight (Kg):1,586
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+1,000.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="626" xml:space="preserve">
+      <c r="A626" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 304-1.4301 Coil, BA,
+0.40 x 270.0 x coil mm</v>
+      </c>
+      <c r="B626" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 304-1.4301 Coil, BA,
+0.40 x 270.0 x coil mm
+Weight (Kg):2,572
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,075.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="627" xml:space="preserve">
+      <c r="A627" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, BA,
+0.60 x 130.0 x coil mm</v>
+      </c>
+      <c r="B627" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, BA,
+0.60 x 130.0 x coil mm
+Weight (Kg):1,490
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+1,000.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="628" xml:space="preserve">
+      <c r="A628" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 441-1.4509 Coil, BA,
+0.40 x 110.0 x coil mm</v>
+      </c>
+      <c r="B628" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 441-1.4509 Coil, BA,
+0.40 x 110.0 x coil mm
+Weight (Kg):1,870
+Quality:Prime
+Help
+Location:FABRICA ALGECIRAS
+1,100.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="629" xml:space="preserve">
+      <c r="A629" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 441-1.4509 Coil, BA,
+0.40 x 110.0 x coil mm</v>
+      </c>
+      <c r="B629" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 441-1.4509 Coil, BA,
+0.40 x 110.0 x coil mm
+Weight (Kg):1,882
+Quality:Prime
+Help
+Location:FABRICA ALGECIRAS
+1,100.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="630" xml:space="preserve">
+      <c r="A630" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 301-1.4310 Coil, BA,
+0.40 x 110.0 x coil mm</v>
+      </c>
+      <c r="B630" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 301-1.4310 Coil, BA,
+0.40 x 110.0 x coil mm
+Weight (Kg):1,934
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+1,925.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="631" xml:space="preserve">
+      <c r="A631" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 301-1.4310 Coil, BA,
+0.40 x 110.0 x coil mm</v>
+      </c>
+      <c r="B631" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 301-1.4310 Coil, BA,
+0.40 x 110.0 x coil mm
+Weight (Kg):1,860
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+1,925.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="632" xml:space="preserve">
+      <c r="A632" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 321-1.4541 Coil, 2B,
+1.90 x 104.5 x coil mm</v>
+      </c>
+      <c r="B632" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 321-1.4541 Coil, 2B,
+1.90 x 104.5 x coil mm
+Weight (Kg):2,304
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,235.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="633" xml:space="preserve">
+      <c r="A633" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 304L/304-4301/4307 Coil, Polished N4-G-180,
+1.20 x 255.9 x coil mm</v>
+      </c>
+      <c r="B633" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 304L/304-4301/4307 Coil, Polished N4-G-180,
+1.20 x 255.9 x coil mm
+Weight (Kg):4,298
+Quality:Prime
+Help
+Location:FABRICA ALGECIRAS
+2,075.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="634" xml:space="preserve">
+      <c r="A634" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 301-1.4310 Coil, BA,
+0.40 x 110.0 x coil mm</v>
+      </c>
+      <c r="B634" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 301-1.4310 Coil, BA,
+0.40 x 110.0 x coil mm
+Weight (Kg):1,698
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+1,925.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="635" xml:space="preserve">
+      <c r="A635" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, BA,
+0.40 x 130.0 x coil mm</v>
+      </c>
+      <c r="B635" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, BA,
+0.40 x 130.0 x coil mm
+Weight (Kg):1,916
+Quality:Prime
+Help
+Location:FABRICA ALGECIRAS
+1,000.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="636" xml:space="preserve">
+      <c r="A636" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 430Ti-1.4510 Coil, BA,
+0.50 x 140.0 x coil mm</v>
+      </c>
+      <c r="B636" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 430Ti-1.4510 Coil, BA,
+0.50 x 140.0 x coil mm
+Weight (Kg):3,054
+Quality:Prime
+Help
+Location:FABRICA ALGECIRAS
+1,000.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="637" xml:space="preserve">
+      <c r="A637" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 430Ti-1.4510 Coil, BA,
+0.50 x 140.0 x coil mm</v>
+      </c>
+      <c r="B637" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 430Ti-1.4510 Coil, BA,
+0.50 x 140.0 x coil mm
+Weight (Kg):3,060
+Quality:Prime
+Help
+Location:FABRICA ALGECIRAS
+1,000.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="638" xml:space="preserve">
+      <c r="A638" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 430Ti-1.4510 Coil, BA,
+0.50 x 140.0 x coil mm</v>
+      </c>
+      <c r="B638" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 430Ti-1.4510 Coil, BA,
+0.50 x 140.0 x coil mm
+Weight (Kg):2,220
+Quality:Prime
+Help
+Location:FABRICA ALGECIRAS
+1,000.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="639" xml:space="preserve">
+      <c r="A639" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 430Ti-1.4510 Coil, BA,
+0.50 x 140.0 x coil mm</v>
+      </c>
+      <c r="B639" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 430Ti-1.4510 Coil, BA,
+0.50 x 140.0 x coil mm
+Weight (Kg):2,224
+Quality:Prime
+Help
+Location:FABRICA ALGECIRAS
+1,000.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="640" xml:space="preserve">
+      <c r="A640" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 304L/304-4301/4307 Coil, 2B,
+1.40 x 100.9 x coil mm</v>
+      </c>
+      <c r="B640" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 304L/304-4301/4307 Coil, 2B,
+1.40 x 100.9 x coil mm
+Weight (Kg):1,612
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,075.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="641" xml:space="preserve">
+      <c r="A641" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 304L/304-4301/4307 Coil, 2B,
+1.40 x 100.9 x coil mm</v>
+      </c>
+      <c r="B641" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 304L/304-4301/4307 Coil, 2B,
+1.40 x 100.9 x coil mm
+Weight (Kg):1,600
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,075.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="642" xml:space="preserve">
+      <c r="A642" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 304-1.4301 Coil, Emboss Chequered,
+0.70 x 174.9 x coil mm</v>
+      </c>
+      <c r="B642" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 304-1.4301 Coil, Emboss Chequered,
+0.70 x 174.9 x coil mm
+Weight (Kg):1,494
+Quality:Prime
+Help
+Location:FABRICA ALGECIRAS
+2,075.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="643" xml:space="preserve">
+      <c r="A643" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 304-1.4301 Coil, Emboss Chequered,
+0.70 x 174.9 x coil mm</v>
+      </c>
+      <c r="B643" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 304-1.4301 Coil, Emboss Chequered,
+0.70 x 174.9 x coil mm
+Weight (Kg):1,472
+Quality:Prime
+Help
+Location:FABRICA ALGECIRAS
+2,075.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="644" xml:space="preserve">
+      <c r="A644" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, SB-G-240,
+0.50 x 290.9 x coil mm</v>
+      </c>
+      <c r="B644" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, SB-G-240,
+0.50 x 290.9 x coil mm
+Weight (Kg):4,408
+Quality:Prime
+Help
+Location:FABRICA ALGECIRAS
+1,000.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="645" xml:space="preserve">
+      <c r="A645" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 304-1.4301 Coil, BA,
+0.60 x 110.0 x coil mm</v>
+      </c>
+      <c r="B645" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 304-1.4301 Coil, BA,
+0.60 x 110.0 x coil mm
+Weight (Kg):1,032
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,075.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="646" xml:space="preserve">
+      <c r="A646" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 304-1.4301 Coil, BA,
+0.40 x 270.0 x coil mm</v>
+      </c>
+      <c r="B646" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 304-1.4301 Coil, BA,
+0.40 x 270.0 x coil mm
+Weight (Kg):3,124
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,075.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="647" xml:space="preserve">
+      <c r="A647" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 304-1.4301 Coil, BA,
+0.60 x 135.0 x coil mm</v>
+      </c>
+      <c r="B647" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 304-1.4301 Coil, BA,
+0.60 x 135.0 x coil mm
+Weight (Kg):2,078
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,075.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="648" xml:space="preserve">
+      <c r="A648" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 441-1.4509 Coil, 2B,
+2.00 x 245.9 x coil mm</v>
+      </c>
+      <c r="B648" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 441-1.4509 Coil, 2B,
+2.00 x 245.9 x coil mm
+Weight (Kg):3,492
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+1,100.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B621"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B648"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/scraped_data.xlsx
+++ b/scraped_data.xlsx
@@ -410,9 +410,25 @@
     <row r="2" xml:space="preserve">
       <c r="A2" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4310 301-Coil, 2B,
+0.80 x 1128.0 x coil mm</v>
+      </c>
+      <c r="B2" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4310 301-Coil, 2B,
+0.80 x 1128.0 x coil mm
+Weight (Kg):10,677
+Quality:Prime
+Help
+Location:FABRICA ALGECIRAS
+2,700.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="3" xml:space="preserve">
+      <c r="A3" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4310 301-Coil, 2B,
 0.80 x 1139.0 x coil mm</v>
       </c>
-      <c r="B2" t="str" xml:space="preserve">
+      <c r="B3" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4310 301-Coil, 2B,
 0.80 x 1139.0 x coil mm
 Weight (Kg):7,820
@@ -423,12 +439,28 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="3" xml:space="preserve">
-      <c r="A3" t="str" xml:space="preserve">
+    <row r="4" xml:space="preserve">
+      <c r="A4" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4310 301-Coil, 2B,
+0.80 x 1288.0 x coil mm</v>
+      </c>
+      <c r="B4" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4310 301-Coil, 2B,
+0.80 x 1288.0 x coil mm
+Weight (Kg):20,316
+Quality:Prime
+Help
+Location:FABRICA ALGECIRAS
+2,700.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="5" xml:space="preserve">
+      <c r="A5" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4310 301-Coil, 2B,
 1.00 x 1270.0 x coil mm</v>
       </c>
-      <c r="B3" t="str" xml:space="preserve">
+      <c r="B5" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4310 301-Coil, 2B,
 1.00 x 1270.0 x coil mm
 Weight (Kg):17,550
@@ -439,12 +471,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="4" xml:space="preserve">
-      <c r="A4" t="str" xml:space="preserve">
+    <row r="6" xml:space="preserve">
+      <c r="A6" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4310 301-Coil, 2B,
 1.50 x 625.0 x coil mm</v>
       </c>
-      <c r="B4" t="str" xml:space="preserve">
+      <c r="B6" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4310 301-Coil, 2B,
 1.50 x 625.0 x coil mm
 Weight (Kg):950
@@ -455,12 +487,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="5" xml:space="preserve">
-      <c r="A5" t="str" xml:space="preserve">
+    <row r="7" xml:space="preserve">
+      <c r="A7" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4310 301-Coil, 2B,
 2.00 x 1279.0 x coil mm</v>
       </c>
-      <c r="B5" t="str" xml:space="preserve">
+      <c r="B7" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4310 301-Coil, 2B,
 2.00 x 1279.0 x coil mm
 Weight (Kg):23,630
@@ -471,12 +503,28 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="6" xml:space="preserve">
-      <c r="A6" t="str" xml:space="preserve">
+    <row r="8" xml:space="preserve">
+      <c r="A8" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4310 301-Coil, 2B,
 3.00 x 160.0 x coil mm</v>
       </c>
-      <c r="B6" t="str" xml:space="preserve">
+      <c r="B8" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4310 301-Coil, 2B,
+3.00 x 160.0 x coil mm
+Weight (Kg):2,880
+Quality:Prime
+Help
+Location:FABRICA ALGECIRAS
+1,925.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="9" xml:space="preserve">
+      <c r="A9" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4310 301-Coil, 2B,
+3.00 x 160.0 x coil mm</v>
+      </c>
+      <c r="B9" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4310 301-Coil, 2B,
 3.00 x 160.0 x coil mm
 Weight (Kg):2,678
@@ -487,12 +535,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="7" xml:space="preserve">
-      <c r="A7" t="str" xml:space="preserve">
+    <row r="10" xml:space="preserve">
+      <c r="A10" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4310 301-Coil, 2B,
 3.00 x 180.9 x coil mm</v>
       </c>
-      <c r="B7" t="str" xml:space="preserve">
+      <c r="B10" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4310 301-Coil, 2B,
 3.00 x 180.9 x coil mm
 Weight (Kg):3,078
@@ -503,12 +551,28 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="8" xml:space="preserve">
-      <c r="A8" t="str" xml:space="preserve">
+    <row r="11" xml:space="preserve">
+      <c r="A11" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4310 301-Coil, 2D,
+0.80 x 1263.0 x coil mm</v>
+      </c>
+      <c r="B11" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4310 301-Coil, 2D,
+0.80 x 1263.0 x coil mm
+Weight (Kg):17,770
+Quality:Prime
+Help
+Location:FABRICA ALGECIRAS
+2,700.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="12" xml:space="preserve">
+      <c r="A12" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4310 301-Coil, BA,
 0.40 x 120.9 x coil mm</v>
       </c>
-      <c r="B8" t="str" xml:space="preserve">
+      <c r="B12" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4310 301-Coil, BA,
 0.40 x 120.9 x coil mm
 Weight (Kg):886
@@ -519,12 +583,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="9" xml:space="preserve">
-      <c r="A9" t="str" xml:space="preserve">
+    <row r="13" xml:space="preserve">
+      <c r="A13" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4310 301-Coil, BA,
 0.40 x 1290.0 x coil mm</v>
       </c>
-      <c r="B9" t="str" xml:space="preserve">
+      <c r="B13" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4310 301-Coil, BA,
 0.40 x 1290.0 x coil mm
 Weight (Kg):9,500
@@ -535,12 +599,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="10" xml:space="preserve">
-      <c r="A10" t="str" xml:space="preserve">
+    <row r="14" xml:space="preserve">
+      <c r="A14" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4310 301-Coil, BA,
 0.40 x 140.9 x coil mm</v>
       </c>
-      <c r="B10" t="str" xml:space="preserve">
+      <c r="B14" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4310 301-Coil, BA,
 0.40 x 140.9 x coil mm
 Weight (Kg):922
@@ -551,12 +615,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="11" xml:space="preserve">
-      <c r="A11" t="str" xml:space="preserve">
+    <row r="15" xml:space="preserve">
+      <c r="A15" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4310 301-Coil, BA,
 0.40 x 150.9 x coil mm</v>
       </c>
-      <c r="B11" t="str" xml:space="preserve">
+      <c r="B15" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4310 301-Coil, BA,
 0.40 x 150.9 x coil mm
 Weight (Kg):912
@@ -567,12 +631,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="12" xml:space="preserve">
-      <c r="A12" t="str" xml:space="preserve">
+    <row r="16" xml:space="preserve">
+      <c r="A16" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4310 301-Coil, BA,
 0.40 x 170.0 x coil mm</v>
       </c>
-      <c r="B12" t="str" xml:space="preserve">
+      <c r="B16" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4310 301-Coil, BA,
 0.40 x 170.0 x coil mm
 Weight (Kg):1,694
@@ -583,12 +647,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="13" xml:space="preserve">
-      <c r="A13" t="str" xml:space="preserve">
+    <row r="17" xml:space="preserve">
+      <c r="A17" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4310 301-Coil, BA,
 0.40 x 180.9 x coil mm</v>
       </c>
-      <c r="B13" t="str" xml:space="preserve">
+      <c r="B17" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4310 301-Coil, BA,
 0.40 x 180.9 x coil mm
 Weight (Kg):1,401
@@ -599,12 +663,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="14" xml:space="preserve">
-      <c r="A14" t="str" xml:space="preserve">
+    <row r="18" xml:space="preserve">
+      <c r="A18" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4310 301-Coil, BA,
 0.40 x 190.0 x coil mm</v>
       </c>
-      <c r="B14" t="str" xml:space="preserve">
+      <c r="B18" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4310 301-Coil, BA,
 0.40 x 190.0 x coil mm
 Weight (Kg):1,034
@@ -615,12 +679,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="15" xml:space="preserve">
-      <c r="A15" t="str" xml:space="preserve">
+    <row r="19" xml:space="preserve">
+      <c r="A19" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4310 301-Coil, BA,
 0.40 x 520.0 x coil mm</v>
       </c>
-      <c r="B15" t="str" xml:space="preserve">
+      <c r="B19" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4310 301-Coil, BA,
 0.40 x 520.0 x coil mm
 Weight (Kg):4,059
@@ -631,12 +695,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="16" xml:space="preserve">
-      <c r="A16" t="str" xml:space="preserve">
+    <row r="20" xml:space="preserve">
+      <c r="A20" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4310 301-Coil, BA,
 0.40 x 536.5 x coil mm</v>
       </c>
-      <c r="B16" t="str" xml:space="preserve">
+      <c r="B20" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4310 301-Coil, BA,
 0.40 x 536.5 x coil mm
 Weight (Kg):2,565
@@ -647,12 +711,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="17" xml:space="preserve">
-      <c r="A17" t="str" xml:space="preserve">
+    <row r="21" xml:space="preserve">
+      <c r="A21" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4310 301-Coil, BA,
 0.40 x 536.5 x coil mm</v>
       </c>
-      <c r="B17" t="str" xml:space="preserve">
+      <c r="B21" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4310 301-Coil, BA,
 0.40 x 536.5 x coil mm
 Weight (Kg):2,738
@@ -661,70 +725,6 @@
 Location:FABRICA ALGECIRAS
 1,975.00 €/ton
 Add to cart</v>
-      </c>
-    </row>
-    <row r="18" xml:space="preserve">
-      <c r="A18" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4310 301-Coil, 2B,
-0.80 x 1128.0 x coil mm</v>
-      </c>
-      <c r="B18" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4310 301-Coil, 2B,
-0.80 x 1128.0 x coil mm
-Weight (Kg):10,677
-Quality:Prime
-Help
-Location:FABRICA ALGECIRAS
-2,700.00 €/ton
-Reserved</v>
-      </c>
-    </row>
-    <row r="19" xml:space="preserve">
-      <c r="A19" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4310 301-Coil, 2B,
-0.80 x 1288.0 x coil mm</v>
-      </c>
-      <c r="B19" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4310 301-Coil, 2B,
-0.80 x 1288.0 x coil mm
-Weight (Kg):20,316
-Quality:Prime
-Help
-Location:FABRICA ALGECIRAS
-2,700.00 €/ton
-Reserved</v>
-      </c>
-    </row>
-    <row r="20" xml:space="preserve">
-      <c r="A20" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4310 301-Coil, 2B,
-3.00 x 160.0 x coil mm</v>
-      </c>
-      <c r="B20" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4310 301-Coil, 2B,
-3.00 x 160.0 x coil mm
-Weight (Kg):2,880
-Quality:Prime
-Help
-Location:FABRICA ALGECIRAS
-1,925.00 €/ton
-Reserved</v>
-      </c>
-    </row>
-    <row r="21" xml:space="preserve">
-      <c r="A21" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4310 301-Coil, 2D,
-0.80 x 1263.0 x coil mm</v>
-      </c>
-      <c r="B21" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4310 301-Coil, 2D,
-0.80 x 1263.0 x coil mm
-Weight (Kg):17,770
-Quality:Prime
-Help
-Location:FABRICA ALGECIRAS
-2,700.00 €/ton
-Reserved</v>
       </c>
     </row>
     <row r="22" xml:space="preserve">

--- a/scraped_data.xlsx
+++ b/scraped_data.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B21"/>
+  <dimension ref="A1:B141"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -420,7 +420,7 @@
 Help
 Location:FABRICA ALGECIRAS
 2,700.00 €/ton
-Add to Cart</v>
+Add to cart</v>
       </c>
     </row>
     <row r="3" xml:space="preserve">
@@ -436,7 +436,7 @@
 Help
 Location:FABRICA ALGECIRAS
 2,275.00 €/ton
-Add to Cart</v>
+Add to cart</v>
       </c>
     </row>
     <row r="4" xml:space="preserve">
@@ -452,7 +452,7 @@
 Help
 Location:FABRICA ALGECIRAS
 2,700.00 €/ton
-Add to Cart</v>
+Add to cart</v>
       </c>
     </row>
     <row r="5" xml:space="preserve">
@@ -468,7 +468,7 @@
 Help
 Location:FABRICA ALGECIRAS
 2,700.00 €/ton
-Add to Cart</v>
+Add to cart</v>
       </c>
     </row>
     <row r="6" xml:space="preserve">
@@ -484,7 +484,7 @@
 Help
 Location:FABRICA ALGECIRAS
 1,875.00 €/ton
-Add to Cart</v>
+Add to cart</v>
       </c>
     </row>
     <row r="7" xml:space="preserve">
@@ -500,7 +500,7 @@
 Help
 Location:FABRICA ALGECIRAS
 2,700.00 €/ton
-Add to Cart</v>
+Add to cart</v>
       </c>
     </row>
     <row r="8" xml:space="preserve">
@@ -516,7 +516,7 @@
 Help
 Location:FABRICA ALGECIRAS
 1,925.00 €/ton
-Add to Cart</v>
+Add to cart</v>
       </c>
     </row>
     <row r="9" xml:space="preserve">
@@ -532,7 +532,7 @@
 Help
 Location:FABRICA ALGECIRAS
 1,925.00 €/ton
-Add to Cart</v>
+Add to cart</v>
       </c>
     </row>
     <row r="10" xml:space="preserve">
@@ -548,7 +548,7 @@
 Help
 Location:FABRICA ALGECIRAS
 1,925.00 €/ton
-Add to Cart</v>
+Add to cart</v>
       </c>
     </row>
     <row r="11" xml:space="preserve">
@@ -564,7 +564,7 @@
 Help
 Location:FABRICA ALGECIRAS
 2,700.00 €/ton
-Add to Cart</v>
+Add to cart</v>
       </c>
     </row>
     <row r="12" xml:space="preserve">
@@ -580,7 +580,7 @@
 Help
 Location:FABRICA ALGECIRAS
 1,875.00 €/ton
-Add to Cart</v>
+Add to cart</v>
       </c>
     </row>
     <row r="13" xml:space="preserve">
@@ -596,7 +596,7 @@
 Help
 Location:FABRICA ALGECIRAS
 2,075.00 €/ton
-Add to Cart</v>
+Add to cart</v>
       </c>
     </row>
     <row r="14" xml:space="preserve">
@@ -612,7 +612,7 @@
 Help
 Location:FABRICA ALGECIRAS
 1,875.00 €/ton
-Add to Cart</v>
+Add to cart</v>
       </c>
     </row>
     <row r="15" xml:space="preserve">
@@ -628,7 +628,7 @@
 Help
 Location:FABRICA ALGECIRAS
 1,875.00 €/ton
-Add to Cart</v>
+Add to cart</v>
       </c>
     </row>
     <row r="16" xml:space="preserve">
@@ -644,7 +644,7 @@
 Help
 Location:FABRICA ALGECIRAS
 1,925.00 €/ton
-Add to Cart</v>
+Add to cart</v>
       </c>
     </row>
     <row r="17" xml:space="preserve">
@@ -660,7 +660,7 @@
 Help
 Location:FABRICA ALGECIRAS
 1,875.00 €/ton
-Add to Cart</v>
+Add to cart</v>
       </c>
     </row>
     <row r="18" xml:space="preserve">
@@ -676,7 +676,7 @@
 Help
 Location:FABRICA ALGECIRAS
 1,925.00 €/ton
-Add to Cart</v>
+Add to cart</v>
       </c>
     </row>
     <row r="19" xml:space="preserve">
@@ -692,7 +692,7 @@
 Help
 Location:FABRICA ALGECIRAS
 1,975.00 €/ton
-Add to Cart</v>
+Add to cart</v>
       </c>
     </row>
     <row r="20" xml:space="preserve">
@@ -708,7 +708,7 @@
 Help
 Location:FABRICA ALGECIRAS
 1,975.00 €/ton
-Add to Cart</v>
+Add to cart</v>
       </c>
     </row>
     <row r="21" xml:space="preserve">
@@ -724,12 +724,1932 @@
 Help
 Location:FABRICA ALGECIRAS
 1,975.00 €/ton
-Add to Cart</v>
+Add to cart</v>
+      </c>
+    </row>
+    <row r="22" xml:space="preserve">
+      <c r="A22" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4310 301-Coil, BA,
+0.40 x 536.5 x coil mm</v>
+      </c>
+      <c r="B22" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4310 301-Coil, BA,
+0.40 x 536.5 x coil mm
+Weight (Kg):2,524
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+1,975.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="23" xml:space="preserve">
+      <c r="A23" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4310 301-Coil, BA,
+0.40 x 536.5 x coil mm</v>
+      </c>
+      <c r="B23" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4310 301-Coil, BA,
+0.40 x 536.5 x coil mm
+Weight (Kg):4,374
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+1,975.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="24" xml:space="preserve">
+      <c r="A24" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4310 301-Coil, BA,
+0.40 x 536.5 x coil mm</v>
+      </c>
+      <c r="B24" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4310 301-Coil, BA,
+0.40 x 536.5 x coil mm
+Weight (Kg):4,586
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+1,975.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="25" xml:space="preserve">
+      <c r="A25" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4310 301-Coil, BA,
+0.40 x 536.5 x coil mm</v>
+      </c>
+      <c r="B25" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4310 301-Coil, BA,
+0.40 x 536.5 x coil mm
+Weight (Kg):4,773
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+1,975.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="26" xml:space="preserve">
+      <c r="A26" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4310 301-Coil, BA,
+0.40 x 536.5 x coil mm</v>
+      </c>
+      <c r="B26" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4310 301-Coil, BA,
+0.40 x 536.5 x coil mm
+Weight (Kg):4,404
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+1,975.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="27" xml:space="preserve">
+      <c r="A27" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4310 301-Coil, BA,
+0.40 x 536.5 x coil mm</v>
+      </c>
+      <c r="B27" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4310 301-Coil, BA,
+0.40 x 536.5 x coil mm
+Weight (Kg):4,913
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+1,975.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="28" xml:space="preserve">
+      <c r="A28" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4310 301-Coil, BA,
+0.40 x 536.5 x coil mm</v>
+      </c>
+      <c r="B28" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4310 301-Coil, BA,
+0.40 x 536.5 x coil mm
+Weight (Kg):4,493
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+1,975.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="29" xml:space="preserve">
+      <c r="A29" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4310 301-Coil, BA,
+0.40 x 536.5 x coil mm</v>
+      </c>
+      <c r="B29" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4310 301-Coil, BA,
+0.40 x 536.5 x coil mm
+Weight (Kg):4,560
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+1,975.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="30" xml:space="preserve">
+      <c r="A30" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4310 301-Sheet, 3/4 HT,
+2.00 x 1250.0 x 2500.0 mm</v>
+      </c>
+      <c r="B30" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4310 301-Sheet, 3/4 HT,
+2.00 x 1250.0 x 2500.0 mm
+Weight (Kg):788
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,075.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="31" xml:space="preserve">
+      <c r="A31" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4310 301-Sheet, 3/4 HT,
+2.00 x 1250.0 x 2500.0 mm</v>
+      </c>
+      <c r="B31" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4310 301-Sheet, 3/4 HT,
+2.00 x 1250.0 x 2500.0 mm
+Weight (Kg):642
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,075.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="32" xml:space="preserve">
+      <c r="A32" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4310 301-Sheet, 3/4 HT,
+2.00 x 1250.0 x 2500.0 mm</v>
+      </c>
+      <c r="B32" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4310 301-Sheet, 3/4 HT,
+2.00 x 1250.0 x 2500.0 mm
+Weight (Kg):1,884
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,075.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="33" xml:space="preserve">
+      <c r="A33" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4310 301-Sheet, 3/4 HT,
+2.00 x 1250.0 x 2500.0 mm</v>
+      </c>
+      <c r="B33" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4310 301-Sheet, 3/4 HT,
+2.00 x 1250.0 x 2500.0 mm
+Weight (Kg):1,794
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,075.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="34" xml:space="preserve">
+      <c r="A34" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4310 301-Sheet, 3/4 HT,
+2.00 x 1250.0 x 2500.0 mm</v>
+      </c>
+      <c r="B34" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4310 301-Sheet, 3/4 HT,
+2.00 x 1250.0 x 2500.0 mm
+Weight (Kg):1,404
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,075.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="35" xml:space="preserve">
+      <c r="A35" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4310 301-Sheet, 3/4 HT,
+2.00 x 1250.0 x 2500.0 mm</v>
+      </c>
+      <c r="B35" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4310 301-Sheet, 3/4 HT,
+2.00 x 1250.0 x 2500.0 mm
+Weight (Kg):1,642
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,075.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="36" xml:space="preserve">
+      <c r="A36" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4310 301-Untrimmed, Coil, 1/4 HT,
+0.30 x 1291.0 x coil mm</v>
+      </c>
+      <c r="B36" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4310 301-Untrimmed, Coil, 1/4 HT,
+0.30 x 1291.0 x coil mm
+Weight (Kg):2,782
+Quality:Prime
+Help
+Location:FABRICA ALGECIRAS
+2,275.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="37" xml:space="preserve">
+      <c r="A37" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4310 301-Untrimmed, Coil, BA,
+0.40 x 837.0 x coil mm</v>
+      </c>
+      <c r="B37" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4310 301-Untrimmed, Coil, BA,
+0.40 x 837.0 x coil mm
+Weight (Kg):2,312
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,075.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="38" xml:space="preserve">
+      <c r="A38" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4310Mo 301-Coil, 2B,
+0.80 x 1270.0 x coil mm</v>
+      </c>
+      <c r="B38" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4310Mo 301-Coil, 2B,
+0.80 x 1270.0 x coil mm
+Weight (Kg):22,630
+Quality:Prime
+Help
+Location:FABRICA ALGECIRAS
+2,700.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="39" xml:space="preserve">
+      <c r="A39" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4310Mo 301-Coil, 2B,
+0.80 x 1545.0 x coil mm</v>
+      </c>
+      <c r="B39" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4310Mo 301-Coil, 2B,
+0.80 x 1545.0 x coil mm
+Weight (Kg):12,820
+Quality:Prime
+Help
+Location:FABRICA ALGECIRAS
+2,700.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="40" xml:space="preserve">
+      <c r="A40" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4310Mo 301-Coil, 2B,
+0.80 x 1546.0 x coil mm</v>
+      </c>
+      <c r="B40" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4310Mo 301-Coil, 2B,
+0.80 x 1546.0 x coil mm
+Weight (Kg):9,850
+Quality:Prime
+Help
+Location:FABRICA ALGECIRAS
+2,700.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="41" xml:space="preserve">
+      <c r="A41" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4310 301-Untrimmed, Coil, BA,
+0.40 x 701.0 x coil mm</v>
+      </c>
+      <c r="B41" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4310 301-Untrimmed, Coil, BA,
+0.40 x 701.0 x coil mm
+Weight (Kg):2,745
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+1,975.00 €/ton
+Reserved</v>
+      </c>
+    </row>
+    <row r="42" xml:space="preserve">
+      <c r="A42" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4310Mo 301-Coil, 2B,
+0.80 x 268.0 x coil mm</v>
+      </c>
+      <c r="B42" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4310Mo 301-Coil, 2B,
+0.80 x 268.0 x coil mm
+Weight (Kg):4,850
+Quality:Prime
+Help
+Location:FABRICA ALGECIRAS
+1,925.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="43" xml:space="preserve">
+      <c r="A43" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4310Mo 301-Coil, 2B,
+0.80 x 268.0 x coil mm</v>
+      </c>
+      <c r="B43" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4310Mo 301-Coil, 2B,
+0.80 x 268.0 x coil mm
+Weight (Kg):4,814
+Quality:Prime
+Help
+Location:FABRICA ALGECIRAS
+1,925.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="44" xml:space="preserve">
+      <c r="A44" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4310Mo 301-Coil, 2B,
+0.80 x 725.0 x coil mm</v>
+      </c>
+      <c r="B44" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4310Mo 301-Coil, 2B,
+0.80 x 725.0 x coil mm
+Weight (Kg):3,670
+Quality:Prime
+Help
+Location:FABRICA ALGECIRAS
+1,975.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="45" xml:space="preserve">
+      <c r="A45" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4310Mo 301-Coil, 2B,
+0.80 x 725.0 x coil mm</v>
+      </c>
+      <c r="B45" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4310Mo 301-Coil, 2B,
+0.80 x 725.0 x coil mm
+Weight (Kg):3,670
+Quality:Prime
+Help
+Location:FABRICA ALGECIRAS
+1,975.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="46" xml:space="preserve">
+      <c r="A46" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4310Mo 301-Coil, 2B,
+1.40 x 635.0 x coil mm</v>
+      </c>
+      <c r="B46" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4310Mo 301-Coil, 2B,
+1.40 x 635.0 x coil mm
+Weight (Kg):10,970
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+1,975.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="47" xml:space="preserve">
+      <c r="A47" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4310Mo 301-Untrimmed, Coil, 2B,
+0.70 x 1543.0 x coil mm</v>
+      </c>
+      <c r="B47" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4310Mo 301-Untrimmed, Coil, 2B,
+0.70 x 1543.0 x coil mm
+Weight (Kg):18,333
+Quality:Prime
+Help
+Location:FABRICA ALGECIRAS
+2,700.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="48" xml:space="preserve">
+      <c r="A48" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4310Mo 301-Untrimmed, Coil, 2B,
+0.90 x 1540.0 x coil mm</v>
+      </c>
+      <c r="B48" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4310Mo 301-Untrimmed, Coil, 2B,
+0.90 x 1540.0 x coil mm
+Weight (Kg):3,390
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,075.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="49" xml:space="preserve">
+      <c r="A49" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4301 304-Coil, 1/4 HT,
+1.60 x 1230.0 x coil mm</v>
+      </c>
+      <c r="B49" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4301 304-Coil, 1/4 HT,
+1.60 x 1230.0 x coil mm
+Weight (Kg):6,560
+Quality:Prime
+Help
+Location:FABRICA ALGECIRAS
+2,425.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="50" xml:space="preserve">
+      <c r="A50" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4301 304-Coil, 1/4 HT,
+1.90 x 1230.0 x coil mm</v>
+      </c>
+      <c r="B50" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4301 304-Coil, 1/4 HT,
+1.90 x 1230.0 x coil mm
+Weight (Kg):7,428
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,225.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="51" xml:space="preserve">
+      <c r="A51" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4301 304-Coil, 1/4 HT,
+1.90 x 1230.0 x coil mm</v>
+      </c>
+      <c r="B51" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4301 304-Coil, 1/4 HT,
+1.90 x 1230.0 x coil mm
+Weight (Kg):7,104
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,225.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="52" xml:space="preserve">
+      <c r="A52" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4301 304-Coil, 1/4 HT,
+1.90 x 1230.0 x coil mm</v>
+      </c>
+      <c r="B52" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4301 304-Coil, 1/4 HT,
+1.90 x 1230.0 x coil mm
+Weight (Kg):2,971
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,225.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="53" xml:space="preserve">
+      <c r="A53" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4301 304-Coil, 1/4 HT,
+2.00 x 879.0 x coil mm</v>
+      </c>
+      <c r="B53" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4301 304-Coil, 1/4 HT,
+2.00 x 879.0 x coil mm
+Weight (Kg):6,958
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,225.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="54" xml:space="preserve">
+      <c r="A54" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4301 304-Coil, 2B,
+0.50 x 385.0 x coil mm</v>
+      </c>
+      <c r="B54" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4301 304-Coil, 2B,
+0.50 x 385.0 x coil mm
+Weight (Kg):740
+Quality:Downgraded
+Help
+Location:FABRICA ALGECIRAS
+2,025.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="55" xml:space="preserve">
+      <c r="A55" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4301 304-Coil, 2B,
+0.50 x 385.0 x coil mm</v>
+      </c>
+      <c r="B55" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4301 304-Coil, 2B,
+0.50 x 385.0 x coil mm
+Weight (Kg):740
+Quality:Downgraded
+Help
+Location:FABRICA ALGECIRAS
+2,025.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="56" xml:space="preserve">
+      <c r="A56" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4301 304-Coil, 2B,
+0.60 x 100.9 x coil mm</v>
+      </c>
+      <c r="B56" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4301 304-Coil, 2B,
+0.60 x 100.9 x coil mm
+Weight (Kg):574
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,075.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="57" xml:space="preserve">
+      <c r="A57" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4301 304-Coil, 2B,
+0.60 x 110.9 x coil mm</v>
+      </c>
+      <c r="B57" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4301 304-Coil, 2B,
+0.60 x 110.9 x coil mm
+Weight (Kg):728
+Quality:Prime
+Help
+Location:FABRICA ALGECIRAS
+2,075.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="58" xml:space="preserve">
+      <c r="A58" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4301 304-Coil, 2B,
+0.60 x 128.7 x coil mm</v>
+      </c>
+      <c r="B58" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4301 304-Coil, 2B,
+0.60 x 128.7 x coil mm
+Weight (Kg):921
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,075.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="59" xml:space="preserve">
+      <c r="A59" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4301 304-Coil, 2B,
+0.70 x 1044.0 x coil mm</v>
+      </c>
+      <c r="B59" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4301 304-Coil, 2B,
+0.70 x 1044.0 x coil mm
+Weight (Kg):3,776
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,225.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="60" xml:space="preserve">
+      <c r="A60" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4301 304-Coil, 2B,
+0.70 x 1075.0 x coil mm</v>
+      </c>
+      <c r="B60" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4301 304-Coil, 2B,
+0.70 x 1075.0 x coil mm
+Weight (Kg):2,100
+Quality:Prime
+Help
+Location:FABRICA ALGECIRAS
+2,425.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="61" xml:space="preserve">
+      <c r="A61" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4301 304-Coil, 2B,
+0.90 x 195.9 x coil mm</v>
+      </c>
+      <c r="B61" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4301 304-Coil, 2B,
+0.90 x 195.9 x coil mm
+Weight (Kg):562
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,075.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="62" xml:space="preserve">
+      <c r="A62" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4301 304-Coil, 2D,
+0.90 x 1027.0 x coil mm</v>
+      </c>
+      <c r="B62" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4301 304-Coil, 2D,
+0.90 x 1027.0 x coil mm
+Weight (Kg):17,981
+Quality:Prime
+Help
+Location:FABRICA ALGECIRAS
+2,900.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="63" xml:space="preserve">
+      <c r="A63" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4301 304-Coil, 2D,
+0.90 x 937.0 x coil mm</v>
+      </c>
+      <c r="B63" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4301 304-Coil, 2D,
+0.90 x 937.0 x coil mm
+Weight (Kg):6,680
+Quality:Prime
+Help
+Location:FABRICA ALGECIRAS
+2,425.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="64" xml:space="preserve">
+      <c r="A64" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4301 304-Coil, BA,
+0.30 x 931.0 x coil mm</v>
+      </c>
+      <c r="B64" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4301 304-Coil, BA,
+0.30 x 931.0 x coil mm
+Weight (Kg):16,870
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,225.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="65" xml:space="preserve">
+      <c r="A65" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4301 304-Coil, BA,
+0.30 x 935.0 x coil mm</v>
+      </c>
+      <c r="B65" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4301 304-Coil, BA,
+0.30 x 935.0 x coil mm
+Weight (Kg):17,020
+Quality:Prime
+Help
+Location:FABRICA ALGECIRAS
+2,900.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="66" xml:space="preserve">
+      <c r="A66" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4301 304-Coil, BA,
+0.30 x 938.0 x coil mm</v>
+      </c>
+      <c r="B66" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4301 304-Coil, BA,
+0.30 x 938.0 x coil mm
+Weight (Kg):17,060
+Quality:Prime
+Help
+Location:FABRICA ALGECIRAS
+2,900.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="67" xml:space="preserve">
+      <c r="A67" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4301 304-Coil, BA,
+0.30 x 940.0 x coil mm</v>
+      </c>
+      <c r="B67" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4301 304-Coil, BA,
+0.30 x 940.0 x coil mm
+Weight (Kg):16,780
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,225.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="68" xml:space="preserve">
+      <c r="A68" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4301 304-Coil, BA,
+0.30 x 940.0 x coil mm</v>
+      </c>
+      <c r="B68" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4301 304-Coil, BA,
+0.30 x 940.0 x coil mm
+Weight (Kg):17,110
+Quality:Prime
+Help
+Location:FABRICA ALGECIRAS
+2,900.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="69" xml:space="preserve">
+      <c r="A69" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4301 304-Coil, BA,
+0.40 x 112.9 x coil mm</v>
+      </c>
+      <c r="B69" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4301 304-Coil, BA,
+0.40 x 112.9 x coil mm
+Weight (Kg):1,162
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,075.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="70" xml:space="preserve">
+      <c r="A70" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4301 304-Coil, BA,
+0.40 x 115.0 x coil mm</v>
+      </c>
+      <c r="B70" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4301 304-Coil, BA,
+0.40 x 115.0 x coil mm
+Weight (Kg):598
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,075.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="71" xml:space="preserve">
+      <c r="A71" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4301 304-Coil, BA,
+0.40 x 140.0 x coil mm</v>
+      </c>
+      <c r="B71" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4301 304-Coil, BA,
+0.40 x 140.0 x coil mm
+Weight (Kg):1,166
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,075.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="72" xml:space="preserve">
+      <c r="A72" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4301 304-Coil, BA,
+0.40 x 200.0 x coil mm</v>
+      </c>
+      <c r="B72" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4301 304-Coil, BA,
+0.40 x 200.0 x coil mm
+Weight (Kg):526
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,075.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="73" xml:space="preserve">
+      <c r="A73" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4301 304-Coil, BA,
+0.40 x 280.0 x coil mm</v>
+      </c>
+      <c r="B73" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4301 304-Coil, BA,
+0.40 x 280.0 x coil mm
+Weight (Kg):2,620
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,075.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="74" xml:space="preserve">
+      <c r="A74" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4301 304-Coil, BA,
+0.40 x 280.0 x coil mm</v>
+      </c>
+      <c r="B74" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4301 304-Coil, BA,
+0.40 x 280.0 x coil mm
+Weight (Kg):2,242
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,075.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="75" xml:space="preserve">
+      <c r="A75" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4301 304-Coil, BA,
+0.40 x 330.0 x coil mm</v>
+      </c>
+      <c r="B75" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4301 304-Coil, BA,
+0.40 x 330.0 x coil mm
+Weight (Kg):1,034
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,075.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="76" xml:space="preserve">
+      <c r="A76" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4301 304-Coil, BA,
+0.40 x 578.8 x coil mm</v>
+      </c>
+      <c r="B76" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4301 304-Coil, BA,
+0.40 x 578.8 x coil mm
+Weight (Kg):4,322
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,125.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="77" xml:space="preserve">
+      <c r="A77" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4301 304-Coil, BA,
+0.40 x 578.8 x coil mm</v>
+      </c>
+      <c r="B77" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4301 304-Coil, BA,
+0.40 x 578.8 x coil mm
+Weight (Kg):1,774
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,125.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="78" xml:space="preserve">
+      <c r="A78" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4301 304-Coil, BA,
+0.40 x 578.8 x coil mm</v>
+      </c>
+      <c r="B78" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4301 304-Coil, BA,
+0.40 x 578.8 x coil mm
+Weight (Kg):4,408
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,125.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="79" xml:space="preserve">
+      <c r="A79" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4301 304-Coil, BA,
+0.40 x 718.0 x coil mm</v>
+      </c>
+      <c r="B79" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4301 304-Coil, BA,
+0.40 x 718.0 x coil mm
+Weight (Kg):5,128
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,125.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="80" xml:space="preserve">
+      <c r="A80" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4301 304-Coil, BA,
+0.40 x 718.0 x coil mm</v>
+      </c>
+      <c r="B80" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4301 304-Coil, BA,
+0.40 x 718.0 x coil mm
+Weight (Kg):2,992
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,125.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="81" xml:space="preserve">
+      <c r="A81" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4301 304-Coil, BA,
+0.40 x 1000.0 x coil mm</v>
+      </c>
+      <c r="B81" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4301 304-Coil, BA,
+0.40 x 1000.0 x coil mm
+Weight (Kg):2,427
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,225.00 €/ton
+Out of Stock</v>
+      </c>
+    </row>
+    <row r="82" xml:space="preserve">
+      <c r="A82" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4301 304-Coil, BA,
+0.40 x 718.0 x coil mm</v>
+      </c>
+      <c r="B82" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4301 304-Coil, BA,
+0.40 x 718.0 x coil mm
+Weight (Kg):3,403
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,125.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="83" xml:space="preserve">
+      <c r="A83" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4301 304-Coil, BA,
+0.40 x 935.0 x coil mm</v>
+      </c>
+      <c r="B83" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4301 304-Coil, BA,
+0.40 x 935.0 x coil mm
+Weight (Kg):2,733
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,225.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="84" xml:space="preserve">
+      <c r="A84" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4301 304-Coil, BA,
+0.40 x 938.0 x coil mm</v>
+      </c>
+      <c r="B84" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4301 304-Coil, BA,
+0.40 x 938.0 x coil mm
+Weight (Kg):2,410
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,225.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="85" xml:space="preserve">
+      <c r="A85" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4301 304-Coil, BA,
+0.40 x 939.0 x coil mm</v>
+      </c>
+      <c r="B85" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4301 304-Coil, BA,
+0.40 x 939.0 x coil mm
+Weight (Kg):2,982
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,225.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="86" xml:space="preserve">
+      <c r="A86" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4301 304-Coil, BA,
+0.50 x 935.0 x coil mm</v>
+      </c>
+      <c r="B86" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4301 304-Coil, BA,
+0.50 x 935.0 x coil mm
+Weight (Kg):16,840
+Quality:Prime
+Help
+Location:FABRICA ALGECIRAS
+2,900.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="87" xml:space="preserve">
+      <c r="A87" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4301 304-Coil, BA,
+0.60 x 1228.0 x coil mm</v>
+      </c>
+      <c r="B87" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4301 304-Coil, BA,
+0.60 x 1228.0 x coil mm
+Weight (Kg):20,070
+Quality:Prime
+Help
+Location:FABRICA ALGECIRAS
+2,900.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="88" xml:space="preserve">
+      <c r="A88" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4301 304-Coil, BA,
+0.60 x 155.9 x coil mm</v>
+      </c>
+      <c r="B88" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4301 304-Coil, BA,
+0.60 x 155.9 x coil mm
+Weight (Kg):674
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,075.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="89" xml:space="preserve">
+      <c r="A89" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4301 304-Coil, BA,
+0.60 x 211.9 x coil mm</v>
+      </c>
+      <c r="B89" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4301 304-Coil, BA,
+0.60 x 211.9 x coil mm
+Weight (Kg):508
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,075.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="90" xml:space="preserve">
+      <c r="A90" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4301 304-Coil, BA,
+0.60 x 211.9 x coil mm</v>
+      </c>
+      <c r="B90" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4301 304-Coil, BA,
+0.60 x 211.9 x coil mm
+Weight (Kg):504
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,075.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="91" xml:space="preserve">
+      <c r="A91" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4301 304-Coil, BA,
+0.60 x 937.0 x coil mm</v>
+      </c>
+      <c r="B91" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4301 304-Coil, BA,
+0.60 x 937.0 x coil mm
+Weight (Kg):16,860
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,225.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="92" xml:space="preserve">
+      <c r="A92" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4301 304-Coil, BA,
+0.60 x 978.0 x coil mm</v>
+      </c>
+      <c r="B92" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4301 304-Coil, BA,
+0.60 x 978.0 x coil mm
+Weight (Kg):17,840
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,225.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="93" xml:space="preserve">
+      <c r="A93" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4301 304-Coil, BA,
+0.70 x 1150.0 x coil mm</v>
+      </c>
+      <c r="B93" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4301 304-Coil, BA,
+0.70 x 1150.0 x coil mm
+Weight (Kg):4,200
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,225.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="94" xml:space="preserve">
+      <c r="A94" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4301 304-Coil, BA,
+0.70 x 1224.0 x coil mm</v>
+      </c>
+      <c r="B94" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4301 304-Coil, BA,
+0.70 x 1224.0 x coil mm
+Weight (Kg):21,300
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,225.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="95" xml:space="preserve">
+      <c r="A95" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4301 304-Coil, BA,
+0.90 x 1240.0 x coil mm</v>
+      </c>
+      <c r="B95" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4301 304-Coil, BA,
+0.90 x 1240.0 x coil mm
+Weight (Kg):9,786
+Quality:Prime
+Help
+Location:FABRICA ALGECIRAS
+2,900.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="96" xml:space="preserve">
+      <c r="A96" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4301 304-Coil, BA, ET-60
+0.40 x 238.0 x coil mm</v>
+      </c>
+      <c r="B96" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4301 304-Coil, BA, ET-60
+0.40 x 238.0 x coil mm
+Weight (Kg):928
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,075.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="97" xml:space="preserve">
+      <c r="A97" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4301 304-Coil, Emboss Chequered,
+0.70 x 105.9 x coil mm</v>
+      </c>
+      <c r="B97" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4301 304-Coil, Emboss Chequered,
+0.70 x 105.9 x coil mm
+Weight (Kg):550
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,075.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="98" xml:space="preserve">
+      <c r="A98" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4301 304-Coil, Emboss Chequered,
+0.70 x 265.9 x coil mm</v>
+      </c>
+      <c r="B98" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4301 304-Coil, Emboss Chequered,
+0.70 x 265.9 x coil mm
+Weight (Kg):1,484
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,075.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="99" xml:space="preserve">
+      <c r="A99" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4301 304-Coil, Emboss Chequered,
+0.70 x 265.9 x coil mm</v>
+      </c>
+      <c r="B99" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4301 304-Coil, Emboss Chequered,
+0.70 x 265.9 x coil mm
+Weight (Kg):1,490
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,075.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="100" xml:space="preserve">
+      <c r="A100" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4301 304-Coil, Emboss Chequered,
+0.70 x 270.9 x coil mm</v>
+      </c>
+      <c r="B100" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4301 304-Coil, Emboss Chequered,
+0.70 x 270.9 x coil mm
+Weight (Kg):1,442
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,075.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="101" xml:space="preserve">
+      <c r="A101" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4301 304-Coil, BA,
+0.60 x 940.0 x coil mm</v>
+      </c>
+      <c r="B101" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4301 304-Coil, BA,
+0.60 x 940.0 x coil mm
+Weight (Kg):16,760
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,225.00 €/ton
+Reserved</v>
+      </c>
+    </row>
+    <row r="102" xml:space="preserve">
+      <c r="A102" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4301 304-Coil, Emboss Chequered,
+0.70 x 285.0 x coil mm</v>
+      </c>
+      <c r="B102" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4301 304-Coil, Emboss Chequered,
+0.70 x 285.0 x coil mm
+Weight (Kg):1,502
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,075.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="103" xml:space="preserve">
+      <c r="A103" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4301 304-Coil, Emboss Chequered,
+0.95 x 915.0 x coil mm</v>
+      </c>
+      <c r="B103" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4301 304-Coil, Emboss Chequered,
+0.95 x 915.0 x coil mm
+Weight (Kg):3,271
+Quality:Prime
+Help
+Location:FABRICA ALGECIRAS
+2,425.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="104" xml:space="preserve">
+      <c r="A104" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4301 304-Coil, Emboss Chequered,
+0.95 x 999.0 x coil mm</v>
+      </c>
+      <c r="B104" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4301 304-Coil, Emboss Chequered,
+0.95 x 999.0 x coil mm
+Weight (Kg):4,214
+Quality:Prime
+Help
+Location:FABRICA ALGECIRAS
+2,425.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="105" xml:space="preserve">
+      <c r="A105" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4301 304-Coil, Emboss Linen,
+0.60 x 630.0 x coil mm</v>
+      </c>
+      <c r="B105" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4301 304-Coil, Emboss Linen,
+0.60 x 630.0 x coil mm
+Weight (Kg):1,878
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,125.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="106" xml:space="preserve">
+      <c r="A106" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4301 304-Coil, Emboss Linen,
+0.60 x 630.0 x coil mm</v>
+      </c>
+      <c r="B106" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4301 304-Coil, Emboss Linen,
+0.60 x 630.0 x coil mm
+Weight (Kg):1,872
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,125.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="107" xml:space="preserve">
+      <c r="A107" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4301 304-Coil, Emboss Linen,
+0.60 x 630.0 x coil mm</v>
+      </c>
+      <c r="B107" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4301 304-Coil, Emboss Linen,
+0.60 x 630.0 x coil mm
+Weight (Kg):1,837
+Quality:Prime
+Help
+Location:FABRICA ALGECIRAS
+2,125.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="108" xml:space="preserve">
+      <c r="A108" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4301 304-Coil, Emboss Linen,
+0.70 x 260.9 x coil mm</v>
+      </c>
+      <c r="B108" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4301 304-Coil, Emboss Linen,
+0.70 x 260.9 x coil mm
+Weight (Kg):632
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,075.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="109" xml:space="preserve">
+      <c r="A109" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4301 304-Coil, Emboss Linen, PVC-80
+0.70 x 209.9 x coil mm</v>
+      </c>
+      <c r="B109" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4301 304-Coil, Emboss Linen, PVC-80
+0.70 x 209.9 x coil mm
+Weight (Kg):1,006
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,075.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="110" xml:space="preserve">
+      <c r="A110" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4301 304-Coil, Emboss Linen, PVC-80
+0.70 x 209.9 x coil mm</v>
+      </c>
+      <c r="B110" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4301 304-Coil, Emboss Linen, PVC-80
+0.70 x 209.9 x coil mm
+Weight (Kg):1,208
+Quality:Prime
+Help
+Location:FABRICA ALGECIRAS
+2,075.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="111" xml:space="preserve">
+      <c r="A111" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4301 304-Coil, Emboss Linen, PVC-80
+0.70 x 209.9 x coil mm</v>
+      </c>
+      <c r="B111" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4301 304-Coil, Emboss Linen, PVC-80
+0.70 x 209.9 x coil mm
+Weight (Kg):1,256
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,075.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="112" xml:space="preserve">
+      <c r="A112" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4301 304-Coil, Polished N4-G-320,
+1.00 x 991.0 x coil mm</v>
+      </c>
+      <c r="B112" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4301 304-Coil, Polished N4-G-320,
+1.00 x 991.0 x coil mm
+Weight (Kg):18,760
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,225.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="113" xml:space="preserve">
+      <c r="A113" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4301 304-Coil, SB-G-400,
+0.80 x 205.9 x coil mm</v>
+      </c>
+      <c r="B113" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4301 304-Coil, SB-G-400,
+0.80 x 205.9 x coil mm
+Weight (Kg):1,876
+Quality:Prime
+Help
+Location:FABRICA ALGECIRAS
+2,075.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="114" xml:space="preserve">
+      <c r="A114" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4301 304-Coil, SB-G-400,
+0.80 x 260.9 x coil mm</v>
+      </c>
+      <c r="B114" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4301 304-Coil, SB-G-400,
+0.80 x 260.9 x coil mm
+Weight (Kg):1,626
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,075.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="115" xml:space="preserve">
+      <c r="A115" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4301 304-Sheet, BA,
+0.40 x 1000.0 x 2000.0 mm</v>
+      </c>
+      <c r="B115" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4301 304-Sheet, BA,
+0.40 x 1000.0 x 2000.0 mm
+Weight (Kg):1,038
+Quality:Downgraded
+Help
+Location:FABRICA ALGECIRAS
+2,075.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="116" xml:space="preserve">
+      <c r="A116" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4301 304-Sheet, BA,
+0.40 x 536.5 x 696.0 mm</v>
+      </c>
+      <c r="B116" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4301 304-Sheet, BA,
+0.40 x 536.5 x 696.0 mm
+Weight (Kg):1,060
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,225.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="117" xml:space="preserve">
+      <c r="A117" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4301 304-Sheet, BA,
+0.80 x 1000.0 x 2000.0 mm</v>
+      </c>
+      <c r="B117" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4301 304-Sheet, BA,
+0.80 x 1000.0 x 2000.0 mm
+Weight (Kg):738
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,225.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="118" xml:space="preserve">
+      <c r="A118" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4301 304-Sheet, BA,
+1.50 x 1000.0 x 2000.0 mm</v>
+      </c>
+      <c r="B118" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4301 304-Sheet, BA,
+1.50 x 1000.0 x 2000.0 mm
+Weight (Kg):1,918
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,225.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="119" xml:space="preserve">
+      <c r="A119" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4301 304-Untrimmed, Coil, 1/4 HT,
+1.50 x 1024.0 x coil mm</v>
+      </c>
+      <c r="B119" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4301 304-Untrimmed, Coil, 1/4 HT,
+1.50 x 1024.0 x coil mm
+Weight (Kg):4,500
+Quality:Prime
+Help
+Location:FABRICA ALGECIRAS
+2,425.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="120" xml:space="preserve">
+      <c r="A120" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4301 304-Coil, Emboss Linen,
+0.70 x 650.0 x coil mm</v>
+      </c>
+      <c r="B120" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4301 304-Coil, Emboss Linen,
+0.70 x 650.0 x coil mm
+Weight (Kg):3,670
+Quality:Prime
+Help
+Location:FABRICA ALGECIRAS
+2,125.00 €/ton
+Reserved</v>
+      </c>
+    </row>
+    <row r="121" xml:space="preserve">
+      <c r="A121" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4301 304-Coil, Emboss Linen,
+0.70 x 650.0 x coil mm</v>
+      </c>
+      <c r="B121" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4301 304-Coil, Emboss Linen,
+0.70 x 650.0 x coil mm
+Weight (Kg):3,321
+Quality:Prime
+Help
+Location:FABRICA ALGECIRAS
+2,125.00 €/ton
+Reserved</v>
+      </c>
+    </row>
+    <row r="122" xml:space="preserve">
+      <c r="A122" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4301 304-Untrimmed, Coil, 2B,
+0.70 x 1085.0 x coil mm</v>
+      </c>
+      <c r="B122" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4301 304-Untrimmed, Coil, 2B,
+0.70 x 1085.0 x coil mm
+Weight (Kg):2,772
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,225.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="123" xml:space="preserve">
+      <c r="A123" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4301 304-Untrimmed, Coil, 2D,
+1.00 x 942.0 x coil mm</v>
+      </c>
+      <c r="B123" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4301 304-Untrimmed, Coil, 2D,
+1.00 x 942.0 x coil mm
+Weight (Kg):2,046
+Quality:Prime
+Help
+Location:FABRICA ALGECIRAS
+2,425.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="124" xml:space="preserve">
+      <c r="A124" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4301 304-Untrimmed, Coil, BA,
+0.30 x 940.0 x coil mm</v>
+      </c>
+      <c r="B124" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4301 304-Untrimmed, Coil, BA,
+0.30 x 940.0 x coil mm
+Weight (Kg):2,140
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,225.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="125" xml:space="preserve">
+      <c r="A125" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4301 304-Untrimmed, Coil, BA,
+0.40 x 1280.0 x coil mm</v>
+      </c>
+      <c r="B125" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4301 304-Untrimmed, Coil, BA,
+0.40 x 1280.0 x coil mm
+Weight (Kg):5,495
+Quality:Prime
+Help
+Location:FABRICA ALGECIRAS
+2,425.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="126" xml:space="preserve">
+      <c r="A126" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4301 304-Untrimmed, Coil, BA,
+0.40 x 578.8 x coil mm</v>
+      </c>
+      <c r="B126" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4301 304-Untrimmed, Coil, BA,
+0.40 x 578.8 x coil mm
+Weight (Kg):3,320
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,125.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="127" xml:space="preserve">
+      <c r="A127" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4301 304-Untrimmed, Coil, BA,
+0.40 x 578.8 x coil mm</v>
+      </c>
+      <c r="B127" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4301 304-Untrimmed, Coil, BA,
+0.40 x 578.8 x coil mm
+Weight (Kg):4,300
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,125.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="128" xml:space="preserve">
+      <c r="A128" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4301 304-Untrimmed, Coil, BA,
+0.40 x 934.0 x coil mm</v>
+      </c>
+      <c r="B128" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4301 304-Untrimmed, Coil, BA,
+0.40 x 934.0 x coil mm
+Weight (Kg):6,960
+Quality:Prime
+Help
+Location:FABRICA ALGECIRAS
+2,425.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="129" xml:space="preserve">
+      <c r="A129" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4301 304-Untrimmed, Coil, BA,
+0.40 x 940.0 x coil mm</v>
+      </c>
+      <c r="B129" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4301 304-Untrimmed, Coil, BA,
+0.40 x 940.0 x coil mm
+Weight (Kg):2,125
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,225.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="130" xml:space="preserve">
+      <c r="A130" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4301 304-Untrimmed, Coil, BA,
+0.40 x 940.0 x coil mm</v>
+      </c>
+      <c r="B130" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4301 304-Untrimmed, Coil, BA,
+0.40 x 940.0 x coil mm
+Weight (Kg):6,505
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,225.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="131" xml:space="preserve">
+      <c r="A131" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4301 304-Untrimmed, Coil, BA,
+0.40 x 941.0 x coil mm</v>
+      </c>
+      <c r="B131" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4301 304-Untrimmed, Coil, BA,
+0.40 x 941.0 x coil mm
+Weight (Kg):2,375
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,225.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="132" xml:space="preserve">
+      <c r="A132" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4301 304-Untrimmed, Coil, BA,
+0.40 x 941.0 x coil mm</v>
+      </c>
+      <c r="B132" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4301 304-Untrimmed, Coil, BA,
+0.40 x 941.0 x coil mm
+Weight (Kg):2,126
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,225.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="133" xml:space="preserve">
+      <c r="A133" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4301 304-Untrimmed, Coil, BA,
+0.40 x 943.0 x coil mm</v>
+      </c>
+      <c r="B133" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4301 304-Untrimmed, Coil, BA,
+0.40 x 943.0 x coil mm
+Weight (Kg):3,205
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,225.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="134" xml:space="preserve">
+      <c r="A134" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4301 304-Untrimmed, Coil, BA,
+0.40 x 943.0 x coil mm</v>
+      </c>
+      <c r="B134" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4301 304-Untrimmed, Coil, BA,
+0.40 x 943.0 x coil mm
+Weight (Kg):2,585
+Quality:Prime
+Help
+Location:FABRICA ALGECIRAS
+2,425.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="135" xml:space="preserve">
+      <c r="A135" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4301 304-Untrimmed, Coil, BA,
+0.40 x 943.0 x coil mm</v>
+      </c>
+      <c r="B135" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4301 304-Untrimmed, Coil, BA,
+0.40 x 943.0 x coil mm
+Weight (Kg):3,349
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,225.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="136" xml:space="preserve">
+      <c r="A136" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4301 304-Untrimmed, Coil, BA,
+0.60 x 1280.0 x coil mm</v>
+      </c>
+      <c r="B136" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4301 304-Untrimmed, Coil, BA,
+0.60 x 1280.0 x coil mm
+Weight (Kg):2,150
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,225.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="137" xml:space="preserve">
+      <c r="A137" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4301 304-Untrimmed, Coil, BA,
+0.60 x 938.0 x coil mm</v>
+      </c>
+      <c r="B137" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4301 304-Untrimmed, Coil, BA,
+0.60 x 938.0 x coil mm
+Weight (Kg):1,785
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,225.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="138" xml:space="preserve">
+      <c r="A138" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4301 304-Untrimmed, Coil, BA,
+0.70 x 1190.0 x coil mm</v>
+      </c>
+      <c r="B138" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4301 304-Untrimmed, Coil, BA,
+0.70 x 1190.0 x coil mm
+Weight (Kg):3,320
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,225.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="139" xml:space="preserve">
+      <c r="A139" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4301 304-Untrimmed, Coil, BA,
+0.70 x 1223.0 x coil mm</v>
+      </c>
+      <c r="B139" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4301 304-Untrimmed, Coil, BA,
+0.70 x 1223.0 x coil mm
+Weight (Kg):8,790
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,225.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="140" xml:space="preserve">
+      <c r="A140" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4301 304-Untrimmed, Coil, BA,
+0.60 x 1197.0 x coil mm</v>
+      </c>
+      <c r="B140" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4301 304-Untrimmed, Coil, BA,
+0.60 x 1197.0 x coil mm
+Weight (Kg):5,662
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,225.00 €/ton
+Reserved</v>
+      </c>
+    </row>
+    <row r="141" xml:space="preserve">
+      <c r="A141" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4301 304-Untrimmed, Coil, BA,
+0.60 x 1222.0 x coil mm</v>
+      </c>
+      <c r="B141" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4301 304-Untrimmed, Coil, BA,
+0.60 x 1222.0 x coil mm
+Weight (Kg):2,896
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,225.00 €/ton
+Reserved</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B21"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B141"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/scraped_data.xlsx
+++ b/scraped_data.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B141"/>
+  <dimension ref="A1:B661"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -2647,9 +2647,8329 @@
 Reserved</v>
       </c>
     </row>
+    <row r="142" xml:space="preserve">
+      <c r="A142" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4301 304-Untrimmed, Coil, BA,
+0.70 x 1273.0 x coil mm</v>
+      </c>
+      <c r="B142" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4301 304-Untrimmed, Coil, BA,
+0.70 x 1273.0 x coil mm
+Weight (Kg):3,140
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,225.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="143" xml:space="preserve">
+      <c r="A143" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4301 304-Untrimmed, Coil, BA,
+0.70 x 1273.0 x coil mm</v>
+      </c>
+      <c r="B143" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4301 304-Untrimmed, Coil, BA,
+0.70 x 1273.0 x coil mm
+Weight (Kg):3,323
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,225.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="144" xml:space="preserve">
+      <c r="A144" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4301 304-Untrimmed, Coil, BA,
+0.90 x 1245.0 x coil mm</v>
+      </c>
+      <c r="B144" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4301 304-Untrimmed, Coil, BA,
+0.90 x 1245.0 x coil mm
+Weight (Kg):2,372
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,225.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="145" xml:space="preserve">
+      <c r="A145" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4301 304-Untrimmed, Coil, SB-G-400,
+1.00 x 850.0 x coil mm</v>
+      </c>
+      <c r="B145" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4301 304-Untrimmed, Coil, SB-G-400,
+1.00 x 850.0 x coil mm
+Weight (Kg):5,870
+Quality:Prime
+Help
+Location:FABRICA ALGECIRAS
+2,425.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="146" xml:space="preserve">
+      <c r="A146" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4301 304DDQ-Coil, BA,
+0.70 x 1020.0 x coil mm</v>
+      </c>
+      <c r="B146" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4301 304DDQ-Coil, BA,
+0.70 x 1020.0 x coil mm
+Weight (Kg):7,100
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,225.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="147" xml:space="preserve">
+      <c r="A147" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4301 304DDQ-Coil, BA,
+0.70 x 340.0 x coil mm</v>
+      </c>
+      <c r="B147" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4301 304DDQ-Coil, BA,
+0.70 x 340.0 x coil mm
+Weight (Kg):4,352
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,075.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="148" xml:space="preserve">
+      <c r="A148" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4301 304DDQ-Coil, BA,
+0.70 x 943.0 x coil mm</v>
+      </c>
+      <c r="B148" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4301 304DDQ-Coil, BA,
+0.70 x 943.0 x coil mm
+Weight (Kg):16,790
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,225.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="149" xml:space="preserve">
+      <c r="A149" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4301 304DDQ-Coil, BA,
+0.70 x 943.0 x coil mm</v>
+      </c>
+      <c r="B149" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4301 304DDQ-Coil, BA,
+0.70 x 943.0 x coil mm
+Weight (Kg):16,740
+Quality:Prime
+Help
+Location:FABRICA ALGECIRAS
+2,900.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="150" xml:space="preserve">
+      <c r="A150" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4301 304DDQ-Coil, BA,
+0.70 x 943.0 x coil mm</v>
+      </c>
+      <c r="B150" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4301 304DDQ-Coil, BA,
+0.70 x 943.0 x coil mm
+Weight (Kg):16,670
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,225.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="151" xml:space="preserve">
+      <c r="A151" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4301 304DDQ-Coil, BA,
+0.70 x 943.0 x coil mm</v>
+      </c>
+      <c r="B151" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4301 304DDQ-Coil, BA,
+0.70 x 943.0 x coil mm
+Weight (Kg):16,680
+Quality:Prime
+Help
+Location:FABRICA ALGECIRAS
+2,900.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="152" xml:space="preserve">
+      <c r="A152" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4301 304DDQ-Coil, BA,
+0.70 x 951.0 x coil mm</v>
+      </c>
+      <c r="B152" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4301 304DDQ-Coil, BA,
+0.70 x 951.0 x coil mm
+Weight (Kg):3,561
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,225.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="153" xml:space="preserve">
+      <c r="A153" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4301 304DDQ-Coil, BA,
+0.70 x 951.0 x coil mm</v>
+      </c>
+      <c r="B153" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4301 304DDQ-Coil, BA,
+0.70 x 951.0 x coil mm
+Weight (Kg):2,860
+Quality:Prime
+Help
+Location:FABRICA ALGECIRAS
+2,425.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="154" xml:space="preserve">
+      <c r="A154" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4301 304DDQ-Untrimmed, Coil, BA,
+0.80 x 1265.0 x coil mm</v>
+      </c>
+      <c r="B154" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4301 304DDQ-Untrimmed, Coil, BA,
+0.80 x 1265.0 x coil mm
+Weight (Kg):2,700
+Quality:Prime
+Help
+Location:FABRICA ALGECIRAS
+2,425.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="155" xml:space="preserve">
+      <c r="A155" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4306 304L-Coil, 2B,
+0.40 x 1270.0 x coil mm</v>
+      </c>
+      <c r="B155" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4306 304L-Coil, 2B,
+0.40 x 1270.0 x coil mm
+Weight (Kg):3,940
+Quality:Prime
+Help
+Location:FABRICA ALGECIRAS
+2,425.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="156" xml:space="preserve">
+      <c r="A156" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4306 304L-Coil, 2B,
+0.40 x 390.0 x coil mm</v>
+      </c>
+      <c r="B156" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4306 304L-Coil, 2B,
+0.40 x 390.0 x coil mm
+Weight (Kg):1,250
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,075.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="157" xml:space="preserve">
+      <c r="A157" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4306 304L-Coil, 2B,
+0.90 x 1271.0 x coil mm</v>
+      </c>
+      <c r="B157" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4306 304L-Coil, 2B,
+0.90 x 1271.0 x coil mm
+Weight (Kg):3,100
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,225.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="158" xml:space="preserve">
+      <c r="A158" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L-Sheet, SB-G-500,
+3.00 x 1500.0 x 3000.0 mm</v>
+      </c>
+      <c r="B158" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L-Sheet, SB-G-500,
+3.00 x 1500.0 x 3000.0 mm
+Weight (Kg):1,466
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,225.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="159" xml:space="preserve">
+      <c r="A159" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Coil, 2B,
+0.80 x 150.9 x coil mm</v>
+      </c>
+      <c r="B159" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Coil, 2B,
+0.80 x 150.9 x coil mm
+Weight (Kg):670
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,075.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="160" xml:space="preserve">
+      <c r="A160" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Coil, 2B,
+1.00 x 125.9 x coil mm</v>
+      </c>
+      <c r="B160" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Coil, 2B,
+1.00 x 125.9 x coil mm
+Weight (Kg):568
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,075.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="161" xml:space="preserve">
+      <c r="A161" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4301 304DDQ-Coil, BA,
+0.70 x 265.9 x coil mm</v>
+      </c>
+      <c r="B161" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4301 304DDQ-Coil, BA,
+0.70 x 265.9 x coil mm
+Weight (Kg):2,906
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,075.00 €/ton
+Out of Stock</v>
+      </c>
+    </row>
+    <row r="162" xml:space="preserve">
+      <c r="A162" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Coil, 2B,
+1.00 x 135.9 x coil mm</v>
+      </c>
+      <c r="B162" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Coil, 2B,
+1.00 x 135.9 x coil mm
+Weight (Kg):538
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,075.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="163" xml:space="preserve">
+      <c r="A163" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Coil, 2B,
+1.40 x 101.0 x coil mm</v>
+      </c>
+      <c r="B163" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Coil, 2B,
+1.40 x 101.0 x coil mm
+Weight (Kg):504
+Quality:Prime
+Help
+Location:FABRICA ALGECIRAS
+2,075.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="164" xml:space="preserve">
+      <c r="A164" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Coil, 2B,
+1.40 x 105.0 x coil mm</v>
+      </c>
+      <c r="B164" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Coil, 2B,
+1.40 x 105.0 x coil mm
+Weight (Kg):530
+Quality:Prime
+Help
+Location:FABRICA ALGECIRAS
+2,075.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="165" xml:space="preserve">
+      <c r="A165" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Coil, 2B,
+1.40 x 110.9 x coil mm</v>
+      </c>
+      <c r="B165" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Coil, 2B,
+1.40 x 110.9 x coil mm
+Weight (Kg):616
+Quality:Prime
+Help
+Location:FABRICA ALGECIRAS
+2,075.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="166" xml:space="preserve">
+      <c r="A166" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Coil, 2B,
+1.50 x 1289.0 x coil mm</v>
+      </c>
+      <c r="B166" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Coil, 2B,
+1.50 x 1289.0 x coil mm
+Weight (Kg):3,070
+Quality:Prime
+Help
+Location:FABRICA ALGECIRAS
+2,425.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="167" xml:space="preserve">
+      <c r="A167" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Coil, 2B,
+1.50 x 200.9 x coil mm</v>
+      </c>
+      <c r="B167" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Coil, 2B,
+1.50 x 200.9 x coil mm
+Weight (Kg):964
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,075.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="168" xml:space="preserve">
+      <c r="A168" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Coil, 2B,
+1.50 x 230.9 x coil mm</v>
+      </c>
+      <c r="B168" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Coil, 2B,
+1.50 x 230.9 x coil mm
+Weight (Kg):4,140
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,075.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="169" xml:space="preserve">
+      <c r="A169" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Coil, 2B,
+1.80 x 102.0 x coil mm</v>
+      </c>
+      <c r="B169" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Coil, 2B,
+1.80 x 102.0 x coil mm
+Weight (Kg):794
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,075.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="170" xml:space="preserve">
+      <c r="A170" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Coil, 2B,
+2.00 x 1277.0 x coil mm</v>
+      </c>
+      <c r="B170" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Coil, 2B,
+2.00 x 1277.0 x coil mm
+Weight (Kg):2,940
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,225.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="171" xml:space="preserve">
+      <c r="A171" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Coil, 2B,
+2.00 x 553.0 x coil mm</v>
+      </c>
+      <c r="B171" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Coil, 2B,
+2.00 x 553.0 x coil mm
+Weight (Kg):385
+Quality:Downgraded
+Help
+Location:FABRICA ALGECIRAS
+2,025.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="172" xml:space="preserve">
+      <c r="A172" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Coil, 2B,
+2.00 x 553.0 x coil mm</v>
+      </c>
+      <c r="B172" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Coil, 2B,
+2.00 x 553.0 x coil mm
+Weight (Kg):385
+Quality:Downgraded
+Help
+Location:FABRICA ALGECIRAS
+2,025.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="173" xml:space="preserve">
+      <c r="A173" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Coil, 2B,
+2.50 x 1000.0 x coil mm</v>
+      </c>
+      <c r="B173" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Coil, 2B,
+2.50 x 1000.0 x coil mm
+Weight (Kg):2,280
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,225.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="174" xml:space="preserve">
+      <c r="A174" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Coil, 2B,
+5.00 x 265.9 x coil mm</v>
+      </c>
+      <c r="B174" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Coil, 2B,
+5.00 x 265.9 x coil mm
+Weight (Kg):1,596
+Quality:Prime
+Help
+Location:FABRICA ALGECIRAS
+2,075.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="175" xml:space="preserve">
+      <c r="A175" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Coil, 2B,
+5.00 x 286.0 x coil mm</v>
+      </c>
+      <c r="B175" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Coil, 2B,
+5.00 x 286.0 x coil mm
+Weight (Kg):2,451
+Quality:Prime
+Help
+Location:FABRICA ALGECIRAS
+2,075.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="176" xml:space="preserve">
+      <c r="A176" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Coil, 2B,
+5.00 x 286.0 x coil mm</v>
+      </c>
+      <c r="B176" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Coil, 2B,
+5.00 x 286.0 x coil mm
+Weight (Kg):2,451
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,075.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="177" xml:space="preserve">
+      <c r="A177" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Coil, 2B,
+6.00 x 1500.0 x coil mm</v>
+      </c>
+      <c r="B177" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Coil, 2B,
+6.00 x 1500.0 x coil mm
+Weight (Kg):1,700
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,225.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="178" xml:space="preserve">
+      <c r="A178" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Coil, 2B,
+6.00 x 1500.0 x coil mm</v>
+      </c>
+      <c r="B178" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Coil, 2B,
+6.00 x 1500.0 x coil mm
+Weight (Kg):2,355
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,225.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="179" xml:space="preserve">
+      <c r="A179" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Coil, 2B,
+6.00 x 1500.0 x coil mm</v>
+      </c>
+      <c r="B179" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Coil, 2B,
+6.00 x 1500.0 x coil mm
+Weight (Kg):2,375
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,225.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="180" xml:space="preserve">
+      <c r="A180" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Coil, 2B,
+6.00 x 1500.0 x coil mm</v>
+      </c>
+      <c r="B180" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Coil, 2B,
+6.00 x 1500.0 x coil mm
+Weight (Kg):2,204
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,225.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="181" xml:space="preserve">
+      <c r="A181" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Coil, 2B,
+6.00 x 1500.0 x coil mm</v>
+      </c>
+      <c r="B181" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Coil, 2B,
+6.00 x 1500.0 x coil mm
+Weight (Kg):2,204
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,225.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="182" xml:space="preserve">
+      <c r="A182" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Coil, 2B,
+6.00 x 1500.0 x coil mm</v>
+      </c>
+      <c r="B182" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Coil, 2B,
+6.00 x 1500.0 x coil mm
+Weight (Kg):2,844
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,225.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="183" xml:space="preserve">
+      <c r="A183" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Coil, 2B,
+6.00 x 220.0 x coil mm</v>
+      </c>
+      <c r="B183" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Coil, 2B,
+6.00 x 220.0 x coil mm
+Weight (Kg):4,046
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,075.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="184" xml:space="preserve">
+      <c r="A184" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Coil, 2B,
+6.00 x 250.0 x coil mm</v>
+      </c>
+      <c r="B184" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Coil, 2B,
+6.00 x 250.0 x coil mm
+Weight (Kg):3,086
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,075.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="185" xml:space="preserve">
+      <c r="A185" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Coil, BA,
+0.70 x 1268.0 x coil mm</v>
+      </c>
+      <c r="B185" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Coil, BA,
+0.70 x 1268.0 x coil mm
+Weight (Kg):20,010
+Quality:Prime
+Help
+Location:FABRICA ALGECIRAS
+2,900.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="186" xml:space="preserve">
+      <c r="A186" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Coil, Emboss Skin,
+0.50 x 1250.0 x coil mm</v>
+      </c>
+      <c r="B186" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Coil, Emboss Skin,
+0.50 x 1250.0 x coil mm
+Weight (Kg):3,950
+Quality:Prime
+Help
+Location:FABRICA ALGECIRAS
+2,425.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="187" xml:space="preserve">
+      <c r="A187" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Coil, Emboss Skin,
+0.50 x 1261.0 x coil mm</v>
+      </c>
+      <c r="B187" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Coil, Emboss Skin,
+0.50 x 1261.0 x coil mm
+Weight (Kg):10,590
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,225.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="188" xml:space="preserve">
+      <c r="A188" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Coil, Nb. 1,
+4.70 x 220.0 x coil mm</v>
+      </c>
+      <c r="B188" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Coil, Nb. 1,
+4.70 x 220.0 x coil mm
+Weight (Kg):3,704
+Quality:Prime
+Help
+Location:FABRICA ALGECIRAS
+1,975.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="189" xml:space="preserve">
+      <c r="A189" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Coil, Nb. 1,
+8.00 x 1500.0 x coil mm</v>
+      </c>
+      <c r="B189" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Coil, Nb. 1,
+8.00 x 1500.0 x coil mm
+Weight (Kg):4,076
+Quality:Prime
+Help
+Location:FABRICA ALGECIRAS
+2,325.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="190" xml:space="preserve">
+      <c r="A190" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Coil, Nb. 1,
+8.00 x 1500.0 x coil mm</v>
+      </c>
+      <c r="B190" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Coil, Nb. 1,
+8.00 x 1500.0 x coil mm
+Weight (Kg):2,749
+Quality:Prime
+Help
+Location:FABRICA ALGECIRAS
+2,325.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="191" xml:space="preserve">
+      <c r="A191" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Coil, Nb. 2 Chequered,
+6.00 x 1250.0 x coil mm</v>
+      </c>
+      <c r="B191" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Coil, Nb. 2 Chequered,
+6.00 x 1250.0 x coil mm
+Weight (Kg):19,244
+Quality:Prime
+Help
+Location:FABRICA ALGECIRAS
+2,900.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="192" xml:space="preserve">
+      <c r="A192" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Coil, Nb. 3 Chequered,
+4.00 x 1548.0 x coil mm</v>
+      </c>
+      <c r="B192" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Coil, Nb. 3 Chequered,
+4.00 x 1548.0 x coil mm
+Weight (Kg):3,000
+Quality:Prime
+Help
+Location:FABRICA ALGECIRAS
+2,425.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="193" xml:space="preserve">
+      <c r="A193" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Coil, Polished N4-G-180,
+0.90 x 190.0 x coil mm</v>
+      </c>
+      <c r="B193" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Coil, Polished N4-G-180,
+0.90 x 190.0 x coil mm
+Weight (Kg):1,424
+Quality:Prime
+Help
+Location:FABRICA ALGECIRAS
+2,075.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="194" xml:space="preserve">
+      <c r="A194" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Coil, Polished N4-G-180,
+0.90 x 205.9 x coil mm</v>
+      </c>
+      <c r="B194" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Coil, Polished N4-G-180,
+0.90 x 205.9 x coil mm
+Weight (Kg):802
+Quality:Prime
+Help
+Location:FABRICA ALGECIRAS
+2,075.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="195" xml:space="preserve">
+      <c r="A195" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Coil, SB-G-400,
+1.00 x 154.9 x coil mm</v>
+      </c>
+      <c r="B195" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Coil, SB-G-400,
+1.00 x 154.9 x coil mm
+Weight (Kg):1,152
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,075.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="196" xml:space="preserve">
+      <c r="A196" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Coil, SB-G-500,
+0.90 x 1250.0 x coil mm</v>
+      </c>
+      <c r="B196" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Coil, SB-G-500,
+0.90 x 1250.0 x coil mm
+Weight (Kg):2,329
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,225.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="197" xml:space="preserve">
+      <c r="A197" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
+0.70 x 1500.0 x 3000.0 mm</v>
+      </c>
+      <c r="B197" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
+0.70 x 1500.0 x 3000.0 mm
+Weight (Kg):612
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,225.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="198" xml:space="preserve">
+      <c r="A198" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
+0.70 x 1500.0 x 3000.0 mm</v>
+      </c>
+      <c r="B198" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
+0.70 x 1500.0 x 3000.0 mm
+Weight (Kg):702
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,225.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="199" xml:space="preserve">
+      <c r="A199" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Coil, Emboss Skin,
+0.50 x 1250.0 x coil mm</v>
+      </c>
+      <c r="B199" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Coil, Emboss Skin,
+0.50 x 1250.0 x coil mm
+Weight (Kg):6,073
+Quality:Prime
+Help
+Location:FABRICA ALGECIRAS
+2,425.00 €/ton
+Reserved</v>
+      </c>
+    </row>
+    <row r="200" xml:space="preserve">
+      <c r="A200" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Coil, Emboss Skin,
+1.50 x 1250.0 x coil mm</v>
+      </c>
+      <c r="B200" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Coil, Emboss Skin,
+1.50 x 1250.0 x coil mm
+Weight (Kg):3,390
+Quality:Prime
+Help
+Location:FABRICA ALGECIRAS
+2,425.00 €/ton
+Reserved</v>
+      </c>
+    </row>
+    <row r="201" xml:space="preserve">
+      <c r="A201" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Coil, Nb. 1,
+3.00 x 1500.0 x coil mm</v>
+      </c>
+      <c r="B201" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Coil, Nb. 1,
+3.00 x 1500.0 x coil mm
+Weight (Kg):3,662
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,125.00 €/ton
+Out of Stock</v>
+      </c>
+    </row>
+    <row r="202" xml:space="preserve">
+      <c r="A202" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
+0.80 x 1000.0 x 2000.0 mm</v>
+      </c>
+      <c r="B202" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
+0.80 x 1000.0 x 2000.0 mm
+Weight (Kg):580
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,225.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="203" xml:space="preserve">
+      <c r="A203" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
+1.00 x 1500.0 x 3000.0 mm</v>
+      </c>
+      <c r="B203" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
+1.00 x 1500.0 x 3000.0 mm
+Weight (Kg):959
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,225.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="204" xml:space="preserve">
+      <c r="A204" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
+1.00 x 1500.0 x 3000.0 mm</v>
+      </c>
+      <c r="B204" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
+1.00 x 1500.0 x 3000.0 mm
+Weight (Kg):794
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,225.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="205" xml:space="preserve">
+      <c r="A205" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
+1.00 x 1500.0 x 3000.0 mm</v>
+      </c>
+      <c r="B205" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
+1.00 x 1500.0 x 3000.0 mm
+Weight (Kg):659
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,225.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="206" xml:space="preserve">
+      <c r="A206" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
+1.00 x 1500.0 x 3000.0 mm</v>
+      </c>
+      <c r="B206" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
+1.00 x 1500.0 x 3000.0 mm
+Weight (Kg):1,508
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,225.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="207" xml:space="preserve">
+      <c r="A207" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
+1.00 x 1500.0 x 3000.0 mm</v>
+      </c>
+      <c r="B207" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
+1.00 x 1500.0 x 3000.0 mm
+Weight (Kg):1,921
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,225.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="208" xml:space="preserve">
+      <c r="A208" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
+1.00 x 1500.0 x 3000.0 mm</v>
+      </c>
+      <c r="B208" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
+1.00 x 1500.0 x 3000.0 mm
+Weight (Kg):894
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,225.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="209" xml:space="preserve">
+      <c r="A209" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
+1.00 x 1500.0 x 3000.0 mm</v>
+      </c>
+      <c r="B209" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
+1.00 x 1500.0 x 3000.0 mm
+Weight (Kg):700
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,225.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="210" xml:space="preserve">
+      <c r="A210" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
+1.00 x 1500.0 x 3000.0 mm</v>
+      </c>
+      <c r="B210" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
+1.00 x 1500.0 x 3000.0 mm
+Weight (Kg):842
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,225.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="211" xml:space="preserve">
+      <c r="A211" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
+2.00 x 1000.0 x 2000.0 mm</v>
+      </c>
+      <c r="B211" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
+2.00 x 1000.0 x 2000.0 mm
+Weight (Kg):512
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,225.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="212" xml:space="preserve">
+      <c r="A212" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
+2.00 x 1000.0 x 2000.0 mm</v>
+      </c>
+      <c r="B212" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
+2.00 x 1000.0 x 2000.0 mm
+Weight (Kg):949
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,225.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="213" xml:space="preserve">
+      <c r="A213" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
+2.00 x 1250.0 x 2500.0 mm</v>
+      </c>
+      <c r="B213" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
+2.00 x 1250.0 x 2500.0 mm
+Weight (Kg):735
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,225.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="214" xml:space="preserve">
+      <c r="A214" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
+2.00 x 1250.0 x 2500.0 mm</v>
+      </c>
+      <c r="B214" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
+2.00 x 1250.0 x 2500.0 mm
+Weight (Kg):805
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,225.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="215" xml:space="preserve">
+      <c r="A215" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
+2.00 x 1250.0 x 2500.0 mm</v>
+      </c>
+      <c r="B215" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
+2.00 x 1250.0 x 2500.0 mm
+Weight (Kg):777
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,225.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="216" xml:space="preserve">
+      <c r="A216" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
+2.00 x 1250.0 x 2500.0 mm</v>
+      </c>
+      <c r="B216" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
+2.00 x 1250.0 x 2500.0 mm
+Weight (Kg):576
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,225.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="217" xml:space="preserve">
+      <c r="A217" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
+2.00 x 1250.0 x 2500.0 mm</v>
+      </c>
+      <c r="B217" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
+2.00 x 1250.0 x 2500.0 mm
+Weight (Kg):622
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,225.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="218" xml:space="preserve">
+      <c r="A218" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
+2.00 x 1250.0 x 2500.0 mm</v>
+      </c>
+      <c r="B218" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
+2.00 x 1250.0 x 2500.0 mm
+Weight (Kg):862
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,225.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="219" xml:space="preserve">
+      <c r="A219" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
+2.00 x 1250.0 x 2500.0 mm</v>
+      </c>
+      <c r="B219" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
+2.00 x 1250.0 x 2500.0 mm
+Weight (Kg):619
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,225.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="220" xml:space="preserve">
+      <c r="A220" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
+2.00 x 1250.0 x 2500.0 mm</v>
+      </c>
+      <c r="B220" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
+2.00 x 1250.0 x 2500.0 mm
+Weight (Kg):867
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,225.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="221" xml:space="preserve">
+      <c r="A221" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
+2.00 x 1250.0 x 2500.0 mm</v>
+      </c>
+      <c r="B221" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
+2.00 x 1250.0 x 2500.0 mm
+Weight (Kg):774
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,225.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="222" xml:space="preserve">
+      <c r="A222" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
+2.00 x 1250.0 x 3000.0 mm</v>
+      </c>
+      <c r="B222" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
+2.00 x 1250.0 x 3000.0 mm
+Weight (Kg):877
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,225.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="223" xml:space="preserve">
+      <c r="A223" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
+2.50 x 1000.0 x 2000.0 mm</v>
+      </c>
+      <c r="B223" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
+2.50 x 1000.0 x 2000.0 mm
+Weight (Kg):781
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,225.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="224" xml:space="preserve">
+      <c r="A224" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
+2.50 x 1000.0 x 2000.0 mm</v>
+      </c>
+      <c r="B224" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
+2.50 x 1000.0 x 2000.0 mm
+Weight (Kg):590
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,225.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="225" xml:space="preserve">
+      <c r="A225" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
+2.50 x 1250.0 x 2500.0 mm</v>
+      </c>
+      <c r="B225" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
+2.50 x 1250.0 x 2500.0 mm
+Weight (Kg):660
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,225.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="226" xml:space="preserve">
+      <c r="A226" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
+2.50 x 1250.0 x 2500.0 mm</v>
+      </c>
+      <c r="B226" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
+2.50 x 1250.0 x 2500.0 mm
+Weight (Kg):852
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,225.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="227" xml:space="preserve">
+      <c r="A227" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
+2.50 x 1500.0 x 3000.0 mm</v>
+      </c>
+      <c r="B227" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
+2.50 x 1500.0 x 3000.0 mm
+Weight (Kg):792
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,225.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="228" xml:space="preserve">
+      <c r="A228" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
+2.50 x 1500.0 x 3000.0 mm</v>
+      </c>
+      <c r="B228" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
+2.50 x 1500.0 x 3000.0 mm
+Weight (Kg):1,390
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,225.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="229" xml:space="preserve">
+      <c r="A229" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
+2.50 x 1500.0 x 3000.0 mm</v>
+      </c>
+      <c r="B229" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
+2.50 x 1500.0 x 3000.0 mm
+Weight (Kg):1,224
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,225.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="230" xml:space="preserve">
+      <c r="A230" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
+2.50 x 1500.0 x 3000.0 mm</v>
+      </c>
+      <c r="B230" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
+2.50 x 1500.0 x 3000.0 mm
+Weight (Kg):2,098
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,225.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="231" xml:space="preserve">
+      <c r="A231" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
+2.50 x 1500.0 x 3000.0 mm</v>
+      </c>
+      <c r="B231" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
+2.50 x 1500.0 x 3000.0 mm
+Weight (Kg):1,238
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,225.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="232" xml:space="preserve">
+      <c r="A232" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
+2.50 x 1500.0 x 3000.0 mm</v>
+      </c>
+      <c r="B232" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
+2.50 x 1500.0 x 3000.0 mm
+Weight (Kg):856
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,225.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="233" xml:space="preserve">
+      <c r="A233" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
+2.50 x 1500.0 x 3000.0 mm</v>
+      </c>
+      <c r="B233" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
+2.50 x 1500.0 x 3000.0 mm
+Weight (Kg):605
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,225.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="234" xml:space="preserve">
+      <c r="A234" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
+2.50 x 1500.0 x 3000.0 mm</v>
+      </c>
+      <c r="B234" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
+2.50 x 1500.0 x 3000.0 mm
+Weight (Kg):521
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,225.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="235" xml:space="preserve">
+      <c r="A235" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
+2.50 x 1500.0 x 3000.0 mm</v>
+      </c>
+      <c r="B235" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
+2.50 x 1500.0 x 3000.0 mm
+Weight (Kg):527
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,225.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="236" xml:space="preserve">
+      <c r="A236" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
+2.50 x 1500.0 x 3000.0 mm</v>
+      </c>
+      <c r="B236" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
+2.50 x 1500.0 x 3000.0 mm
+Weight (Kg):862
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,225.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="237" xml:space="preserve">
+      <c r="A237" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
+3.00 x 1000.0 x 2000.0 mm</v>
+      </c>
+      <c r="B237" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
+3.00 x 1000.0 x 2000.0 mm
+Weight (Kg):992
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,225.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="238" xml:space="preserve">
+      <c r="A238" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
+3.00 x 1000.0 x 2000.0 mm</v>
+      </c>
+      <c r="B238" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
+3.00 x 1000.0 x 2000.0 mm
+Weight (Kg):1,038
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,225.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="239" xml:space="preserve">
+      <c r="A239" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
+3.00 x 1000.0 x 2000.0 mm</v>
+      </c>
+      <c r="B239" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
+3.00 x 1000.0 x 2000.0 mm
+Weight (Kg):946
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,225.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="240" xml:space="preserve">
+      <c r="A240" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
+3.00 x 1000.0 x 2000.0 mm</v>
+      </c>
+      <c r="B240" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
+3.00 x 1000.0 x 2000.0 mm
+Weight (Kg):503
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,225.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="241" xml:space="preserve">
+      <c r="A241" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
+3.00 x 1000.0 x 2000.0 mm</v>
+      </c>
+      <c r="B241" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
+3.00 x 1000.0 x 2000.0 mm
+Weight (Kg):880
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,225.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="242" xml:space="preserve">
+      <c r="A242" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
+3.00 x 1000.0 x 2000.0 mm</v>
+      </c>
+      <c r="B242" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
+3.00 x 1000.0 x 2000.0 mm
+Weight (Kg):796
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,225.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="243" xml:space="preserve">
+      <c r="A243" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
+3.00 x 1000.0 x 2000.0 mm</v>
+      </c>
+      <c r="B243" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
+3.00 x 1000.0 x 2000.0 mm
+Weight (Kg):578
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,225.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="244" xml:space="preserve">
+      <c r="A244" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
+3.00 x 1000.0 x 2000.0 mm</v>
+      </c>
+      <c r="B244" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
+3.00 x 1000.0 x 2000.0 mm
+Weight (Kg):1,506
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,225.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="245" xml:space="preserve">
+      <c r="A245" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
+3.00 x 1000.0 x 2000.0 mm</v>
+      </c>
+      <c r="B245" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
+3.00 x 1000.0 x 2000.0 mm
+Weight (Kg):1,538
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,225.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="246" xml:space="preserve">
+      <c r="A246" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
+3.00 x 1000.0 x 2000.0 mm</v>
+      </c>
+      <c r="B246" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
+3.00 x 1000.0 x 2000.0 mm
+Weight (Kg):520
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,225.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="247" xml:space="preserve">
+      <c r="A247" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
+3.00 x 1250.0 x 2500.0 mm</v>
+      </c>
+      <c r="B247" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
+3.00 x 1250.0 x 2500.0 mm
+Weight (Kg):886
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,225.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="248" xml:space="preserve">
+      <c r="A248" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
+3.00 x 1250.0 x 2500.0 mm</v>
+      </c>
+      <c r="B248" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
+3.00 x 1250.0 x 2500.0 mm
+Weight (Kg):1,233
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,225.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="249" xml:space="preserve">
+      <c r="A249" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
+3.00 x 1250.0 x 2500.0 mm</v>
+      </c>
+      <c r="B249" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
+3.00 x 1250.0 x 2500.0 mm
+Weight (Kg):742
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,225.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="250" xml:space="preserve">
+      <c r="A250" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
+3.00 x 1250.0 x 2500.0 mm</v>
+      </c>
+      <c r="B250" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
+3.00 x 1250.0 x 2500.0 mm
+Weight (Kg):858
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,225.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="251" xml:space="preserve">
+      <c r="A251" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
+3.00 x 1250.0 x 2500.0 mm</v>
+      </c>
+      <c r="B251" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
+3.00 x 1250.0 x 2500.0 mm
+Weight (Kg):1,450
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,225.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="252" xml:space="preserve">
+      <c r="A252" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
+3.00 x 1250.0 x 2500.0 mm</v>
+      </c>
+      <c r="B252" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
+3.00 x 1250.0 x 2500.0 mm
+Weight (Kg):1,818
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,225.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="253" xml:space="preserve">
+      <c r="A253" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
+3.00 x 1250.0 x 2500.0 mm</v>
+      </c>
+      <c r="B253" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
+3.00 x 1250.0 x 2500.0 mm
+Weight (Kg):1,220
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,225.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="254" xml:space="preserve">
+      <c r="A254" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
+3.00 x 1250.0 x 2500.0 mm</v>
+      </c>
+      <c r="B254" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
+3.00 x 1250.0 x 2500.0 mm
+Weight (Kg):812
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,225.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="255" xml:space="preserve">
+      <c r="A255" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
+3.00 x 1250.0 x 2500.0 mm</v>
+      </c>
+      <c r="B255" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
+3.00 x 1250.0 x 2500.0 mm
+Weight (Kg):816
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,225.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="256" xml:space="preserve">
+      <c r="A256" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
+3.00 x 1250.0 x 2500.0 mm</v>
+      </c>
+      <c r="B256" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
+3.00 x 1250.0 x 2500.0 mm
+Weight (Kg):1,320
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,225.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="257" xml:space="preserve">
+      <c r="A257" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
+3.00 x 1250.0 x 2500.0 mm</v>
+      </c>
+      <c r="B257" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
+3.00 x 1250.0 x 2500.0 mm
+Weight (Kg):830
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,225.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="258" xml:space="preserve">
+      <c r="A258" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
+3.00 x 1250.0 x 2500.0 mm</v>
+      </c>
+      <c r="B258" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
+3.00 x 1250.0 x 2500.0 mm
+Weight (Kg):1,446
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,225.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="259" xml:space="preserve">
+      <c r="A259" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
+3.00 x 1250.0 x 2500.0 mm</v>
+      </c>
+      <c r="B259" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
+3.00 x 1250.0 x 2500.0 mm
+Weight (Kg):670
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,225.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="260" xml:space="preserve">
+      <c r="A260" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
+3.00 x 1250.0 x 2500.0 mm</v>
+      </c>
+      <c r="B260" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
+3.00 x 1250.0 x 2500.0 mm
+Weight (Kg):884
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,225.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="261" xml:space="preserve">
+      <c r="A261" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
+3.00 x 1250.0 x 2500.0 mm</v>
+      </c>
+      <c r="B261" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
+3.00 x 1250.0 x 2500.0 mm
+Weight (Kg):762
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,225.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="262" xml:space="preserve">
+      <c r="A262" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
+3.00 x 1500.0 x 3000.0 mm</v>
+      </c>
+      <c r="B262" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
+3.00 x 1500.0 x 3000.0 mm
+Weight (Kg):744
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,225.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="263" xml:space="preserve">
+      <c r="A263" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
+3.00 x 1500.0 x 3000.0 mm</v>
+      </c>
+      <c r="B263" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
+3.00 x 1500.0 x 3000.0 mm
+Weight (Kg):1,394
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,225.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="264" xml:space="preserve">
+      <c r="A264" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
+3.00 x 1500.0 x 3000.0 mm</v>
+      </c>
+      <c r="B264" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
+3.00 x 1500.0 x 3000.0 mm
+Weight (Kg):2,224
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,225.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="265" xml:space="preserve">
+      <c r="A265" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
+3.00 x 1500.0 x 3000.0 mm</v>
+      </c>
+      <c r="B265" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
+3.00 x 1500.0 x 3000.0 mm
+Weight (Kg):1,156
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,225.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="266" xml:space="preserve">
+      <c r="A266" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
+3.00 x 1500.0 x 3000.0 mm</v>
+      </c>
+      <c r="B266" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
+3.00 x 1500.0 x 3000.0 mm
+Weight (Kg):632
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,225.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="267" xml:space="preserve">
+      <c r="A267" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
+3.00 x 1500.0 x 3000.0 mm</v>
+      </c>
+      <c r="B267" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
+3.00 x 1500.0 x 3000.0 mm
+Weight (Kg):950
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,225.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="268" xml:space="preserve">
+      <c r="A268" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
+3.00 x 1500.0 x 3000.0 mm</v>
+      </c>
+      <c r="B268" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
+3.00 x 1500.0 x 3000.0 mm
+Weight (Kg):750
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,225.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="269" xml:space="preserve">
+      <c r="A269" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
+3.00 x 1500.0 x 3000.0 mm</v>
+      </c>
+      <c r="B269" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
+3.00 x 1500.0 x 3000.0 mm
+Weight (Kg):1,906
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,225.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="270" xml:space="preserve">
+      <c r="A270" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
+3.00 x 1500.0 x 3000.0 mm</v>
+      </c>
+      <c r="B270" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
+3.00 x 1500.0 x 3000.0 mm
+Weight (Kg):640
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,225.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="271" xml:space="preserve">
+      <c r="A271" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
+3.00 x 1500.0 x 3000.0 mm</v>
+      </c>
+      <c r="B271" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
+3.00 x 1500.0 x 3000.0 mm
+Weight (Kg):1,496
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,225.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="272" xml:space="preserve">
+      <c r="A272" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
+4.00 x 1000.0 x 2000.0 mm</v>
+      </c>
+      <c r="B272" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
+4.00 x 1000.0 x 2000.0 mm
+Weight (Kg):1,348
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,225.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="273" xml:space="preserve">
+      <c r="A273" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
+4.00 x 1500.0 x 3000.0 mm</v>
+      </c>
+      <c r="B273" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
+4.00 x 1500.0 x 3000.0 mm
+Weight (Kg):1,574
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,225.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="274" xml:space="preserve">
+      <c r="A274" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
+4.00 x 1500.0 x 3000.0 mm</v>
+      </c>
+      <c r="B274" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
+4.00 x 1500.0 x 3000.0 mm
+Weight (Kg):1,861
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,225.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="275" xml:space="preserve">
+      <c r="A275" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
+4.00 x 1500.0 x 3000.0 mm</v>
+      </c>
+      <c r="B275" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
+4.00 x 1500.0 x 3000.0 mm
+Weight (Kg):1,722
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,225.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="276" xml:space="preserve">
+      <c r="A276" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
+4.00 x 1500.0 x 3000.0 mm</v>
+      </c>
+      <c r="B276" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
+4.00 x 1500.0 x 3000.0 mm
+Weight (Kg):1,726
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,225.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="277" xml:space="preserve">
+      <c r="A277" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
+4.00 x 1500.0 x 3000.0 mm</v>
+      </c>
+      <c r="B277" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
+4.00 x 1500.0 x 3000.0 mm
+Weight (Kg):999
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,225.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="278" xml:space="preserve">
+      <c r="A278" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
+4.00 x 1500.0 x 3000.0 mm</v>
+      </c>
+      <c r="B278" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
+4.00 x 1500.0 x 3000.0 mm
+Weight (Kg):724
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,225.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="279" xml:space="preserve">
+      <c r="A279" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
+4.00 x 1500.0 x 3000.0 mm</v>
+      </c>
+      <c r="B279" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
+4.00 x 1500.0 x 3000.0 mm
+Weight (Kg):854
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,225.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="280" xml:space="preserve">
+      <c r="A280" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
+4.00 x 1500.0 x 3000.0 mm</v>
+      </c>
+      <c r="B280" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
+4.00 x 1500.0 x 3000.0 mm
+Weight (Kg):1,987
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,225.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="281" xml:space="preserve">
+      <c r="A281" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
+4.00 x 1500.0 x 3000.0 mm</v>
+      </c>
+      <c r="B281" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
+4.00 x 1500.0 x 3000.0 mm
+Weight (Kg):1,708
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,225.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="282" xml:space="preserve">
+      <c r="A282" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
+4.00 x 1500.0 x 3000.0 mm</v>
+      </c>
+      <c r="B282" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
+4.00 x 1500.0 x 3000.0 mm
+Weight (Kg):1,562
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,225.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="283" xml:space="preserve">
+      <c r="A283" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
+5.00 x 1250.0 x 2500.0 mm</v>
+      </c>
+      <c r="B283" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
+5.00 x 1250.0 x 2500.0 mm
+Weight (Kg):2,220
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,225.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="284" xml:space="preserve">
+      <c r="A284" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
+5.00 x 1250.0 x 2500.0 mm</v>
+      </c>
+      <c r="B284" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
+5.00 x 1250.0 x 2500.0 mm
+Weight (Kg):1,580
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,225.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="285" xml:space="preserve">
+      <c r="A285" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
+5.00 x 1250.0 x 2500.0 mm</v>
+      </c>
+      <c r="B285" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
+5.00 x 1250.0 x 2500.0 mm
+Weight (Kg):750
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,225.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="286" xml:space="preserve">
+      <c r="A286" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
+5.00 x 1500.0 x 3000.0 mm</v>
+      </c>
+      <c r="B286" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
+5.00 x 1500.0 x 3000.0 mm
+Weight (Kg):1,777
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,225.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="287" xml:space="preserve">
+      <c r="A287" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
+5.00 x 1500.0 x 3000.0 mm</v>
+      </c>
+      <c r="B287" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
+5.00 x 1500.0 x 3000.0 mm
+Weight (Kg):1,436
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,225.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="288" xml:space="preserve">
+      <c r="A288" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
+5.00 x 1500.0 x 3000.0 mm</v>
+      </c>
+      <c r="B288" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
+5.00 x 1500.0 x 3000.0 mm
+Weight (Kg):890
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,225.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="289" xml:space="preserve">
+      <c r="A289" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
+5.00 x 1500.0 x 3000.0 mm</v>
+      </c>
+      <c r="B289" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
+5.00 x 1500.0 x 3000.0 mm
+Weight (Kg):1,252
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,225.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="290" xml:space="preserve">
+      <c r="A290" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
+5.00 x 1500.0 x 3000.0 mm</v>
+      </c>
+      <c r="B290" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
+5.00 x 1500.0 x 3000.0 mm
+Weight (Kg):1,646
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,225.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="291" xml:space="preserve">
+      <c r="A291" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
+5.00 x 1500.0 x 3000.0 mm</v>
+      </c>
+      <c r="B291" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
+5.00 x 1500.0 x 3000.0 mm
+Weight (Kg):1,434
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,225.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="292" xml:space="preserve">
+      <c r="A292" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
+5.00 x 1500.0 x 3000.0 mm</v>
+      </c>
+      <c r="B292" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
+5.00 x 1500.0 x 3000.0 mm
+Weight (Kg):1,778
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,225.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="293" xml:space="preserve">
+      <c r="A293" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
+5.00 x 1500.0 x 3000.0 mm</v>
+      </c>
+      <c r="B293" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
+5.00 x 1500.0 x 3000.0 mm
+Weight (Kg):1,818
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,225.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="294" xml:space="preserve">
+      <c r="A294" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
+5.00 x 1500.0 x 3000.0 mm</v>
+      </c>
+      <c r="B294" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
+5.00 x 1500.0 x 3000.0 mm
+Weight (Kg):1,807
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,225.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="295" xml:space="preserve">
+      <c r="A295" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
+5.00 x 1500.0 x 3000.0 mm</v>
+      </c>
+      <c r="B295" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
+5.00 x 1500.0 x 3000.0 mm
+Weight (Kg):1,978
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,225.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="296" xml:space="preserve">
+      <c r="A296" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
+5.00 x 1500.0 x 3000.0 mm</v>
+      </c>
+      <c r="B296" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
+5.00 x 1500.0 x 3000.0 mm
+Weight (Kg):1,760
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,225.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="297" xml:space="preserve">
+      <c r="A297" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
+5.00 x 1500.0 x 3000.0 mm</v>
+      </c>
+      <c r="B297" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
+5.00 x 1500.0 x 3000.0 mm
+Weight (Kg):1,976
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,225.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="298" xml:space="preserve">
+      <c r="A298" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
+5.00 x 1500.0 x 3000.0 mm</v>
+      </c>
+      <c r="B298" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
+5.00 x 1500.0 x 3000.0 mm
+Weight (Kg):1,236
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,225.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="299" xml:space="preserve">
+      <c r="A299" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
+5.00 x 1500.0 x 3000.0 mm</v>
+      </c>
+      <c r="B299" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
+5.00 x 1500.0 x 3000.0 mm
+Weight (Kg):1,968
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,225.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="300" xml:space="preserve">
+      <c r="A300" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
+5.00 x 1500.0 x 3000.0 mm</v>
+      </c>
+      <c r="B300" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
+5.00 x 1500.0 x 3000.0 mm
+Weight (Kg):1,240
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,225.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="301" xml:space="preserve">
+      <c r="A301" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
+5.00 x 1500.0 x 3000.0 mm</v>
+      </c>
+      <c r="B301" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
+5.00 x 1500.0 x 3000.0 mm
+Weight (Kg):1,070
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,225.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="302" xml:space="preserve">
+      <c r="A302" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
+5.00 x 1500.0 x 3000.0 mm</v>
+      </c>
+      <c r="B302" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
+5.00 x 1500.0 x 3000.0 mm
+Weight (Kg):1,960
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,225.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="303" xml:space="preserve">
+      <c r="A303" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
+5.00 x 1500.0 x 3000.0 mm</v>
+      </c>
+      <c r="B303" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
+5.00 x 1500.0 x 3000.0 mm
+Weight (Kg):1,734
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,225.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="304" xml:space="preserve">
+      <c r="A304" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
+5.00 x 1500.0 x 3000.0 mm</v>
+      </c>
+      <c r="B304" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
+5.00 x 1500.0 x 3000.0 mm
+Weight (Kg):1,874
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,225.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="305" xml:space="preserve">
+      <c r="A305" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
+5.00 x 1500.0 x 3000.0 mm</v>
+      </c>
+      <c r="B305" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
+5.00 x 1500.0 x 3000.0 mm
+Weight (Kg):884
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,225.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="306" xml:space="preserve">
+      <c r="A306" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
+5.00 x 1500.0 x 3000.0 mm</v>
+      </c>
+      <c r="B306" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
+5.00 x 1500.0 x 3000.0 mm
+Weight (Kg):1,578
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,225.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="307" xml:space="preserve">
+      <c r="A307" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
+5.00 x 1500.0 x 3000.0 mm</v>
+      </c>
+      <c r="B307" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
+5.00 x 1500.0 x 3000.0 mm
+Weight (Kg):852
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,225.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="308" xml:space="preserve">
+      <c r="A308" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
+5.00 x 1500.0 x 3000.0 mm</v>
+      </c>
+      <c r="B308" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
+5.00 x 1500.0 x 3000.0 mm
+Weight (Kg):1,942
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,225.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="309" xml:space="preserve">
+      <c r="A309" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
+6.00 x 1000.0 x 2000.0 mm</v>
+      </c>
+      <c r="B309" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
+6.00 x 1000.0 x 2000.0 mm
+Weight (Kg):1,906
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,225.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="310" xml:space="preserve">
+      <c r="A310" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
+6.00 x 1000.0 x 2000.0 mm</v>
+      </c>
+      <c r="B310" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
+6.00 x 1000.0 x 2000.0 mm
+Weight (Kg):1,886
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,225.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="311" xml:space="preserve">
+      <c r="A311" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
+6.00 x 1000.0 x 2000.0 mm</v>
+      </c>
+      <c r="B311" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
+6.00 x 1000.0 x 2000.0 mm
+Weight (Kg):1,414
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,225.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="312" xml:space="preserve">
+      <c r="A312" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
+6.00 x 1000.0 x 2000.0 mm</v>
+      </c>
+      <c r="B312" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
+6.00 x 1000.0 x 2000.0 mm
+Weight (Kg):1,620
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,225.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="313" xml:space="preserve">
+      <c r="A313" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
+6.00 x 1000.0 x 2000.0 mm</v>
+      </c>
+      <c r="B313" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
+6.00 x 1000.0 x 2000.0 mm
+Weight (Kg):938
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,225.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="314" xml:space="preserve">
+      <c r="A314" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
+6.00 x 1000.0 x 2000.0 mm</v>
+      </c>
+      <c r="B314" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
+6.00 x 1000.0 x 2000.0 mm
+Weight (Kg):1,406
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,225.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="315" xml:space="preserve">
+      <c r="A315" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
+6.00 x 1000.0 x 2000.0 mm</v>
+      </c>
+      <c r="B315" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
+6.00 x 1000.0 x 2000.0 mm
+Weight (Kg):1,140
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,225.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="316" xml:space="preserve">
+      <c r="A316" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
+6.00 x 1250.0 x 2500.0 mm</v>
+      </c>
+      <c r="B316" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
+6.00 x 1250.0 x 2500.0 mm
+Weight (Kg):1,494
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,225.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="317" xml:space="preserve">
+      <c r="A317" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
+6.00 x 1250.0 x 2500.0 mm</v>
+      </c>
+      <c r="B317" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
+6.00 x 1250.0 x 2500.0 mm
+Weight (Kg):1,652
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,225.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="318" xml:space="preserve">
+      <c r="A318" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
+6.00 x 1250.0 x 2500.0 mm</v>
+      </c>
+      <c r="B318" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
+6.00 x 1250.0 x 2500.0 mm
+Weight (Kg):1,610
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,225.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="319" xml:space="preserve">
+      <c r="A319" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
+6.00 x 1250.0 x 2500.0 mm</v>
+      </c>
+      <c r="B319" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
+6.00 x 1250.0 x 2500.0 mm
+Weight (Kg):1,900
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,225.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="320" xml:space="preserve">
+      <c r="A320" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
+6.00 x 1250.0 x 2500.0 mm</v>
+      </c>
+      <c r="B320" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
+6.00 x 1250.0 x 2500.0 mm
+Weight (Kg):2,346
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,225.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="321" xml:space="preserve">
+      <c r="A321" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
+6.00 x 1250.0 x 2500.0 mm</v>
+      </c>
+      <c r="B321" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
+6.00 x 1250.0 x 2500.0 mm
+Weight (Kg):1,624
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,225.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="322" xml:space="preserve">
+      <c r="A322" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
+6.00 x 1500.0 x 3000.0 mm</v>
+      </c>
+      <c r="B322" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
+6.00 x 1500.0 x 3000.0 mm
+Weight (Kg):1,296
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,225.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="323" xml:space="preserve">
+      <c r="A323" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
+6.00 x 1500.0 x 3000.0 mm</v>
+      </c>
+      <c r="B323" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
+6.00 x 1500.0 x 3000.0 mm
+Weight (Kg):1,716
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,225.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="324" xml:space="preserve">
+      <c r="A324" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
+6.00 x 1500.0 x 3000.0 mm</v>
+      </c>
+      <c r="B324" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
+6.00 x 1500.0 x 3000.0 mm
+Weight (Kg):1,917
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,225.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="325" xml:space="preserve">
+      <c r="A325" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
+6.00 x 1500.0 x 3000.0 mm</v>
+      </c>
+      <c r="B325" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
+6.00 x 1500.0 x 3000.0 mm
+Weight (Kg):1,922
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,225.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="326" xml:space="preserve">
+      <c r="A326" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
+6.00 x 1500.0 x 3000.0 mm</v>
+      </c>
+      <c r="B326" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
+6.00 x 1500.0 x 3000.0 mm
+Weight (Kg):1,728
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,225.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="327" xml:space="preserve">
+      <c r="A327" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
+6.00 x 1500.0 x 3000.0 mm</v>
+      </c>
+      <c r="B327" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
+6.00 x 1500.0 x 3000.0 mm
+Weight (Kg):864
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,225.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="328" xml:space="preserve">
+      <c r="A328" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
+6.00 x 1500.0 x 3000.0 mm</v>
+      </c>
+      <c r="B328" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
+6.00 x 1500.0 x 3000.0 mm
+Weight (Kg):1,302
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,225.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="329" xml:space="preserve">
+      <c r="A329" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
+6.00 x 1500.0 x 3000.0 mm</v>
+      </c>
+      <c r="B329" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
+6.00 x 1500.0 x 3000.0 mm
+Weight (Kg):1,062
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,225.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="330" xml:space="preserve">
+      <c r="A330" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
+6.00 x 1500.0 x 3000.0 mm</v>
+      </c>
+      <c r="B330" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
+6.00 x 1500.0 x 3000.0 mm
+Weight (Kg):1,966
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,225.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="331" xml:space="preserve">
+      <c r="A331" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
+6.00 x 1500.0 x 3000.0 mm</v>
+      </c>
+      <c r="B331" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
+6.00 x 1500.0 x 3000.0 mm
+Weight (Kg):1,496
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,225.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="332" xml:space="preserve">
+      <c r="A332" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
+6.00 x 1500.0 x 3000.0 mm</v>
+      </c>
+      <c r="B332" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
+6.00 x 1500.0 x 3000.0 mm
+Weight (Kg):1,320
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,225.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="333" xml:space="preserve">
+      <c r="A333" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
+6.00 x 1500.0 x 3000.0 mm</v>
+      </c>
+      <c r="B333" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
+6.00 x 1500.0 x 3000.0 mm
+Weight (Kg):1,071
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,225.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="334" xml:space="preserve">
+      <c r="A334" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
+6.00 x 1500.0 x 3000.0 mm</v>
+      </c>
+      <c r="B334" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
+6.00 x 1500.0 x 3000.0 mm
+Weight (Kg):1,264
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,225.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="335" xml:space="preserve">
+      <c r="A335" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
+6.00 x 1500.0 x 3000.0 mm</v>
+      </c>
+      <c r="B335" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
+6.00 x 1500.0 x 3000.0 mm
+Weight (Kg):1,916
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,225.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="336" xml:space="preserve">
+      <c r="A336" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
+6.00 x 1500.0 x 3000.0 mm</v>
+      </c>
+      <c r="B336" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
+6.00 x 1500.0 x 3000.0 mm
+Weight (Kg):1,908
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,225.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="337" xml:space="preserve">
+      <c r="A337" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
+6.00 x 1500.0 x 3000.0 mm</v>
+      </c>
+      <c r="B337" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
+6.00 x 1500.0 x 3000.0 mm
+Weight (Kg):1,928
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,225.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="338" xml:space="preserve">
+      <c r="A338" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
+6.00 x 1500.0 x 3000.0 mm</v>
+      </c>
+      <c r="B338" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
+6.00 x 1500.0 x 3000.0 mm
+Weight (Kg):1,290
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,225.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="339" xml:space="preserve">
+      <c r="A339" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
+6.00 x 1500.0 x 3000.0 mm</v>
+      </c>
+      <c r="B339" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
+6.00 x 1500.0 x 3000.0 mm
+Weight (Kg):1,698
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,225.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="340" xml:space="preserve">
+      <c r="A340" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
+6.00 x 1500.0 x 3000.0 mm</v>
+      </c>
+      <c r="B340" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
+6.00 x 1500.0 x 3000.0 mm
+Weight (Kg):1,754
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,225.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="341" xml:space="preserve">
+      <c r="A341" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
+6.00 x 1500.0 x 3000.0 mm</v>
+      </c>
+      <c r="B341" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
+6.00 x 1500.0 x 3000.0 mm
+Weight (Kg):1,716
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,225.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="342" xml:space="preserve">
+      <c r="A342" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
+6.00 x 1500.0 x 3000.0 mm</v>
+      </c>
+      <c r="B342" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
+6.00 x 1500.0 x 3000.0 mm
+Weight (Kg):1,548
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,225.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="343" xml:space="preserve">
+      <c r="A343" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
+6.00 x 1500.0 x 3000.0 mm</v>
+      </c>
+      <c r="B343" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
+6.00 x 1500.0 x 3000.0 mm
+Weight (Kg):1,916
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,225.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="344" xml:space="preserve">
+      <c r="A344" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
+6.00 x 1500.0 x 3000.0 mm</v>
+      </c>
+      <c r="B344" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
+6.00 x 1500.0 x 3000.0 mm
+Weight (Kg):1,485
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,225.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="345" xml:space="preserve">
+      <c r="A345" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
+6.00 x 1500.0 x 3000.0 mm</v>
+      </c>
+      <c r="B345" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
+6.00 x 1500.0 x 3000.0 mm
+Weight (Kg):1,940
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,225.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="346" xml:space="preserve">
+      <c r="A346" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
+6.00 x 1500.0 x 3000.0 mm</v>
+      </c>
+      <c r="B346" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
+6.00 x 1500.0 x 3000.0 mm
+Weight (Kg):1,762
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,225.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="347" xml:space="preserve">
+      <c r="A347" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
+6.00 x 1500.0 x 3000.0 mm</v>
+      </c>
+      <c r="B347" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
+6.00 x 1500.0 x 3000.0 mm
+Weight (Kg):1,918
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,225.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="348" xml:space="preserve">
+      <c r="A348" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
+6.00 x 1500.0 x 3000.0 mm</v>
+      </c>
+      <c r="B348" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
+6.00 x 1500.0 x 3000.0 mm
+Weight (Kg):1,306
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,225.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="349" xml:space="preserve">
+      <c r="A349" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
+6.00 x 1500.0 x 3000.0 mm</v>
+      </c>
+      <c r="B349" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
+6.00 x 1500.0 x 3000.0 mm
+Weight (Kg):1,066
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,225.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="350" xml:space="preserve">
+      <c r="A350" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
+6.00 x 1500.0 x 3000.0 mm</v>
+      </c>
+      <c r="B350" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
+6.00 x 1500.0 x 3000.0 mm
+Weight (Kg):1,936
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,225.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="351" xml:space="preserve">
+      <c r="A351" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
+6.00 x 1500.0 x 3000.0 mm</v>
+      </c>
+      <c r="B351" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
+6.00 x 1500.0 x 3000.0 mm
+Weight (Kg):2,390
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,225.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="352" xml:space="preserve">
+      <c r="A352" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
+6.00 x 1500.0 x 3000.0 mm</v>
+      </c>
+      <c r="B352" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
+6.00 x 1500.0 x 3000.0 mm
+Weight (Kg):1,728
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,225.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="353" xml:space="preserve">
+      <c r="A353" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
+6.00 x 1500.0 x 3000.0 mm</v>
+      </c>
+      <c r="B353" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
+6.00 x 1500.0 x 3000.0 mm
+Weight (Kg):1,514
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,225.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="354" xml:space="preserve">
+      <c r="A354" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
+6.00 x 1500.0 x 3000.0 mm</v>
+      </c>
+      <c r="B354" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
+6.00 x 1500.0 x 3000.0 mm
+Weight (Kg):1,922
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,225.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="355" xml:space="preserve">
+      <c r="A355" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
+6.00 x 1500.0 x 3000.0 mm</v>
+      </c>
+      <c r="B355" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
+6.00 x 1500.0 x 3000.0 mm
+Weight (Kg):1,942
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,225.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="356" xml:space="preserve">
+      <c r="A356" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
+6.00 x 1500.0 x 3000.0 mm</v>
+      </c>
+      <c r="B356" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
+6.00 x 1500.0 x 3000.0 mm
+Weight (Kg):2,114
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,225.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="357" xml:space="preserve">
+      <c r="A357" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
+6.00 x 1500.0 x 3000.0 mm</v>
+      </c>
+      <c r="B357" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
+6.00 x 1500.0 x 3000.0 mm
+Weight (Kg):1,088
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,225.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="358" xml:space="preserve">
+      <c r="A358" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
+6.00 x 1500.0 x 3000.0 mm</v>
+      </c>
+      <c r="B358" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
+6.00 x 1500.0 x 3000.0 mm
+Weight (Kg):1,274
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,225.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="359" xml:space="preserve">
+      <c r="A359" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
+6.00 x 1500.0 x 3000.0 mm</v>
+      </c>
+      <c r="B359" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
+6.00 x 1500.0 x 3000.0 mm
+Weight (Kg):1,718
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,225.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="360" xml:space="preserve">
+      <c r="A360" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
+6.00 x 1500.0 x 3000.0 mm</v>
+      </c>
+      <c r="B360" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
+6.00 x 1500.0 x 3000.0 mm
+Weight (Kg):1,922
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,225.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="361" xml:space="preserve">
+      <c r="A361" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
+6.00 x 1500.0 x 3000.0 mm</v>
+      </c>
+      <c r="B361" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
+6.00 x 1500.0 x 3000.0 mm
+Weight (Kg):1,878
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,225.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="362" xml:space="preserve">
+      <c r="A362" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
+6.00 x 1500.0 x 3000.0 mm</v>
+      </c>
+      <c r="B362" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
+6.00 x 1500.0 x 3000.0 mm
+Weight (Kg):1,714
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,225.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="363" xml:space="preserve">
+      <c r="A363" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
+6.00 x 1500.0 x 3000.0 mm</v>
+      </c>
+      <c r="B363" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
+6.00 x 1500.0 x 3000.0 mm
+Weight (Kg):1,918
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,225.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="364" xml:space="preserve">
+      <c r="A364" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
+6.00 x 1500.0 x 3000.0 mm</v>
+      </c>
+      <c r="B364" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
+6.00 x 1500.0 x 3000.0 mm
+Weight (Kg):1,754
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,225.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="365" xml:space="preserve">
+      <c r="A365" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
+6.00 x 1500.0 x 3000.0 mm</v>
+      </c>
+      <c r="B365" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
+6.00 x 1500.0 x 3000.0 mm
+Weight (Kg):1,528
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,225.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="366" xml:space="preserve">
+      <c r="A366" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
+6.00 x 1500.0 x 3000.0 mm</v>
+      </c>
+      <c r="B366" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
+6.00 x 1500.0 x 3000.0 mm
+Weight (Kg):2,136
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,225.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="367" xml:space="preserve">
+      <c r="A367" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
+6.00 x 1500.0 x 3000.0 mm</v>
+      </c>
+      <c r="B367" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
+6.00 x 1500.0 x 3000.0 mm
+Weight (Kg):1,946
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,225.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="368" xml:space="preserve">
+      <c r="A368" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, BA,
+0.80 x 1000.0 x 2000.0 mm</v>
+      </c>
+      <c r="B368" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, BA,
+0.80 x 1000.0 x 2000.0 mm
+Weight (Kg):1,633
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,225.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="369" xml:space="preserve">
+      <c r="A369" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, BA,
+0.80 x 1000.0 x 2000.0 mm</v>
+      </c>
+      <c r="B369" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, BA,
+0.80 x 1000.0 x 2000.0 mm
+Weight (Kg):1,286
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,225.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="370" xml:space="preserve">
+      <c r="A370" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, BA,
+0.80 x 1000.0 x 2000.0 mm</v>
+      </c>
+      <c r="B370" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, BA,
+0.80 x 1000.0 x 2000.0 mm
+Weight (Kg):727
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,225.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="371" xml:space="preserve">
+      <c r="A371" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, BA,
+1.00 x 1000.0 x 2000.0 mm</v>
+      </c>
+      <c r="B371" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, BA,
+1.00 x 1000.0 x 2000.0 mm
+Weight (Kg):650
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,225.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="372" xml:space="preserve">
+      <c r="A372" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, BA,
+1.00 x 1000.0 x 2000.0 mm</v>
+      </c>
+      <c r="B372" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, BA,
+1.00 x 1000.0 x 2000.0 mm
+Weight (Kg):869
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,225.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="373" xml:space="preserve">
+      <c r="A373" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, BA,
+1.00 x 1000.0 x 2000.0 mm</v>
+      </c>
+      <c r="B373" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, BA,
+1.00 x 1000.0 x 2000.0 mm
+Weight (Kg):885
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,225.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="374" xml:space="preserve">
+      <c r="A374" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, BA,
+1.00 x 1000.0 x 2000.0 mm</v>
+      </c>
+      <c r="B374" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, BA,
+1.00 x 1000.0 x 2000.0 mm
+Weight (Kg):931
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,225.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="375" xml:space="preserve">
+      <c r="A375" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, BA,
+1.00 x 1250.0 x 3000.0 mm</v>
+      </c>
+      <c r="B375" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, BA,
+1.00 x 1250.0 x 3000.0 mm
+Weight (Kg):766
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,225.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="376" xml:space="preserve">
+      <c r="A376" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, BA,
+1.00 x 1250.0 x 3000.0 mm</v>
+      </c>
+      <c r="B376" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, BA,
+1.00 x 1250.0 x 3000.0 mm
+Weight (Kg):1,417
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,225.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="377" xml:space="preserve">
+      <c r="A377" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, BA,
+1.50 x 1000.0 x 2000.0 mm</v>
+      </c>
+      <c r="B377" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, BA,
+1.50 x 1000.0 x 2000.0 mm
+Weight (Kg):1,459
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,225.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="378" xml:space="preserve">
+      <c r="A378" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, BA,
+1.50 x 1000.0 x 2000.0 mm</v>
+      </c>
+      <c r="B378" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, BA,
+1.50 x 1000.0 x 2000.0 mm
+Weight (Kg):825
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,225.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="379" xml:space="preserve">
+      <c r="A379" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, BA,
+1.50 x 1000.0 x 2000.0 mm</v>
+      </c>
+      <c r="B379" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, BA,
+1.50 x 1000.0 x 2000.0 mm
+Weight (Kg):738
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,225.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="380" xml:space="preserve">
+      <c r="A380" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, BA,
+1.50 x 1000.0 x 2000.0 mm</v>
+      </c>
+      <c r="B380" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, BA,
+1.50 x 1000.0 x 2000.0 mm
+Weight (Kg):886
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,225.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="381" xml:space="preserve">
+      <c r="A381" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, BA,
+1.50 x 1000.0 x 2000.0 mm</v>
+      </c>
+      <c r="B381" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, BA,
+1.50 x 1000.0 x 2000.0 mm
+Weight (Kg):1,116
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,225.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="382" xml:space="preserve">
+      <c r="A382" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, BA,
+1.50 x 1000.0 x 2000.0 mm</v>
+      </c>
+      <c r="B382" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, BA,
+1.50 x 1000.0 x 2000.0 mm
+Weight (Kg):692
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,225.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="383" xml:space="preserve">
+      <c r="A383" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, BA,
+1.50 x 1000.0 x 2000.0 mm</v>
+      </c>
+      <c r="B383" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, BA,
+1.50 x 1000.0 x 2000.0 mm
+Weight (Kg):1,613
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,225.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="384" xml:space="preserve">
+      <c r="A384" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, BA,
+1.50 x 1000.0 x 2000.0 mm</v>
+      </c>
+      <c r="B384" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, BA,
+1.50 x 1000.0 x 2000.0 mm
+Weight (Kg):946
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,225.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="385" xml:space="preserve">
+      <c r="A385" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, BA,
+1.50 x 1250.0 x 2500.0 mm</v>
+      </c>
+      <c r="B385" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, BA,
+1.50 x 1250.0 x 2500.0 mm
+Weight (Kg):1,628
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,225.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="386" xml:space="preserve">
+      <c r="A386" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, BA,
+1.80 x 1000.0 x 2000.0 mm</v>
+      </c>
+      <c r="B386" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, BA,
+1.80 x 1000.0 x 2000.0 mm
+Weight (Kg):1,405
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,225.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="387" xml:space="preserve">
+      <c r="A387" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, Nb. 1,
+3.00 x 1500.0 x 3000.0 mm</v>
+      </c>
+      <c r="B387" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, Nb. 1,
+3.00 x 1500.0 x 3000.0 mm
+Weight (Kg):1,728
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,125.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="388" xml:space="preserve">
+      <c r="A388" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, Nb. 3 Chequered,
+4.50 x 1250.0 x 3000.0 mm</v>
+      </c>
+      <c r="B388" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, Nb. 3 Chequered,
+4.50 x 1250.0 x 3000.0 mm
+Weight (Kg):1,046
+Quality:Prime
+Help
+Location:FABRICA ALGECIRAS
+2,900.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="389" xml:space="preserve">
+      <c r="A389" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, Nb. 3 Chequered,
+4.50 x 1250.0 x 3000.0 mm</v>
+      </c>
+      <c r="B389" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, Nb. 3 Chequered,
+4.50 x 1250.0 x 3000.0 mm
+Weight (Kg):1,316
+Quality:Prime
+Help
+Location:FABRICA ALGECIRAS
+2,900.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="390" xml:space="preserve">
+      <c r="A390" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, Polished N4-G-240,
+0.80 x 1500.0 x 3000.0 mm</v>
+      </c>
+      <c r="B390" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, Polished N4-G-240,
+0.80 x 1500.0 x 3000.0 mm
+Weight (Kg):630
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,225.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="391" xml:space="preserve">
+      <c r="A391" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, Polished N4-G-240,
+0.90 x 1500.0 x 3000.0 mm</v>
+      </c>
+      <c r="B391" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, Polished N4-G-240,
+0.90 x 1500.0 x 3000.0 mm
+Weight (Kg):807
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,225.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="392" xml:space="preserve">
+      <c r="A392" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, Polished N4-G-240,
+0.90 x 1500.0 x 3000.0 mm</v>
+      </c>
+      <c r="B392" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, Polished N4-G-240,
+0.90 x 1500.0 x 3000.0 mm
+Weight (Kg):622
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,225.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="393" xml:space="preserve">
+      <c r="A393" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, SB-G-400,
+1.50 x 1000.0 x 2000.0 mm</v>
+      </c>
+      <c r="B393" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, SB-G-400,
+1.50 x 1000.0 x 2000.0 mm
+Weight (Kg):674
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,225.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="394" xml:space="preserve">
+      <c r="A394" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, SB-G-400,
+1.50 x 1000.0 x 2000.0 mm</v>
+      </c>
+      <c r="B394" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, SB-G-400,
+1.50 x 1000.0 x 2000.0 mm
+Weight (Kg):535
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,225.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="395" xml:space="preserve">
+      <c r="A395" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, SB-G-400,
+3.00 x 1500.0 x 3000.0 mm</v>
+      </c>
+      <c r="B395" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, SB-G-400,
+3.00 x 1500.0 x 3000.0 mm
+Weight (Kg):1,877
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,225.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="396" xml:space="preserve">
+      <c r="A396" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, SB-G-400,
+3.00 x 1500.0 x 3000.0 mm</v>
+      </c>
+      <c r="B396" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, SB-G-400,
+3.00 x 1500.0 x 3000.0 mm
+Weight (Kg):629
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,225.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="397" xml:space="preserve">
+      <c r="A397" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, SB-G-400,
+3.00 x 1500.0 x 3000.0 mm</v>
+      </c>
+      <c r="B397" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, SB-G-400,
+3.00 x 1500.0 x 3000.0 mm
+Weight (Kg):1,887
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,225.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="398" xml:space="preserve">
+      <c r="A398" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, SB-G-500,
+0.70 x 1500.0 x 3000.0 mm</v>
+      </c>
+      <c r="B398" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, SB-G-500,
+0.70 x 1500.0 x 3000.0 mm
+Weight (Kg):1,226
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,225.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="399" xml:space="preserve">
+      <c r="A399" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, SB-G-500,
+0.70 x 1500.0 x 3000.0 mm</v>
+      </c>
+      <c r="B399" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, SB-G-500,
+0.70 x 1500.0 x 3000.0 mm
+Weight (Kg):1,001
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,225.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="400" xml:space="preserve">
+      <c r="A400" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, SB-G-500,
+0.70 x 1500.0 x 3000.0 mm</v>
+      </c>
+      <c r="B400" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, SB-G-500,
+0.70 x 1500.0 x 3000.0 mm
+Weight (Kg):681
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,225.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="401" xml:space="preserve">
+      <c r="A401" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, Nb. 1,
+8.00 x 1500.0 x 3000.0 mm</v>
+      </c>
+      <c r="B401" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, Nb. 1,
+8.00 x 1500.0 x 3000.0 mm
+Weight (Kg):1,162
+Quality:Prime
+Help
+Location:FABRICA ALGECIRAS
+2,900.00 €/ton
+Reserved</v>
+      </c>
+    </row>
+    <row r="402" xml:space="preserve">
+      <c r="A402" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, SB-G-500,
+0.70 x 1500.0 x 3000.0 mm</v>
+      </c>
+      <c r="B402" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, SB-G-500,
+0.70 x 1500.0 x 3000.0 mm
+Weight (Kg):673
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,225.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="403" xml:space="preserve">
+      <c r="A403" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, SB-G-500,
+0.70 x 1500.0 x 3000.0 mm</v>
+      </c>
+      <c r="B403" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, SB-G-500,
+0.70 x 1500.0 x 3000.0 mm
+Weight (Kg):722
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,225.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="404" xml:space="preserve">
+      <c r="A404" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, SB-G-500,
+0.80 x 1000.0 x 2000.0 mm</v>
+      </c>
+      <c r="B404" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, SB-G-500,
+0.80 x 1000.0 x 2000.0 mm
+Weight (Kg):1,256
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,225.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="405" xml:space="preserve">
+      <c r="A405" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, SB-G-500,
+0.80 x 1250.0 x 3000.0 mm</v>
+      </c>
+      <c r="B405" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, SB-G-500,
+0.80 x 1250.0 x 3000.0 mm
+Weight (Kg):535
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,225.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="406" xml:space="preserve">
+      <c r="A406" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, SB-G-500,
+3.00 x 1500.0 x 3000.0 mm</v>
+      </c>
+      <c r="B406" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, SB-G-500,
+3.00 x 1500.0 x 3000.0 mm
+Weight (Kg):839
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,225.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="407" xml:space="preserve">
+      <c r="A407" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Untrimmed, Coil,
+0.80 x 1271.0 x coil mm</v>
+      </c>
+      <c r="B407" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Untrimmed, Coil,
+0.80 x 1271.0 x coil mm
+Weight (Kg):2,950
+Quality:Prime
+Help
+Location:FABRICA ALGECIRAS
+2,425.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="408" xml:space="preserve">
+      <c r="A408" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Untrimmed, Coil, 2B,
+0.40 x 1017.0 x coil mm</v>
+      </c>
+      <c r="B408" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Untrimmed, Coil, 2B,
+0.40 x 1017.0 x coil mm
+Weight (Kg):9,900
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,225.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="409" xml:space="preserve">
+      <c r="A409" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Untrimmed, Coil, 2B,
+1.20 x 1277.0 x coil mm</v>
+      </c>
+      <c r="B409" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Untrimmed, Coil, 2B,
+1.20 x 1277.0 x coil mm
+Weight (Kg):2,230
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,225.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="410" xml:space="preserve">
+      <c r="A410" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Untrimmed, Coil, 2B,
+2.00 x 1275.0 x coil mm</v>
+      </c>
+      <c r="B410" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Untrimmed, Coil, 2B,
+2.00 x 1275.0 x coil mm
+Weight (Kg):2,619
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,225.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="411" xml:space="preserve">
+      <c r="A411" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Untrimmed, Coil, 2B,
+5.00 x 1540.0 x coil mm</v>
+      </c>
+      <c r="B411" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Untrimmed, Coil, 2B,
+5.00 x 1540.0 x coil mm
+Weight (Kg):7,140
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,225.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="412" xml:space="preserve">
+      <c r="A412" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Untrimmed, Coil, 2B,
+5.00 x 1540.0 x coil mm</v>
+      </c>
+      <c r="B412" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Untrimmed, Coil, 2B,
+5.00 x 1540.0 x coil mm
+Weight (Kg):13,250
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,225.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="413" xml:space="preserve">
+      <c r="A413" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Untrimmed, Coil, 2D,
+1.00 x 1027.0 x coil mm</v>
+      </c>
+      <c r="B413" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Untrimmed, Coil, 2D,
+1.00 x 1027.0 x coil mm
+Weight (Kg):2,410
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,225.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="414" xml:space="preserve">
+      <c r="A414" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Untrimmed, Coil, BA,
+0.40 x 1017.0 x coil mm</v>
+      </c>
+      <c r="B414" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Untrimmed, Coil, BA,
+0.40 x 1017.0 x coil mm
+Weight (Kg):5,705
+Quality:Prime
+Help
+Location:FABRICA ALGECIRAS
+2,425.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="415" xml:space="preserve">
+      <c r="A415" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Untrimmed, Coil, BA,
+0.90 x 1275.0 x coil mm</v>
+      </c>
+      <c r="B415" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Untrimmed, Coil, BA,
+0.90 x 1275.0 x coil mm
+Weight (Kg):2,500
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,225.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="416" xml:space="preserve">
+      <c r="A416" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Untrimmed, Coil, BA,
+0.90 x 1288.0 x coil mm</v>
+      </c>
+      <c r="B416" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Untrimmed, Coil, BA,
+0.90 x 1288.0 x coil mm
+Weight (Kg):7,960
+Quality:Prime
+Help
+Location:FABRICA ALGECIRAS
+2,425.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="417" xml:space="preserve">
+      <c r="A417" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Untrimmed, Coil, SB-G-400,
+1.20 x 1500.0 x coil mm</v>
+      </c>
+      <c r="B417" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Untrimmed, Coil, SB-G-400,
+1.20 x 1500.0 x coil mm
+Weight (Kg):2,640
+Quality:Prime
+Help
+Location:FABRICA ALGECIRAS
+2,425.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="418" xml:space="preserve">
+      <c r="A418" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Coil, 2B,
+1.20 x 1536.0 x coil mm</v>
+      </c>
+      <c r="B418" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Coil, 2B,
+1.20 x 1536.0 x coil mm
+Weight (Kg):1,260
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+3,395.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="419" xml:space="preserve">
+      <c r="A419" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Untrimmed, Coil,
+0.50 x 1272.0 x coil mm</v>
+      </c>
+      <c r="B419" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Untrimmed, Coil,
+0.50 x 1272.0 x coil mm
+Weight (Kg):5,960
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,225.00 €/ton
+Reserved</v>
+      </c>
+    </row>
+    <row r="420" xml:space="preserve">
+      <c r="A420" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Untrimmed, Coil, 2B,
+1.00 x 1290.0 x coil mm</v>
+      </c>
+      <c r="B420" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Untrimmed, Coil, 2B,
+1.00 x 1290.0 x coil mm
+Weight (Kg):2,160
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,225.00 €/ton
+Out of Stock</v>
+      </c>
+    </row>
+    <row r="421" xml:space="preserve">
+      <c r="A421" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Untrimmed, Coil, BA,
+0.80 x 1277.0 x coil mm</v>
+      </c>
+      <c r="B421" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Untrimmed, Coil, BA,
+0.80 x 1277.0 x coil mm
+Weight (Kg):5,250
+Quality:Prime
+Help
+Location:FABRICA ALGECIRAS
+2,425.00 €/ton
+Reserved</v>
+      </c>
+    </row>
+    <row r="422" xml:space="preserve">
+      <c r="A422" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Coil, 2B,
+1.50 x 140.0 x coil mm</v>
+      </c>
+      <c r="B422" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Coil, 2B,
+1.50 x 140.0 x coil mm
+Weight (Kg):758
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+3,270.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="423" xml:space="preserve">
+      <c r="A423" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Coil, 2B,
+1.50 x 160.9 x coil mm</v>
+      </c>
+      <c r="B423" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Coil, 2B,
+1.50 x 160.9 x coil mm
+Weight (Kg):848
+Quality:Prime
+Help
+Location:FABRICA ALGECIRAS
+3,270.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="424" xml:space="preserve">
+      <c r="A424" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Coil, 2B,
+1.50 x 230.9 x coil mm</v>
+      </c>
+      <c r="B424" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Coil, 2B,
+1.50 x 230.9 x coil mm
+Weight (Kg):1,044
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+3,270.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="425" xml:space="preserve">
+      <c r="A425" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Coil, 2B,
+2.00 x 1498.0 x coil mm</v>
+      </c>
+      <c r="B425" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Coil, 2B,
+2.00 x 1498.0 x coil mm
+Weight (Kg):2,770
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+3,395.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="426" xml:space="preserve">
+      <c r="A426" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Coil, 2B,
+5.00 x 1250.0 x coil mm</v>
+      </c>
+      <c r="B426" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Coil, 2B,
+5.00 x 1250.0 x coil mm
+Weight (Kg):12,055
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+3,375.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="427" xml:space="preserve">
+      <c r="A427" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Coil, 2B,
+5.00 x 240.0 x coil mm</v>
+      </c>
+      <c r="B427" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Coil, 2B,
+5.00 x 240.0 x coil mm
+Weight (Kg):2,314
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+3,270.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="428" xml:space="preserve">
+      <c r="A428" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Coil, 2B,
+5.00 x 240.0 x coil mm</v>
+      </c>
+      <c r="B428" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Coil, 2B,
+5.00 x 240.0 x coil mm
+Weight (Kg):2,237
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+3,270.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="429" xml:space="preserve">
+      <c r="A429" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Coil, 2B,
+6.00 x 1500.0 x coil mm</v>
+      </c>
+      <c r="B429" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Coil, 2B,
+6.00 x 1500.0 x coil mm
+Weight (Kg):2,016
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+3,395.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="430" xml:space="preserve">
+      <c r="A430" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Coil, 2B,
+6.00 x 250.9 x coil mm</v>
+      </c>
+      <c r="B430" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Coil, 2B,
+6.00 x 250.9 x coil mm
+Weight (Kg):548
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+3,270.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="431" xml:space="preserve">
+      <c r="A431" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Coil, 2B,
+6.00 x 250.9 x coil mm</v>
+      </c>
+      <c r="B431" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Coil, 2B,
+6.00 x 250.9 x coil mm
+Weight (Kg):1,880
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+3,270.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="432" xml:space="preserve">
+      <c r="A432" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Coil, 2D,
+3.30 x 112.0 x coil mm</v>
+      </c>
+      <c r="B432" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Coil, 2D,
+3.30 x 112.0 x coil mm
+Weight (Kg):1,017
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+3,270.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="433" xml:space="preserve">
+      <c r="A433" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Coil, 2D,
+3.30 x 112.0 x coil mm</v>
+      </c>
+      <c r="B433" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Coil, 2D,
+3.30 x 112.0 x coil mm
+Weight (Kg):878
+Quality:Prime
+Help
+Location:FABRICA ALGECIRAS
+3,270.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="434" xml:space="preserve">
+      <c r="A434" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Coil, 2D,
+3.30 x 449.0 x coil mm</v>
+      </c>
+      <c r="B434" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Coil, 2D,
+3.30 x 449.0 x coil mm
+Weight (Kg):1,850
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+3,270.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="435" xml:space="preserve">
+      <c r="A435" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Coil, 2D,
+3.30 x 449.0 x coil mm</v>
+      </c>
+      <c r="B435" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Coil, 2D,
+3.30 x 449.0 x coil mm
+Weight (Kg):1,854
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+3,270.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="436" xml:space="preserve">
+      <c r="A436" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Coil, BA,
+0.40 x 295.9 x coil mm</v>
+      </c>
+      <c r="B436" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Coil, BA,
+0.40 x 295.9 x coil mm
+Weight (Kg):662
+Quality:Prime
+Help
+Location:FABRICA ALGECIRAS
+3,270.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="437" xml:space="preserve">
+      <c r="A437" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Coil, BA,
+0.40 x 295.9 x coil mm</v>
+      </c>
+      <c r="B437" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Coil, BA,
+0.40 x 295.9 x coil mm
+Weight (Kg):650
+Quality:Prime
+Help
+Location:FABRICA ALGECIRAS
+3,270.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="438" xml:space="preserve">
+      <c r="A438" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Coil, BA,
+0.50 x 160.0 x coil mm</v>
+      </c>
+      <c r="B438" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Coil, BA,
+0.50 x 160.0 x coil mm
+Weight (Kg):1,066
+Quality:Prime
+Help
+Location:FABRICA ALGECIRAS
+3,270.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="439" xml:space="preserve">
+      <c r="A439" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Coil, Nb. 1,
+3.70 x 310.0 x coil mm</v>
+      </c>
+      <c r="B439" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Coil, Nb. 1,
+3.70 x 310.0 x coil mm
+Weight (Kg):5,921
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+3,170.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="440" xml:space="preserve">
+      <c r="A440" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Coil, Nb. 1,
+4.10 x 150.0 x coil mm</v>
+      </c>
+      <c r="B440" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Coil, Nb. 1,
+4.10 x 150.0 x coil mm
+Weight (Kg):1,593
+Quality:Prime
+Help
+Location:FABRICA ALGECIRAS
+3,170.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="441" xml:space="preserve">
+      <c r="A441" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Coil, Nb. 1,
+4.10 x 150.0 x coil mm</v>
+      </c>
+      <c r="B441" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Coil, Nb. 1,
+4.10 x 150.0 x coil mm
+Weight (Kg):1,438
+Quality:Prime
+Help
+Location:FABRICA ALGECIRAS
+3,170.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="442" xml:space="preserve">
+      <c r="A442" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Coil, Nb. 1,
+4.50 x 220.0 x coil mm</v>
+      </c>
+      <c r="B442" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Coil, Nb. 1,
+4.50 x 220.0 x coil mm
+Weight (Kg):3,869
+Quality:Prime
+Help
+Location:FABRICA ALGECIRAS
+3,170.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="443" xml:space="preserve">
+      <c r="A443" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Coil, SB-G-400,
+1.00 x 250.9 x coil mm</v>
+      </c>
+      <c r="B443" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Coil, SB-G-400,
+1.00 x 250.9 x coil mm
+Weight (Kg):1,428
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+3,270.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="444" xml:space="preserve">
+      <c r="A444" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
+0.70 x 1250.0 x 2500.0 mm</v>
+      </c>
+      <c r="B444" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
+0.70 x 1250.0 x 2500.0 mm
+Weight (Kg):1,756
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+3,395.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="445" xml:space="preserve">
+      <c r="A445" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
+0.80 x 1250.0 x 3000.0 mm</v>
+      </c>
+      <c r="B445" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
+0.80 x 1250.0 x 3000.0 mm
+Weight (Kg):695
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+3,395.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="446" xml:space="preserve">
+      <c r="A446" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
+0.80 x 1500.0 x 3000.0 mm</v>
+      </c>
+      <c r="B446" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
+0.80 x 1500.0 x 3000.0 mm
+Weight (Kg):978
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+3,395.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="447" xml:space="preserve">
+      <c r="A447" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
+0.80 x 1500.0 x 3000.0 mm</v>
+      </c>
+      <c r="B447" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
+0.80 x 1500.0 x 3000.0 mm
+Weight (Kg):1,741
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+3,395.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="448" xml:space="preserve">
+      <c r="A448" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
+0.80 x 1500.0 x 3000.0 mm</v>
+      </c>
+      <c r="B448" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
+0.80 x 1500.0 x 3000.0 mm
+Weight (Kg):803
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+3,395.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="449" xml:space="preserve">
+      <c r="A449" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
+0.80 x 1500.0 x 3000.0 mm</v>
+      </c>
+      <c r="B449" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
+0.80 x 1500.0 x 3000.0 mm
+Weight (Kg):1,136
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+3,395.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="450" xml:space="preserve">
+      <c r="A450" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
+0.90 x 1000.0 x 2000.0 mm</v>
+      </c>
+      <c r="B450" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
+0.90 x 1000.0 x 2000.0 mm
+Weight (Kg):576
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+3,395.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="451" xml:space="preserve">
+      <c r="A451" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
+0.90 x 1500.0 x 3000.0 mm</v>
+      </c>
+      <c r="B451" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
+0.90 x 1500.0 x 3000.0 mm
+Weight (Kg):553
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+3,395.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="452" xml:space="preserve">
+      <c r="A452" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
+1.10 x 1500.0 x 3000.0 mm</v>
+      </c>
+      <c r="B452" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
+1.10 x 1500.0 x 3000.0 mm
+Weight (Kg):1,233
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+3,395.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="453" xml:space="preserve">
+      <c r="A453" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
+1.20 x 1250.0 x 2500.0 mm</v>
+      </c>
+      <c r="B453" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
+1.20 x 1250.0 x 2500.0 mm
+Weight (Kg):685
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+3,395.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="454" xml:space="preserve">
+      <c r="A454" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
+1.50 x 1000.0 x 2000.0 mm</v>
+      </c>
+      <c r="B454" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
+1.50 x 1000.0 x 2000.0 mm
+Weight (Kg):598
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+3,395.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="455" xml:space="preserve">
+      <c r="A455" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
+1.50 x 1250.0 x 2500.0 mm</v>
+      </c>
+      <c r="B455" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
+1.50 x 1250.0 x 2500.0 mm
+Weight (Kg):681
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+3,395.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="456" xml:space="preserve">
+      <c r="A456" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
+2.00 x 1000.0 x 2000.0 mm</v>
+      </c>
+      <c r="B456" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
+2.00 x 1000.0 x 2000.0 mm
+Weight (Kg):2,359
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+3,395.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="457" xml:space="preserve">
+      <c r="A457" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
+2.00 x 1000.0 x 2000.0 mm</v>
+      </c>
+      <c r="B457" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
+2.00 x 1000.0 x 2000.0 mm
+Weight (Kg):529
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+3,395.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="458" xml:space="preserve">
+      <c r="A458" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
+2.00 x 1000.0 x 2000.0 mm</v>
+      </c>
+      <c r="B458" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
+2.00 x 1000.0 x 2000.0 mm
+Weight (Kg):889
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+3,395.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="459" xml:space="preserve">
+      <c r="A459" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
+2.00 x 1000.0 x 2000.0 mm</v>
+      </c>
+      <c r="B459" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
+2.00 x 1000.0 x 2000.0 mm
+Weight (Kg):628
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+3,395.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="460" xml:space="preserve">
+      <c r="A460" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
+2.00 x 1000.0 x 2000.0 mm</v>
+      </c>
+      <c r="B460" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
+2.00 x 1000.0 x 2000.0 mm
+Weight (Kg):1,968
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+3,395.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="461" xml:space="preserve">
+      <c r="A461" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
+2.00 x 1250.0 x 2500.0 mm</v>
+      </c>
+      <c r="B461" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
+2.00 x 1250.0 x 2500.0 mm
+Weight (Kg):928
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+3,395.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="462" xml:space="preserve">
+      <c r="A462" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
+2.00 x 1250.0 x 2500.0 mm</v>
+      </c>
+      <c r="B462" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
+2.00 x 1250.0 x 2500.0 mm
+Weight (Kg):816
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+3,395.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="463" xml:space="preserve">
+      <c r="A463" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
+2.00 x 1250.0 x 2500.0 mm</v>
+      </c>
+      <c r="B463" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
+2.00 x 1250.0 x 2500.0 mm
+Weight (Kg):976
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+3,395.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="464" xml:space="preserve">
+      <c r="A464" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
+2.00 x 1250.0 x 2500.0 mm</v>
+      </c>
+      <c r="B464" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
+2.00 x 1250.0 x 2500.0 mm
+Weight (Kg):585
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+3,395.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="465" xml:space="preserve">
+      <c r="A465" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
+2.00 x 1250.0 x 2500.0 mm</v>
+      </c>
+      <c r="B465" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
+2.00 x 1250.0 x 2500.0 mm
+Weight (Kg):1,956
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+3,395.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="466" xml:space="preserve">
+      <c r="A466" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
+2.00 x 1250.0 x 2500.0 mm</v>
+      </c>
+      <c r="B466" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
+2.00 x 1250.0 x 2500.0 mm
+Weight (Kg):1,779
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+3,395.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="467" xml:space="preserve">
+      <c r="A467" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
+2.00 x 1500.0 x 3000.0 mm</v>
+      </c>
+      <c r="B467" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
+2.00 x 1500.0 x 3000.0 mm
+Weight (Kg):693
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+3,395.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="468" xml:space="preserve">
+      <c r="A468" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
+2.00 x 1500.0 x 3000.0 mm</v>
+      </c>
+      <c r="B468" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
+2.00 x 1500.0 x 3000.0 mm
+Weight (Kg):1,122
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+3,395.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="469" xml:space="preserve">
+      <c r="A469" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
+2.00 x 1500.0 x 3000.0 mm</v>
+      </c>
+      <c r="B469" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
+2.00 x 1500.0 x 3000.0 mm
+Weight (Kg):1,108
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+3,395.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="470" xml:space="preserve">
+      <c r="A470" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
+2.00 x 1500.0 x 3000.0 mm</v>
+      </c>
+      <c r="B470" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
+2.00 x 1500.0 x 3000.0 mm
+Weight (Kg):1,836
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+3,395.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="471" xml:space="preserve">
+      <c r="A471" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
+2.00 x 1500.0 x 3000.0 mm</v>
+      </c>
+      <c r="B471" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
+2.00 x 1500.0 x 3000.0 mm
+Weight (Kg):630
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+3,395.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="472" xml:space="preserve">
+      <c r="A472" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
+2.00 x 1500.0 x 3000.0 mm</v>
+      </c>
+      <c r="B472" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
+2.00 x 1500.0 x 3000.0 mm
+Weight (Kg):726
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+3,395.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="473" xml:space="preserve">
+      <c r="A473" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
+2.00 x 1500.0 x 3000.0 mm</v>
+      </c>
+      <c r="B473" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
+2.00 x 1500.0 x 3000.0 mm
+Weight (Kg):565
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+3,395.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="474" xml:space="preserve">
+      <c r="A474" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
+2.00 x 1500.0 x 3000.0 mm</v>
+      </c>
+      <c r="B474" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
+2.00 x 1500.0 x 3000.0 mm
+Weight (Kg):729
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+3,395.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="475" xml:space="preserve">
+      <c r="A475" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
+2.00 x 1500.0 x 3000.0 mm</v>
+      </c>
+      <c r="B475" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
+2.00 x 1500.0 x 3000.0 mm
+Weight (Kg):792
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+3,395.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="476" xml:space="preserve">
+      <c r="A476" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
+2.00 x 1500.0 x 3000.0 mm</v>
+      </c>
+      <c r="B476" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
+2.00 x 1500.0 x 3000.0 mm
+Weight (Kg):637
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+3,395.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="477" xml:space="preserve">
+      <c r="A477" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
+2.00 x 1500.0 x 3000.0 mm</v>
+      </c>
+      <c r="B477" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
+2.00 x 1500.0 x 3000.0 mm
+Weight (Kg):1,289
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+3,395.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="478" xml:space="preserve">
+      <c r="A478" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
+2.50 x 1500.0 x 3000.0 mm</v>
+      </c>
+      <c r="B478" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
+2.50 x 1500.0 x 3000.0 mm
+Weight (Kg):1,826
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+3,395.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="479" xml:space="preserve">
+      <c r="A479" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
+2.50 x 1500.0 x 3000.0 mm</v>
+      </c>
+      <c r="B479" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
+2.50 x 1500.0 x 3000.0 mm
+Weight (Kg):1,040
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+3,395.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="480" xml:space="preserve">
+      <c r="A480" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
+2.50 x 1500.0 x 3000.0 mm</v>
+      </c>
+      <c r="B480" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
+2.50 x 1500.0 x 3000.0 mm
+Weight (Kg):1,328
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+3,395.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="481" xml:space="preserve">
+      <c r="A481" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
+3.00 x 1000.0 x 2000.0 mm</v>
+      </c>
+      <c r="B481" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
+3.00 x 1000.0 x 2000.0 mm
+Weight (Kg):940
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+3,395.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="482" xml:space="preserve">
+      <c r="A482" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
+3.00 x 1250.0 x 2500.0 mm</v>
+      </c>
+      <c r="B482" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
+3.00 x 1250.0 x 2500.0 mm
+Weight (Kg):1,396
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+3,395.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="483" xml:space="preserve">
+      <c r="A483" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
+3.00 x 1250.0 x 2500.0 mm</v>
+      </c>
+      <c r="B483" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
+3.00 x 1250.0 x 2500.0 mm
+Weight (Kg):2,318
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+3,395.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="484" xml:space="preserve">
+      <c r="A484" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
+3.00 x 1250.0 x 2500.0 mm</v>
+      </c>
+      <c r="B484" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
+3.00 x 1250.0 x 2500.0 mm
+Weight (Kg):1,074
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+3,395.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="485" xml:space="preserve">
+      <c r="A485" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
+3.00 x 1250.0 x 2500.0 mm</v>
+      </c>
+      <c r="B485" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
+3.00 x 1250.0 x 2500.0 mm
+Weight (Kg):1,584
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+3,395.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="486" xml:space="preserve">
+      <c r="A486" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
+3.00 x 1250.0 x 2500.0 mm</v>
+      </c>
+      <c r="B486" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
+3.00 x 1250.0 x 2500.0 mm
+Weight (Kg):1,028
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+3,395.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="487" xml:space="preserve">
+      <c r="A487" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
+3.00 x 1250.0 x 2500.0 mm</v>
+      </c>
+      <c r="B487" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
+3.00 x 1250.0 x 2500.0 mm
+Weight (Kg):598
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+3,395.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="488" xml:space="preserve">
+      <c r="A488" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
+3.00 x 1340.0 x 2480.0 mm</v>
+      </c>
+      <c r="B488" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
+3.00 x 1340.0 x 2480.0 mm
+Weight (Kg):1,174
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+3,395.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="489" xml:space="preserve">
+      <c r="A489" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
+3.00 x 1340.0 x 2480.0 mm</v>
+      </c>
+      <c r="B489" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
+3.00 x 1340.0 x 2480.0 mm
+Weight (Kg):1,020
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+3,395.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="490" xml:space="preserve">
+      <c r="A490" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
+3.00 x 1340.0 x 2480.0 mm</v>
+      </c>
+      <c r="B490" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
+3.00 x 1340.0 x 2480.0 mm
+Weight (Kg):1,169
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+3,395.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="491" xml:space="preserve">
+      <c r="A491" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
+3.00 x 1340.0 x 2480.0 mm</v>
+      </c>
+      <c r="B491" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
+3.00 x 1340.0 x 2480.0 mm
+Weight (Kg):1,951
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+3,395.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="492" xml:space="preserve">
+      <c r="A492" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
+5.00 x 1000.0 x 2000.0 mm</v>
+      </c>
+      <c r="B492" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
+5.00 x 1000.0 x 2000.0 mm
+Weight (Kg):943
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+3,395.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="493" xml:space="preserve">
+      <c r="A493" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
+5.00 x 1000.0 x 2000.0 mm</v>
+      </c>
+      <c r="B493" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
+5.00 x 1000.0 x 2000.0 mm
+Weight (Kg):947
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+3,395.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="494" xml:space="preserve">
+      <c r="A494" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
+5.00 x 1000.0 x 2000.0 mm</v>
+      </c>
+      <c r="B494" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
+5.00 x 1000.0 x 2000.0 mm
+Weight (Kg):1,588
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+3,395.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="495" xml:space="preserve">
+      <c r="A495" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
+5.00 x 1250.0 x 2500.0 mm</v>
+      </c>
+      <c r="B495" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
+5.00 x 1250.0 x 2500.0 mm
+Weight (Kg):742
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+3,395.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="496" xml:space="preserve">
+      <c r="A496" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
+6.00 x 1000.0 x 2000.0 mm</v>
+      </c>
+      <c r="B496" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
+6.00 x 1000.0 x 2000.0 mm
+Weight (Kg):1,452
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+3,395.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="497" xml:space="preserve">
+      <c r="A497" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
+6.00 x 1000.0 x 2000.0 mm</v>
+      </c>
+      <c r="B497" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
+6.00 x 1000.0 x 2000.0 mm
+Weight (Kg):1,624
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+3,395.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="498" xml:space="preserve">
+      <c r="A498" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
+6.00 x 1000.0 x 2000.0 mm</v>
+      </c>
+      <c r="B498" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
+6.00 x 1000.0 x 2000.0 mm
+Weight (Kg):1,434
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+3,395.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="499" xml:space="preserve">
+      <c r="A499" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
+6.00 x 1000.0 x 2000.0 mm</v>
+      </c>
+      <c r="B499" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
+6.00 x 1000.0 x 2000.0 mm
+Weight (Kg):580
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+3,395.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="500" xml:space="preserve">
+      <c r="A500" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
+6.00 x 1000.0 x 2000.0 mm</v>
+      </c>
+      <c r="B500" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
+6.00 x 1000.0 x 2000.0 mm
+Weight (Kg):1,054
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+3,395.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="501" xml:space="preserve">
+      <c r="A501" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
+6.00 x 1000.0 x 2000.0 mm</v>
+      </c>
+      <c r="B501" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
+6.00 x 1000.0 x 2000.0 mm
+Weight (Kg):1,716
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+3,395.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="502" xml:space="preserve">
+      <c r="A502" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
+6.00 x 1000.0 x 2000.0 mm</v>
+      </c>
+      <c r="B502" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
+6.00 x 1000.0 x 2000.0 mm
+Weight (Kg):1,148
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+3,395.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="503" xml:space="preserve">
+      <c r="A503" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
+6.00 x 1000.0 x 2000.0 mm</v>
+      </c>
+      <c r="B503" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
+6.00 x 1000.0 x 2000.0 mm
+Weight (Kg):960
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+3,395.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="504" xml:space="preserve">
+      <c r="A504" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
+6.00 x 1000.0 x 2000.0 mm</v>
+      </c>
+      <c r="B504" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
+6.00 x 1000.0 x 2000.0 mm
+Weight (Kg):772
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+3,395.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="505" xml:space="preserve">
+      <c r="A505" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
+6.00 x 1500.0 x 3000.0 mm</v>
+      </c>
+      <c r="B505" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
+6.00 x 1500.0 x 3000.0 mm
+Weight (Kg):2,146
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+3,395.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="506" xml:space="preserve">
+      <c r="A506" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
+6.00 x 1500.0 x 3000.0 mm</v>
+      </c>
+      <c r="B506" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
+6.00 x 1500.0 x 3000.0 mm
+Weight (Kg):1,994
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+3,395.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="507" xml:space="preserve">
+      <c r="A507" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
+6.00 x 1500.0 x 3000.0 mm</v>
+      </c>
+      <c r="B507" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
+6.00 x 1500.0 x 3000.0 mm
+Weight (Kg):1,488
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+3,395.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="508" xml:space="preserve">
+      <c r="A508" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
+6.00 x 1500.0 x 3000.0 mm</v>
+      </c>
+      <c r="B508" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
+6.00 x 1500.0 x 3000.0 mm
+Weight (Kg):1,278
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+3,395.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="509" xml:space="preserve">
+      <c r="A509" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
+6.00 x 1500.0 x 3000.0 mm</v>
+      </c>
+      <c r="B509" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
+6.00 x 1500.0 x 3000.0 mm
+Weight (Kg):1,062
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+3,395.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="510" xml:space="preserve">
+      <c r="A510" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
+6.00 x 1500.0 x 3000.0 mm</v>
+      </c>
+      <c r="B510" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
+6.00 x 1500.0 x 3000.0 mm
+Weight (Kg):1,526
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+3,395.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="511" xml:space="preserve">
+      <c r="A511" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
+6.00 x 1500.0 x 3000.0 mm</v>
+      </c>
+      <c r="B511" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
+6.00 x 1500.0 x 3000.0 mm
+Weight (Kg):1,280
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+3,395.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="512" xml:space="preserve">
+      <c r="A512" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
+6.00 x 1510.0 x 3010.0 mm</v>
+      </c>
+      <c r="B512" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
+6.00 x 1510.0 x 3010.0 mm
+Weight (Kg):1,986
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+3,395.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="513" xml:space="preserve">
+      <c r="A513" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
+6.00 x 1510.0 x 3010.0 mm</v>
+      </c>
+      <c r="B513" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
+6.00 x 1510.0 x 3010.0 mm
+Weight (Kg):1,784
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+3,395.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="514" xml:space="preserve">
+      <c r="A514" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, Nb. 1,
+6.00 x 1000.0 x 2000.0 mm</v>
+      </c>
+      <c r="B514" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, Nb. 1,
+6.00 x 1000.0 x 2000.0 mm
+Weight (Kg):570
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+3,395.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="515" xml:space="preserve">
+      <c r="A515" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, SB-G-400,
+1.50 x 1500.0 x 3000.0 mm</v>
+      </c>
+      <c r="B515" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, SB-G-400,
+1.50 x 1500.0 x 3000.0 mm
+Weight (Kg):723
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+3,395.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="516" xml:space="preserve">
+      <c r="A516" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, SB-G-400,
+2.00 x 1500.0 x 3000.0 mm</v>
+      </c>
+      <c r="B516" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, SB-G-400,
+2.00 x 1500.0 x 3000.0 mm
+Weight (Kg):819
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+3,395.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="517" xml:space="preserve">
+      <c r="A517" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, SB-G-400,
+2.00 x 1500.0 x 3000.0 mm</v>
+      </c>
+      <c r="B517" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, SB-G-400,
+2.00 x 1500.0 x 3000.0 mm
+Weight (Kg):1,935
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+3,395.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="518" xml:space="preserve">
+      <c r="A518" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Untrimmed, Coil, 2B,
+1.20 x 1537.0 x coil mm</v>
+      </c>
+      <c r="B518" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Untrimmed, Coil, 2B,
+1.20 x 1537.0 x coil mm
+Weight (Kg):2,125
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+3,395.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="519" xml:space="preserve">
+      <c r="A519" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Untrimmed, Coil, 2B,
+1.80 x 1530.0 x coil mm</v>
+      </c>
+      <c r="B519" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Untrimmed, Coil, 2B,
+1.80 x 1530.0 x coil mm
+Weight (Kg):5,263
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+3,395.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="520" xml:space="preserve">
+      <c r="A520" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Untrimmed, Coil, 2B,
+1.80 x 1535.0 x coil mm</v>
+      </c>
+      <c r="B520" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Untrimmed, Coil, 2B,
+1.80 x 1535.0 x coil mm
+Weight (Kg):2,726
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+3,395.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="521" xml:space="preserve">
+      <c r="A521" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Untrimmed, Coil, 2B,
+2.00 x 1023.0 x coil mm</v>
+      </c>
+      <c r="B521" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Untrimmed, Coil, 2B,
+2.00 x 1023.0 x coil mm
+Weight (Kg):1,825
+Quality:Prime
+Help
+Location:FABRICA ALGECIRAS
+3,595.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="522" xml:space="preserve">
+      <c r="A522" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Untrimmed, Coil, 2B,
+3.00 x 1552.0 x coil mm</v>
+      </c>
+      <c r="B522" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Untrimmed, Coil, 2B,
+3.00 x 1552.0 x coil mm
+Weight (Kg):2,868
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+3,395.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="523" xml:space="preserve">
+      <c r="A523" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Untrimmed, Coil, 2B,
+6.00 x 1030.0 x coil mm</v>
+      </c>
+      <c r="B523" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Untrimmed, Coil, 2B,
+6.00 x 1030.0 x coil mm
+Weight (Kg):2,225
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+3,395.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="524" xml:space="preserve">
+      <c r="A524" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4571 316Ti-Coil, 2B,
+4.00 x 210.0 x coil mm</v>
+      </c>
+      <c r="B524" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4571 316Ti-Coil, 2B,
+4.00 x 210.0 x coil mm
+Weight (Kg):3,817
+Quality:Prime
+Help
+Location:FABRICA ALGECIRAS
+3,370.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="525" xml:space="preserve">
+      <c r="A525" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4571 316Ti-Coil, Nb. 1,
+3.00 x 184.0 x coil mm</v>
+      </c>
+      <c r="B525" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4571 316Ti-Coil, Nb. 1,
+3.00 x 184.0 x coil mm
+Weight (Kg):1,794
+Quality:Prime
+Help
+Location:FABRICA ALGECIRAS
+3,270.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="526" xml:space="preserve">
+      <c r="A526" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4571 316Ti-Coil, Nb. 1,
+3.00 x 184.0 x coil mm</v>
+      </c>
+      <c r="B526" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4571 316Ti-Coil, Nb. 1,
+3.00 x 184.0 x coil mm
+Weight (Kg):1,806
+Quality:Prime
+Help
+Location:FABRICA ALGECIRAS
+3,270.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="527" xml:space="preserve">
+      <c r="A527" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4571 316Ti-Coil, Nb. 1,
+3.00 x 184.0 x coil mm</v>
+      </c>
+      <c r="B527" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4571 316Ti-Coil, Nb. 1,
+3.00 x 184.0 x coil mm
+Weight (Kg):1,808
+Quality:Prime
+Help
+Location:FABRICA ALGECIRAS
+3,270.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="528" xml:space="preserve">
+      <c r="A528" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4571 316Ti-Coil, Nb. 1,
+4.00 x 200.0 x coil mm</v>
+      </c>
+      <c r="B528" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4571 316Ti-Coil, Nb. 1,
+4.00 x 200.0 x coil mm
+Weight (Kg):1,918
+Quality:Prime
+Help
+Location:FABRICA ALGECIRAS
+3,270.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="529" xml:space="preserve">
+      <c r="A529" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4571 316Ti-Plate, Nb. 1,
+45.00 x 1500.0 x 3000.0 mm</v>
+      </c>
+      <c r="B529" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4571 316Ti-Plate, Nb. 1,
+45.00 x 1500.0 x 3000.0 mm
+Weight (Kg):1,640
+Quality:Prime
+Help
+Location:FABRICA ALGECIRAS
+4,600.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="530" xml:space="preserve">
+      <c r="A530" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4571 316Ti-Sheet, 2B,
+3.00 x 1000.0 x 2000.0 mm</v>
+      </c>
+      <c r="B530" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4571 316Ti-Sheet, 2B,
+3.00 x 1000.0 x 2000.0 mm
+Weight (Kg):918
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+3,495.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="531" xml:space="preserve">
+      <c r="A531" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4571 316Ti-Sheet, 2B,
+3.00 x 1000.0 x 2000.0 mm</v>
+      </c>
+      <c r="B531" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4571 316Ti-Sheet, 2B,
+3.00 x 1000.0 x 2000.0 mm
+Weight (Kg):518
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+3,495.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="532" xml:space="preserve">
+      <c r="A532" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4571 316Ti-Sheet, 2B,
+3.00 x 1000.0 x 2000.0 mm</v>
+      </c>
+      <c r="B532" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4571 316Ti-Sheet, 2B,
+3.00 x 1000.0 x 2000.0 mm
+Weight (Kg):848
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+3,495.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="533" xml:space="preserve">
+      <c r="A533" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4571 316Ti-Sheet, 2B,
+5.00 x 1000.0 x 2000.0 mm</v>
+      </c>
+      <c r="B533" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4571 316Ti-Sheet, 2B,
+5.00 x 1000.0 x 2000.0 mm
+Weight (Kg):1,102
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+3,495.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="534" xml:space="preserve">
+      <c r="A534" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4571 316Ti-Sheet, 2B,
+6.00 x 1000.0 x 2000.0 mm</v>
+      </c>
+      <c r="B534" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4571 316Ti-Sheet, 2B,
+6.00 x 1000.0 x 2000.0 mm
+Weight (Kg):1,050
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+3,495.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="535" xml:space="preserve">
+      <c r="A535" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4571 316Ti-Sheet, 2B,
+6.00 x 1000.0 x 2000.0 mm</v>
+      </c>
+      <c r="B535" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4571 316Ti-Sheet, 2B,
+6.00 x 1000.0 x 2000.0 mm
+Weight (Kg):952
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+3,495.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="536" xml:space="preserve">
+      <c r="A536" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4571 316Ti-Sheet, Nb. 1,
+8.00 x 1500.0 x 3000.0 mm</v>
+      </c>
+      <c r="B536" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4571 316Ti-Sheet, Nb. 1,
+8.00 x 1500.0 x 3000.0 mm
+Weight (Kg):1,136
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+3,495.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="537" xml:space="preserve">
+      <c r="A537" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4541 321-Coil, 2B,
+1.90 x 217.0 x coil mm</v>
+      </c>
+      <c r="B537" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4541 321-Coil, 2B,
+1.90 x 217.0 x coil mm
+Weight (Kg):3,537
+Quality:Prime
+Help
+Location:FABRICA ALGECIRAS
+2,235.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="538" xml:space="preserve">
+      <c r="A538" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4541 321-Coil, 2B,
+1.90 x 217.0 x coil mm</v>
+      </c>
+      <c r="B538" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4541 321-Coil, 2B,
+1.90 x 217.0 x coil mm
+Weight (Kg):3,484
+Quality:Prime
+Help
+Location:FABRICA ALGECIRAS
+2,235.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="539" xml:space="preserve">
+      <c r="A539" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4541 321-Coil, 2B,
+1.90 x 217.0 x coil mm</v>
+      </c>
+      <c r="B539" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4541 321-Coil, 2B,
+1.90 x 217.0 x coil mm
+Weight (Kg):3,537
+Quality:Prime
+Help
+Location:FABRICA ALGECIRAS
+2,235.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="540" xml:space="preserve">
+      <c r="A540" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4541 321-Coil, 2B,
+1.90 x 217.0 x coil mm</v>
+      </c>
+      <c r="B540" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4541 321-Coil, 2B,
+1.90 x 217.0 x coil mm
+Weight (Kg):3,490
+Quality:Prime
+Help
+Location:FABRICA ALGECIRAS
+2,235.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="541" xml:space="preserve">
+      <c r="A541" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Untrimmed, Coil, 2B,
+2.00 x 1532.0 x coil mm</v>
+      </c>
+      <c r="B541" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Untrimmed, Coil, 2B,
+2.00 x 1532.0 x coil mm
+Weight (Kg):2,540
+Quality:Prime
+Help
+Location:FABRICA ALGECIRAS
+3,595.00 €/ton
+Reserved</v>
+      </c>
+    </row>
+    <row r="542" xml:space="preserve">
+      <c r="A542" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4541 321-Coil, 2B,
+1.90 x 217.0 x coil mm</v>
+      </c>
+      <c r="B542" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4541 321-Coil, 2B,
+1.90 x 217.0 x coil mm
+Weight (Kg):3,537
+Quality:Prime
+Help
+Location:FABRICA ALGECIRAS
+2,235.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="543" xml:space="preserve">
+      <c r="A543" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4541 321-Coil, 2B,
+1.90 x 217.0 x coil mm</v>
+      </c>
+      <c r="B543" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4541 321-Coil, 2B,
+1.90 x 217.0 x coil mm
+Weight (Kg):3,492
+Quality:Prime
+Help
+Location:FABRICA ALGECIRAS
+2,235.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="544" xml:space="preserve">
+      <c r="A544" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4541 321-Coil, 2B,
+1.90 x 217.0 x coil mm</v>
+      </c>
+      <c r="B544" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4541 321-Coil, 2B,
+1.90 x 217.0 x coil mm
+Weight (Kg):3,480
+Quality:Prime
+Help
+Location:FABRICA ALGECIRAS
+2,235.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="545" xml:space="preserve">
+      <c r="A545" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4541 321-Coil, 2B,
+4.00 x 520.0 x coil mm</v>
+      </c>
+      <c r="B545" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4541 321-Coil, 2B,
+4.00 x 520.0 x coil mm
+Weight (Kg):7,263
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,285.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="546" xml:space="preserve">
+      <c r="A546" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4541 321-Coil, Nb. 1,
+5.00 x 1542.0 x coil mm</v>
+      </c>
+      <c r="B546" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4541 321-Coil, Nb. 1,
+5.00 x 1542.0 x coil mm
+Weight (Kg):4,890
+Quality:Prime
+Help
+Location:FABRICA ALGECIRAS
+2,875.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="547" xml:space="preserve">
+      <c r="A547" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4541 321-Coil, Nb. 1,
+5.00 x 230.9 x coil mm</v>
+      </c>
+      <c r="B547" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4541 321-Coil, Nb. 1,
+5.00 x 230.9 x coil mm
+Weight (Kg):4,198
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,135.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="548" xml:space="preserve">
+      <c r="A548" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4541 321-Sheet, 2B,
+3.00 x 1000.0 x 2000.0 mm</v>
+      </c>
+      <c r="B548" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4541 321-Sheet, 2B,
+3.00 x 1000.0 x 2000.0 mm
+Weight (Kg):1,104
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,385.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="549" xml:space="preserve">
+      <c r="A549" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4541 321-Sheet, 2B,
+4.00 x 1000.0 x 2000.0 mm</v>
+      </c>
+      <c r="B549" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4541 321-Sheet, 2B,
+4.00 x 1000.0 x 2000.0 mm
+Weight (Kg):1,552
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,385.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="550" xml:space="preserve">
+      <c r="A550" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4541 321-Sheet, 2B,
+6.00 x 1250.0 x 2500.0 mm</v>
+      </c>
+      <c r="B550" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4541 321-Sheet, 2B,
+6.00 x 1250.0 x 2500.0 mm
+Weight (Kg):1,296
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,385.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="551" xml:space="preserve">
+      <c r="A551" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4541 321-Sheet, Nb. 1,
+8.00 x 1000.0 x 2000.0 mm</v>
+      </c>
+      <c r="B551" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4541 321-Sheet, Nb. 1,
+8.00 x 1000.0 x 2000.0 mm
+Weight (Kg):640
+Quality:Prime
+Help
+Location:FABRICA ALGECIRAS
+3,350.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="552" xml:space="preserve">
+      <c r="A552" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4512 409L-Coil, 2B,
+1.00 x 1304.0 x coil mm</v>
+      </c>
+      <c r="B552" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4512 409L-Coil, 2B,
+1.00 x 1304.0 x coil mm
+Weight (Kg):10,360
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+1,125.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="553" xml:space="preserve">
+      <c r="A553" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4512 409L-Coil, 2B,
+1.00 x 625.0 x coil mm</v>
+      </c>
+      <c r="B553" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4512 409L-Coil, 2B,
+1.00 x 625.0 x coil mm
+Weight (Kg):6,700
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+1,025.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="554" xml:space="preserve">
+      <c r="A554" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4512 409L-Coil, 2D,
+2.00 x 1291.0 x coil mm</v>
+      </c>
+      <c r="B554" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4512 409L-Coil, 2D,
+2.00 x 1291.0 x coil mm
+Weight (Kg):3,579
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+1,125.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="555" xml:space="preserve">
+      <c r="A555" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4512 409L-Coil, 2D,
+2.00 x 150.0 x coil mm</v>
+      </c>
+      <c r="B555" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4512 409L-Coil, 2D,
+2.00 x 150.0 x coil mm
+Weight (Kg):2,270
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+1,000.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="556" xml:space="preserve">
+      <c r="A556" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4512 409L-Coil, Nb. 1,
+4.00 x 140.0 x coil mm</v>
+      </c>
+      <c r="B556" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4512 409L-Coil, Nb. 1,
+4.00 x 140.0 x coil mm
+Weight (Kg):2,354
+Quality:Prime
+Help
+Location:FABRICA ALGECIRAS
+900.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="557" xml:space="preserve">
+      <c r="A557" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4512 409L-Coil, Nb. 1,
+5.00 x 190.0 x coil mm</v>
+      </c>
+      <c r="B557" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4512 409L-Coil, Nb. 1,
+5.00 x 190.0 x coil mm
+Weight (Kg):2,447
+Quality:Prime
+Help
+Location:FABRICA ALGECIRAS
+900.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="558" xml:space="preserve">
+      <c r="A558" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4512 409L-Coil, Nb. 1,
+6.00 x 270.0 x coil mm</v>
+      </c>
+      <c r="B558" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4512 409L-Coil, Nb. 1,
+6.00 x 270.0 x coil mm
+Weight (Kg):2,116
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+900.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="559" xml:space="preserve">
+      <c r="A559" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4512 409L-Coil, Nb. 1,
+6.00 x 270.0 x coil mm</v>
+      </c>
+      <c r="B559" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4512 409L-Coil, Nb. 1,
+6.00 x 270.0 x coil mm
+Weight (Kg):1,780
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+900.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="560" xml:space="preserve">
+      <c r="A560" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4512 409L-Coil, Nb. 1,
+8.00 x 115.9 x coil mm</v>
+      </c>
+      <c r="B560" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4512 409L-Coil, Nb. 1,
+8.00 x 115.9 x coil mm
+Weight (Kg):1,238
+Quality:Prime
+Help
+Location:FABRICA ALGECIRAS
+900.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="561" xml:space="preserve">
+      <c r="A561" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4512 409L-Coil, Nb. 1,
+8.00 x 125.9 x coil mm</v>
+      </c>
+      <c r="B561" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4512 409L-Coil, Nb. 1,
+8.00 x 125.9 x coil mm
+Weight (Kg):1,214
+Quality:Prime
+Help
+Location:FABRICA ALGECIRAS
+900.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="562" xml:space="preserve">
+      <c r="A562" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4512 409L-Coil, Nb. 1,
+8.00 x 230.9 x coil mm</v>
+      </c>
+      <c r="B562" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4512 409L-Coil, Nb. 1,
+8.00 x 230.9 x coil mm
+Weight (Kg):2,960
+Quality:Prime
+Help
+Location:FABRICA ALGECIRAS
+900.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="563" xml:space="preserve">
+      <c r="A563" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4512 409L-Untrimmed, Coil, 2B,
+1.00 x 625.0 x coil mm</v>
+      </c>
+      <c r="B563" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4512 409L-Untrimmed, Coil, 2B,
+1.00 x 625.0 x coil mm
+Weight (Kg):3,441
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+1,025.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="564" xml:space="preserve">
+      <c r="A564" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4512 409L-Untrimmed, Coil, 2D,
+1.50 x 1295.0 x coil mm</v>
+      </c>
+      <c r="B564" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4512 409L-Untrimmed, Coil, 2D,
+1.50 x 1295.0 x coil mm
+Weight (Kg):2,445
+Quality:Prime
+Help
+Location:FABRICA ALGECIRAS
+1,325.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="565" xml:space="preserve">
+      <c r="A565" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, 2B,
+0.70 x 299.9 x coil mm</v>
+      </c>
+      <c r="B565" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, 2B,
+0.70 x 299.9 x coil mm
+Weight (Kg):2,518
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+1,000.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="566" xml:space="preserve">
+      <c r="A566" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, 2B,
+2.00 x 220.0 x coil mm</v>
+      </c>
+      <c r="B566" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, 2B,
+2.00 x 220.0 x coil mm
+Weight (Kg):776
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+1,000.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="567" xml:space="preserve">
+      <c r="A567" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, 2D,
+0.50 x 1518.0 x coil mm</v>
+      </c>
+      <c r="B567" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, 2D,
+0.50 x 1518.0 x coil mm
+Weight (Kg):4,480
+Quality:Prime
+Help
+Location:FABRICA ALGECIRAS
+1,325.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="568" xml:space="preserve">
+      <c r="A568" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, 2D,
+0.70 x 1007.0 x coil mm</v>
+      </c>
+      <c r="B568" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, 2D,
+0.70 x 1007.0 x coil mm
+Weight (Kg):14,970
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+1,125.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="569" xml:space="preserve">
+      <c r="A569" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, 2D,
+0.70 x 1450.0 x coil mm</v>
+      </c>
+      <c r="B569" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, 2D,
+0.70 x 1450.0 x coil mm
+Weight (Kg):4,780
+Quality:Prime
+Help
+Location:FABRICA ALGECIRAS
+1,325.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="570" xml:space="preserve">
+      <c r="A570" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, 2D,
+0.70 x 869.0 x coil mm</v>
+      </c>
+      <c r="B570" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, 2D,
+0.70 x 869.0 x coil mm
+Weight (Kg):13,570
+Quality:Prime
+Help
+Location:FABRICA ALGECIRAS
+1,900.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="571" xml:space="preserve">
+      <c r="A571" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, BA,
+0.60 x 310.0 x coil mm</v>
+      </c>
+      <c r="B571" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, BA,
+0.60 x 310.0 x coil mm
+Weight (Kg):786
+Quality:Prime
+Help
+Location:FABRICA ALGECIRAS
+1,000.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="572" xml:space="preserve">
+      <c r="A572" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, BA,
+0.70 x 100.9 x coil mm</v>
+      </c>
+      <c r="B572" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, BA,
+0.70 x 100.9 x coil mm
+Weight (Kg):778
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+1,000.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="573" xml:space="preserve">
+      <c r="A573" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, BA,
+0.70 x 110.9 x coil mm</v>
+      </c>
+      <c r="B573" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, BA,
+0.70 x 110.9 x coil mm
+Weight (Kg):634
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+1,000.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="574" xml:space="preserve">
+      <c r="A574" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, BA,
+0.70 x 110.9 x coil mm</v>
+      </c>
+      <c r="B574" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, BA,
+0.70 x 110.9 x coil mm
+Weight (Kg):658
+Quality:Prime
+Help
+Location:FABRICA ALGECIRAS
+1,000.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="575" xml:space="preserve">
+      <c r="A575" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, BA,
+0.40 x 474.0 x coil mm</v>
+      </c>
+      <c r="B575" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, BA,
+0.40 x 474.0 x coil mm
+Weight (Kg):2,997
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+1,050.00 €/ton
+Out of Stock</v>
+      </c>
+    </row>
+    <row r="576" xml:space="preserve">
+      <c r="A576" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, BA,
+0.40 x 596.2 x coil mm</v>
+      </c>
+      <c r="B576" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, BA,
+0.40 x 596.2 x coil mm
+Weight (Kg):4,288
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+1,050.00 €/ton
+Out of Stock</v>
+      </c>
+    </row>
+    <row r="577" xml:space="preserve">
+      <c r="A577" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, BA,
+0.40 x 596.2 x coil mm</v>
+      </c>
+      <c r="B577" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, BA,
+0.40 x 596.2 x coil mm
+Weight (Kg):2,150
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+1,050.00 €/ton
+Out of Stock</v>
+      </c>
+    </row>
+    <row r="578" xml:space="preserve">
+      <c r="A578" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, BA,
+0.40 x 596.2 x coil mm</v>
+      </c>
+      <c r="B578" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, BA,
+0.40 x 596.2 x coil mm
+Weight (Kg):4,371
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+1,050.00 €/ton
+Out of Stock</v>
+      </c>
+    </row>
+    <row r="579" xml:space="preserve">
+      <c r="A579" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, BA,
+0.50 x 114.0 x coil mm</v>
+      </c>
+      <c r="B579" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, BA,
+0.50 x 114.0 x coil mm
+Weight (Kg):1,225
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+1,000.00 €/ton
+Reserved</v>
+      </c>
+    </row>
+    <row r="580" xml:space="preserve">
+      <c r="A580" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, BA,
+0.60 x 340.0 x coil mm</v>
+      </c>
+      <c r="B580" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, BA,
+0.60 x 340.0 x coil mm
+Weight (Kg):4,383
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+1,000.00 €/ton
+Reserved</v>
+      </c>
+    </row>
+    <row r="581" xml:space="preserve">
+      <c r="A581" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, BA,
+0.60 x 440.0 x coil mm</v>
+      </c>
+      <c r="B581" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, BA,
+0.60 x 440.0 x coil mm
+Weight (Kg):5,670
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+1,000.00 €/ton
+Reserved</v>
+      </c>
+    </row>
+    <row r="582" xml:space="preserve">
+      <c r="A582" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, BA,
+0.70 x 120.0 x coil mm</v>
+      </c>
+      <c r="B582" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, BA,
+0.70 x 120.0 x coil mm
+Weight (Kg):836
+Quality:Prime
+Help
+Location:FABRICA ALGECIRAS
+1,000.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="583" xml:space="preserve">
+      <c r="A583" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, BA,
+0.70 x 125.0 x coil mm</v>
+      </c>
+      <c r="B583" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, BA,
+0.70 x 125.0 x coil mm
+Weight (Kg):1,288
+Quality:Prime
+Help
+Location:FABRICA ALGECIRAS
+1,000.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="584" xml:space="preserve">
+      <c r="A584" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, BA,
+0.70 x 125.9 x coil mm</v>
+      </c>
+      <c r="B584" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, BA,
+0.70 x 125.9 x coil mm
+Weight (Kg):708
+Quality:Prime
+Help
+Location:FABRICA ALGECIRAS
+1,000.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="585" xml:space="preserve">
+      <c r="A585" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, BA,
+0.70 x 126.0 x coil mm</v>
+      </c>
+      <c r="B585" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, BA,
+0.70 x 126.0 x coil mm
+Weight (Kg):804
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+1,000.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="586" xml:space="preserve">
+      <c r="A586" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, BA,
+0.70 x 155.9 x coil mm</v>
+      </c>
+      <c r="B586" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, BA,
+0.70 x 155.9 x coil mm
+Weight (Kg):1,148
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+1,000.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="587" xml:space="preserve">
+      <c r="A587" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, BA,
+0.70 x 175.9 x coil mm</v>
+      </c>
+      <c r="B587" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, BA,
+0.70 x 175.9 x coil mm
+Weight (Kg):944
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+1,000.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="588" xml:space="preserve">
+      <c r="A588" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, BA,
+0.70 x 175.9 x coil mm</v>
+      </c>
+      <c r="B588" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, BA,
+0.70 x 175.9 x coil mm
+Weight (Kg):1,054
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+1,000.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="589" xml:space="preserve">
+      <c r="A589" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, BA,
+0.70 x 181.9 x coil mm</v>
+      </c>
+      <c r="B589" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, BA,
+0.70 x 181.9 x coil mm
+Weight (Kg):1,632
+Quality:Prime
+Help
+Location:FABRICA ALGECIRAS
+1,000.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="590" xml:space="preserve">
+      <c r="A590" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, BA,
+0.70 x 195.9 x coil mm</v>
+      </c>
+      <c r="B590" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, BA,
+0.70 x 195.9 x coil mm
+Weight (Kg):1,174
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+1,000.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="591" xml:space="preserve">
+      <c r="A591" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, BA,
+0.70 x 195.9 x coil mm</v>
+      </c>
+      <c r="B591" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, BA,
+0.70 x 195.9 x coil mm
+Weight (Kg):1,541
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+1,000.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="592" xml:space="preserve">
+      <c r="A592" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, BA,
+0.70 x 200.9 x coil mm</v>
+      </c>
+      <c r="B592" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, BA,
+0.70 x 200.9 x coil mm
+Weight (Kg):1,098
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+1,000.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="593" xml:space="preserve">
+      <c r="A593" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, BA,
+0.70 x 260.9 x coil mm</v>
+      </c>
+      <c r="B593" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, BA,
+0.70 x 260.9 x coil mm
+Weight (Kg):2,121
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+1,000.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="594" xml:space="preserve">
+      <c r="A594" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, BA,
+0.70 x 825.0 x coil mm</v>
+      </c>
+      <c r="B594" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, BA,
+0.70 x 825.0 x coil mm
+Weight (Kg):5,270
+Quality:Prime
+Help
+Location:FABRICA ALGECIRAS
+1,325.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="595" xml:space="preserve">
+      <c r="A595" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, BA,
+0.70 x 842.0 x coil mm</v>
+      </c>
+      <c r="B595" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, BA,
+0.70 x 842.0 x coil mm
+Weight (Kg):10,370
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+1,125.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="596" xml:space="preserve">
+      <c r="A596" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, BA,
+0.70 x 855.0 x coil mm</v>
+      </c>
+      <c r="B596" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, BA,
+0.70 x 855.0 x coil mm
+Weight (Kg):3,990
+Quality:Prime
+Help
+Location:FABRICA ALGECIRAS
+1,325.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="597" xml:space="preserve">
+      <c r="A597" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, BA,
+0.70 x 870.0 x coil mm</v>
+      </c>
+      <c r="B597" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, BA,
+0.70 x 870.0 x coil mm
+Weight (Kg):13,910
+Quality:Prime
+Help
+Location:FABRICA ALGECIRAS
+1,900.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="598" xml:space="preserve">
+      <c r="A598" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, BA,
+0.70 x 953.0 x coil mm</v>
+      </c>
+      <c r="B598" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, BA,
+0.70 x 953.0 x coil mm
+Weight (Kg):6,970
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+1,125.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="599" xml:space="preserve">
+      <c r="A599" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, BA,
+1.00 x 530.0 x coil mm</v>
+      </c>
+      <c r="B599" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, BA,
+1.00 x 530.0 x coil mm
+Weight (Kg):880
+Quality:Downgraded
+Help
+Location:FABRICA ALGECIRAS
+975.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="600" xml:space="preserve">
+      <c r="A600" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, Polished N4-G-180,
+0.90 x 1250.0 x coil mm</v>
+      </c>
+      <c r="B600" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, Polished N4-G-180,
+0.90 x 1250.0 x coil mm
+Weight (Kg):2,218
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+1,125.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="601" xml:space="preserve">
+      <c r="A601" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, BA,
+0.70 x 825.0 x coil mm</v>
+      </c>
+      <c r="B601" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, BA,
+0.70 x 825.0 x coil mm
+Weight (Kg):6,340
+Quality:Prime
+Help
+Location:FABRICA ALGECIRAS
+1,325.00 €/ton
+Reserved</v>
+      </c>
+    </row>
+    <row r="602" xml:space="preserve">
+      <c r="A602" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, Polished N4-G-180,
+1.20 x 120.0 x coil mm</v>
+      </c>
+      <c r="B602" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, Polished N4-G-180,
+1.20 x 120.0 x coil mm
+Weight (Kg):1,430
+Quality:Prime
+Help
+Location:FABRICA ALGECIRAS
+1,000.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="603" xml:space="preserve">
+      <c r="A603" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, Polished N4-G-180,
+1.20 x 250.0 x coil mm</v>
+      </c>
+      <c r="B603" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, Polished N4-G-180,
+1.20 x 250.0 x coil mm
+Weight (Kg):1,902
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+1,000.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="604" xml:space="preserve">
+      <c r="A604" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, Polished N4-G-180,
+1.20 x 250.9 x coil mm</v>
+      </c>
+      <c r="B604" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, Polished N4-G-180,
+1.20 x 250.9 x coil mm
+Weight (Kg):1,960
+Quality:Prime
+Help
+Location:FABRICA ALGECIRAS
+1,000.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="605" xml:space="preserve">
+      <c r="A605" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, Polished N4-G-180,
+1.20 x 250.9 x coil mm</v>
+      </c>
+      <c r="B605" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, Polished N4-G-180,
+1.20 x 250.9 x coil mm
+Weight (Kg):1,918
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+1,000.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="606" xml:space="preserve">
+      <c r="A606" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, Polished N4-G-180,
+1.20 x 260.9 x coil mm</v>
+      </c>
+      <c r="B606" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, Polished N4-G-180,
+1.20 x 260.9 x coil mm
+Weight (Kg):1,524
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+1,000.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="607" xml:space="preserve">
+      <c r="A607" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, Polished N4-G-180,
+1.20 x 260.9 x coil mm</v>
+      </c>
+      <c r="B607" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, Polished N4-G-180,
+1.20 x 260.9 x coil mm
+Weight (Kg):1,934
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+1,000.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="608" xml:space="preserve">
+      <c r="A608" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, SB-G-400,
+0.60 x 134.9 x coil mm</v>
+      </c>
+      <c r="B608" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, SB-G-400,
+0.60 x 134.9 x coil mm
+Weight (Kg):1,134
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+1,000.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="609" xml:space="preserve">
+      <c r="A609" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, SB-G-400,
+0.60 x 134.9 x coil mm</v>
+      </c>
+      <c r="B609" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, SB-G-400,
+0.60 x 134.9 x coil mm
+Weight (Kg):962
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+1,000.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="610" xml:space="preserve">
+      <c r="A610" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, SB-G-400,
+0.60 x 245.9 x coil mm</v>
+      </c>
+      <c r="B610" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, SB-G-400,
+0.60 x 245.9 x coil mm
+Weight (Kg):1,778
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+1,000.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="611" xml:space="preserve">
+      <c r="A611" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, SB-G-400,
+1.00 x 118.9 x coil mm</v>
+      </c>
+      <c r="B611" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, SB-G-400,
+1.00 x 118.9 x coil mm
+Weight (Kg):754
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+1,000.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="612" xml:space="preserve">
+      <c r="A612" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, SB-G-400,
+1.00 x 118.9 x coil mm</v>
+      </c>
+      <c r="B612" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, SB-G-400,
+1.00 x 118.9 x coil mm
+Weight (Kg):802
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+1,000.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="613" xml:space="preserve">
+      <c r="A613" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, SB-G-400,
+1.00 x 266.9 x coil mm</v>
+      </c>
+      <c r="B613" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, SB-G-400,
+1.00 x 266.9 x coil mm
+Weight (Kg):1,322
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+1,000.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="614" xml:space="preserve">
+      <c r="A614" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, SB-G-500,
+0.70 x 245.9 x coil mm</v>
+      </c>
+      <c r="B614" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, SB-G-500,
+0.70 x 245.9 x coil mm
+Weight (Kg):1,496
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+1,000.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="615" xml:space="preserve">
+      <c r="A615" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, SBA,
+0.70 x 1056.0 x coil mm</v>
+      </c>
+      <c r="B615" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, SBA,
+0.70 x 1056.0 x coil mm
+Weight (Kg):15,197
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+1,125.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="616" xml:space="preserve">
+      <c r="A616" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, SBA,
+0.70 x 150.9 x coil mm</v>
+      </c>
+      <c r="B616" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, SBA,
+0.70 x 150.9 x coil mm
+Weight (Kg):1,268
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+1,000.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="617" xml:space="preserve">
+      <c r="A617" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, SBA,
+0.70 x 173.0 x coil mm</v>
+      </c>
+      <c r="B617" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, SBA,
+0.70 x 173.0 x coil mm
+Weight (Kg):890
+Quality:Prime
+Help
+Location:FABRICA ALGECIRAS
+1,000.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="618" xml:space="preserve">
+      <c r="A618" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, SBA,
+0.70 x 195.9 x coil mm</v>
+      </c>
+      <c r="B618" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, SBA,
+0.70 x 195.9 x coil mm
+Weight (Kg):962
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+1,000.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="619" xml:space="preserve">
+      <c r="A619" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, SBA,
+0.70 x 682.0 x coil mm</v>
+      </c>
+      <c r="B619" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, SBA,
+0.70 x 682.0 x coil mm
+Weight (Kg):3,870
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+1,025.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="620" xml:space="preserve">
+      <c r="A620" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, SBA,
+0.70 x 825.0 x coil mm</v>
+      </c>
+      <c r="B620" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, SBA,
+0.70 x 825.0 x coil mm
+Weight (Kg):6,448
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+1,125.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="621" xml:space="preserve">
+      <c r="A621" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, SBA,
+0.70 x 942.0 x coil mm</v>
+      </c>
+      <c r="B621" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, SBA,
+0.70 x 942.0 x coil mm
+Weight (Kg):1,810
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+1,125.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="622" xml:space="preserve">
+      <c r="A622" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, SBA,
+0.70 x 948.0 x coil mm</v>
+      </c>
+      <c r="B622" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, SBA,
+0.70 x 948.0 x coil mm
+Weight (Kg):3,410
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+1,125.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="623" xml:space="preserve">
+      <c r="A623" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, SBA,
+0.70 x 960.0 x coil mm</v>
+      </c>
+      <c r="B623" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, SBA,
+0.70 x 960.0 x coil mm
+Weight (Kg):2,780
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+1,125.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="624" xml:space="preserve">
+      <c r="A624" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, SBA,
+0.70 x 963.0 x coil mm</v>
+      </c>
+      <c r="B624" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, SBA,
+0.70 x 963.0 x coil mm
+Weight (Kg):4,570
+Quality:Prime
+Help
+Location:FABRICA ALGECIRAS
+1,325.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="625" xml:space="preserve">
+      <c r="A625" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Disk, BA,
+0.60 x 550.0 x 0.0 mm</v>
+      </c>
+      <c r="B625" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Disk, BA,
+0.60 x 550.0 x 0.0 mm
+Weight (Kg):578
+Quality:Prime
+Help
+Location:FABRICA ALGECIRAS
+1,900.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="626" xml:space="preserve">
+      <c r="A626" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Disk, BA,
+0.60 x 550.0 x 0.0 mm</v>
+      </c>
+      <c r="B626" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Disk, BA,
+0.60 x 550.0 x 0.0 mm
+Weight (Kg):572
+Quality:Prime
+Help
+Location:FABRICA ALGECIRAS
+1,900.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="627" xml:space="preserve">
+      <c r="A627" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Disk, BA,
+0.60 x 550.0 x 0.0 mm</v>
+      </c>
+      <c r="B627" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Disk, BA,
+0.60 x 550.0 x 0.0 mm
+Weight (Kg):576
+Quality:Prime
+Help
+Location:FABRICA ALGECIRAS
+1,900.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="628" xml:space="preserve">
+      <c r="A628" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Disk, BA,
+0.60 x 550.0 x 0.0 mm</v>
+      </c>
+      <c r="B628" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Disk, BA,
+0.60 x 550.0 x 0.0 mm
+Weight (Kg):578
+Quality:Prime
+Help
+Location:FABRICA ALGECIRAS
+1,900.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="629" xml:space="preserve">
+      <c r="A629" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Disk, BA,
+0.60 x 550.0 x 0.0 mm</v>
+      </c>
+      <c r="B629" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Disk, BA,
+0.60 x 550.0 x 0.0 mm
+Weight (Kg):582
+Quality:Prime
+Help
+Location:FABRICA ALGECIRAS
+1,900.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="630" xml:space="preserve">
+      <c r="A630" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Sheet, 2B,
+2.00 x 1250.0 x 2500.0 mm</v>
+      </c>
+      <c r="B630" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Sheet, 2B,
+2.00 x 1250.0 x 2500.0 mm
+Weight (Kg):619
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+1,125.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="631" xml:space="preserve">
+      <c r="A631" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Sheet, 2B,
+3.00 x 1250.0 x 2500.0 mm</v>
+      </c>
+      <c r="B631" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Sheet, 2B,
+3.00 x 1250.0 x 2500.0 mm
+Weight (Kg):566
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+1,125.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="632" xml:space="preserve">
+      <c r="A632" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Sheet, 2B,
+3.00 x 1250.0 x 2500.0 mm</v>
+      </c>
+      <c r="B632" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Sheet, 2B,
+3.00 x 1250.0 x 2500.0 mm
+Weight (Kg):640
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+1,125.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="633" xml:space="preserve">
+      <c r="A633" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Sheet, BA,
+0.70 x 1250.0 x 2500.0 mm</v>
+      </c>
+      <c r="B633" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Sheet, BA,
+0.70 x 1250.0 x 2500.0 mm
+Weight (Kg):766
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+1,125.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="634" xml:space="preserve">
+      <c r="A634" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Untrimmed, Coil, 1/4 HT,
+3.00 x 1292.0 x coil mm</v>
+      </c>
+      <c r="B634" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Untrimmed, Coil, 1/4 HT,
+3.00 x 1292.0 x coil mm
+Weight (Kg):3,641
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+1,125.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="635" xml:space="preserve">
+      <c r="A635" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Untrimmed, Coil, 2B,
+1.20 x 1500.0 x coil mm</v>
+      </c>
+      <c r="B635" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Untrimmed, Coil, 2B,
+1.20 x 1500.0 x coil mm
+Weight (Kg):4,750
+Quality:Downgraded
+Help
+Location:FABRICA ALGECIRAS
+1,000.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="636" xml:space="preserve">
+      <c r="A636" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Untrimmed, Coil, 2D, ET-100
+0.50 x 1250.0 x coil mm</v>
+      </c>
+      <c r="B636" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Untrimmed, Coil, 2D, ET-100
+0.50 x 1250.0 x coil mm
+Weight (Kg):5,160
+Quality:Prime
+Help
+Location:FABRICA ALGECIRAS
+1,325.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="637" xml:space="preserve">
+      <c r="A637" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Untrimmed, Coil, 2D, ET-100
+0.50 x 1250.0 x coil mm</v>
+      </c>
+      <c r="B637" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Untrimmed, Coil, 2D, ET-100
+0.50 x 1250.0 x coil mm
+Weight (Kg):3,695
+Quality:Prime
+Help
+Location:FABRICA ALGECIRAS
+1,325.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="638" xml:space="preserve">
+      <c r="A638" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Sheet, SB-G-400,
+1.00 x 1500.0 x 3000.0 mm</v>
+      </c>
+      <c r="B638" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Sheet, SB-G-400,
+1.00 x 1500.0 x 3000.0 mm
+Weight (Kg):1,940
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+1,125.00 €/ton
+Reserved</v>
+      </c>
+    </row>
+    <row r="639" xml:space="preserve">
+      <c r="A639" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Untrimmed, Coil, 2B,
+0.40 x 1264.0 x coil mm</v>
+      </c>
+      <c r="B639" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Untrimmed, Coil, 2B,
+0.40 x 1264.0 x coil mm
+Weight (Kg):5,720
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+1,125.00 €/ton
+Out of Stock</v>
+      </c>
+    </row>
+    <row r="640" xml:space="preserve">
+      <c r="A640" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Untrimmed, Coil, 2B,
+0.40 x 1273.0 x coil mm</v>
+      </c>
+      <c r="B640" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Untrimmed, Coil, 2B,
+0.40 x 1273.0 x coil mm
+Weight (Kg):5,176
+Quality:Prime
+Help
+Location:FABRICA ALGECIRAS
+1,325.00 €/ton
+Reserved</v>
+      </c>
+    </row>
+    <row r="641" xml:space="preserve">
+      <c r="A641" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Untrimmed, Coil, BA,
+0.40 x 1014.0 x coil mm</v>
+      </c>
+      <c r="B641" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Untrimmed, Coil, BA,
+0.40 x 1014.0 x coil mm
+Weight (Kg):2,400
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+1,050.00 €/ton
+Out of Stock</v>
+      </c>
+    </row>
+    <row r="642" xml:space="preserve">
+      <c r="A642" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Untrimmed, Coil, BA,
+0.60 x 1246.0 x coil mm</v>
+      </c>
+      <c r="B642" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Untrimmed, Coil, BA,
+0.60 x 1246.0 x coil mm
+Weight (Kg):2,585
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+1,125.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="643" xml:space="preserve">
+      <c r="A643" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Untrimmed, Coil, BA,
+1.00 x 1028.0 x coil mm</v>
+      </c>
+      <c r="B643" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Untrimmed, Coil, BA,
+1.00 x 1028.0 x coil mm
+Weight (Kg):2,430
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+1,125.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="644" xml:space="preserve">
+      <c r="A644" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Untrimmed, Coil, SBA,
+0.70 x 825.0 x coil mm</v>
+      </c>
+      <c r="B644" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Untrimmed, Coil, SBA,
+0.70 x 825.0 x coil mm
+Weight (Kg):7,260
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+1,125.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="645" xml:space="preserve">
+      <c r="A645" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Untrimmed, Coil, SBA,
+0.70 x 873.0 x coil mm</v>
+      </c>
+      <c r="B645" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Untrimmed, Coil, SBA,
+0.70 x 873.0 x coil mm
+Weight (Kg):4,020
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+1,125.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="646" xml:space="preserve">
+      <c r="A646" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4510 430Ti-Coil, 2B,
+2.00 x 100.9 x coil mm</v>
+      </c>
+      <c r="B646" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4510 430Ti-Coil, 2B,
+2.00 x 100.9 x coil mm
+Weight (Kg):1,710
+Quality:Prime
+Help
+Location:FABRICA ALGECIRAS
+1,000.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="647" xml:space="preserve">
+      <c r="A647" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4510 430Ti-Coil, BA,
+0.40 x 180.0 x coil mm</v>
+      </c>
+      <c r="B647" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4510 430Ti-Coil, BA,
+0.40 x 180.0 x coil mm
+Weight (Kg):1,188
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+1,000.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="648" xml:space="preserve">
+      <c r="A648" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4510 430Ti-Coil, BA,
+0.40 x 508.0 x coil mm</v>
+      </c>
+      <c r="B648" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4510 430Ti-Coil, BA,
+0.40 x 508.0 x coil mm
+Weight (Kg):3,364
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+1,025.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="649" xml:space="preserve">
+      <c r="A649" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4510 430Ti-Coil, BA,
+0.50 x 170.0 x coil mm</v>
+      </c>
+      <c r="B649" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4510 430Ti-Coil, BA,
+0.50 x 170.0 x coil mm
+Weight (Kg):914
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+1,000.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="650" xml:space="preserve">
+      <c r="A650" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4510 430Ti-Coil, BA,
+0.70 x 100.9 x coil mm</v>
+      </c>
+      <c r="B650" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4510 430Ti-Coil, BA,
+0.70 x 100.9 x coil mm
+Weight (Kg):638
+Quality:Prime
+Help
+Location:FABRICA ALGECIRAS
+1,000.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="651" xml:space="preserve">
+      <c r="A651" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4510 430Ti-Coil, BA,
+0.70 x 1020.0 x coil mm</v>
+      </c>
+      <c r="B651" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4510 430Ti-Coil, BA,
+0.70 x 1020.0 x coil mm
+Weight (Kg):16,000
+Quality:Prime
+Help
+Location:FABRICA ALGECIRAS
+1,900.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="652" xml:space="preserve">
+      <c r="A652" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4510 430Ti-Coil, BA,
+0.70 x 108.0 x coil mm</v>
+      </c>
+      <c r="B652" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4510 430Ti-Coil, BA,
+0.70 x 108.0 x coil mm
+Weight (Kg):714
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+1,000.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="653" xml:space="preserve">
+      <c r="A653" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4510 430Ti-Coil, BA,
+0.70 x 120.9 x coil mm</v>
+      </c>
+      <c r="B653" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4510 430Ti-Coil, BA,
+0.70 x 120.9 x coil mm
+Weight (Kg):976
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+1,000.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="654" xml:space="preserve">
+      <c r="A654" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4510 430Ti-Coil, BA,
+0.70 x 325.0 x coil mm</v>
+      </c>
+      <c r="B654" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4510 430Ti-Coil, BA,
+0.70 x 325.0 x coil mm
+Weight (Kg):4,156
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+1,000.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="655" xml:space="preserve">
+      <c r="A655" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Untrimmed, Coil, BA,
+0.40 x 1016.0 x coil mm</v>
+      </c>
+      <c r="B655" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Untrimmed, Coil, BA,
+0.40 x 1016.0 x coil mm
+Weight (Kg):2,500
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+1,050.00 €/ton
+Out of Stock</v>
+      </c>
+    </row>
+    <row r="656" xml:space="preserve">
+      <c r="A656" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Untrimmed, Coil, BA,
+0.50 x 1015.0 x coil mm</v>
+      </c>
+      <c r="B656" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Untrimmed, Coil, BA,
+0.50 x 1015.0 x coil mm
+Weight (Kg):2,340
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+1,125.00 €/ton
+Out of Stock</v>
+      </c>
+    </row>
+    <row r="657" xml:space="preserve">
+      <c r="A657" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Untrimmed, Coil, BA,
+0.50 x 1107.0 x coil mm</v>
+      </c>
+      <c r="B657" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Untrimmed, Coil, BA,
+0.50 x 1107.0 x coil mm
+Weight (Kg):2,230
+Quality:Prime
+Help
+Location:FABRICA ALGECIRAS
+1,325.00 €/ton
+Reserved</v>
+      </c>
+    </row>
+    <row r="658" xml:space="preserve">
+      <c r="A658" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Untrimmed, Coil, BA,
+0.60 x 1270.0 x coil mm</v>
+      </c>
+      <c r="B658" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Untrimmed, Coil, BA,
+0.60 x 1270.0 x coil mm
+Weight (Kg):3,385
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+1,125.00 €/ton
+Reserved</v>
+      </c>
+    </row>
+    <row r="659" xml:space="preserve">
+      <c r="A659" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Untrimmed, Coil, BA,
+0.60 x 1275.0 x coil mm</v>
+      </c>
+      <c r="B659" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Untrimmed, Coil, BA,
+0.60 x 1275.0 x coil mm
+Weight (Kg):3,535
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+1,125.00 €/ton
+Reserved</v>
+      </c>
+    </row>
+    <row r="660" xml:space="preserve">
+      <c r="A660" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Untrimmed, Coil, BA,
+1.00 x 1024.0 x coil mm</v>
+      </c>
+      <c r="B660" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Untrimmed, Coil, BA,
+1.00 x 1024.0 x coil mm
+Weight (Kg):2,641
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+1,050.00 €/ton
+Out of Stock</v>
+      </c>
+    </row>
+    <row r="661" xml:space="preserve">
+      <c r="A661" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Untrimmed, Coil, BA,
+1.00 x 1285.0 x coil mm</v>
+      </c>
+      <c r="B661" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Untrimmed, Coil, BA,
+1.00 x 1285.0 x coil mm
+Weight (Kg):5,491
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+1,125.00 €/ton
+Out of Stock</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B141"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B661"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/scraped_data.xlsx
+++ b/scraped_data.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B661"/>
+  <dimension ref="A1:B767"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -10521,10 +10521,26 @@
     </row>
     <row r="634" xml:space="preserve">
       <c r="A634" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Sheet, SB-G-400,
+1.00 x 1500.0 x 3000.0 mm</v>
+      </c>
+      <c r="B634" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Sheet, SB-G-400,
+1.00 x 1500.0 x 3000.0 mm
+Weight (Kg):1,940
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+1,125.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="635" xml:space="preserve">
+      <c r="A635" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Untrimmed, Coil, 1/4 HT,
 3.00 x 1292.0 x coil mm</v>
       </c>
-      <c r="B634" t="str" xml:space="preserve">
+      <c r="B635" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Untrimmed, Coil, 1/4 HT,
 3.00 x 1292.0 x coil mm
 Weight (Kg):3,641
@@ -10535,12 +10551,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="635" xml:space="preserve">
-      <c r="A635" t="str" xml:space="preserve">
+    <row r="636" xml:space="preserve">
+      <c r="A636" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Untrimmed, Coil, 2B,
 1.20 x 1500.0 x coil mm</v>
       </c>
-      <c r="B635" t="str" xml:space="preserve">
+      <c r="B636" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Untrimmed, Coil, 2B,
 1.20 x 1500.0 x coil mm
 Weight (Kg):4,750
@@ -10551,22 +10567,6 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="636" xml:space="preserve">
-      <c r="A636" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Untrimmed, Coil, 2D, ET-100
-0.50 x 1250.0 x coil mm</v>
-      </c>
-      <c r="B636" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Untrimmed, Coil, 2D, ET-100
-0.50 x 1250.0 x coil mm
-Weight (Kg):5,160
-Quality:Prime
-Help
-Location:FABRICA ALGECIRAS
-1,325.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
     <row r="637" xml:space="preserve">
       <c r="A637" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Untrimmed, Coil, 2D, ET-100
@@ -10575,7 +10575,7 @@
       <c r="B637" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Untrimmed, Coil, 2D, ET-100
 0.50 x 1250.0 x coil mm
-Weight (Kg):3,695
+Weight (Kg):5,160
 Quality:Prime
 Help
 Location:FABRICA ALGECIRAS
@@ -10585,18 +10585,18 @@
     </row>
     <row r="638" xml:space="preserve">
       <c r="A638" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Sheet, SB-G-400,
-1.00 x 1500.0 x 3000.0 mm</v>
+        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Untrimmed, Coil, 2D, ET-100
+0.50 x 1250.0 x coil mm</v>
       </c>
       <c r="B638" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Sheet, SB-G-400,
-1.00 x 1500.0 x 3000.0 mm
-Weight (Kg):1,940
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-1,125.00 €/ton
-Reserved</v>
+        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Untrimmed, Coil, 2D, ET-100
+0.50 x 1250.0 x coil mm
+Weight (Kg):3,695
+Quality:Prime
+Help
+Location:FABRICA ALGECIRAS
+1,325.00 €/ton
+Add to cart</v>
       </c>
     </row>
     <row r="639" xml:space="preserve">
@@ -10857,10 +10857,26 @@
     </row>
     <row r="655" xml:space="preserve">
       <c r="A655" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4510 430Ti-Coil, BA,
+0.70 x 900.0 x coil mm</v>
+      </c>
+      <c r="B655" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4510 430Ti-Coil, BA,
+0.70 x 900.0 x coil mm
+Weight (Kg):2,800
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+1,125.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="656" xml:space="preserve">
+      <c r="A656" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Untrimmed, Coil, BA,
 0.40 x 1016.0 x coil mm</v>
       </c>
-      <c r="B655" t="str" xml:space="preserve">
+      <c r="B656" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Untrimmed, Coil, BA,
 0.40 x 1016.0 x coil mm
 Weight (Kg):2,500
@@ -10871,12 +10887,12 @@
 Out of Stock</v>
       </c>
     </row>
-    <row r="656" xml:space="preserve">
-      <c r="A656" t="str" xml:space="preserve">
+    <row r="657" xml:space="preserve">
+      <c r="A657" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Untrimmed, Coil, BA,
 0.50 x 1015.0 x coil mm</v>
       </c>
-      <c r="B656" t="str" xml:space="preserve">
+      <c r="B657" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Untrimmed, Coil, BA,
 0.50 x 1015.0 x coil mm
 Weight (Kg):2,340
@@ -10887,12 +10903,12 @@
 Out of Stock</v>
       </c>
     </row>
-    <row r="657" xml:space="preserve">
-      <c r="A657" t="str" xml:space="preserve">
+    <row r="658" xml:space="preserve">
+      <c r="A658" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Untrimmed, Coil, BA,
 0.50 x 1107.0 x coil mm</v>
       </c>
-      <c r="B657" t="str" xml:space="preserve">
+      <c r="B658" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Untrimmed, Coil, BA,
 0.50 x 1107.0 x coil mm
 Weight (Kg):2,230
@@ -10903,12 +10919,12 @@
 Reserved</v>
       </c>
     </row>
-    <row r="658" xml:space="preserve">
-      <c r="A658" t="str" xml:space="preserve">
+    <row r="659" xml:space="preserve">
+      <c r="A659" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Untrimmed, Coil, BA,
 0.60 x 1270.0 x coil mm</v>
       </c>
-      <c r="B658" t="str" xml:space="preserve">
+      <c r="B659" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Untrimmed, Coil, BA,
 0.60 x 1270.0 x coil mm
 Weight (Kg):3,385
@@ -10919,12 +10935,12 @@
 Reserved</v>
       </c>
     </row>
-    <row r="659" xml:space="preserve">
-      <c r="A659" t="str" xml:space="preserve">
+    <row r="660" xml:space="preserve">
+      <c r="A660" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Untrimmed, Coil, BA,
 0.60 x 1275.0 x coil mm</v>
       </c>
-      <c r="B659" t="str" xml:space="preserve">
+      <c r="B660" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Untrimmed, Coil, BA,
 0.60 x 1275.0 x coil mm
 Weight (Kg):3,535
@@ -10933,22 +10949,6 @@
 Location:FABRICA ALGECIRAS
 1,125.00 €/ton
 Reserved</v>
-      </c>
-    </row>
-    <row r="660" xml:space="preserve">
-      <c r="A660" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Untrimmed, Coil, BA,
-1.00 x 1024.0 x coil mm</v>
-      </c>
-      <c r="B660" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Untrimmed, Coil, BA,
-1.00 x 1024.0 x coil mm
-Weight (Kg):2,641
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-1,050.00 €/ton
-Out of Stock</v>
       </c>
     </row>
     <row r="661" xml:space="preserve">
@@ -10967,9 +10967,1705 @@
 Out of Stock</v>
       </c>
     </row>
+    <row r="662" xml:space="preserve">
+      <c r="A662" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4510 430Ti-Coil, BA,
+0.70 x 900.0 x coil mm</v>
+      </c>
+      <c r="B662" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4510 430Ti-Coil, BA,
+0.70 x 900.0 x coil mm
+Weight (Kg):6,570
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+1,125.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="663" xml:space="preserve">
+      <c r="A663" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4510 430Ti-Coil, BA,
+0.70 x 905.0 x coil mm</v>
+      </c>
+      <c r="B663" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4510 430Ti-Coil, BA,
+0.70 x 905.0 x coil mm
+Weight (Kg):9,410
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+1,125.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="664" xml:space="preserve">
+      <c r="A664" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4510 430Ti-Coil, BA,
+0.70 x 932.0 x coil mm</v>
+      </c>
+      <c r="B664" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4510 430Ti-Coil, BA,
+0.70 x 932.0 x coil mm
+Weight (Kg):2,270
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+1,125.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="665" xml:space="preserve">
+      <c r="A665" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4510 430Ti-Coil, BA,
+0.70 x 940.0 x coil mm</v>
+      </c>
+      <c r="B665" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4510 430Ti-Coil, BA,
+0.70 x 940.0 x coil mm
+Weight (Kg):14,920
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+1,125.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="666" xml:space="preserve">
+      <c r="A666" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4510 430Ti-Untrimmed, Coil, BA,
+0.50 x 1275.0 x coil mm</v>
+      </c>
+      <c r="B666" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4510 430Ti-Untrimmed, Coil, BA,
+0.50 x 1275.0 x coil mm
+Weight (Kg):2,258
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+1,125.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="667" xml:space="preserve">
+      <c r="A667" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4510 430Ti-Untrimmed, Coil, BA,
+0.70 x 928.0 x coil mm</v>
+      </c>
+      <c r="B667" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4510 430Ti-Untrimmed, Coil, BA,
+0.70 x 928.0 x coil mm
+Weight (Kg):4,257
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+1,125.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="668" xml:space="preserve">
+      <c r="A668" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4509 441-Coil, 2B,
+1.20 x 275.9 x coil mm</v>
+      </c>
+      <c r="B668" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4509 441-Coil, 2B,
+1.20 x 275.9 x coil mm
+Weight (Kg):2,416
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+1,100.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="669" xml:space="preserve">
+      <c r="A669" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4509 441-Coil, 2D,
+1.20 x 196.0 x coil mm</v>
+      </c>
+      <c r="B669" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4509 441-Coil, 2D,
+1.20 x 196.0 x coil mm
+Weight (Kg):2,970
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+1,100.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="670" xml:space="preserve">
+      <c r="A670" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4509 441-Coil, 2D,
+1.20 x 200.0 x coil mm</v>
+      </c>
+      <c r="B670" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4509 441-Coil, 2D,
+1.20 x 200.0 x coil mm
+Weight (Kg):3,310
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+1,100.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="671" xml:space="preserve">
+      <c r="A671" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4509 441-Coil, 2D,
+1.20 x 214.9 x coil mm</v>
+      </c>
+      <c r="B671" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4509 441-Coil, 2D,
+1.20 x 214.9 x coil mm
+Weight (Kg):3,220
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+1,100.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="672" xml:space="preserve">
+      <c r="A672" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4509 441-Coil, 2D,
+1.20 x 223.9 x coil mm</v>
+      </c>
+      <c r="B672" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4509 441-Coil, 2D,
+1.20 x 223.9 x coil mm
+Weight (Kg):3,798
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+1,100.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="673" xml:space="preserve">
+      <c r="A673" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4509 441-Coil, 2D,
+1.20 x 224.0 x coil mm</v>
+      </c>
+      <c r="B673" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4509 441-Coil, 2D,
+1.20 x 224.0 x coil mm
+Weight (Kg):3,808
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+1,100.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="674" xml:space="preserve">
+      <c r="A674" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4509 441-Coil, BA,
+0.80 x 130.9 x coil mm</v>
+      </c>
+      <c r="B674" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4509 441-Coil, BA,
+0.80 x 130.9 x coil mm
+Weight (Kg):245
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+1,100.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="675" xml:space="preserve">
+      <c r="A675" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4509 441-Coil, BA,
+0.80 x 130.9 x coil mm</v>
+      </c>
+      <c r="B675" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4509 441-Coil, BA,
+0.80 x 130.9 x coil mm
+Weight (Kg):245
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+1,100.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="676" xml:space="preserve">
+      <c r="A676" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4509 441-Coil, BA,
+0.80 x 130.9 x coil mm</v>
+      </c>
+      <c r="B676" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4509 441-Coil, BA,
+0.80 x 130.9 x coil mm
+Weight (Kg):213
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+1,100.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="677" xml:space="preserve">
+      <c r="A677" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4509 441-Coil, BA,
+0.80 x 130.9 x coil mm</v>
+      </c>
+      <c r="B677" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4509 441-Coil, BA,
+0.80 x 130.9 x coil mm
+Weight (Kg):244
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+1,100.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="678" xml:space="preserve">
+      <c r="A678" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4509 441-Coil, SB-G-400,
+1.00 x 1000.0 x coil mm</v>
+      </c>
+      <c r="B678" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4509 441-Coil, SB-G-400,
+1.00 x 1000.0 x coil mm
+Weight (Kg):7,550
+Quality:Prime
+Help
+Location:FABRICA ALGECIRAS
+1,625.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="679" xml:space="preserve">
+      <c r="A679" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4509 441-Coil, SB-G-400,
+1.00 x 255.0 x coil mm</v>
+      </c>
+      <c r="B679" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4509 441-Coil, SB-G-400,
+1.00 x 255.0 x coil mm
+Weight (Kg):2,182
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+1,100.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="680" xml:space="preserve">
+      <c r="A680" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4509 441-Coil, SB-G-400,
+1.00 x 290.9 x coil mm</v>
+      </c>
+      <c r="B680" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4509 441-Coil, SB-G-400,
+1.00 x 290.9 x coil mm
+Weight (Kg):2,370
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+1,100.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="681" xml:space="preserve">
+      <c r="A681" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4509 441-Coil, BA,
+0.40 x 1000.0 x coil mm</v>
+      </c>
+      <c r="B681" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4509 441-Coil, BA,
+0.40 x 1000.0 x coil mm
+Weight (Kg):3,222
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+1,225.00 €/ton
+Out of Stock</v>
+      </c>
+    </row>
+    <row r="682" xml:space="preserve">
+      <c r="A682" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4509 441-Coil, SB-G-400,
+1.20 x 110.9 x coil mm</v>
+      </c>
+      <c r="B682" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4509 441-Coil, SB-G-400,
+1.20 x 110.9 x coil mm
+Weight (Kg):856
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+1,100.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="683" xml:space="preserve">
+      <c r="A683" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4509 441-Coil, SB-G-400,
+1.20 x 130.9 x coil mm</v>
+      </c>
+      <c r="B683" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4509 441-Coil, SB-G-400,
+1.20 x 130.9 x coil mm
+Weight (Kg):564
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+1,100.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="684" xml:space="preserve">
+      <c r="A684" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4509 441-Coil, SB-G-400,
+1.20 x 130.9 x coil mm</v>
+      </c>
+      <c r="B684" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4509 441-Coil, SB-G-400,
+1.20 x 130.9 x coil mm
+Weight (Kg):532
+Quality:Prime
+Help
+Location:FABRICA ALGECIRAS
+1,100.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="685" xml:space="preserve">
+      <c r="A685" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4509 441-Coil, SB-G-400,
+1.50 x 130.9 x coil mm</v>
+      </c>
+      <c r="B685" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4509 441-Coil, SB-G-400,
+1.50 x 130.9 x coil mm
+Weight (Kg):640
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+1,100.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="686" xml:space="preserve">
+      <c r="A686" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4509 441-Coil, SB-G-400,
+1.50 x 360.0 x coil mm</v>
+      </c>
+      <c r="B686" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4509 441-Coil, SB-G-400,
+1.50 x 360.0 x coil mm
+Weight (Kg):1,488
+Quality:Downgraded
+Help
+Location:FABRICA ALGECIRAS
+1,100.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="687" xml:space="preserve">
+      <c r="A687" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4509 441-Untrimmed, Coil, 2B,
+1.50 x 1539.0 x coil mm</v>
+      </c>
+      <c r="B687" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4509 441-Untrimmed, Coil, 2B,
+1.50 x 1539.0 x coil mm
+Weight (Kg):14,230
+Quality:Prime
+Help
+Location:FABRICA ALGECIRAS
+2,200.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="688" xml:space="preserve">
+      <c r="A688" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4509 441-Untrimmed, Coil, BA,
+0.40 x 1075.0 x coil mm</v>
+      </c>
+      <c r="B688" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4509 441-Untrimmed, Coil, BA,
+0.40 x 1075.0 x coil mm
+Weight (Kg):9,750
+Quality:Prime
+Help
+Location:FABRICA ALGECIRAS
+2,200.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="689" xml:space="preserve">
+      <c r="A689" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4509 441-Untrimmed, Coil, Nb. 1,
+5.00 x 1045.0 x coil mm</v>
+      </c>
+      <c r="B689" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4509 441-Untrimmed, Coil, Nb. 1,
+5.00 x 1045.0 x coil mm
+Weight (Kg):7,880
+Quality:Prime
+Help
+Location:FABRICA ALGECIRAS
+1,525.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="690" xml:space="preserve">
+      <c r="A690" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 441-1.4509 Coil, 2B,
+1.20 x 240.9 x coil mm</v>
+      </c>
+      <c r="B690" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 441-1.4509 Coil, 2B,
+1.20 x 240.9 x coil mm
+Weight (Kg):3,882
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+1,100.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="691" xml:space="preserve">
+      <c r="A691" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 304-1.4301 Coil,
+0.70 x 270.9 x coil mm</v>
+      </c>
+      <c r="B691" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 304-1.4301 Coil,
+0.70 x 270.9 x coil mm
+Weight (Kg):2,704
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,075.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="692" xml:space="preserve">
+      <c r="A692" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 316L-1.4404 Coil,
+1.20 x 136.0 x coil mm</v>
+      </c>
+      <c r="B692" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 316L-1.4404 Coil,
+1.20 x 136.0 x coil mm
+Weight (Kg):2,300
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+3,270.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="693" xml:space="preserve">
+      <c r="A693" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 304L/304-4301/4307 Coil, 2B,
+6.00 x 245.0 x coil mm</v>
+      </c>
+      <c r="B693" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 304L/304-4301/4307 Coil, 2B,
+6.00 x 245.0 x coil mm
+Weight (Kg):2,394
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,075.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="694" xml:space="preserve">
+      <c r="A694" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, 2B,
+0.70 x 197.5 x coil mm</v>
+      </c>
+      <c r="B694" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, 2B,
+0.70 x 197.5 x coil mm
+Weight (Kg):2,442
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+1,000.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="695" xml:space="preserve">
+      <c r="A695" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 441-1.4509 Coil, 2B,
+2.00 x 120.9 x coil mm</v>
+      </c>
+      <c r="B695" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 441-1.4509 Coil, 2B,
+2.00 x 120.9 x coil mm
+Weight (Kg):1,956
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+1,100.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="696" xml:space="preserve">
+      <c r="A696" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 304-1.4301 Coil, 2B,
+1.20 x 119.9 x coil mm</v>
+      </c>
+      <c r="B696" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 304-1.4301 Coil, 2B,
+1.20 x 119.9 x coil mm
+Weight (Kg):1,500
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,075.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="697" xml:space="preserve">
+      <c r="A697" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 304-1.4301 Coil, 2B,
+1.20 x 119.9 x coil mm</v>
+      </c>
+      <c r="B697" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 304-1.4301 Coil, 2B,
+1.20 x 119.9 x coil mm
+Weight (Kg):1,400
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,075.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="698" xml:space="preserve">
+      <c r="A698" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, BA,
+0.70 x 125.0 x coil mm</v>
+      </c>
+      <c r="B698" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, BA,
+0.70 x 125.0 x coil mm
+Weight (Kg):1,764
+Quality:Prime
+Help
+Location:FABRICA ALGECIRAS
+1,000.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="699" xml:space="preserve">
+      <c r="A699" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, BA,
+0.70 x 104.9 x coil mm</v>
+      </c>
+      <c r="B699" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, BA,
+0.70 x 104.9 x coil mm
+Weight (Kg):1,240
+Quality:Prime
+Help
+Location:FABRICA ALGECIRAS
+1,000.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="700" xml:space="preserve">
+      <c r="A700" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, BA,
+0.70 x 118.9 x coil mm</v>
+      </c>
+      <c r="B700" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, BA,
+0.70 x 118.9 x coil mm
+Weight (Kg):1,802
+Quality:Prime
+Help
+Location:FABRICA ALGECIRAS
+1,000.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="701" xml:space="preserve">
+      <c r="A701" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, BA,
+0.70 x 115.9 x coil mm</v>
+      </c>
+      <c r="B701" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, BA,
+0.70 x 115.9 x coil mm
+Weight (Kg):1,368
+Quality:Prime
+Help
+Location:FABRICA ALGECIRAS
+1,000.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="702" xml:space="preserve">
+      <c r="A702" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, BA,
+0.70 x 119.0 x coil mm</v>
+      </c>
+      <c r="B702" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, BA,
+0.70 x 119.0 x coil mm
+Weight (Kg):1,622
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+1,000.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="703" xml:space="preserve">
+      <c r="A703" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 304L/304-4301/4307 Coil, 2B,
+1.40 x 110.9 x coil mm</v>
+      </c>
+      <c r="B703" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 304L/304-4301/4307 Coil, 2B,
+1.40 x 110.9 x coil mm
+Weight (Kg):1,240
+Quality:Prime
+Help
+Location:FABRICA ALGECIRAS
+2,075.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="704" xml:space="preserve">
+      <c r="A704" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, BA,
+0.70 x 104.0 x coil mm</v>
+      </c>
+      <c r="B704" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, BA,
+0.70 x 104.0 x coil mm
+Weight (Kg):1,622
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+1,000.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="705" xml:space="preserve">
+      <c r="A705" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, BA,
+0.70 x 104.0 x coil mm</v>
+      </c>
+      <c r="B705" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, BA,
+0.70 x 104.0 x coil mm
+Weight (Kg):1,688
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+1,000.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="706" xml:space="preserve">
+      <c r="A706" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 304L/304-4301/4307 Coil, 2B,
+1.40 x 110.9 x coil mm</v>
+      </c>
+      <c r="B706" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 304L/304-4301/4307 Coil, 2B,
+1.40 x 110.9 x coil mm
+Weight (Kg):1,162
+Quality:Prime
+Help
+Location:FABRICA ALGECIRAS
+2,075.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="707" xml:space="preserve">
+      <c r="A707" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 430Ti-1.4510 Coil, BA,
+0.70 x 165.9 x coil mm</v>
+      </c>
+      <c r="B707" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 430Ti-1.4510 Coil, BA,
+0.70 x 165.9 x coil mm
+Weight (Kg):2,692
+Quality:Prime
+Help
+Location:FABRICA ALGECIRAS
+1,000.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="708" xml:space="preserve">
+      <c r="A708" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 430Ti-1.4510 Coil, BA,
+0.70 x 165.9 x coil mm</v>
+      </c>
+      <c r="B708" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 430Ti-1.4510 Coil, BA,
+0.70 x 165.9 x coil mm
+Weight (Kg):2,756
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+1,000.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="709" xml:space="preserve">
+      <c r="A709" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, BA,
+0.70 x 140.9 x coil mm</v>
+      </c>
+      <c r="B709" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, BA,
+0.70 x 140.9 x coil mm
+Weight (Kg):1,676
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+1,000.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="710" xml:space="preserve">
+      <c r="A710" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, BA,
+0.70 x 100.9 x coil mm</v>
+      </c>
+      <c r="B710" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, BA,
+0.70 x 100.9 x coil mm
+Weight (Kg):1,340
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+1,000.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="711" xml:space="preserve">
+      <c r="A711" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, BA,
+0.70 x 125.0 x coil mm</v>
+      </c>
+      <c r="B711" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, BA,
+0.70 x 125.0 x coil mm
+Weight (Kg):1,550
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+1,000.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="712" xml:space="preserve">
+      <c r="A712" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, BA,
+0.70 x 125.0 x coil mm</v>
+      </c>
+      <c r="B712" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, BA,
+0.70 x 125.0 x coil mm
+Weight (Kg):1,414
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+1,000.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="713" xml:space="preserve">
+      <c r="A713" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, BA,
+0.70 x 100.9 x coil mm</v>
+      </c>
+      <c r="B713" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, BA,
+0.70 x 100.9 x coil mm
+Weight (Kg):2,188
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+1,000.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="714" xml:space="preserve">
+      <c r="A714" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 304L/304-4301/4307 Coil, Nb. 1,
+4.70 x 110.0 x coil mm</v>
+      </c>
+      <c r="B714" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 304L/304-4301/4307 Coil, Nb. 1,
+4.70 x 110.0 x coil mm
+Weight (Kg):1,796
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+1,975.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="715" xml:space="preserve">
+      <c r="A715" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 304L/304-4301/4307 Coil, Nb. 1,
+4.70 x 110.0 x coil mm</v>
+      </c>
+      <c r="B715" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 304L/304-4301/4307 Coil, Nb. 1,
+4.70 x 110.0 x coil mm
+Weight (Kg):2,038
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+1,975.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="716" xml:space="preserve">
+      <c r="A716" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, BA,
+0.70 x 165.9 x coil mm</v>
+      </c>
+      <c r="B716" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, BA,
+0.70 x 165.9 x coil mm
+Weight (Kg):2,620
+Quality:Prime
+Help
+Location:FABRICA ALGECIRAS
+1,000.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="717" xml:space="preserve">
+      <c r="A717" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 304-1.4301 Coil,
+0.70 x 260.9 x coil mm</v>
+      </c>
+      <c r="B717" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 304-1.4301 Coil,
+0.70 x 260.9 x coil mm
+Weight (Kg):1,330
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,075.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="718" xml:space="preserve">
+      <c r="A718" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 304-1.4301 Coil,
+0.70 x 260.9 x coil mm</v>
+      </c>
+      <c r="B718" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 304-1.4301 Coil,
+0.70 x 260.9 x coil mm
+Weight (Kg):1,264
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,075.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="719" xml:space="preserve">
+      <c r="A719" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, BA,
+0.70 x 110.0 x coil mm</v>
+      </c>
+      <c r="B719" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, BA,
+0.70 x 110.0 x coil mm
+Weight (Kg):1,250
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+1,000.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="720" xml:space="preserve">
+      <c r="A720" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, BA,
+0.70 x 122.9 x coil mm</v>
+      </c>
+      <c r="B720" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, BA,
+0.70 x 122.9 x coil mm
+Weight (Kg):1,460
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+1,000.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="721" xml:space="preserve">
+      <c r="A721" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 304L/304-4301/4307 Coil, 2B,
+1.40 x 110.0 x coil mm</v>
+      </c>
+      <c r="B721" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 304L/304-4301/4307 Coil, 2B,
+1.40 x 110.0 x coil mm
+Weight (Kg):1,554
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,075.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="722" xml:space="preserve">
+      <c r="A722" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 304L/304-4301/4307 Coil, 2B,
+1.40 x 110.0 x coil mm</v>
+      </c>
+      <c r="B722" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 304L/304-4301/4307 Coil, 2B,
+1.40 x 110.0 x coil mm
+Weight (Kg):1,586
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,075.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="723" xml:space="preserve">
+      <c r="A723" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 304L/304-4301/4307 Coil, 2B,
+1.40 x 104.0 x coil mm</v>
+      </c>
+      <c r="B723" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 304L/304-4301/4307 Coil, 2B,
+1.40 x 104.0 x coil mm
+Weight (Kg):1,030
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,075.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="724" xml:space="preserve">
+      <c r="A724" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 304DDQ-1.4301 Coil, BA,
+0.70 x 181.9 x coil mm</v>
+      </c>
+      <c r="B724" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 304DDQ-1.4301 Coil, BA,
+0.70 x 181.9 x coil mm
+Weight (Kg):2,912
+Quality:Prime
+Help
+Location:FABRICA ALGECIRAS
+2,075.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="725" xml:space="preserve">
+      <c r="A725" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 304-1.4301 Coil,
+1.50 x 136.0 x coil mm</v>
+      </c>
+      <c r="B725" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 304-1.4301 Coil,
+1.50 x 136.0 x coil mm
+Weight (Kg):3,450
+Quality:Prime
+Help
+Location:FABRICA ALGECIRAS
+2,075.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="726" xml:space="preserve">
+      <c r="A726" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 304-1.4301 Coil, BA,
+0.40 x 200.0 x coil mm</v>
+      </c>
+      <c r="B726" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 304-1.4301 Coil, BA,
+0.40 x 200.0 x coil mm
+Weight (Kg):1,964
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,075.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="727" xml:space="preserve">
+      <c r="A727" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 304-1.4301 Coil, BA, ET-60
+0.60 x 120.0 x coil mm</v>
+      </c>
+      <c r="B727" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 304-1.4301 Coil, BA, ET-60
+0.60 x 120.0 x coil mm
+Weight (Kg):1,302
+Quality:Prime
+Help
+Location:FABRICA ALGECIRAS
+2,075.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="728" xml:space="preserve">
+      <c r="A728" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, ET-100
+0.70 x 124.9 x coil mm</v>
+      </c>
+      <c r="B728" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, ET-100
+0.70 x 124.9 x coil mm
+Weight (Kg):2,106
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+1,000.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="729" xml:space="preserve">
+      <c r="A729" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, ET-100
+0.70 x 124.9 x coil mm</v>
+      </c>
+      <c r="B729" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, ET-100
+0.70 x 124.9 x coil mm
+Weight (Kg):1,972
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+1,000.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="730" xml:space="preserve">
+      <c r="A730" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 430Ti-1.4510 Coil, 2B,
+0.80 x 155.9 x coil mm</v>
+      </c>
+      <c r="B730" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 430Ti-1.4510 Coil, 2B,
+0.80 x 155.9 x coil mm
+Weight (Kg):1,586
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+1,000.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="731" xml:space="preserve">
+      <c r="A731" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 304-1.4301 Coil, BA,
+0.40 x 270.0 x coil mm</v>
+      </c>
+      <c r="B731" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 304-1.4301 Coil, BA,
+0.40 x 270.0 x coil mm
+Weight (Kg):2,572
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,075.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="732" xml:space="preserve">
+      <c r="A732" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, BA,
+0.60 x 130.0 x coil mm</v>
+      </c>
+      <c r="B732" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, BA,
+0.60 x 130.0 x coil mm
+Weight (Kg):1,490
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+1,000.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="733" xml:space="preserve">
+      <c r="A733" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 441-1.4509 Coil, BA,
+0.40 x 110.0 x coil mm</v>
+      </c>
+      <c r="B733" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 441-1.4509 Coil, BA,
+0.40 x 110.0 x coil mm
+Weight (Kg):1,870
+Quality:Prime
+Help
+Location:FABRICA ALGECIRAS
+1,100.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="734" xml:space="preserve">
+      <c r="A734" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 441-1.4509 Coil, BA,
+0.40 x 110.0 x coil mm</v>
+      </c>
+      <c r="B734" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 441-1.4509 Coil, BA,
+0.40 x 110.0 x coil mm
+Weight (Kg):1,882
+Quality:Prime
+Help
+Location:FABRICA ALGECIRAS
+1,100.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="735" xml:space="preserve">
+      <c r="A735" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 301-1.4310 Coil, BA,
+0.40 x 110.0 x coil mm</v>
+      </c>
+      <c r="B735" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 301-1.4310 Coil, BA,
+0.40 x 110.0 x coil mm
+Weight (Kg):1,934
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+1,925.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="736" xml:space="preserve">
+      <c r="A736" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 301-1.4310 Coil, BA,
+0.40 x 110.0 x coil mm</v>
+      </c>
+      <c r="B736" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 301-1.4310 Coil, BA,
+0.40 x 110.0 x coil mm
+Weight (Kg):1,860
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+1,925.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="737" xml:space="preserve">
+      <c r="A737" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 321-1.4541 Coil, 2B,
+1.90 x 104.5 x coil mm</v>
+      </c>
+      <c r="B737" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 321-1.4541 Coil, 2B,
+1.90 x 104.5 x coil mm
+Weight (Kg):2,304
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,235.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="738" xml:space="preserve">
+      <c r="A738" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 304L/304-4301/4307 Coil, Polished N4-G-180,
+1.20 x 255.9 x coil mm</v>
+      </c>
+      <c r="B738" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 304L/304-4301/4307 Coil, Polished N4-G-180,
+1.20 x 255.9 x coil mm
+Weight (Kg):4,298
+Quality:Prime
+Help
+Location:FABRICA ALGECIRAS
+2,075.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="739" xml:space="preserve">
+      <c r="A739" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 301-1.4310 Coil, BA,
+0.40 x 110.0 x coil mm</v>
+      </c>
+      <c r="B739" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 301-1.4310 Coil, BA,
+0.40 x 110.0 x coil mm
+Weight (Kg):1,698
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+1,925.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="740" xml:space="preserve">
+      <c r="A740" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, BA,
+0.40 x 130.0 x coil mm</v>
+      </c>
+      <c r="B740" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, BA,
+0.40 x 130.0 x coil mm
+Weight (Kg):1,916
+Quality:Prime
+Help
+Location:FABRICA ALGECIRAS
+1,000.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="741" xml:space="preserve">
+      <c r="A741" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 430Ti-1.4510 Coil, BA,
+0.50 x 140.0 x coil mm</v>
+      </c>
+      <c r="B741" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 430Ti-1.4510 Coil, BA,
+0.50 x 140.0 x coil mm
+Weight (Kg):3,054
+Quality:Prime
+Help
+Location:FABRICA ALGECIRAS
+1,000.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="742" xml:space="preserve">
+      <c r="A742" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 430Ti-1.4510 Coil, BA,
+0.50 x 140.0 x coil mm</v>
+      </c>
+      <c r="B742" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 430Ti-1.4510 Coil, BA,
+0.50 x 140.0 x coil mm
+Weight (Kg):3,060
+Quality:Prime
+Help
+Location:FABRICA ALGECIRAS
+1,000.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="743" xml:space="preserve">
+      <c r="A743" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 430Ti-1.4510 Coil, BA,
+0.50 x 140.0 x coil mm</v>
+      </c>
+      <c r="B743" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 430Ti-1.4510 Coil, BA,
+0.50 x 140.0 x coil mm
+Weight (Kg):2,220
+Quality:Prime
+Help
+Location:FABRICA ALGECIRAS
+1,000.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="744" xml:space="preserve">
+      <c r="A744" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 430Ti-1.4510 Coil, BA,
+0.50 x 140.0 x coil mm</v>
+      </c>
+      <c r="B744" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 430Ti-1.4510 Coil, BA,
+0.50 x 140.0 x coil mm
+Weight (Kg):2,224
+Quality:Prime
+Help
+Location:FABRICA ALGECIRAS
+1,000.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="745" xml:space="preserve">
+      <c r="A745" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 304L/304-4301/4307 Coil, 2B,
+1.40 x 100.9 x coil mm</v>
+      </c>
+      <c r="B745" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 304L/304-4301/4307 Coil, 2B,
+1.40 x 100.9 x coil mm
+Weight (Kg):1,612
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,075.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="746" xml:space="preserve">
+      <c r="A746" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 304L/304-4301/4307 Coil, 2B,
+1.40 x 100.9 x coil mm</v>
+      </c>
+      <c r="B746" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 304L/304-4301/4307 Coil, 2B,
+1.40 x 100.9 x coil mm
+Weight (Kg):1,600
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,075.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="747" xml:space="preserve">
+      <c r="A747" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 304-1.4301 Coil, Emboss Chequered,
+0.70 x 174.9 x coil mm</v>
+      </c>
+      <c r="B747" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 304-1.4301 Coil, Emboss Chequered,
+0.70 x 174.9 x coil mm
+Weight (Kg):1,494
+Quality:Prime
+Help
+Location:FABRICA ALGECIRAS
+2,075.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="748" xml:space="preserve">
+      <c r="A748" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 304-1.4301 Coil, Emboss Chequered,
+0.70 x 174.9 x coil mm</v>
+      </c>
+      <c r="B748" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 304-1.4301 Coil, Emboss Chequered,
+0.70 x 174.9 x coil mm
+Weight (Kg):1,472
+Quality:Prime
+Help
+Location:FABRICA ALGECIRAS
+2,075.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="749" xml:space="preserve">
+      <c r="A749" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, SB-G-240,
+0.50 x 290.9 x coil mm</v>
+      </c>
+      <c r="B749" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, SB-G-240,
+0.50 x 290.9 x coil mm
+Weight (Kg):4,408
+Quality:Prime
+Help
+Location:FABRICA ALGECIRAS
+1,000.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="750" xml:space="preserve">
+      <c r="A750" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 304-1.4301 Coil, BA,
+0.60 x 110.0 x coil mm</v>
+      </c>
+      <c r="B750" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 304-1.4301 Coil, BA,
+0.60 x 110.0 x coil mm
+Weight (Kg):1,032
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,075.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="751" xml:space="preserve">
+      <c r="A751" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 304-1.4301 Coil, BA,
+0.40 x 270.0 x coil mm</v>
+      </c>
+      <c r="B751" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 304-1.4301 Coil, BA,
+0.40 x 270.0 x coil mm
+Weight (Kg):3,124
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,075.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="752" xml:space="preserve">
+      <c r="A752" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 304-1.4301 Coil, BA,
+0.60 x 135.0 x coil mm</v>
+      </c>
+      <c r="B752" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 304-1.4301 Coil, BA,
+0.60 x 135.0 x coil mm
+Weight (Kg):2,078
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,075.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="753" xml:space="preserve">
+      <c r="A753" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 441-1.4509 Coil, 2B,
+2.00 x 245.9 x coil mm</v>
+      </c>
+      <c r="B753" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 441-1.4509 Coil, 2B,
+2.00 x 245.9 x coil mm
+Weight (Kg):3,492
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+1,100.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="754" xml:space="preserve">
+      <c r="A754" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 304-1.4301 Coil, 2B,
+0.60 x 101.9 x coil mm</v>
+      </c>
+      <c r="B754" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 304-1.4301 Coil, 2B,
+0.60 x 101.9 x coil mm
+Weight (Kg):1,350
+Quality:Prime
+Help
+Location:FABRICA ALGECIRAS
+2,075.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="755" xml:space="preserve">
+      <c r="A755" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 430Ti-1.4510 Coil, BA,
+0.70 x 118.9 x coil mm</v>
+      </c>
+      <c r="B755" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 430Ti-1.4510 Coil, BA,
+0.70 x 118.9 x coil mm
+Weight (Kg):1,768
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+1,000.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="756" xml:space="preserve">
+      <c r="A756" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 304L/304-4301/4307 Coil, 2B,
+1.00 x 135.9 x coil mm</v>
+      </c>
+      <c r="B756" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 304L/304-4301/4307 Coil, 2B,
+1.00 x 135.9 x coil mm
+Weight (Kg):1,056
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,075.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="757" xml:space="preserve">
+      <c r="A757" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 304L/304-4301/4307 Coil, 2B,
+2.00 x 250.0 x coil mm</v>
+      </c>
+      <c r="B757" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 304L/304-4301/4307 Coil, 2B,
+2.00 x 250.0 x coil mm
+Weight (Kg):2,388
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,075.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="758" xml:space="preserve">
+      <c r="A758" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, BA,
+0.70 x 125.9 x coil mm</v>
+      </c>
+      <c r="B758" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, BA,
+0.70 x 125.9 x coil mm
+Weight (Kg):1,788
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+1,000.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="759" xml:space="preserve">
+      <c r="A759" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, BA,
+0.70 x 125.9 x coil mm</v>
+      </c>
+      <c r="B759" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, BA,
+0.70 x 125.9 x coil mm
+Weight (Kg):1,794
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+1,000.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="760" xml:space="preserve">
+      <c r="A760" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 430Ti-1.4510 Coil, BA,
+0.70 x 112.0 x coil mm</v>
+      </c>
+      <c r="B760" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 430Ti-1.4510 Coil, BA,
+0.70 x 112.0 x coil mm
+Weight (Kg):1,550
+Quality:Prime
+Help
+Location:FABRICA ALGECIRAS
+1,000.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="761" xml:space="preserve">
+      <c r="A761" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 304-1.4301 Coil, BA,
+0.60 x 320.0 x coil mm</v>
+      </c>
+      <c r="B761" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 304-1.4301 Coil, BA,
+0.60 x 320.0 x coil mm
+Weight (Kg):2,534
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,075.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="762" xml:space="preserve">
+      <c r="A762" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 304-1.4301 Coil, BA,
+0.60 x 320.0 x coil mm</v>
+      </c>
+      <c r="B762" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 304-1.4301 Coil, BA,
+0.60 x 320.0 x coil mm
+Weight (Kg):3,148
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,075.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="763" xml:space="preserve">
+      <c r="A763" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 304-1.4301 Coil, 2B,
+0.80 x 199.9 x coil mm</v>
+      </c>
+      <c r="B763" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 304-1.4301 Coil, 2B,
+0.80 x 199.9 x coil mm
+Weight (Kg):2,602
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,075.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="764" xml:space="preserve">
+      <c r="A764" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 304L/304-4301/4307 Coil, 2B,
+1.00 x 125.9 x coil mm</v>
+      </c>
+      <c r="B764" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 304L/304-4301/4307 Coil, 2B,
+1.00 x 125.9 x coil mm
+Weight (Kg):1,726
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,075.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="765" xml:space="preserve">
+      <c r="A765" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 316L-1.4404 Coil, 2B,
+1.50 x 230.9 x coil mm</v>
+      </c>
+      <c r="B765" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 316L-1.4404 Coil, 2B,
+1.50 x 230.9 x coil mm
+Weight (Kg):1,956
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+3,270.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="766" xml:space="preserve">
+      <c r="A766" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, SBA,
+0.70 x 180.9 x coil mm</v>
+      </c>
+      <c r="B766" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, SBA,
+0.70 x 180.9 x coil mm
+Weight (Kg):2,402
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+1,000.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="767" xml:space="preserve">
+      <c r="A767" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 301-1.4310 Coil, BA,
+0.40 x 110.0 x coil mm</v>
+      </c>
+      <c r="B767" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 301-1.4310 Coil, BA,
+0.40 x 110.0 x coil mm
+Weight (Kg):1,734
+Quality:Prime
+Help
+Location:FABRICA ALGECIRAS
+1,925.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B661"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B767"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/scraped_data.xlsx
+++ b/scraped_data.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B767"/>
+  <dimension ref="A1:B441"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -7447,5225 +7447,9 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="442" xml:space="preserve">
-      <c r="A442" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Coil, Nb. 1,
-4.50 x 220.0 x coil mm</v>
-      </c>
-      <c r="B442" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Coil, Nb. 1,
-4.50 x 220.0 x coil mm
-Weight (Kg):3,869
-Quality:Prime
-Help
-Location:FABRICA ALGECIRAS
-3,170.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="443" xml:space="preserve">
-      <c r="A443" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Coil, SB-G-400,
-1.00 x 250.9 x coil mm</v>
-      </c>
-      <c r="B443" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Coil, SB-G-400,
-1.00 x 250.9 x coil mm
-Weight (Kg):1,428
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-3,270.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="444" xml:space="preserve">
-      <c r="A444" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
-0.70 x 1250.0 x 2500.0 mm</v>
-      </c>
-      <c r="B444" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
-0.70 x 1250.0 x 2500.0 mm
-Weight (Kg):1,756
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-3,395.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="445" xml:space="preserve">
-      <c r="A445" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
-0.80 x 1250.0 x 3000.0 mm</v>
-      </c>
-      <c r="B445" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
-0.80 x 1250.0 x 3000.0 mm
-Weight (Kg):695
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-3,395.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="446" xml:space="preserve">
-      <c r="A446" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
-0.80 x 1500.0 x 3000.0 mm</v>
-      </c>
-      <c r="B446" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
-0.80 x 1500.0 x 3000.0 mm
-Weight (Kg):978
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-3,395.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="447" xml:space="preserve">
-      <c r="A447" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
-0.80 x 1500.0 x 3000.0 mm</v>
-      </c>
-      <c r="B447" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
-0.80 x 1500.0 x 3000.0 mm
-Weight (Kg):1,741
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-3,395.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="448" xml:space="preserve">
-      <c r="A448" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
-0.80 x 1500.0 x 3000.0 mm</v>
-      </c>
-      <c r="B448" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
-0.80 x 1500.0 x 3000.0 mm
-Weight (Kg):803
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-3,395.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="449" xml:space="preserve">
-      <c r="A449" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
-0.80 x 1500.0 x 3000.0 mm</v>
-      </c>
-      <c r="B449" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
-0.80 x 1500.0 x 3000.0 mm
-Weight (Kg):1,136
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-3,395.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="450" xml:space="preserve">
-      <c r="A450" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
-0.90 x 1000.0 x 2000.0 mm</v>
-      </c>
-      <c r="B450" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
-0.90 x 1000.0 x 2000.0 mm
-Weight (Kg):576
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-3,395.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="451" xml:space="preserve">
-      <c r="A451" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
-0.90 x 1500.0 x 3000.0 mm</v>
-      </c>
-      <c r="B451" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
-0.90 x 1500.0 x 3000.0 mm
-Weight (Kg):553
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-3,395.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="452" xml:space="preserve">
-      <c r="A452" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
-1.10 x 1500.0 x 3000.0 mm</v>
-      </c>
-      <c r="B452" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
-1.10 x 1500.0 x 3000.0 mm
-Weight (Kg):1,233
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-3,395.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="453" xml:space="preserve">
-      <c r="A453" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
-1.20 x 1250.0 x 2500.0 mm</v>
-      </c>
-      <c r="B453" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
-1.20 x 1250.0 x 2500.0 mm
-Weight (Kg):685
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-3,395.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="454" xml:space="preserve">
-      <c r="A454" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
-1.50 x 1000.0 x 2000.0 mm</v>
-      </c>
-      <c r="B454" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
-1.50 x 1000.0 x 2000.0 mm
-Weight (Kg):598
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-3,395.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="455" xml:space="preserve">
-      <c r="A455" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
-1.50 x 1250.0 x 2500.0 mm</v>
-      </c>
-      <c r="B455" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
-1.50 x 1250.0 x 2500.0 mm
-Weight (Kg):681
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-3,395.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="456" xml:space="preserve">
-      <c r="A456" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
-2.00 x 1000.0 x 2000.0 mm</v>
-      </c>
-      <c r="B456" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
-2.00 x 1000.0 x 2000.0 mm
-Weight (Kg):2,359
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-3,395.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="457" xml:space="preserve">
-      <c r="A457" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
-2.00 x 1000.0 x 2000.0 mm</v>
-      </c>
-      <c r="B457" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
-2.00 x 1000.0 x 2000.0 mm
-Weight (Kg):529
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-3,395.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="458" xml:space="preserve">
-      <c r="A458" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
-2.00 x 1000.0 x 2000.0 mm</v>
-      </c>
-      <c r="B458" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
-2.00 x 1000.0 x 2000.0 mm
-Weight (Kg):889
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-3,395.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="459" xml:space="preserve">
-      <c r="A459" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
-2.00 x 1000.0 x 2000.0 mm</v>
-      </c>
-      <c r="B459" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
-2.00 x 1000.0 x 2000.0 mm
-Weight (Kg):628
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-3,395.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="460" xml:space="preserve">
-      <c r="A460" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
-2.00 x 1000.0 x 2000.0 mm</v>
-      </c>
-      <c r="B460" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
-2.00 x 1000.0 x 2000.0 mm
-Weight (Kg):1,968
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-3,395.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="461" xml:space="preserve">
-      <c r="A461" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
-2.00 x 1250.0 x 2500.0 mm</v>
-      </c>
-      <c r="B461" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
-2.00 x 1250.0 x 2500.0 mm
-Weight (Kg):928
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-3,395.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="462" xml:space="preserve">
-      <c r="A462" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
-2.00 x 1250.0 x 2500.0 mm</v>
-      </c>
-      <c r="B462" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
-2.00 x 1250.0 x 2500.0 mm
-Weight (Kg):816
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-3,395.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="463" xml:space="preserve">
-      <c r="A463" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
-2.00 x 1250.0 x 2500.0 mm</v>
-      </c>
-      <c r="B463" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
-2.00 x 1250.0 x 2500.0 mm
-Weight (Kg):976
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-3,395.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="464" xml:space="preserve">
-      <c r="A464" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
-2.00 x 1250.0 x 2500.0 mm</v>
-      </c>
-      <c r="B464" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
-2.00 x 1250.0 x 2500.0 mm
-Weight (Kg):585
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-3,395.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="465" xml:space="preserve">
-      <c r="A465" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
-2.00 x 1250.0 x 2500.0 mm</v>
-      </c>
-      <c r="B465" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
-2.00 x 1250.0 x 2500.0 mm
-Weight (Kg):1,956
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-3,395.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="466" xml:space="preserve">
-      <c r="A466" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
-2.00 x 1250.0 x 2500.0 mm</v>
-      </c>
-      <c r="B466" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
-2.00 x 1250.0 x 2500.0 mm
-Weight (Kg):1,779
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-3,395.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="467" xml:space="preserve">
-      <c r="A467" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
-2.00 x 1500.0 x 3000.0 mm</v>
-      </c>
-      <c r="B467" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
-2.00 x 1500.0 x 3000.0 mm
-Weight (Kg):693
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-3,395.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="468" xml:space="preserve">
-      <c r="A468" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
-2.00 x 1500.0 x 3000.0 mm</v>
-      </c>
-      <c r="B468" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
-2.00 x 1500.0 x 3000.0 mm
-Weight (Kg):1,122
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-3,395.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="469" xml:space="preserve">
-      <c r="A469" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
-2.00 x 1500.0 x 3000.0 mm</v>
-      </c>
-      <c r="B469" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
-2.00 x 1500.0 x 3000.0 mm
-Weight (Kg):1,108
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-3,395.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="470" xml:space="preserve">
-      <c r="A470" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
-2.00 x 1500.0 x 3000.0 mm</v>
-      </c>
-      <c r="B470" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
-2.00 x 1500.0 x 3000.0 mm
-Weight (Kg):1,836
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-3,395.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="471" xml:space="preserve">
-      <c r="A471" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
-2.00 x 1500.0 x 3000.0 mm</v>
-      </c>
-      <c r="B471" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
-2.00 x 1500.0 x 3000.0 mm
-Weight (Kg):630
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-3,395.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="472" xml:space="preserve">
-      <c r="A472" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
-2.00 x 1500.0 x 3000.0 mm</v>
-      </c>
-      <c r="B472" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
-2.00 x 1500.0 x 3000.0 mm
-Weight (Kg):726
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-3,395.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="473" xml:space="preserve">
-      <c r="A473" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
-2.00 x 1500.0 x 3000.0 mm</v>
-      </c>
-      <c r="B473" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
-2.00 x 1500.0 x 3000.0 mm
-Weight (Kg):565
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-3,395.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="474" xml:space="preserve">
-      <c r="A474" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
-2.00 x 1500.0 x 3000.0 mm</v>
-      </c>
-      <c r="B474" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
-2.00 x 1500.0 x 3000.0 mm
-Weight (Kg):729
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-3,395.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="475" xml:space="preserve">
-      <c r="A475" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
-2.00 x 1500.0 x 3000.0 mm</v>
-      </c>
-      <c r="B475" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
-2.00 x 1500.0 x 3000.0 mm
-Weight (Kg):792
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-3,395.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="476" xml:space="preserve">
-      <c r="A476" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
-2.00 x 1500.0 x 3000.0 mm</v>
-      </c>
-      <c r="B476" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
-2.00 x 1500.0 x 3000.0 mm
-Weight (Kg):637
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-3,395.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="477" xml:space="preserve">
-      <c r="A477" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
-2.00 x 1500.0 x 3000.0 mm</v>
-      </c>
-      <c r="B477" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
-2.00 x 1500.0 x 3000.0 mm
-Weight (Kg):1,289
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-3,395.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="478" xml:space="preserve">
-      <c r="A478" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
-2.50 x 1500.0 x 3000.0 mm</v>
-      </c>
-      <c r="B478" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
-2.50 x 1500.0 x 3000.0 mm
-Weight (Kg):1,826
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-3,395.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="479" xml:space="preserve">
-      <c r="A479" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
-2.50 x 1500.0 x 3000.0 mm</v>
-      </c>
-      <c r="B479" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
-2.50 x 1500.0 x 3000.0 mm
-Weight (Kg):1,040
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-3,395.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="480" xml:space="preserve">
-      <c r="A480" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
-2.50 x 1500.0 x 3000.0 mm</v>
-      </c>
-      <c r="B480" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
-2.50 x 1500.0 x 3000.0 mm
-Weight (Kg):1,328
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-3,395.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="481" xml:space="preserve">
-      <c r="A481" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
-3.00 x 1000.0 x 2000.0 mm</v>
-      </c>
-      <c r="B481" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
-3.00 x 1000.0 x 2000.0 mm
-Weight (Kg):940
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-3,395.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="482" xml:space="preserve">
-      <c r="A482" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
-3.00 x 1250.0 x 2500.0 mm</v>
-      </c>
-      <c r="B482" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
-3.00 x 1250.0 x 2500.0 mm
-Weight (Kg):1,396
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-3,395.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="483" xml:space="preserve">
-      <c r="A483" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
-3.00 x 1250.0 x 2500.0 mm</v>
-      </c>
-      <c r="B483" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
-3.00 x 1250.0 x 2500.0 mm
-Weight (Kg):2,318
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-3,395.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="484" xml:space="preserve">
-      <c r="A484" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
-3.00 x 1250.0 x 2500.0 mm</v>
-      </c>
-      <c r="B484" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
-3.00 x 1250.0 x 2500.0 mm
-Weight (Kg):1,074
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-3,395.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="485" xml:space="preserve">
-      <c r="A485" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
-3.00 x 1250.0 x 2500.0 mm</v>
-      </c>
-      <c r="B485" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
-3.00 x 1250.0 x 2500.0 mm
-Weight (Kg):1,584
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-3,395.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="486" xml:space="preserve">
-      <c r="A486" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
-3.00 x 1250.0 x 2500.0 mm</v>
-      </c>
-      <c r="B486" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
-3.00 x 1250.0 x 2500.0 mm
-Weight (Kg):1,028
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-3,395.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="487" xml:space="preserve">
-      <c r="A487" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
-3.00 x 1250.0 x 2500.0 mm</v>
-      </c>
-      <c r="B487" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
-3.00 x 1250.0 x 2500.0 mm
-Weight (Kg):598
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-3,395.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="488" xml:space="preserve">
-      <c r="A488" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
-3.00 x 1340.0 x 2480.0 mm</v>
-      </c>
-      <c r="B488" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
-3.00 x 1340.0 x 2480.0 mm
-Weight (Kg):1,174
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-3,395.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="489" xml:space="preserve">
-      <c r="A489" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
-3.00 x 1340.0 x 2480.0 mm</v>
-      </c>
-      <c r="B489" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
-3.00 x 1340.0 x 2480.0 mm
-Weight (Kg):1,020
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-3,395.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="490" xml:space="preserve">
-      <c r="A490" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
-3.00 x 1340.0 x 2480.0 mm</v>
-      </c>
-      <c r="B490" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
-3.00 x 1340.0 x 2480.0 mm
-Weight (Kg):1,169
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-3,395.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="491" xml:space="preserve">
-      <c r="A491" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
-3.00 x 1340.0 x 2480.0 mm</v>
-      </c>
-      <c r="B491" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
-3.00 x 1340.0 x 2480.0 mm
-Weight (Kg):1,951
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-3,395.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="492" xml:space="preserve">
-      <c r="A492" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
-5.00 x 1000.0 x 2000.0 mm</v>
-      </c>
-      <c r="B492" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
-5.00 x 1000.0 x 2000.0 mm
-Weight (Kg):943
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-3,395.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="493" xml:space="preserve">
-      <c r="A493" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
-5.00 x 1000.0 x 2000.0 mm</v>
-      </c>
-      <c r="B493" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
-5.00 x 1000.0 x 2000.0 mm
-Weight (Kg):947
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-3,395.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="494" xml:space="preserve">
-      <c r="A494" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
-5.00 x 1000.0 x 2000.0 mm</v>
-      </c>
-      <c r="B494" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
-5.00 x 1000.0 x 2000.0 mm
-Weight (Kg):1,588
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-3,395.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="495" xml:space="preserve">
-      <c r="A495" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
-5.00 x 1250.0 x 2500.0 mm</v>
-      </c>
-      <c r="B495" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
-5.00 x 1250.0 x 2500.0 mm
-Weight (Kg):742
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-3,395.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="496" xml:space="preserve">
-      <c r="A496" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
-6.00 x 1000.0 x 2000.0 mm</v>
-      </c>
-      <c r="B496" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
-6.00 x 1000.0 x 2000.0 mm
-Weight (Kg):1,452
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-3,395.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="497" xml:space="preserve">
-      <c r="A497" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
-6.00 x 1000.0 x 2000.0 mm</v>
-      </c>
-      <c r="B497" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
-6.00 x 1000.0 x 2000.0 mm
-Weight (Kg):1,624
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-3,395.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="498" xml:space="preserve">
-      <c r="A498" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
-6.00 x 1000.0 x 2000.0 mm</v>
-      </c>
-      <c r="B498" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
-6.00 x 1000.0 x 2000.0 mm
-Weight (Kg):1,434
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-3,395.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="499" xml:space="preserve">
-      <c r="A499" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
-6.00 x 1000.0 x 2000.0 mm</v>
-      </c>
-      <c r="B499" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
-6.00 x 1000.0 x 2000.0 mm
-Weight (Kg):580
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-3,395.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="500" xml:space="preserve">
-      <c r="A500" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
-6.00 x 1000.0 x 2000.0 mm</v>
-      </c>
-      <c r="B500" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
-6.00 x 1000.0 x 2000.0 mm
-Weight (Kg):1,054
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-3,395.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="501" xml:space="preserve">
-      <c r="A501" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
-6.00 x 1000.0 x 2000.0 mm</v>
-      </c>
-      <c r="B501" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
-6.00 x 1000.0 x 2000.0 mm
-Weight (Kg):1,716
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-3,395.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="502" xml:space="preserve">
-      <c r="A502" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
-6.00 x 1000.0 x 2000.0 mm</v>
-      </c>
-      <c r="B502" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
-6.00 x 1000.0 x 2000.0 mm
-Weight (Kg):1,148
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-3,395.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="503" xml:space="preserve">
-      <c r="A503" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
-6.00 x 1000.0 x 2000.0 mm</v>
-      </c>
-      <c r="B503" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
-6.00 x 1000.0 x 2000.0 mm
-Weight (Kg):960
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-3,395.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="504" xml:space="preserve">
-      <c r="A504" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
-6.00 x 1000.0 x 2000.0 mm</v>
-      </c>
-      <c r="B504" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
-6.00 x 1000.0 x 2000.0 mm
-Weight (Kg):772
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-3,395.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="505" xml:space="preserve">
-      <c r="A505" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
-6.00 x 1500.0 x 3000.0 mm</v>
-      </c>
-      <c r="B505" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
-6.00 x 1500.0 x 3000.0 mm
-Weight (Kg):2,146
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-3,395.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="506" xml:space="preserve">
-      <c r="A506" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
-6.00 x 1500.0 x 3000.0 mm</v>
-      </c>
-      <c r="B506" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
-6.00 x 1500.0 x 3000.0 mm
-Weight (Kg):1,994
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-3,395.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="507" xml:space="preserve">
-      <c r="A507" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
-6.00 x 1500.0 x 3000.0 mm</v>
-      </c>
-      <c r="B507" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
-6.00 x 1500.0 x 3000.0 mm
-Weight (Kg):1,488
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-3,395.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="508" xml:space="preserve">
-      <c r="A508" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
-6.00 x 1500.0 x 3000.0 mm</v>
-      </c>
-      <c r="B508" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
-6.00 x 1500.0 x 3000.0 mm
-Weight (Kg):1,278
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-3,395.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="509" xml:space="preserve">
-      <c r="A509" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
-6.00 x 1500.0 x 3000.0 mm</v>
-      </c>
-      <c r="B509" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
-6.00 x 1500.0 x 3000.0 mm
-Weight (Kg):1,062
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-3,395.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="510" xml:space="preserve">
-      <c r="A510" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
-6.00 x 1500.0 x 3000.0 mm</v>
-      </c>
-      <c r="B510" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
-6.00 x 1500.0 x 3000.0 mm
-Weight (Kg):1,526
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-3,395.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="511" xml:space="preserve">
-      <c r="A511" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
-6.00 x 1500.0 x 3000.0 mm</v>
-      </c>
-      <c r="B511" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
-6.00 x 1500.0 x 3000.0 mm
-Weight (Kg):1,280
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-3,395.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="512" xml:space="preserve">
-      <c r="A512" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
-6.00 x 1510.0 x 3010.0 mm</v>
-      </c>
-      <c r="B512" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
-6.00 x 1510.0 x 3010.0 mm
-Weight (Kg):1,986
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-3,395.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="513" xml:space="preserve">
-      <c r="A513" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
-6.00 x 1510.0 x 3010.0 mm</v>
-      </c>
-      <c r="B513" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
-6.00 x 1510.0 x 3010.0 mm
-Weight (Kg):1,784
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-3,395.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="514" xml:space="preserve">
-      <c r="A514" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, Nb. 1,
-6.00 x 1000.0 x 2000.0 mm</v>
-      </c>
-      <c r="B514" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, Nb. 1,
-6.00 x 1000.0 x 2000.0 mm
-Weight (Kg):570
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-3,395.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="515" xml:space="preserve">
-      <c r="A515" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, SB-G-400,
-1.50 x 1500.0 x 3000.0 mm</v>
-      </c>
-      <c r="B515" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, SB-G-400,
-1.50 x 1500.0 x 3000.0 mm
-Weight (Kg):723
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-3,395.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="516" xml:space="preserve">
-      <c r="A516" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, SB-G-400,
-2.00 x 1500.0 x 3000.0 mm</v>
-      </c>
-      <c r="B516" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, SB-G-400,
-2.00 x 1500.0 x 3000.0 mm
-Weight (Kg):819
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-3,395.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="517" xml:space="preserve">
-      <c r="A517" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, SB-G-400,
-2.00 x 1500.0 x 3000.0 mm</v>
-      </c>
-      <c r="B517" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, SB-G-400,
-2.00 x 1500.0 x 3000.0 mm
-Weight (Kg):1,935
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-3,395.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="518" xml:space="preserve">
-      <c r="A518" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Untrimmed, Coil, 2B,
-1.20 x 1537.0 x coil mm</v>
-      </c>
-      <c r="B518" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Untrimmed, Coil, 2B,
-1.20 x 1537.0 x coil mm
-Weight (Kg):2,125
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-3,395.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="519" xml:space="preserve">
-      <c r="A519" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Untrimmed, Coil, 2B,
-1.80 x 1530.0 x coil mm</v>
-      </c>
-      <c r="B519" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Untrimmed, Coil, 2B,
-1.80 x 1530.0 x coil mm
-Weight (Kg):5,263
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-3,395.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="520" xml:space="preserve">
-      <c r="A520" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Untrimmed, Coil, 2B,
-1.80 x 1535.0 x coil mm</v>
-      </c>
-      <c r="B520" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Untrimmed, Coil, 2B,
-1.80 x 1535.0 x coil mm
-Weight (Kg):2,726
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-3,395.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="521" xml:space="preserve">
-      <c r="A521" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Untrimmed, Coil, 2B,
-2.00 x 1023.0 x coil mm</v>
-      </c>
-      <c r="B521" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Untrimmed, Coil, 2B,
-2.00 x 1023.0 x coil mm
-Weight (Kg):1,825
-Quality:Prime
-Help
-Location:FABRICA ALGECIRAS
-3,595.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="522" xml:space="preserve">
-      <c r="A522" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Untrimmed, Coil, 2B,
-3.00 x 1552.0 x coil mm</v>
-      </c>
-      <c r="B522" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Untrimmed, Coil, 2B,
-3.00 x 1552.0 x coil mm
-Weight (Kg):2,868
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-3,395.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="523" xml:space="preserve">
-      <c r="A523" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Untrimmed, Coil, 2B,
-6.00 x 1030.0 x coil mm</v>
-      </c>
-      <c r="B523" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Untrimmed, Coil, 2B,
-6.00 x 1030.0 x coil mm
-Weight (Kg):2,225
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-3,395.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="524" xml:space="preserve">
-      <c r="A524" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4571 316Ti-Coil, 2B,
-4.00 x 210.0 x coil mm</v>
-      </c>
-      <c r="B524" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4571 316Ti-Coil, 2B,
-4.00 x 210.0 x coil mm
-Weight (Kg):3,817
-Quality:Prime
-Help
-Location:FABRICA ALGECIRAS
-3,370.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="525" xml:space="preserve">
-      <c r="A525" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4571 316Ti-Coil, Nb. 1,
-3.00 x 184.0 x coil mm</v>
-      </c>
-      <c r="B525" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4571 316Ti-Coil, Nb. 1,
-3.00 x 184.0 x coil mm
-Weight (Kg):1,794
-Quality:Prime
-Help
-Location:FABRICA ALGECIRAS
-3,270.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="526" xml:space="preserve">
-      <c r="A526" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4571 316Ti-Coil, Nb. 1,
-3.00 x 184.0 x coil mm</v>
-      </c>
-      <c r="B526" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4571 316Ti-Coil, Nb. 1,
-3.00 x 184.0 x coil mm
-Weight (Kg):1,806
-Quality:Prime
-Help
-Location:FABRICA ALGECIRAS
-3,270.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="527" xml:space="preserve">
-      <c r="A527" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4571 316Ti-Coil, Nb. 1,
-3.00 x 184.0 x coil mm</v>
-      </c>
-      <c r="B527" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4571 316Ti-Coil, Nb. 1,
-3.00 x 184.0 x coil mm
-Weight (Kg):1,808
-Quality:Prime
-Help
-Location:FABRICA ALGECIRAS
-3,270.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="528" xml:space="preserve">
-      <c r="A528" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4571 316Ti-Coil, Nb. 1,
-4.00 x 200.0 x coil mm</v>
-      </c>
-      <c r="B528" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4571 316Ti-Coil, Nb. 1,
-4.00 x 200.0 x coil mm
-Weight (Kg):1,918
-Quality:Prime
-Help
-Location:FABRICA ALGECIRAS
-3,270.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="529" xml:space="preserve">
-      <c r="A529" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4571 316Ti-Plate, Nb. 1,
-45.00 x 1500.0 x 3000.0 mm</v>
-      </c>
-      <c r="B529" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4571 316Ti-Plate, Nb. 1,
-45.00 x 1500.0 x 3000.0 mm
-Weight (Kg):1,640
-Quality:Prime
-Help
-Location:FABRICA ALGECIRAS
-4,600.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="530" xml:space="preserve">
-      <c r="A530" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4571 316Ti-Sheet, 2B,
-3.00 x 1000.0 x 2000.0 mm</v>
-      </c>
-      <c r="B530" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4571 316Ti-Sheet, 2B,
-3.00 x 1000.0 x 2000.0 mm
-Weight (Kg):918
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-3,495.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="531" xml:space="preserve">
-      <c r="A531" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4571 316Ti-Sheet, 2B,
-3.00 x 1000.0 x 2000.0 mm</v>
-      </c>
-      <c r="B531" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4571 316Ti-Sheet, 2B,
-3.00 x 1000.0 x 2000.0 mm
-Weight (Kg):518
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-3,495.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="532" xml:space="preserve">
-      <c r="A532" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4571 316Ti-Sheet, 2B,
-3.00 x 1000.0 x 2000.0 mm</v>
-      </c>
-      <c r="B532" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4571 316Ti-Sheet, 2B,
-3.00 x 1000.0 x 2000.0 mm
-Weight (Kg):848
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-3,495.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="533" xml:space="preserve">
-      <c r="A533" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4571 316Ti-Sheet, 2B,
-5.00 x 1000.0 x 2000.0 mm</v>
-      </c>
-      <c r="B533" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4571 316Ti-Sheet, 2B,
-5.00 x 1000.0 x 2000.0 mm
-Weight (Kg):1,102
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-3,495.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="534" xml:space="preserve">
-      <c r="A534" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4571 316Ti-Sheet, 2B,
-6.00 x 1000.0 x 2000.0 mm</v>
-      </c>
-      <c r="B534" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4571 316Ti-Sheet, 2B,
-6.00 x 1000.0 x 2000.0 mm
-Weight (Kg):1,050
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-3,495.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="535" xml:space="preserve">
-      <c r="A535" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4571 316Ti-Sheet, 2B,
-6.00 x 1000.0 x 2000.0 mm</v>
-      </c>
-      <c r="B535" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4571 316Ti-Sheet, 2B,
-6.00 x 1000.0 x 2000.0 mm
-Weight (Kg):952
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-3,495.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="536" xml:space="preserve">
-      <c r="A536" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4571 316Ti-Sheet, Nb. 1,
-8.00 x 1500.0 x 3000.0 mm</v>
-      </c>
-      <c r="B536" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4571 316Ti-Sheet, Nb. 1,
-8.00 x 1500.0 x 3000.0 mm
-Weight (Kg):1,136
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-3,495.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="537" xml:space="preserve">
-      <c r="A537" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4541 321-Coil, 2B,
-1.90 x 217.0 x coil mm</v>
-      </c>
-      <c r="B537" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4541 321-Coil, 2B,
-1.90 x 217.0 x coil mm
-Weight (Kg):3,537
-Quality:Prime
-Help
-Location:FABRICA ALGECIRAS
-2,235.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="538" xml:space="preserve">
-      <c r="A538" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4541 321-Coil, 2B,
-1.90 x 217.0 x coil mm</v>
-      </c>
-      <c r="B538" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4541 321-Coil, 2B,
-1.90 x 217.0 x coil mm
-Weight (Kg):3,484
-Quality:Prime
-Help
-Location:FABRICA ALGECIRAS
-2,235.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="539" xml:space="preserve">
-      <c r="A539" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4541 321-Coil, 2B,
-1.90 x 217.0 x coil mm</v>
-      </c>
-      <c r="B539" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4541 321-Coil, 2B,
-1.90 x 217.0 x coil mm
-Weight (Kg):3,537
-Quality:Prime
-Help
-Location:FABRICA ALGECIRAS
-2,235.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="540" xml:space="preserve">
-      <c r="A540" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4541 321-Coil, 2B,
-1.90 x 217.0 x coil mm</v>
-      </c>
-      <c r="B540" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4541 321-Coil, 2B,
-1.90 x 217.0 x coil mm
-Weight (Kg):3,490
-Quality:Prime
-Help
-Location:FABRICA ALGECIRAS
-2,235.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="541" xml:space="preserve">
-      <c r="A541" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Untrimmed, Coil, 2B,
-2.00 x 1532.0 x coil mm</v>
-      </c>
-      <c r="B541" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Untrimmed, Coil, 2B,
-2.00 x 1532.0 x coil mm
-Weight (Kg):2,540
-Quality:Prime
-Help
-Location:FABRICA ALGECIRAS
-3,595.00 €/ton
-Reserved</v>
-      </c>
-    </row>
-    <row r="542" xml:space="preserve">
-      <c r="A542" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4541 321-Coil, 2B,
-1.90 x 217.0 x coil mm</v>
-      </c>
-      <c r="B542" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4541 321-Coil, 2B,
-1.90 x 217.0 x coil mm
-Weight (Kg):3,537
-Quality:Prime
-Help
-Location:FABRICA ALGECIRAS
-2,235.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="543" xml:space="preserve">
-      <c r="A543" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4541 321-Coil, 2B,
-1.90 x 217.0 x coil mm</v>
-      </c>
-      <c r="B543" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4541 321-Coil, 2B,
-1.90 x 217.0 x coil mm
-Weight (Kg):3,492
-Quality:Prime
-Help
-Location:FABRICA ALGECIRAS
-2,235.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="544" xml:space="preserve">
-      <c r="A544" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4541 321-Coil, 2B,
-1.90 x 217.0 x coil mm</v>
-      </c>
-      <c r="B544" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4541 321-Coil, 2B,
-1.90 x 217.0 x coil mm
-Weight (Kg):3,480
-Quality:Prime
-Help
-Location:FABRICA ALGECIRAS
-2,235.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="545" xml:space="preserve">
-      <c r="A545" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4541 321-Coil, 2B,
-4.00 x 520.0 x coil mm</v>
-      </c>
-      <c r="B545" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4541 321-Coil, 2B,
-4.00 x 520.0 x coil mm
-Weight (Kg):7,263
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-2,285.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="546" xml:space="preserve">
-      <c r="A546" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4541 321-Coil, Nb. 1,
-5.00 x 1542.0 x coil mm</v>
-      </c>
-      <c r="B546" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4541 321-Coil, Nb. 1,
-5.00 x 1542.0 x coil mm
-Weight (Kg):4,890
-Quality:Prime
-Help
-Location:FABRICA ALGECIRAS
-2,875.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="547" xml:space="preserve">
-      <c r="A547" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4541 321-Coil, Nb. 1,
-5.00 x 230.9 x coil mm</v>
-      </c>
-      <c r="B547" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4541 321-Coil, Nb. 1,
-5.00 x 230.9 x coil mm
-Weight (Kg):4,198
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-2,135.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="548" xml:space="preserve">
-      <c r="A548" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4541 321-Sheet, 2B,
-3.00 x 1000.0 x 2000.0 mm</v>
-      </c>
-      <c r="B548" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4541 321-Sheet, 2B,
-3.00 x 1000.0 x 2000.0 mm
-Weight (Kg):1,104
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-2,385.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="549" xml:space="preserve">
-      <c r="A549" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4541 321-Sheet, 2B,
-4.00 x 1000.0 x 2000.0 mm</v>
-      </c>
-      <c r="B549" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4541 321-Sheet, 2B,
-4.00 x 1000.0 x 2000.0 mm
-Weight (Kg):1,552
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-2,385.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="550" xml:space="preserve">
-      <c r="A550" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4541 321-Sheet, 2B,
-6.00 x 1250.0 x 2500.0 mm</v>
-      </c>
-      <c r="B550" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4541 321-Sheet, 2B,
-6.00 x 1250.0 x 2500.0 mm
-Weight (Kg):1,296
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-2,385.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="551" xml:space="preserve">
-      <c r="A551" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4541 321-Sheet, Nb. 1,
-8.00 x 1000.0 x 2000.0 mm</v>
-      </c>
-      <c r="B551" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4541 321-Sheet, Nb. 1,
-8.00 x 1000.0 x 2000.0 mm
-Weight (Kg):640
-Quality:Prime
-Help
-Location:FABRICA ALGECIRAS
-3,350.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="552" xml:space="preserve">
-      <c r="A552" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4512 409L-Coil, 2B,
-1.00 x 1304.0 x coil mm</v>
-      </c>
-      <c r="B552" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4512 409L-Coil, 2B,
-1.00 x 1304.0 x coil mm
-Weight (Kg):10,360
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-1,125.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="553" xml:space="preserve">
-      <c r="A553" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4512 409L-Coil, 2B,
-1.00 x 625.0 x coil mm</v>
-      </c>
-      <c r="B553" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4512 409L-Coil, 2B,
-1.00 x 625.0 x coil mm
-Weight (Kg):6,700
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-1,025.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="554" xml:space="preserve">
-      <c r="A554" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4512 409L-Coil, 2D,
-2.00 x 1291.0 x coil mm</v>
-      </c>
-      <c r="B554" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4512 409L-Coil, 2D,
-2.00 x 1291.0 x coil mm
-Weight (Kg):3,579
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-1,125.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="555" xml:space="preserve">
-      <c r="A555" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4512 409L-Coil, 2D,
-2.00 x 150.0 x coil mm</v>
-      </c>
-      <c r="B555" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4512 409L-Coil, 2D,
-2.00 x 150.0 x coil mm
-Weight (Kg):2,270
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-1,000.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="556" xml:space="preserve">
-      <c r="A556" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4512 409L-Coil, Nb. 1,
-4.00 x 140.0 x coil mm</v>
-      </c>
-      <c r="B556" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4512 409L-Coil, Nb. 1,
-4.00 x 140.0 x coil mm
-Weight (Kg):2,354
-Quality:Prime
-Help
-Location:FABRICA ALGECIRAS
-900.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="557" xml:space="preserve">
-      <c r="A557" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4512 409L-Coil, Nb. 1,
-5.00 x 190.0 x coil mm</v>
-      </c>
-      <c r="B557" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4512 409L-Coil, Nb. 1,
-5.00 x 190.0 x coil mm
-Weight (Kg):2,447
-Quality:Prime
-Help
-Location:FABRICA ALGECIRAS
-900.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="558" xml:space="preserve">
-      <c r="A558" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4512 409L-Coil, Nb. 1,
-6.00 x 270.0 x coil mm</v>
-      </c>
-      <c r="B558" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4512 409L-Coil, Nb. 1,
-6.00 x 270.0 x coil mm
-Weight (Kg):2,116
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-900.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="559" xml:space="preserve">
-      <c r="A559" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4512 409L-Coil, Nb. 1,
-6.00 x 270.0 x coil mm</v>
-      </c>
-      <c r="B559" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4512 409L-Coil, Nb. 1,
-6.00 x 270.0 x coil mm
-Weight (Kg):1,780
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-900.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="560" xml:space="preserve">
-      <c r="A560" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4512 409L-Coil, Nb. 1,
-8.00 x 115.9 x coil mm</v>
-      </c>
-      <c r="B560" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4512 409L-Coil, Nb. 1,
-8.00 x 115.9 x coil mm
-Weight (Kg):1,238
-Quality:Prime
-Help
-Location:FABRICA ALGECIRAS
-900.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="561" xml:space="preserve">
-      <c r="A561" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4512 409L-Coil, Nb. 1,
-8.00 x 125.9 x coil mm</v>
-      </c>
-      <c r="B561" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4512 409L-Coil, Nb. 1,
-8.00 x 125.9 x coil mm
-Weight (Kg):1,214
-Quality:Prime
-Help
-Location:FABRICA ALGECIRAS
-900.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="562" xml:space="preserve">
-      <c r="A562" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4512 409L-Coil, Nb. 1,
-8.00 x 230.9 x coil mm</v>
-      </c>
-      <c r="B562" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4512 409L-Coil, Nb. 1,
-8.00 x 230.9 x coil mm
-Weight (Kg):2,960
-Quality:Prime
-Help
-Location:FABRICA ALGECIRAS
-900.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="563" xml:space="preserve">
-      <c r="A563" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4512 409L-Untrimmed, Coil, 2B,
-1.00 x 625.0 x coil mm</v>
-      </c>
-      <c r="B563" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4512 409L-Untrimmed, Coil, 2B,
-1.00 x 625.0 x coil mm
-Weight (Kg):3,441
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-1,025.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="564" xml:space="preserve">
-      <c r="A564" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4512 409L-Untrimmed, Coil, 2D,
-1.50 x 1295.0 x coil mm</v>
-      </c>
-      <c r="B564" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4512 409L-Untrimmed, Coil, 2D,
-1.50 x 1295.0 x coil mm
-Weight (Kg):2,445
-Quality:Prime
-Help
-Location:FABRICA ALGECIRAS
-1,325.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="565" xml:space="preserve">
-      <c r="A565" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, 2B,
-0.70 x 299.9 x coil mm</v>
-      </c>
-      <c r="B565" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, 2B,
-0.70 x 299.9 x coil mm
-Weight (Kg):2,518
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-1,000.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="566" xml:space="preserve">
-      <c r="A566" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, 2B,
-2.00 x 220.0 x coil mm</v>
-      </c>
-      <c r="B566" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, 2B,
-2.00 x 220.0 x coil mm
-Weight (Kg):776
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-1,000.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="567" xml:space="preserve">
-      <c r="A567" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, 2D,
-0.50 x 1518.0 x coil mm</v>
-      </c>
-      <c r="B567" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, 2D,
-0.50 x 1518.0 x coil mm
-Weight (Kg):4,480
-Quality:Prime
-Help
-Location:FABRICA ALGECIRAS
-1,325.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="568" xml:space="preserve">
-      <c r="A568" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, 2D,
-0.70 x 1007.0 x coil mm</v>
-      </c>
-      <c r="B568" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, 2D,
-0.70 x 1007.0 x coil mm
-Weight (Kg):14,970
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-1,125.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="569" xml:space="preserve">
-      <c r="A569" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, 2D,
-0.70 x 1450.0 x coil mm</v>
-      </c>
-      <c r="B569" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, 2D,
-0.70 x 1450.0 x coil mm
-Weight (Kg):4,780
-Quality:Prime
-Help
-Location:FABRICA ALGECIRAS
-1,325.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="570" xml:space="preserve">
-      <c r="A570" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, 2D,
-0.70 x 869.0 x coil mm</v>
-      </c>
-      <c r="B570" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, 2D,
-0.70 x 869.0 x coil mm
-Weight (Kg):13,570
-Quality:Prime
-Help
-Location:FABRICA ALGECIRAS
-1,900.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="571" xml:space="preserve">
-      <c r="A571" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, BA,
-0.60 x 310.0 x coil mm</v>
-      </c>
-      <c r="B571" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, BA,
-0.60 x 310.0 x coil mm
-Weight (Kg):786
-Quality:Prime
-Help
-Location:FABRICA ALGECIRAS
-1,000.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="572" xml:space="preserve">
-      <c r="A572" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, BA,
-0.70 x 100.9 x coil mm</v>
-      </c>
-      <c r="B572" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, BA,
-0.70 x 100.9 x coil mm
-Weight (Kg):778
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-1,000.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="573" xml:space="preserve">
-      <c r="A573" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, BA,
-0.70 x 110.9 x coil mm</v>
-      </c>
-      <c r="B573" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, BA,
-0.70 x 110.9 x coil mm
-Weight (Kg):634
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-1,000.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="574" xml:space="preserve">
-      <c r="A574" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, BA,
-0.70 x 110.9 x coil mm</v>
-      </c>
-      <c r="B574" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, BA,
-0.70 x 110.9 x coil mm
-Weight (Kg):658
-Quality:Prime
-Help
-Location:FABRICA ALGECIRAS
-1,000.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="575" xml:space="preserve">
-      <c r="A575" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, BA,
-0.40 x 474.0 x coil mm</v>
-      </c>
-      <c r="B575" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, BA,
-0.40 x 474.0 x coil mm
-Weight (Kg):2,997
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-1,050.00 €/ton
-Out of Stock</v>
-      </c>
-    </row>
-    <row r="576" xml:space="preserve">
-      <c r="A576" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, BA,
-0.40 x 596.2 x coil mm</v>
-      </c>
-      <c r="B576" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, BA,
-0.40 x 596.2 x coil mm
-Weight (Kg):4,288
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-1,050.00 €/ton
-Out of Stock</v>
-      </c>
-    </row>
-    <row r="577" xml:space="preserve">
-      <c r="A577" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, BA,
-0.40 x 596.2 x coil mm</v>
-      </c>
-      <c r="B577" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, BA,
-0.40 x 596.2 x coil mm
-Weight (Kg):2,150
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-1,050.00 €/ton
-Out of Stock</v>
-      </c>
-    </row>
-    <row r="578" xml:space="preserve">
-      <c r="A578" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, BA,
-0.40 x 596.2 x coil mm</v>
-      </c>
-      <c r="B578" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, BA,
-0.40 x 596.2 x coil mm
-Weight (Kg):4,371
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-1,050.00 €/ton
-Out of Stock</v>
-      </c>
-    </row>
-    <row r="579" xml:space="preserve">
-      <c r="A579" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, BA,
-0.50 x 114.0 x coil mm</v>
-      </c>
-      <c r="B579" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, BA,
-0.50 x 114.0 x coil mm
-Weight (Kg):1,225
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-1,000.00 €/ton
-Reserved</v>
-      </c>
-    </row>
-    <row r="580" xml:space="preserve">
-      <c r="A580" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, BA,
-0.60 x 340.0 x coil mm</v>
-      </c>
-      <c r="B580" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, BA,
-0.60 x 340.0 x coil mm
-Weight (Kg):4,383
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-1,000.00 €/ton
-Reserved</v>
-      </c>
-    </row>
-    <row r="581" xml:space="preserve">
-      <c r="A581" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, BA,
-0.60 x 440.0 x coil mm</v>
-      </c>
-      <c r="B581" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, BA,
-0.60 x 440.0 x coil mm
-Weight (Kg):5,670
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-1,000.00 €/ton
-Reserved</v>
-      </c>
-    </row>
-    <row r="582" xml:space="preserve">
-      <c r="A582" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, BA,
-0.70 x 120.0 x coil mm</v>
-      </c>
-      <c r="B582" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, BA,
-0.70 x 120.0 x coil mm
-Weight (Kg):836
-Quality:Prime
-Help
-Location:FABRICA ALGECIRAS
-1,000.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="583" xml:space="preserve">
-      <c r="A583" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, BA,
-0.70 x 125.0 x coil mm</v>
-      </c>
-      <c r="B583" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, BA,
-0.70 x 125.0 x coil mm
-Weight (Kg):1,288
-Quality:Prime
-Help
-Location:FABRICA ALGECIRAS
-1,000.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="584" xml:space="preserve">
-      <c r="A584" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, BA,
-0.70 x 125.9 x coil mm</v>
-      </c>
-      <c r="B584" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, BA,
-0.70 x 125.9 x coil mm
-Weight (Kg):708
-Quality:Prime
-Help
-Location:FABRICA ALGECIRAS
-1,000.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="585" xml:space="preserve">
-      <c r="A585" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, BA,
-0.70 x 126.0 x coil mm</v>
-      </c>
-      <c r="B585" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, BA,
-0.70 x 126.0 x coil mm
-Weight (Kg):804
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-1,000.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="586" xml:space="preserve">
-      <c r="A586" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, BA,
-0.70 x 155.9 x coil mm</v>
-      </c>
-      <c r="B586" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, BA,
-0.70 x 155.9 x coil mm
-Weight (Kg):1,148
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-1,000.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="587" xml:space="preserve">
-      <c r="A587" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, BA,
-0.70 x 175.9 x coil mm</v>
-      </c>
-      <c r="B587" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, BA,
-0.70 x 175.9 x coil mm
-Weight (Kg):944
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-1,000.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="588" xml:space="preserve">
-      <c r="A588" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, BA,
-0.70 x 175.9 x coil mm</v>
-      </c>
-      <c r="B588" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, BA,
-0.70 x 175.9 x coil mm
-Weight (Kg):1,054
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-1,000.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="589" xml:space="preserve">
-      <c r="A589" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, BA,
-0.70 x 181.9 x coil mm</v>
-      </c>
-      <c r="B589" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, BA,
-0.70 x 181.9 x coil mm
-Weight (Kg):1,632
-Quality:Prime
-Help
-Location:FABRICA ALGECIRAS
-1,000.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="590" xml:space="preserve">
-      <c r="A590" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, BA,
-0.70 x 195.9 x coil mm</v>
-      </c>
-      <c r="B590" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, BA,
-0.70 x 195.9 x coil mm
-Weight (Kg):1,174
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-1,000.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="591" xml:space="preserve">
-      <c r="A591" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, BA,
-0.70 x 195.9 x coil mm</v>
-      </c>
-      <c r="B591" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, BA,
-0.70 x 195.9 x coil mm
-Weight (Kg):1,541
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-1,000.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="592" xml:space="preserve">
-      <c r="A592" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, BA,
-0.70 x 200.9 x coil mm</v>
-      </c>
-      <c r="B592" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, BA,
-0.70 x 200.9 x coil mm
-Weight (Kg):1,098
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-1,000.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="593" xml:space="preserve">
-      <c r="A593" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, BA,
-0.70 x 260.9 x coil mm</v>
-      </c>
-      <c r="B593" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, BA,
-0.70 x 260.9 x coil mm
-Weight (Kg):2,121
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-1,000.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="594" xml:space="preserve">
-      <c r="A594" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, BA,
-0.70 x 825.0 x coil mm</v>
-      </c>
-      <c r="B594" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, BA,
-0.70 x 825.0 x coil mm
-Weight (Kg):5,270
-Quality:Prime
-Help
-Location:FABRICA ALGECIRAS
-1,325.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="595" xml:space="preserve">
-      <c r="A595" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, BA,
-0.70 x 842.0 x coil mm</v>
-      </c>
-      <c r="B595" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, BA,
-0.70 x 842.0 x coil mm
-Weight (Kg):10,370
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-1,125.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="596" xml:space="preserve">
-      <c r="A596" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, BA,
-0.70 x 855.0 x coil mm</v>
-      </c>
-      <c r="B596" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, BA,
-0.70 x 855.0 x coil mm
-Weight (Kg):3,990
-Quality:Prime
-Help
-Location:FABRICA ALGECIRAS
-1,325.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="597" xml:space="preserve">
-      <c r="A597" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, BA,
-0.70 x 870.0 x coil mm</v>
-      </c>
-      <c r="B597" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, BA,
-0.70 x 870.0 x coil mm
-Weight (Kg):13,910
-Quality:Prime
-Help
-Location:FABRICA ALGECIRAS
-1,900.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="598" xml:space="preserve">
-      <c r="A598" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, BA,
-0.70 x 953.0 x coil mm</v>
-      </c>
-      <c r="B598" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, BA,
-0.70 x 953.0 x coil mm
-Weight (Kg):6,970
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-1,125.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="599" xml:space="preserve">
-      <c r="A599" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, BA,
-1.00 x 530.0 x coil mm</v>
-      </c>
-      <c r="B599" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, BA,
-1.00 x 530.0 x coil mm
-Weight (Kg):880
-Quality:Downgraded
-Help
-Location:FABRICA ALGECIRAS
-975.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="600" xml:space="preserve">
-      <c r="A600" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, Polished N4-G-180,
-0.90 x 1250.0 x coil mm</v>
-      </c>
-      <c r="B600" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, Polished N4-G-180,
-0.90 x 1250.0 x coil mm
-Weight (Kg):2,218
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-1,125.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="601" xml:space="preserve">
-      <c r="A601" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, BA,
-0.70 x 825.0 x coil mm</v>
-      </c>
-      <c r="B601" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, BA,
-0.70 x 825.0 x coil mm
-Weight (Kg):6,340
-Quality:Prime
-Help
-Location:FABRICA ALGECIRAS
-1,325.00 €/ton
-Reserved</v>
-      </c>
-    </row>
-    <row r="602" xml:space="preserve">
-      <c r="A602" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, Polished N4-G-180,
-1.20 x 120.0 x coil mm</v>
-      </c>
-      <c r="B602" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, Polished N4-G-180,
-1.20 x 120.0 x coil mm
-Weight (Kg):1,430
-Quality:Prime
-Help
-Location:FABRICA ALGECIRAS
-1,000.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="603" xml:space="preserve">
-      <c r="A603" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, Polished N4-G-180,
-1.20 x 250.0 x coil mm</v>
-      </c>
-      <c r="B603" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, Polished N4-G-180,
-1.20 x 250.0 x coil mm
-Weight (Kg):1,902
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-1,000.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="604" xml:space="preserve">
-      <c r="A604" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, Polished N4-G-180,
-1.20 x 250.9 x coil mm</v>
-      </c>
-      <c r="B604" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, Polished N4-G-180,
-1.20 x 250.9 x coil mm
-Weight (Kg):1,960
-Quality:Prime
-Help
-Location:FABRICA ALGECIRAS
-1,000.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="605" xml:space="preserve">
-      <c r="A605" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, Polished N4-G-180,
-1.20 x 250.9 x coil mm</v>
-      </c>
-      <c r="B605" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, Polished N4-G-180,
-1.20 x 250.9 x coil mm
-Weight (Kg):1,918
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-1,000.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="606" xml:space="preserve">
-      <c r="A606" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, Polished N4-G-180,
-1.20 x 260.9 x coil mm</v>
-      </c>
-      <c r="B606" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, Polished N4-G-180,
-1.20 x 260.9 x coil mm
-Weight (Kg):1,524
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-1,000.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="607" xml:space="preserve">
-      <c r="A607" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, Polished N4-G-180,
-1.20 x 260.9 x coil mm</v>
-      </c>
-      <c r="B607" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, Polished N4-G-180,
-1.20 x 260.9 x coil mm
-Weight (Kg):1,934
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-1,000.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="608" xml:space="preserve">
-      <c r="A608" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, SB-G-400,
-0.60 x 134.9 x coil mm</v>
-      </c>
-      <c r="B608" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, SB-G-400,
-0.60 x 134.9 x coil mm
-Weight (Kg):1,134
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-1,000.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="609" xml:space="preserve">
-      <c r="A609" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, SB-G-400,
-0.60 x 134.9 x coil mm</v>
-      </c>
-      <c r="B609" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, SB-G-400,
-0.60 x 134.9 x coil mm
-Weight (Kg):962
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-1,000.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="610" xml:space="preserve">
-      <c r="A610" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, SB-G-400,
-0.60 x 245.9 x coil mm</v>
-      </c>
-      <c r="B610" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, SB-G-400,
-0.60 x 245.9 x coil mm
-Weight (Kg):1,778
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-1,000.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="611" xml:space="preserve">
-      <c r="A611" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, SB-G-400,
-1.00 x 118.9 x coil mm</v>
-      </c>
-      <c r="B611" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, SB-G-400,
-1.00 x 118.9 x coil mm
-Weight (Kg):754
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-1,000.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="612" xml:space="preserve">
-      <c r="A612" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, SB-G-400,
-1.00 x 118.9 x coil mm</v>
-      </c>
-      <c r="B612" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, SB-G-400,
-1.00 x 118.9 x coil mm
-Weight (Kg):802
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-1,000.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="613" xml:space="preserve">
-      <c r="A613" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, SB-G-400,
-1.00 x 266.9 x coil mm</v>
-      </c>
-      <c r="B613" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, SB-G-400,
-1.00 x 266.9 x coil mm
-Weight (Kg):1,322
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-1,000.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="614" xml:space="preserve">
-      <c r="A614" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, SB-G-500,
-0.70 x 245.9 x coil mm</v>
-      </c>
-      <c r="B614" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, SB-G-500,
-0.70 x 245.9 x coil mm
-Weight (Kg):1,496
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-1,000.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="615" xml:space="preserve">
-      <c r="A615" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, SBA,
-0.70 x 1056.0 x coil mm</v>
-      </c>
-      <c r="B615" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, SBA,
-0.70 x 1056.0 x coil mm
-Weight (Kg):15,197
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-1,125.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="616" xml:space="preserve">
-      <c r="A616" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, SBA,
-0.70 x 150.9 x coil mm</v>
-      </c>
-      <c r="B616" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, SBA,
-0.70 x 150.9 x coil mm
-Weight (Kg):1,268
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-1,000.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="617" xml:space="preserve">
-      <c r="A617" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, SBA,
-0.70 x 173.0 x coil mm</v>
-      </c>
-      <c r="B617" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, SBA,
-0.70 x 173.0 x coil mm
-Weight (Kg):890
-Quality:Prime
-Help
-Location:FABRICA ALGECIRAS
-1,000.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="618" xml:space="preserve">
-      <c r="A618" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, SBA,
-0.70 x 195.9 x coil mm</v>
-      </c>
-      <c r="B618" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, SBA,
-0.70 x 195.9 x coil mm
-Weight (Kg):962
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-1,000.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="619" xml:space="preserve">
-      <c r="A619" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, SBA,
-0.70 x 682.0 x coil mm</v>
-      </c>
-      <c r="B619" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, SBA,
-0.70 x 682.0 x coil mm
-Weight (Kg):3,870
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-1,025.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="620" xml:space="preserve">
-      <c r="A620" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, SBA,
-0.70 x 825.0 x coil mm</v>
-      </c>
-      <c r="B620" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, SBA,
-0.70 x 825.0 x coil mm
-Weight (Kg):6,448
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-1,125.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="621" xml:space="preserve">
-      <c r="A621" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, SBA,
-0.70 x 942.0 x coil mm</v>
-      </c>
-      <c r="B621" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, SBA,
-0.70 x 942.0 x coil mm
-Weight (Kg):1,810
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-1,125.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="622" xml:space="preserve">
-      <c r="A622" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, SBA,
-0.70 x 948.0 x coil mm</v>
-      </c>
-      <c r="B622" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, SBA,
-0.70 x 948.0 x coil mm
-Weight (Kg):3,410
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-1,125.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="623" xml:space="preserve">
-      <c r="A623" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, SBA,
-0.70 x 960.0 x coil mm</v>
-      </c>
-      <c r="B623" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, SBA,
-0.70 x 960.0 x coil mm
-Weight (Kg):2,780
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-1,125.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="624" xml:space="preserve">
-      <c r="A624" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, SBA,
-0.70 x 963.0 x coil mm</v>
-      </c>
-      <c r="B624" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, SBA,
-0.70 x 963.0 x coil mm
-Weight (Kg):4,570
-Quality:Prime
-Help
-Location:FABRICA ALGECIRAS
-1,325.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="625" xml:space="preserve">
-      <c r="A625" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Disk, BA,
-0.60 x 550.0 x 0.0 mm</v>
-      </c>
-      <c r="B625" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Disk, BA,
-0.60 x 550.0 x 0.0 mm
-Weight (Kg):578
-Quality:Prime
-Help
-Location:FABRICA ALGECIRAS
-1,900.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="626" xml:space="preserve">
-      <c r="A626" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Disk, BA,
-0.60 x 550.0 x 0.0 mm</v>
-      </c>
-      <c r="B626" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Disk, BA,
-0.60 x 550.0 x 0.0 mm
-Weight (Kg):572
-Quality:Prime
-Help
-Location:FABRICA ALGECIRAS
-1,900.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="627" xml:space="preserve">
-      <c r="A627" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Disk, BA,
-0.60 x 550.0 x 0.0 mm</v>
-      </c>
-      <c r="B627" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Disk, BA,
-0.60 x 550.0 x 0.0 mm
-Weight (Kg):576
-Quality:Prime
-Help
-Location:FABRICA ALGECIRAS
-1,900.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="628" xml:space="preserve">
-      <c r="A628" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Disk, BA,
-0.60 x 550.0 x 0.0 mm</v>
-      </c>
-      <c r="B628" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Disk, BA,
-0.60 x 550.0 x 0.0 mm
-Weight (Kg):578
-Quality:Prime
-Help
-Location:FABRICA ALGECIRAS
-1,900.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="629" xml:space="preserve">
-      <c r="A629" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Disk, BA,
-0.60 x 550.0 x 0.0 mm</v>
-      </c>
-      <c r="B629" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Disk, BA,
-0.60 x 550.0 x 0.0 mm
-Weight (Kg):582
-Quality:Prime
-Help
-Location:FABRICA ALGECIRAS
-1,900.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="630" xml:space="preserve">
-      <c r="A630" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Sheet, 2B,
-2.00 x 1250.0 x 2500.0 mm</v>
-      </c>
-      <c r="B630" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Sheet, 2B,
-2.00 x 1250.0 x 2500.0 mm
-Weight (Kg):619
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-1,125.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="631" xml:space="preserve">
-      <c r="A631" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Sheet, 2B,
-3.00 x 1250.0 x 2500.0 mm</v>
-      </c>
-      <c r="B631" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Sheet, 2B,
-3.00 x 1250.0 x 2500.0 mm
-Weight (Kg):566
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-1,125.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="632" xml:space="preserve">
-      <c r="A632" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Sheet, 2B,
-3.00 x 1250.0 x 2500.0 mm</v>
-      </c>
-      <c r="B632" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Sheet, 2B,
-3.00 x 1250.0 x 2500.0 mm
-Weight (Kg):640
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-1,125.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="633" xml:space="preserve">
-      <c r="A633" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Sheet, BA,
-0.70 x 1250.0 x 2500.0 mm</v>
-      </c>
-      <c r="B633" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Sheet, BA,
-0.70 x 1250.0 x 2500.0 mm
-Weight (Kg):766
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-1,125.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="634" xml:space="preserve">
-      <c r="A634" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Sheet, SB-G-400,
-1.00 x 1500.0 x 3000.0 mm</v>
-      </c>
-      <c r="B634" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Sheet, SB-G-400,
-1.00 x 1500.0 x 3000.0 mm
-Weight (Kg):1,940
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-1,125.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="635" xml:space="preserve">
-      <c r="A635" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Untrimmed, Coil, 1/4 HT,
-3.00 x 1292.0 x coil mm</v>
-      </c>
-      <c r="B635" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Untrimmed, Coil, 1/4 HT,
-3.00 x 1292.0 x coil mm
-Weight (Kg):3,641
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-1,125.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="636" xml:space="preserve">
-      <c r="A636" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Untrimmed, Coil, 2B,
-1.20 x 1500.0 x coil mm</v>
-      </c>
-      <c r="B636" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Untrimmed, Coil, 2B,
-1.20 x 1500.0 x coil mm
-Weight (Kg):4,750
-Quality:Downgraded
-Help
-Location:FABRICA ALGECIRAS
-1,000.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="637" xml:space="preserve">
-      <c r="A637" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Untrimmed, Coil, 2D, ET-100
-0.50 x 1250.0 x coil mm</v>
-      </c>
-      <c r="B637" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Untrimmed, Coil, 2D, ET-100
-0.50 x 1250.0 x coil mm
-Weight (Kg):5,160
-Quality:Prime
-Help
-Location:FABRICA ALGECIRAS
-1,325.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="638" xml:space="preserve">
-      <c r="A638" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Untrimmed, Coil, 2D, ET-100
-0.50 x 1250.0 x coil mm</v>
-      </c>
-      <c r="B638" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Untrimmed, Coil, 2D, ET-100
-0.50 x 1250.0 x coil mm
-Weight (Kg):3,695
-Quality:Prime
-Help
-Location:FABRICA ALGECIRAS
-1,325.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="639" xml:space="preserve">
-      <c r="A639" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Untrimmed, Coil, 2B,
-0.40 x 1264.0 x coil mm</v>
-      </c>
-      <c r="B639" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Untrimmed, Coil, 2B,
-0.40 x 1264.0 x coil mm
-Weight (Kg):5,720
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-1,125.00 €/ton
-Out of Stock</v>
-      </c>
-    </row>
-    <row r="640" xml:space="preserve">
-      <c r="A640" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Untrimmed, Coil, 2B,
-0.40 x 1273.0 x coil mm</v>
-      </c>
-      <c r="B640" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Untrimmed, Coil, 2B,
-0.40 x 1273.0 x coil mm
-Weight (Kg):5,176
-Quality:Prime
-Help
-Location:FABRICA ALGECIRAS
-1,325.00 €/ton
-Reserved</v>
-      </c>
-    </row>
-    <row r="641" xml:space="preserve">
-      <c r="A641" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Untrimmed, Coil, BA,
-0.40 x 1014.0 x coil mm</v>
-      </c>
-      <c r="B641" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Untrimmed, Coil, BA,
-0.40 x 1014.0 x coil mm
-Weight (Kg):2,400
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-1,050.00 €/ton
-Out of Stock</v>
-      </c>
-    </row>
-    <row r="642" xml:space="preserve">
-      <c r="A642" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Untrimmed, Coil, BA,
-0.60 x 1246.0 x coil mm</v>
-      </c>
-      <c r="B642" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Untrimmed, Coil, BA,
-0.60 x 1246.0 x coil mm
-Weight (Kg):2,585
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-1,125.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="643" xml:space="preserve">
-      <c r="A643" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Untrimmed, Coil, BA,
-1.00 x 1028.0 x coil mm</v>
-      </c>
-      <c r="B643" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Untrimmed, Coil, BA,
-1.00 x 1028.0 x coil mm
-Weight (Kg):2,430
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-1,125.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="644" xml:space="preserve">
-      <c r="A644" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Untrimmed, Coil, SBA,
-0.70 x 825.0 x coil mm</v>
-      </c>
-      <c r="B644" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Untrimmed, Coil, SBA,
-0.70 x 825.0 x coil mm
-Weight (Kg):7,260
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-1,125.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="645" xml:space="preserve">
-      <c r="A645" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Untrimmed, Coil, SBA,
-0.70 x 873.0 x coil mm</v>
-      </c>
-      <c r="B645" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Untrimmed, Coil, SBA,
-0.70 x 873.0 x coil mm
-Weight (Kg):4,020
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-1,125.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="646" xml:space="preserve">
-      <c r="A646" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4510 430Ti-Coil, 2B,
-2.00 x 100.9 x coil mm</v>
-      </c>
-      <c r="B646" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4510 430Ti-Coil, 2B,
-2.00 x 100.9 x coil mm
-Weight (Kg):1,710
-Quality:Prime
-Help
-Location:FABRICA ALGECIRAS
-1,000.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="647" xml:space="preserve">
-      <c r="A647" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4510 430Ti-Coil, BA,
-0.40 x 180.0 x coil mm</v>
-      </c>
-      <c r="B647" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4510 430Ti-Coil, BA,
-0.40 x 180.0 x coil mm
-Weight (Kg):1,188
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-1,000.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="648" xml:space="preserve">
-      <c r="A648" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4510 430Ti-Coil, BA,
-0.40 x 508.0 x coil mm</v>
-      </c>
-      <c r="B648" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4510 430Ti-Coil, BA,
-0.40 x 508.0 x coil mm
-Weight (Kg):3,364
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-1,025.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="649" xml:space="preserve">
-      <c r="A649" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4510 430Ti-Coil, BA,
-0.50 x 170.0 x coil mm</v>
-      </c>
-      <c r="B649" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4510 430Ti-Coil, BA,
-0.50 x 170.0 x coil mm
-Weight (Kg):914
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-1,000.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="650" xml:space="preserve">
-      <c r="A650" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4510 430Ti-Coil, BA,
-0.70 x 100.9 x coil mm</v>
-      </c>
-      <c r="B650" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4510 430Ti-Coil, BA,
-0.70 x 100.9 x coil mm
-Weight (Kg):638
-Quality:Prime
-Help
-Location:FABRICA ALGECIRAS
-1,000.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="651" xml:space="preserve">
-      <c r="A651" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4510 430Ti-Coil, BA,
-0.70 x 1020.0 x coil mm</v>
-      </c>
-      <c r="B651" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4510 430Ti-Coil, BA,
-0.70 x 1020.0 x coil mm
-Weight (Kg):16,000
-Quality:Prime
-Help
-Location:FABRICA ALGECIRAS
-1,900.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="652" xml:space="preserve">
-      <c r="A652" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4510 430Ti-Coil, BA,
-0.70 x 108.0 x coil mm</v>
-      </c>
-      <c r="B652" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4510 430Ti-Coil, BA,
-0.70 x 108.0 x coil mm
-Weight (Kg):714
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-1,000.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="653" xml:space="preserve">
-      <c r="A653" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4510 430Ti-Coil, BA,
-0.70 x 120.9 x coil mm</v>
-      </c>
-      <c r="B653" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4510 430Ti-Coil, BA,
-0.70 x 120.9 x coil mm
-Weight (Kg):976
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-1,000.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="654" xml:space="preserve">
-      <c r="A654" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4510 430Ti-Coil, BA,
-0.70 x 325.0 x coil mm</v>
-      </c>
-      <c r="B654" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4510 430Ti-Coil, BA,
-0.70 x 325.0 x coil mm
-Weight (Kg):4,156
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-1,000.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="655" xml:space="preserve">
-      <c r="A655" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4510 430Ti-Coil, BA,
-0.70 x 900.0 x coil mm</v>
-      </c>
-      <c r="B655" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4510 430Ti-Coil, BA,
-0.70 x 900.0 x coil mm
-Weight (Kg):2,800
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-1,125.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="656" xml:space="preserve">
-      <c r="A656" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Untrimmed, Coil, BA,
-0.40 x 1016.0 x coil mm</v>
-      </c>
-      <c r="B656" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Untrimmed, Coil, BA,
-0.40 x 1016.0 x coil mm
-Weight (Kg):2,500
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-1,050.00 €/ton
-Out of Stock</v>
-      </c>
-    </row>
-    <row r="657" xml:space="preserve">
-      <c r="A657" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Untrimmed, Coil, BA,
-0.50 x 1015.0 x coil mm</v>
-      </c>
-      <c r="B657" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Untrimmed, Coil, BA,
-0.50 x 1015.0 x coil mm
-Weight (Kg):2,340
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-1,125.00 €/ton
-Out of Stock</v>
-      </c>
-    </row>
-    <row r="658" xml:space="preserve">
-      <c r="A658" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Untrimmed, Coil, BA,
-0.50 x 1107.0 x coil mm</v>
-      </c>
-      <c r="B658" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Untrimmed, Coil, BA,
-0.50 x 1107.0 x coil mm
-Weight (Kg):2,230
-Quality:Prime
-Help
-Location:FABRICA ALGECIRAS
-1,325.00 €/ton
-Reserved</v>
-      </c>
-    </row>
-    <row r="659" xml:space="preserve">
-      <c r="A659" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Untrimmed, Coil, BA,
-0.60 x 1270.0 x coil mm</v>
-      </c>
-      <c r="B659" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Untrimmed, Coil, BA,
-0.60 x 1270.0 x coil mm
-Weight (Kg):3,385
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-1,125.00 €/ton
-Reserved</v>
-      </c>
-    </row>
-    <row r="660" xml:space="preserve">
-      <c r="A660" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Untrimmed, Coil, BA,
-0.60 x 1275.0 x coil mm</v>
-      </c>
-      <c r="B660" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Untrimmed, Coil, BA,
-0.60 x 1275.0 x coil mm
-Weight (Kg):3,535
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-1,125.00 €/ton
-Reserved</v>
-      </c>
-    </row>
-    <row r="661" xml:space="preserve">
-      <c r="A661" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Untrimmed, Coil, BA,
-1.00 x 1285.0 x coil mm</v>
-      </c>
-      <c r="B661" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Untrimmed, Coil, BA,
-1.00 x 1285.0 x coil mm
-Weight (Kg):5,491
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-1,125.00 €/ton
-Out of Stock</v>
-      </c>
-    </row>
-    <row r="662" xml:space="preserve">
-      <c r="A662" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4510 430Ti-Coil, BA,
-0.70 x 900.0 x coil mm</v>
-      </c>
-      <c r="B662" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4510 430Ti-Coil, BA,
-0.70 x 900.0 x coil mm
-Weight (Kg):6,570
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-1,125.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="663" xml:space="preserve">
-      <c r="A663" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4510 430Ti-Coil, BA,
-0.70 x 905.0 x coil mm</v>
-      </c>
-      <c r="B663" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4510 430Ti-Coil, BA,
-0.70 x 905.0 x coil mm
-Weight (Kg):9,410
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-1,125.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="664" xml:space="preserve">
-      <c r="A664" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4510 430Ti-Coil, BA,
-0.70 x 932.0 x coil mm</v>
-      </c>
-      <c r="B664" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4510 430Ti-Coil, BA,
-0.70 x 932.0 x coil mm
-Weight (Kg):2,270
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-1,125.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="665" xml:space="preserve">
-      <c r="A665" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4510 430Ti-Coil, BA,
-0.70 x 940.0 x coil mm</v>
-      </c>
-      <c r="B665" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4510 430Ti-Coil, BA,
-0.70 x 940.0 x coil mm
-Weight (Kg):14,920
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-1,125.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="666" xml:space="preserve">
-      <c r="A666" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4510 430Ti-Untrimmed, Coil, BA,
-0.50 x 1275.0 x coil mm</v>
-      </c>
-      <c r="B666" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4510 430Ti-Untrimmed, Coil, BA,
-0.50 x 1275.0 x coil mm
-Weight (Kg):2,258
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-1,125.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="667" xml:space="preserve">
-      <c r="A667" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4510 430Ti-Untrimmed, Coil, BA,
-0.70 x 928.0 x coil mm</v>
-      </c>
-      <c r="B667" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4510 430Ti-Untrimmed, Coil, BA,
-0.70 x 928.0 x coil mm
-Weight (Kg):4,257
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-1,125.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="668" xml:space="preserve">
-      <c r="A668" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4509 441-Coil, 2B,
-1.20 x 275.9 x coil mm</v>
-      </c>
-      <c r="B668" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4509 441-Coil, 2B,
-1.20 x 275.9 x coil mm
-Weight (Kg):2,416
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-1,100.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="669" xml:space="preserve">
-      <c r="A669" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4509 441-Coil, 2D,
-1.20 x 196.0 x coil mm</v>
-      </c>
-      <c r="B669" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4509 441-Coil, 2D,
-1.20 x 196.0 x coil mm
-Weight (Kg):2,970
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-1,100.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="670" xml:space="preserve">
-      <c r="A670" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4509 441-Coil, 2D,
-1.20 x 200.0 x coil mm</v>
-      </c>
-      <c r="B670" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4509 441-Coil, 2D,
-1.20 x 200.0 x coil mm
-Weight (Kg):3,310
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-1,100.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="671" xml:space="preserve">
-      <c r="A671" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4509 441-Coil, 2D,
-1.20 x 214.9 x coil mm</v>
-      </c>
-      <c r="B671" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4509 441-Coil, 2D,
-1.20 x 214.9 x coil mm
-Weight (Kg):3,220
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-1,100.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="672" xml:space="preserve">
-      <c r="A672" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4509 441-Coil, 2D,
-1.20 x 223.9 x coil mm</v>
-      </c>
-      <c r="B672" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4509 441-Coil, 2D,
-1.20 x 223.9 x coil mm
-Weight (Kg):3,798
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-1,100.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="673" xml:space="preserve">
-      <c r="A673" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4509 441-Coil, 2D,
-1.20 x 224.0 x coil mm</v>
-      </c>
-      <c r="B673" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4509 441-Coil, 2D,
-1.20 x 224.0 x coil mm
-Weight (Kg):3,808
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-1,100.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="674" xml:space="preserve">
-      <c r="A674" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4509 441-Coil, BA,
-0.80 x 130.9 x coil mm</v>
-      </c>
-      <c r="B674" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4509 441-Coil, BA,
-0.80 x 130.9 x coil mm
-Weight (Kg):245
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-1,100.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="675" xml:space="preserve">
-      <c r="A675" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4509 441-Coil, BA,
-0.80 x 130.9 x coil mm</v>
-      </c>
-      <c r="B675" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4509 441-Coil, BA,
-0.80 x 130.9 x coil mm
-Weight (Kg):245
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-1,100.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="676" xml:space="preserve">
-      <c r="A676" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4509 441-Coil, BA,
-0.80 x 130.9 x coil mm</v>
-      </c>
-      <c r="B676" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4509 441-Coil, BA,
-0.80 x 130.9 x coil mm
-Weight (Kg):213
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-1,100.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="677" xml:space="preserve">
-      <c r="A677" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4509 441-Coil, BA,
-0.80 x 130.9 x coil mm</v>
-      </c>
-      <c r="B677" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4509 441-Coil, BA,
-0.80 x 130.9 x coil mm
-Weight (Kg):244
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-1,100.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="678" xml:space="preserve">
-      <c r="A678" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4509 441-Coil, SB-G-400,
-1.00 x 1000.0 x coil mm</v>
-      </c>
-      <c r="B678" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4509 441-Coil, SB-G-400,
-1.00 x 1000.0 x coil mm
-Weight (Kg):7,550
-Quality:Prime
-Help
-Location:FABRICA ALGECIRAS
-1,625.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="679" xml:space="preserve">
-      <c r="A679" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4509 441-Coil, SB-G-400,
-1.00 x 255.0 x coil mm</v>
-      </c>
-      <c r="B679" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4509 441-Coil, SB-G-400,
-1.00 x 255.0 x coil mm
-Weight (Kg):2,182
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-1,100.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="680" xml:space="preserve">
-      <c r="A680" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4509 441-Coil, SB-G-400,
-1.00 x 290.9 x coil mm</v>
-      </c>
-      <c r="B680" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4509 441-Coil, SB-G-400,
-1.00 x 290.9 x coil mm
-Weight (Kg):2,370
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-1,100.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="681" xml:space="preserve">
-      <c r="A681" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4509 441-Coil, BA,
-0.40 x 1000.0 x coil mm</v>
-      </c>
-      <c r="B681" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4509 441-Coil, BA,
-0.40 x 1000.0 x coil mm
-Weight (Kg):3,222
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-1,225.00 €/ton
-Out of Stock</v>
-      </c>
-    </row>
-    <row r="682" xml:space="preserve">
-      <c r="A682" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4509 441-Coil, SB-G-400,
-1.20 x 110.9 x coil mm</v>
-      </c>
-      <c r="B682" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4509 441-Coil, SB-G-400,
-1.20 x 110.9 x coil mm
-Weight (Kg):856
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-1,100.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="683" xml:space="preserve">
-      <c r="A683" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4509 441-Coil, SB-G-400,
-1.20 x 130.9 x coil mm</v>
-      </c>
-      <c r="B683" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4509 441-Coil, SB-G-400,
-1.20 x 130.9 x coil mm
-Weight (Kg):564
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-1,100.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="684" xml:space="preserve">
-      <c r="A684" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4509 441-Coil, SB-G-400,
-1.20 x 130.9 x coil mm</v>
-      </c>
-      <c r="B684" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4509 441-Coil, SB-G-400,
-1.20 x 130.9 x coil mm
-Weight (Kg):532
-Quality:Prime
-Help
-Location:FABRICA ALGECIRAS
-1,100.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="685" xml:space="preserve">
-      <c r="A685" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4509 441-Coil, SB-G-400,
-1.50 x 130.9 x coil mm</v>
-      </c>
-      <c r="B685" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4509 441-Coil, SB-G-400,
-1.50 x 130.9 x coil mm
-Weight (Kg):640
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-1,100.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="686" xml:space="preserve">
-      <c r="A686" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4509 441-Coil, SB-G-400,
-1.50 x 360.0 x coil mm</v>
-      </c>
-      <c r="B686" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4509 441-Coil, SB-G-400,
-1.50 x 360.0 x coil mm
-Weight (Kg):1,488
-Quality:Downgraded
-Help
-Location:FABRICA ALGECIRAS
-1,100.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="687" xml:space="preserve">
-      <c r="A687" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4509 441-Untrimmed, Coil, 2B,
-1.50 x 1539.0 x coil mm</v>
-      </c>
-      <c r="B687" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4509 441-Untrimmed, Coil, 2B,
-1.50 x 1539.0 x coil mm
-Weight (Kg):14,230
-Quality:Prime
-Help
-Location:FABRICA ALGECIRAS
-2,200.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="688" xml:space="preserve">
-      <c r="A688" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4509 441-Untrimmed, Coil, BA,
-0.40 x 1075.0 x coil mm</v>
-      </c>
-      <c r="B688" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4509 441-Untrimmed, Coil, BA,
-0.40 x 1075.0 x coil mm
-Weight (Kg):9,750
-Quality:Prime
-Help
-Location:FABRICA ALGECIRAS
-2,200.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="689" xml:space="preserve">
-      <c r="A689" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4509 441-Untrimmed, Coil, Nb. 1,
-5.00 x 1045.0 x coil mm</v>
-      </c>
-      <c r="B689" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4509 441-Untrimmed, Coil, Nb. 1,
-5.00 x 1045.0 x coil mm
-Weight (Kg):7,880
-Quality:Prime
-Help
-Location:FABRICA ALGECIRAS
-1,525.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="690" xml:space="preserve">
-      <c r="A690" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 441-1.4509 Coil, 2B,
-1.20 x 240.9 x coil mm</v>
-      </c>
-      <c r="B690" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 441-1.4509 Coil, 2B,
-1.20 x 240.9 x coil mm
-Weight (Kg):3,882
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-1,100.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="691" xml:space="preserve">
-      <c r="A691" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 304-1.4301 Coil,
-0.70 x 270.9 x coil mm</v>
-      </c>
-      <c r="B691" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 304-1.4301 Coil,
-0.70 x 270.9 x coil mm
-Weight (Kg):2,704
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-2,075.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="692" xml:space="preserve">
-      <c r="A692" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 316L-1.4404 Coil,
-1.20 x 136.0 x coil mm</v>
-      </c>
-      <c r="B692" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 316L-1.4404 Coil,
-1.20 x 136.0 x coil mm
-Weight (Kg):2,300
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-3,270.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="693" xml:space="preserve">
-      <c r="A693" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 304L/304-4301/4307 Coil, 2B,
-6.00 x 245.0 x coil mm</v>
-      </c>
-      <c r="B693" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 304L/304-4301/4307 Coil, 2B,
-6.00 x 245.0 x coil mm
-Weight (Kg):2,394
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-2,075.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="694" xml:space="preserve">
-      <c r="A694" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, 2B,
-0.70 x 197.5 x coil mm</v>
-      </c>
-      <c r="B694" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, 2B,
-0.70 x 197.5 x coil mm
-Weight (Kg):2,442
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-1,000.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="695" xml:space="preserve">
-      <c r="A695" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 441-1.4509 Coil, 2B,
-2.00 x 120.9 x coil mm</v>
-      </c>
-      <c r="B695" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 441-1.4509 Coil, 2B,
-2.00 x 120.9 x coil mm
-Weight (Kg):1,956
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-1,100.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="696" xml:space="preserve">
-      <c r="A696" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 304-1.4301 Coil, 2B,
-1.20 x 119.9 x coil mm</v>
-      </c>
-      <c r="B696" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 304-1.4301 Coil, 2B,
-1.20 x 119.9 x coil mm
-Weight (Kg):1,500
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-2,075.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="697" xml:space="preserve">
-      <c r="A697" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 304-1.4301 Coil, 2B,
-1.20 x 119.9 x coil mm</v>
-      </c>
-      <c r="B697" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 304-1.4301 Coil, 2B,
-1.20 x 119.9 x coil mm
-Weight (Kg):1,400
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-2,075.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="698" xml:space="preserve">
-      <c r="A698" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, BA,
-0.70 x 125.0 x coil mm</v>
-      </c>
-      <c r="B698" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, BA,
-0.70 x 125.0 x coil mm
-Weight (Kg):1,764
-Quality:Prime
-Help
-Location:FABRICA ALGECIRAS
-1,000.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="699" xml:space="preserve">
-      <c r="A699" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, BA,
-0.70 x 104.9 x coil mm</v>
-      </c>
-      <c r="B699" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, BA,
-0.70 x 104.9 x coil mm
-Weight (Kg):1,240
-Quality:Prime
-Help
-Location:FABRICA ALGECIRAS
-1,000.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="700" xml:space="preserve">
-      <c r="A700" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, BA,
-0.70 x 118.9 x coil mm</v>
-      </c>
-      <c r="B700" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, BA,
-0.70 x 118.9 x coil mm
-Weight (Kg):1,802
-Quality:Prime
-Help
-Location:FABRICA ALGECIRAS
-1,000.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="701" xml:space="preserve">
-      <c r="A701" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, BA,
-0.70 x 115.9 x coil mm</v>
-      </c>
-      <c r="B701" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, BA,
-0.70 x 115.9 x coil mm
-Weight (Kg):1,368
-Quality:Prime
-Help
-Location:FABRICA ALGECIRAS
-1,000.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="702" xml:space="preserve">
-      <c r="A702" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, BA,
-0.70 x 119.0 x coil mm</v>
-      </c>
-      <c r="B702" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, BA,
-0.70 x 119.0 x coil mm
-Weight (Kg):1,622
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-1,000.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="703" xml:space="preserve">
-      <c r="A703" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 304L/304-4301/4307 Coil, 2B,
-1.40 x 110.9 x coil mm</v>
-      </c>
-      <c r="B703" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 304L/304-4301/4307 Coil, 2B,
-1.40 x 110.9 x coil mm
-Weight (Kg):1,240
-Quality:Prime
-Help
-Location:FABRICA ALGECIRAS
-2,075.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="704" xml:space="preserve">
-      <c r="A704" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, BA,
-0.70 x 104.0 x coil mm</v>
-      </c>
-      <c r="B704" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, BA,
-0.70 x 104.0 x coil mm
-Weight (Kg):1,622
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-1,000.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="705" xml:space="preserve">
-      <c r="A705" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, BA,
-0.70 x 104.0 x coil mm</v>
-      </c>
-      <c r="B705" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, BA,
-0.70 x 104.0 x coil mm
-Weight (Kg):1,688
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-1,000.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="706" xml:space="preserve">
-      <c r="A706" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 304L/304-4301/4307 Coil, 2B,
-1.40 x 110.9 x coil mm</v>
-      </c>
-      <c r="B706" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 304L/304-4301/4307 Coil, 2B,
-1.40 x 110.9 x coil mm
-Weight (Kg):1,162
-Quality:Prime
-Help
-Location:FABRICA ALGECIRAS
-2,075.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="707" xml:space="preserve">
-      <c r="A707" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 430Ti-1.4510 Coil, BA,
-0.70 x 165.9 x coil mm</v>
-      </c>
-      <c r="B707" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 430Ti-1.4510 Coil, BA,
-0.70 x 165.9 x coil mm
-Weight (Kg):2,692
-Quality:Prime
-Help
-Location:FABRICA ALGECIRAS
-1,000.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="708" xml:space="preserve">
-      <c r="A708" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 430Ti-1.4510 Coil, BA,
-0.70 x 165.9 x coil mm</v>
-      </c>
-      <c r="B708" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 430Ti-1.4510 Coil, BA,
-0.70 x 165.9 x coil mm
-Weight (Kg):2,756
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-1,000.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="709" xml:space="preserve">
-      <c r="A709" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, BA,
-0.70 x 140.9 x coil mm</v>
-      </c>
-      <c r="B709" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, BA,
-0.70 x 140.9 x coil mm
-Weight (Kg):1,676
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-1,000.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="710" xml:space="preserve">
-      <c r="A710" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, BA,
-0.70 x 100.9 x coil mm</v>
-      </c>
-      <c r="B710" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, BA,
-0.70 x 100.9 x coil mm
-Weight (Kg):1,340
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-1,000.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="711" xml:space="preserve">
-      <c r="A711" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, BA,
-0.70 x 125.0 x coil mm</v>
-      </c>
-      <c r="B711" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, BA,
-0.70 x 125.0 x coil mm
-Weight (Kg):1,550
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-1,000.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="712" xml:space="preserve">
-      <c r="A712" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, BA,
-0.70 x 125.0 x coil mm</v>
-      </c>
-      <c r="B712" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, BA,
-0.70 x 125.0 x coil mm
-Weight (Kg):1,414
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-1,000.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="713" xml:space="preserve">
-      <c r="A713" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, BA,
-0.70 x 100.9 x coil mm</v>
-      </c>
-      <c r="B713" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, BA,
-0.70 x 100.9 x coil mm
-Weight (Kg):2,188
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-1,000.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="714" xml:space="preserve">
-      <c r="A714" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 304L/304-4301/4307 Coil, Nb. 1,
-4.70 x 110.0 x coil mm</v>
-      </c>
-      <c r="B714" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 304L/304-4301/4307 Coil, Nb. 1,
-4.70 x 110.0 x coil mm
-Weight (Kg):1,796
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-1,975.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="715" xml:space="preserve">
-      <c r="A715" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 304L/304-4301/4307 Coil, Nb. 1,
-4.70 x 110.0 x coil mm</v>
-      </c>
-      <c r="B715" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 304L/304-4301/4307 Coil, Nb. 1,
-4.70 x 110.0 x coil mm
-Weight (Kg):2,038
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-1,975.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="716" xml:space="preserve">
-      <c r="A716" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, BA,
-0.70 x 165.9 x coil mm</v>
-      </c>
-      <c r="B716" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, BA,
-0.70 x 165.9 x coil mm
-Weight (Kg):2,620
-Quality:Prime
-Help
-Location:FABRICA ALGECIRAS
-1,000.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="717" xml:space="preserve">
-      <c r="A717" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 304-1.4301 Coil,
-0.70 x 260.9 x coil mm</v>
-      </c>
-      <c r="B717" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 304-1.4301 Coil,
-0.70 x 260.9 x coil mm
-Weight (Kg):1,330
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-2,075.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="718" xml:space="preserve">
-      <c r="A718" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 304-1.4301 Coil,
-0.70 x 260.9 x coil mm</v>
-      </c>
-      <c r="B718" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 304-1.4301 Coil,
-0.70 x 260.9 x coil mm
-Weight (Kg):1,264
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-2,075.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="719" xml:space="preserve">
-      <c r="A719" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, BA,
-0.70 x 110.0 x coil mm</v>
-      </c>
-      <c r="B719" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, BA,
-0.70 x 110.0 x coil mm
-Weight (Kg):1,250
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-1,000.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="720" xml:space="preserve">
-      <c r="A720" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, BA,
-0.70 x 122.9 x coil mm</v>
-      </c>
-      <c r="B720" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, BA,
-0.70 x 122.9 x coil mm
-Weight (Kg):1,460
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-1,000.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="721" xml:space="preserve">
-      <c r="A721" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 304L/304-4301/4307 Coil, 2B,
-1.40 x 110.0 x coil mm</v>
-      </c>
-      <c r="B721" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 304L/304-4301/4307 Coil, 2B,
-1.40 x 110.0 x coil mm
-Weight (Kg):1,554
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-2,075.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="722" xml:space="preserve">
-      <c r="A722" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 304L/304-4301/4307 Coil, 2B,
-1.40 x 110.0 x coil mm</v>
-      </c>
-      <c r="B722" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 304L/304-4301/4307 Coil, 2B,
-1.40 x 110.0 x coil mm
-Weight (Kg):1,586
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-2,075.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="723" xml:space="preserve">
-      <c r="A723" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 304L/304-4301/4307 Coil, 2B,
-1.40 x 104.0 x coil mm</v>
-      </c>
-      <c r="B723" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 304L/304-4301/4307 Coil, 2B,
-1.40 x 104.0 x coil mm
-Weight (Kg):1,030
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-2,075.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="724" xml:space="preserve">
-      <c r="A724" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 304DDQ-1.4301 Coil, BA,
-0.70 x 181.9 x coil mm</v>
-      </c>
-      <c r="B724" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 304DDQ-1.4301 Coil, BA,
-0.70 x 181.9 x coil mm
-Weight (Kg):2,912
-Quality:Prime
-Help
-Location:FABRICA ALGECIRAS
-2,075.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="725" xml:space="preserve">
-      <c r="A725" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 304-1.4301 Coil,
-1.50 x 136.0 x coil mm</v>
-      </c>
-      <c r="B725" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 304-1.4301 Coil,
-1.50 x 136.0 x coil mm
-Weight (Kg):3,450
-Quality:Prime
-Help
-Location:FABRICA ALGECIRAS
-2,075.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="726" xml:space="preserve">
-      <c r="A726" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 304-1.4301 Coil, BA,
-0.40 x 200.0 x coil mm</v>
-      </c>
-      <c r="B726" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 304-1.4301 Coil, BA,
-0.40 x 200.0 x coil mm
-Weight (Kg):1,964
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-2,075.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="727" xml:space="preserve">
-      <c r="A727" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 304-1.4301 Coil, BA, ET-60
-0.60 x 120.0 x coil mm</v>
-      </c>
-      <c r="B727" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 304-1.4301 Coil, BA, ET-60
-0.60 x 120.0 x coil mm
-Weight (Kg):1,302
-Quality:Prime
-Help
-Location:FABRICA ALGECIRAS
-2,075.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="728" xml:space="preserve">
-      <c r="A728" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, ET-100
-0.70 x 124.9 x coil mm</v>
-      </c>
-      <c r="B728" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, ET-100
-0.70 x 124.9 x coil mm
-Weight (Kg):2,106
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-1,000.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="729" xml:space="preserve">
-      <c r="A729" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, ET-100
-0.70 x 124.9 x coil mm</v>
-      </c>
-      <c r="B729" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, ET-100
-0.70 x 124.9 x coil mm
-Weight (Kg):1,972
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-1,000.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="730" xml:space="preserve">
-      <c r="A730" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 430Ti-1.4510 Coil, 2B,
-0.80 x 155.9 x coil mm</v>
-      </c>
-      <c r="B730" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 430Ti-1.4510 Coil, 2B,
-0.80 x 155.9 x coil mm
-Weight (Kg):1,586
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-1,000.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="731" xml:space="preserve">
-      <c r="A731" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 304-1.4301 Coil, BA,
-0.40 x 270.0 x coil mm</v>
-      </c>
-      <c r="B731" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 304-1.4301 Coil, BA,
-0.40 x 270.0 x coil mm
-Weight (Kg):2,572
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-2,075.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="732" xml:space="preserve">
-      <c r="A732" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, BA,
-0.60 x 130.0 x coil mm</v>
-      </c>
-      <c r="B732" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, BA,
-0.60 x 130.0 x coil mm
-Weight (Kg):1,490
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-1,000.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="733" xml:space="preserve">
-      <c r="A733" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 441-1.4509 Coil, BA,
-0.40 x 110.0 x coil mm</v>
-      </c>
-      <c r="B733" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 441-1.4509 Coil, BA,
-0.40 x 110.0 x coil mm
-Weight (Kg):1,870
-Quality:Prime
-Help
-Location:FABRICA ALGECIRAS
-1,100.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="734" xml:space="preserve">
-      <c r="A734" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 441-1.4509 Coil, BA,
-0.40 x 110.0 x coil mm</v>
-      </c>
-      <c r="B734" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 441-1.4509 Coil, BA,
-0.40 x 110.0 x coil mm
-Weight (Kg):1,882
-Quality:Prime
-Help
-Location:FABRICA ALGECIRAS
-1,100.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="735" xml:space="preserve">
-      <c r="A735" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 301-1.4310 Coil, BA,
-0.40 x 110.0 x coil mm</v>
-      </c>
-      <c r="B735" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 301-1.4310 Coil, BA,
-0.40 x 110.0 x coil mm
-Weight (Kg):1,934
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-1,925.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="736" xml:space="preserve">
-      <c r="A736" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 301-1.4310 Coil, BA,
-0.40 x 110.0 x coil mm</v>
-      </c>
-      <c r="B736" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 301-1.4310 Coil, BA,
-0.40 x 110.0 x coil mm
-Weight (Kg):1,860
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-1,925.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="737" xml:space="preserve">
-      <c r="A737" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 321-1.4541 Coil, 2B,
-1.90 x 104.5 x coil mm</v>
-      </c>
-      <c r="B737" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 321-1.4541 Coil, 2B,
-1.90 x 104.5 x coil mm
-Weight (Kg):2,304
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-2,235.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="738" xml:space="preserve">
-      <c r="A738" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 304L/304-4301/4307 Coil, Polished N4-G-180,
-1.20 x 255.9 x coil mm</v>
-      </c>
-      <c r="B738" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 304L/304-4301/4307 Coil, Polished N4-G-180,
-1.20 x 255.9 x coil mm
-Weight (Kg):4,298
-Quality:Prime
-Help
-Location:FABRICA ALGECIRAS
-2,075.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="739" xml:space="preserve">
-      <c r="A739" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 301-1.4310 Coil, BA,
-0.40 x 110.0 x coil mm</v>
-      </c>
-      <c r="B739" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 301-1.4310 Coil, BA,
-0.40 x 110.0 x coil mm
-Weight (Kg):1,698
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-1,925.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="740" xml:space="preserve">
-      <c r="A740" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, BA,
-0.40 x 130.0 x coil mm</v>
-      </c>
-      <c r="B740" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, BA,
-0.40 x 130.0 x coil mm
-Weight (Kg):1,916
-Quality:Prime
-Help
-Location:FABRICA ALGECIRAS
-1,000.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="741" xml:space="preserve">
-      <c r="A741" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 430Ti-1.4510 Coil, BA,
-0.50 x 140.0 x coil mm</v>
-      </c>
-      <c r="B741" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 430Ti-1.4510 Coil, BA,
-0.50 x 140.0 x coil mm
-Weight (Kg):3,054
-Quality:Prime
-Help
-Location:FABRICA ALGECIRAS
-1,000.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="742" xml:space="preserve">
-      <c r="A742" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 430Ti-1.4510 Coil, BA,
-0.50 x 140.0 x coil mm</v>
-      </c>
-      <c r="B742" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 430Ti-1.4510 Coil, BA,
-0.50 x 140.0 x coil mm
-Weight (Kg):3,060
-Quality:Prime
-Help
-Location:FABRICA ALGECIRAS
-1,000.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="743" xml:space="preserve">
-      <c r="A743" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 430Ti-1.4510 Coil, BA,
-0.50 x 140.0 x coil mm</v>
-      </c>
-      <c r="B743" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 430Ti-1.4510 Coil, BA,
-0.50 x 140.0 x coil mm
-Weight (Kg):2,220
-Quality:Prime
-Help
-Location:FABRICA ALGECIRAS
-1,000.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="744" xml:space="preserve">
-      <c r="A744" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 430Ti-1.4510 Coil, BA,
-0.50 x 140.0 x coil mm</v>
-      </c>
-      <c r="B744" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 430Ti-1.4510 Coil, BA,
-0.50 x 140.0 x coil mm
-Weight (Kg):2,224
-Quality:Prime
-Help
-Location:FABRICA ALGECIRAS
-1,000.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="745" xml:space="preserve">
-      <c r="A745" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 304L/304-4301/4307 Coil, 2B,
-1.40 x 100.9 x coil mm</v>
-      </c>
-      <c r="B745" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 304L/304-4301/4307 Coil, 2B,
-1.40 x 100.9 x coil mm
-Weight (Kg):1,612
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-2,075.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="746" xml:space="preserve">
-      <c r="A746" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 304L/304-4301/4307 Coil, 2B,
-1.40 x 100.9 x coil mm</v>
-      </c>
-      <c r="B746" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 304L/304-4301/4307 Coil, 2B,
-1.40 x 100.9 x coil mm
-Weight (Kg):1,600
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-2,075.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="747" xml:space="preserve">
-      <c r="A747" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 304-1.4301 Coil, Emboss Chequered,
-0.70 x 174.9 x coil mm</v>
-      </c>
-      <c r="B747" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 304-1.4301 Coil, Emboss Chequered,
-0.70 x 174.9 x coil mm
-Weight (Kg):1,494
-Quality:Prime
-Help
-Location:FABRICA ALGECIRAS
-2,075.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="748" xml:space="preserve">
-      <c r="A748" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 304-1.4301 Coil, Emboss Chequered,
-0.70 x 174.9 x coil mm</v>
-      </c>
-      <c r="B748" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 304-1.4301 Coil, Emboss Chequered,
-0.70 x 174.9 x coil mm
-Weight (Kg):1,472
-Quality:Prime
-Help
-Location:FABRICA ALGECIRAS
-2,075.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="749" xml:space="preserve">
-      <c r="A749" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, SB-G-240,
-0.50 x 290.9 x coil mm</v>
-      </c>
-      <c r="B749" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, SB-G-240,
-0.50 x 290.9 x coil mm
-Weight (Kg):4,408
-Quality:Prime
-Help
-Location:FABRICA ALGECIRAS
-1,000.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="750" xml:space="preserve">
-      <c r="A750" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 304-1.4301 Coil, BA,
-0.60 x 110.0 x coil mm</v>
-      </c>
-      <c r="B750" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 304-1.4301 Coil, BA,
-0.60 x 110.0 x coil mm
-Weight (Kg):1,032
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-2,075.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="751" xml:space="preserve">
-      <c r="A751" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 304-1.4301 Coil, BA,
-0.40 x 270.0 x coil mm</v>
-      </c>
-      <c r="B751" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 304-1.4301 Coil, BA,
-0.40 x 270.0 x coil mm
-Weight (Kg):3,124
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-2,075.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="752" xml:space="preserve">
-      <c r="A752" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 304-1.4301 Coil, BA,
-0.60 x 135.0 x coil mm</v>
-      </c>
-      <c r="B752" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 304-1.4301 Coil, BA,
-0.60 x 135.0 x coil mm
-Weight (Kg):2,078
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-2,075.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="753" xml:space="preserve">
-      <c r="A753" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 441-1.4509 Coil, 2B,
-2.00 x 245.9 x coil mm</v>
-      </c>
-      <c r="B753" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 441-1.4509 Coil, 2B,
-2.00 x 245.9 x coil mm
-Weight (Kg):3,492
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-1,100.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="754" xml:space="preserve">
-      <c r="A754" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 304-1.4301 Coil, 2B,
-0.60 x 101.9 x coil mm</v>
-      </c>
-      <c r="B754" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 304-1.4301 Coil, 2B,
-0.60 x 101.9 x coil mm
-Weight (Kg):1,350
-Quality:Prime
-Help
-Location:FABRICA ALGECIRAS
-2,075.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="755" xml:space="preserve">
-      <c r="A755" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 430Ti-1.4510 Coil, BA,
-0.70 x 118.9 x coil mm</v>
-      </c>
-      <c r="B755" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 430Ti-1.4510 Coil, BA,
-0.70 x 118.9 x coil mm
-Weight (Kg):1,768
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-1,000.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="756" xml:space="preserve">
-      <c r="A756" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 304L/304-4301/4307 Coil, 2B,
-1.00 x 135.9 x coil mm</v>
-      </c>
-      <c r="B756" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 304L/304-4301/4307 Coil, 2B,
-1.00 x 135.9 x coil mm
-Weight (Kg):1,056
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-2,075.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="757" xml:space="preserve">
-      <c r="A757" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 304L/304-4301/4307 Coil, 2B,
-2.00 x 250.0 x coil mm</v>
-      </c>
-      <c r="B757" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 304L/304-4301/4307 Coil, 2B,
-2.00 x 250.0 x coil mm
-Weight (Kg):2,388
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-2,075.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="758" xml:space="preserve">
-      <c r="A758" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, BA,
-0.70 x 125.9 x coil mm</v>
-      </c>
-      <c r="B758" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, BA,
-0.70 x 125.9 x coil mm
-Weight (Kg):1,788
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-1,000.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="759" xml:space="preserve">
-      <c r="A759" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, BA,
-0.70 x 125.9 x coil mm</v>
-      </c>
-      <c r="B759" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, BA,
-0.70 x 125.9 x coil mm
-Weight (Kg):1,794
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-1,000.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="760" xml:space="preserve">
-      <c r="A760" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 430Ti-1.4510 Coil, BA,
-0.70 x 112.0 x coil mm</v>
-      </c>
-      <c r="B760" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 430Ti-1.4510 Coil, BA,
-0.70 x 112.0 x coil mm
-Weight (Kg):1,550
-Quality:Prime
-Help
-Location:FABRICA ALGECIRAS
-1,000.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="761" xml:space="preserve">
-      <c r="A761" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 304-1.4301 Coil, BA,
-0.60 x 320.0 x coil mm</v>
-      </c>
-      <c r="B761" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 304-1.4301 Coil, BA,
-0.60 x 320.0 x coil mm
-Weight (Kg):2,534
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-2,075.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="762" xml:space="preserve">
-      <c r="A762" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 304-1.4301 Coil, BA,
-0.60 x 320.0 x coil mm</v>
-      </c>
-      <c r="B762" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 304-1.4301 Coil, BA,
-0.60 x 320.0 x coil mm
-Weight (Kg):3,148
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-2,075.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="763" xml:space="preserve">
-      <c r="A763" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 304-1.4301 Coil, 2B,
-0.80 x 199.9 x coil mm</v>
-      </c>
-      <c r="B763" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 304-1.4301 Coil, 2B,
-0.80 x 199.9 x coil mm
-Weight (Kg):2,602
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-2,075.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="764" xml:space="preserve">
-      <c r="A764" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 304L/304-4301/4307 Coil, 2B,
-1.00 x 125.9 x coil mm</v>
-      </c>
-      <c r="B764" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 304L/304-4301/4307 Coil, 2B,
-1.00 x 125.9 x coil mm
-Weight (Kg):1,726
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-2,075.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="765" xml:space="preserve">
-      <c r="A765" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 316L-1.4404 Coil, 2B,
-1.50 x 230.9 x coil mm</v>
-      </c>
-      <c r="B765" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 316L-1.4404 Coil, 2B,
-1.50 x 230.9 x coil mm
-Weight (Kg):1,956
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-3,270.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="766" xml:space="preserve">
-      <c r="A766" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, SBA,
-0.70 x 180.9 x coil mm</v>
-      </c>
-      <c r="B766" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, SBA,
-0.70 x 180.9 x coil mm
-Weight (Kg):2,402
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-1,000.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="767" xml:space="preserve">
-      <c r="A767" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 301-1.4310 Coil, BA,
-0.40 x 110.0 x coil mm</v>
-      </c>
-      <c r="B767" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 301-1.4310 Coil, BA,
-0.40 x 110.0 x coil mm
-Weight (Kg):1,734
-Quality:Prime
-Help
-Location:FABRICA ALGECIRAS
-1,925.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B767"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B441"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/scraped_data.xlsx
+++ b/scraped_data.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B759"/>
+  <dimension ref="A1:B757"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -2858,25 +2858,9 @@
     <row r="155" xml:space="preserve">
       <c r="A155" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4306 304L-Coil, 2B,
-0.40 x 390.0 x coil mm</v>
+0.90 x 1271.0 x coil mm</v>
       </c>
       <c r="B155" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4306 304L-Coil, 2B,
-0.40 x 390.0 x coil mm
-Weight (Kg):1,250
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-2,075.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="156" xml:space="preserve">
-      <c r="A156" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4306 304L-Coil, 2B,
-0.90 x 1271.0 x coil mm</v>
-      </c>
-      <c r="B156" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4306 304L-Coil, 2B,
 0.90 x 1271.0 x coil mm
 Weight (Kg):3,100
@@ -2887,12 +2871,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="157" xml:space="preserve">
-      <c r="A157" t="str" xml:space="preserve">
+    <row r="156" xml:space="preserve">
+      <c r="A156" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L-Sheet, SB-G-500,
 3.00 x 1500.0 x 3000.0 mm</v>
       </c>
-      <c r="B157" t="str" xml:space="preserve">
+      <c r="B156" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L-Sheet, SB-G-500,
 3.00 x 1500.0 x 3000.0 mm
 Weight (Kg):1,466
@@ -2903,15 +2887,31 @@
 Add to cart</v>
       </c>
     </row>
+    <row r="157" xml:space="preserve">
+      <c r="A157" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Coil, 2B,
+0.80 x 150.9 x coil mm</v>
+      </c>
+      <c r="B157" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Coil, 2B,
+0.80 x 150.9 x coil mm
+Weight (Kg):670
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,075.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
     <row r="158" xml:space="preserve">
       <c r="A158" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Coil, 2B,
-0.80 x 150.9 x coil mm</v>
+1.00 x 125.9 x coil mm</v>
       </c>
       <c r="B158" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Coil, 2B,
-0.80 x 150.9 x coil mm
-Weight (Kg):670
+1.00 x 125.9 x coil mm
+Weight (Kg):568
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -2922,12 +2922,12 @@
     <row r="159" xml:space="preserve">
       <c r="A159" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Coil, 2B,
-1.00 x 125.9 x coil mm</v>
+1.00 x 135.9 x coil mm</v>
       </c>
       <c r="B159" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Coil, 2B,
-1.00 x 125.9 x coil mm
-Weight (Kg):568
+1.00 x 135.9 x coil mm
+Weight (Kg):538
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -2938,13 +2938,13 @@
     <row r="160" xml:space="preserve">
       <c r="A160" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Coil, 2B,
-1.00 x 135.9 x coil mm</v>
+1.40 x 101.0 x coil mm</v>
       </c>
       <c r="B160" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Coil, 2B,
-1.00 x 135.9 x coil mm
-Weight (Kg):538
-Quality:Prime-2
+1.40 x 101.0 x coil mm
+Weight (Kg):504
+Quality:Prime
 Help
 Location:FABRICA ALGECIRAS
 2,075.00 €/ton
@@ -2970,12 +2970,12 @@
     <row r="162" xml:space="preserve">
       <c r="A162" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Coil, 2B,
-1.40 x 101.0 x coil mm</v>
+1.40 x 105.0 x coil mm</v>
       </c>
       <c r="B162" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Coil, 2B,
-1.40 x 101.0 x coil mm
-Weight (Kg):504
+1.40 x 105.0 x coil mm
+Weight (Kg):530
 Quality:Prime
 Help
 Location:FABRICA ALGECIRAS
@@ -2986,12 +2986,12 @@
     <row r="163" xml:space="preserve">
       <c r="A163" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Coil, 2B,
-1.40 x 105.0 x coil mm</v>
+1.40 x 110.9 x coil mm</v>
       </c>
       <c r="B163" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Coil, 2B,
-1.40 x 105.0 x coil mm
-Weight (Kg):530
+1.40 x 110.9 x coil mm
+Weight (Kg):616
 Quality:Prime
 Help
 Location:FABRICA ALGECIRAS
@@ -3002,44 +3002,44 @@
     <row r="164" xml:space="preserve">
       <c r="A164" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Coil, 2B,
-1.40 x 110.9 x coil mm</v>
+1.50 x 1289.0 x coil mm</v>
       </c>
       <c r="B164" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Coil, 2B,
-1.40 x 110.9 x coil mm
-Weight (Kg):616
-Quality:Prime
-Help
-Location:FABRICA ALGECIRAS
-2,075.00 €/ton
+1.50 x 1289.0 x coil mm
+Weight (Kg):3,070
+Quality:Prime
+Help
+Location:FABRICA ALGECIRAS
+2,425.00 €/ton
 Add to cart</v>
       </c>
     </row>
     <row r="165" xml:space="preserve">
       <c r="A165" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Coil, 2B,
-1.50 x 1289.0 x coil mm</v>
+1.50 x 200.9 x coil mm</v>
       </c>
       <c r="B165" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Coil, 2B,
-1.50 x 1289.0 x coil mm
-Weight (Kg):3,070
-Quality:Prime
-Help
-Location:FABRICA ALGECIRAS
-2,425.00 €/ton
+1.50 x 200.9 x coil mm
+Weight (Kg):964
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,075.00 €/ton
 Add to cart</v>
       </c>
     </row>
     <row r="166" xml:space="preserve">
       <c r="A166" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Coil, 2B,
-1.50 x 200.9 x coil mm</v>
+1.50 x 230.9 x coil mm</v>
       </c>
       <c r="B166" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Coil, 2B,
-1.50 x 200.9 x coil mm
-Weight (Kg):964
+1.50 x 230.9 x coil mm
+Weight (Kg):4,140
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -3050,12 +3050,12 @@
     <row r="167" xml:space="preserve">
       <c r="A167" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Coil, 2B,
-1.50 x 230.9 x coil mm</v>
+1.80 x 102.0 x coil mm</v>
       </c>
       <c r="B167" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Coil, 2B,
-1.50 x 230.9 x coil mm
-Weight (Kg):4,140
+1.80 x 102.0 x coil mm
+Weight (Kg):794
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -3066,32 +3066,32 @@
     <row r="168" xml:space="preserve">
       <c r="A168" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Coil, 2B,
-1.80 x 102.0 x coil mm</v>
+2.00 x 1277.0 x coil mm</v>
       </c>
       <c r="B168" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Coil, 2B,
-1.80 x 102.0 x coil mm
-Weight (Kg):794
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-2,075.00 €/ton
+2.00 x 1277.0 x coil mm
+Weight (Kg):2,940
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,225.00 €/ton
 Add to cart</v>
       </c>
     </row>
     <row r="169" xml:space="preserve">
       <c r="A169" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Coil, 2B,
-2.00 x 1277.0 x coil mm</v>
+2.00 x 553.0 x coil mm</v>
       </c>
       <c r="B169" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Coil, 2B,
-2.00 x 1277.0 x coil mm
-Weight (Kg):2,940
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-2,225.00 €/ton
+2.00 x 553.0 x coil mm
+Weight (Kg):385
+Quality:Downgraded
+Help
+Location:FABRICA ALGECIRAS
+2,025.00 €/ton
 Add to cart</v>
       </c>
     </row>
@@ -3114,44 +3114,44 @@
     <row r="171" xml:space="preserve">
       <c r="A171" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Coil, 2B,
-2.00 x 553.0 x coil mm</v>
+2.50 x 1000.0 x coil mm</v>
       </c>
       <c r="B171" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Coil, 2B,
-2.00 x 553.0 x coil mm
-Weight (Kg):385
-Quality:Downgraded
-Help
-Location:FABRICA ALGECIRAS
-2,025.00 €/ton
+2.50 x 1000.0 x coil mm
+Weight (Kg):2,280
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,225.00 €/ton
 Add to cart</v>
       </c>
     </row>
     <row r="172" xml:space="preserve">
       <c r="A172" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Coil, 2B,
-2.50 x 1000.0 x coil mm</v>
+5.00 x 265.9 x coil mm</v>
       </c>
       <c r="B172" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Coil, 2B,
-2.50 x 1000.0 x coil mm
-Weight (Kg):2,280
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-2,225.00 €/ton
+5.00 x 265.9 x coil mm
+Weight (Kg):1,596
+Quality:Prime
+Help
+Location:FABRICA ALGECIRAS
+2,075.00 €/ton
 Add to cart</v>
       </c>
     </row>
     <row r="173" xml:space="preserve">
       <c r="A173" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Coil, 2B,
-5.00 x 265.9 x coil mm</v>
+5.00 x 286.0 x coil mm</v>
       </c>
       <c r="B173" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Coil, 2B,
-5.00 x 265.9 x coil mm
-Weight (Kg):1,596
+5.00 x 286.0 x coil mm
+Weight (Kg):2,451
 Quality:Prime
 Help
 Location:FABRICA ALGECIRAS
@@ -3168,7 +3168,7 @@
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Coil, 2B,
 5.00 x 286.0 x coil mm
 Weight (Kg):2,451
-Quality:Prime
+Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
 2,075.00 €/ton
@@ -3178,16 +3178,16 @@
     <row r="175" xml:space="preserve">
       <c r="A175" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Coil, 2B,
-5.00 x 286.0 x coil mm</v>
+6.00 x 1500.0 x coil mm</v>
       </c>
       <c r="B175" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Coil, 2B,
-5.00 x 286.0 x coil mm
-Weight (Kg):2,451
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-2,075.00 €/ton
+6.00 x 1500.0 x coil mm
+Weight (Kg):1,700
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,225.00 €/ton
 Add to cart</v>
       </c>
     </row>
@@ -3199,7 +3199,7 @@
       <c r="B176" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Coil, 2B,
 6.00 x 1500.0 x coil mm
-Weight (Kg):1,700
+Weight (Kg):2,355
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -3215,7 +3215,7 @@
       <c r="B177" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Coil, 2B,
 6.00 x 1500.0 x coil mm
-Weight (Kg):2,355
+Weight (Kg):2,375
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -3231,7 +3231,7 @@
       <c r="B178" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Coil, 2B,
 6.00 x 1500.0 x coil mm
-Weight (Kg):2,375
+Weight (Kg):2,204
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -3263,7 +3263,7 @@
       <c r="B180" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Coil, 2B,
 6.00 x 1500.0 x coil mm
-Weight (Kg):2,204
+Weight (Kg):2,844
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -3274,41 +3274,25 @@
     <row r="181" xml:space="preserve">
       <c r="A181" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Coil, 2B,
-6.00 x 1500.0 x coil mm</v>
+6.00 x 220.0 x coil mm</v>
       </c>
       <c r="B181" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Coil, 2B,
-6.00 x 1500.0 x coil mm
-Weight (Kg):2,844
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-2,225.00 €/ton
+6.00 x 220.0 x coil mm
+Weight (Kg):4,046
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,075.00 €/ton
 Add to cart</v>
       </c>
     </row>
     <row r="182" xml:space="preserve">
       <c r="A182" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Coil, 2B,
-6.00 x 220.0 x coil mm</v>
+6.00 x 250.0 x coil mm</v>
       </c>
       <c r="B182" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Coil, 2B,
-6.00 x 220.0 x coil mm
-Weight (Kg):4,046
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-2,075.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="183" xml:space="preserve">
-      <c r="A183" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Coil, 2B,
-6.00 x 250.0 x coil mm</v>
-      </c>
-      <c r="B183" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Coil, 2B,
 6.00 x 250.0 x coil mm
 Weight (Kg):3,086
@@ -3319,12 +3303,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="184" xml:space="preserve">
-      <c r="A184" t="str" xml:space="preserve">
+    <row r="183" xml:space="preserve">
+      <c r="A183" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Coil, BA,
 0.70 x 1268.0 x coil mm</v>
       </c>
-      <c r="B184" t="str" xml:space="preserve">
+      <c r="B183" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Coil, BA,
 0.70 x 1268.0 x coil mm
 Weight (Kg):20,010
@@ -3335,28 +3319,28 @@
 Add to cart</v>
       </c>
     </row>
+    <row r="184" xml:space="preserve">
+      <c r="A184" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Coil, Emboss Skin,
+0.50 x 1250.0 x coil mm</v>
+      </c>
+      <c r="B184" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Coil, Emboss Skin,
+0.50 x 1250.0 x coil mm
+Weight (Kg):3,950
+Quality:Prime
+Help
+Location:FABRICA ALGECIRAS
+2,425.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
     <row r="185" xml:space="preserve">
       <c r="A185" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Coil, Emboss Skin,
-0.50 x 1250.0 x coil mm</v>
+0.50 x 1261.0 x coil mm</v>
       </c>
       <c r="B185" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Coil, Emboss Skin,
-0.50 x 1250.0 x coil mm
-Weight (Kg):3,950
-Quality:Prime
-Help
-Location:FABRICA ALGECIRAS
-2,425.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="186" xml:space="preserve">
-      <c r="A186" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Coil, Emboss Skin,
-0.50 x 1261.0 x coil mm</v>
-      </c>
-      <c r="B186" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Coil, Emboss Skin,
 0.50 x 1261.0 x coil mm
 Weight (Kg):10,590
@@ -3367,19 +3351,35 @@
 Add to cart</v>
       </c>
     </row>
+    <row r="186" xml:space="preserve">
+      <c r="A186" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Coil, Nb. 1,
+4.70 x 220.0 x coil mm</v>
+      </c>
+      <c r="B186" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Coil, Nb. 1,
+4.70 x 220.0 x coil mm
+Weight (Kg):3,704
+Quality:Prime
+Help
+Location:FABRICA ALGECIRAS
+1,975.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
     <row r="187" xml:space="preserve">
       <c r="A187" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Coil, Nb. 1,
-4.70 x 220.0 x coil mm</v>
+8.00 x 1500.0 x coil mm</v>
       </c>
       <c r="B187" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Coil, Nb. 1,
-4.70 x 220.0 x coil mm
-Weight (Kg):3,704
-Quality:Prime
-Help
-Location:FABRICA ALGECIRAS
-1,975.00 €/ton
+8.00 x 1500.0 x coil mm
+Weight (Kg):4,076
+Quality:Prime
+Help
+Location:FABRICA ALGECIRAS
+2,325.00 €/ton
 Add to cart</v>
       </c>
     </row>
@@ -3391,7 +3391,7 @@
       <c r="B188" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Coil, Nb. 1,
 8.00 x 1500.0 x coil mm
-Weight (Kg):4,076
+Weight (Kg):2,749
 Quality:Prime
 Help
 Location:FABRICA ALGECIRAS
@@ -3401,26 +3401,10 @@
     </row>
     <row r="189" xml:space="preserve">
       <c r="A189" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Coil, Nb. 1,
-8.00 x 1500.0 x coil mm</v>
-      </c>
-      <c r="B189" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Coil, Nb. 1,
-8.00 x 1500.0 x coil mm
-Weight (Kg):2,749
-Quality:Prime
-Help
-Location:FABRICA ALGECIRAS
-2,325.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="190" xml:space="preserve">
-      <c r="A190" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Coil, Nb. 2 Chequered,
 6.00 x 1250.0 x coil mm</v>
       </c>
-      <c r="B190" t="str" xml:space="preserve">
+      <c r="B189" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Coil, Nb. 2 Chequered,
 6.00 x 1250.0 x coil mm
 Weight (Kg):19,244
@@ -3431,12 +3415,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="191" xml:space="preserve">
-      <c r="A191" t="str" xml:space="preserve">
+    <row r="190" xml:space="preserve">
+      <c r="A190" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Coil, Nb. 3 Chequered,
 4.00 x 1548.0 x coil mm</v>
       </c>
-      <c r="B191" t="str" xml:space="preserve">
+      <c r="B190" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Coil, Nb. 3 Chequered,
 4.00 x 1548.0 x coil mm
 Weight (Kg):3,000
@@ -3447,28 +3431,28 @@
 Add to cart</v>
       </c>
     </row>
+    <row r="191" xml:space="preserve">
+      <c r="A191" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Coil, Polished N4-G-180,
+0.90 x 190.0 x coil mm</v>
+      </c>
+      <c r="B191" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Coil, Polished N4-G-180,
+0.90 x 190.0 x coil mm
+Weight (Kg):1,424
+Quality:Prime
+Help
+Location:FABRICA ALGECIRAS
+2,075.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
     <row r="192" xml:space="preserve">
       <c r="A192" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Coil, Polished N4-G-180,
-0.90 x 190.0 x coil mm</v>
+0.90 x 205.9 x coil mm</v>
       </c>
       <c r="B192" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Coil, Polished N4-G-180,
-0.90 x 190.0 x coil mm
-Weight (Kg):1,424
-Quality:Prime
-Help
-Location:FABRICA ALGECIRAS
-2,075.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="193" xml:space="preserve">
-      <c r="A193" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Coil, Polished N4-G-180,
-0.90 x 205.9 x coil mm</v>
-      </c>
-      <c r="B193" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Coil, Polished N4-G-180,
 0.90 x 205.9 x coil mm
 Weight (Kg):802
@@ -3479,12 +3463,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="194" xml:space="preserve">
-      <c r="A194" t="str" xml:space="preserve">
+    <row r="193" xml:space="preserve">
+      <c r="A193" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Coil, SB-G-400,
 1.00 x 154.9 x coil mm</v>
       </c>
-      <c r="B194" t="str" xml:space="preserve">
+      <c r="B193" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Coil, SB-G-400,
 1.00 x 154.9 x coil mm
 Weight (Kg):1,152
@@ -3495,12 +3479,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="195" xml:space="preserve">
-      <c r="A195" t="str" xml:space="preserve">
+    <row r="194" xml:space="preserve">
+      <c r="A194" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Coil, SB-G-500,
 0.90 x 1250.0 x coil mm</v>
       </c>
-      <c r="B195" t="str" xml:space="preserve">
+      <c r="B194" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Coil, SB-G-500,
 0.90 x 1250.0 x coil mm
 Weight (Kg):2,329
@@ -3511,6 +3495,22 @@
 Add to cart</v>
       </c>
     </row>
+    <row r="195" xml:space="preserve">
+      <c r="A195" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
+0.70 x 1500.0 x 3000.0 mm</v>
+      </c>
+      <c r="B195" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
+0.70 x 1500.0 x 3000.0 mm
+Weight (Kg):612
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,225.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
     <row r="196" xml:space="preserve">
       <c r="A196" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
@@ -3519,7 +3519,7 @@
       <c r="B196" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 0.70 x 1500.0 x 3000.0 mm
-Weight (Kg):612
+Weight (Kg):702
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -3530,12 +3530,12 @@
     <row r="197" xml:space="preserve">
       <c r="A197" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
-0.70 x 1500.0 x 3000.0 mm</v>
+0.80 x 1000.0 x 2000.0 mm</v>
       </c>
       <c r="B197" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
-0.70 x 1500.0 x 3000.0 mm
-Weight (Kg):702
+0.80 x 1000.0 x 2000.0 mm
+Weight (Kg):580
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -3546,12 +3546,12 @@
     <row r="198" xml:space="preserve">
       <c r="A198" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
-0.80 x 1000.0 x 2000.0 mm</v>
+1.00 x 1500.0 x 3000.0 mm</v>
       </c>
       <c r="B198" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
-0.80 x 1000.0 x 2000.0 mm
-Weight (Kg):580
+1.00 x 1500.0 x 3000.0 mm
+Weight (Kg):959
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -3615,7 +3615,7 @@
       <c r="B202" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 1.00 x 1500.0 x 3000.0 mm
-Weight (Kg):959
+Weight (Kg):794
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -3631,7 +3631,7 @@
       <c r="B203" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 1.00 x 1500.0 x 3000.0 mm
-Weight (Kg):794
+Weight (Kg):659
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -3647,7 +3647,7 @@
       <c r="B204" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 1.00 x 1500.0 x 3000.0 mm
-Weight (Kg):659
+Weight (Kg):1,508
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -3663,7 +3663,7 @@
       <c r="B205" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 1.00 x 1500.0 x 3000.0 mm
-Weight (Kg):1,508
+Weight (Kg):1,921
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -3679,7 +3679,7 @@
       <c r="B206" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 1.00 x 1500.0 x 3000.0 mm
-Weight (Kg):1,921
+Weight (Kg):894
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -3695,7 +3695,7 @@
       <c r="B207" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 1.00 x 1500.0 x 3000.0 mm
-Weight (Kg):894
+Weight (Kg):700
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -3711,7 +3711,7 @@
       <c r="B208" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 1.00 x 1500.0 x 3000.0 mm
-Weight (Kg):700
+Weight (Kg):842
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -3722,12 +3722,12 @@
     <row r="209" xml:space="preserve">
       <c r="A209" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
-1.00 x 1500.0 x 3000.0 mm</v>
+2.00 x 1000.0 x 2000.0 mm</v>
       </c>
       <c r="B209" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
-1.00 x 1500.0 x 3000.0 mm
-Weight (Kg):842
+2.00 x 1000.0 x 2000.0 mm
+Weight (Kg):512
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -3743,7 +3743,7 @@
       <c r="B210" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 2.00 x 1000.0 x 2000.0 mm
-Weight (Kg):512
+Weight (Kg):949
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -3754,12 +3754,12 @@
     <row r="211" xml:space="preserve">
       <c r="A211" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
-2.00 x 1000.0 x 2000.0 mm</v>
+2.00 x 1250.0 x 2500.0 mm</v>
       </c>
       <c r="B211" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
-2.00 x 1000.0 x 2000.0 mm
-Weight (Kg):949
+2.00 x 1250.0 x 2500.0 mm
+Weight (Kg):735
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -3775,7 +3775,7 @@
       <c r="B212" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 2.00 x 1250.0 x 2500.0 mm
-Weight (Kg):735
+Weight (Kg):805
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -3791,7 +3791,7 @@
       <c r="B213" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 2.00 x 1250.0 x 2500.0 mm
-Weight (Kg):805
+Weight (Kg):777
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -3807,7 +3807,7 @@
       <c r="B214" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 2.00 x 1250.0 x 2500.0 mm
-Weight (Kg):777
+Weight (Kg):576
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -3823,7 +3823,7 @@
       <c r="B215" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 2.00 x 1250.0 x 2500.0 mm
-Weight (Kg):576
+Weight (Kg):622
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -3839,7 +3839,7 @@
       <c r="B216" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 2.00 x 1250.0 x 2500.0 mm
-Weight (Kg):622
+Weight (Kg):862
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -3855,7 +3855,7 @@
       <c r="B217" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 2.00 x 1250.0 x 2500.0 mm
-Weight (Kg):862
+Weight (Kg):619
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -3871,7 +3871,7 @@
       <c r="B218" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 2.00 x 1250.0 x 2500.0 mm
-Weight (Kg):619
+Weight (Kg):867
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -3887,7 +3887,7 @@
       <c r="B219" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 2.00 x 1250.0 x 2500.0 mm
-Weight (Kg):867
+Weight (Kg):774
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -3898,12 +3898,12 @@
     <row r="220" xml:space="preserve">
       <c r="A220" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
-2.00 x 1250.0 x 2500.0 mm</v>
+2.00 x 1250.0 x 3000.0 mm</v>
       </c>
       <c r="B220" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
-2.00 x 1250.0 x 2500.0 mm
-Weight (Kg):774
+2.00 x 1250.0 x 3000.0 mm
+Weight (Kg):877
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -3914,12 +3914,12 @@
     <row r="221" xml:space="preserve">
       <c r="A221" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
-2.00 x 1250.0 x 3000.0 mm</v>
+2.50 x 1000.0 x 2000.0 mm</v>
       </c>
       <c r="B221" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
-2.00 x 1250.0 x 3000.0 mm
-Weight (Kg):877
+2.50 x 1000.0 x 2000.0 mm
+Weight (Kg):781
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -3935,7 +3935,7 @@
       <c r="B222" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 2.50 x 1000.0 x 2000.0 mm
-Weight (Kg):781
+Weight (Kg):590
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -3946,12 +3946,12 @@
     <row r="223" xml:space="preserve">
       <c r="A223" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
-2.50 x 1000.0 x 2000.0 mm</v>
+2.50 x 1250.0 x 2500.0 mm</v>
       </c>
       <c r="B223" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
-2.50 x 1000.0 x 2000.0 mm
-Weight (Kg):590
+2.50 x 1250.0 x 2500.0 mm
+Weight (Kg):660
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -3967,7 +3967,7 @@
       <c r="B224" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 2.50 x 1250.0 x 2500.0 mm
-Weight (Kg):660
+Weight (Kg):852
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -3978,12 +3978,12 @@
     <row r="225" xml:space="preserve">
       <c r="A225" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
-2.50 x 1250.0 x 2500.0 mm</v>
+2.50 x 1500.0 x 3000.0 mm</v>
       </c>
       <c r="B225" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
-2.50 x 1250.0 x 2500.0 mm
-Weight (Kg):852
+2.50 x 1500.0 x 3000.0 mm
+Weight (Kg):792
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -3999,7 +3999,7 @@
       <c r="B226" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 2.50 x 1500.0 x 3000.0 mm
-Weight (Kg):792
+Weight (Kg):1,390
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -4015,7 +4015,7 @@
       <c r="B227" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 2.50 x 1500.0 x 3000.0 mm
-Weight (Kg):1,390
+Weight (Kg):1,224
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -4031,7 +4031,7 @@
       <c r="B228" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 2.50 x 1500.0 x 3000.0 mm
-Weight (Kg):1,224
+Weight (Kg):2,098
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -4047,7 +4047,7 @@
       <c r="B229" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 2.50 x 1500.0 x 3000.0 mm
-Weight (Kg):2,098
+Weight (Kg):1,238
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -4063,7 +4063,7 @@
       <c r="B230" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 2.50 x 1500.0 x 3000.0 mm
-Weight (Kg):1,238
+Weight (Kg):856
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -4079,7 +4079,7 @@
       <c r="B231" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 2.50 x 1500.0 x 3000.0 mm
-Weight (Kg):856
+Weight (Kg):605
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -4095,7 +4095,7 @@
       <c r="B232" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 2.50 x 1500.0 x 3000.0 mm
-Weight (Kg):605
+Weight (Kg):521
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -4111,7 +4111,7 @@
       <c r="B233" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 2.50 x 1500.0 x 3000.0 mm
-Weight (Kg):521
+Weight (Kg):527
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -4127,7 +4127,7 @@
       <c r="B234" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 2.50 x 1500.0 x 3000.0 mm
-Weight (Kg):527
+Weight (Kg):862
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -4138,12 +4138,12 @@
     <row r="235" xml:space="preserve">
       <c r="A235" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
-2.50 x 1500.0 x 3000.0 mm</v>
+3.00 x 1000.0 x 2000.0 mm</v>
       </c>
       <c r="B235" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
-2.50 x 1500.0 x 3000.0 mm
-Weight (Kg):862
+3.00 x 1000.0 x 2000.0 mm
+Weight (Kg):992
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -4159,7 +4159,7 @@
       <c r="B236" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 3.00 x 1000.0 x 2000.0 mm
-Weight (Kg):992
+Weight (Kg):1,038
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -4175,7 +4175,7 @@
       <c r="B237" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 3.00 x 1000.0 x 2000.0 mm
-Weight (Kg):1,038
+Weight (Kg):946
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -4191,7 +4191,7 @@
       <c r="B238" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 3.00 x 1000.0 x 2000.0 mm
-Weight (Kg):946
+Weight (Kg):503
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -4207,7 +4207,7 @@
       <c r="B239" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 3.00 x 1000.0 x 2000.0 mm
-Weight (Kg):503
+Weight (Kg):880
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -4223,7 +4223,7 @@
       <c r="B240" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 3.00 x 1000.0 x 2000.0 mm
-Weight (Kg):880
+Weight (Kg):796
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -4239,7 +4239,7 @@
       <c r="B241" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 3.00 x 1000.0 x 2000.0 mm
-Weight (Kg):796
+Weight (Kg):578
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -4255,7 +4255,7 @@
       <c r="B242" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 3.00 x 1000.0 x 2000.0 mm
-Weight (Kg):578
+Weight (Kg):1,506
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -4271,7 +4271,7 @@
       <c r="B243" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 3.00 x 1000.0 x 2000.0 mm
-Weight (Kg):1,506
+Weight (Kg):1,538
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -4287,7 +4287,7 @@
       <c r="B244" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 3.00 x 1000.0 x 2000.0 mm
-Weight (Kg):1,538
+Weight (Kg):520
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -4298,12 +4298,12 @@
     <row r="245" xml:space="preserve">
       <c r="A245" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
-3.00 x 1000.0 x 2000.0 mm</v>
+3.00 x 1250.0 x 2500.0 mm</v>
       </c>
       <c r="B245" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
-3.00 x 1000.0 x 2000.0 mm
-Weight (Kg):520
+3.00 x 1250.0 x 2500.0 mm
+Weight (Kg):886
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -4319,7 +4319,7 @@
       <c r="B246" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 3.00 x 1250.0 x 2500.0 mm
-Weight (Kg):886
+Weight (Kg):1,233
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -4335,7 +4335,7 @@
       <c r="B247" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 3.00 x 1250.0 x 2500.0 mm
-Weight (Kg):1,233
+Weight (Kg):742
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -4351,7 +4351,7 @@
       <c r="B248" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 3.00 x 1250.0 x 2500.0 mm
-Weight (Kg):742
+Weight (Kg):858
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -4367,7 +4367,7 @@
       <c r="B249" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 3.00 x 1250.0 x 2500.0 mm
-Weight (Kg):858
+Weight (Kg):1,450
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -4383,7 +4383,7 @@
       <c r="B250" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 3.00 x 1250.0 x 2500.0 mm
-Weight (Kg):1,450
+Weight (Kg):1,818
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -4399,7 +4399,7 @@
       <c r="B251" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 3.00 x 1250.0 x 2500.0 mm
-Weight (Kg):1,818
+Weight (Kg):1,220
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -4415,7 +4415,7 @@
       <c r="B252" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 3.00 x 1250.0 x 2500.0 mm
-Weight (Kg):1,220
+Weight (Kg):812
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -4431,7 +4431,7 @@
       <c r="B253" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 3.00 x 1250.0 x 2500.0 mm
-Weight (Kg):812
+Weight (Kg):816
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -4447,7 +4447,7 @@
       <c r="B254" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 3.00 x 1250.0 x 2500.0 mm
-Weight (Kg):816
+Weight (Kg):1,320
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -4463,7 +4463,7 @@
       <c r="B255" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 3.00 x 1250.0 x 2500.0 mm
-Weight (Kg):1,320
+Weight (Kg):830
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -4479,7 +4479,7 @@
       <c r="B256" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 3.00 x 1250.0 x 2500.0 mm
-Weight (Kg):830
+Weight (Kg):1,446
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -4495,7 +4495,7 @@
       <c r="B257" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 3.00 x 1250.0 x 2500.0 mm
-Weight (Kg):1,446
+Weight (Kg):670
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -4511,7 +4511,7 @@
       <c r="B258" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 3.00 x 1250.0 x 2500.0 mm
-Weight (Kg):670
+Weight (Kg):884
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -4527,7 +4527,7 @@
       <c r="B259" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 3.00 x 1250.0 x 2500.0 mm
-Weight (Kg):884
+Weight (Kg):762
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -4538,12 +4538,12 @@
     <row r="260" xml:space="preserve">
       <c r="A260" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
-3.00 x 1250.0 x 2500.0 mm</v>
+3.00 x 1500.0 x 3000.0 mm</v>
       </c>
       <c r="B260" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
-3.00 x 1250.0 x 2500.0 mm
-Weight (Kg):762
+3.00 x 1500.0 x 3000.0 mm
+Weight (Kg):744
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -4559,7 +4559,7 @@
       <c r="B261" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 3.00 x 1500.0 x 3000.0 mm
-Weight (Kg):744
+Weight (Kg):1,394
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -4575,7 +4575,7 @@
       <c r="B262" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 3.00 x 1500.0 x 3000.0 mm
-Weight (Kg):1,394
+Weight (Kg):2,224
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -4591,7 +4591,7 @@
       <c r="B263" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 3.00 x 1500.0 x 3000.0 mm
-Weight (Kg):2,224
+Weight (Kg):1,156
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -4607,7 +4607,7 @@
       <c r="B264" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 3.00 x 1500.0 x 3000.0 mm
-Weight (Kg):1,156
+Weight (Kg):632
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -4623,7 +4623,7 @@
       <c r="B265" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 3.00 x 1500.0 x 3000.0 mm
-Weight (Kg):632
+Weight (Kg):950
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -4639,7 +4639,7 @@
       <c r="B266" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 3.00 x 1500.0 x 3000.0 mm
-Weight (Kg):950
+Weight (Kg):750
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -4655,7 +4655,7 @@
       <c r="B267" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 3.00 x 1500.0 x 3000.0 mm
-Weight (Kg):750
+Weight (Kg):1,906
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -4671,7 +4671,7 @@
       <c r="B268" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 3.00 x 1500.0 x 3000.0 mm
-Weight (Kg):1,906
+Weight (Kg):640
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -4687,7 +4687,7 @@
       <c r="B269" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 3.00 x 1500.0 x 3000.0 mm
-Weight (Kg):640
+Weight (Kg):1,496
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -4698,12 +4698,12 @@
     <row r="270" xml:space="preserve">
       <c r="A270" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
-3.00 x 1500.0 x 3000.0 mm</v>
+4.00 x 1000.0 x 2000.0 mm</v>
       </c>
       <c r="B270" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
-3.00 x 1500.0 x 3000.0 mm
-Weight (Kg):1,496
+4.00 x 1000.0 x 2000.0 mm
+Weight (Kg):1,348
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -4714,12 +4714,12 @@
     <row r="271" xml:space="preserve">
       <c r="A271" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
-4.00 x 1000.0 x 2000.0 mm</v>
+4.00 x 1500.0 x 3000.0 mm</v>
       </c>
       <c r="B271" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
-4.00 x 1000.0 x 2000.0 mm
-Weight (Kg):1,348
+4.00 x 1500.0 x 3000.0 mm
+Weight (Kg):1,574
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -4735,7 +4735,7 @@
       <c r="B272" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 4.00 x 1500.0 x 3000.0 mm
-Weight (Kg):1,574
+Weight (Kg):1,861
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -4751,7 +4751,7 @@
       <c r="B273" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 4.00 x 1500.0 x 3000.0 mm
-Weight (Kg):1,861
+Weight (Kg):1,722
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -4767,7 +4767,7 @@
       <c r="B274" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 4.00 x 1500.0 x 3000.0 mm
-Weight (Kg):1,722
+Weight (Kg):1,726
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -4783,7 +4783,7 @@
       <c r="B275" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 4.00 x 1500.0 x 3000.0 mm
-Weight (Kg):1,726
+Weight (Kg):999
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -4799,7 +4799,7 @@
       <c r="B276" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 4.00 x 1500.0 x 3000.0 mm
-Weight (Kg):999
+Weight (Kg):724
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -4815,7 +4815,7 @@
       <c r="B277" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 4.00 x 1500.0 x 3000.0 mm
-Weight (Kg):724
+Weight (Kg):854
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -4831,7 +4831,7 @@
       <c r="B278" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 4.00 x 1500.0 x 3000.0 mm
-Weight (Kg):854
+Weight (Kg):1,987
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -4847,7 +4847,7 @@
       <c r="B279" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 4.00 x 1500.0 x 3000.0 mm
-Weight (Kg):1,987
+Weight (Kg):1,708
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -4863,7 +4863,7 @@
       <c r="B280" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 4.00 x 1500.0 x 3000.0 mm
-Weight (Kg):1,708
+Weight (Kg):1,562
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -4874,12 +4874,12 @@
     <row r="281" xml:space="preserve">
       <c r="A281" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
-4.00 x 1500.0 x 3000.0 mm</v>
+5.00 x 1250.0 x 2500.0 mm</v>
       </c>
       <c r="B281" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
-4.00 x 1500.0 x 3000.0 mm
-Weight (Kg):1,562
+5.00 x 1250.0 x 2500.0 mm
+Weight (Kg):2,220
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -4895,7 +4895,7 @@
       <c r="B282" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 5.00 x 1250.0 x 2500.0 mm
-Weight (Kg):2,220
+Weight (Kg):1,580
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -4911,7 +4911,7 @@
       <c r="B283" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 5.00 x 1250.0 x 2500.0 mm
-Weight (Kg):1,580
+Weight (Kg):750
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -4922,12 +4922,12 @@
     <row r="284" xml:space="preserve">
       <c r="A284" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
-5.00 x 1250.0 x 2500.0 mm</v>
+5.00 x 1500.0 x 3000.0 mm</v>
       </c>
       <c r="B284" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
-5.00 x 1250.0 x 2500.0 mm
-Weight (Kg):750
+5.00 x 1500.0 x 3000.0 mm
+Weight (Kg):1,777
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -4943,7 +4943,7 @@
       <c r="B285" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 5.00 x 1500.0 x 3000.0 mm
-Weight (Kg):1,777
+Weight (Kg):1,436
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -4959,7 +4959,7 @@
       <c r="B286" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 5.00 x 1500.0 x 3000.0 mm
-Weight (Kg):1,436
+Weight (Kg):890
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -4975,7 +4975,7 @@
       <c r="B287" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 5.00 x 1500.0 x 3000.0 mm
-Weight (Kg):890
+Weight (Kg):1,252
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -4991,7 +4991,7 @@
       <c r="B288" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 5.00 x 1500.0 x 3000.0 mm
-Weight (Kg):1,252
+Weight (Kg):1,646
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -5007,7 +5007,7 @@
       <c r="B289" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 5.00 x 1500.0 x 3000.0 mm
-Weight (Kg):1,646
+Weight (Kg):1,434
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -5023,7 +5023,7 @@
       <c r="B290" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 5.00 x 1500.0 x 3000.0 mm
-Weight (Kg):1,434
+Weight (Kg):1,778
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -5039,7 +5039,7 @@
       <c r="B291" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 5.00 x 1500.0 x 3000.0 mm
-Weight (Kg):1,778
+Weight (Kg):1,818
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -5055,7 +5055,7 @@
       <c r="B292" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 5.00 x 1500.0 x 3000.0 mm
-Weight (Kg):1,818
+Weight (Kg):1,807
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -5071,7 +5071,7 @@
       <c r="B293" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 5.00 x 1500.0 x 3000.0 mm
-Weight (Kg):1,807
+Weight (Kg):1,978
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -5087,7 +5087,7 @@
       <c r="B294" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 5.00 x 1500.0 x 3000.0 mm
-Weight (Kg):1,978
+Weight (Kg):1,760
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -5103,7 +5103,7 @@
       <c r="B295" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 5.00 x 1500.0 x 3000.0 mm
-Weight (Kg):1,760
+Weight (Kg):1,976
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -5119,7 +5119,7 @@
       <c r="B296" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 5.00 x 1500.0 x 3000.0 mm
-Weight (Kg):1,976
+Weight (Kg):1,236
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -5135,7 +5135,7 @@
       <c r="B297" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 5.00 x 1500.0 x 3000.0 mm
-Weight (Kg):1,236
+Weight (Kg):1,968
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -5151,7 +5151,7 @@
       <c r="B298" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 5.00 x 1500.0 x 3000.0 mm
-Weight (Kg):1,968
+Weight (Kg):1,240
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -5167,7 +5167,7 @@
       <c r="B299" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 5.00 x 1500.0 x 3000.0 mm
-Weight (Kg):1,240
+Weight (Kg):1,070
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -5183,7 +5183,7 @@
       <c r="B300" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 5.00 x 1500.0 x 3000.0 mm
-Weight (Kg):1,070
+Weight (Kg):1,960
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -5199,7 +5199,7 @@
       <c r="B301" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 5.00 x 1500.0 x 3000.0 mm
-Weight (Kg):1,960
+Weight (Kg):1,734
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -5215,7 +5215,7 @@
       <c r="B302" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 5.00 x 1500.0 x 3000.0 mm
-Weight (Kg):1,734
+Weight (Kg):1,874
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -5231,7 +5231,7 @@
       <c r="B303" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 5.00 x 1500.0 x 3000.0 mm
-Weight (Kg):1,874
+Weight (Kg):884
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -5247,7 +5247,7 @@
       <c r="B304" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 5.00 x 1500.0 x 3000.0 mm
-Weight (Kg):884
+Weight (Kg):1,578
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -5263,7 +5263,7 @@
       <c r="B305" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 5.00 x 1500.0 x 3000.0 mm
-Weight (Kg):1,578
+Weight (Kg):852
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -5279,7 +5279,7 @@
       <c r="B306" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 5.00 x 1500.0 x 3000.0 mm
-Weight (Kg):852
+Weight (Kg):1,942
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -5290,12 +5290,12 @@
     <row r="307" xml:space="preserve">
       <c r="A307" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
-5.00 x 1500.0 x 3000.0 mm</v>
+6.00 x 1000.0 x 2000.0 mm</v>
       </c>
       <c r="B307" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
-5.00 x 1500.0 x 3000.0 mm
-Weight (Kg):1,942
+6.00 x 1000.0 x 2000.0 mm
+Weight (Kg):1,906
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -5311,7 +5311,7 @@
       <c r="B308" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 6.00 x 1000.0 x 2000.0 mm
-Weight (Kg):1,906
+Weight (Kg):1,886
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -5327,7 +5327,7 @@
       <c r="B309" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 6.00 x 1000.0 x 2000.0 mm
-Weight (Kg):1,886
+Weight (Kg):1,414
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -5343,7 +5343,7 @@
       <c r="B310" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 6.00 x 1000.0 x 2000.0 mm
-Weight (Kg):1,414
+Weight (Kg):1,620
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -5359,7 +5359,7 @@
       <c r="B311" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 6.00 x 1000.0 x 2000.0 mm
-Weight (Kg):1,620
+Weight (Kg):938
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -5375,7 +5375,7 @@
       <c r="B312" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 6.00 x 1000.0 x 2000.0 mm
-Weight (Kg):938
+Weight (Kg):1,406
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -5391,7 +5391,7 @@
       <c r="B313" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 6.00 x 1000.0 x 2000.0 mm
-Weight (Kg):1,406
+Weight (Kg):1,140
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -5402,12 +5402,12 @@
     <row r="314" xml:space="preserve">
       <c r="A314" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
-6.00 x 1000.0 x 2000.0 mm</v>
+6.00 x 1250.0 x 2500.0 mm</v>
       </c>
       <c r="B314" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
-6.00 x 1000.0 x 2000.0 mm
-Weight (Kg):1,140
+6.00 x 1250.0 x 2500.0 mm
+Weight (Kg):1,494
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -5423,7 +5423,7 @@
       <c r="B315" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 6.00 x 1250.0 x 2500.0 mm
-Weight (Kg):1,494
+Weight (Kg):1,652
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -5439,7 +5439,7 @@
       <c r="B316" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 6.00 x 1250.0 x 2500.0 mm
-Weight (Kg):1,652
+Weight (Kg):1,610
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -5455,7 +5455,7 @@
       <c r="B317" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 6.00 x 1250.0 x 2500.0 mm
-Weight (Kg):1,610
+Weight (Kg):1,900
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -5471,7 +5471,7 @@
       <c r="B318" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 6.00 x 1250.0 x 2500.0 mm
-Weight (Kg):1,900
+Weight (Kg):2,346
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -5487,7 +5487,7 @@
       <c r="B319" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 6.00 x 1250.0 x 2500.0 mm
-Weight (Kg):2,346
+Weight (Kg):1,624
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -5498,12 +5498,12 @@
     <row r="320" xml:space="preserve">
       <c r="A320" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
-6.00 x 1250.0 x 2500.0 mm</v>
+6.00 x 1500.0 x 3000.0 mm</v>
       </c>
       <c r="B320" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
-6.00 x 1250.0 x 2500.0 mm
-Weight (Kg):1,624
+6.00 x 1500.0 x 3000.0 mm
+Weight (Kg):1,296
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -5519,7 +5519,7 @@
       <c r="B321" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 6.00 x 1500.0 x 3000.0 mm
-Weight (Kg):1,296
+Weight (Kg):1,716
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -5535,7 +5535,7 @@
       <c r="B322" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 6.00 x 1500.0 x 3000.0 mm
-Weight (Kg):1,716
+Weight (Kg):1,917
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -5551,7 +5551,7 @@
       <c r="B323" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 6.00 x 1500.0 x 3000.0 mm
-Weight (Kg):1,917
+Weight (Kg):1,922
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -5567,7 +5567,7 @@
       <c r="B324" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 6.00 x 1500.0 x 3000.0 mm
-Weight (Kg):1,922
+Weight (Kg):1,728
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -5583,7 +5583,7 @@
       <c r="B325" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 6.00 x 1500.0 x 3000.0 mm
-Weight (Kg):1,728
+Weight (Kg):864
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -5599,7 +5599,7 @@
       <c r="B326" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 6.00 x 1500.0 x 3000.0 mm
-Weight (Kg):864
+Weight (Kg):1,302
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -5615,7 +5615,7 @@
       <c r="B327" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 6.00 x 1500.0 x 3000.0 mm
-Weight (Kg):1,302
+Weight (Kg):1,062
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -5631,7 +5631,7 @@
       <c r="B328" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 6.00 x 1500.0 x 3000.0 mm
-Weight (Kg):1,062
+Weight (Kg):1,966
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -5647,7 +5647,7 @@
       <c r="B329" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 6.00 x 1500.0 x 3000.0 mm
-Weight (Kg):1,966
+Weight (Kg):1,496
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -5663,7 +5663,7 @@
       <c r="B330" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 6.00 x 1500.0 x 3000.0 mm
-Weight (Kg):1,496
+Weight (Kg):1,320
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -5679,7 +5679,7 @@
       <c r="B331" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 6.00 x 1500.0 x 3000.0 mm
-Weight (Kg):1,320
+Weight (Kg):1,071
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -5695,7 +5695,7 @@
       <c r="B332" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 6.00 x 1500.0 x 3000.0 mm
-Weight (Kg):1,071
+Weight (Kg):1,264
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -5711,7 +5711,7 @@
       <c r="B333" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 6.00 x 1500.0 x 3000.0 mm
-Weight (Kg):1,264
+Weight (Kg):1,916
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -5727,7 +5727,7 @@
       <c r="B334" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 6.00 x 1500.0 x 3000.0 mm
-Weight (Kg):1,916
+Weight (Kg):1,908
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -5743,7 +5743,7 @@
       <c r="B335" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 6.00 x 1500.0 x 3000.0 mm
-Weight (Kg):1,908
+Weight (Kg):1,928
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -5759,7 +5759,7 @@
       <c r="B336" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 6.00 x 1500.0 x 3000.0 mm
-Weight (Kg):1,928
+Weight (Kg):1,290
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -5775,7 +5775,7 @@
       <c r="B337" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 6.00 x 1500.0 x 3000.0 mm
-Weight (Kg):1,290
+Weight (Kg):1,698
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -5791,7 +5791,7 @@
       <c r="B338" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 6.00 x 1500.0 x 3000.0 mm
-Weight (Kg):1,698
+Weight (Kg):1,754
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -5807,7 +5807,7 @@
       <c r="B339" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 6.00 x 1500.0 x 3000.0 mm
-Weight (Kg):1,754
+Weight (Kg):1,716
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -5823,7 +5823,7 @@
       <c r="B340" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 6.00 x 1500.0 x 3000.0 mm
-Weight (Kg):1,716
+Weight (Kg):1,548
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -5839,7 +5839,7 @@
       <c r="B341" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 6.00 x 1500.0 x 3000.0 mm
-Weight (Kg):1,548
+Weight (Kg):1,916
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -5855,7 +5855,7 @@
       <c r="B342" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 6.00 x 1500.0 x 3000.0 mm
-Weight (Kg):1,916
+Weight (Kg):1,485
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -5871,7 +5871,7 @@
       <c r="B343" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 6.00 x 1500.0 x 3000.0 mm
-Weight (Kg):1,485
+Weight (Kg):1,940
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -5887,7 +5887,7 @@
       <c r="B344" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 6.00 x 1500.0 x 3000.0 mm
-Weight (Kg):1,940
+Weight (Kg):1,762
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -5903,7 +5903,7 @@
       <c r="B345" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 6.00 x 1500.0 x 3000.0 mm
-Weight (Kg):1,762
+Weight (Kg):1,918
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -5919,7 +5919,7 @@
       <c r="B346" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 6.00 x 1500.0 x 3000.0 mm
-Weight (Kg):1,918
+Weight (Kg):1,306
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -5935,7 +5935,7 @@
       <c r="B347" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 6.00 x 1500.0 x 3000.0 mm
-Weight (Kg):1,306
+Weight (Kg):1,066
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -5951,7 +5951,7 @@
       <c r="B348" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 6.00 x 1500.0 x 3000.0 mm
-Weight (Kg):1,066
+Weight (Kg):1,936
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -5967,7 +5967,7 @@
       <c r="B349" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 6.00 x 1500.0 x 3000.0 mm
-Weight (Kg):1,936
+Weight (Kg):2,390
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -5983,7 +5983,7 @@
       <c r="B350" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 6.00 x 1500.0 x 3000.0 mm
-Weight (Kg):2,390
+Weight (Kg):1,728
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -5999,7 +5999,7 @@
       <c r="B351" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 6.00 x 1500.0 x 3000.0 mm
-Weight (Kg):1,728
+Weight (Kg):1,514
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -6015,7 +6015,7 @@
       <c r="B352" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 6.00 x 1500.0 x 3000.0 mm
-Weight (Kg):1,514
+Weight (Kg):1,922
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -6031,7 +6031,7 @@
       <c r="B353" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 6.00 x 1500.0 x 3000.0 mm
-Weight (Kg):1,922
+Weight (Kg):1,942
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -6047,7 +6047,7 @@
       <c r="B354" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 6.00 x 1500.0 x 3000.0 mm
-Weight (Kg):1,942
+Weight (Kg):2,114
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -6063,7 +6063,7 @@
       <c r="B355" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 6.00 x 1500.0 x 3000.0 mm
-Weight (Kg):2,114
+Weight (Kg):1,088
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -6079,7 +6079,7 @@
       <c r="B356" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 6.00 x 1500.0 x 3000.0 mm
-Weight (Kg):1,088
+Weight (Kg):1,274
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -6095,7 +6095,7 @@
       <c r="B357" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 6.00 x 1500.0 x 3000.0 mm
-Weight (Kg):1,274
+Weight (Kg):1,718
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -6111,7 +6111,7 @@
       <c r="B358" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 6.00 x 1500.0 x 3000.0 mm
-Weight (Kg):1,718
+Weight (Kg):1,922
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -6127,7 +6127,7 @@
       <c r="B359" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 6.00 x 1500.0 x 3000.0 mm
-Weight (Kg):1,922
+Weight (Kg):1,878
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -6143,7 +6143,7 @@
       <c r="B360" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 6.00 x 1500.0 x 3000.0 mm
-Weight (Kg):1,878
+Weight (Kg):1,714
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -6159,7 +6159,7 @@
       <c r="B361" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 6.00 x 1500.0 x 3000.0 mm
-Weight (Kg):1,714
+Weight (Kg):1,918
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -6175,7 +6175,7 @@
       <c r="B362" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 6.00 x 1500.0 x 3000.0 mm
-Weight (Kg):1,918
+Weight (Kg):1,754
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -6191,7 +6191,7 @@
       <c r="B363" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 6.00 x 1500.0 x 3000.0 mm
-Weight (Kg):1,754
+Weight (Kg):1,528
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -6207,7 +6207,7 @@
       <c r="B364" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 6.00 x 1500.0 x 3000.0 mm
-Weight (Kg):1,528
+Weight (Kg):2,136
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -6223,7 +6223,7 @@
       <c r="B365" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 6.00 x 1500.0 x 3000.0 mm
-Weight (Kg):2,136
+Weight (Kg):1,946
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -6233,13 +6233,13 @@
     </row>
     <row r="366" xml:space="preserve">
       <c r="A366" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
-6.00 x 1500.0 x 3000.0 mm</v>
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, BA,
+0.80 x 1000.0 x 2000.0 mm</v>
       </c>
       <c r="B366" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
-6.00 x 1500.0 x 3000.0 mm
-Weight (Kg):1,946
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, BA,
+0.80 x 1000.0 x 2000.0 mm
+Weight (Kg):1,633
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -6255,7 +6255,7 @@
       <c r="B367" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, BA,
 0.80 x 1000.0 x 2000.0 mm
-Weight (Kg):1,633
+Weight (Kg):1,286
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -6271,7 +6271,7 @@
       <c r="B368" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, BA,
 0.80 x 1000.0 x 2000.0 mm
-Weight (Kg):1,286
+Weight (Kg):727
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -6282,12 +6282,12 @@
     <row r="369" xml:space="preserve">
       <c r="A369" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, BA,
-0.80 x 1000.0 x 2000.0 mm</v>
+1.00 x 1000.0 x 2000.0 mm</v>
       </c>
       <c r="B369" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, BA,
-0.80 x 1000.0 x 2000.0 mm
-Weight (Kg):727
+1.00 x 1000.0 x 2000.0 mm
+Weight (Kg):650
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -6303,7 +6303,7 @@
       <c r="B370" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, BA,
 1.00 x 1000.0 x 2000.0 mm
-Weight (Kg):650
+Weight (Kg):869
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -6319,7 +6319,7 @@
       <c r="B371" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, BA,
 1.00 x 1000.0 x 2000.0 mm
-Weight (Kg):869
+Weight (Kg):885
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -6335,7 +6335,7 @@
       <c r="B372" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, BA,
 1.00 x 1000.0 x 2000.0 mm
-Weight (Kg):885
+Weight (Kg):931
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -6346,12 +6346,12 @@
     <row r="373" xml:space="preserve">
       <c r="A373" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, BA,
-1.00 x 1000.0 x 2000.0 mm</v>
+1.00 x 1250.0 x 3000.0 mm</v>
       </c>
       <c r="B373" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, BA,
-1.00 x 1000.0 x 2000.0 mm
-Weight (Kg):931
+1.00 x 1250.0 x 3000.0 mm
+Weight (Kg):766
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -6367,7 +6367,7 @@
       <c r="B374" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, BA,
 1.00 x 1250.0 x 3000.0 mm
-Weight (Kg):766
+Weight (Kg):1,417
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -6378,12 +6378,12 @@
     <row r="375" xml:space="preserve">
       <c r="A375" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, BA,
-1.00 x 1250.0 x 3000.0 mm</v>
+1.50 x 1000.0 x 2000.0 mm</v>
       </c>
       <c r="B375" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, BA,
-1.00 x 1250.0 x 3000.0 mm
-Weight (Kg):1,417
+1.50 x 1000.0 x 2000.0 mm
+Weight (Kg):1,459
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -6399,7 +6399,7 @@
       <c r="B376" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, BA,
 1.50 x 1000.0 x 2000.0 mm
-Weight (Kg):1,459
+Weight (Kg):825
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -6415,7 +6415,7 @@
       <c r="B377" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, BA,
 1.50 x 1000.0 x 2000.0 mm
-Weight (Kg):825
+Weight (Kg):738
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -6431,7 +6431,7 @@
       <c r="B378" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, BA,
 1.50 x 1000.0 x 2000.0 mm
-Weight (Kg):738
+Weight (Kg):886
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -6447,7 +6447,7 @@
       <c r="B379" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, BA,
 1.50 x 1000.0 x 2000.0 mm
-Weight (Kg):886
+Weight (Kg):1,116
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -6463,7 +6463,7 @@
       <c r="B380" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, BA,
 1.50 x 1000.0 x 2000.0 mm
-Weight (Kg):1,116
+Weight (Kg):692
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -6479,7 +6479,7 @@
       <c r="B381" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, BA,
 1.50 x 1000.0 x 2000.0 mm
-Weight (Kg):692
+Weight (Kg):1,613
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -6495,7 +6495,7 @@
       <c r="B382" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, BA,
 1.50 x 1000.0 x 2000.0 mm
-Weight (Kg):1,613
+Weight (Kg):946
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -6506,12 +6506,12 @@
     <row r="383" xml:space="preserve">
       <c r="A383" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, BA,
-1.50 x 1000.0 x 2000.0 mm</v>
+1.50 x 1250.0 x 2500.0 mm</v>
       </c>
       <c r="B383" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, BA,
-1.50 x 1000.0 x 2000.0 mm
-Weight (Kg):946
+1.50 x 1250.0 x 2500.0 mm
+Weight (Kg):1,628
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -6522,25 +6522,9 @@
     <row r="384" xml:space="preserve">
       <c r="A384" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, BA,
-1.50 x 1250.0 x 2500.0 mm</v>
+1.80 x 1000.0 x 2000.0 mm</v>
       </c>
       <c r="B384" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, BA,
-1.50 x 1250.0 x 2500.0 mm
-Weight (Kg):1,628
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-2,225.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="385" xml:space="preserve">
-      <c r="A385" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, BA,
-1.80 x 1000.0 x 2000.0 mm</v>
-      </c>
-      <c r="B385" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, BA,
 1.80 x 1000.0 x 2000.0 mm
 Weight (Kg):1,405
@@ -6551,12 +6535,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="386" xml:space="preserve">
-      <c r="A386" t="str" xml:space="preserve">
+    <row r="385" xml:space="preserve">
+      <c r="A385" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, Nb. 1,
 3.00 x 1500.0 x 3000.0 mm</v>
       </c>
-      <c r="B386" t="str" xml:space="preserve">
+      <c r="B385" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, Nb. 1,
 3.00 x 1500.0 x 3000.0 mm
 Weight (Kg):1,728
@@ -6564,6 +6548,22 @@
 Help
 Location:FABRICA ALGECIRAS
 2,125.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="386" xml:space="preserve">
+      <c r="A386" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, Nb. 3 Chequered,
+4.50 x 1250.0 x 3000.0 mm</v>
+      </c>
+      <c r="B386" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, Nb. 3 Chequered,
+4.50 x 1250.0 x 3000.0 mm
+Weight (Kg):1,046
+Quality:Prime
+Help
+Location:FABRICA ALGECIRAS
+2,900.00 €/ton
 Add to cart</v>
       </c>
     </row>
@@ -6575,7 +6575,7 @@
       <c r="B387" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, Nb. 3 Chequered,
 4.50 x 1250.0 x 3000.0 mm
-Weight (Kg):1,046
+Weight (Kg):1,316
 Quality:Prime
 Help
 Location:FABRICA ALGECIRAS
@@ -6585,29 +6585,29 @@
     </row>
     <row r="388" xml:space="preserve">
       <c r="A388" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, Nb. 3 Chequered,
-4.50 x 1250.0 x 3000.0 mm</v>
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, Polished N4-G-240,
+0.80 x 1500.0 x 3000.0 mm</v>
       </c>
       <c r="B388" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, Nb. 3 Chequered,
-4.50 x 1250.0 x 3000.0 mm
-Weight (Kg):1,316
-Quality:Prime
-Help
-Location:FABRICA ALGECIRAS
-2,900.00 €/ton
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, Polished N4-G-240,
+0.80 x 1500.0 x 3000.0 mm
+Weight (Kg):630
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,225.00 €/ton
 Add to cart</v>
       </c>
     </row>
     <row r="389" xml:space="preserve">
       <c r="A389" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, Polished N4-G-240,
-0.80 x 1500.0 x 3000.0 mm</v>
+0.90 x 1500.0 x 3000.0 mm</v>
       </c>
       <c r="B389" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, Polished N4-G-240,
-0.80 x 1500.0 x 3000.0 mm
-Weight (Kg):630
+0.90 x 1500.0 x 3000.0 mm
+Weight (Kg):807
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -6623,7 +6623,7 @@
       <c r="B390" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, Polished N4-G-240,
 0.90 x 1500.0 x 3000.0 mm
-Weight (Kg):807
+Weight (Kg):622
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -6633,13 +6633,13 @@
     </row>
     <row r="391" xml:space="preserve">
       <c r="A391" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, Polished N4-G-240,
-0.90 x 1500.0 x 3000.0 mm</v>
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, SB-G-400,
+1.50 x 1000.0 x 2000.0 mm</v>
       </c>
       <c r="B391" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, Polished N4-G-240,
-0.90 x 1500.0 x 3000.0 mm
-Weight (Kg):622
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, SB-G-400,
+1.50 x 1000.0 x 2000.0 mm
+Weight (Kg):674
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -6655,7 +6655,7 @@
       <c r="B392" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, SB-G-400,
 1.50 x 1000.0 x 2000.0 mm
-Weight (Kg):674
+Weight (Kg):535
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -6666,12 +6666,12 @@
     <row r="393" xml:space="preserve">
       <c r="A393" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, SB-G-400,
-1.50 x 1000.0 x 2000.0 mm</v>
+3.00 x 1500.0 x 3000.0 mm</v>
       </c>
       <c r="B393" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, SB-G-400,
-1.50 x 1000.0 x 2000.0 mm
-Weight (Kg):535
+3.00 x 1500.0 x 3000.0 mm
+Weight (Kg):1,877
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -6687,7 +6687,7 @@
       <c r="B394" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, SB-G-400,
 3.00 x 1500.0 x 3000.0 mm
-Weight (Kg):1,877
+Weight (Kg):629
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -6703,7 +6703,7 @@
       <c r="B395" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, SB-G-400,
 3.00 x 1500.0 x 3000.0 mm
-Weight (Kg):629
+Weight (Kg):1,887
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -6713,13 +6713,13 @@
     </row>
     <row r="396" xml:space="preserve">
       <c r="A396" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, SB-G-400,
-3.00 x 1500.0 x 3000.0 mm</v>
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, SB-G-500,
+0.70 x 1500.0 x 3000.0 mm</v>
       </c>
       <c r="B396" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, SB-G-400,
-3.00 x 1500.0 x 3000.0 mm
-Weight (Kg):1,887
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, SB-G-500,
+0.70 x 1500.0 x 3000.0 mm
+Weight (Kg):1,226
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -6735,7 +6735,7 @@
       <c r="B397" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, SB-G-500,
 0.70 x 1500.0 x 3000.0 mm
-Weight (Kg):1,226
+Weight (Kg):1,001
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -6751,7 +6751,7 @@
       <c r="B398" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, SB-G-500,
 0.70 x 1500.0 x 3000.0 mm
-Weight (Kg):1,001
+Weight (Kg):681
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -6767,7 +6767,7 @@
       <c r="B399" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, SB-G-500,
 0.70 x 1500.0 x 3000.0 mm
-Weight (Kg):681
+Weight (Kg):673
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -6783,7 +6783,7 @@
       <c r="B400" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, SB-G-500,
 0.70 x 1500.0 x 3000.0 mm
-Weight (Kg):673
+Weight (Kg):722
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -6810,12 +6810,12 @@
     <row r="402" xml:space="preserve">
       <c r="A402" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, SB-G-500,
-0.70 x 1500.0 x 3000.0 mm</v>
+0.80 x 1000.0 x 2000.0 mm</v>
       </c>
       <c r="B402" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, SB-G-500,
-0.70 x 1500.0 x 3000.0 mm
-Weight (Kg):722
+0.80 x 1000.0 x 2000.0 mm
+Weight (Kg):1,256
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -6826,12 +6826,12 @@
     <row r="403" xml:space="preserve">
       <c r="A403" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, SB-G-500,
-0.80 x 1000.0 x 2000.0 mm</v>
+0.80 x 1250.0 x 3000.0 mm</v>
       </c>
       <c r="B403" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, SB-G-500,
-0.80 x 1000.0 x 2000.0 mm
-Weight (Kg):1,256
+0.80 x 1250.0 x 3000.0 mm
+Weight (Kg):535
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -6842,25 +6842,9 @@
     <row r="404" xml:space="preserve">
       <c r="A404" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, SB-G-500,
-0.80 x 1250.0 x 3000.0 mm</v>
+3.00 x 1500.0 x 3000.0 mm</v>
       </c>
       <c r="B404" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, SB-G-500,
-0.80 x 1250.0 x 3000.0 mm
-Weight (Kg):535
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-2,225.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="405" xml:space="preserve">
-      <c r="A405" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, SB-G-500,
-3.00 x 1500.0 x 3000.0 mm</v>
-      </c>
-      <c r="B405" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, SB-G-500,
 3.00 x 1500.0 x 3000.0 mm
 Weight (Kg):839
@@ -6871,12 +6855,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="406" xml:space="preserve">
-      <c r="A406" t="str" xml:space="preserve">
+    <row r="405" xml:space="preserve">
+      <c r="A405" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Untrimmed, Coil,
 0.80 x 1271.0 x coil mm</v>
       </c>
-      <c r="B406" t="str" xml:space="preserve">
+      <c r="B405" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Untrimmed, Coil,
 0.80 x 1271.0 x coil mm
 Weight (Kg):2,950
@@ -6887,15 +6871,31 @@
 Add to cart</v>
       </c>
     </row>
+    <row r="406" xml:space="preserve">
+      <c r="A406" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Untrimmed, Coil, 2B,
+1.20 x 1277.0 x coil mm</v>
+      </c>
+      <c r="B406" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Untrimmed, Coil, 2B,
+1.20 x 1277.0 x coil mm
+Weight (Kg):2,230
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,225.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
     <row r="407" xml:space="preserve">
       <c r="A407" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Untrimmed, Coil, 2B,
-1.20 x 1277.0 x coil mm</v>
+2.00 x 1275.0 x coil mm</v>
       </c>
       <c r="B407" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Untrimmed, Coil, 2B,
-1.20 x 1277.0 x coil mm
-Weight (Kg):2,230
+2.00 x 1275.0 x coil mm
+Weight (Kg):2,619
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -6906,12 +6906,12 @@
     <row r="408" xml:space="preserve">
       <c r="A408" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Untrimmed, Coil, 2B,
-2.00 x 1275.0 x coil mm</v>
+5.00 x 1540.0 x coil mm</v>
       </c>
       <c r="B408" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Untrimmed, Coil, 2B,
-2.00 x 1275.0 x coil mm
-Weight (Kg):2,619
+5.00 x 1540.0 x coil mm
+Weight (Kg):7,140
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -6927,7 +6927,7 @@
       <c r="B409" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Untrimmed, Coil, 2B,
 5.00 x 1540.0 x coil mm
-Weight (Kg):7,140
+Weight (Kg):13,250
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -6937,26 +6937,10 @@
     </row>
     <row r="410" xml:space="preserve">
       <c r="A410" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Untrimmed, Coil, 2B,
-5.00 x 1540.0 x coil mm</v>
-      </c>
-      <c r="B410" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Untrimmed, Coil, 2B,
-5.00 x 1540.0 x coil mm
-Weight (Kg):13,250
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-2,225.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="411" xml:space="preserve">
-      <c r="A411" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Untrimmed, Coil, 2D,
 1.00 x 1027.0 x coil mm</v>
       </c>
-      <c r="B411" t="str" xml:space="preserve">
+      <c r="B410" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Untrimmed, Coil, 2D,
 1.00 x 1027.0 x coil mm
 Weight (Kg):2,410
@@ -6967,44 +6951,44 @@
 Add to cart</v>
       </c>
     </row>
+    <row r="411" xml:space="preserve">
+      <c r="A411" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Untrimmed, Coil, BA,
+0.40 x 1017.0 x coil mm</v>
+      </c>
+      <c r="B411" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Untrimmed, Coil, BA,
+0.40 x 1017.0 x coil mm
+Weight (Kg):5,705
+Quality:Prime
+Help
+Location:FABRICA ALGECIRAS
+2,425.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
     <row r="412" xml:space="preserve">
       <c r="A412" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Untrimmed, Coil, BA,
-0.40 x 1017.0 x coil mm</v>
+0.90 x 1275.0 x coil mm</v>
       </c>
       <c r="B412" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Untrimmed, Coil, BA,
-0.40 x 1017.0 x coil mm
-Weight (Kg):5,705
-Quality:Prime
-Help
-Location:FABRICA ALGECIRAS
-2,425.00 €/ton
+0.90 x 1275.0 x coil mm
+Weight (Kg):2,500
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,225.00 €/ton
 Add to cart</v>
       </c>
     </row>
     <row r="413" xml:space="preserve">
       <c r="A413" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Untrimmed, Coil, BA,
-0.90 x 1275.0 x coil mm</v>
+0.90 x 1288.0 x coil mm</v>
       </c>
       <c r="B413" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Untrimmed, Coil, BA,
-0.90 x 1275.0 x coil mm
-Weight (Kg):2,500
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-2,225.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="414" xml:space="preserve">
-      <c r="A414" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Untrimmed, Coil, BA,
-0.90 x 1288.0 x coil mm</v>
-      </c>
-      <c r="B414" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Untrimmed, Coil, BA,
 0.90 x 1288.0 x coil mm
 Weight (Kg):7,960
@@ -7015,12 +6999,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="415" xml:space="preserve">
-      <c r="A415" t="str" xml:space="preserve">
+    <row r="414" xml:space="preserve">
+      <c r="A414" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Untrimmed, Coil, SB-G-400,
 1.20 x 1500.0 x coil mm</v>
       </c>
-      <c r="B415" t="str" xml:space="preserve">
+      <c r="B414" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Untrimmed, Coil, SB-G-400,
 1.20 x 1500.0 x coil mm
 Weight (Kg):2,640
@@ -7031,32 +7015,48 @@
 Add to cart</v>
       </c>
     </row>
+    <row r="415" xml:space="preserve">
+      <c r="A415" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Coil, 2B,
+1.20 x 1536.0 x coil mm</v>
+      </c>
+      <c r="B415" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Coil, 2B,
+1.20 x 1536.0 x coil mm
+Weight (Kg):1,260
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+3,395.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
     <row r="416" xml:space="preserve">
       <c r="A416" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Coil, 2B,
-1.20 x 1536.0 x coil mm</v>
+1.50 x 140.0 x coil mm</v>
       </c>
       <c r="B416" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Coil, 2B,
-1.20 x 1536.0 x coil mm
-Weight (Kg):1,260
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-3,395.00 €/ton
+1.50 x 140.0 x coil mm
+Weight (Kg):758
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+3,270.00 €/ton
 Add to cart</v>
       </c>
     </row>
     <row r="417" xml:space="preserve">
       <c r="A417" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Coil, 2B,
-1.50 x 140.0 x coil mm</v>
+1.50 x 160.9 x coil mm</v>
       </c>
       <c r="B417" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Coil, 2B,
-1.50 x 140.0 x coil mm
-Weight (Kg):758
-Quality:Prime-2
+1.50 x 160.9 x coil mm
+Weight (Kg):848
+Quality:Prime
 Help
 Location:FABRICA ALGECIRAS
 3,270.00 €/ton
@@ -7066,13 +7066,13 @@
     <row r="418" xml:space="preserve">
       <c r="A418" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Coil, 2B,
-1.50 x 160.9 x coil mm</v>
+1.50 x 230.9 x coil mm</v>
       </c>
       <c r="B418" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Coil, 2B,
-1.50 x 160.9 x coil mm
-Weight (Kg):848
-Quality:Prime
+1.50 x 230.9 x coil mm
+Weight (Kg):1,044
+Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
 3,270.00 €/ton
@@ -7130,48 +7130,48 @@
     <row r="422" xml:space="preserve">
       <c r="A422" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Coil, 2B,
-1.50 x 230.9 x coil mm</v>
+2.00 x 1498.0 x coil mm</v>
       </c>
       <c r="B422" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Coil, 2B,
-1.50 x 230.9 x coil mm
-Weight (Kg):1,044
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-3,270.00 €/ton
+2.00 x 1498.0 x coil mm
+Weight (Kg):2,770
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+3,395.00 €/ton
 Add to cart</v>
       </c>
     </row>
     <row r="423" xml:space="preserve">
       <c r="A423" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Coil, 2B,
-2.00 x 1498.0 x coil mm</v>
+5.00 x 1250.0 x coil mm</v>
       </c>
       <c r="B423" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Coil, 2B,
-2.00 x 1498.0 x coil mm
-Weight (Kg):2,770
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-3,395.00 €/ton
+5.00 x 1250.0 x coil mm
+Weight (Kg):12,055
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+3,375.00 €/ton
 Add to cart</v>
       </c>
     </row>
     <row r="424" xml:space="preserve">
       <c r="A424" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Coil, 2B,
-5.00 x 1250.0 x coil mm</v>
+5.00 x 240.0 x coil mm</v>
       </c>
       <c r="B424" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Coil, 2B,
-5.00 x 1250.0 x coil mm
-Weight (Kg):12,055
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-3,375.00 €/ton
+5.00 x 240.0 x coil mm
+Weight (Kg):2,314
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+3,270.00 €/ton
 Add to cart</v>
       </c>
     </row>
@@ -7183,7 +7183,7 @@
       <c r="B425" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Coil, 2B,
 5.00 x 240.0 x coil mm
-Weight (Kg):2,314
+Weight (Kg):2,237
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -7194,32 +7194,32 @@
     <row r="426" xml:space="preserve">
       <c r="A426" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Coil, 2B,
-5.00 x 240.0 x coil mm</v>
+6.00 x 1500.0 x coil mm</v>
       </c>
       <c r="B426" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Coil, 2B,
-5.00 x 240.0 x coil mm
-Weight (Kg):2,237
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-3,270.00 €/ton
+6.00 x 1500.0 x coil mm
+Weight (Kg):2,016
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+3,395.00 €/ton
 Add to cart</v>
       </c>
     </row>
     <row r="427" xml:space="preserve">
       <c r="A427" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Coil, 2B,
-6.00 x 1500.0 x coil mm</v>
+6.00 x 250.9 x coil mm</v>
       </c>
       <c r="B427" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Coil, 2B,
-6.00 x 1500.0 x coil mm
-Weight (Kg):2,016
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-3,395.00 €/ton
+6.00 x 250.9 x coil mm
+Weight (Kg):548
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+3,270.00 €/ton
 Add to cart</v>
       </c>
     </row>
@@ -7231,7 +7231,7 @@
       <c r="B428" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Coil, 2B,
 6.00 x 250.9 x coil mm
-Weight (Kg):548
+Weight (Kg):1,880
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -7241,13 +7241,13 @@
     </row>
     <row r="429" xml:space="preserve">
       <c r="A429" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Coil, 2B,
-6.00 x 250.9 x coil mm</v>
+        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Coil, 2D,
+3.30 x 112.0 x coil mm</v>
       </c>
       <c r="B429" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Coil, 2B,
-6.00 x 250.9 x coil mm
-Weight (Kg):1,880
+        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Coil, 2D,
+3.30 x 112.0 x coil mm
+Weight (Kg):1,017
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -7263,8 +7263,8 @@
       <c r="B430" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Coil, 2D,
 3.30 x 112.0 x coil mm
-Weight (Kg):1,017
-Quality:Prime-2
+Weight (Kg):878
+Quality:Prime
 Help
 Location:FABRICA ALGECIRAS
 3,270.00 €/ton
@@ -7274,13 +7274,13 @@
     <row r="431" xml:space="preserve">
       <c r="A431" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Coil, 2D,
-3.30 x 112.0 x coil mm</v>
+3.30 x 449.0 x coil mm</v>
       </c>
       <c r="B431" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Coil, 2D,
-3.30 x 112.0 x coil mm
-Weight (Kg):878
-Quality:Prime
+3.30 x 449.0 x coil mm
+Weight (Kg):1,850
+Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
 3,270.00 €/ton
@@ -7295,7 +7295,7 @@
       <c r="B432" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Coil, 2D,
 3.30 x 449.0 x coil mm
-Weight (Kg):1,850
+Weight (Kg):1,854
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -7305,14 +7305,14 @@
     </row>
     <row r="433" xml:space="preserve">
       <c r="A433" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Coil, 2D,
-3.30 x 449.0 x coil mm</v>
+        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Coil, BA,
+0.40 x 295.9 x coil mm</v>
       </c>
       <c r="B433" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Coil, 2D,
-3.30 x 449.0 x coil mm
-Weight (Kg):1,854
-Quality:Prime-2
+        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Coil, BA,
+0.40 x 295.9 x coil mm
+Weight (Kg):662
+Quality:Prime
 Help
 Location:FABRICA ALGECIRAS
 3,270.00 €/ton
@@ -7327,7 +7327,7 @@
       <c r="B434" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Coil, BA,
 0.40 x 295.9 x coil mm
-Weight (Kg):662
+Weight (Kg):650
 Quality:Prime
 Help
 Location:FABRICA ALGECIRAS
@@ -7338,25 +7338,9 @@
     <row r="435" xml:space="preserve">
       <c r="A435" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Coil, BA,
-0.40 x 295.9 x coil mm</v>
+0.50 x 160.0 x coil mm</v>
       </c>
       <c r="B435" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Coil, BA,
-0.40 x 295.9 x coil mm
-Weight (Kg):650
-Quality:Prime
-Help
-Location:FABRICA ALGECIRAS
-3,270.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="436" xml:space="preserve">
-      <c r="A436" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Coil, BA,
-0.50 x 160.0 x coil mm</v>
-      </c>
-      <c r="B436" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Coil, BA,
 0.50 x 160.0 x coil mm
 Weight (Kg):1,066
@@ -7367,16 +7351,32 @@
 Add to cart</v>
       </c>
     </row>
+    <row r="436" xml:space="preserve">
+      <c r="A436" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Coil, Nb. 1,
+3.70 x 310.0 x coil mm</v>
+      </c>
+      <c r="B436" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Coil, Nb. 1,
+3.70 x 310.0 x coil mm
+Weight (Kg):5,921
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+3,170.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
     <row r="437" xml:space="preserve">
       <c r="A437" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Coil, Nb. 1,
-3.70 x 310.0 x coil mm</v>
+4.10 x 150.0 x coil mm</v>
       </c>
       <c r="B437" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Coil, Nb. 1,
-3.70 x 310.0 x coil mm
-Weight (Kg):5,921
-Quality:Prime-2
+4.10 x 150.0 x coil mm
+Weight (Kg):1,593
+Quality:Prime
 Help
 Location:FABRICA ALGECIRAS
 3,170.00 €/ton
@@ -7391,7 +7391,7 @@
       <c r="B438" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Coil, Nb. 1,
 4.10 x 150.0 x coil mm
-Weight (Kg):1,593
+Weight (Kg):1,438
 Quality:Prime
 Help
 Location:FABRICA ALGECIRAS
@@ -7402,25 +7402,9 @@
     <row r="439" xml:space="preserve">
       <c r="A439" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Coil, Nb. 1,
-4.10 x 150.0 x coil mm</v>
+4.50 x 220.0 x coil mm</v>
       </c>
       <c r="B439" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Coil, Nb. 1,
-4.10 x 150.0 x coil mm
-Weight (Kg):1,438
-Quality:Prime
-Help
-Location:FABRICA ALGECIRAS
-3,170.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="440" xml:space="preserve">
-      <c r="A440" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Coil, Nb. 1,
-4.50 x 220.0 x coil mm</v>
-      </c>
-      <c r="B440" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Coil, Nb. 1,
 4.50 x 220.0 x coil mm
 Weight (Kg):3,869
@@ -7431,12 +7415,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="441" xml:space="preserve">
-      <c r="A441" t="str" xml:space="preserve">
+    <row r="440" xml:space="preserve">
+      <c r="A440" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Coil, SB-G-400,
 1.00 x 250.9 x coil mm</v>
       </c>
-      <c r="B441" t="str" xml:space="preserve">
+      <c r="B440" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Coil, SB-G-400,
 1.00 x 250.9 x coil mm
 Weight (Kg):1,428
@@ -7447,15 +7431,31 @@
 Add to cart</v>
       </c>
     </row>
+    <row r="441" xml:space="preserve">
+      <c r="A441" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
+0.70 x 1250.0 x 2500.0 mm</v>
+      </c>
+      <c r="B441" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
+0.70 x 1250.0 x 2500.0 mm
+Weight (Kg):1,756
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+3,395.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
     <row r="442" xml:space="preserve">
       <c r="A442" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
-0.70 x 1250.0 x 2500.0 mm</v>
+0.80 x 1250.0 x 3000.0 mm</v>
       </c>
       <c r="B442" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
-0.70 x 1250.0 x 2500.0 mm
-Weight (Kg):1,756
+0.80 x 1250.0 x 3000.0 mm
+Weight (Kg):695
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -7466,12 +7466,12 @@
     <row r="443" xml:space="preserve">
       <c r="A443" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
-0.80 x 1250.0 x 3000.0 mm</v>
+0.80 x 1500.0 x 3000.0 mm</v>
       </c>
       <c r="B443" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
-0.80 x 1250.0 x 3000.0 mm
-Weight (Kg):695
+0.80 x 1500.0 x 3000.0 mm
+Weight (Kg):978
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -7487,7 +7487,7 @@
       <c r="B444" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
 0.80 x 1500.0 x 3000.0 mm
-Weight (Kg):978
+Weight (Kg):1,741
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -7503,7 +7503,7 @@
       <c r="B445" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
 0.80 x 1500.0 x 3000.0 mm
-Weight (Kg):1,741
+Weight (Kg):803
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -7519,7 +7519,7 @@
       <c r="B446" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
 0.80 x 1500.0 x 3000.0 mm
-Weight (Kg):803
+Weight (Kg):1,136
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -7530,12 +7530,12 @@
     <row r="447" xml:space="preserve">
       <c r="A447" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
-0.80 x 1500.0 x 3000.0 mm</v>
+0.90 x 1000.0 x 2000.0 mm</v>
       </c>
       <c r="B447" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
-0.80 x 1500.0 x 3000.0 mm
-Weight (Kg):1,136
+0.90 x 1000.0 x 2000.0 mm
+Weight (Kg):576
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -7546,12 +7546,12 @@
     <row r="448" xml:space="preserve">
       <c r="A448" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
-0.90 x 1000.0 x 2000.0 mm</v>
+0.90 x 1500.0 x 3000.0 mm</v>
       </c>
       <c r="B448" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
-0.90 x 1000.0 x 2000.0 mm
-Weight (Kg):576
+0.90 x 1500.0 x 3000.0 mm
+Weight (Kg):553
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -7562,12 +7562,12 @@
     <row r="449" xml:space="preserve">
       <c r="A449" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
-0.90 x 1500.0 x 3000.0 mm</v>
+1.10 x 1500.0 x 3000.0 mm</v>
       </c>
       <c r="B449" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
-0.90 x 1500.0 x 3000.0 mm
-Weight (Kg):553
+1.10 x 1500.0 x 3000.0 mm
+Weight (Kg):1,233
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -7578,12 +7578,12 @@
     <row r="450" xml:space="preserve">
       <c r="A450" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
-1.10 x 1500.0 x 3000.0 mm</v>
+1.20 x 1250.0 x 2500.0 mm</v>
       </c>
       <c r="B450" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
-1.10 x 1500.0 x 3000.0 mm
-Weight (Kg):1,233
+1.20 x 1250.0 x 2500.0 mm
+Weight (Kg):685
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -7594,12 +7594,12 @@
     <row r="451" xml:space="preserve">
       <c r="A451" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
-1.20 x 1250.0 x 2500.0 mm</v>
+1.50 x 1000.0 x 2000.0 mm</v>
       </c>
       <c r="B451" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
-1.20 x 1250.0 x 2500.0 mm
-Weight (Kg):685
+1.50 x 1000.0 x 2000.0 mm
+Weight (Kg):598
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -7610,12 +7610,12 @@
     <row r="452" xml:space="preserve">
       <c r="A452" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
-1.50 x 1000.0 x 2000.0 mm</v>
+1.50 x 1250.0 x 2500.0 mm</v>
       </c>
       <c r="B452" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
-1.50 x 1000.0 x 2000.0 mm
-Weight (Kg):598
+1.50 x 1250.0 x 2500.0 mm
+Weight (Kg):681
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -7626,12 +7626,12 @@
     <row r="453" xml:space="preserve">
       <c r="A453" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
-1.50 x 1250.0 x 2500.0 mm</v>
+2.00 x 1000.0 x 2000.0 mm</v>
       </c>
       <c r="B453" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
-1.50 x 1250.0 x 2500.0 mm
-Weight (Kg):681
+2.00 x 1000.0 x 2000.0 mm
+Weight (Kg):2,359
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -7647,7 +7647,7 @@
       <c r="B454" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
 2.00 x 1000.0 x 2000.0 mm
-Weight (Kg):2,359
+Weight (Kg):529
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -7663,7 +7663,7 @@
       <c r="B455" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
 2.00 x 1000.0 x 2000.0 mm
-Weight (Kg):529
+Weight (Kg):889
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -7679,7 +7679,7 @@
       <c r="B456" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
 2.00 x 1000.0 x 2000.0 mm
-Weight (Kg):889
+Weight (Kg):628
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -7695,7 +7695,7 @@
       <c r="B457" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
 2.00 x 1000.0 x 2000.0 mm
-Weight (Kg):628
+Weight (Kg):1,968
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -7706,12 +7706,12 @@
     <row r="458" xml:space="preserve">
       <c r="A458" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
-2.00 x 1000.0 x 2000.0 mm</v>
+2.00 x 1250.0 x 2500.0 mm</v>
       </c>
       <c r="B458" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
-2.00 x 1000.0 x 2000.0 mm
-Weight (Kg):1,968
+2.00 x 1250.0 x 2500.0 mm
+Weight (Kg):928
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -7727,7 +7727,7 @@
       <c r="B459" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
 2.00 x 1250.0 x 2500.0 mm
-Weight (Kg):928
+Weight (Kg):816
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -7743,7 +7743,7 @@
       <c r="B460" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
 2.00 x 1250.0 x 2500.0 mm
-Weight (Kg):816
+Weight (Kg):976
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -7759,7 +7759,7 @@
       <c r="B461" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
 2.00 x 1250.0 x 2500.0 mm
-Weight (Kg):976
+Weight (Kg):585
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -7775,7 +7775,7 @@
       <c r="B462" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
 2.00 x 1250.0 x 2500.0 mm
-Weight (Kg):585
+Weight (Kg):1,956
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -7791,7 +7791,7 @@
       <c r="B463" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
 2.00 x 1250.0 x 2500.0 mm
-Weight (Kg):1,956
+Weight (Kg):1,779
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -7802,12 +7802,12 @@
     <row r="464" xml:space="preserve">
       <c r="A464" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
-2.00 x 1250.0 x 2500.0 mm</v>
+2.00 x 1500.0 x 3000.0 mm</v>
       </c>
       <c r="B464" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
-2.00 x 1250.0 x 2500.0 mm
-Weight (Kg):1,779
+2.00 x 1500.0 x 3000.0 mm
+Weight (Kg):693
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -7823,7 +7823,7 @@
       <c r="B465" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
 2.00 x 1500.0 x 3000.0 mm
-Weight (Kg):693
+Weight (Kg):1,122
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -7839,7 +7839,7 @@
       <c r="B466" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
 2.00 x 1500.0 x 3000.0 mm
-Weight (Kg):1,122
+Weight (Kg):1,108
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -7855,7 +7855,7 @@
       <c r="B467" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
 2.00 x 1500.0 x 3000.0 mm
-Weight (Kg):1,108
+Weight (Kg):1,836
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -7871,7 +7871,7 @@
       <c r="B468" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
 2.00 x 1500.0 x 3000.0 mm
-Weight (Kg):1,836
+Weight (Kg):630
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -7887,7 +7887,7 @@
       <c r="B469" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
 2.00 x 1500.0 x 3000.0 mm
-Weight (Kg):630
+Weight (Kg):726
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -7903,7 +7903,7 @@
       <c r="B470" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
 2.00 x 1500.0 x 3000.0 mm
-Weight (Kg):726
+Weight (Kg):565
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -7919,7 +7919,7 @@
       <c r="B471" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
 2.00 x 1500.0 x 3000.0 mm
-Weight (Kg):565
+Weight (Kg):729
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -7935,7 +7935,7 @@
       <c r="B472" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
 2.00 x 1500.0 x 3000.0 mm
-Weight (Kg):729
+Weight (Kg):792
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -7951,7 +7951,7 @@
       <c r="B473" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
 2.00 x 1500.0 x 3000.0 mm
-Weight (Kg):792
+Weight (Kg):637
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -7967,7 +7967,7 @@
       <c r="B474" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
 2.00 x 1500.0 x 3000.0 mm
-Weight (Kg):637
+Weight (Kg):1,289
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -7978,12 +7978,12 @@
     <row r="475" xml:space="preserve">
       <c r="A475" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
-2.00 x 1500.0 x 3000.0 mm</v>
+2.50 x 1500.0 x 3000.0 mm</v>
       </c>
       <c r="B475" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
-2.00 x 1500.0 x 3000.0 mm
-Weight (Kg):1,289
+2.50 x 1500.0 x 3000.0 mm
+Weight (Kg):1,826
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -7999,7 +7999,7 @@
       <c r="B476" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
 2.50 x 1500.0 x 3000.0 mm
-Weight (Kg):1,826
+Weight (Kg):1,040
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -8015,7 +8015,7 @@
       <c r="B477" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
 2.50 x 1500.0 x 3000.0 mm
-Weight (Kg):1,040
+Weight (Kg):1,328
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -8026,12 +8026,12 @@
     <row r="478" xml:space="preserve">
       <c r="A478" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
-2.50 x 1500.0 x 3000.0 mm</v>
+3.00 x 1000.0 x 2000.0 mm</v>
       </c>
       <c r="B478" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
-2.50 x 1500.0 x 3000.0 mm
-Weight (Kg):1,328
+3.00 x 1000.0 x 2000.0 mm
+Weight (Kg):940
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -8042,12 +8042,12 @@
     <row r="479" xml:space="preserve">
       <c r="A479" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
-3.00 x 1000.0 x 2000.0 mm</v>
+3.00 x 1250.0 x 2500.0 mm</v>
       </c>
       <c r="B479" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
-3.00 x 1000.0 x 2000.0 mm
-Weight (Kg):940
+3.00 x 1250.0 x 2500.0 mm
+Weight (Kg):1,396
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -8063,7 +8063,7 @@
       <c r="B480" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
 3.00 x 1250.0 x 2500.0 mm
-Weight (Kg):1,396
+Weight (Kg):2,318
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -8079,7 +8079,7 @@
       <c r="B481" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
 3.00 x 1250.0 x 2500.0 mm
-Weight (Kg):2,318
+Weight (Kg):1,074
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -8095,7 +8095,7 @@
       <c r="B482" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
 3.00 x 1250.0 x 2500.0 mm
-Weight (Kg):1,074
+Weight (Kg):1,584
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -8111,7 +8111,7 @@
       <c r="B483" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
 3.00 x 1250.0 x 2500.0 mm
-Weight (Kg):1,584
+Weight (Kg):1,028
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -8127,7 +8127,7 @@
       <c r="B484" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
 3.00 x 1250.0 x 2500.0 mm
-Weight (Kg):1,028
+Weight (Kg):598
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -8138,12 +8138,12 @@
     <row r="485" xml:space="preserve">
       <c r="A485" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
-3.00 x 1250.0 x 2500.0 mm</v>
+3.00 x 1340.0 x 2480.0 mm</v>
       </c>
       <c r="B485" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
-3.00 x 1250.0 x 2500.0 mm
-Weight (Kg):598
+3.00 x 1340.0 x 2480.0 mm
+Weight (Kg):1,174
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -8159,7 +8159,7 @@
       <c r="B486" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
 3.00 x 1340.0 x 2480.0 mm
-Weight (Kg):1,174
+Weight (Kg):1,020
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -8175,7 +8175,7 @@
       <c r="B487" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
 3.00 x 1340.0 x 2480.0 mm
-Weight (Kg):1,020
+Weight (Kg):1,169
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -8191,7 +8191,7 @@
       <c r="B488" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
 3.00 x 1340.0 x 2480.0 mm
-Weight (Kg):1,169
+Weight (Kg):1,951
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -8202,12 +8202,12 @@
     <row r="489" xml:space="preserve">
       <c r="A489" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
-3.00 x 1340.0 x 2480.0 mm</v>
+5.00 x 1000.0 x 2000.0 mm</v>
       </c>
       <c r="B489" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
-3.00 x 1340.0 x 2480.0 mm
-Weight (Kg):1,951
+5.00 x 1000.0 x 2000.0 mm
+Weight (Kg):943
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -8223,7 +8223,7 @@
       <c r="B490" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
 5.00 x 1000.0 x 2000.0 mm
-Weight (Kg):943
+Weight (Kg):947
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -8239,7 +8239,7 @@
       <c r="B491" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
 5.00 x 1000.0 x 2000.0 mm
-Weight (Kg):947
+Weight (Kg):1,588
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -8250,12 +8250,12 @@
     <row r="492" xml:space="preserve">
       <c r="A492" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
-5.00 x 1000.0 x 2000.0 mm</v>
+5.00 x 1250.0 x 2500.0 mm</v>
       </c>
       <c r="B492" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
-5.00 x 1000.0 x 2000.0 mm
-Weight (Kg):1,588
+5.00 x 1250.0 x 2500.0 mm
+Weight (Kg):742
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -8266,12 +8266,12 @@
     <row r="493" xml:space="preserve">
       <c r="A493" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
-5.00 x 1250.0 x 2500.0 mm</v>
+6.00 x 1000.0 x 2000.0 mm</v>
       </c>
       <c r="B493" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
-5.00 x 1250.0 x 2500.0 mm
-Weight (Kg):742
+6.00 x 1000.0 x 2000.0 mm
+Weight (Kg):1,452
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -8287,7 +8287,7 @@
       <c r="B494" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
 6.00 x 1000.0 x 2000.0 mm
-Weight (Kg):1,452
+Weight (Kg):1,624
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -8303,7 +8303,7 @@
       <c r="B495" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
 6.00 x 1000.0 x 2000.0 mm
-Weight (Kg):1,624
+Weight (Kg):1,434
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -8319,7 +8319,7 @@
       <c r="B496" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
 6.00 x 1000.0 x 2000.0 mm
-Weight (Kg):1,434
+Weight (Kg):580
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -8335,7 +8335,7 @@
       <c r="B497" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
 6.00 x 1000.0 x 2000.0 mm
-Weight (Kg):580
+Weight (Kg):1,054
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -8351,7 +8351,7 @@
       <c r="B498" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
 6.00 x 1000.0 x 2000.0 mm
-Weight (Kg):1,054
+Weight (Kg):1,716
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -8367,7 +8367,7 @@
       <c r="B499" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
 6.00 x 1000.0 x 2000.0 mm
-Weight (Kg):1,716
+Weight (Kg):1,148
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -8383,7 +8383,7 @@
       <c r="B500" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
 6.00 x 1000.0 x 2000.0 mm
-Weight (Kg):1,148
+Weight (Kg):960
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -8399,7 +8399,7 @@
       <c r="B501" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
 6.00 x 1000.0 x 2000.0 mm
-Weight (Kg):960
+Weight (Kg):772
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -8410,12 +8410,12 @@
     <row r="502" xml:space="preserve">
       <c r="A502" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
-6.00 x 1000.0 x 2000.0 mm</v>
+6.00 x 1500.0 x 3000.0 mm</v>
       </c>
       <c r="B502" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
-6.00 x 1000.0 x 2000.0 mm
-Weight (Kg):772
+6.00 x 1500.0 x 3000.0 mm
+Weight (Kg):2,146
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -8431,7 +8431,7 @@
       <c r="B503" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
 6.00 x 1500.0 x 3000.0 mm
-Weight (Kg):2,146
+Weight (Kg):1,994
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -8447,7 +8447,7 @@
       <c r="B504" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
 6.00 x 1500.0 x 3000.0 mm
-Weight (Kg):1,994
+Weight (Kg):1,488
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -8463,7 +8463,7 @@
       <c r="B505" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
 6.00 x 1500.0 x 3000.0 mm
-Weight (Kg):1,488
+Weight (Kg):1,278
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -8479,7 +8479,7 @@
       <c r="B506" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
 6.00 x 1500.0 x 3000.0 mm
-Weight (Kg):1,278
+Weight (Kg):1,062
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -8495,7 +8495,7 @@
       <c r="B507" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
 6.00 x 1500.0 x 3000.0 mm
-Weight (Kg):1,062
+Weight (Kg):1,526
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -8511,7 +8511,7 @@
       <c r="B508" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
 6.00 x 1500.0 x 3000.0 mm
-Weight (Kg):1,526
+Weight (Kg):1,280
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -8522,12 +8522,12 @@
     <row r="509" xml:space="preserve">
       <c r="A509" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
-6.00 x 1500.0 x 3000.0 mm</v>
+6.00 x 1510.0 x 3010.0 mm</v>
       </c>
       <c r="B509" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
-6.00 x 1500.0 x 3000.0 mm
-Weight (Kg):1,280
+6.00 x 1510.0 x 3010.0 mm
+Weight (Kg):1,986
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -8543,7 +8543,7 @@
       <c r="B510" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
 6.00 x 1510.0 x 3010.0 mm
-Weight (Kg):1,986
+Weight (Kg):1,784
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -8553,26 +8553,10 @@
     </row>
     <row r="511" xml:space="preserve">
       <c r="A511" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
-6.00 x 1510.0 x 3010.0 mm</v>
-      </c>
-      <c r="B511" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
-6.00 x 1510.0 x 3010.0 mm
-Weight (Kg):1,784
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-3,395.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="512" xml:space="preserve">
-      <c r="A512" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, Nb. 1,
 6.00 x 1000.0 x 2000.0 mm</v>
       </c>
-      <c r="B512" t="str" xml:space="preserve">
+      <c r="B511" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, Nb. 1,
 6.00 x 1000.0 x 2000.0 mm
 Weight (Kg):570
@@ -8583,15 +8567,31 @@
 Add to cart</v>
       </c>
     </row>
+    <row r="512" xml:space="preserve">
+      <c r="A512" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, SB-G-400,
+1.50 x 1500.0 x 3000.0 mm</v>
+      </c>
+      <c r="B512" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, SB-G-400,
+1.50 x 1500.0 x 3000.0 mm
+Weight (Kg):723
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+3,395.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
     <row r="513" xml:space="preserve">
       <c r="A513" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, SB-G-400,
-1.50 x 1500.0 x 3000.0 mm</v>
+2.00 x 1500.0 x 3000.0 mm</v>
       </c>
       <c r="B513" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, SB-G-400,
-1.50 x 1500.0 x 3000.0 mm
-Weight (Kg):723
+2.00 x 1500.0 x 3000.0 mm
+Weight (Kg):819
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -8607,7 +8607,7 @@
       <c r="B514" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, SB-G-400,
 2.00 x 1500.0 x 3000.0 mm
-Weight (Kg):819
+Weight (Kg):1,935
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -8617,13 +8617,13 @@
     </row>
     <row r="515" xml:space="preserve">
       <c r="A515" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, SB-G-400,
-2.00 x 1500.0 x 3000.0 mm</v>
+        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Untrimmed, Coil, 2B,
+1.20 x 1537.0 x coil mm</v>
       </c>
       <c r="B515" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, SB-G-400,
-2.00 x 1500.0 x 3000.0 mm
-Weight (Kg):1,935
+        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Untrimmed, Coil, 2B,
+1.20 x 1537.0 x coil mm
+Weight (Kg):2,125
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -8634,12 +8634,12 @@
     <row r="516" xml:space="preserve">
       <c r="A516" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Untrimmed, Coil, 2B,
-1.20 x 1537.0 x coil mm</v>
+1.80 x 1530.0 x coil mm</v>
       </c>
       <c r="B516" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Untrimmed, Coil, 2B,
-1.20 x 1537.0 x coil mm
-Weight (Kg):2,125
+1.80 x 1530.0 x coil mm
+Weight (Kg):5,263
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -8650,12 +8650,12 @@
     <row r="517" xml:space="preserve">
       <c r="A517" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Untrimmed, Coil, 2B,
-1.80 x 1530.0 x coil mm</v>
+1.80 x 1535.0 x coil mm</v>
       </c>
       <c r="B517" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Untrimmed, Coil, 2B,
-1.80 x 1530.0 x coil mm
-Weight (Kg):5,263
+1.80 x 1535.0 x coil mm
+Weight (Kg):2,726
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -8666,44 +8666,44 @@
     <row r="518" xml:space="preserve">
       <c r="A518" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Untrimmed, Coil, 2B,
-1.80 x 1535.0 x coil mm</v>
+2.00 x 1023.0 x coil mm</v>
       </c>
       <c r="B518" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Untrimmed, Coil, 2B,
-1.80 x 1535.0 x coil mm
-Weight (Kg):2,726
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-3,395.00 €/ton
+2.00 x 1023.0 x coil mm
+Weight (Kg):1,825
+Quality:Prime
+Help
+Location:FABRICA ALGECIRAS
+3,595.00 €/ton
 Add to cart</v>
       </c>
     </row>
     <row r="519" xml:space="preserve">
       <c r="A519" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Untrimmed, Coil, 2B,
-2.00 x 1023.0 x coil mm</v>
+3.00 x 1552.0 x coil mm</v>
       </c>
       <c r="B519" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Untrimmed, Coil, 2B,
-2.00 x 1023.0 x coil mm
-Weight (Kg):1,825
-Quality:Prime
-Help
-Location:FABRICA ALGECIRAS
-3,595.00 €/ton
+3.00 x 1552.0 x coil mm
+Weight (Kg):2,868
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+3,395.00 €/ton
 Add to cart</v>
       </c>
     </row>
     <row r="520" xml:space="preserve">
       <c r="A520" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Untrimmed, Coil, 2B,
-3.00 x 1552.0 x coil mm</v>
+6.00 x 1030.0 x coil mm</v>
       </c>
       <c r="B520" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Untrimmed, Coil, 2B,
-3.00 x 1552.0 x coil mm
-Weight (Kg):2,868
+6.00 x 1030.0 x coil mm
+Weight (Kg):2,225
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -8729,26 +8729,10 @@
     </row>
     <row r="522" xml:space="preserve">
       <c r="A522" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Untrimmed, Coil, 2B,
-6.00 x 1030.0 x coil mm</v>
-      </c>
-      <c r="B522" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Untrimmed, Coil, 2B,
-6.00 x 1030.0 x coil mm
-Weight (Kg):2,225
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-3,395.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="523" xml:space="preserve">
-      <c r="A523" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4571 316Ti-Coil, 2B,
 4.00 x 210.0 x coil mm</v>
       </c>
-      <c r="B523" t="str" xml:space="preserve">
+      <c r="B522" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4571 316Ti-Coil, 2B,
 4.00 x 210.0 x coil mm
 Weight (Kg):3,817
@@ -8756,6 +8740,22 @@
 Help
 Location:FABRICA ALGECIRAS
 3,370.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="523" xml:space="preserve">
+      <c r="A523" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4571 316Ti-Coil, Nb. 1,
+3.00 x 184.0 x coil mm</v>
+      </c>
+      <c r="B523" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4571 316Ti-Coil, Nb. 1,
+3.00 x 184.0 x coil mm
+Weight (Kg):1,794
+Quality:Prime
+Help
+Location:FABRICA ALGECIRAS
+3,270.00 €/ton
 Add to cart</v>
       </c>
     </row>
@@ -8767,7 +8767,7 @@
       <c r="B524" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4571 316Ti-Coil, Nb. 1,
 3.00 x 184.0 x coil mm
-Weight (Kg):1,794
+Weight (Kg):1,806
 Quality:Prime
 Help
 Location:FABRICA ALGECIRAS
@@ -8783,7 +8783,7 @@
       <c r="B525" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4571 316Ti-Coil, Nb. 1,
 3.00 x 184.0 x coil mm
-Weight (Kg):1,806
+Weight (Kg):1,808
 Quality:Prime
 Help
 Location:FABRICA ALGECIRAS
@@ -8794,25 +8794,9 @@
     <row r="526" xml:space="preserve">
       <c r="A526" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4571 316Ti-Coil, Nb. 1,
-3.00 x 184.0 x coil mm</v>
+4.00 x 200.0 x coil mm</v>
       </c>
       <c r="B526" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4571 316Ti-Coil, Nb. 1,
-3.00 x 184.0 x coil mm
-Weight (Kg):1,808
-Quality:Prime
-Help
-Location:FABRICA ALGECIRAS
-3,270.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="527" xml:space="preserve">
-      <c r="A527" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4571 316Ti-Coil, Nb. 1,
-4.00 x 200.0 x coil mm</v>
-      </c>
-      <c r="B527" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4571 316Ti-Coil, Nb. 1,
 4.00 x 200.0 x coil mm
 Weight (Kg):1,918
@@ -8823,12 +8807,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="528" xml:space="preserve">
-      <c r="A528" t="str" xml:space="preserve">
+    <row r="527" xml:space="preserve">
+      <c r="A527" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4571 316Ti-Plate, Nb. 1,
 45.00 x 1500.0 x 3000.0 mm</v>
       </c>
-      <c r="B528" t="str" xml:space="preserve">
+      <c r="B527" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4571 316Ti-Plate, Nb. 1,
 45.00 x 1500.0 x 3000.0 mm
 Weight (Kg):1,640
@@ -8836,6 +8820,22 @@
 Help
 Location:FABRICA ALGECIRAS
 4,600.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="528" xml:space="preserve">
+      <c r="A528" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4571 316Ti-Sheet, 2B,
+3.00 x 1000.0 x 2000.0 mm</v>
+      </c>
+      <c r="B528" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4571 316Ti-Sheet, 2B,
+3.00 x 1000.0 x 2000.0 mm
+Weight (Kg):918
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+3,495.00 €/ton
 Add to cart</v>
       </c>
     </row>
@@ -8847,7 +8847,7 @@
       <c r="B529" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4571 316Ti-Sheet, 2B,
 3.00 x 1000.0 x 2000.0 mm
-Weight (Kg):918
+Weight (Kg):518
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -8863,7 +8863,7 @@
       <c r="B530" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4571 316Ti-Sheet, 2B,
 3.00 x 1000.0 x 2000.0 mm
-Weight (Kg):518
+Weight (Kg):848
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -8874,12 +8874,12 @@
     <row r="531" xml:space="preserve">
       <c r="A531" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4571 316Ti-Sheet, 2B,
-3.00 x 1000.0 x 2000.0 mm</v>
+5.00 x 1000.0 x 2000.0 mm</v>
       </c>
       <c r="B531" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4571 316Ti-Sheet, 2B,
-3.00 x 1000.0 x 2000.0 mm
-Weight (Kg):848
+5.00 x 1000.0 x 2000.0 mm
+Weight (Kg):1,102
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -8890,12 +8890,12 @@
     <row r="532" xml:space="preserve">
       <c r="A532" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4571 316Ti-Sheet, 2B,
-5.00 x 1000.0 x 2000.0 mm</v>
+6.00 x 1000.0 x 2000.0 mm</v>
       </c>
       <c r="B532" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4571 316Ti-Sheet, 2B,
-5.00 x 1000.0 x 2000.0 mm
-Weight (Kg):1,102
+6.00 x 1000.0 x 2000.0 mm
+Weight (Kg):1,050
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -8911,7 +8911,7 @@
       <c r="B533" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4571 316Ti-Sheet, 2B,
 6.00 x 1000.0 x 2000.0 mm
-Weight (Kg):1,050
+Weight (Kg):952
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -8921,26 +8921,10 @@
     </row>
     <row r="534" xml:space="preserve">
       <c r="A534" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4571 316Ti-Sheet, 2B,
-6.00 x 1000.0 x 2000.0 mm</v>
-      </c>
-      <c r="B534" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4571 316Ti-Sheet, 2B,
-6.00 x 1000.0 x 2000.0 mm
-Weight (Kg):952
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-3,495.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="535" xml:space="preserve">
-      <c r="A535" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4571 316Ti-Sheet, Nb. 1,
 8.00 x 1500.0 x 3000.0 mm</v>
       </c>
-      <c r="B535" t="str" xml:space="preserve">
+      <c r="B534" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4571 316Ti-Sheet, Nb. 1,
 8.00 x 1500.0 x 3000.0 mm
 Weight (Kg):1,136
@@ -8948,6 +8932,22 @@
 Help
 Location:FABRICA ALGECIRAS
 3,495.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="535" xml:space="preserve">
+      <c r="A535" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4541 321-Coil, 2B,
+1.90 x 217.0 x coil mm</v>
+      </c>
+      <c r="B535" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4541 321-Coil, 2B,
+1.90 x 217.0 x coil mm
+Weight (Kg):3,537
+Quality:Prime
+Help
+Location:FABRICA ALGECIRAS
+2,235.00 €/ton
 Add to cart</v>
       </c>
     </row>
@@ -8959,7 +8959,7 @@
       <c r="B536" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4541 321-Coil, 2B,
 1.90 x 217.0 x coil mm
-Weight (Kg):3,537
+Weight (Kg):3,484
 Quality:Prime
 Help
 Location:FABRICA ALGECIRAS
@@ -8975,7 +8975,7 @@
       <c r="B537" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4541 321-Coil, 2B,
 1.90 x 217.0 x coil mm
-Weight (Kg):3,484
+Weight (Kg):3,537
 Quality:Prime
 Help
 Location:FABRICA ALGECIRAS
@@ -8991,7 +8991,7 @@
       <c r="B538" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4541 321-Coil, 2B,
 1.90 x 217.0 x coil mm
-Weight (Kg):3,537
+Weight (Kg):3,490
 Quality:Prime
 Help
 Location:FABRICA ALGECIRAS
@@ -9007,7 +9007,7 @@
       <c r="B539" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4541 321-Coil, 2B,
 1.90 x 217.0 x coil mm
-Weight (Kg):3,490
+Weight (Kg):3,537
 Quality:Prime
 Help
 Location:FABRICA ALGECIRAS
@@ -9023,7 +9023,7 @@
       <c r="B540" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4541 321-Coil, 2B,
 1.90 x 217.0 x coil mm
-Weight (Kg):3,537
+Weight (Kg):3,492
 Quality:Prime
 Help
 Location:FABRICA ALGECIRAS
@@ -9039,7 +9039,7 @@
       <c r="B541" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4541 321-Coil, 2B,
 1.90 x 217.0 x coil mm
-Weight (Kg):3,492
+Weight (Kg):3,480
 Quality:Prime
 Help
 Location:FABRICA ALGECIRAS
@@ -9050,25 +9050,9 @@
     <row r="542" xml:space="preserve">
       <c r="A542" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4541 321-Coil, 2B,
-1.90 x 217.0 x coil mm</v>
+4.00 x 520.0 x coil mm</v>
       </c>
       <c r="B542" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4541 321-Coil, 2B,
-1.90 x 217.0 x coil mm
-Weight (Kg):3,480
-Quality:Prime
-Help
-Location:FABRICA ALGECIRAS
-2,235.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="543" xml:space="preserve">
-      <c r="A543" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4541 321-Coil, 2B,
-4.00 x 520.0 x coil mm</v>
-      </c>
-      <c r="B543" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4541 321-Coil, 2B,
 4.00 x 520.0 x coil mm
 Weight (Kg):7,263
@@ -9079,28 +9063,28 @@
 Add to cart</v>
       </c>
     </row>
+    <row r="543" xml:space="preserve">
+      <c r="A543" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4541 321-Coil, Nb. 1,
+5.00 x 1542.0 x coil mm</v>
+      </c>
+      <c r="B543" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4541 321-Coil, Nb. 1,
+5.00 x 1542.0 x coil mm
+Weight (Kg):4,890
+Quality:Prime
+Help
+Location:FABRICA ALGECIRAS
+2,875.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
     <row r="544" xml:space="preserve">
       <c r="A544" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4541 321-Coil, Nb. 1,
-5.00 x 1542.0 x coil mm</v>
+5.00 x 230.9 x coil mm</v>
       </c>
       <c r="B544" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4541 321-Coil, Nb. 1,
-5.00 x 1542.0 x coil mm
-Weight (Kg):4,890
-Quality:Prime
-Help
-Location:FABRICA ALGECIRAS
-2,875.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="545" xml:space="preserve">
-      <c r="A545" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4541 321-Coil, Nb. 1,
-5.00 x 230.9 x coil mm</v>
-      </c>
-      <c r="B545" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4541 321-Coil, Nb. 1,
 5.00 x 230.9 x coil mm
 Weight (Kg):4,198
@@ -9111,15 +9095,31 @@
 Add to cart</v>
       </c>
     </row>
+    <row r="545" xml:space="preserve">
+      <c r="A545" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4541 321-Sheet, 2B,
+3.00 x 1000.0 x 2000.0 mm</v>
+      </c>
+      <c r="B545" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4541 321-Sheet, 2B,
+3.00 x 1000.0 x 2000.0 mm
+Weight (Kg):1,104
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,385.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
     <row r="546" xml:space="preserve">
       <c r="A546" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4541 321-Sheet, 2B,
-3.00 x 1000.0 x 2000.0 mm</v>
+4.00 x 1000.0 x 2000.0 mm</v>
       </c>
       <c r="B546" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4541 321-Sheet, 2B,
-3.00 x 1000.0 x 2000.0 mm
-Weight (Kg):1,104
+4.00 x 1000.0 x 2000.0 mm
+Weight (Kg):1,552
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -9130,25 +9130,9 @@
     <row r="547" xml:space="preserve">
       <c r="A547" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4541 321-Sheet, 2B,
-4.00 x 1000.0 x 2000.0 mm</v>
+6.00 x 1250.0 x 2500.0 mm</v>
       </c>
       <c r="B547" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4541 321-Sheet, 2B,
-4.00 x 1000.0 x 2000.0 mm
-Weight (Kg):1,552
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-2,385.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="548" xml:space="preserve">
-      <c r="A548" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4541 321-Sheet, 2B,
-6.00 x 1250.0 x 2500.0 mm</v>
-      </c>
-      <c r="B548" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4541 321-Sheet, 2B,
 6.00 x 1250.0 x 2500.0 mm
 Weight (Kg):1,296
@@ -9159,12 +9143,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="549" xml:space="preserve">
-      <c r="A549" t="str" xml:space="preserve">
+    <row r="548" xml:space="preserve">
+      <c r="A548" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4541 321-Sheet, Nb. 1,
 8.00 x 1000.0 x 2000.0 mm</v>
       </c>
-      <c r="B549" t="str" xml:space="preserve">
+      <c r="B548" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4541 321-Sheet, Nb. 1,
 8.00 x 1000.0 x 2000.0 mm
 Weight (Kg):640
@@ -9175,28 +9159,28 @@
 Add to cart</v>
       </c>
     </row>
+    <row r="549" xml:space="preserve">
+      <c r="A549" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4512 409L-Coil, 2B,
+1.00 x 1304.0 x coil mm</v>
+      </c>
+      <c r="B549" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4512 409L-Coil, 2B,
+1.00 x 1304.0 x coil mm
+Weight (Kg):10,360
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+1,125.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
     <row r="550" xml:space="preserve">
       <c r="A550" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4512 409L-Coil, 2B,
-1.00 x 1304.0 x coil mm</v>
+1.00 x 625.0 x coil mm</v>
       </c>
       <c r="B550" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4512 409L-Coil, 2B,
-1.00 x 1304.0 x coil mm
-Weight (Kg):10,360
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-1,125.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="551" xml:space="preserve">
-      <c r="A551" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4512 409L-Coil, 2B,
-1.00 x 625.0 x coil mm</v>
-      </c>
-      <c r="B551" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4512 409L-Coil, 2B,
 1.00 x 625.0 x coil mm
 Weight (Kg):6,700
@@ -9207,28 +9191,28 @@
 Add to cart</v>
       </c>
     </row>
+    <row r="551" xml:space="preserve">
+      <c r="A551" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4512 409L-Coil, 2D,
+2.00 x 1291.0 x coil mm</v>
+      </c>
+      <c r="B551" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4512 409L-Coil, 2D,
+2.00 x 1291.0 x coil mm
+Weight (Kg):3,579
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+1,125.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
     <row r="552" xml:space="preserve">
       <c r="A552" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4512 409L-Coil, 2D,
-2.00 x 1291.0 x coil mm</v>
+2.00 x 150.0 x coil mm</v>
       </c>
       <c r="B552" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4512 409L-Coil, 2D,
-2.00 x 1291.0 x coil mm
-Weight (Kg):3,579
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-1,125.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="553" xml:space="preserve">
-      <c r="A553" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4512 409L-Coil, 2D,
-2.00 x 150.0 x coil mm</v>
-      </c>
-      <c r="B553" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4512 409L-Coil, 2D,
 2.00 x 150.0 x coil mm
 Weight (Kg):2,270
@@ -9239,15 +9223,31 @@
 Add to cart</v>
       </c>
     </row>
+    <row r="553" xml:space="preserve">
+      <c r="A553" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4512 409L-Coil, Nb. 1,
+4.00 x 140.0 x coil mm</v>
+      </c>
+      <c r="B553" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4512 409L-Coil, Nb. 1,
+4.00 x 140.0 x coil mm
+Weight (Kg):2,354
+Quality:Prime
+Help
+Location:FABRICA ALGECIRAS
+900.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
     <row r="554" xml:space="preserve">
       <c r="A554" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4512 409L-Coil, Nb. 1,
-4.00 x 140.0 x coil mm</v>
+5.00 x 190.0 x coil mm</v>
       </c>
       <c r="B554" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4512 409L-Coil, Nb. 1,
-4.00 x 140.0 x coil mm
-Weight (Kg):2,354
+5.00 x 190.0 x coil mm
+Weight (Kg):2,447
 Quality:Prime
 Help
 Location:FABRICA ALGECIRAS
@@ -9258,13 +9258,13 @@
     <row r="555" xml:space="preserve">
       <c r="A555" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4512 409L-Coil, Nb. 1,
-5.00 x 190.0 x coil mm</v>
+6.00 x 270.0 x coil mm</v>
       </c>
       <c r="B555" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4512 409L-Coil, Nb. 1,
-5.00 x 190.0 x coil mm
-Weight (Kg):2,447
-Quality:Prime
+6.00 x 270.0 x coil mm
+Weight (Kg):2,116
+Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
 900.00 €/ton
@@ -9279,7 +9279,7 @@
       <c r="B556" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4512 409L-Coil, Nb. 1,
 6.00 x 270.0 x coil mm
-Weight (Kg):2,116
+Weight (Kg):1,780
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -9290,13 +9290,13 @@
     <row r="557" xml:space="preserve">
       <c r="A557" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4512 409L-Coil, Nb. 1,
-6.00 x 270.0 x coil mm</v>
+8.00 x 115.9 x coil mm</v>
       </c>
       <c r="B557" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4512 409L-Coil, Nb. 1,
-6.00 x 270.0 x coil mm
-Weight (Kg):1,780
-Quality:Prime-2
+8.00 x 115.9 x coil mm
+Weight (Kg):1,238
+Quality:Prime
 Help
 Location:FABRICA ALGECIRAS
 900.00 €/ton
@@ -9306,12 +9306,12 @@
     <row r="558" xml:space="preserve">
       <c r="A558" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4512 409L-Coil, Nb. 1,
-8.00 x 115.9 x coil mm</v>
+8.00 x 125.9 x coil mm</v>
       </c>
       <c r="B558" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4512 409L-Coil, Nb. 1,
-8.00 x 115.9 x coil mm
-Weight (Kg):1,238
+8.00 x 125.9 x coil mm
+Weight (Kg):1,214
 Quality:Prime
 Help
 Location:FABRICA ALGECIRAS
@@ -9322,25 +9322,9 @@
     <row r="559" xml:space="preserve">
       <c r="A559" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4512 409L-Coil, Nb. 1,
-8.00 x 125.9 x coil mm</v>
+8.00 x 230.9 x coil mm</v>
       </c>
       <c r="B559" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4512 409L-Coil, Nb. 1,
-8.00 x 125.9 x coil mm
-Weight (Kg):1,214
-Quality:Prime
-Help
-Location:FABRICA ALGECIRAS
-900.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="560" xml:space="preserve">
-      <c r="A560" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4512 409L-Coil, Nb. 1,
-8.00 x 230.9 x coil mm</v>
-      </c>
-      <c r="B560" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4512 409L-Coil, Nb. 1,
 8.00 x 230.9 x coil mm
 Weight (Kg):2,960
@@ -9351,12 +9335,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="561" xml:space="preserve">
-      <c r="A561" t="str" xml:space="preserve">
+    <row r="560" xml:space="preserve">
+      <c r="A560" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4512 409L-Untrimmed, Coil, 2B,
 1.00 x 625.0 x coil mm</v>
       </c>
-      <c r="B561" t="str" xml:space="preserve">
+      <c r="B560" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4512 409L-Untrimmed, Coil, 2B,
 1.00 x 625.0 x coil mm
 Weight (Kg):3,441
@@ -9367,12 +9351,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="562" xml:space="preserve">
-      <c r="A562" t="str" xml:space="preserve">
+    <row r="561" xml:space="preserve">
+      <c r="A561" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4512 409L-Untrimmed, Coil, 2D,
 1.50 x 1295.0 x coil mm</v>
       </c>
-      <c r="B562" t="str" xml:space="preserve">
+      <c r="B561" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4512 409L-Untrimmed, Coil, 2D,
 1.50 x 1295.0 x coil mm
 Weight (Kg):2,445
@@ -9383,28 +9367,28 @@
 Add to cart</v>
       </c>
     </row>
+    <row r="562" xml:space="preserve">
+      <c r="A562" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, 2B,
+0.70 x 299.9 x coil mm</v>
+      </c>
+      <c r="B562" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, 2B,
+0.70 x 299.9 x coil mm
+Weight (Kg):2,518
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+1,000.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
     <row r="563" xml:space="preserve">
       <c r="A563" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, 2B,
-0.70 x 299.9 x coil mm</v>
+2.00 x 220.0 x coil mm</v>
       </c>
       <c r="B563" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, 2B,
-0.70 x 299.9 x coil mm
-Weight (Kg):2,518
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-1,000.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="564" xml:space="preserve">
-      <c r="A564" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, 2B,
-2.00 x 220.0 x coil mm</v>
-      </c>
-      <c r="B564" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, 2B,
 2.00 x 220.0 x coil mm
 Weight (Kg):776
@@ -9415,60 +9399,60 @@
 Add to cart</v>
       </c>
     </row>
+    <row r="564" xml:space="preserve">
+      <c r="A564" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, 2D,
+0.50 x 1518.0 x coil mm</v>
+      </c>
+      <c r="B564" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, 2D,
+0.50 x 1518.0 x coil mm
+Weight (Kg):4,480
+Quality:Prime
+Help
+Location:FABRICA ALGECIRAS
+1,325.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
     <row r="565" xml:space="preserve">
       <c r="A565" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, 2D,
-0.50 x 1518.0 x coil mm</v>
+0.70 x 1007.0 x coil mm</v>
       </c>
       <c r="B565" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, 2D,
-0.50 x 1518.0 x coil mm
-Weight (Kg):4,480
-Quality:Prime
-Help
-Location:FABRICA ALGECIRAS
-1,325.00 €/ton
+0.70 x 1007.0 x coil mm
+Weight (Kg):14,970
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+1,125.00 €/ton
 Add to cart</v>
       </c>
     </row>
     <row r="566" xml:space="preserve">
       <c r="A566" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, 2D,
-0.70 x 1007.0 x coil mm</v>
+0.70 x 1450.0 x coil mm</v>
       </c>
       <c r="B566" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, 2D,
-0.70 x 1007.0 x coil mm
-Weight (Kg):14,970
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-1,125.00 €/ton
+0.70 x 1450.0 x coil mm
+Weight (Kg):4,780
+Quality:Prime
+Help
+Location:FABRICA ALGECIRAS
+1,325.00 €/ton
 Add to cart</v>
       </c>
     </row>
     <row r="567" xml:space="preserve">
       <c r="A567" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, 2D,
-0.70 x 1450.0 x coil mm</v>
+0.70 x 869.0 x coil mm</v>
       </c>
       <c r="B567" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, 2D,
-0.70 x 1450.0 x coil mm
-Weight (Kg):4,780
-Quality:Prime
-Help
-Location:FABRICA ALGECIRAS
-1,325.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="568" xml:space="preserve">
-      <c r="A568" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, 2D,
-0.70 x 869.0 x coil mm</v>
-      </c>
-      <c r="B568" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, 2D,
 0.70 x 869.0 x coil mm
 Weight (Kg):13,570
@@ -9479,16 +9463,32 @@
 Add to cart</v>
       </c>
     </row>
+    <row r="568" xml:space="preserve">
+      <c r="A568" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, BA,
+0.70 x 100.9 x coil mm</v>
+      </c>
+      <c r="B568" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, BA,
+0.70 x 100.9 x coil mm
+Weight (Kg):778
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+1,000.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
     <row r="569" xml:space="preserve">
       <c r="A569" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, BA,
-0.60 x 310.0 x coil mm</v>
+0.70 x 110.9 x coil mm</v>
       </c>
       <c r="B569" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, BA,
-0.60 x 310.0 x coil mm
-Weight (Kg):786
-Quality:Prime
+0.70 x 110.9 x coil mm
+Weight (Kg):634
+Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
 1,000.00 €/ton
@@ -9498,13 +9498,13 @@
     <row r="570" xml:space="preserve">
       <c r="A570" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, BA,
-0.70 x 100.9 x coil mm</v>
+0.70 x 110.9 x coil mm</v>
       </c>
       <c r="B570" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, BA,
-0.70 x 100.9 x coil mm
-Weight (Kg):778
-Quality:Prime-2
+0.70 x 110.9 x coil mm
+Weight (Kg):658
+Quality:Prime
 Help
 Location:FABRICA ALGECIRAS
 1,000.00 €/ton
@@ -9514,13 +9514,13 @@
     <row r="571" xml:space="preserve">
       <c r="A571" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, BA,
-0.70 x 110.9 x coil mm</v>
+0.70 x 120.0 x coil mm</v>
       </c>
       <c r="B571" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, BA,
-0.70 x 110.9 x coil mm
-Weight (Kg):634
-Quality:Prime-2
+0.70 x 120.0 x coil mm
+Weight (Kg):836
+Quality:Prime
 Help
 Location:FABRICA ALGECIRAS
 1,000.00 €/ton
@@ -9530,12 +9530,12 @@
     <row r="572" xml:space="preserve">
       <c r="A572" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, BA,
-0.70 x 110.9 x coil mm</v>
+0.70 x 125.0 x coil mm</v>
       </c>
       <c r="B572" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, BA,
-0.70 x 110.9 x coil mm
-Weight (Kg):658
+0.70 x 125.0 x coil mm
+Weight (Kg):1,288
 Quality:Prime
 Help
 Location:FABRICA ALGECIRAS
@@ -9546,12 +9546,12 @@
     <row r="573" xml:space="preserve">
       <c r="A573" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, BA,
-0.70 x 120.0 x coil mm</v>
+0.70 x 125.9 x coil mm</v>
       </c>
       <c r="B573" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, BA,
-0.70 x 120.0 x coil mm
-Weight (Kg):836
+0.70 x 125.9 x coil mm
+Weight (Kg):708
 Quality:Prime
 Help
 Location:FABRICA ALGECIRAS
@@ -9562,13 +9562,13 @@
     <row r="574" xml:space="preserve">
       <c r="A574" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, BA,
-0.70 x 125.0 x coil mm</v>
+0.70 x 126.0 x coil mm</v>
       </c>
       <c r="B574" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, BA,
-0.70 x 125.0 x coil mm
-Weight (Kg):1,288
-Quality:Prime
+0.70 x 126.0 x coil mm
+Weight (Kg):804
+Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
 1,000.00 €/ton
@@ -9578,13 +9578,13 @@
     <row r="575" xml:space="preserve">
       <c r="A575" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, BA,
-0.70 x 125.9 x coil mm</v>
+0.70 x 155.9 x coil mm</v>
       </c>
       <c r="B575" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, BA,
-0.70 x 125.9 x coil mm
-Weight (Kg):708
-Quality:Prime
+0.70 x 155.9 x coil mm
+Weight (Kg):1,148
+Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
 1,000.00 €/ton
@@ -9594,12 +9594,12 @@
     <row r="576" xml:space="preserve">
       <c r="A576" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, BA,
-0.70 x 126.0 x coil mm</v>
+0.70 x 175.9 x coil mm</v>
       </c>
       <c r="B576" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, BA,
-0.70 x 126.0 x coil mm
-Weight (Kg):804
+0.70 x 175.9 x coil mm
+Weight (Kg):944
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -9690,12 +9690,12 @@
     <row r="582" xml:space="preserve">
       <c r="A582" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, BA,
-0.70 x 155.9 x coil mm</v>
+0.70 x 175.9 x coil mm</v>
       </c>
       <c r="B582" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, BA,
-0.70 x 155.9 x coil mm
-Weight (Kg):1,148
+0.70 x 175.9 x coil mm
+Weight (Kg):1,054
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -9706,13 +9706,13 @@
     <row r="583" xml:space="preserve">
       <c r="A583" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, BA,
-0.70 x 175.9 x coil mm</v>
+0.70 x 181.9 x coil mm</v>
       </c>
       <c r="B583" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, BA,
-0.70 x 175.9 x coil mm
-Weight (Kg):944
-Quality:Prime-2
+0.70 x 181.9 x coil mm
+Weight (Kg):1,632
+Quality:Prime
 Help
 Location:FABRICA ALGECIRAS
 1,000.00 €/ton
@@ -9722,12 +9722,12 @@
     <row r="584" xml:space="preserve">
       <c r="A584" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, BA,
-0.70 x 175.9 x coil mm</v>
+0.70 x 195.9 x coil mm</v>
       </c>
       <c r="B584" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, BA,
-0.70 x 175.9 x coil mm
-Weight (Kg):1,054
+0.70 x 195.9 x coil mm
+Weight (Kg):1,174
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -9738,13 +9738,13 @@
     <row r="585" xml:space="preserve">
       <c r="A585" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, BA,
-0.70 x 181.9 x coil mm</v>
+0.70 x 195.9 x coil mm</v>
       </c>
       <c r="B585" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, BA,
-0.70 x 181.9 x coil mm
-Weight (Kg):1,632
-Quality:Prime
+0.70 x 195.9 x coil mm
+Weight (Kg):1,541
+Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
 1,000.00 €/ton
@@ -9754,12 +9754,12 @@
     <row r="586" xml:space="preserve">
       <c r="A586" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, BA,
-0.70 x 195.9 x coil mm</v>
+0.70 x 200.9 x coil mm</v>
       </c>
       <c r="B586" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, BA,
-0.70 x 195.9 x coil mm
-Weight (Kg):1,174
+0.70 x 200.9 x coil mm
+Weight (Kg):1,098
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -9770,12 +9770,12 @@
     <row r="587" xml:space="preserve">
       <c r="A587" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, BA,
-0.70 x 195.9 x coil mm</v>
+0.70 x 260.9 x coil mm</v>
       </c>
       <c r="B587" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, BA,
-0.70 x 195.9 x coil mm
-Weight (Kg):1,541
+0.70 x 260.9 x coil mm
+Weight (Kg):2,121
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -9786,44 +9786,44 @@
     <row r="588" xml:space="preserve">
       <c r="A588" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, BA,
-0.70 x 200.9 x coil mm</v>
+0.70 x 825.0 x coil mm</v>
       </c>
       <c r="B588" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, BA,
-0.70 x 200.9 x coil mm
-Weight (Kg):1,098
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-1,000.00 €/ton
+0.70 x 825.0 x coil mm
+Weight (Kg):5,270
+Quality:Prime
+Help
+Location:FABRICA ALGECIRAS
+1,325.00 €/ton
 Add to cart</v>
       </c>
     </row>
     <row r="589" xml:space="preserve">
       <c r="A589" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, BA,
-0.70 x 260.9 x coil mm</v>
+0.70 x 842.0 x coil mm</v>
       </c>
       <c r="B589" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, BA,
-0.70 x 260.9 x coil mm
-Weight (Kg):2,121
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-1,000.00 €/ton
+0.70 x 842.0 x coil mm
+Weight (Kg):10,370
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+1,125.00 €/ton
 Add to cart</v>
       </c>
     </row>
     <row r="590" xml:space="preserve">
       <c r="A590" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, BA,
-0.70 x 825.0 x coil mm</v>
+0.70 x 855.0 x coil mm</v>
       </c>
       <c r="B590" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, BA,
-0.70 x 825.0 x coil mm
-Weight (Kg):5,270
+0.70 x 855.0 x coil mm
+Weight (Kg):3,990
 Quality:Prime
 Help
 Location:FABRICA ALGECIRAS
@@ -9834,73 +9834,41 @@
     <row r="591" xml:space="preserve">
       <c r="A591" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, BA,
-0.70 x 842.0 x coil mm</v>
+0.70 x 870.0 x coil mm</v>
       </c>
       <c r="B591" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, BA,
-0.70 x 842.0 x coil mm
-Weight (Kg):10,370
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-1,125.00 €/ton
+0.70 x 870.0 x coil mm
+Weight (Kg):13,910
+Quality:Prime
+Help
+Location:FABRICA ALGECIRAS
+1,900.00 €/ton
 Add to cart</v>
       </c>
     </row>
     <row r="592" xml:space="preserve">
       <c r="A592" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, BA,
-0.70 x 855.0 x coil mm</v>
+0.70 x 953.0 x coil mm</v>
       </c>
       <c r="B592" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, BA,
-0.70 x 855.0 x coil mm
-Weight (Kg):3,990
-Quality:Prime
-Help
-Location:FABRICA ALGECIRAS
-1,325.00 €/ton
+0.70 x 953.0 x coil mm
+Weight (Kg):6,970
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+1,125.00 €/ton
 Add to cart</v>
       </c>
     </row>
     <row r="593" xml:space="preserve">
       <c r="A593" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, BA,
-0.70 x 870.0 x coil mm</v>
+1.00 x 530.0 x coil mm</v>
       </c>
       <c r="B593" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, BA,
-0.70 x 870.0 x coil mm
-Weight (Kg):13,910
-Quality:Prime
-Help
-Location:FABRICA ALGECIRAS
-1,900.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="594" xml:space="preserve">
-      <c r="A594" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, BA,
-0.70 x 953.0 x coil mm</v>
-      </c>
-      <c r="B594" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, BA,
-0.70 x 953.0 x coil mm
-Weight (Kg):6,970
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-1,125.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="595" xml:space="preserve">
-      <c r="A595" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, BA,
-1.00 x 530.0 x coil mm</v>
-      </c>
-      <c r="B595" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, BA,
 1.00 x 530.0 x coil mm
 Weight (Kg):880
@@ -9911,31 +9879,63 @@
 Add to cart</v>
       </c>
     </row>
+    <row r="594" xml:space="preserve">
+      <c r="A594" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, Polished N4-G-180,
+0.90 x 1250.0 x coil mm</v>
+      </c>
+      <c r="B594" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, Polished N4-G-180,
+0.90 x 1250.0 x coil mm
+Weight (Kg):2,218
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+1,125.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="595" xml:space="preserve">
+      <c r="A595" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, Polished N4-G-180,
+1.20 x 120.0 x coil mm</v>
+      </c>
+      <c r="B595" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, Polished N4-G-180,
+1.20 x 120.0 x coil mm
+Weight (Kg):1,430
+Quality:Prime
+Help
+Location:FABRICA ALGECIRAS
+1,000.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
     <row r="596" xml:space="preserve">
       <c r="A596" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, Polished N4-G-180,
-0.90 x 1250.0 x coil mm</v>
+1.20 x 250.0 x coil mm</v>
       </c>
       <c r="B596" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, Polished N4-G-180,
-0.90 x 1250.0 x coil mm
-Weight (Kg):2,218
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-1,125.00 €/ton
+1.20 x 250.0 x coil mm
+Weight (Kg):1,902
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+1,000.00 €/ton
 Add to cart</v>
       </c>
     </row>
     <row r="597" xml:space="preserve">
       <c r="A597" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, Polished N4-G-180,
-1.20 x 120.0 x coil mm</v>
+1.20 x 250.9 x coil mm</v>
       </c>
       <c r="B597" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, Polished N4-G-180,
-1.20 x 120.0 x coil mm
-Weight (Kg):1,430
+1.20 x 250.9 x coil mm
+Weight (Kg):1,960
 Quality:Prime
 Help
 Location:FABRICA ALGECIRAS
@@ -9946,12 +9946,12 @@
     <row r="598" xml:space="preserve">
       <c r="A598" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, Polished N4-G-180,
-1.20 x 250.0 x coil mm</v>
+1.20 x 250.9 x coil mm</v>
       </c>
       <c r="B598" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, Polished N4-G-180,
-1.20 x 250.0 x coil mm
-Weight (Kg):1,902
+1.20 x 250.9 x coil mm
+Weight (Kg):1,918
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -9962,13 +9962,13 @@
     <row r="599" xml:space="preserve">
       <c r="A599" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, Polished N4-G-180,
-1.20 x 250.9 x coil mm</v>
+1.20 x 260.9 x coil mm</v>
       </c>
       <c r="B599" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, Polished N4-G-180,
-1.20 x 250.9 x coil mm
-Weight (Kg):1,960
-Quality:Prime
+1.20 x 260.9 x coil mm
+Weight (Kg):1,524
+Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
 1,000.00 €/ton
@@ -9978,12 +9978,12 @@
     <row r="600" xml:space="preserve">
       <c r="A600" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, Polished N4-G-180,
-1.20 x 250.9 x coil mm</v>
+1.20 x 260.9 x coil mm</v>
       </c>
       <c r="B600" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, Polished N4-G-180,
-1.20 x 250.9 x coil mm
-Weight (Kg):1,918
+1.20 x 260.9 x coil mm
+Weight (Kg):1,934
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -10009,13 +10009,13 @@
     </row>
     <row r="602" xml:space="preserve">
       <c r="A602" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, Polished N4-G-180,
-1.20 x 260.9 x coil mm</v>
+        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, SB-G-400,
+0.60 x 134.9 x coil mm</v>
       </c>
       <c r="B602" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, Polished N4-G-180,
-1.20 x 260.9 x coil mm
-Weight (Kg):1,524
+        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, SB-G-400,
+0.60 x 134.9 x coil mm
+Weight (Kg):1,134
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -10025,13 +10025,13 @@
     </row>
     <row r="603" xml:space="preserve">
       <c r="A603" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, Polished N4-G-180,
-1.20 x 260.9 x coil mm</v>
+        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, SB-G-400,
+0.60 x 134.9 x coil mm</v>
       </c>
       <c r="B603" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, Polished N4-G-180,
-1.20 x 260.9 x coil mm
-Weight (Kg):1,934
+        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, SB-G-400,
+0.60 x 134.9 x coil mm
+Weight (Kg):962
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -10042,12 +10042,12 @@
     <row r="604" xml:space="preserve">
       <c r="A604" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, SB-G-400,
-0.60 x 134.9 x coil mm</v>
+0.60 x 245.9 x coil mm</v>
       </c>
       <c r="B604" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, SB-G-400,
-0.60 x 134.9 x coil mm
-Weight (Kg):1,134
+0.60 x 245.9 x coil mm
+Weight (Kg):1,778
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -10058,12 +10058,12 @@
     <row r="605" xml:space="preserve">
       <c r="A605" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, SB-G-400,
-0.60 x 134.9 x coil mm</v>
+1.00 x 118.9 x coil mm</v>
       </c>
       <c r="B605" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, SB-G-400,
-0.60 x 134.9 x coil mm
-Weight (Kg):962
+1.00 x 118.9 x coil mm
+Weight (Kg):754
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -10074,12 +10074,12 @@
     <row r="606" xml:space="preserve">
       <c r="A606" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, SB-G-400,
-0.60 x 245.9 x coil mm</v>
+1.00 x 118.9 x coil mm</v>
       </c>
       <c r="B606" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, SB-G-400,
-0.60 x 245.9 x coil mm
-Weight (Kg):1,778
+1.00 x 118.9 x coil mm
+Weight (Kg):802
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -10090,41 +10090,9 @@
     <row r="607" xml:space="preserve">
       <c r="A607" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, SB-G-400,
-1.00 x 118.9 x coil mm</v>
+1.00 x 266.9 x coil mm</v>
       </c>
       <c r="B607" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, SB-G-400,
-1.00 x 118.9 x coil mm
-Weight (Kg):754
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-1,000.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="608" xml:space="preserve">
-      <c r="A608" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, SB-G-400,
-1.00 x 118.9 x coil mm</v>
-      </c>
-      <c r="B608" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, SB-G-400,
-1.00 x 118.9 x coil mm
-Weight (Kg):802
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-1,000.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="609" xml:space="preserve">
-      <c r="A609" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, SB-G-400,
-1.00 x 266.9 x coil mm</v>
-      </c>
-      <c r="B609" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, SB-G-400,
 1.00 x 266.9 x coil mm
 Weight (Kg):1,322
@@ -10135,12 +10103,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="610" xml:space="preserve">
-      <c r="A610" t="str" xml:space="preserve">
+    <row r="608" xml:space="preserve">
+      <c r="A608" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, SB-G-500,
 0.70 x 245.9 x coil mm</v>
       </c>
-      <c r="B610" t="str" xml:space="preserve">
+      <c r="B608" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, SB-G-500,
 0.70 x 245.9 x coil mm
 Weight (Kg):1,496
@@ -10151,31 +10119,63 @@
 Add to cart</v>
       </c>
     </row>
+    <row r="609" xml:space="preserve">
+      <c r="A609" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, SBA,
+0.70 x 1056.0 x coil mm</v>
+      </c>
+      <c r="B609" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, SBA,
+0.70 x 1056.0 x coil mm
+Weight (Kg):15,197
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+1,125.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="610" xml:space="preserve">
+      <c r="A610" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, SBA,
+0.70 x 150.9 x coil mm</v>
+      </c>
+      <c r="B610" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, SBA,
+0.70 x 150.9 x coil mm
+Weight (Kg):1,268
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+1,000.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
     <row r="611" xml:space="preserve">
       <c r="A611" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, SBA,
-0.70 x 1056.0 x coil mm</v>
+0.70 x 173.0 x coil mm</v>
       </c>
       <c r="B611" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, SBA,
-0.70 x 1056.0 x coil mm
-Weight (Kg):15,197
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-1,125.00 €/ton
+0.70 x 173.0 x coil mm
+Weight (Kg):890
+Quality:Prime
+Help
+Location:FABRICA ALGECIRAS
+1,000.00 €/ton
 Add to cart</v>
       </c>
     </row>
     <row r="612" xml:space="preserve">
       <c r="A612" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, SBA,
-0.70 x 150.9 x coil mm</v>
+0.70 x 195.9 x coil mm</v>
       </c>
       <c r="B612" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, SBA,
-0.70 x 150.9 x coil mm
-Weight (Kg):1,268
+0.70 x 195.9 x coil mm
+Weight (Kg):962
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -10186,60 +10186,60 @@
     <row r="613" xml:space="preserve">
       <c r="A613" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, SBA,
-0.70 x 173.0 x coil mm</v>
+0.70 x 682.0 x coil mm</v>
       </c>
       <c r="B613" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, SBA,
-0.70 x 173.0 x coil mm
-Weight (Kg):890
-Quality:Prime
-Help
-Location:FABRICA ALGECIRAS
-1,000.00 €/ton
+0.70 x 682.0 x coil mm
+Weight (Kg):3,870
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+1,025.00 €/ton
 Add to cart</v>
       </c>
     </row>
     <row r="614" xml:space="preserve">
       <c r="A614" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, SBA,
-0.70 x 195.9 x coil mm</v>
+0.70 x 825.0 x coil mm</v>
       </c>
       <c r="B614" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, SBA,
-0.70 x 195.9 x coil mm
-Weight (Kg):962
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-1,000.00 €/ton
+0.70 x 825.0 x coil mm
+Weight (Kg):6,448
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+1,125.00 €/ton
 Add to cart</v>
       </c>
     </row>
     <row r="615" xml:space="preserve">
       <c r="A615" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, SBA,
-0.70 x 682.0 x coil mm</v>
+0.70 x 942.0 x coil mm</v>
       </c>
       <c r="B615" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, SBA,
-0.70 x 682.0 x coil mm
-Weight (Kg):3,870
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-1,025.00 €/ton
+0.70 x 942.0 x coil mm
+Weight (Kg):1,810
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+1,125.00 €/ton
 Add to cart</v>
       </c>
     </row>
     <row r="616" xml:space="preserve">
       <c r="A616" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, SBA,
-0.70 x 825.0 x coil mm</v>
+0.70 x 948.0 x coil mm</v>
       </c>
       <c r="B616" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, SBA,
-0.70 x 825.0 x coil mm
-Weight (Kg):6,448
+0.70 x 948.0 x coil mm
+Weight (Kg):3,410
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -10250,12 +10250,12 @@
     <row r="617" xml:space="preserve">
       <c r="A617" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, SBA,
-0.70 x 942.0 x coil mm</v>
+0.70 x 960.0 x coil mm</v>
       </c>
       <c r="B617" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, SBA,
-0.70 x 942.0 x coil mm
-Weight (Kg):1,810
+0.70 x 960.0 x coil mm
+Weight (Kg):2,780
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -10266,41 +10266,9 @@
     <row r="618" xml:space="preserve">
       <c r="A618" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, SBA,
-0.70 x 948.0 x coil mm</v>
+0.70 x 963.0 x coil mm</v>
       </c>
       <c r="B618" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, SBA,
-0.70 x 948.0 x coil mm
-Weight (Kg):3,410
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-1,125.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="619" xml:space="preserve">
-      <c r="A619" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, SBA,
-0.70 x 960.0 x coil mm</v>
-      </c>
-      <c r="B619" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, SBA,
-0.70 x 960.0 x coil mm
-Weight (Kg):2,780
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-1,125.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="620" xml:space="preserve">
-      <c r="A620" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, SBA,
-0.70 x 963.0 x coil mm</v>
-      </c>
-      <c r="B620" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, SBA,
 0.70 x 963.0 x coil mm
 Weight (Kg):4,570
@@ -10308,6 +10276,38 @@
 Help
 Location:FABRICA ALGECIRAS
 1,325.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="619" xml:space="preserve">
+      <c r="A619" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Disk, BA,
+0.60 x 550.0 x 0.0 mm</v>
+      </c>
+      <c r="B619" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Disk, BA,
+0.60 x 550.0 x 0.0 mm
+Weight (Kg):578
+Quality:Prime
+Help
+Location:FABRICA ALGECIRAS
+1,900.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="620" xml:space="preserve">
+      <c r="A620" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Disk, BA,
+0.60 x 550.0 x 0.0 mm</v>
+      </c>
+      <c r="B620" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Disk, BA,
+0.60 x 550.0 x 0.0 mm
+Weight (Kg):572
+Quality:Prime
+Help
+Location:FABRICA ALGECIRAS
+1,900.00 €/ton
 Add to cart</v>
       </c>
     </row>
@@ -10319,7 +10319,7 @@
       <c r="B621" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Disk, BA,
 0.60 x 550.0 x 0.0 mm
-Weight (Kg):578
+Weight (Kg):576
 Quality:Prime
 Help
 Location:FABRICA ALGECIRAS
@@ -10335,7 +10335,7 @@
       <c r="B622" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Disk, BA,
 0.60 x 550.0 x 0.0 mm
-Weight (Kg):572
+Weight (Kg):578
 Quality:Prime
 Help
 Location:FABRICA ALGECIRAS
@@ -10351,7 +10351,7 @@
       <c r="B623" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Disk, BA,
 0.60 x 550.0 x 0.0 mm
-Weight (Kg):576
+Weight (Kg):582
 Quality:Prime
 Help
 Location:FABRICA ALGECIRAS
@@ -10361,74 +10361,42 @@
     </row>
     <row r="624" xml:space="preserve">
       <c r="A624" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Disk, BA,
-0.60 x 550.0 x 0.0 mm</v>
+        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Sheet, 2B,
+2.00 x 1250.0 x 2500.0 mm</v>
       </c>
       <c r="B624" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Disk, BA,
-0.60 x 550.0 x 0.0 mm
-Weight (Kg):578
-Quality:Prime
-Help
-Location:FABRICA ALGECIRAS
-1,900.00 €/ton
+        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Sheet, 2B,
+2.00 x 1250.0 x 2500.0 mm
+Weight (Kg):619
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+1,125.00 €/ton
 Add to cart</v>
       </c>
     </row>
     <row r="625" xml:space="preserve">
       <c r="A625" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Disk, BA,
-0.60 x 550.0 x 0.0 mm</v>
+        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Sheet, 2B,
+3.00 x 1250.0 x 2500.0 mm</v>
       </c>
       <c r="B625" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Disk, BA,
-0.60 x 550.0 x 0.0 mm
-Weight (Kg):582
-Quality:Prime
-Help
-Location:FABRICA ALGECIRAS
-1,900.00 €/ton
+        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Sheet, 2B,
+3.00 x 1250.0 x 2500.0 mm
+Weight (Kg):566
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+1,125.00 €/ton
 Add to cart</v>
       </c>
     </row>
     <row r="626" xml:space="preserve">
       <c r="A626" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Sheet, 2B,
-2.00 x 1250.0 x 2500.0 mm</v>
+3.00 x 1250.0 x 2500.0 mm</v>
       </c>
       <c r="B626" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Sheet, 2B,
-2.00 x 1250.0 x 2500.0 mm
-Weight (Kg):619
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-1,125.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="627" xml:space="preserve">
-      <c r="A627" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Sheet, 2B,
-3.00 x 1250.0 x 2500.0 mm</v>
-      </c>
-      <c r="B627" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Sheet, 2B,
-3.00 x 1250.0 x 2500.0 mm
-Weight (Kg):566
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-1,125.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="628" xml:space="preserve">
-      <c r="A628" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Sheet, 2B,
-3.00 x 1250.0 x 2500.0 mm</v>
-      </c>
-      <c r="B628" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Sheet, 2B,
 3.00 x 1250.0 x 2500.0 mm
 Weight (Kg):640
@@ -10439,12 +10407,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="629" xml:space="preserve">
-      <c r="A629" t="str" xml:space="preserve">
+    <row r="627" xml:space="preserve">
+      <c r="A627" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Sheet, BA,
 0.70 x 1250.0 x 2500.0 mm</v>
       </c>
-      <c r="B629" t="str" xml:space="preserve">
+      <c r="B627" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Sheet, BA,
 0.70 x 1250.0 x 2500.0 mm
 Weight (Kg):766
@@ -10455,12 +10423,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="630" xml:space="preserve">
-      <c r="A630" t="str" xml:space="preserve">
+    <row r="628" xml:space="preserve">
+      <c r="A628" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Sheet, SB-G-400,
 1.00 x 1500.0 x 3000.0 mm</v>
       </c>
-      <c r="B630" t="str" xml:space="preserve">
+      <c r="B628" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Sheet, SB-G-400,
 1.00 x 1500.0 x 3000.0 mm
 Weight (Kg):1,940
@@ -10471,12 +10439,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="631" xml:space="preserve">
-      <c r="A631" t="str" xml:space="preserve">
+    <row r="629" xml:space="preserve">
+      <c r="A629" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Untrimmed, Coil, 1/4 HT,
 3.00 x 1292.0 x coil mm</v>
       </c>
-      <c r="B631" t="str" xml:space="preserve">
+      <c r="B629" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Untrimmed, Coil, 1/4 HT,
 3.00 x 1292.0 x coil mm
 Weight (Kg):3,641
@@ -10487,12 +10455,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="632" xml:space="preserve">
-      <c r="A632" t="str" xml:space="preserve">
+    <row r="630" xml:space="preserve">
+      <c r="A630" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Untrimmed, Coil, 2B,
 1.20 x 1500.0 x coil mm</v>
       </c>
-      <c r="B632" t="str" xml:space="preserve">
+      <c r="B630" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Untrimmed, Coil, 2B,
 1.20 x 1500.0 x coil mm
 Weight (Kg):4,750
@@ -10503,12 +10471,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="633" xml:space="preserve">
-      <c r="A633" t="str" xml:space="preserve">
+    <row r="631" xml:space="preserve">
+      <c r="A631" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Untrimmed, Coil, 2D, ET-100
 0.50 x 1250.0 x coil mm</v>
       </c>
-      <c r="B633" t="str" xml:space="preserve">
+      <c r="B631" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Untrimmed, Coil, 2D, ET-100
 0.50 x 1250.0 x coil mm
 Weight (Kg):5,160
@@ -10519,12 +10487,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="634" xml:space="preserve">
-      <c r="A634" t="str" xml:space="preserve">
+    <row r="632" xml:space="preserve">
+      <c r="A632" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Untrimmed, Coil, 2D, ET-100
 0.50 x 1250.0 x coil mm</v>
       </c>
-      <c r="B634" t="str" xml:space="preserve">
+      <c r="B632" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Untrimmed, Coil, 2D, ET-100
 0.50 x 1250.0 x coil mm
 Weight (Kg):3,695
@@ -10535,12 +10503,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="635" xml:space="preserve">
-      <c r="A635" t="str" xml:space="preserve">
+    <row r="633" xml:space="preserve">
+      <c r="A633" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Untrimmed, Coil, BA,
 0.60 x 1246.0 x coil mm</v>
       </c>
-      <c r="B635" t="str" xml:space="preserve">
+      <c r="B633" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Untrimmed, Coil, BA,
 0.60 x 1246.0 x coil mm
 Weight (Kg):2,585
@@ -10551,28 +10519,44 @@
 Add to cart</v>
       </c>
     </row>
+    <row r="634" xml:space="preserve">
+      <c r="A634" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Untrimmed, Coil, BA,
+1.00 x 1028.0 x coil mm</v>
+      </c>
+      <c r="B634" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Untrimmed, Coil, BA,
+1.00 x 1028.0 x coil mm
+Weight (Kg):2,430
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+1,125.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="635" xml:space="preserve">
+      <c r="A635" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Untrimmed, Coil, 2B,
+0.40 x 1264.0 x coil mm</v>
+      </c>
+      <c r="B635" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Untrimmed, Coil, 2B,
+0.40 x 1264.0 x coil mm
+Weight (Kg):5,720
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+1,125.00 €/ton
+Out of Stock</v>
+      </c>
+    </row>
     <row r="636" xml:space="preserve">
       <c r="A636" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Untrimmed, Coil, 2B,
-0.40 x 1264.0 x coil mm</v>
+0.40 x 1273.0 x coil mm</v>
       </c>
       <c r="B636" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Untrimmed, Coil, 2B,
-0.40 x 1264.0 x coil mm
-Weight (Kg):5,720
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-1,125.00 €/ton
-Out of Stock</v>
-      </c>
-    </row>
-    <row r="637" xml:space="preserve">
-      <c r="A637" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Untrimmed, Coil, 2B,
-0.40 x 1273.0 x coil mm</v>
-      </c>
-      <c r="B637" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Untrimmed, Coil, 2B,
 0.40 x 1273.0 x coil mm
 Weight (Kg):5,176
@@ -10583,47 +10567,63 @@
 Reserved</v>
       </c>
     </row>
+    <row r="637" xml:space="preserve">
+      <c r="A637" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Untrimmed, Coil, BA,
+0.50 x 1015.0 x coil mm</v>
+      </c>
+      <c r="B637" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Untrimmed, Coil, BA,
+0.50 x 1015.0 x coil mm
+Weight (Kg):2,340
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+1,125.00 €/ton
+Out of Stock</v>
+      </c>
+    </row>
     <row r="638" xml:space="preserve">
       <c r="A638" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Untrimmed, Coil, BA,
-0.50 x 1015.0 x coil mm</v>
+0.50 x 1107.0 x coil mm</v>
       </c>
       <c r="B638" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Untrimmed, Coil, BA,
-0.50 x 1015.0 x coil mm
-Weight (Kg):2,340
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-1,125.00 €/ton
-Out of Stock</v>
+0.50 x 1107.0 x coil mm
+Weight (Kg):2,230
+Quality:Prime
+Help
+Location:FABRICA ALGECIRAS
+1,325.00 €/ton
+Reserved</v>
       </c>
     </row>
     <row r="639" xml:space="preserve">
       <c r="A639" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Untrimmed, Coil, BA,
-0.50 x 1107.0 x coil mm</v>
+0.60 x 1270.0 x coil mm</v>
       </c>
       <c r="B639" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Untrimmed, Coil, BA,
-0.50 x 1107.0 x coil mm
-Weight (Kg):2,230
-Quality:Prime
-Help
-Location:FABRICA ALGECIRAS
-1,325.00 €/ton
+0.60 x 1270.0 x coil mm
+Weight (Kg):3,385
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+1,125.00 €/ton
 Reserved</v>
       </c>
     </row>
     <row r="640" xml:space="preserve">
       <c r="A640" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Untrimmed, Coil, BA,
-0.60 x 1270.0 x coil mm</v>
+0.60 x 1275.0 x coil mm</v>
       </c>
       <c r="B640" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Untrimmed, Coil, BA,
-0.60 x 1270.0 x coil mm
-Weight (Kg):3,385
+0.60 x 1275.0 x coil mm
+Weight (Kg):3,535
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -10634,28 +10634,28 @@
     <row r="641" xml:space="preserve">
       <c r="A641" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Untrimmed, Coil, BA,
-0.60 x 1275.0 x coil mm</v>
+1.00 x 1285.0 x coil mm</v>
       </c>
       <c r="B641" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Untrimmed, Coil, BA,
-0.60 x 1275.0 x coil mm
-Weight (Kg):3,535
+1.00 x 1285.0 x coil mm
+Weight (Kg):5,491
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
 1,125.00 €/ton
-Reserved</v>
+Out of Stock</v>
       </c>
     </row>
     <row r="642" xml:space="preserve">
       <c r="A642" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Untrimmed, Coil, BA,
-1.00 x 1028.0 x coil mm</v>
+        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Untrimmed, Coil, SBA,
+0.70 x 825.0 x coil mm</v>
       </c>
       <c r="B642" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Untrimmed, Coil, BA,
-1.00 x 1028.0 x coil mm
-Weight (Kg):2,430
+        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Untrimmed, Coil, SBA,
+0.70 x 825.0 x coil mm
+Weight (Kg):7,260
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -10666,25 +10666,9 @@
     <row r="643" xml:space="preserve">
       <c r="A643" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Untrimmed, Coil, SBA,
-0.70 x 825.0 x coil mm</v>
+0.70 x 873.0 x coil mm</v>
       </c>
       <c r="B643" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Untrimmed, Coil, SBA,
-0.70 x 825.0 x coil mm
-Weight (Kg):7,260
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-1,125.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="644" xml:space="preserve">
-      <c r="A644" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Untrimmed, Coil, SBA,
-0.70 x 873.0 x coil mm</v>
-      </c>
-      <c r="B644" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Untrimmed, Coil, SBA,
 0.70 x 873.0 x coil mm
 Weight (Kg):4,020
@@ -10695,12 +10679,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="645" xml:space="preserve">
-      <c r="A645" t="str" xml:space="preserve">
+    <row r="644" xml:space="preserve">
+      <c r="A644" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4510 430Ti-Coil, 2B,
 2.00 x 100.9 x coil mm</v>
       </c>
-      <c r="B645" t="str" xml:space="preserve">
+      <c r="B644" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4510 430Ti-Coil, 2B,
 2.00 x 100.9 x coil mm
 Weight (Kg):1,710
@@ -10711,16 +10695,32 @@
 Add to cart</v>
       </c>
     </row>
+    <row r="645" xml:space="preserve">
+      <c r="A645" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4510 430Ti-Coil, BA,
+0.50 x 170.0 x coil mm</v>
+      </c>
+      <c r="B645" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4510 430Ti-Coil, BA,
+0.50 x 170.0 x coil mm
+Weight (Kg):914
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+1,000.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
     <row r="646" xml:space="preserve">
       <c r="A646" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4510 430Ti-Coil, BA,
-0.50 x 170.0 x coil mm</v>
+0.70 x 100.9 x coil mm</v>
       </c>
       <c r="B646" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4510 430Ti-Coil, BA,
-0.50 x 170.0 x coil mm
-Weight (Kg):914
-Quality:Prime-2
+0.70 x 100.9 x coil mm
+Weight (Kg):638
+Quality:Prime
 Help
 Location:FABRICA ALGECIRAS
 1,000.00 €/ton
@@ -10730,44 +10730,44 @@
     <row r="647" xml:space="preserve">
       <c r="A647" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4510 430Ti-Coil, BA,
-0.70 x 100.9 x coil mm</v>
+0.70 x 1020.0 x coil mm</v>
       </c>
       <c r="B647" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4510 430Ti-Coil, BA,
-0.70 x 100.9 x coil mm
-Weight (Kg):638
-Quality:Prime
-Help
-Location:FABRICA ALGECIRAS
-1,000.00 €/ton
+0.70 x 1020.0 x coil mm
+Weight (Kg):16,000
+Quality:Prime
+Help
+Location:FABRICA ALGECIRAS
+1,900.00 €/ton
 Add to cart</v>
       </c>
     </row>
     <row r="648" xml:space="preserve">
       <c r="A648" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4510 430Ti-Coil, BA,
-0.70 x 1020.0 x coil mm</v>
+0.70 x 108.0 x coil mm</v>
       </c>
       <c r="B648" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4510 430Ti-Coil, BA,
-0.70 x 1020.0 x coil mm
-Weight (Kg):16,000
-Quality:Prime
-Help
-Location:FABRICA ALGECIRAS
-1,900.00 €/ton
+0.70 x 108.0 x coil mm
+Weight (Kg):714
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+1,000.00 €/ton
 Add to cart</v>
       </c>
     </row>
     <row r="649" xml:space="preserve">
       <c r="A649" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4510 430Ti-Coil, BA,
-0.70 x 108.0 x coil mm</v>
+0.70 x 120.9 x coil mm</v>
       </c>
       <c r="B649" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4510 430Ti-Coil, BA,
-0.70 x 108.0 x coil mm
-Weight (Kg):714
+0.70 x 120.9 x coil mm
+Weight (Kg):976
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -10778,12 +10778,12 @@
     <row r="650" xml:space="preserve">
       <c r="A650" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4510 430Ti-Coil, BA,
-0.70 x 120.9 x coil mm</v>
+0.70 x 325.0 x coil mm</v>
       </c>
       <c r="B650" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4510 430Ti-Coil, BA,
-0.70 x 120.9 x coil mm
-Weight (Kg):976
+0.70 x 325.0 x coil mm
+Weight (Kg):4,156
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -10794,16 +10794,16 @@
     <row r="651" xml:space="preserve">
       <c r="A651" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4510 430Ti-Coil, BA,
-0.70 x 325.0 x coil mm</v>
+0.70 x 900.0 x coil mm</v>
       </c>
       <c r="B651" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4510 430Ti-Coil, BA,
-0.70 x 325.0 x coil mm
-Weight (Kg):4,156
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-1,000.00 €/ton
+0.70 x 900.0 x coil mm
+Weight (Kg):2,800
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+1,125.00 €/ton
 Add to cart</v>
       </c>
     </row>
@@ -10815,7 +10815,7 @@
       <c r="B652" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4510 430Ti-Coil, BA,
 0.70 x 900.0 x coil mm
-Weight (Kg):2,800
+Weight (Kg):6,570
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -10826,12 +10826,12 @@
     <row r="653" xml:space="preserve">
       <c r="A653" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4510 430Ti-Coil, BA,
-0.70 x 900.0 x coil mm</v>
+0.70 x 905.0 x coil mm</v>
       </c>
       <c r="B653" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4510 430Ti-Coil, BA,
-0.70 x 900.0 x coil mm
-Weight (Kg):6,570
+0.70 x 905.0 x coil mm
+Weight (Kg):9,410
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -10842,12 +10842,12 @@
     <row r="654" xml:space="preserve">
       <c r="A654" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4510 430Ti-Coil, BA,
-0.70 x 905.0 x coil mm</v>
+0.70 x 932.0 x coil mm</v>
       </c>
       <c r="B654" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4510 430Ti-Coil, BA,
-0.70 x 905.0 x coil mm
-Weight (Kg):9,410
+0.70 x 932.0 x coil mm
+Weight (Kg):2,270
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -10858,25 +10858,9 @@
     <row r="655" xml:space="preserve">
       <c r="A655" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4510 430Ti-Coil, BA,
-0.70 x 932.0 x coil mm</v>
+0.70 x 940.0 x coil mm</v>
       </c>
       <c r="B655" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4510 430Ti-Coil, BA,
-0.70 x 932.0 x coil mm
-Weight (Kg):2,270
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-1,125.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="656" xml:space="preserve">
-      <c r="A656" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4510 430Ti-Coil, BA,
-0.70 x 940.0 x coil mm</v>
-      </c>
-      <c r="B656" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4510 430Ti-Coil, BA,
 0.70 x 940.0 x coil mm
 Weight (Kg):14,920
@@ -10887,28 +10871,28 @@
 Add to cart</v>
       </c>
     </row>
+    <row r="656" xml:space="preserve">
+      <c r="A656" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4510 430Ti-Untrimmed, Coil, BA,
+0.50 x 1275.0 x coil mm</v>
+      </c>
+      <c r="B656" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4510 430Ti-Untrimmed, Coil, BA,
+0.50 x 1275.0 x coil mm
+Weight (Kg):2,258
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+1,125.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
     <row r="657" xml:space="preserve">
       <c r="A657" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4510 430Ti-Untrimmed, Coil, BA,
-0.50 x 1275.0 x coil mm</v>
+0.70 x 928.0 x coil mm</v>
       </c>
       <c r="B657" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4510 430Ti-Untrimmed, Coil, BA,
-0.50 x 1275.0 x coil mm
-Weight (Kg):2,258
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-1,125.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="658" xml:space="preserve">
-      <c r="A658" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4510 430Ti-Untrimmed, Coil, BA,
-0.70 x 928.0 x coil mm</v>
-      </c>
-      <c r="B658" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4510 430Ti-Untrimmed, Coil, BA,
 0.70 x 928.0 x coil mm
 Weight (Kg):4,257
@@ -10919,12 +10903,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="659" xml:space="preserve">
-      <c r="A659" t="str" xml:space="preserve">
+    <row r="658" xml:space="preserve">
+      <c r="A658" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4509 441-Coil, 2B,
 1.20 x 275.9 x coil mm</v>
       </c>
-      <c r="B659" t="str" xml:space="preserve">
+      <c r="B658" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4509 441-Coil, 2B,
 1.20 x 275.9 x coil mm
 Weight (Kg):2,416
@@ -10935,20 +10919,36 @@
 Add to cart</v>
       </c>
     </row>
+    <row r="659" xml:space="preserve">
+      <c r="A659" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4509 441-Coil, 2D,
+1.20 x 196.0 x coil mm</v>
+      </c>
+      <c r="B659" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4509 441-Coil, 2D,
+1.20 x 196.0 x coil mm
+Weight (Kg):2,970
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+1,100.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
     <row r="660" xml:space="preserve">
       <c r="A660" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Untrimmed, Coil, BA,
-1.00 x 1285.0 x coil mm</v>
+        <v xml:space="preserve">Acerinox Europa, 1.4509 441-Coil, 2D,
+1.20 x 200.0 x coil mm</v>
       </c>
       <c r="B660" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Untrimmed, Coil, BA,
-1.00 x 1285.0 x coil mm
-Weight (Kg):5,491
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-1,125.00 €/ton
-Out of Stock</v>
+        <v xml:space="preserve">Acerinox Europa, 1.4509 441-Coil, 2D,
+1.20 x 200.0 x coil mm
+Weight (Kg):3,310
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+1,100.00 €/ton
+Add to cart</v>
       </c>
     </row>
     <row r="661" xml:space="preserve">
@@ -10970,12 +10970,12 @@
     <row r="662" xml:space="preserve">
       <c r="A662" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4509 441-Coil, 2D,
-1.20 x 196.0 x coil mm</v>
+1.20 x 214.9 x coil mm</v>
       </c>
       <c r="B662" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4509 441-Coil, 2D,
-1.20 x 196.0 x coil mm
-Weight (Kg):2,970
+1.20 x 214.9 x coil mm
+Weight (Kg):3,220
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -10986,12 +10986,12 @@
     <row r="663" xml:space="preserve">
       <c r="A663" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4509 441-Coil, 2D,
-1.20 x 200.0 x coil mm</v>
+1.20 x 223.9 x coil mm</v>
       </c>
       <c r="B663" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4509 441-Coil, 2D,
-1.20 x 200.0 x coil mm
-Weight (Kg):3,310
+1.20 x 223.9 x coil mm
+Weight (Kg):3,798
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -11002,44 +11002,44 @@
     <row r="664" xml:space="preserve">
       <c r="A664" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4509 441-Coil, 2D,
-1.20 x 214.9 x coil mm</v>
+1.20 x 224.0 x coil mm</v>
       </c>
       <c r="B664" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4509 441-Coil, 2D,
-1.20 x 214.9 x coil mm
-Weight (Kg):3,220
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-1,100.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="665" xml:space="preserve">
-      <c r="A665" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4509 441-Coil, 2D,
-1.20 x 223.9 x coil mm</v>
-      </c>
-      <c r="B665" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4509 441-Coil, 2D,
-1.20 x 223.9 x coil mm
-Weight (Kg):3,798
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-1,100.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="666" xml:space="preserve">
-      <c r="A666" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4509 441-Coil, 2D,
-1.20 x 224.0 x coil mm</v>
-      </c>
-      <c r="B666" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4509 441-Coil, 2D,
 1.20 x 224.0 x coil mm
 Weight (Kg):3,808
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+1,100.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="665" xml:space="preserve">
+      <c r="A665" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4509 441-Coil, BA,
+0.80 x 130.9 x coil mm</v>
+      </c>
+      <c r="B665" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4509 441-Coil, BA,
+0.80 x 130.9 x coil mm
+Weight (Kg):245
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+1,100.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="666" xml:space="preserve">
+      <c r="A666" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4509 441-Coil, BA,
+0.80 x 130.9 x coil mm</v>
+      </c>
+      <c r="B666" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4509 441-Coil, BA,
+0.80 x 130.9 x coil mm
+Weight (Kg):245
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -11055,7 +11055,7 @@
       <c r="B667" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4509 441-Coil, BA,
 0.80 x 130.9 x coil mm
-Weight (Kg):245
+Weight (Kg):213
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -11071,7 +11071,7 @@
       <c r="B668" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4509 441-Coil, BA,
 0.80 x 130.9 x coil mm
-Weight (Kg):245
+Weight (Kg):244
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -11081,29 +11081,29 @@
     </row>
     <row r="669" xml:space="preserve">
       <c r="A669" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4509 441-Coil, BA,
-0.80 x 130.9 x coil mm</v>
+        <v xml:space="preserve">Acerinox Europa, 1.4509 441-Coil, SB-G-400,
+1.00 x 1000.0 x coil mm</v>
       </c>
       <c r="B669" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4509 441-Coil, BA,
-0.80 x 130.9 x coil mm
-Weight (Kg):213
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-1,100.00 €/ton
+        <v xml:space="preserve">Acerinox Europa, 1.4509 441-Coil, SB-G-400,
+1.00 x 1000.0 x coil mm
+Weight (Kg):7,550
+Quality:Prime
+Help
+Location:FABRICA ALGECIRAS
+1,625.00 €/ton
 Add to cart</v>
       </c>
     </row>
     <row r="670" xml:space="preserve">
       <c r="A670" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4509 441-Coil, BA,
-0.80 x 130.9 x coil mm</v>
+        <v xml:space="preserve">Acerinox Europa, 1.4509 441-Coil, SB-G-400,
+1.00 x 255.0 x coil mm</v>
       </c>
       <c r="B670" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4509 441-Coil, BA,
-0.80 x 130.9 x coil mm
-Weight (Kg):244
+        <v xml:space="preserve">Acerinox Europa, 1.4509 441-Coil, SB-G-400,
+1.00 x 255.0 x coil mm
+Weight (Kg):2,182
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -11114,28 +11114,28 @@
     <row r="671" xml:space="preserve">
       <c r="A671" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4509 441-Coil, SB-G-400,
-1.00 x 1000.0 x coil mm</v>
+1.00 x 290.9 x coil mm</v>
       </c>
       <c r="B671" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4509 441-Coil, SB-G-400,
-1.00 x 1000.0 x coil mm
-Weight (Kg):7,550
-Quality:Prime
-Help
-Location:FABRICA ALGECIRAS
-1,625.00 €/ton
+1.00 x 290.9 x coil mm
+Weight (Kg):2,370
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+1,100.00 €/ton
 Add to cart</v>
       </c>
     </row>
     <row r="672" xml:space="preserve">
       <c r="A672" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4509 441-Coil, SB-G-400,
-1.00 x 255.0 x coil mm</v>
+1.20 x 110.9 x coil mm</v>
       </c>
       <c r="B672" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4509 441-Coil, SB-G-400,
-1.00 x 255.0 x coil mm
-Weight (Kg):2,182
+1.20 x 110.9 x coil mm
+Weight (Kg):856
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -11146,12 +11146,12 @@
     <row r="673" xml:space="preserve">
       <c r="A673" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4509 441-Coil, SB-G-400,
-1.00 x 290.9 x coil mm</v>
+1.20 x 130.9 x coil mm</v>
       </c>
       <c r="B673" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4509 441-Coil, SB-G-400,
-1.00 x 290.9 x coil mm
-Weight (Kg):2,370
+1.20 x 130.9 x coil mm
+Weight (Kg):564
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -11162,13 +11162,13 @@
     <row r="674" xml:space="preserve">
       <c r="A674" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4509 441-Coil, SB-G-400,
-1.20 x 110.9 x coil mm</v>
+1.20 x 130.9 x coil mm</v>
       </c>
       <c r="B674" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4509 441-Coil, SB-G-400,
-1.20 x 110.9 x coil mm
-Weight (Kg):856
-Quality:Prime-2
+1.20 x 130.9 x coil mm
+Weight (Kg):532
+Quality:Prime
 Help
 Location:FABRICA ALGECIRAS
 1,100.00 €/ton
@@ -11178,12 +11178,12 @@
     <row r="675" xml:space="preserve">
       <c r="A675" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4509 441-Coil, SB-G-400,
-1.20 x 130.9 x coil mm</v>
+1.50 x 130.9 x coil mm</v>
       </c>
       <c r="B675" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4509 441-Coil, SB-G-400,
-1.20 x 130.9 x coil mm
-Weight (Kg):564
+1.50 x 130.9 x coil mm
+Weight (Kg):640
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -11194,41 +11194,9 @@
     <row r="676" xml:space="preserve">
       <c r="A676" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4509 441-Coil, SB-G-400,
-1.20 x 130.9 x coil mm</v>
+1.50 x 360.0 x coil mm</v>
       </c>
       <c r="B676" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4509 441-Coil, SB-G-400,
-1.20 x 130.9 x coil mm
-Weight (Kg):532
-Quality:Prime
-Help
-Location:FABRICA ALGECIRAS
-1,100.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="677" xml:space="preserve">
-      <c r="A677" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4509 441-Coil, SB-G-400,
-1.50 x 130.9 x coil mm</v>
-      </c>
-      <c r="B677" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4509 441-Coil, SB-G-400,
-1.50 x 130.9 x coil mm
-Weight (Kg):640
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-1,100.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="678" xml:space="preserve">
-      <c r="A678" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4509 441-Coil, SB-G-400,
-1.50 x 360.0 x coil mm</v>
-      </c>
-      <c r="B678" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4509 441-Coil, SB-G-400,
 1.50 x 360.0 x coil mm
 Weight (Kg):1,488
@@ -11239,12 +11207,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="679" xml:space="preserve">
-      <c r="A679" t="str" xml:space="preserve">
+    <row r="677" xml:space="preserve">
+      <c r="A677" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4509 441-Untrimmed, Coil, 2B,
 1.50 x 1539.0 x coil mm</v>
       </c>
-      <c r="B679" t="str" xml:space="preserve">
+      <c r="B677" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4509 441-Untrimmed, Coil, 2B,
 1.50 x 1539.0 x coil mm
 Weight (Kg):14,230
@@ -11255,12 +11223,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="680" xml:space="preserve">
-      <c r="A680" t="str" xml:space="preserve">
+    <row r="678" xml:space="preserve">
+      <c r="A678" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4509 441-Untrimmed, Coil, BA,
 0.40 x 1075.0 x coil mm</v>
       </c>
-      <c r="B680" t="str" xml:space="preserve">
+      <c r="B678" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4509 441-Untrimmed, Coil, BA,
 0.40 x 1075.0 x coil mm
 Weight (Kg):9,750
@@ -11271,12 +11239,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="681" xml:space="preserve">
-      <c r="A681" t="str" xml:space="preserve">
+    <row r="679" xml:space="preserve">
+      <c r="A679" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4509 441-Untrimmed, Coil, Nb. 1,
 5.00 x 1045.0 x coil mm</v>
       </c>
-      <c r="B681" t="str" xml:space="preserve">
+      <c r="B679" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4509 441-Untrimmed, Coil, Nb. 1,
 5.00 x 1045.0 x coil mm
 Weight (Kg):7,880
@@ -11287,12 +11255,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="682" xml:space="preserve">
-      <c r="A682" t="str" xml:space="preserve">
+    <row r="680" xml:space="preserve">
+      <c r="A680" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 441-1.4509 Coil, 2B,
 1.20 x 240.9 x coil mm</v>
       </c>
-      <c r="B682" t="str" xml:space="preserve">
+      <c r="B680" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 441-1.4509 Coil, 2B,
 1.20 x 240.9 x coil mm
 Weight (Kg):3,882
@@ -11303,12 +11271,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="683" xml:space="preserve">
-      <c r="A683" t="str" xml:space="preserve">
+    <row r="681" xml:space="preserve">
+      <c r="A681" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 304-1.4301 Coil,
 0.70 x 270.9 x coil mm</v>
       </c>
-      <c r="B683" t="str" xml:space="preserve">
+      <c r="B681" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 304-1.4301 Coil,
 0.70 x 270.9 x coil mm
 Weight (Kg):2,704
@@ -11319,12 +11287,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="684" xml:space="preserve">
-      <c r="A684" t="str" xml:space="preserve">
+    <row r="682" xml:space="preserve">
+      <c r="A682" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 316L-1.4404 Coil,
 1.20 x 136.0 x coil mm</v>
       </c>
-      <c r="B684" t="str" xml:space="preserve">
+      <c r="B682" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 316L-1.4404 Coil,
 1.20 x 136.0 x coil mm
 Weight (Kg):2,300
@@ -11335,12 +11303,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="685" xml:space="preserve">
-      <c r="A685" t="str" xml:space="preserve">
+    <row r="683" xml:space="preserve">
+      <c r="A683" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 304L/304-4301/4307 Coil, 2B,
 6.00 x 245.0 x coil mm</v>
       </c>
-      <c r="B685" t="str" xml:space="preserve">
+      <c r="B683" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 304L/304-4301/4307 Coil, 2B,
 6.00 x 245.0 x coil mm
 Weight (Kg):2,394
@@ -11351,12 +11319,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="686" xml:space="preserve">
-      <c r="A686" t="str" xml:space="preserve">
+    <row r="684" xml:space="preserve">
+      <c r="A684" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, 2B,
 0.70 x 197.5 x coil mm</v>
       </c>
-      <c r="B686" t="str" xml:space="preserve">
+      <c r="B684" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, 2B,
 0.70 x 197.5 x coil mm
 Weight (Kg):2,442
@@ -11367,12 +11335,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="687" xml:space="preserve">
-      <c r="A687" t="str" xml:space="preserve">
+    <row r="685" xml:space="preserve">
+      <c r="A685" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 441-1.4509 Coil, 2B,
 2.00 x 120.9 x coil mm</v>
       </c>
-      <c r="B687" t="str" xml:space="preserve">
+      <c r="B685" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 441-1.4509 Coil, 2B,
 2.00 x 120.9 x coil mm
 Weight (Kg):1,956
@@ -11383,12 +11351,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="688" xml:space="preserve">
-      <c r="A688" t="str" xml:space="preserve">
+    <row r="686" xml:space="preserve">
+      <c r="A686" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 304-1.4301 Coil, 2B,
 1.20 x 119.9 x coil mm</v>
       </c>
-      <c r="B688" t="str" xml:space="preserve">
+      <c r="B686" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 304-1.4301 Coil, 2B,
 1.20 x 119.9 x coil mm
 Weight (Kg):1,500
@@ -11399,12 +11367,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="689" xml:space="preserve">
-      <c r="A689" t="str" xml:space="preserve">
+    <row r="687" xml:space="preserve">
+      <c r="A687" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 304-1.4301 Coil, 2B,
 1.20 x 119.9 x coil mm</v>
       </c>
-      <c r="B689" t="str" xml:space="preserve">
+      <c r="B687" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 304-1.4301 Coil, 2B,
 1.20 x 119.9 x coil mm
 Weight (Kg):1,400
@@ -11415,15 +11383,47 @@
 Add to cart</v>
       </c>
     </row>
+    <row r="688" xml:space="preserve">
+      <c r="A688" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, BA,
+0.70 x 125.0 x coil mm</v>
+      </c>
+      <c r="B688" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, BA,
+0.70 x 125.0 x coil mm
+Weight (Kg):1,764
+Quality:Prime
+Help
+Location:FABRICA ALGECIRAS
+1,000.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="689" xml:space="preserve">
+      <c r="A689" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, BA,
+0.70 x 104.9 x coil mm</v>
+      </c>
+      <c r="B689" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, BA,
+0.70 x 104.9 x coil mm
+Weight (Kg):1,240
+Quality:Prime
+Help
+Location:FABRICA ALGECIRAS
+1,000.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
     <row r="690" xml:space="preserve">
       <c r="A690" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, BA,
-0.70 x 125.0 x coil mm</v>
+0.70 x 118.9 x coil mm</v>
       </c>
       <c r="B690" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, BA,
-0.70 x 125.0 x coil mm
-Weight (Kg):1,764
+0.70 x 118.9 x coil mm
+Weight (Kg):1,802
 Quality:Prime
 Help
 Location:FABRICA ALGECIRAS
@@ -11434,12 +11434,12 @@
     <row r="691" xml:space="preserve">
       <c r="A691" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, BA,
-0.70 x 104.9 x coil mm</v>
+0.70 x 115.9 x coil mm</v>
       </c>
       <c r="B691" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, BA,
-0.70 x 104.9 x coil mm
-Weight (Kg):1,240
+0.70 x 115.9 x coil mm
+Weight (Kg):1,368
 Quality:Prime
 Help
 Location:FABRICA ALGECIRAS
@@ -11450,13 +11450,13 @@
     <row r="692" xml:space="preserve">
       <c r="A692" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, BA,
-0.70 x 118.9 x coil mm</v>
+0.70 x 119.0 x coil mm</v>
       </c>
       <c r="B692" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, BA,
-0.70 x 118.9 x coil mm
-Weight (Kg):1,802
-Quality:Prime
+0.70 x 119.0 x coil mm
+Weight (Kg):1,622
+Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
 1,000.00 €/ton
@@ -11465,58 +11465,26 @@
     </row>
     <row r="693" xml:space="preserve">
       <c r="A693" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, BA,
-0.70 x 115.9 x coil mm</v>
+        <v xml:space="preserve">Acerinox Europa, 304L/304-4301/4307 Coil, 2B,
+1.40 x 110.9 x coil mm</v>
       </c>
       <c r="B693" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, BA,
-0.70 x 115.9 x coil mm
-Weight (Kg):1,368
-Quality:Prime
-Help
-Location:FABRICA ALGECIRAS
-1,000.00 €/ton
+        <v xml:space="preserve">Acerinox Europa, 304L/304-4301/4307 Coil, 2B,
+1.40 x 110.9 x coil mm
+Weight (Kg):1,240
+Quality:Prime
+Help
+Location:FABRICA ALGECIRAS
+2,075.00 €/ton
 Add to cart</v>
       </c>
     </row>
     <row r="694" xml:space="preserve">
       <c r="A694" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, BA,
-0.70 x 119.0 x coil mm</v>
+0.70 x 104.0 x coil mm</v>
       </c>
       <c r="B694" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, BA,
-0.70 x 119.0 x coil mm
-Weight (Kg):1,622
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-1,000.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="695" xml:space="preserve">
-      <c r="A695" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 304L/304-4301/4307 Coil, 2B,
-1.40 x 110.9 x coil mm</v>
-      </c>
-      <c r="B695" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 304L/304-4301/4307 Coil, 2B,
-1.40 x 110.9 x coil mm
-Weight (Kg):1,240
-Quality:Prime
-Help
-Location:FABRICA ALGECIRAS
-2,075.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="696" xml:space="preserve">
-      <c r="A696" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, BA,
-0.70 x 104.0 x coil mm</v>
-      </c>
-      <c r="B696" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, BA,
 0.70 x 104.0 x coil mm
 Weight (Kg):1,622
@@ -11527,12 +11495,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="697" xml:space="preserve">
-      <c r="A697" t="str" xml:space="preserve">
+    <row r="695" xml:space="preserve">
+      <c r="A695" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, BA,
 0.70 x 104.0 x coil mm</v>
       </c>
-      <c r="B697" t="str" xml:space="preserve">
+      <c r="B695" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, BA,
 0.70 x 104.0 x coil mm
 Weight (Kg):1,688
@@ -11543,12 +11511,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="698" xml:space="preserve">
-      <c r="A698" t="str" xml:space="preserve">
+    <row r="696" xml:space="preserve">
+      <c r="A696" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 304L/304-4301/4307 Coil, 2B,
 1.40 x 110.9 x coil mm</v>
       </c>
-      <c r="B698" t="str" xml:space="preserve">
+      <c r="B696" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 304L/304-4301/4307 Coil, 2B,
 1.40 x 110.9 x coil mm
 Weight (Kg):1,162
@@ -11559,12 +11527,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="699" xml:space="preserve">
-      <c r="A699" t="str" xml:space="preserve">
+    <row r="697" xml:space="preserve">
+      <c r="A697" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 430Ti-1.4510 Coil, BA,
 0.70 x 165.9 x coil mm</v>
       </c>
-      <c r="B699" t="str" xml:space="preserve">
+      <c r="B697" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 430Ti-1.4510 Coil, BA,
 0.70 x 165.9 x coil mm
 Weight (Kg):2,692
@@ -11575,12 +11543,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="700" xml:space="preserve">
-      <c r="A700" t="str" xml:space="preserve">
+    <row r="698" xml:space="preserve">
+      <c r="A698" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 430Ti-1.4510 Coil, BA,
 0.70 x 165.9 x coil mm</v>
       </c>
-      <c r="B700" t="str" xml:space="preserve">
+      <c r="B698" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 430Ti-1.4510 Coil, BA,
 0.70 x 165.9 x coil mm
 Weight (Kg):2,756
@@ -11591,15 +11559,47 @@
 Add to cart</v>
       </c>
     </row>
+    <row r="699" xml:space="preserve">
+      <c r="A699" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, BA,
+0.70 x 140.9 x coil mm</v>
+      </c>
+      <c r="B699" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, BA,
+0.70 x 140.9 x coil mm
+Weight (Kg):1,676
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+1,000.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="700" xml:space="preserve">
+      <c r="A700" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, BA,
+0.70 x 100.9 x coil mm</v>
+      </c>
+      <c r="B700" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, BA,
+0.70 x 100.9 x coil mm
+Weight (Kg):1,340
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+1,000.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
     <row r="701" xml:space="preserve">
       <c r="A701" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, BA,
-0.70 x 140.9 x coil mm</v>
+0.70 x 125.0 x coil mm</v>
       </c>
       <c r="B701" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, BA,
-0.70 x 140.9 x coil mm
-Weight (Kg):1,676
+0.70 x 125.0 x coil mm
+Weight (Kg):1,550
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -11610,12 +11610,12 @@
     <row r="702" xml:space="preserve">
       <c r="A702" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, BA,
-0.70 x 100.9 x coil mm</v>
+0.70 x 125.0 x coil mm</v>
       </c>
       <c r="B702" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, BA,
-0.70 x 100.9 x coil mm
-Weight (Kg):1,340
+0.70 x 125.0 x coil mm
+Weight (Kg):1,414
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -11626,41 +11626,9 @@
     <row r="703" xml:space="preserve">
       <c r="A703" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, BA,
-0.70 x 125.0 x coil mm</v>
+0.70 x 100.9 x coil mm</v>
       </c>
       <c r="B703" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, BA,
-0.70 x 125.0 x coil mm
-Weight (Kg):1,550
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-1,000.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="704" xml:space="preserve">
-      <c r="A704" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, BA,
-0.70 x 125.0 x coil mm</v>
-      </c>
-      <c r="B704" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, BA,
-0.70 x 125.0 x coil mm
-Weight (Kg):1,414
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-1,000.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="705" xml:space="preserve">
-      <c r="A705" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, BA,
-0.70 x 100.9 x coil mm</v>
-      </c>
-      <c r="B705" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, BA,
 0.70 x 100.9 x coil mm
 Weight (Kg):2,188
@@ -11671,12 +11639,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="706" xml:space="preserve">
-      <c r="A706" t="str" xml:space="preserve">
+    <row r="704" xml:space="preserve">
+      <c r="A704" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 304L/304-4301/4307 Coil, Nb. 1,
 4.70 x 110.0 x coil mm</v>
       </c>
-      <c r="B706" t="str" xml:space="preserve">
+      <c r="B704" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 304L/304-4301/4307 Coil, Nb. 1,
 4.70 x 110.0 x coil mm
 Weight (Kg):1,796
@@ -11687,12 +11655,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="707" xml:space="preserve">
-      <c r="A707" t="str" xml:space="preserve">
+    <row r="705" xml:space="preserve">
+      <c r="A705" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 304L/304-4301/4307 Coil, Nb. 1,
 4.70 x 110.0 x coil mm</v>
       </c>
-      <c r="B707" t="str" xml:space="preserve">
+      <c r="B705" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 304L/304-4301/4307 Coil, Nb. 1,
 4.70 x 110.0 x coil mm
 Weight (Kg):2,038
@@ -11703,12 +11671,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="708" xml:space="preserve">
-      <c r="A708" t="str" xml:space="preserve">
+    <row r="706" xml:space="preserve">
+      <c r="A706" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, BA,
 0.70 x 165.9 x coil mm</v>
       </c>
-      <c r="B708" t="str" xml:space="preserve">
+      <c r="B706" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, BA,
 0.70 x 165.9 x coil mm
 Weight (Kg):2,620
@@ -11719,12 +11687,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="709" xml:space="preserve">
-      <c r="A709" t="str" xml:space="preserve">
+    <row r="707" xml:space="preserve">
+      <c r="A707" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 304-1.4301 Coil,
 0.70 x 260.9 x coil mm</v>
       </c>
-      <c r="B709" t="str" xml:space="preserve">
+      <c r="B707" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 304-1.4301 Coil,
 0.70 x 260.9 x coil mm
 Weight (Kg):1,330
@@ -11735,12 +11703,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="710" xml:space="preserve">
-      <c r="A710" t="str" xml:space="preserve">
+    <row r="708" xml:space="preserve">
+      <c r="A708" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 304-1.4301 Coil,
 0.70 x 260.9 x coil mm</v>
       </c>
-      <c r="B710" t="str" xml:space="preserve">
+      <c r="B708" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 304-1.4301 Coil,
 0.70 x 260.9 x coil mm
 Weight (Kg):1,264
@@ -11751,12 +11719,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="711" xml:space="preserve">
-      <c r="A711" t="str" xml:space="preserve">
+    <row r="709" xml:space="preserve">
+      <c r="A709" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, BA,
 0.70 x 110.0 x coil mm</v>
       </c>
-      <c r="B711" t="str" xml:space="preserve">
+      <c r="B709" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, BA,
 0.70 x 110.0 x coil mm
 Weight (Kg):1,250
@@ -11767,12 +11735,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="712" xml:space="preserve">
-      <c r="A712" t="str" xml:space="preserve">
+    <row r="710" xml:space="preserve">
+      <c r="A710" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, BA,
 0.70 x 122.9 x coil mm</v>
       </c>
-      <c r="B712" t="str" xml:space="preserve">
+      <c r="B710" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, BA,
 0.70 x 122.9 x coil mm
 Weight (Kg):1,460
@@ -11783,44 +11751,44 @@
 Add to cart</v>
       </c>
     </row>
+    <row r="711" xml:space="preserve">
+      <c r="A711" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 304L/304-4301/4307 Coil, 2B,
+1.40 x 110.0 x coil mm</v>
+      </c>
+      <c r="B711" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 304L/304-4301/4307 Coil, 2B,
+1.40 x 110.0 x coil mm
+Weight (Kg):1,554
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,075.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="712" xml:space="preserve">
+      <c r="A712" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 304L/304-4301/4307 Coil, 2B,
+1.40 x 110.0 x coil mm</v>
+      </c>
+      <c r="B712" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 304L/304-4301/4307 Coil, 2B,
+1.40 x 110.0 x coil mm
+Weight (Kg):1,586
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,075.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
     <row r="713" xml:space="preserve">
       <c r="A713" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 304L/304-4301/4307 Coil, 2B,
-1.40 x 110.0 x coil mm</v>
+1.40 x 104.0 x coil mm</v>
       </c>
       <c r="B713" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 304L/304-4301/4307 Coil, 2B,
-1.40 x 110.0 x coil mm
-Weight (Kg):1,554
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-2,075.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="714" xml:space="preserve">
-      <c r="A714" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 304L/304-4301/4307 Coil, 2B,
-1.40 x 110.0 x coil mm</v>
-      </c>
-      <c r="B714" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 304L/304-4301/4307 Coil, 2B,
-1.40 x 110.0 x coil mm
-Weight (Kg):1,586
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-2,075.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="715" xml:space="preserve">
-      <c r="A715" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 304L/304-4301/4307 Coil, 2B,
-1.40 x 104.0 x coil mm</v>
-      </c>
-      <c r="B715" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 304L/304-4301/4307 Coil, 2B,
 1.40 x 104.0 x coil mm
 Weight (Kg):1,030
@@ -11831,12 +11799,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="716" xml:space="preserve">
-      <c r="A716" t="str" xml:space="preserve">
+    <row r="714" xml:space="preserve">
+      <c r="A714" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 304DDQ-1.4301 Coil, BA,
 0.70 x 181.9 x coil mm</v>
       </c>
-      <c r="B716" t="str" xml:space="preserve">
+      <c r="B714" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 304DDQ-1.4301 Coil, BA,
 0.70 x 181.9 x coil mm
 Weight (Kg):2,912
@@ -11847,12 +11815,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="717" xml:space="preserve">
-      <c r="A717" t="str" xml:space="preserve">
+    <row r="715" xml:space="preserve">
+      <c r="A715" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 304-1.4301 Coil,
 1.50 x 136.0 x coil mm</v>
       </c>
-      <c r="B717" t="str" xml:space="preserve">
+      <c r="B715" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 304-1.4301 Coil,
 1.50 x 136.0 x coil mm
 Weight (Kg):3,450
@@ -11863,12 +11831,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="718" xml:space="preserve">
-      <c r="A718" t="str" xml:space="preserve">
+    <row r="716" xml:space="preserve">
+      <c r="A716" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 304-1.4301 Coil, BA,
 0.40 x 200.0 x coil mm</v>
       </c>
-      <c r="B718" t="str" xml:space="preserve">
+      <c r="B716" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 304-1.4301 Coil, BA,
 0.40 x 200.0 x coil mm
 Weight (Kg):1,964
@@ -11879,12 +11847,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="719" xml:space="preserve">
-      <c r="A719" t="str" xml:space="preserve">
+    <row r="717" xml:space="preserve">
+      <c r="A717" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 304-1.4301 Coil, BA, ET-60
 0.60 x 120.0 x coil mm</v>
       </c>
-      <c r="B719" t="str" xml:space="preserve">
+      <c r="B717" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 304-1.4301 Coil, BA, ET-60
 0.60 x 120.0 x coil mm
 Weight (Kg):1,302
@@ -11895,12 +11863,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="720" xml:space="preserve">
-      <c r="A720" t="str" xml:space="preserve">
+    <row r="718" xml:space="preserve">
+      <c r="A718" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, ET-100
 0.70 x 124.9 x coil mm</v>
       </c>
-      <c r="B720" t="str" xml:space="preserve">
+      <c r="B718" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, ET-100
 0.70 x 124.9 x coil mm
 Weight (Kg):2,106
@@ -11911,12 +11879,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="721" xml:space="preserve">
-      <c r="A721" t="str" xml:space="preserve">
+    <row r="719" xml:space="preserve">
+      <c r="A719" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, ET-100
 0.70 x 124.9 x coil mm</v>
       </c>
-      <c r="B721" t="str" xml:space="preserve">
+      <c r="B719" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, ET-100
 0.70 x 124.9 x coil mm
 Weight (Kg):1,972
@@ -11927,12 +11895,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="722" xml:space="preserve">
-      <c r="A722" t="str" xml:space="preserve">
+    <row r="720" xml:space="preserve">
+      <c r="A720" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 430Ti-1.4510 Coil, 2B,
 0.80 x 155.9 x coil mm</v>
       </c>
-      <c r="B722" t="str" xml:space="preserve">
+      <c r="B720" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 430Ti-1.4510 Coil, 2B,
 0.80 x 155.9 x coil mm
 Weight (Kg):1,586
@@ -11943,12 +11911,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="723" xml:space="preserve">
-      <c r="A723" t="str" xml:space="preserve">
+    <row r="721" xml:space="preserve">
+      <c r="A721" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 304-1.4301 Coil, BA,
 0.40 x 270.0 x coil mm</v>
       </c>
-      <c r="B723" t="str" xml:space="preserve">
+      <c r="B721" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 304-1.4301 Coil, BA,
 0.40 x 270.0 x coil mm
 Weight (Kg):2,572
@@ -11959,12 +11927,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="724" xml:space="preserve">
-      <c r="A724" t="str" xml:space="preserve">
+    <row r="722" xml:space="preserve">
+      <c r="A722" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, BA,
 0.60 x 130.0 x coil mm</v>
       </c>
-      <c r="B724" t="str" xml:space="preserve">
+      <c r="B722" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, BA,
 0.60 x 130.0 x coil mm
 Weight (Kg):1,490
@@ -11975,12 +11943,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="725" xml:space="preserve">
-      <c r="A725" t="str" xml:space="preserve">
+    <row r="723" xml:space="preserve">
+      <c r="A723" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 441-1.4509 Coil, BA,
 0.40 x 110.0 x coil mm</v>
       </c>
-      <c r="B725" t="str" xml:space="preserve">
+      <c r="B723" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 441-1.4509 Coil, BA,
 0.40 x 110.0 x coil mm
 Weight (Kg):1,870
@@ -11991,12 +11959,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="726" xml:space="preserve">
-      <c r="A726" t="str" xml:space="preserve">
+    <row r="724" xml:space="preserve">
+      <c r="A724" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 441-1.4509 Coil, BA,
 0.40 x 110.0 x coil mm</v>
       </c>
-      <c r="B726" t="str" xml:space="preserve">
+      <c r="B724" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 441-1.4509 Coil, BA,
 0.40 x 110.0 x coil mm
 Weight (Kg):1,882
@@ -12007,12 +11975,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="727" xml:space="preserve">
-      <c r="A727" t="str" xml:space="preserve">
+    <row r="725" xml:space="preserve">
+      <c r="A725" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 301-1.4310 Coil, BA,
 0.40 x 110.0 x coil mm</v>
       </c>
-      <c r="B727" t="str" xml:space="preserve">
+      <c r="B725" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 301-1.4310 Coil, BA,
 0.40 x 110.0 x coil mm
 Weight (Kg):1,934
@@ -12023,12 +11991,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="728" xml:space="preserve">
-      <c r="A728" t="str" xml:space="preserve">
+    <row r="726" xml:space="preserve">
+      <c r="A726" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 301-1.4310 Coil, BA,
 0.40 x 110.0 x coil mm</v>
       </c>
-      <c r="B728" t="str" xml:space="preserve">
+      <c r="B726" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 301-1.4310 Coil, BA,
 0.40 x 110.0 x coil mm
 Weight (Kg):1,860
@@ -12039,12 +12007,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="729" xml:space="preserve">
-      <c r="A729" t="str" xml:space="preserve">
+    <row r="727" xml:space="preserve">
+      <c r="A727" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 321-1.4541 Coil, 2B,
 1.90 x 104.5 x coil mm</v>
       </c>
-      <c r="B729" t="str" xml:space="preserve">
+      <c r="B727" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 321-1.4541 Coil, 2B,
 1.90 x 104.5 x coil mm
 Weight (Kg):2,304
@@ -12055,12 +12023,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="730" xml:space="preserve">
-      <c r="A730" t="str" xml:space="preserve">
+    <row r="728" xml:space="preserve">
+      <c r="A728" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 304L/304-4301/4307 Coil, Polished N4-G-180,
 1.20 x 255.9 x coil mm</v>
       </c>
-      <c r="B730" t="str" xml:space="preserve">
+      <c r="B728" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 304L/304-4301/4307 Coil, Polished N4-G-180,
 1.20 x 255.9 x coil mm
 Weight (Kg):4,298
@@ -12071,12 +12039,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="731" xml:space="preserve">
-      <c r="A731" t="str" xml:space="preserve">
+    <row r="729" xml:space="preserve">
+      <c r="A729" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 301-1.4310 Coil, BA,
 0.40 x 110.0 x coil mm</v>
       </c>
-      <c r="B731" t="str" xml:space="preserve">
+      <c r="B729" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 301-1.4310 Coil, BA,
 0.40 x 110.0 x coil mm
 Weight (Kg):1,698
@@ -12087,15 +12055,47 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="732" xml:space="preserve">
-      <c r="A732" t="str" xml:space="preserve">
+    <row r="730" xml:space="preserve">
+      <c r="A730" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, BA,
 0.40 x 130.0 x coil mm</v>
       </c>
-      <c r="B732" t="str" xml:space="preserve">
+      <c r="B730" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, BA,
 0.40 x 130.0 x coil mm
 Weight (Kg):1,916
+Quality:Prime
+Help
+Location:FABRICA ALGECIRAS
+1,000.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="731" xml:space="preserve">
+      <c r="A731" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 430Ti-1.4510 Coil, BA,
+0.50 x 140.0 x coil mm</v>
+      </c>
+      <c r="B731" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 430Ti-1.4510 Coil, BA,
+0.50 x 140.0 x coil mm
+Weight (Kg):3,054
+Quality:Prime
+Help
+Location:FABRICA ALGECIRAS
+1,000.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="732" xml:space="preserve">
+      <c r="A732" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 430Ti-1.4510 Coil, BA,
+0.50 x 140.0 x coil mm</v>
+      </c>
+      <c r="B732" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 430Ti-1.4510 Coil, BA,
+0.50 x 140.0 x coil mm
+Weight (Kg):3,060
 Quality:Prime
 Help
 Location:FABRICA ALGECIRAS
@@ -12111,7 +12111,7 @@
       <c r="B733" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 430Ti-1.4510 Coil, BA,
 0.50 x 140.0 x coil mm
-Weight (Kg):3,054
+Weight (Kg):2,220
 Quality:Prime
 Help
 Location:FABRICA ALGECIRAS
@@ -12127,7 +12127,7 @@
       <c r="B734" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 430Ti-1.4510 Coil, BA,
 0.50 x 140.0 x coil mm
-Weight (Kg):3,060
+Weight (Kg):2,224
 Quality:Prime
 Help
 Location:FABRICA ALGECIRAS
@@ -12137,42 +12137,10 @@
     </row>
     <row r="735" xml:space="preserve">
       <c r="A735" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 430Ti-1.4510 Coil, BA,
-0.50 x 140.0 x coil mm</v>
-      </c>
-      <c r="B735" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 430Ti-1.4510 Coil, BA,
-0.50 x 140.0 x coil mm
-Weight (Kg):2,220
-Quality:Prime
-Help
-Location:FABRICA ALGECIRAS
-1,000.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="736" xml:space="preserve">
-      <c r="A736" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 430Ti-1.4510 Coil, BA,
-0.50 x 140.0 x coil mm</v>
-      </c>
-      <c r="B736" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 430Ti-1.4510 Coil, BA,
-0.50 x 140.0 x coil mm
-Weight (Kg):2,224
-Quality:Prime
-Help
-Location:FABRICA ALGECIRAS
-1,000.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="737" xml:space="preserve">
-      <c r="A737" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 304L/304-4301/4307 Coil, 2B,
 1.40 x 100.9 x coil mm</v>
       </c>
-      <c r="B737" t="str" xml:space="preserve">
+      <c r="B735" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 304L/304-4301/4307 Coil, 2B,
 1.40 x 100.9 x coil mm
 Weight (Kg):1,612
@@ -12183,12 +12151,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="738" xml:space="preserve">
-      <c r="A738" t="str" xml:space="preserve">
+    <row r="736" xml:space="preserve">
+      <c r="A736" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 304L/304-4301/4307 Coil, 2B,
 1.40 x 100.9 x coil mm</v>
       </c>
-      <c r="B738" t="str" xml:space="preserve">
+      <c r="B736" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 304L/304-4301/4307 Coil, 2B,
 1.40 x 100.9 x coil mm
 Weight (Kg):1,600
@@ -12199,12 +12167,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="739" xml:space="preserve">
-      <c r="A739" t="str" xml:space="preserve">
+    <row r="737" xml:space="preserve">
+      <c r="A737" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 304-1.4301 Coil, Emboss Chequered,
 0.70 x 174.9 x coil mm</v>
       </c>
-      <c r="B739" t="str" xml:space="preserve">
+      <c r="B737" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 304-1.4301 Coil, Emboss Chequered,
 0.70 x 174.9 x coil mm
 Weight (Kg):1,494
@@ -12215,12 +12183,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="740" xml:space="preserve">
-      <c r="A740" t="str" xml:space="preserve">
+    <row r="738" xml:space="preserve">
+      <c r="A738" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 304-1.4301 Coil, Emboss Chequered,
 0.70 x 174.9 x coil mm</v>
       </c>
-      <c r="B740" t="str" xml:space="preserve">
+      <c r="B738" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 304-1.4301 Coil, Emboss Chequered,
 0.70 x 174.9 x coil mm
 Weight (Kg):1,472
@@ -12231,12 +12199,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="741" xml:space="preserve">
-      <c r="A741" t="str" xml:space="preserve">
+    <row r="739" xml:space="preserve">
+      <c r="A739" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, SB-G-240,
 0.50 x 290.9 x coil mm</v>
       </c>
-      <c r="B741" t="str" xml:space="preserve">
+      <c r="B739" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, SB-G-240,
 0.50 x 290.9 x coil mm
 Weight (Kg):4,408
@@ -12247,44 +12215,44 @@
 Add to cart</v>
       </c>
     </row>
+    <row r="740" xml:space="preserve">
+      <c r="A740" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 304-1.4301 Coil, BA,
+0.60 x 110.0 x coil mm</v>
+      </c>
+      <c r="B740" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 304-1.4301 Coil, BA,
+0.60 x 110.0 x coil mm
+Weight (Kg):1,032
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,075.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="741" xml:space="preserve">
+      <c r="A741" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 304-1.4301 Coil, BA,
+0.40 x 270.0 x coil mm</v>
+      </c>
+      <c r="B741" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 304-1.4301 Coil, BA,
+0.40 x 270.0 x coil mm
+Weight (Kg):3,124
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,075.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
     <row r="742" xml:space="preserve">
       <c r="A742" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 304-1.4301 Coil, BA,
-0.60 x 110.0 x coil mm</v>
+0.60 x 135.0 x coil mm</v>
       </c>
       <c r="B742" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 304-1.4301 Coil, BA,
-0.60 x 110.0 x coil mm
-Weight (Kg):1,032
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-2,075.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="743" xml:space="preserve">
-      <c r="A743" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 304-1.4301 Coil, BA,
-0.40 x 270.0 x coil mm</v>
-      </c>
-      <c r="B743" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 304-1.4301 Coil, BA,
-0.40 x 270.0 x coil mm
-Weight (Kg):3,124
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-2,075.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="744" xml:space="preserve">
-      <c r="A744" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 304-1.4301 Coil, BA,
-0.60 x 135.0 x coil mm</v>
-      </c>
-      <c r="B744" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 304-1.4301 Coil, BA,
 0.60 x 135.0 x coil mm
 Weight (Kg):2,078
@@ -12295,12 +12263,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="745" xml:space="preserve">
-      <c r="A745" t="str" xml:space="preserve">
+    <row r="743" xml:space="preserve">
+      <c r="A743" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 441-1.4509 Coil, 2B,
 2.00 x 245.9 x coil mm</v>
       </c>
-      <c r="B745" t="str" xml:space="preserve">
+      <c r="B743" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 441-1.4509 Coil, 2B,
 2.00 x 245.9 x coil mm
 Weight (Kg):3,492
@@ -12311,12 +12279,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="746" xml:space="preserve">
-      <c r="A746" t="str" xml:space="preserve">
+    <row r="744" xml:space="preserve">
+      <c r="A744" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 304-1.4301 Coil, 2B,
 0.60 x 101.9 x coil mm</v>
       </c>
-      <c r="B746" t="str" xml:space="preserve">
+      <c r="B744" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 304-1.4301 Coil, 2B,
 0.60 x 101.9 x coil mm
 Weight (Kg):1,350
@@ -12327,12 +12295,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="747" xml:space="preserve">
-      <c r="A747" t="str" xml:space="preserve">
+    <row r="745" xml:space="preserve">
+      <c r="A745" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 430Ti-1.4510 Coil, BA,
 0.70 x 118.9 x coil mm</v>
       </c>
-      <c r="B747" t="str" xml:space="preserve">
+      <c r="B745" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 430Ti-1.4510 Coil, BA,
 0.70 x 118.9 x coil mm
 Weight (Kg):1,768
@@ -12343,12 +12311,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="748" xml:space="preserve">
-      <c r="A748" t="str" xml:space="preserve">
+    <row r="746" xml:space="preserve">
+      <c r="A746" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 304L/304-4301/4307 Coil, 2B,
 1.00 x 135.9 x coil mm</v>
       </c>
-      <c r="B748" t="str" xml:space="preserve">
+      <c r="B746" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 304L/304-4301/4307 Coil, 2B,
 1.00 x 135.9 x coil mm
 Weight (Kg):1,056
@@ -12359,12 +12327,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="749" xml:space="preserve">
-      <c r="A749" t="str" xml:space="preserve">
+    <row r="747" xml:space="preserve">
+      <c r="A747" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 304L/304-4301/4307 Coil, 2B,
 2.00 x 250.0 x coil mm</v>
       </c>
-      <c r="B749" t="str" xml:space="preserve">
+      <c r="B747" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 304L/304-4301/4307 Coil, 2B,
 2.00 x 250.0 x coil mm
 Weight (Kg):2,388
@@ -12375,12 +12343,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="750" xml:space="preserve">
-      <c r="A750" t="str" xml:space="preserve">
+    <row r="748" xml:space="preserve">
+      <c r="A748" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, BA,
 0.70 x 125.9 x coil mm</v>
       </c>
-      <c r="B750" t="str" xml:space="preserve">
+      <c r="B748" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, BA,
 0.70 x 125.9 x coil mm
 Weight (Kg):1,788
@@ -12391,12 +12359,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="751" xml:space="preserve">
-      <c r="A751" t="str" xml:space="preserve">
+    <row r="749" xml:space="preserve">
+      <c r="A749" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, BA,
 0.70 x 125.9 x coil mm</v>
       </c>
-      <c r="B751" t="str" xml:space="preserve">
+      <c r="B749" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, BA,
 0.70 x 125.9 x coil mm
 Weight (Kg):1,794
@@ -12407,12 +12375,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="752" xml:space="preserve">
-      <c r="A752" t="str" xml:space="preserve">
+    <row r="750" xml:space="preserve">
+      <c r="A750" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 430Ti-1.4510 Coil, BA,
 0.70 x 112.0 x coil mm</v>
       </c>
-      <c r="B752" t="str" xml:space="preserve">
+      <c r="B750" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 430Ti-1.4510 Coil, BA,
 0.70 x 112.0 x coil mm
 Weight (Kg):1,550
@@ -12423,12 +12391,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="753" xml:space="preserve">
-      <c r="A753" t="str" xml:space="preserve">
+    <row r="751" xml:space="preserve">
+      <c r="A751" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 304-1.4301 Coil, BA,
 0.60 x 320.0 x coil mm</v>
       </c>
-      <c r="B753" t="str" xml:space="preserve">
+      <c r="B751" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 304-1.4301 Coil, BA,
 0.60 x 320.0 x coil mm
 Weight (Kg):2,534
@@ -12439,12 +12407,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="754" xml:space="preserve">
-      <c r="A754" t="str" xml:space="preserve">
+    <row r="752" xml:space="preserve">
+      <c r="A752" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 304-1.4301 Coil, BA,
 0.60 x 320.0 x coil mm</v>
       </c>
-      <c r="B754" t="str" xml:space="preserve">
+      <c r="B752" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 304-1.4301 Coil, BA,
 0.60 x 320.0 x coil mm
 Weight (Kg):3,148
@@ -12455,12 +12423,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="755" xml:space="preserve">
-      <c r="A755" t="str" xml:space="preserve">
+    <row r="753" xml:space="preserve">
+      <c r="A753" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 304-1.4301 Coil, 2B,
 0.80 x 199.9 x coil mm</v>
       </c>
-      <c r="B755" t="str" xml:space="preserve">
+      <c r="B753" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 304-1.4301 Coil, 2B,
 0.80 x 199.9 x coil mm
 Weight (Kg):2,602
@@ -12471,12 +12439,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="756" xml:space="preserve">
-      <c r="A756" t="str" xml:space="preserve">
+    <row r="754" xml:space="preserve">
+      <c r="A754" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 304L/304-4301/4307 Coil, 2B,
 1.00 x 125.9 x coil mm</v>
       </c>
-      <c r="B756" t="str" xml:space="preserve">
+      <c r="B754" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 304L/304-4301/4307 Coil, 2B,
 1.00 x 125.9 x coil mm
 Weight (Kg):1,726
@@ -12487,12 +12455,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="757" xml:space="preserve">
-      <c r="A757" t="str" xml:space="preserve">
+    <row r="755" xml:space="preserve">
+      <c r="A755" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 316L-1.4404 Coil, 2B,
 1.50 x 230.9 x coil mm</v>
       </c>
-      <c r="B757" t="str" xml:space="preserve">
+      <c r="B755" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 316L-1.4404 Coil, 2B,
 1.50 x 230.9 x coil mm
 Weight (Kg):1,956
@@ -12503,12 +12471,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="758" xml:space="preserve">
-      <c r="A758" t="str" xml:space="preserve">
+    <row r="756" xml:space="preserve">
+      <c r="A756" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, SBA,
 0.70 x 180.9 x coil mm</v>
       </c>
-      <c r="B758" t="str" xml:space="preserve">
+      <c r="B756" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, SBA,
 0.70 x 180.9 x coil mm
 Weight (Kg):2,402
@@ -12519,12 +12487,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="759" xml:space="preserve">
-      <c r="A759" t="str" xml:space="preserve">
+    <row r="757" xml:space="preserve">
+      <c r="A757" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 301-1.4310 Coil, BA,
 0.40 x 110.0 x coil mm</v>
       </c>
-      <c r="B759" t="str" xml:space="preserve">
+      <c r="B757" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 301-1.4310 Coil, BA,
 0.40 x 110.0 x coil mm
 Weight (Kg):1,734
@@ -12537,7 +12505,7 @@
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B759"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B757"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/scraped_data.xlsx
+++ b/scraped_data.xlsx
@@ -1017,18 +1017,17 @@
     </row>
     <row r="40" xml:space="preserve">
       <c r="A40" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4310Mo 301-Coil, 2B,
-0.80 x 1546.0 x coil mm</v>
+        <v xml:space="preserve">Acerinox Europa, 1.4310 301-Untrimmed, Coil, BA,
+0.40 x 1280.0 x coil mm</v>
       </c>
       <c r="B40" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4310Mo 301-Coil, 2B,
-0.80 x 1546.0 x coil mm
-Weight (Kg):9,850
-Quality:Prime
-Help
-Location:FABRICA ALGECIRAS
-2,700.00 €/ton
-Add to cart</v>
+        <v xml:space="preserve">Acerinox Europa, 1.4310 301-Untrimmed, Coil, BA,
+0.40 x 1280.0 x coil mm
+Weight (Kg):13,520
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+Out of Stock</v>
       </c>
     </row>
     <row r="41" xml:space="preserve">
@@ -1050,16 +1049,16 @@
     <row r="42" xml:space="preserve">
       <c r="A42" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4310Mo 301-Coil, 2B,
-0.80 x 268.0 x coil mm</v>
+0.80 x 1546.0 x coil mm</v>
       </c>
       <c r="B42" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4310Mo 301-Coil, 2B,
-0.80 x 268.0 x coil mm
-Weight (Kg):4,850
-Quality:Prime
-Help
-Location:FABRICA ALGECIRAS
-1,925.00 €/ton
+0.80 x 1546.0 x coil mm
+Weight (Kg):9,850
+Quality:Prime
+Help
+Location:FABRICA ALGECIRAS
+2,700.00 €/ton
 Add to cart</v>
       </c>
     </row>
@@ -1071,7 +1070,7 @@
       <c r="B43" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4310Mo 301-Coil, 2B,
 0.80 x 268.0 x coil mm
-Weight (Kg):4,814
+Weight (Kg):4,850
 Quality:Prime
 Help
 Location:FABRICA ALGECIRAS
@@ -1082,16 +1081,16 @@
     <row r="44" xml:space="preserve">
       <c r="A44" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4310Mo 301-Coil, 2B,
-0.80 x 725.0 x coil mm</v>
+0.80 x 268.0 x coil mm</v>
       </c>
       <c r="B44" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4310Mo 301-Coil, 2B,
-0.80 x 725.0 x coil mm
-Weight (Kg):3,670
-Quality:Prime
-Help
-Location:FABRICA ALGECIRAS
-1,975.00 €/ton
+0.80 x 268.0 x coil mm
+Weight (Kg):4,814
+Quality:Prime
+Help
+Location:FABRICA ALGECIRAS
+1,925.00 €/ton
 Add to cart</v>
       </c>
     </row>
@@ -1114,9 +1113,25 @@
     <row r="46" xml:space="preserve">
       <c r="A46" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4310Mo 301-Coil, 2B,
+0.80 x 725.0 x coil mm</v>
+      </c>
+      <c r="B46" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4310Mo 301-Coil, 2B,
+0.80 x 725.0 x coil mm
+Weight (Kg):3,670
+Quality:Prime
+Help
+Location:FABRICA ALGECIRAS
+1,975.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="47" xml:space="preserve">
+      <c r="A47" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4310Mo 301-Coil, 2B,
 1.40 x 635.0 x coil mm</v>
       </c>
-      <c r="B46" t="str" xml:space="preserve">
+      <c r="B47" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4310Mo 301-Coil, 2B,
 1.40 x 635.0 x coil mm
 Weight (Kg):10,970
@@ -1127,12 +1142,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="47" xml:space="preserve">
-      <c r="A47" t="str" xml:space="preserve">
+    <row r="48" xml:space="preserve">
+      <c r="A48" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4310Mo 301-Untrimmed, Coil, 2B,
 0.70 x 1543.0 x coil mm</v>
       </c>
-      <c r="B47" t="str" xml:space="preserve">
+      <c r="B48" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4310Mo 301-Untrimmed, Coil, 2B,
 0.70 x 1543.0 x coil mm
 Weight (Kg):18,333
@@ -1143,12 +1158,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="48" xml:space="preserve">
-      <c r="A48" t="str" xml:space="preserve">
+    <row r="49" xml:space="preserve">
+      <c r="A49" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4310Mo 301-Untrimmed, Coil, 2B,
 0.90 x 1540.0 x coil mm</v>
       </c>
-      <c r="B48" t="str" xml:space="preserve">
+      <c r="B49" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4310Mo 301-Untrimmed, Coil, 2B,
 0.90 x 1540.0 x coil mm
 Weight (Kg):3,390
@@ -1159,12 +1174,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="49" xml:space="preserve">
-      <c r="A49" t="str" xml:space="preserve">
+    <row r="50" xml:space="preserve">
+      <c r="A50" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4301 304-Coil, 1/4 HT,
 1.60 x 1230.0 x coil mm</v>
       </c>
-      <c r="B49" t="str" xml:space="preserve">
+      <c r="B50" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4301 304-Coil, 1/4 HT,
 1.60 x 1230.0 x coil mm
 Weight (Kg):6,560
@@ -1172,22 +1187,6 @@
 Help
 Location:FABRICA ALGECIRAS
 2,425.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="50" xml:space="preserve">
-      <c r="A50" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4301 304-Coil, 1/4 HT,
-1.90 x 1230.0 x coil mm</v>
-      </c>
-      <c r="B50" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4301 304-Coil, 1/4 HT,
-1.90 x 1230.0 x coil mm
-Weight (Kg):7,428
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-2,225.00 €/ton
 Add to cart</v>
       </c>
     </row>
@@ -1199,7 +1198,7 @@
       <c r="B51" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4301 304-Coil, 1/4 HT,
 1.90 x 1230.0 x coil mm
-Weight (Kg):7,104
+Weight (Kg):7,428
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -1215,7 +1214,7 @@
       <c r="B52" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4301 304-Coil, 1/4 HT,
 1.90 x 1230.0 x coil mm
-Weight (Kg):2,971
+Weight (Kg):7,104
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -1226,9 +1225,25 @@
     <row r="53" xml:space="preserve">
       <c r="A53" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4301 304-Coil, 1/4 HT,
+1.90 x 1230.0 x coil mm</v>
+      </c>
+      <c r="B53" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4301 304-Coil, 1/4 HT,
+1.90 x 1230.0 x coil mm
+Weight (Kg):2,971
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,225.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="54" xml:space="preserve">
+      <c r="A54" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4301 304-Coil, 1/4 HT,
 2.00 x 879.0 x coil mm</v>
       </c>
-      <c r="B53" t="str" xml:space="preserve">
+      <c r="B54" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4301 304-Coil, 1/4 HT,
 2.00 x 879.0 x coil mm
 Weight (Kg):6,958
@@ -1236,22 +1251,6 @@
 Help
 Location:FABRICA ALGECIRAS
 2,225.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="54" xml:space="preserve">
-      <c r="A54" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4301 304-Coil, 2B,
-0.50 x 385.0 x coil mm</v>
-      </c>
-      <c r="B54" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4301 304-Coil, 2B,
-0.50 x 385.0 x coil mm
-Weight (Kg):740
-Quality:Downgraded
-Help
-Location:FABRICA ALGECIRAS
-2,025.00 €/ton
 Add to cart</v>
       </c>
     </row>
@@ -1274,9 +1273,25 @@
     <row r="56" xml:space="preserve">
       <c r="A56" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4301 304-Coil, 2B,
+0.50 x 385.0 x coil mm</v>
+      </c>
+      <c r="B56" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4301 304-Coil, 2B,
+0.50 x 385.0 x coil mm
+Weight (Kg):740
+Quality:Downgraded
+Help
+Location:FABRICA ALGECIRAS
+2,025.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="57" xml:space="preserve">
+      <c r="A57" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4301 304-Coil, 2B,
 0.60 x 100.9 x coil mm</v>
       </c>
-      <c r="B56" t="str" xml:space="preserve">
+      <c r="B57" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4301 304-Coil, 2B,
 0.60 x 100.9 x coil mm
 Weight (Kg):574
@@ -1287,12 +1302,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="57" xml:space="preserve">
-      <c r="A57" t="str" xml:space="preserve">
+    <row r="58" xml:space="preserve">
+      <c r="A58" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4301 304-Coil, 2B,
 0.60 x 110.9 x coil mm</v>
       </c>
-      <c r="B57" t="str" xml:space="preserve">
+      <c r="B58" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4301 304-Coil, 2B,
 0.60 x 110.9 x coil mm
 Weight (Kg):728
@@ -1303,12 +1318,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="58" xml:space="preserve">
-      <c r="A58" t="str" xml:space="preserve">
+    <row r="59" xml:space="preserve">
+      <c r="A59" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4301 304-Coil, 2B,
 0.60 x 128.7 x coil mm</v>
       </c>
-      <c r="B58" t="str" xml:space="preserve">
+      <c r="B59" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4301 304-Coil, 2B,
 0.60 x 128.7 x coil mm
 Weight (Kg):921
@@ -1319,12 +1334,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="59" xml:space="preserve">
-      <c r="A59" t="str" xml:space="preserve">
+    <row r="60" xml:space="preserve">
+      <c r="A60" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4301 304-Coil, 2B,
 0.70 x 1044.0 x coil mm</v>
       </c>
-      <c r="B59" t="str" xml:space="preserve">
+      <c r="B60" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4301 304-Coil, 2B,
 0.70 x 1044.0 x coil mm
 Weight (Kg):3,776
@@ -1335,12 +1350,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="60" xml:space="preserve">
-      <c r="A60" t="str" xml:space="preserve">
+    <row r="61" xml:space="preserve">
+      <c r="A61" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4301 304-Coil, 2B,
 0.70 x 1075.0 x coil mm</v>
       </c>
-      <c r="B60" t="str" xml:space="preserve">
+      <c r="B61" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4301 304-Coil, 2B,
 0.70 x 1075.0 x coil mm
 Weight (Kg):2,100
@@ -1351,12 +1366,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="61" xml:space="preserve">
-      <c r="A61" t="str" xml:space="preserve">
+    <row r="62" xml:space="preserve">
+      <c r="A62" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4301 304-Coil, 2B,
 0.90 x 195.9 x coil mm</v>
       </c>
-      <c r="B61" t="str" xml:space="preserve">
+      <c r="B62" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4301 304-Coil, 2B,
 0.90 x 195.9 x coil mm
 Weight (Kg):562
@@ -1367,12 +1382,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="62" xml:space="preserve">
-      <c r="A62" t="str" xml:space="preserve">
+    <row r="63" xml:space="preserve">
+      <c r="A63" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4301 304-Coil, 2D,
 0.90 x 1027.0 x coil mm</v>
       </c>
-      <c r="B62" t="str" xml:space="preserve">
+      <c r="B63" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4301 304-Coil, 2D,
 0.90 x 1027.0 x coil mm
 Weight (Kg):17,981
@@ -1383,12 +1398,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="63" xml:space="preserve">
-      <c r="A63" t="str" xml:space="preserve">
+    <row r="64" xml:space="preserve">
+      <c r="A64" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4301 304-Coil, 2D,
 0.90 x 937.0 x coil mm</v>
       </c>
-      <c r="B63" t="str" xml:space="preserve">
+      <c r="B64" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4301 304-Coil, 2D,
 0.90 x 937.0 x coil mm
 Weight (Kg):6,680
@@ -1399,12 +1414,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="64" xml:space="preserve">
-      <c r="A64" t="str" xml:space="preserve">
+    <row r="65" xml:space="preserve">
+      <c r="A65" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4301 304-Coil, BA,
 0.30 x 931.0 x coil mm</v>
       </c>
-      <c r="B64" t="str" xml:space="preserve">
+      <c r="B65" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4301 304-Coil, BA,
 0.30 x 931.0 x coil mm
 Weight (Kg):16,870
@@ -1415,12 +1430,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="65" xml:space="preserve">
-      <c r="A65" t="str" xml:space="preserve">
+    <row r="66" xml:space="preserve">
+      <c r="A66" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4301 304-Coil, BA,
 0.30 x 935.0 x coil mm</v>
       </c>
-      <c r="B65" t="str" xml:space="preserve">
+      <c r="B66" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4301 304-Coil, BA,
 0.30 x 935.0 x coil mm
 Weight (Kg):17,020
@@ -1431,12 +1446,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="66" xml:space="preserve">
-      <c r="A66" t="str" xml:space="preserve">
+    <row r="67" xml:space="preserve">
+      <c r="A67" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4301 304-Coil, BA,
 0.30 x 938.0 x coil mm</v>
       </c>
-      <c r="B66" t="str" xml:space="preserve">
+      <c r="B67" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4301 304-Coil, BA,
 0.30 x 938.0 x coil mm
 Weight (Kg):17,060
@@ -1444,22 +1459,6 @@
 Help
 Location:FABRICA ALGECIRAS
 2,900.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="67" xml:space="preserve">
-      <c r="A67" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4301 304-Coil, BA,
-0.30 x 940.0 x coil mm</v>
-      </c>
-      <c r="B67" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4301 304-Coil, BA,
-0.30 x 940.0 x coil mm
-Weight (Kg):16,780
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-2,225.00 €/ton
 Add to cart</v>
       </c>
     </row>
@@ -1471,20 +1470,36 @@
       <c r="B68" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4301 304-Coil, BA,
 0.30 x 940.0 x coil mm
-Weight (Kg):17,110
-Quality:Prime
-Help
-Location:FABRICA ALGECIRAS
-2,900.00 €/ton
+Weight (Kg):16,780
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,225.00 €/ton
 Add to cart</v>
       </c>
     </row>
     <row r="69" xml:space="preserve">
       <c r="A69" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4301 304-Coil, BA,
+0.30 x 940.0 x coil mm</v>
+      </c>
+      <c r="B69" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4301 304-Coil, BA,
+0.30 x 940.0 x coil mm
+Weight (Kg):17,110
+Quality:Prime
+Help
+Location:FABRICA ALGECIRAS
+2,900.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="70" xml:space="preserve">
+      <c r="A70" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4301 304-Coil, BA,
 0.40 x 112.9 x coil mm</v>
       </c>
-      <c r="B69" t="str" xml:space="preserve">
+      <c r="B70" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4301 304-Coil, BA,
 0.40 x 112.9 x coil mm
 Weight (Kg):1,162
@@ -1495,12 +1510,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="70" xml:space="preserve">
-      <c r="A70" t="str" xml:space="preserve">
+    <row r="71" xml:space="preserve">
+      <c r="A71" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4301 304-Coil, BA,
 0.40 x 115.0 x coil mm</v>
       </c>
-      <c r="B70" t="str" xml:space="preserve">
+      <c r="B71" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4301 304-Coil, BA,
 0.40 x 115.0 x coil mm
 Weight (Kg):598
@@ -1511,12 +1526,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="71" xml:space="preserve">
-      <c r="A71" t="str" xml:space="preserve">
+    <row r="72" xml:space="preserve">
+      <c r="A72" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4301 304-Coil, BA,
 0.40 x 140.0 x coil mm</v>
       </c>
-      <c r="B71" t="str" xml:space="preserve">
+      <c r="B72" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4301 304-Coil, BA,
 0.40 x 140.0 x coil mm
 Weight (Kg):1,166
@@ -1527,31 +1542,15 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="72" xml:space="preserve">
-      <c r="A72" t="str" xml:space="preserve">
+    <row r="73" xml:space="preserve">
+      <c r="A73" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4301 304-Coil, BA,
 0.40 x 200.0 x coil mm</v>
       </c>
-      <c r="B72" t="str" xml:space="preserve">
+      <c r="B73" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4301 304-Coil, BA,
 0.40 x 200.0 x coil mm
 Weight (Kg):526
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-2,075.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="73" xml:space="preserve">
-      <c r="A73" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4301 304-Coil, BA,
-0.40 x 280.0 x coil mm</v>
-      </c>
-      <c r="B73" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4301 304-Coil, BA,
-0.40 x 280.0 x coil mm
-Weight (Kg):2,620
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -1567,7 +1566,7 @@
       <c r="B74" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4301 304-Coil, BA,
 0.40 x 280.0 x coil mm
-Weight (Kg):2,242
+Weight (Kg):2,620
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -1578,9 +1577,25 @@
     <row r="75" xml:space="preserve">
       <c r="A75" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4301 304-Coil, BA,
+0.40 x 280.0 x coil mm</v>
+      </c>
+      <c r="B75" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4301 304-Coil, BA,
+0.40 x 280.0 x coil mm
+Weight (Kg):2,242
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,075.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="76" xml:space="preserve">
+      <c r="A76" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4301 304-Coil, BA,
 0.40 x 330.0 x coil mm</v>
       </c>
-      <c r="B75" t="str" xml:space="preserve">
+      <c r="B76" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4301 304-Coil, BA,
 0.40 x 330.0 x coil mm
 Weight (Kg):1,034
@@ -1588,22 +1603,6 @@
 Help
 Location:FABRICA ALGECIRAS
 2,075.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="76" xml:space="preserve">
-      <c r="A76" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4301 304-Coil, BA,
-0.40 x 578.8 x coil mm</v>
-      </c>
-      <c r="B76" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4301 304-Coil, BA,
-0.40 x 578.8 x coil mm
-Weight (Kg):4,322
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-2,125.00 €/ton
 Add to cart</v>
       </c>
     </row>
@@ -1615,7 +1614,7 @@
       <c r="B77" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4301 304-Coil, BA,
 0.40 x 578.8 x coil mm
-Weight (Kg):1,774
+Weight (Kg):4,322
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -1631,7 +1630,7 @@
       <c r="B78" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4301 304-Coil, BA,
 0.40 x 578.8 x coil mm
-Weight (Kg):4,408
+Weight (Kg):1,774
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -1642,12 +1641,12 @@
     <row r="79" xml:space="preserve">
       <c r="A79" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4301 304-Coil, BA,
-0.40 x 718.0 x coil mm</v>
+0.40 x 578.8 x coil mm</v>
       </c>
       <c r="B79" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4301 304-Coil, BA,
-0.40 x 718.0 x coil mm
-Weight (Kg):5,128
+0.40 x 578.8 x coil mm
+Weight (Kg):4,408
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -1663,7 +1662,7 @@
       <c r="B80" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4301 304-Coil, BA,
 0.40 x 718.0 x coil mm
-Weight (Kg):2,992
+Weight (Kg):5,128
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -1679,7 +1678,7 @@
       <c r="B81" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4301 304-Coil, BA,
 0.40 x 718.0 x coil mm
-Weight (Kg):3,403
+Weight (Kg):2,992
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -1690,9 +1689,25 @@
     <row r="82" xml:space="preserve">
       <c r="A82" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4301 304-Coil, BA,
+0.40 x 718.0 x coil mm</v>
+      </c>
+      <c r="B82" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4301 304-Coil, BA,
+0.40 x 718.0 x coil mm
+Weight (Kg):3,403
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,125.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="83" xml:space="preserve">
+      <c r="A83" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4301 304-Coil, BA,
 0.40 x 935.0 x coil mm</v>
       </c>
-      <c r="B82" t="str" xml:space="preserve">
+      <c r="B83" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4301 304-Coil, BA,
 0.40 x 935.0 x coil mm
 Weight (Kg):2,733
@@ -1703,12 +1718,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="83" xml:space="preserve">
-      <c r="A83" t="str" xml:space="preserve">
+    <row r="84" xml:space="preserve">
+      <c r="A84" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4301 304-Coil, BA,
 0.40 x 938.0 x coil mm</v>
       </c>
-      <c r="B83" t="str" xml:space="preserve">
+      <c r="B84" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4301 304-Coil, BA,
 0.40 x 938.0 x coil mm
 Weight (Kg):2,410
@@ -1719,12 +1734,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="84" xml:space="preserve">
-      <c r="A84" t="str" xml:space="preserve">
+    <row r="85" xml:space="preserve">
+      <c r="A85" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4301 304-Coil, BA,
 0.40 x 939.0 x coil mm</v>
       </c>
-      <c r="B84" t="str" xml:space="preserve">
+      <c r="B85" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4301 304-Coil, BA,
 0.40 x 939.0 x coil mm
 Weight (Kg):2,982
@@ -1735,12 +1750,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="85" xml:space="preserve">
-      <c r="A85" t="str" xml:space="preserve">
+    <row r="86" xml:space="preserve">
+      <c r="A86" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4301 304-Coil, BA,
 0.50 x 935.0 x coil mm</v>
       </c>
-      <c r="B85" t="str" xml:space="preserve">
+      <c r="B86" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4301 304-Coil, BA,
 0.50 x 935.0 x coil mm
 Weight (Kg):16,840
@@ -1751,12 +1766,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="86" xml:space="preserve">
-      <c r="A86" t="str" xml:space="preserve">
+    <row r="87" xml:space="preserve">
+      <c r="A87" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4301 304-Coil, BA,
 0.60 x 1228.0 x coil mm</v>
       </c>
-      <c r="B86" t="str" xml:space="preserve">
+      <c r="B87" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4301 304-Coil, BA,
 0.60 x 1228.0 x coil mm
 Weight (Kg):20,070
@@ -1767,31 +1782,15 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="87" xml:space="preserve">
-      <c r="A87" t="str" xml:space="preserve">
+    <row r="88" xml:space="preserve">
+      <c r="A88" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4301 304-Coil, BA,
 0.60 x 155.9 x coil mm</v>
       </c>
-      <c r="B87" t="str" xml:space="preserve">
+      <c r="B88" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4301 304-Coil, BA,
 0.60 x 155.9 x coil mm
 Weight (Kg):674
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-2,075.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="88" xml:space="preserve">
-      <c r="A88" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4301 304-Coil, BA,
-0.60 x 211.9 x coil mm</v>
-      </c>
-      <c r="B88" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4301 304-Coil, BA,
-0.60 x 211.9 x coil mm
-Weight (Kg):508
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -1807,7 +1806,7 @@
       <c r="B89" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4301 304-Coil, BA,
 0.60 x 211.9 x coil mm
-Weight (Kg):504
+Weight (Kg):508
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -1818,9 +1817,25 @@
     <row r="90" xml:space="preserve">
       <c r="A90" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4301 304-Coil, BA,
+0.60 x 211.9 x coil mm</v>
+      </c>
+      <c r="B90" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4301 304-Coil, BA,
+0.60 x 211.9 x coil mm
+Weight (Kg):504
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,075.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="91" xml:space="preserve">
+      <c r="A91" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4301 304-Coil, BA,
 0.60 x 937.0 x coil mm</v>
       </c>
-      <c r="B90" t="str" xml:space="preserve">
+      <c r="B91" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4301 304-Coil, BA,
 0.60 x 937.0 x coil mm
 Weight (Kg):16,860
@@ -1831,12 +1846,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="91" xml:space="preserve">
-      <c r="A91" t="str" xml:space="preserve">
+    <row r="92" xml:space="preserve">
+      <c r="A92" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4301 304-Coil, BA,
 0.60 x 978.0 x coil mm</v>
       </c>
-      <c r="B91" t="str" xml:space="preserve">
+      <c r="B92" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4301 304-Coil, BA,
 0.60 x 978.0 x coil mm
 Weight (Kg):17,840
@@ -1847,12 +1862,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="92" xml:space="preserve">
-      <c r="A92" t="str" xml:space="preserve">
+    <row r="93" xml:space="preserve">
+      <c r="A93" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4301 304-Coil, BA,
 0.70 x 1150.0 x coil mm</v>
       </c>
-      <c r="B92" t="str" xml:space="preserve">
+      <c r="B93" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4301 304-Coil, BA,
 0.70 x 1150.0 x coil mm
 Weight (Kg):4,200
@@ -1863,12 +1878,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="93" xml:space="preserve">
-      <c r="A93" t="str" xml:space="preserve">
+    <row r="94" xml:space="preserve">
+      <c r="A94" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4301 304-Coil, BA,
 0.70 x 1224.0 x coil mm</v>
       </c>
-      <c r="B93" t="str" xml:space="preserve">
+      <c r="B94" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4301 304-Coil, BA,
 0.70 x 1224.0 x coil mm
 Weight (Kg):21,300
@@ -1879,12 +1894,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="94" xml:space="preserve">
-      <c r="A94" t="str" xml:space="preserve">
+    <row r="95" xml:space="preserve">
+      <c r="A95" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4301 304-Coil, BA,
 0.90 x 1240.0 x coil mm</v>
       </c>
-      <c r="B94" t="str" xml:space="preserve">
+      <c r="B95" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4301 304-Coil, BA,
 0.90 x 1240.0 x coil mm
 Weight (Kg):9,786
@@ -1895,12 +1910,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="95" xml:space="preserve">
-      <c r="A95" t="str" xml:space="preserve">
+    <row r="96" xml:space="preserve">
+      <c r="A96" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4301 304-Coil, BA, ET-60
 0.40 x 238.0 x coil mm</v>
       </c>
-      <c r="B95" t="str" xml:space="preserve">
+      <c r="B96" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4301 304-Coil, BA, ET-60
 0.40 x 238.0 x coil mm
 Weight (Kg):928
@@ -1911,31 +1926,15 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="96" xml:space="preserve">
-      <c r="A96" t="str" xml:space="preserve">
+    <row r="97" xml:space="preserve">
+      <c r="A97" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4301 304-Coil, Emboss Chequered,
 0.70 x 105.9 x coil mm</v>
       </c>
-      <c r="B96" t="str" xml:space="preserve">
+      <c r="B97" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4301 304-Coil, Emboss Chequered,
 0.70 x 105.9 x coil mm
 Weight (Kg):550
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-2,075.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="97" xml:space="preserve">
-      <c r="A97" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4301 304-Coil, Emboss Chequered,
-0.70 x 265.9 x coil mm</v>
-      </c>
-      <c r="B97" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4301 304-Coil, Emboss Chequered,
-0.70 x 265.9 x coil mm
-Weight (Kg):1,484
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -1951,7 +1950,7 @@
       <c r="B98" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4301 304-Coil, Emboss Chequered,
 0.70 x 265.9 x coil mm
-Weight (Kg):1,490
+Weight (Kg):1,484
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -1962,28 +1961,28 @@
     <row r="99" xml:space="preserve">
       <c r="A99" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4301 304-Coil, Emboss Chequered,
+0.70 x 265.9 x coil mm</v>
+      </c>
+      <c r="B99" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4301 304-Coil, Emboss Chequered,
+0.70 x 265.9 x coil mm
+Weight (Kg):1,490
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,075.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="100" xml:space="preserve">
+      <c r="A100" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4301 304-Coil, Emboss Chequered,
 0.70 x 270.9 x coil mm</v>
       </c>
-      <c r="B99" t="str" xml:space="preserve">
+      <c r="B100" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4301 304-Coil, Emboss Chequered,
 0.70 x 270.9 x coil mm
 Weight (Kg):1,442
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-2,075.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="100" xml:space="preserve">
-      <c r="A100" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4301 304-Coil, Emboss Chequered,
-0.70 x 285.0 x coil mm</v>
-      </c>
-      <c r="B100" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4301 304-Coil, Emboss Chequered,
-0.70 x 285.0 x coil mm
-Weight (Kg):1,502
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -2010,9 +2009,25 @@
     <row r="102" xml:space="preserve">
       <c r="A102" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4301 304-Coil, Emboss Chequered,
+0.70 x 285.0 x coil mm</v>
+      </c>
+      <c r="B102" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4301 304-Coil, Emboss Chequered,
+0.70 x 285.0 x coil mm
+Weight (Kg):1,502
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,075.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="103" xml:space="preserve">
+      <c r="A103" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4301 304-Coil, Emboss Chequered,
 0.95 x 915.0 x coil mm</v>
       </c>
-      <c r="B102" t="str" xml:space="preserve">
+      <c r="B103" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4301 304-Coil, Emboss Chequered,
 0.95 x 915.0 x coil mm
 Weight (Kg):3,271
@@ -2023,12 +2038,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="103" xml:space="preserve">
-      <c r="A103" t="str" xml:space="preserve">
+    <row r="104" xml:space="preserve">
+      <c r="A104" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4301 304-Coil, Emboss Chequered,
 0.95 x 999.0 x coil mm</v>
       </c>
-      <c r="B103" t="str" xml:space="preserve">
+      <c r="B104" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4301 304-Coil, Emboss Chequered,
 0.95 x 999.0 x coil mm
 Weight (Kg):4,214
@@ -2036,22 +2051,6 @@
 Help
 Location:FABRICA ALGECIRAS
 2,425.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="104" xml:space="preserve">
-      <c r="A104" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4301 304-Coil, Emboss Linen,
-0.60 x 630.0 x coil mm</v>
-      </c>
-      <c r="B104" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4301 304-Coil, Emboss Linen,
-0.60 x 630.0 x coil mm
-Weight (Kg):1,878
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-2,125.00 €/ton
 Add to cart</v>
       </c>
     </row>
@@ -2063,7 +2062,7 @@
       <c r="B105" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4301 304-Coil, Emboss Linen,
 0.60 x 630.0 x coil mm
-Weight (Kg):1,872
+Weight (Kg):1,878
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -2079,8 +2078,8 @@
       <c r="B106" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4301 304-Coil, Emboss Linen,
 0.60 x 630.0 x coil mm
-Weight (Kg):1,837
-Quality:Prime
+Weight (Kg):1,872
+Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
 2,125.00 €/ton
@@ -2090,28 +2089,28 @@
     <row r="107" xml:space="preserve">
       <c r="A107" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4301 304-Coil, Emboss Linen,
+0.60 x 630.0 x coil mm</v>
+      </c>
+      <c r="B107" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4301 304-Coil, Emboss Linen,
+0.60 x 630.0 x coil mm
+Weight (Kg):1,837
+Quality:Prime
+Help
+Location:FABRICA ALGECIRAS
+2,125.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="108" xml:space="preserve">
+      <c r="A108" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4301 304-Coil, Emboss Linen,
 0.70 x 260.9 x coil mm</v>
       </c>
-      <c r="B107" t="str" xml:space="preserve">
+      <c r="B108" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4301 304-Coil, Emboss Linen,
 0.70 x 260.9 x coil mm
 Weight (Kg):632
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-2,075.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="108" xml:space="preserve">
-      <c r="A108" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4301 304-Coil, Emboss Linen, PVC-80
-0.70 x 209.9 x coil mm</v>
-      </c>
-      <c r="B108" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4301 304-Coil, Emboss Linen, PVC-80
-0.70 x 209.9 x coil mm
-Weight (Kg):1,006
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -2127,8 +2126,8 @@
       <c r="B109" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4301 304-Coil, Emboss Linen, PVC-80
 0.70 x 209.9 x coil mm
-Weight (Kg):1,208
-Quality:Prime
+Weight (Kg):1,006
+Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
 2,075.00 €/ton
@@ -2143,8 +2142,8 @@
       <c r="B110" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4301 304-Coil, Emboss Linen, PVC-80
 0.70 x 209.9 x coil mm
-Weight (Kg):1,256
-Quality:Prime-2
+Weight (Kg):1,208
+Quality:Prime
 Help
 Location:FABRICA ALGECIRAS
 2,075.00 €/ton
@@ -2153,10 +2152,26 @@
     </row>
     <row r="111" xml:space="preserve">
       <c r="A111" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4301 304-Coil, Emboss Linen, PVC-80
+0.70 x 209.9 x coil mm</v>
+      </c>
+      <c r="B111" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4301 304-Coil, Emboss Linen, PVC-80
+0.70 x 209.9 x coil mm
+Weight (Kg):1,256
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,075.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="112" xml:space="preserve">
+      <c r="A112" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4301 304-Coil, Polished N4-G-320,
 1.00 x 991.0 x coil mm</v>
       </c>
-      <c r="B111" t="str" xml:space="preserve">
+      <c r="B112" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4301 304-Coil, Polished N4-G-320,
 1.00 x 991.0 x coil mm
 Weight (Kg):18,760
@@ -2167,12 +2182,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="112" xml:space="preserve">
-      <c r="A112" t="str" xml:space="preserve">
+    <row r="113" xml:space="preserve">
+      <c r="A113" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4301 304-Coil, SB-G-400,
 0.80 x 205.9 x coil mm</v>
       </c>
-      <c r="B112" t="str" xml:space="preserve">
+      <c r="B113" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4301 304-Coil, SB-G-400,
 0.80 x 205.9 x coil mm
 Weight (Kg):1,876
@@ -2183,12 +2198,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="113" xml:space="preserve">
-      <c r="A113" t="str" xml:space="preserve">
+    <row r="114" xml:space="preserve">
+      <c r="A114" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4301 304-Coil, SB-G-400,
 0.80 x 260.9 x coil mm</v>
       </c>
-      <c r="B113" t="str" xml:space="preserve">
+      <c r="B114" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4301 304-Coil, SB-G-400,
 0.80 x 260.9 x coil mm
 Weight (Kg):1,626
@@ -2199,12 +2214,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="114" xml:space="preserve">
-      <c r="A114" t="str" xml:space="preserve">
+    <row r="115" xml:space="preserve">
+      <c r="A115" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4301 304-Sheet, BA,
 0.40 x 1000.0 x 2000.0 mm</v>
       </c>
-      <c r="B114" t="str" xml:space="preserve">
+      <c r="B115" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4301 304-Sheet, BA,
 0.40 x 1000.0 x 2000.0 mm
 Weight (Kg):1,038
@@ -2215,12 +2230,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="115" xml:space="preserve">
-      <c r="A115" t="str" xml:space="preserve">
+    <row r="116" xml:space="preserve">
+      <c r="A116" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4301 304-Sheet, BA,
 0.40 x 536.5 x 696.0 mm</v>
       </c>
-      <c r="B115" t="str" xml:space="preserve">
+      <c r="B116" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4301 304-Sheet, BA,
 0.40 x 536.5 x 696.0 mm
 Weight (Kg):1,060
@@ -2231,12 +2246,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="116" xml:space="preserve">
-      <c r="A116" t="str" xml:space="preserve">
+    <row r="117" xml:space="preserve">
+      <c r="A117" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4301 304-Sheet, BA,
 0.80 x 1000.0 x 2000.0 mm</v>
       </c>
-      <c r="B116" t="str" xml:space="preserve">
+      <c r="B117" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4301 304-Sheet, BA,
 0.80 x 1000.0 x 2000.0 mm
 Weight (Kg):738
@@ -2247,12 +2262,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="117" xml:space="preserve">
-      <c r="A117" t="str" xml:space="preserve">
+    <row r="118" xml:space="preserve">
+      <c r="A118" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4301 304-Sheet, BA,
 1.50 x 1000.0 x 2000.0 mm</v>
       </c>
-      <c r="B117" t="str" xml:space="preserve">
+      <c r="B118" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4301 304-Sheet, BA,
 1.50 x 1000.0 x 2000.0 mm
 Weight (Kg):1,918
@@ -2263,12 +2278,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="118" xml:space="preserve">
-      <c r="A118" t="str" xml:space="preserve">
+    <row r="119" xml:space="preserve">
+      <c r="A119" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4301 304-Untrimmed, Coil, 1/4 HT,
 1.50 x 1024.0 x coil mm</v>
       </c>
-      <c r="B118" t="str" xml:space="preserve">
+      <c r="B119" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4301 304-Untrimmed, Coil, 1/4 HT,
 1.50 x 1024.0 x coil mm
 Weight (Kg):4,500
@@ -2277,22 +2292,6 @@
 Location:FABRICA ALGECIRAS
 2,425.00 €/ton
 Add to cart</v>
-      </c>
-    </row>
-    <row r="119" xml:space="preserve">
-      <c r="A119" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4301 304-Coil, Emboss Linen,
-0.70 x 650.0 x coil mm</v>
-      </c>
-      <c r="B119" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4301 304-Coil, Emboss Linen,
-0.70 x 650.0 x coil mm
-Weight (Kg):3,670
-Quality:Prime
-Help
-Location:FABRICA ALGECIRAS
-2,125.00 €/ton
-Reserved</v>
       </c>
     </row>
     <row r="120" xml:space="preserve">
@@ -2303,7 +2302,7 @@
       <c r="B120" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4301 304-Coil, Emboss Linen,
 0.70 x 650.0 x coil mm
-Weight (Kg):3,321
+Weight (Kg):3,670
 Quality:Prime
 Help
 Location:FABRICA ALGECIRAS
@@ -2313,18 +2312,18 @@
     </row>
     <row r="121" xml:space="preserve">
       <c r="A121" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4301 304-Untrimmed, Coil, 2B,
-0.70 x 1085.0 x coil mm</v>
+        <v xml:space="preserve">Acerinox Europa, 1.4301 304-Coil, Emboss Linen,
+0.70 x 650.0 x coil mm</v>
       </c>
       <c r="B121" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4301 304-Untrimmed, Coil, 2B,
-0.70 x 1085.0 x coil mm
-Weight (Kg):2,772
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-2,225.00 €/ton
-Out of Stock</v>
+        <v xml:space="preserve">Acerinox Europa, 1.4301 304-Coil, Emboss Linen,
+0.70 x 650.0 x coil mm
+Weight (Kg):3,321
+Quality:Prime
+Help
+Location:FABRICA ALGECIRAS
+2,125.00 €/ton
+Reserved</v>
       </c>
     </row>
     <row r="122" xml:space="preserve">
@@ -2601,18 +2600,18 @@
     </row>
     <row r="139" xml:space="preserve">
       <c r="A139" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4301 304-Untrimmed, Coil, BA,
-0.70 x 1273.0 x coil mm</v>
+        <v xml:space="preserve">Acerinox Europa, 1.4301 304-Untrimmed, Coil, 2B,
+0.70 x 1085.0 x coil mm</v>
       </c>
       <c r="B139" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4301 304-Untrimmed, Coil, BA,
-0.70 x 1273.0 x coil mm
-Weight (Kg):3,140
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-2,225.00 €/ton
-Add to cart</v>
+        <v xml:space="preserve">Acerinox Europa, 1.4301 304-Untrimmed, Coil, 2B,
+0.70 x 1085.0 x coil mm
+Weight (Kg):2,772
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,225.00 €/ton
+Out of Stock</v>
       </c>
     </row>
     <row r="140" xml:space="preserve">
@@ -2655,7 +2654,7 @@
       <c r="B142" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4301 304-Untrimmed, Coil, BA,
 0.70 x 1273.0 x coil mm
-Weight (Kg):3,323
+Weight (Kg):3,140
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -2666,9 +2665,25 @@
     <row r="143" xml:space="preserve">
       <c r="A143" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4301 304-Untrimmed, Coil, BA,
+0.70 x 1273.0 x coil mm</v>
+      </c>
+      <c r="B143" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4301 304-Untrimmed, Coil, BA,
+0.70 x 1273.0 x coil mm
+Weight (Kg):3,323
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,225.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="144" xml:space="preserve">
+      <c r="A144" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4301 304-Untrimmed, Coil, BA,
 0.90 x 1245.0 x coil mm</v>
       </c>
-      <c r="B143" t="str" xml:space="preserve">
+      <c r="B144" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4301 304-Untrimmed, Coil, BA,
 0.90 x 1245.0 x coil mm
 Weight (Kg):2,372
@@ -2679,12 +2694,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="144" xml:space="preserve">
-      <c r="A144" t="str" xml:space="preserve">
+    <row r="145" xml:space="preserve">
+      <c r="A145" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4301 304-Untrimmed, Coil, SB-G-400,
 1.00 x 850.0 x coil mm</v>
       </c>
-      <c r="B144" t="str" xml:space="preserve">
+      <c r="B145" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4301 304-Untrimmed, Coil, SB-G-400,
 1.00 x 850.0 x coil mm
 Weight (Kg):5,870
@@ -2695,12 +2710,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="145" xml:space="preserve">
-      <c r="A145" t="str" xml:space="preserve">
+    <row r="146" xml:space="preserve">
+      <c r="A146" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4301 304DDQ-Coil, BA,
 0.70 x 1020.0 x coil mm</v>
       </c>
-      <c r="B145" t="str" xml:space="preserve">
+      <c r="B146" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4301 304DDQ-Coil, BA,
 0.70 x 1020.0 x coil mm
 Weight (Kg):7,100
@@ -2711,12 +2726,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="146" xml:space="preserve">
-      <c r="A146" t="str" xml:space="preserve">
+    <row r="147" xml:space="preserve">
+      <c r="A147" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4301 304DDQ-Coil, BA,
 0.70 x 340.0 x coil mm</v>
       </c>
-      <c r="B146" t="str" xml:space="preserve">
+      <c r="B147" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4301 304DDQ-Coil, BA,
 0.70 x 340.0 x coil mm
 Weight (Kg):4,352
@@ -2724,22 +2739,6 @@
 Help
 Location:FABRICA ALGECIRAS
 2,075.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="147" xml:space="preserve">
-      <c r="A147" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4301 304DDQ-Coil, BA,
-0.70 x 943.0 x coil mm</v>
-      </c>
-      <c r="B147" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4301 304DDQ-Coil, BA,
-0.70 x 943.0 x coil mm
-Weight (Kg):16,790
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-2,225.00 €/ton
 Add to cart</v>
       </c>
     </row>
@@ -2751,11 +2750,11 @@
       <c r="B148" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4301 304DDQ-Coil, BA,
 0.70 x 943.0 x coil mm
-Weight (Kg):16,740
-Quality:Prime
-Help
-Location:FABRICA ALGECIRAS
-2,900.00 €/ton
+Weight (Kg):16,790
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,225.00 €/ton
 Add to cart</v>
       </c>
     </row>
@@ -2767,11 +2766,11 @@
       <c r="B149" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4301 304DDQ-Coil, BA,
 0.70 x 943.0 x coil mm
-Weight (Kg):16,670
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-2,225.00 €/ton
+Weight (Kg):16,740
+Quality:Prime
+Help
+Location:FABRICA ALGECIRAS
+2,900.00 €/ton
 Add to cart</v>
       </c>
     </row>
@@ -2783,27 +2782,27 @@
       <c r="B150" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4301 304DDQ-Coil, BA,
 0.70 x 943.0 x coil mm
-Weight (Kg):16,680
-Quality:Prime
-Help
-Location:FABRICA ALGECIRAS
-2,900.00 €/ton
+Weight (Kg):16,670
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,225.00 €/ton
 Add to cart</v>
       </c>
     </row>
     <row r="151" xml:space="preserve">
       <c r="A151" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4301 304DDQ-Coil, BA,
-0.70 x 951.0 x coil mm</v>
+0.70 x 943.0 x coil mm</v>
       </c>
       <c r="B151" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4301 304DDQ-Coil, BA,
-0.70 x 951.0 x coil mm
-Weight (Kg):3,561
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-2,225.00 €/ton
+0.70 x 943.0 x coil mm
+Weight (Kg):16,680
+Quality:Prime
+Help
+Location:FABRICA ALGECIRAS
+2,900.00 €/ton
 Add to cart</v>
       </c>
     </row>
@@ -2815,20 +2814,36 @@
       <c r="B152" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4301 304DDQ-Coil, BA,
 0.70 x 951.0 x coil mm
-Weight (Kg):2,860
-Quality:Prime
-Help
-Location:FABRICA ALGECIRAS
-2,425.00 €/ton
+Weight (Kg):3,561
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,225.00 €/ton
 Add to cart</v>
       </c>
     </row>
     <row r="153" xml:space="preserve">
       <c r="A153" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4301 304DDQ-Coil, BA,
+0.70 x 951.0 x coil mm</v>
+      </c>
+      <c r="B153" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4301 304DDQ-Coil, BA,
+0.70 x 951.0 x coil mm
+Weight (Kg):2,860
+Quality:Prime
+Help
+Location:FABRICA ALGECIRAS
+2,425.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="154" xml:space="preserve">
+      <c r="A154" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4301 304DDQ-Untrimmed, Coil, BA,
 0.80 x 1265.0 x coil mm</v>
       </c>
-      <c r="B153" t="str" xml:space="preserve">
+      <c r="B154" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4301 304DDQ-Untrimmed, Coil, BA,
 0.80 x 1265.0 x coil mm
 Weight (Kg):2,700
@@ -2839,12 +2854,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="154" xml:space="preserve">
-      <c r="A154" t="str" xml:space="preserve">
+    <row r="155" xml:space="preserve">
+      <c r="A155" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4306 304L-Coil, 2B,
 0.40 x 1270.0 x coil mm</v>
       </c>
-      <c r="B154" t="str" xml:space="preserve">
+      <c r="B155" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4306 304L-Coil, 2B,
 0.40 x 1270.0 x coil mm
 Weight (Kg):3,940
@@ -2855,12 +2870,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="155" xml:space="preserve">
-      <c r="A155" t="str" xml:space="preserve">
+    <row r="156" xml:space="preserve">
+      <c r="A156" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4306 304L-Coil, 2B,
 0.90 x 1271.0 x coil mm</v>
       </c>
-      <c r="B155" t="str" xml:space="preserve">
+      <c r="B156" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4306 304L-Coil, 2B,
 0.90 x 1271.0 x coil mm
 Weight (Kg):3,100
@@ -2871,12 +2886,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="156" xml:space="preserve">
-      <c r="A156" t="str" xml:space="preserve">
+    <row r="157" xml:space="preserve">
+      <c r="A157" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L-Sheet, SB-G-500,
 3.00 x 1500.0 x 3000.0 mm</v>
       </c>
-      <c r="B156" t="str" xml:space="preserve">
+      <c r="B157" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L-Sheet, SB-G-500,
 3.00 x 1500.0 x 3000.0 mm
 Weight (Kg):1,466
@@ -2887,12 +2902,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="157" xml:space="preserve">
-      <c r="A157" t="str" xml:space="preserve">
+    <row r="158" xml:space="preserve">
+      <c r="A158" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Coil, 2B,
 0.80 x 150.9 x coil mm</v>
       </c>
-      <c r="B157" t="str" xml:space="preserve">
+      <c r="B158" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Coil, 2B,
 0.80 x 150.9 x coil mm
 Weight (Kg):670
@@ -2903,12 +2918,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="158" xml:space="preserve">
-      <c r="A158" t="str" xml:space="preserve">
+    <row r="159" xml:space="preserve">
+      <c r="A159" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Coil, 2B,
 1.00 x 125.9 x coil mm</v>
       </c>
-      <c r="B158" t="str" xml:space="preserve">
+      <c r="B159" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Coil, 2B,
 1.00 x 125.9 x coil mm
 Weight (Kg):568
@@ -2919,32 +2934,16 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="159" xml:space="preserve">
-      <c r="A159" t="str" xml:space="preserve">
+    <row r="160" xml:space="preserve">
+      <c r="A160" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Coil, 2B,
 1.00 x 135.9 x coil mm</v>
       </c>
-      <c r="B159" t="str" xml:space="preserve">
+      <c r="B160" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Coil, 2B,
 1.00 x 135.9 x coil mm
 Weight (Kg):538
 Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-2,075.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="160" xml:space="preserve">
-      <c r="A160" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Coil, 2B,
-1.40 x 101.0 x coil mm</v>
-      </c>
-      <c r="B160" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Coil, 2B,
-1.40 x 101.0 x coil mm
-Weight (Kg):504
-Quality:Prime
 Help
 Location:FABRICA ALGECIRAS
 2,075.00 €/ton
@@ -2970,9 +2969,25 @@
     <row r="162" xml:space="preserve">
       <c r="A162" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Coil, 2B,
+1.40 x 101.0 x coil mm</v>
+      </c>
+      <c r="B162" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Coil, 2B,
+1.40 x 101.0 x coil mm
+Weight (Kg):504
+Quality:Prime
+Help
+Location:FABRICA ALGECIRAS
+2,075.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="163" xml:space="preserve">
+      <c r="A163" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Coil, 2B,
 1.40 x 105.0 x coil mm</v>
       </c>
-      <c r="B162" t="str" xml:space="preserve">
+      <c r="B163" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Coil, 2B,
 1.40 x 105.0 x coil mm
 Weight (Kg):530
@@ -2983,12 +2998,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="163" xml:space="preserve">
-      <c r="A163" t="str" xml:space="preserve">
+    <row r="164" xml:space="preserve">
+      <c r="A164" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Coil, 2B,
 1.40 x 110.9 x coil mm</v>
       </c>
-      <c r="B163" t="str" xml:space="preserve">
+      <c r="B164" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Coil, 2B,
 1.40 x 110.9 x coil mm
 Weight (Kg):616
@@ -2999,12 +3014,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="164" xml:space="preserve">
-      <c r="A164" t="str" xml:space="preserve">
+    <row r="165" xml:space="preserve">
+      <c r="A165" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Coil, 2B,
 1.50 x 1289.0 x coil mm</v>
       </c>
-      <c r="B164" t="str" xml:space="preserve">
+      <c r="B165" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Coil, 2B,
 1.50 x 1289.0 x coil mm
 Weight (Kg):3,070
@@ -3015,12 +3030,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="165" xml:space="preserve">
-      <c r="A165" t="str" xml:space="preserve">
+    <row r="166" xml:space="preserve">
+      <c r="A166" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Coil, 2B,
 1.50 x 200.9 x coil mm</v>
       </c>
-      <c r="B165" t="str" xml:space="preserve">
+      <c r="B166" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Coil, 2B,
 1.50 x 200.9 x coil mm
 Weight (Kg):964
@@ -3031,12 +3046,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="166" xml:space="preserve">
-      <c r="A166" t="str" xml:space="preserve">
+    <row r="167" xml:space="preserve">
+      <c r="A167" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Coil, 2B,
 1.50 x 230.9 x coil mm</v>
       </c>
-      <c r="B166" t="str" xml:space="preserve">
+      <c r="B167" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Coil, 2B,
 1.50 x 230.9 x coil mm
 Weight (Kg):4,140
@@ -3047,12 +3062,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="167" xml:space="preserve">
-      <c r="A167" t="str" xml:space="preserve">
+    <row r="168" xml:space="preserve">
+      <c r="A168" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Coil, 2B,
 1.80 x 102.0 x coil mm</v>
       </c>
-      <c r="B167" t="str" xml:space="preserve">
+      <c r="B168" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Coil, 2B,
 1.80 x 102.0 x coil mm
 Weight (Kg):794
@@ -3063,12 +3078,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="168" xml:space="preserve">
-      <c r="A168" t="str" xml:space="preserve">
+    <row r="169" xml:space="preserve">
+      <c r="A169" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Coil, 2B,
 2.00 x 1277.0 x coil mm</v>
       </c>
-      <c r="B168" t="str" xml:space="preserve">
+      <c r="B169" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Coil, 2B,
 2.00 x 1277.0 x coil mm
 Weight (Kg):2,940
@@ -3076,22 +3091,6 @@
 Help
 Location:FABRICA ALGECIRAS
 2,225.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="169" xml:space="preserve">
-      <c r="A169" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Coil, 2B,
-2.00 x 553.0 x coil mm</v>
-      </c>
-      <c r="B169" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Coil, 2B,
-2.00 x 553.0 x coil mm
-Weight (Kg):385
-Quality:Downgraded
-Help
-Location:FABRICA ALGECIRAS
-2,025.00 €/ton
 Add to cart</v>
       </c>
     </row>
@@ -3114,9 +3113,25 @@
     <row r="171" xml:space="preserve">
       <c r="A171" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Coil, 2B,
+2.00 x 553.0 x coil mm</v>
+      </c>
+      <c r="B171" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Coil, 2B,
+2.00 x 553.0 x coil mm
+Weight (Kg):385
+Quality:Downgraded
+Help
+Location:FABRICA ALGECIRAS
+2,025.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="172" xml:space="preserve">
+      <c r="A172" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Coil, 2B,
 2.50 x 1000.0 x coil mm</v>
       </c>
-      <c r="B171" t="str" xml:space="preserve">
+      <c r="B172" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Coil, 2B,
 2.50 x 1000.0 x coil mm
 Weight (Kg):2,280
@@ -3127,31 +3142,15 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="172" xml:space="preserve">
-      <c r="A172" t="str" xml:space="preserve">
+    <row r="173" xml:space="preserve">
+      <c r="A173" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Coil, 2B,
 5.00 x 265.9 x coil mm</v>
       </c>
-      <c r="B172" t="str" xml:space="preserve">
+      <c r="B173" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Coil, 2B,
 5.00 x 265.9 x coil mm
 Weight (Kg):1,596
-Quality:Prime
-Help
-Location:FABRICA ALGECIRAS
-2,075.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="173" xml:space="preserve">
-      <c r="A173" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Coil, 2B,
-5.00 x 286.0 x coil mm</v>
-      </c>
-      <c r="B173" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Coil, 2B,
-5.00 x 286.0 x coil mm
-Weight (Kg):2,451
 Quality:Prime
 Help
 Location:FABRICA ALGECIRAS
@@ -3168,7 +3167,7 @@
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Coil, 2B,
 5.00 x 286.0 x coil mm
 Weight (Kg):2,451
-Quality:Prime-2
+Quality:Prime
 Help
 Location:FABRICA ALGECIRAS
 2,075.00 €/ton
@@ -3178,16 +3177,16 @@
     <row r="175" xml:space="preserve">
       <c r="A175" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Coil, 2B,
-6.00 x 1500.0 x coil mm</v>
+5.00 x 286.0 x coil mm</v>
       </c>
       <c r="B175" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Coil, 2B,
-6.00 x 1500.0 x coil mm
-Weight (Kg):1,700
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-2,225.00 €/ton
+5.00 x 286.0 x coil mm
+Weight (Kg):2,451
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,075.00 €/ton
 Add to cart</v>
       </c>
     </row>
@@ -3199,7 +3198,7 @@
       <c r="B176" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Coil, 2B,
 6.00 x 1500.0 x coil mm
-Weight (Kg):2,355
+Weight (Kg):1,700
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -3215,7 +3214,7 @@
       <c r="B177" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Coil, 2B,
 6.00 x 1500.0 x coil mm
-Weight (Kg):2,375
+Weight (Kg):2,355
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -3231,7 +3230,7 @@
       <c r="B178" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Coil, 2B,
 6.00 x 1500.0 x coil mm
-Weight (Kg):2,204
+Weight (Kg):2,375
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -3263,7 +3262,7 @@
       <c r="B180" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Coil, 2B,
 6.00 x 1500.0 x coil mm
-Weight (Kg):2,844
+Weight (Kg):2,204
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -3274,9 +3273,25 @@
     <row r="181" xml:space="preserve">
       <c r="A181" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Coil, 2B,
+6.00 x 1500.0 x coil mm</v>
+      </c>
+      <c r="B181" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Coil, 2B,
+6.00 x 1500.0 x coil mm
+Weight (Kg):2,844
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,225.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="182" xml:space="preserve">
+      <c r="A182" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Coil, 2B,
 6.00 x 220.0 x coil mm</v>
       </c>
-      <c r="B181" t="str" xml:space="preserve">
+      <c r="B182" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Coil, 2B,
 6.00 x 220.0 x coil mm
 Weight (Kg):4,046
@@ -3287,12 +3302,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="182" xml:space="preserve">
-      <c r="A182" t="str" xml:space="preserve">
+    <row r="183" xml:space="preserve">
+      <c r="A183" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Coil, 2B,
 6.00 x 250.0 x coil mm</v>
       </c>
-      <c r="B182" t="str" xml:space="preserve">
+      <c r="B183" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Coil, 2B,
 6.00 x 250.0 x coil mm
 Weight (Kg):3,086
@@ -3303,12 +3318,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="183" xml:space="preserve">
-      <c r="A183" t="str" xml:space="preserve">
+    <row r="184" xml:space="preserve">
+      <c r="A184" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Coil, BA,
 0.70 x 1268.0 x coil mm</v>
       </c>
-      <c r="B183" t="str" xml:space="preserve">
+      <c r="B184" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Coil, BA,
 0.70 x 1268.0 x coil mm
 Weight (Kg):20,010
@@ -3319,12 +3334,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="184" xml:space="preserve">
-      <c r="A184" t="str" xml:space="preserve">
+    <row r="185" xml:space="preserve">
+      <c r="A185" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Coil, Emboss Skin,
 0.50 x 1250.0 x coil mm</v>
       </c>
-      <c r="B184" t="str" xml:space="preserve">
+      <c r="B185" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Coil, Emboss Skin,
 0.50 x 1250.0 x coil mm
 Weight (Kg):3,950
@@ -3335,12 +3350,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="185" xml:space="preserve">
-      <c r="A185" t="str" xml:space="preserve">
+    <row r="186" xml:space="preserve">
+      <c r="A186" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Coil, Emboss Skin,
 0.50 x 1261.0 x coil mm</v>
       </c>
-      <c r="B185" t="str" xml:space="preserve">
+      <c r="B186" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Coil, Emboss Skin,
 0.50 x 1261.0 x coil mm
 Weight (Kg):10,590
@@ -3351,12 +3366,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="186" xml:space="preserve">
-      <c r="A186" t="str" xml:space="preserve">
+    <row r="187" xml:space="preserve">
+      <c r="A187" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Coil, Nb. 1,
 4.70 x 220.0 x coil mm</v>
       </c>
-      <c r="B186" t="str" xml:space="preserve">
+      <c r="B187" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Coil, Nb. 1,
 4.70 x 220.0 x coil mm
 Weight (Kg):3,704
@@ -3364,22 +3379,6 @@
 Help
 Location:FABRICA ALGECIRAS
 1,975.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="187" xml:space="preserve">
-      <c r="A187" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Coil, Nb. 1,
-8.00 x 1500.0 x coil mm</v>
-      </c>
-      <c r="B187" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Coil, Nb. 1,
-8.00 x 1500.0 x coil mm
-Weight (Kg):4,076
-Quality:Prime
-Help
-Location:FABRICA ALGECIRAS
-2,325.00 €/ton
 Add to cart</v>
       </c>
     </row>
@@ -3391,7 +3390,7 @@
       <c r="B188" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Coil, Nb. 1,
 8.00 x 1500.0 x coil mm
-Weight (Kg):2,749
+Weight (Kg):4,076
 Quality:Prime
 Help
 Location:FABRICA ALGECIRAS
@@ -3401,10 +3400,26 @@
     </row>
     <row r="189" xml:space="preserve">
       <c r="A189" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Coil, Nb. 1,
+8.00 x 1500.0 x coil mm</v>
+      </c>
+      <c r="B189" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Coil, Nb. 1,
+8.00 x 1500.0 x coil mm
+Weight (Kg):2,749
+Quality:Prime
+Help
+Location:FABRICA ALGECIRAS
+2,325.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="190" xml:space="preserve">
+      <c r="A190" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Coil, Nb. 2 Chequered,
 6.00 x 1250.0 x coil mm</v>
       </c>
-      <c r="B189" t="str" xml:space="preserve">
+      <c r="B190" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Coil, Nb. 2 Chequered,
 6.00 x 1250.0 x coil mm
 Weight (Kg):19,244
@@ -3415,12 +3430,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="190" xml:space="preserve">
-      <c r="A190" t="str" xml:space="preserve">
+    <row r="191" xml:space="preserve">
+      <c r="A191" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Coil, Nb. 3 Chequered,
 4.00 x 1548.0 x coil mm</v>
       </c>
-      <c r="B190" t="str" xml:space="preserve">
+      <c r="B191" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Coil, Nb. 3 Chequered,
 4.00 x 1548.0 x coil mm
 Weight (Kg):3,000
@@ -3431,12 +3446,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="191" xml:space="preserve">
-      <c r="A191" t="str" xml:space="preserve">
+    <row r="192" xml:space="preserve">
+      <c r="A192" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Coil, Polished N4-G-180,
 0.90 x 190.0 x coil mm</v>
       </c>
-      <c r="B191" t="str" xml:space="preserve">
+      <c r="B192" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Coil, Polished N4-G-180,
 0.90 x 190.0 x coil mm
 Weight (Kg):1,424
@@ -3447,12 +3462,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="192" xml:space="preserve">
-      <c r="A192" t="str" xml:space="preserve">
+    <row r="193" xml:space="preserve">
+      <c r="A193" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Coil, Polished N4-G-180,
 0.90 x 205.9 x coil mm</v>
       </c>
-      <c r="B192" t="str" xml:space="preserve">
+      <c r="B193" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Coil, Polished N4-G-180,
 0.90 x 205.9 x coil mm
 Weight (Kg):802
@@ -3463,12 +3478,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="193" xml:space="preserve">
-      <c r="A193" t="str" xml:space="preserve">
+    <row r="194" xml:space="preserve">
+      <c r="A194" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Coil, SB-G-400,
 1.00 x 154.9 x coil mm</v>
       </c>
-      <c r="B193" t="str" xml:space="preserve">
+      <c r="B194" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Coil, SB-G-400,
 1.00 x 154.9 x coil mm
 Weight (Kg):1,152
@@ -3479,12 +3494,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="194" xml:space="preserve">
-      <c r="A194" t="str" xml:space="preserve">
+    <row r="195" xml:space="preserve">
+      <c r="A195" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Coil, SB-G-500,
 0.90 x 1250.0 x coil mm</v>
       </c>
-      <c r="B194" t="str" xml:space="preserve">
+      <c r="B195" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Coil, SB-G-500,
 0.90 x 1250.0 x coil mm
 Weight (Kg):2,329
@@ -3495,12 +3510,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="195" xml:space="preserve">
-      <c r="A195" t="str" xml:space="preserve">
+    <row r="196" xml:space="preserve">
+      <c r="A196" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 0.70 x 1500.0 x 3000.0 mm</v>
       </c>
-      <c r="B195" t="str" xml:space="preserve">
+      <c r="B196" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 0.70 x 1500.0 x 3000.0 mm
 Weight (Kg):612
@@ -3511,12 +3526,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="196" xml:space="preserve">
-      <c r="A196" t="str" xml:space="preserve">
+    <row r="197" xml:space="preserve">
+      <c r="A197" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 0.70 x 1500.0 x 3000.0 mm</v>
       </c>
-      <c r="B196" t="str" xml:space="preserve">
+      <c r="B197" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 0.70 x 1500.0 x 3000.0 mm
 Weight (Kg):702
@@ -3527,31 +3542,15 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="197" xml:space="preserve">
-      <c r="A197" t="str" xml:space="preserve">
+    <row r="198" xml:space="preserve">
+      <c r="A198" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 0.80 x 1000.0 x 2000.0 mm</v>
       </c>
-      <c r="B197" t="str" xml:space="preserve">
+      <c r="B198" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 0.80 x 1000.0 x 2000.0 mm
 Weight (Kg):580
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-2,225.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="198" xml:space="preserve">
-      <c r="A198" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
-1.00 x 1500.0 x 3000.0 mm</v>
-      </c>
-      <c r="B198" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
-1.00 x 1500.0 x 3000.0 mm
-Weight (Kg):959
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -3615,7 +3614,7 @@
       <c r="B202" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 1.00 x 1500.0 x 3000.0 mm
-Weight (Kg):794
+Weight (Kg):959
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -3631,7 +3630,7 @@
       <c r="B203" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 1.00 x 1500.0 x 3000.0 mm
-Weight (Kg):659
+Weight (Kg):794
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -3647,7 +3646,7 @@
       <c r="B204" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 1.00 x 1500.0 x 3000.0 mm
-Weight (Kg):1,508
+Weight (Kg):659
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -3663,7 +3662,7 @@
       <c r="B205" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 1.00 x 1500.0 x 3000.0 mm
-Weight (Kg):1,921
+Weight (Kg):1,508
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -3679,7 +3678,7 @@
       <c r="B206" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 1.00 x 1500.0 x 3000.0 mm
-Weight (Kg):894
+Weight (Kg):1,921
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -3695,7 +3694,7 @@
       <c r="B207" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 1.00 x 1500.0 x 3000.0 mm
-Weight (Kg):700
+Weight (Kg):894
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -3711,7 +3710,7 @@
       <c r="B208" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 1.00 x 1500.0 x 3000.0 mm
-Weight (Kg):842
+Weight (Kg):700
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -3722,9 +3721,25 @@
     <row r="209" xml:space="preserve">
       <c r="A209" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
+1.00 x 1500.0 x 3000.0 mm</v>
+      </c>
+      <c r="B209" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
+1.00 x 1500.0 x 3000.0 mm
+Weight (Kg):842
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,225.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="210" xml:space="preserve">
+      <c r="A210" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 2.00 x 1000.0 x 2000.0 mm</v>
       </c>
-      <c r="B209" t="str" xml:space="preserve">
+      <c r="B210" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 2.00 x 1000.0 x 2000.0 mm
 Weight (Kg):512
@@ -3735,12 +3750,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="210" xml:space="preserve">
-      <c r="A210" t="str" xml:space="preserve">
+    <row r="211" xml:space="preserve">
+      <c r="A211" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 2.00 x 1000.0 x 2000.0 mm</v>
       </c>
-      <c r="B210" t="str" xml:space="preserve">
+      <c r="B211" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 2.00 x 1000.0 x 2000.0 mm
 Weight (Kg):949
@@ -3751,12 +3766,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="211" xml:space="preserve">
-      <c r="A211" t="str" xml:space="preserve">
+    <row r="212" xml:space="preserve">
+      <c r="A212" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 2.00 x 1250.0 x 2500.0 mm</v>
       </c>
-      <c r="B211" t="str" xml:space="preserve">
+      <c r="B212" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 2.00 x 1250.0 x 2500.0 mm
 Weight (Kg):735
@@ -3767,12 +3782,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="212" xml:space="preserve">
-      <c r="A212" t="str" xml:space="preserve">
+    <row r="213" xml:space="preserve">
+      <c r="A213" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 2.00 x 1250.0 x 2500.0 mm</v>
       </c>
-      <c r="B212" t="str" xml:space="preserve">
+      <c r="B213" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 2.00 x 1250.0 x 2500.0 mm
 Weight (Kg):805
@@ -3783,12 +3798,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="213" xml:space="preserve">
-      <c r="A213" t="str" xml:space="preserve">
+    <row r="214" xml:space="preserve">
+      <c r="A214" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 2.00 x 1250.0 x 2500.0 mm</v>
       </c>
-      <c r="B213" t="str" xml:space="preserve">
+      <c r="B214" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 2.00 x 1250.0 x 2500.0 mm
 Weight (Kg):777
@@ -3799,12 +3814,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="214" xml:space="preserve">
-      <c r="A214" t="str" xml:space="preserve">
+    <row r="215" xml:space="preserve">
+      <c r="A215" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 2.00 x 1250.0 x 2500.0 mm</v>
       </c>
-      <c r="B214" t="str" xml:space="preserve">
+      <c r="B215" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 2.00 x 1250.0 x 2500.0 mm
 Weight (Kg):576
@@ -3815,12 +3830,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="215" xml:space="preserve">
-      <c r="A215" t="str" xml:space="preserve">
+    <row r="216" xml:space="preserve">
+      <c r="A216" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 2.00 x 1250.0 x 2500.0 mm</v>
       </c>
-      <c r="B215" t="str" xml:space="preserve">
+      <c r="B216" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 2.00 x 1250.0 x 2500.0 mm
 Weight (Kg):622
@@ -3831,12 +3846,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="216" xml:space="preserve">
-      <c r="A216" t="str" xml:space="preserve">
+    <row r="217" xml:space="preserve">
+      <c r="A217" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 2.00 x 1250.0 x 2500.0 mm</v>
       </c>
-      <c r="B216" t="str" xml:space="preserve">
+      <c r="B217" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 2.00 x 1250.0 x 2500.0 mm
 Weight (Kg):862
@@ -3847,12 +3862,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="217" xml:space="preserve">
-      <c r="A217" t="str" xml:space="preserve">
+    <row r="218" xml:space="preserve">
+      <c r="A218" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 2.00 x 1250.0 x 2500.0 mm</v>
       </c>
-      <c r="B217" t="str" xml:space="preserve">
+      <c r="B218" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 2.00 x 1250.0 x 2500.0 mm
 Weight (Kg):619
@@ -3863,12 +3878,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="218" xml:space="preserve">
-      <c r="A218" t="str" xml:space="preserve">
+    <row r="219" xml:space="preserve">
+      <c r="A219" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 2.00 x 1250.0 x 2500.0 mm</v>
       </c>
-      <c r="B218" t="str" xml:space="preserve">
+      <c r="B219" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 2.00 x 1250.0 x 2500.0 mm
 Weight (Kg):867
@@ -3879,12 +3894,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="219" xml:space="preserve">
-      <c r="A219" t="str" xml:space="preserve">
+    <row r="220" xml:space="preserve">
+      <c r="A220" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 2.00 x 1250.0 x 2500.0 mm</v>
       </c>
-      <c r="B219" t="str" xml:space="preserve">
+      <c r="B220" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 2.00 x 1250.0 x 2500.0 mm
 Weight (Kg):774
@@ -3895,12 +3910,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="220" xml:space="preserve">
-      <c r="A220" t="str" xml:space="preserve">
+    <row r="221" xml:space="preserve">
+      <c r="A221" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 2.00 x 1250.0 x 3000.0 mm</v>
       </c>
-      <c r="B220" t="str" xml:space="preserve">
+      <c r="B221" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 2.00 x 1250.0 x 3000.0 mm
 Weight (Kg):877
@@ -3911,12 +3926,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="221" xml:space="preserve">
-      <c r="A221" t="str" xml:space="preserve">
+    <row r="222" xml:space="preserve">
+      <c r="A222" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 2.50 x 1000.0 x 2000.0 mm</v>
       </c>
-      <c r="B221" t="str" xml:space="preserve">
+      <c r="B222" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 2.50 x 1000.0 x 2000.0 mm
 Weight (Kg):781
@@ -3927,12 +3942,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="222" xml:space="preserve">
-      <c r="A222" t="str" xml:space="preserve">
+    <row r="223" xml:space="preserve">
+      <c r="A223" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 2.50 x 1000.0 x 2000.0 mm</v>
       </c>
-      <c r="B222" t="str" xml:space="preserve">
+      <c r="B223" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 2.50 x 1000.0 x 2000.0 mm
 Weight (Kg):590
@@ -3943,12 +3958,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="223" xml:space="preserve">
-      <c r="A223" t="str" xml:space="preserve">
+    <row r="224" xml:space="preserve">
+      <c r="A224" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 2.50 x 1250.0 x 2500.0 mm</v>
       </c>
-      <c r="B223" t="str" xml:space="preserve">
+      <c r="B224" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 2.50 x 1250.0 x 2500.0 mm
 Weight (Kg):660
@@ -3959,12 +3974,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="224" xml:space="preserve">
-      <c r="A224" t="str" xml:space="preserve">
+    <row r="225" xml:space="preserve">
+      <c r="A225" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 2.50 x 1250.0 x 2500.0 mm</v>
       </c>
-      <c r="B224" t="str" xml:space="preserve">
+      <c r="B225" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 2.50 x 1250.0 x 2500.0 mm
 Weight (Kg):852
@@ -3975,12 +3990,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="225" xml:space="preserve">
-      <c r="A225" t="str" xml:space="preserve">
+    <row r="226" xml:space="preserve">
+      <c r="A226" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 2.50 x 1500.0 x 3000.0 mm</v>
       </c>
-      <c r="B225" t="str" xml:space="preserve">
+      <c r="B226" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 2.50 x 1500.0 x 3000.0 mm
 Weight (Kg):792
@@ -3991,12 +4006,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="226" xml:space="preserve">
-      <c r="A226" t="str" xml:space="preserve">
+    <row r="227" xml:space="preserve">
+      <c r="A227" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 2.50 x 1500.0 x 3000.0 mm</v>
       </c>
-      <c r="B226" t="str" xml:space="preserve">
+      <c r="B227" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 2.50 x 1500.0 x 3000.0 mm
 Weight (Kg):1,390
@@ -4007,12 +4022,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="227" xml:space="preserve">
-      <c r="A227" t="str" xml:space="preserve">
+    <row r="228" xml:space="preserve">
+      <c r="A228" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 2.50 x 1500.0 x 3000.0 mm</v>
       </c>
-      <c r="B227" t="str" xml:space="preserve">
+      <c r="B228" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 2.50 x 1500.0 x 3000.0 mm
 Weight (Kg):1,224
@@ -4023,12 +4038,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="228" xml:space="preserve">
-      <c r="A228" t="str" xml:space="preserve">
+    <row r="229" xml:space="preserve">
+      <c r="A229" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 2.50 x 1500.0 x 3000.0 mm</v>
       </c>
-      <c r="B228" t="str" xml:space="preserve">
+      <c r="B229" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 2.50 x 1500.0 x 3000.0 mm
 Weight (Kg):2,098
@@ -4039,12 +4054,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="229" xml:space="preserve">
-      <c r="A229" t="str" xml:space="preserve">
+    <row r="230" xml:space="preserve">
+      <c r="A230" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 2.50 x 1500.0 x 3000.0 mm</v>
       </c>
-      <c r="B229" t="str" xml:space="preserve">
+      <c r="B230" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 2.50 x 1500.0 x 3000.0 mm
 Weight (Kg):1,238
@@ -4055,12 +4070,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="230" xml:space="preserve">
-      <c r="A230" t="str" xml:space="preserve">
+    <row r="231" xml:space="preserve">
+      <c r="A231" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 2.50 x 1500.0 x 3000.0 mm</v>
       </c>
-      <c r="B230" t="str" xml:space="preserve">
+      <c r="B231" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 2.50 x 1500.0 x 3000.0 mm
 Weight (Kg):856
@@ -4071,12 +4086,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="231" xml:space="preserve">
-      <c r="A231" t="str" xml:space="preserve">
+    <row r="232" xml:space="preserve">
+      <c r="A232" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 2.50 x 1500.0 x 3000.0 mm</v>
       </c>
-      <c r="B231" t="str" xml:space="preserve">
+      <c r="B232" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 2.50 x 1500.0 x 3000.0 mm
 Weight (Kg):605
@@ -4087,12 +4102,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="232" xml:space="preserve">
-      <c r="A232" t="str" xml:space="preserve">
+    <row r="233" xml:space="preserve">
+      <c r="A233" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 2.50 x 1500.0 x 3000.0 mm</v>
       </c>
-      <c r="B232" t="str" xml:space="preserve">
+      <c r="B233" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 2.50 x 1500.0 x 3000.0 mm
 Weight (Kg):521
@@ -4103,12 +4118,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="233" xml:space="preserve">
-      <c r="A233" t="str" xml:space="preserve">
+    <row r="234" xml:space="preserve">
+      <c r="A234" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 2.50 x 1500.0 x 3000.0 mm</v>
       </c>
-      <c r="B233" t="str" xml:space="preserve">
+      <c r="B234" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 2.50 x 1500.0 x 3000.0 mm
 Weight (Kg):527
@@ -4119,12 +4134,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="234" xml:space="preserve">
-      <c r="A234" t="str" xml:space="preserve">
+    <row r="235" xml:space="preserve">
+      <c r="A235" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 2.50 x 1500.0 x 3000.0 mm</v>
       </c>
-      <c r="B234" t="str" xml:space="preserve">
+      <c r="B235" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 2.50 x 1500.0 x 3000.0 mm
 Weight (Kg):862
@@ -4135,12 +4150,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="235" xml:space="preserve">
-      <c r="A235" t="str" xml:space="preserve">
+    <row r="236" xml:space="preserve">
+      <c r="A236" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 3.00 x 1000.0 x 2000.0 mm</v>
       </c>
-      <c r="B235" t="str" xml:space="preserve">
+      <c r="B236" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 3.00 x 1000.0 x 2000.0 mm
 Weight (Kg):992
@@ -4151,12 +4166,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="236" xml:space="preserve">
-      <c r="A236" t="str" xml:space="preserve">
+    <row r="237" xml:space="preserve">
+      <c r="A237" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 3.00 x 1000.0 x 2000.0 mm</v>
       </c>
-      <c r="B236" t="str" xml:space="preserve">
+      <c r="B237" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 3.00 x 1000.0 x 2000.0 mm
 Weight (Kg):1,038
@@ -4167,12 +4182,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="237" xml:space="preserve">
-      <c r="A237" t="str" xml:space="preserve">
+    <row r="238" xml:space="preserve">
+      <c r="A238" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 3.00 x 1000.0 x 2000.0 mm</v>
       </c>
-      <c r="B237" t="str" xml:space="preserve">
+      <c r="B238" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 3.00 x 1000.0 x 2000.0 mm
 Weight (Kg):946
@@ -4183,12 +4198,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="238" xml:space="preserve">
-      <c r="A238" t="str" xml:space="preserve">
+    <row r="239" xml:space="preserve">
+      <c r="A239" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 3.00 x 1000.0 x 2000.0 mm</v>
       </c>
-      <c r="B238" t="str" xml:space="preserve">
+      <c r="B239" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 3.00 x 1000.0 x 2000.0 mm
 Weight (Kg):503
@@ -4199,12 +4214,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="239" xml:space="preserve">
-      <c r="A239" t="str" xml:space="preserve">
+    <row r="240" xml:space="preserve">
+      <c r="A240" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 3.00 x 1000.0 x 2000.0 mm</v>
       </c>
-      <c r="B239" t="str" xml:space="preserve">
+      <c r="B240" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 3.00 x 1000.0 x 2000.0 mm
 Weight (Kg):880
@@ -4215,12 +4230,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="240" xml:space="preserve">
-      <c r="A240" t="str" xml:space="preserve">
+    <row r="241" xml:space="preserve">
+      <c r="A241" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 3.00 x 1000.0 x 2000.0 mm</v>
       </c>
-      <c r="B240" t="str" xml:space="preserve">
+      <c r="B241" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 3.00 x 1000.0 x 2000.0 mm
 Weight (Kg):796
@@ -4231,12 +4246,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="241" xml:space="preserve">
-      <c r="A241" t="str" xml:space="preserve">
+    <row r="242" xml:space="preserve">
+      <c r="A242" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 3.00 x 1000.0 x 2000.0 mm</v>
       </c>
-      <c r="B241" t="str" xml:space="preserve">
+      <c r="B242" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 3.00 x 1000.0 x 2000.0 mm
 Weight (Kg):578
@@ -4247,12 +4262,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="242" xml:space="preserve">
-      <c r="A242" t="str" xml:space="preserve">
+    <row r="243" xml:space="preserve">
+      <c r="A243" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 3.00 x 1000.0 x 2000.0 mm</v>
       </c>
-      <c r="B242" t="str" xml:space="preserve">
+      <c r="B243" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 3.00 x 1000.0 x 2000.0 mm
 Weight (Kg):1,506
@@ -4263,12 +4278,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="243" xml:space="preserve">
-      <c r="A243" t="str" xml:space="preserve">
+    <row r="244" xml:space="preserve">
+      <c r="A244" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 3.00 x 1000.0 x 2000.0 mm</v>
       </c>
-      <c r="B243" t="str" xml:space="preserve">
+      <c r="B244" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 3.00 x 1000.0 x 2000.0 mm
 Weight (Kg):1,538
@@ -4279,12 +4294,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="244" xml:space="preserve">
-      <c r="A244" t="str" xml:space="preserve">
+    <row r="245" xml:space="preserve">
+      <c r="A245" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 3.00 x 1000.0 x 2000.0 mm</v>
       </c>
-      <c r="B244" t="str" xml:space="preserve">
+      <c r="B245" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 3.00 x 1000.0 x 2000.0 mm
 Weight (Kg):520
@@ -4295,12 +4310,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="245" xml:space="preserve">
-      <c r="A245" t="str" xml:space="preserve">
+    <row r="246" xml:space="preserve">
+      <c r="A246" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 3.00 x 1250.0 x 2500.0 mm</v>
       </c>
-      <c r="B245" t="str" xml:space="preserve">
+      <c r="B246" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 3.00 x 1250.0 x 2500.0 mm
 Weight (Kg):886
@@ -4311,12 +4326,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="246" xml:space="preserve">
-      <c r="A246" t="str" xml:space="preserve">
+    <row r="247" xml:space="preserve">
+      <c r="A247" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 3.00 x 1250.0 x 2500.0 mm</v>
       </c>
-      <c r="B246" t="str" xml:space="preserve">
+      <c r="B247" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 3.00 x 1250.0 x 2500.0 mm
 Weight (Kg):1,233
@@ -4327,12 +4342,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="247" xml:space="preserve">
-      <c r="A247" t="str" xml:space="preserve">
+    <row r="248" xml:space="preserve">
+      <c r="A248" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 3.00 x 1250.0 x 2500.0 mm</v>
       </c>
-      <c r="B247" t="str" xml:space="preserve">
+      <c r="B248" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 3.00 x 1250.0 x 2500.0 mm
 Weight (Kg):742
@@ -4343,12 +4358,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="248" xml:space="preserve">
-      <c r="A248" t="str" xml:space="preserve">
+    <row r="249" xml:space="preserve">
+      <c r="A249" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 3.00 x 1250.0 x 2500.0 mm</v>
       </c>
-      <c r="B248" t="str" xml:space="preserve">
+      <c r="B249" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 3.00 x 1250.0 x 2500.0 mm
 Weight (Kg):858
@@ -4359,12 +4374,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="249" xml:space="preserve">
-      <c r="A249" t="str" xml:space="preserve">
+    <row r="250" xml:space="preserve">
+      <c r="A250" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 3.00 x 1250.0 x 2500.0 mm</v>
       </c>
-      <c r="B249" t="str" xml:space="preserve">
+      <c r="B250" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 3.00 x 1250.0 x 2500.0 mm
 Weight (Kg):1,450
@@ -4375,12 +4390,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="250" xml:space="preserve">
-      <c r="A250" t="str" xml:space="preserve">
+    <row r="251" xml:space="preserve">
+      <c r="A251" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 3.00 x 1250.0 x 2500.0 mm</v>
       </c>
-      <c r="B250" t="str" xml:space="preserve">
+      <c r="B251" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 3.00 x 1250.0 x 2500.0 mm
 Weight (Kg):1,818
@@ -4391,12 +4406,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="251" xml:space="preserve">
-      <c r="A251" t="str" xml:space="preserve">
+    <row r="252" xml:space="preserve">
+      <c r="A252" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 3.00 x 1250.0 x 2500.0 mm</v>
       </c>
-      <c r="B251" t="str" xml:space="preserve">
+      <c r="B252" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 3.00 x 1250.0 x 2500.0 mm
 Weight (Kg):1,220
@@ -4407,12 +4422,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="252" xml:space="preserve">
-      <c r="A252" t="str" xml:space="preserve">
+    <row r="253" xml:space="preserve">
+      <c r="A253" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 3.00 x 1250.0 x 2500.0 mm</v>
       </c>
-      <c r="B252" t="str" xml:space="preserve">
+      <c r="B253" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 3.00 x 1250.0 x 2500.0 mm
 Weight (Kg):812
@@ -4423,12 +4438,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="253" xml:space="preserve">
-      <c r="A253" t="str" xml:space="preserve">
+    <row r="254" xml:space="preserve">
+      <c r="A254" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 3.00 x 1250.0 x 2500.0 mm</v>
       </c>
-      <c r="B253" t="str" xml:space="preserve">
+      <c r="B254" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 3.00 x 1250.0 x 2500.0 mm
 Weight (Kg):816
@@ -4439,12 +4454,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="254" xml:space="preserve">
-      <c r="A254" t="str" xml:space="preserve">
+    <row r="255" xml:space="preserve">
+      <c r="A255" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 3.00 x 1250.0 x 2500.0 mm</v>
       </c>
-      <c r="B254" t="str" xml:space="preserve">
+      <c r="B255" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 3.00 x 1250.0 x 2500.0 mm
 Weight (Kg):1,320
@@ -4455,12 +4470,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="255" xml:space="preserve">
-      <c r="A255" t="str" xml:space="preserve">
+    <row r="256" xml:space="preserve">
+      <c r="A256" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 3.00 x 1250.0 x 2500.0 mm</v>
       </c>
-      <c r="B255" t="str" xml:space="preserve">
+      <c r="B256" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 3.00 x 1250.0 x 2500.0 mm
 Weight (Kg):830
@@ -4471,12 +4486,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="256" xml:space="preserve">
-      <c r="A256" t="str" xml:space="preserve">
+    <row r="257" xml:space="preserve">
+      <c r="A257" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 3.00 x 1250.0 x 2500.0 mm</v>
       </c>
-      <c r="B256" t="str" xml:space="preserve">
+      <c r="B257" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 3.00 x 1250.0 x 2500.0 mm
 Weight (Kg):1,446
@@ -4487,12 +4502,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="257" xml:space="preserve">
-      <c r="A257" t="str" xml:space="preserve">
+    <row r="258" xml:space="preserve">
+      <c r="A258" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 3.00 x 1250.0 x 2500.0 mm</v>
       </c>
-      <c r="B257" t="str" xml:space="preserve">
+      <c r="B258" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 3.00 x 1250.0 x 2500.0 mm
 Weight (Kg):670
@@ -4503,12 +4518,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="258" xml:space="preserve">
-      <c r="A258" t="str" xml:space="preserve">
+    <row r="259" xml:space="preserve">
+      <c r="A259" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 3.00 x 1250.0 x 2500.0 mm</v>
       </c>
-      <c r="B258" t="str" xml:space="preserve">
+      <c r="B259" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 3.00 x 1250.0 x 2500.0 mm
 Weight (Kg):884
@@ -4519,12 +4534,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="259" xml:space="preserve">
-      <c r="A259" t="str" xml:space="preserve">
+    <row r="260" xml:space="preserve">
+      <c r="A260" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 3.00 x 1250.0 x 2500.0 mm</v>
       </c>
-      <c r="B259" t="str" xml:space="preserve">
+      <c r="B260" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 3.00 x 1250.0 x 2500.0 mm
 Weight (Kg):762
@@ -4535,12 +4550,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="260" xml:space="preserve">
-      <c r="A260" t="str" xml:space="preserve">
+    <row r="261" xml:space="preserve">
+      <c r="A261" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 3.00 x 1500.0 x 3000.0 mm</v>
       </c>
-      <c r="B260" t="str" xml:space="preserve">
+      <c r="B261" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 3.00 x 1500.0 x 3000.0 mm
 Weight (Kg):744
@@ -4551,12 +4566,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="261" xml:space="preserve">
-      <c r="A261" t="str" xml:space="preserve">
+    <row r="262" xml:space="preserve">
+      <c r="A262" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 3.00 x 1500.0 x 3000.0 mm</v>
       </c>
-      <c r="B261" t="str" xml:space="preserve">
+      <c r="B262" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 3.00 x 1500.0 x 3000.0 mm
 Weight (Kg):1,394
@@ -4567,12 +4582,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="262" xml:space="preserve">
-      <c r="A262" t="str" xml:space="preserve">
+    <row r="263" xml:space="preserve">
+      <c r="A263" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 3.00 x 1500.0 x 3000.0 mm</v>
       </c>
-      <c r="B262" t="str" xml:space="preserve">
+      <c r="B263" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 3.00 x 1500.0 x 3000.0 mm
 Weight (Kg):2,224
@@ -4583,12 +4598,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="263" xml:space="preserve">
-      <c r="A263" t="str" xml:space="preserve">
+    <row r="264" xml:space="preserve">
+      <c r="A264" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 3.00 x 1500.0 x 3000.0 mm</v>
       </c>
-      <c r="B263" t="str" xml:space="preserve">
+      <c r="B264" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 3.00 x 1500.0 x 3000.0 mm
 Weight (Kg):1,156
@@ -4599,12 +4614,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="264" xml:space="preserve">
-      <c r="A264" t="str" xml:space="preserve">
+    <row r="265" xml:space="preserve">
+      <c r="A265" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 3.00 x 1500.0 x 3000.0 mm</v>
       </c>
-      <c r="B264" t="str" xml:space="preserve">
+      <c r="B265" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 3.00 x 1500.0 x 3000.0 mm
 Weight (Kg):632
@@ -4615,12 +4630,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="265" xml:space="preserve">
-      <c r="A265" t="str" xml:space="preserve">
+    <row r="266" xml:space="preserve">
+      <c r="A266" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 3.00 x 1500.0 x 3000.0 mm</v>
       </c>
-      <c r="B265" t="str" xml:space="preserve">
+      <c r="B266" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 3.00 x 1500.0 x 3000.0 mm
 Weight (Kg):950
@@ -4631,12 +4646,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="266" xml:space="preserve">
-      <c r="A266" t="str" xml:space="preserve">
+    <row r="267" xml:space="preserve">
+      <c r="A267" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 3.00 x 1500.0 x 3000.0 mm</v>
       </c>
-      <c r="B266" t="str" xml:space="preserve">
+      <c r="B267" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 3.00 x 1500.0 x 3000.0 mm
 Weight (Kg):750
@@ -4647,12 +4662,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="267" xml:space="preserve">
-      <c r="A267" t="str" xml:space="preserve">
+    <row r="268" xml:space="preserve">
+      <c r="A268" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 3.00 x 1500.0 x 3000.0 mm</v>
       </c>
-      <c r="B267" t="str" xml:space="preserve">
+      <c r="B268" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 3.00 x 1500.0 x 3000.0 mm
 Weight (Kg):1,906
@@ -4663,12 +4678,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="268" xml:space="preserve">
-      <c r="A268" t="str" xml:space="preserve">
+    <row r="269" xml:space="preserve">
+      <c r="A269" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 3.00 x 1500.0 x 3000.0 mm</v>
       </c>
-      <c r="B268" t="str" xml:space="preserve">
+      <c r="B269" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 3.00 x 1500.0 x 3000.0 mm
 Weight (Kg):640
@@ -4679,12 +4694,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="269" xml:space="preserve">
-      <c r="A269" t="str" xml:space="preserve">
+    <row r="270" xml:space="preserve">
+      <c r="A270" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 3.00 x 1500.0 x 3000.0 mm</v>
       </c>
-      <c r="B269" t="str" xml:space="preserve">
+      <c r="B270" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 3.00 x 1500.0 x 3000.0 mm
 Weight (Kg):1,496
@@ -4695,12 +4710,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="270" xml:space="preserve">
-      <c r="A270" t="str" xml:space="preserve">
+    <row r="271" xml:space="preserve">
+      <c r="A271" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 4.00 x 1000.0 x 2000.0 mm</v>
       </c>
-      <c r="B270" t="str" xml:space="preserve">
+      <c r="B271" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 4.00 x 1000.0 x 2000.0 mm
 Weight (Kg):1,348
@@ -4711,12 +4726,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="271" xml:space="preserve">
-      <c r="A271" t="str" xml:space="preserve">
+    <row r="272" xml:space="preserve">
+      <c r="A272" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 4.00 x 1500.0 x 3000.0 mm</v>
       </c>
-      <c r="B271" t="str" xml:space="preserve">
+      <c r="B272" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 4.00 x 1500.0 x 3000.0 mm
 Weight (Kg):1,574
@@ -4727,12 +4742,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="272" xml:space="preserve">
-      <c r="A272" t="str" xml:space="preserve">
+    <row r="273" xml:space="preserve">
+      <c r="A273" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 4.00 x 1500.0 x 3000.0 mm</v>
       </c>
-      <c r="B272" t="str" xml:space="preserve">
+      <c r="B273" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 4.00 x 1500.0 x 3000.0 mm
 Weight (Kg):1,861
@@ -4743,12 +4758,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="273" xml:space="preserve">
-      <c r="A273" t="str" xml:space="preserve">
+    <row r="274" xml:space="preserve">
+      <c r="A274" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 4.00 x 1500.0 x 3000.0 mm</v>
       </c>
-      <c r="B273" t="str" xml:space="preserve">
+      <c r="B274" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 4.00 x 1500.0 x 3000.0 mm
 Weight (Kg):1,722
@@ -4759,12 +4774,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="274" xml:space="preserve">
-      <c r="A274" t="str" xml:space="preserve">
+    <row r="275" xml:space="preserve">
+      <c r="A275" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 4.00 x 1500.0 x 3000.0 mm</v>
       </c>
-      <c r="B274" t="str" xml:space="preserve">
+      <c r="B275" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 4.00 x 1500.0 x 3000.0 mm
 Weight (Kg):1,726
@@ -4775,12 +4790,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="275" xml:space="preserve">
-      <c r="A275" t="str" xml:space="preserve">
+    <row r="276" xml:space="preserve">
+      <c r="A276" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 4.00 x 1500.0 x 3000.0 mm</v>
       </c>
-      <c r="B275" t="str" xml:space="preserve">
+      <c r="B276" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 4.00 x 1500.0 x 3000.0 mm
 Weight (Kg):999
@@ -4791,12 +4806,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="276" xml:space="preserve">
-      <c r="A276" t="str" xml:space="preserve">
+    <row r="277" xml:space="preserve">
+      <c r="A277" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 4.00 x 1500.0 x 3000.0 mm</v>
       </c>
-      <c r="B276" t="str" xml:space="preserve">
+      <c r="B277" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 4.00 x 1500.0 x 3000.0 mm
 Weight (Kg):724
@@ -4807,12 +4822,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="277" xml:space="preserve">
-      <c r="A277" t="str" xml:space="preserve">
+    <row r="278" xml:space="preserve">
+      <c r="A278" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 4.00 x 1500.0 x 3000.0 mm</v>
       </c>
-      <c r="B277" t="str" xml:space="preserve">
+      <c r="B278" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 4.00 x 1500.0 x 3000.0 mm
 Weight (Kg):854
@@ -4823,12 +4838,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="278" xml:space="preserve">
-      <c r="A278" t="str" xml:space="preserve">
+    <row r="279" xml:space="preserve">
+      <c r="A279" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 4.00 x 1500.0 x 3000.0 mm</v>
       </c>
-      <c r="B278" t="str" xml:space="preserve">
+      <c r="B279" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 4.00 x 1500.0 x 3000.0 mm
 Weight (Kg):1,987
@@ -4839,12 +4854,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="279" xml:space="preserve">
-      <c r="A279" t="str" xml:space="preserve">
+    <row r="280" xml:space="preserve">
+      <c r="A280" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 4.00 x 1500.0 x 3000.0 mm</v>
       </c>
-      <c r="B279" t="str" xml:space="preserve">
+      <c r="B280" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 4.00 x 1500.0 x 3000.0 mm
 Weight (Kg):1,708
@@ -4855,12 +4870,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="280" xml:space="preserve">
-      <c r="A280" t="str" xml:space="preserve">
+    <row r="281" xml:space="preserve">
+      <c r="A281" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 4.00 x 1500.0 x 3000.0 mm</v>
       </c>
-      <c r="B280" t="str" xml:space="preserve">
+      <c r="B281" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 4.00 x 1500.0 x 3000.0 mm
 Weight (Kg):1,562
@@ -4871,12 +4886,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="281" xml:space="preserve">
-      <c r="A281" t="str" xml:space="preserve">
+    <row r="282" xml:space="preserve">
+      <c r="A282" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 5.00 x 1250.0 x 2500.0 mm</v>
       </c>
-      <c r="B281" t="str" xml:space="preserve">
+      <c r="B282" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 5.00 x 1250.0 x 2500.0 mm
 Weight (Kg):2,220
@@ -4887,12 +4902,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="282" xml:space="preserve">
-      <c r="A282" t="str" xml:space="preserve">
+    <row r="283" xml:space="preserve">
+      <c r="A283" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 5.00 x 1250.0 x 2500.0 mm</v>
       </c>
-      <c r="B282" t="str" xml:space="preserve">
+      <c r="B283" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 5.00 x 1250.0 x 2500.0 mm
 Weight (Kg):1,580
@@ -4903,12 +4918,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="283" xml:space="preserve">
-      <c r="A283" t="str" xml:space="preserve">
+    <row r="284" xml:space="preserve">
+      <c r="A284" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 5.00 x 1250.0 x 2500.0 mm</v>
       </c>
-      <c r="B283" t="str" xml:space="preserve">
+      <c r="B284" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 5.00 x 1250.0 x 2500.0 mm
 Weight (Kg):750
@@ -4919,12 +4934,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="284" xml:space="preserve">
-      <c r="A284" t="str" xml:space="preserve">
+    <row r="285" xml:space="preserve">
+      <c r="A285" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 5.00 x 1500.0 x 3000.0 mm</v>
       </c>
-      <c r="B284" t="str" xml:space="preserve">
+      <c r="B285" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 5.00 x 1500.0 x 3000.0 mm
 Weight (Kg):1,777
@@ -4935,12 +4950,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="285" xml:space="preserve">
-      <c r="A285" t="str" xml:space="preserve">
+    <row r="286" xml:space="preserve">
+      <c r="A286" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 5.00 x 1500.0 x 3000.0 mm</v>
       </c>
-      <c r="B285" t="str" xml:space="preserve">
+      <c r="B286" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 5.00 x 1500.0 x 3000.0 mm
 Weight (Kg):1,436
@@ -4951,12 +4966,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="286" xml:space="preserve">
-      <c r="A286" t="str" xml:space="preserve">
+    <row r="287" xml:space="preserve">
+      <c r="A287" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 5.00 x 1500.0 x 3000.0 mm</v>
       </c>
-      <c r="B286" t="str" xml:space="preserve">
+      <c r="B287" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 5.00 x 1500.0 x 3000.0 mm
 Weight (Kg):890
@@ -4967,12 +4982,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="287" xml:space="preserve">
-      <c r="A287" t="str" xml:space="preserve">
+    <row r="288" xml:space="preserve">
+      <c r="A288" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 5.00 x 1500.0 x 3000.0 mm</v>
       </c>
-      <c r="B287" t="str" xml:space="preserve">
+      <c r="B288" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 5.00 x 1500.0 x 3000.0 mm
 Weight (Kg):1,252
@@ -4983,12 +4998,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="288" xml:space="preserve">
-      <c r="A288" t="str" xml:space="preserve">
+    <row r="289" xml:space="preserve">
+      <c r="A289" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 5.00 x 1500.0 x 3000.0 mm</v>
       </c>
-      <c r="B288" t="str" xml:space="preserve">
+      <c r="B289" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 5.00 x 1500.0 x 3000.0 mm
 Weight (Kg):1,646
@@ -4999,12 +5014,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="289" xml:space="preserve">
-      <c r="A289" t="str" xml:space="preserve">
+    <row r="290" xml:space="preserve">
+      <c r="A290" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 5.00 x 1500.0 x 3000.0 mm</v>
       </c>
-      <c r="B289" t="str" xml:space="preserve">
+      <c r="B290" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 5.00 x 1500.0 x 3000.0 mm
 Weight (Kg):1,434
@@ -5015,12 +5030,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="290" xml:space="preserve">
-      <c r="A290" t="str" xml:space="preserve">
+    <row r="291" xml:space="preserve">
+      <c r="A291" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 5.00 x 1500.0 x 3000.0 mm</v>
       </c>
-      <c r="B290" t="str" xml:space="preserve">
+      <c r="B291" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 5.00 x 1500.0 x 3000.0 mm
 Weight (Kg):1,778
@@ -5031,12 +5046,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="291" xml:space="preserve">
-      <c r="A291" t="str" xml:space="preserve">
+    <row r="292" xml:space="preserve">
+      <c r="A292" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 5.00 x 1500.0 x 3000.0 mm</v>
       </c>
-      <c r="B291" t="str" xml:space="preserve">
+      <c r="B292" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 5.00 x 1500.0 x 3000.0 mm
 Weight (Kg):1,818
@@ -5047,12 +5062,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="292" xml:space="preserve">
-      <c r="A292" t="str" xml:space="preserve">
+    <row r="293" xml:space="preserve">
+      <c r="A293" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 5.00 x 1500.0 x 3000.0 mm</v>
       </c>
-      <c r="B292" t="str" xml:space="preserve">
+      <c r="B293" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 5.00 x 1500.0 x 3000.0 mm
 Weight (Kg):1,807
@@ -5063,12 +5078,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="293" xml:space="preserve">
-      <c r="A293" t="str" xml:space="preserve">
+    <row r="294" xml:space="preserve">
+      <c r="A294" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 5.00 x 1500.0 x 3000.0 mm</v>
       </c>
-      <c r="B293" t="str" xml:space="preserve">
+      <c r="B294" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 5.00 x 1500.0 x 3000.0 mm
 Weight (Kg):1,978
@@ -5079,12 +5094,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="294" xml:space="preserve">
-      <c r="A294" t="str" xml:space="preserve">
+    <row r="295" xml:space="preserve">
+      <c r="A295" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 5.00 x 1500.0 x 3000.0 mm</v>
       </c>
-      <c r="B294" t="str" xml:space="preserve">
+      <c r="B295" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 5.00 x 1500.0 x 3000.0 mm
 Weight (Kg):1,760
@@ -5095,12 +5110,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="295" xml:space="preserve">
-      <c r="A295" t="str" xml:space="preserve">
+    <row r="296" xml:space="preserve">
+      <c r="A296" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 5.00 x 1500.0 x 3000.0 mm</v>
       </c>
-      <c r="B295" t="str" xml:space="preserve">
+      <c r="B296" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 5.00 x 1500.0 x 3000.0 mm
 Weight (Kg):1,976
@@ -5111,12 +5126,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="296" xml:space="preserve">
-      <c r="A296" t="str" xml:space="preserve">
+    <row r="297" xml:space="preserve">
+      <c r="A297" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 5.00 x 1500.0 x 3000.0 mm</v>
       </c>
-      <c r="B296" t="str" xml:space="preserve">
+      <c r="B297" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 5.00 x 1500.0 x 3000.0 mm
 Weight (Kg):1,236
@@ -5127,12 +5142,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="297" xml:space="preserve">
-      <c r="A297" t="str" xml:space="preserve">
+    <row r="298" xml:space="preserve">
+      <c r="A298" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 5.00 x 1500.0 x 3000.0 mm</v>
       </c>
-      <c r="B297" t="str" xml:space="preserve">
+      <c r="B298" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 5.00 x 1500.0 x 3000.0 mm
 Weight (Kg):1,968
@@ -5143,12 +5158,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="298" xml:space="preserve">
-      <c r="A298" t="str" xml:space="preserve">
+    <row r="299" xml:space="preserve">
+      <c r="A299" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 5.00 x 1500.0 x 3000.0 mm</v>
       </c>
-      <c r="B298" t="str" xml:space="preserve">
+      <c r="B299" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 5.00 x 1500.0 x 3000.0 mm
 Weight (Kg):1,240
@@ -5159,12 +5174,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="299" xml:space="preserve">
-      <c r="A299" t="str" xml:space="preserve">
+    <row r="300" xml:space="preserve">
+      <c r="A300" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 5.00 x 1500.0 x 3000.0 mm</v>
       </c>
-      <c r="B299" t="str" xml:space="preserve">
+      <c r="B300" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 5.00 x 1500.0 x 3000.0 mm
 Weight (Kg):1,070
@@ -5175,12 +5190,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="300" xml:space="preserve">
-      <c r="A300" t="str" xml:space="preserve">
+    <row r="301" xml:space="preserve">
+      <c r="A301" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 5.00 x 1500.0 x 3000.0 mm</v>
       </c>
-      <c r="B300" t="str" xml:space="preserve">
+      <c r="B301" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 5.00 x 1500.0 x 3000.0 mm
 Weight (Kg):1,960
@@ -5191,12 +5206,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="301" xml:space="preserve">
-      <c r="A301" t="str" xml:space="preserve">
+    <row r="302" xml:space="preserve">
+      <c r="A302" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 5.00 x 1500.0 x 3000.0 mm</v>
       </c>
-      <c r="B301" t="str" xml:space="preserve">
+      <c r="B302" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 5.00 x 1500.0 x 3000.0 mm
 Weight (Kg):1,734
@@ -5207,12 +5222,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="302" xml:space="preserve">
-      <c r="A302" t="str" xml:space="preserve">
+    <row r="303" xml:space="preserve">
+      <c r="A303" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 5.00 x 1500.0 x 3000.0 mm</v>
       </c>
-      <c r="B302" t="str" xml:space="preserve">
+      <c r="B303" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 5.00 x 1500.0 x 3000.0 mm
 Weight (Kg):1,874
@@ -5223,12 +5238,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="303" xml:space="preserve">
-      <c r="A303" t="str" xml:space="preserve">
+    <row r="304" xml:space="preserve">
+      <c r="A304" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 5.00 x 1500.0 x 3000.0 mm</v>
       </c>
-      <c r="B303" t="str" xml:space="preserve">
+      <c r="B304" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 5.00 x 1500.0 x 3000.0 mm
 Weight (Kg):884
@@ -5239,12 +5254,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="304" xml:space="preserve">
-      <c r="A304" t="str" xml:space="preserve">
+    <row r="305" xml:space="preserve">
+      <c r="A305" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 5.00 x 1500.0 x 3000.0 mm</v>
       </c>
-      <c r="B304" t="str" xml:space="preserve">
+      <c r="B305" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 5.00 x 1500.0 x 3000.0 mm
 Weight (Kg):1,578
@@ -5255,12 +5270,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="305" xml:space="preserve">
-      <c r="A305" t="str" xml:space="preserve">
+    <row r="306" xml:space="preserve">
+      <c r="A306" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 5.00 x 1500.0 x 3000.0 mm</v>
       </c>
-      <c r="B305" t="str" xml:space="preserve">
+      <c r="B306" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 5.00 x 1500.0 x 3000.0 mm
 Weight (Kg):852
@@ -5271,12 +5286,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="306" xml:space="preserve">
-      <c r="A306" t="str" xml:space="preserve">
+    <row r="307" xml:space="preserve">
+      <c r="A307" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 5.00 x 1500.0 x 3000.0 mm</v>
       </c>
-      <c r="B306" t="str" xml:space="preserve">
+      <c r="B307" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 5.00 x 1500.0 x 3000.0 mm
 Weight (Kg):1,942
@@ -5287,12 +5302,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="307" xml:space="preserve">
-      <c r="A307" t="str" xml:space="preserve">
+    <row r="308" xml:space="preserve">
+      <c r="A308" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 6.00 x 1000.0 x 2000.0 mm</v>
       </c>
-      <c r="B307" t="str" xml:space="preserve">
+      <c r="B308" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 6.00 x 1000.0 x 2000.0 mm
 Weight (Kg):1,906
@@ -5303,12 +5318,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="308" xml:space="preserve">
-      <c r="A308" t="str" xml:space="preserve">
+    <row r="309" xml:space="preserve">
+      <c r="A309" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 6.00 x 1000.0 x 2000.0 mm</v>
       </c>
-      <c r="B308" t="str" xml:space="preserve">
+      <c r="B309" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 6.00 x 1000.0 x 2000.0 mm
 Weight (Kg):1,886
@@ -5319,12 +5334,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="309" xml:space="preserve">
-      <c r="A309" t="str" xml:space="preserve">
+    <row r="310" xml:space="preserve">
+      <c r="A310" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 6.00 x 1000.0 x 2000.0 mm</v>
       </c>
-      <c r="B309" t="str" xml:space="preserve">
+      <c r="B310" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 6.00 x 1000.0 x 2000.0 mm
 Weight (Kg):1,414
@@ -5335,12 +5350,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="310" xml:space="preserve">
-      <c r="A310" t="str" xml:space="preserve">
+    <row r="311" xml:space="preserve">
+      <c r="A311" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 6.00 x 1000.0 x 2000.0 mm</v>
       </c>
-      <c r="B310" t="str" xml:space="preserve">
+      <c r="B311" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 6.00 x 1000.0 x 2000.0 mm
 Weight (Kg):1,620
@@ -5351,12 +5366,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="311" xml:space="preserve">
-      <c r="A311" t="str" xml:space="preserve">
+    <row r="312" xml:space="preserve">
+      <c r="A312" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 6.00 x 1000.0 x 2000.0 mm</v>
       </c>
-      <c r="B311" t="str" xml:space="preserve">
+      <c r="B312" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 6.00 x 1000.0 x 2000.0 mm
 Weight (Kg):938
@@ -5367,12 +5382,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="312" xml:space="preserve">
-      <c r="A312" t="str" xml:space="preserve">
+    <row r="313" xml:space="preserve">
+      <c r="A313" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 6.00 x 1000.0 x 2000.0 mm</v>
       </c>
-      <c r="B312" t="str" xml:space="preserve">
+      <c r="B313" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 6.00 x 1000.0 x 2000.0 mm
 Weight (Kg):1,406
@@ -5383,12 +5398,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="313" xml:space="preserve">
-      <c r="A313" t="str" xml:space="preserve">
+    <row r="314" xml:space="preserve">
+      <c r="A314" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 6.00 x 1000.0 x 2000.0 mm</v>
       </c>
-      <c r="B313" t="str" xml:space="preserve">
+      <c r="B314" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 6.00 x 1000.0 x 2000.0 mm
 Weight (Kg):1,140
@@ -5399,12 +5414,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="314" xml:space="preserve">
-      <c r="A314" t="str" xml:space="preserve">
+    <row r="315" xml:space="preserve">
+      <c r="A315" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 6.00 x 1250.0 x 2500.0 mm</v>
       </c>
-      <c r="B314" t="str" xml:space="preserve">
+      <c r="B315" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 6.00 x 1250.0 x 2500.0 mm
 Weight (Kg):1,494
@@ -5415,12 +5430,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="315" xml:space="preserve">
-      <c r="A315" t="str" xml:space="preserve">
+    <row r="316" xml:space="preserve">
+      <c r="A316" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 6.00 x 1250.0 x 2500.0 mm</v>
       </c>
-      <c r="B315" t="str" xml:space="preserve">
+      <c r="B316" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 6.00 x 1250.0 x 2500.0 mm
 Weight (Kg):1,652
@@ -5431,12 +5446,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="316" xml:space="preserve">
-      <c r="A316" t="str" xml:space="preserve">
+    <row r="317" xml:space="preserve">
+      <c r="A317" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 6.00 x 1250.0 x 2500.0 mm</v>
       </c>
-      <c r="B316" t="str" xml:space="preserve">
+      <c r="B317" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 6.00 x 1250.0 x 2500.0 mm
 Weight (Kg):1,610
@@ -5447,12 +5462,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="317" xml:space="preserve">
-      <c r="A317" t="str" xml:space="preserve">
+    <row r="318" xml:space="preserve">
+      <c r="A318" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 6.00 x 1250.0 x 2500.0 mm</v>
       </c>
-      <c r="B317" t="str" xml:space="preserve">
+      <c r="B318" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 6.00 x 1250.0 x 2500.0 mm
 Weight (Kg):1,900
@@ -5463,12 +5478,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="318" xml:space="preserve">
-      <c r="A318" t="str" xml:space="preserve">
+    <row r="319" xml:space="preserve">
+      <c r="A319" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 6.00 x 1250.0 x 2500.0 mm</v>
       </c>
-      <c r="B318" t="str" xml:space="preserve">
+      <c r="B319" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 6.00 x 1250.0 x 2500.0 mm
 Weight (Kg):2,346
@@ -5479,12 +5494,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="319" xml:space="preserve">
-      <c r="A319" t="str" xml:space="preserve">
+    <row r="320" xml:space="preserve">
+      <c r="A320" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 6.00 x 1250.0 x 2500.0 mm</v>
       </c>
-      <c r="B319" t="str" xml:space="preserve">
+      <c r="B320" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 6.00 x 1250.0 x 2500.0 mm
 Weight (Kg):1,624
@@ -5495,12 +5510,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="320" xml:space="preserve">
-      <c r="A320" t="str" xml:space="preserve">
+    <row r="321" xml:space="preserve">
+      <c r="A321" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 6.00 x 1500.0 x 3000.0 mm</v>
       </c>
-      <c r="B320" t="str" xml:space="preserve">
+      <c r="B321" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 6.00 x 1500.0 x 3000.0 mm
 Weight (Kg):1,296
@@ -5511,12 +5526,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="321" xml:space="preserve">
-      <c r="A321" t="str" xml:space="preserve">
+    <row r="322" xml:space="preserve">
+      <c r="A322" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 6.00 x 1500.0 x 3000.0 mm</v>
       </c>
-      <c r="B321" t="str" xml:space="preserve">
+      <c r="B322" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 6.00 x 1500.0 x 3000.0 mm
 Weight (Kg):1,716
@@ -5527,12 +5542,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="322" xml:space="preserve">
-      <c r="A322" t="str" xml:space="preserve">
+    <row r="323" xml:space="preserve">
+      <c r="A323" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 6.00 x 1500.0 x 3000.0 mm</v>
       </c>
-      <c r="B322" t="str" xml:space="preserve">
+      <c r="B323" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 6.00 x 1500.0 x 3000.0 mm
 Weight (Kg):1,917
@@ -5543,12 +5558,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="323" xml:space="preserve">
-      <c r="A323" t="str" xml:space="preserve">
+    <row r="324" xml:space="preserve">
+      <c r="A324" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 6.00 x 1500.0 x 3000.0 mm</v>
       </c>
-      <c r="B323" t="str" xml:space="preserve">
+      <c r="B324" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 6.00 x 1500.0 x 3000.0 mm
 Weight (Kg):1,922
@@ -5559,12 +5574,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="324" xml:space="preserve">
-      <c r="A324" t="str" xml:space="preserve">
+    <row r="325" xml:space="preserve">
+      <c r="A325" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 6.00 x 1500.0 x 3000.0 mm</v>
       </c>
-      <c r="B324" t="str" xml:space="preserve">
+      <c r="B325" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 6.00 x 1500.0 x 3000.0 mm
 Weight (Kg):1,728
@@ -5575,12 +5590,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="325" xml:space="preserve">
-      <c r="A325" t="str" xml:space="preserve">
+    <row r="326" xml:space="preserve">
+      <c r="A326" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 6.00 x 1500.0 x 3000.0 mm</v>
       </c>
-      <c r="B325" t="str" xml:space="preserve">
+      <c r="B326" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 6.00 x 1500.0 x 3000.0 mm
 Weight (Kg):864
@@ -5591,12 +5606,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="326" xml:space="preserve">
-      <c r="A326" t="str" xml:space="preserve">
+    <row r="327" xml:space="preserve">
+      <c r="A327" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 6.00 x 1500.0 x 3000.0 mm</v>
       </c>
-      <c r="B326" t="str" xml:space="preserve">
+      <c r="B327" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 6.00 x 1500.0 x 3000.0 mm
 Weight (Kg):1,302
@@ -5607,12 +5622,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="327" xml:space="preserve">
-      <c r="A327" t="str" xml:space="preserve">
+    <row r="328" xml:space="preserve">
+      <c r="A328" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 6.00 x 1500.0 x 3000.0 mm</v>
       </c>
-      <c r="B327" t="str" xml:space="preserve">
+      <c r="B328" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 6.00 x 1500.0 x 3000.0 mm
 Weight (Kg):1,062
@@ -5623,12 +5638,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="328" xml:space="preserve">
-      <c r="A328" t="str" xml:space="preserve">
+    <row r="329" xml:space="preserve">
+      <c r="A329" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 6.00 x 1500.0 x 3000.0 mm</v>
       </c>
-      <c r="B328" t="str" xml:space="preserve">
+      <c r="B329" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 6.00 x 1500.0 x 3000.0 mm
 Weight (Kg):1,966
@@ -5639,12 +5654,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="329" xml:space="preserve">
-      <c r="A329" t="str" xml:space="preserve">
+    <row r="330" xml:space="preserve">
+      <c r="A330" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 6.00 x 1500.0 x 3000.0 mm</v>
       </c>
-      <c r="B329" t="str" xml:space="preserve">
+      <c r="B330" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 6.00 x 1500.0 x 3000.0 mm
 Weight (Kg):1,496
@@ -5655,12 +5670,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="330" xml:space="preserve">
-      <c r="A330" t="str" xml:space="preserve">
+    <row r="331" xml:space="preserve">
+      <c r="A331" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 6.00 x 1500.0 x 3000.0 mm</v>
       </c>
-      <c r="B330" t="str" xml:space="preserve">
+      <c r="B331" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 6.00 x 1500.0 x 3000.0 mm
 Weight (Kg):1,320
@@ -5671,12 +5686,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="331" xml:space="preserve">
-      <c r="A331" t="str" xml:space="preserve">
+    <row r="332" xml:space="preserve">
+      <c r="A332" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 6.00 x 1500.0 x 3000.0 mm</v>
       </c>
-      <c r="B331" t="str" xml:space="preserve">
+      <c r="B332" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 6.00 x 1500.0 x 3000.0 mm
 Weight (Kg):1,071
@@ -5687,12 +5702,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="332" xml:space="preserve">
-      <c r="A332" t="str" xml:space="preserve">
+    <row r="333" xml:space="preserve">
+      <c r="A333" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 6.00 x 1500.0 x 3000.0 mm</v>
       </c>
-      <c r="B332" t="str" xml:space="preserve">
+      <c r="B333" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 6.00 x 1500.0 x 3000.0 mm
 Weight (Kg):1,264
@@ -5703,12 +5718,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="333" xml:space="preserve">
-      <c r="A333" t="str" xml:space="preserve">
+    <row r="334" xml:space="preserve">
+      <c r="A334" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 6.00 x 1500.0 x 3000.0 mm</v>
       </c>
-      <c r="B333" t="str" xml:space="preserve">
+      <c r="B334" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 6.00 x 1500.0 x 3000.0 mm
 Weight (Kg):1,916
@@ -5719,12 +5734,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="334" xml:space="preserve">
-      <c r="A334" t="str" xml:space="preserve">
+    <row r="335" xml:space="preserve">
+      <c r="A335" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 6.00 x 1500.0 x 3000.0 mm</v>
       </c>
-      <c r="B334" t="str" xml:space="preserve">
+      <c r="B335" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 6.00 x 1500.0 x 3000.0 mm
 Weight (Kg):1,908
@@ -5735,12 +5750,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="335" xml:space="preserve">
-      <c r="A335" t="str" xml:space="preserve">
+    <row r="336" xml:space="preserve">
+      <c r="A336" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 6.00 x 1500.0 x 3000.0 mm</v>
       </c>
-      <c r="B335" t="str" xml:space="preserve">
+      <c r="B336" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 6.00 x 1500.0 x 3000.0 mm
 Weight (Kg):1,928
@@ -5751,12 +5766,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="336" xml:space="preserve">
-      <c r="A336" t="str" xml:space="preserve">
+    <row r="337" xml:space="preserve">
+      <c r="A337" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 6.00 x 1500.0 x 3000.0 mm</v>
       </c>
-      <c r="B336" t="str" xml:space="preserve">
+      <c r="B337" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 6.00 x 1500.0 x 3000.0 mm
 Weight (Kg):1,290
@@ -5767,12 +5782,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="337" xml:space="preserve">
-      <c r="A337" t="str" xml:space="preserve">
+    <row r="338" xml:space="preserve">
+      <c r="A338" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 6.00 x 1500.0 x 3000.0 mm</v>
       </c>
-      <c r="B337" t="str" xml:space="preserve">
+      <c r="B338" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 6.00 x 1500.0 x 3000.0 mm
 Weight (Kg):1,698
@@ -5783,12 +5798,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="338" xml:space="preserve">
-      <c r="A338" t="str" xml:space="preserve">
+    <row r="339" xml:space="preserve">
+      <c r="A339" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 6.00 x 1500.0 x 3000.0 mm</v>
       </c>
-      <c r="B338" t="str" xml:space="preserve">
+      <c r="B339" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 6.00 x 1500.0 x 3000.0 mm
 Weight (Kg):1,754
@@ -5799,12 +5814,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="339" xml:space="preserve">
-      <c r="A339" t="str" xml:space="preserve">
+    <row r="340" xml:space="preserve">
+      <c r="A340" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 6.00 x 1500.0 x 3000.0 mm</v>
       </c>
-      <c r="B339" t="str" xml:space="preserve">
+      <c r="B340" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 6.00 x 1500.0 x 3000.0 mm
 Weight (Kg):1,716
@@ -5815,12 +5830,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="340" xml:space="preserve">
-      <c r="A340" t="str" xml:space="preserve">
+    <row r="341" xml:space="preserve">
+      <c r="A341" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 6.00 x 1500.0 x 3000.0 mm</v>
       </c>
-      <c r="B340" t="str" xml:space="preserve">
+      <c r="B341" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 6.00 x 1500.0 x 3000.0 mm
 Weight (Kg):1,548
@@ -5831,12 +5846,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="341" xml:space="preserve">
-      <c r="A341" t="str" xml:space="preserve">
+    <row r="342" xml:space="preserve">
+      <c r="A342" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 6.00 x 1500.0 x 3000.0 mm</v>
       </c>
-      <c r="B341" t="str" xml:space="preserve">
+      <c r="B342" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 6.00 x 1500.0 x 3000.0 mm
 Weight (Kg):1,916
@@ -5847,12 +5862,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="342" xml:space="preserve">
-      <c r="A342" t="str" xml:space="preserve">
+    <row r="343" xml:space="preserve">
+      <c r="A343" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 6.00 x 1500.0 x 3000.0 mm</v>
       </c>
-      <c r="B342" t="str" xml:space="preserve">
+      <c r="B343" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 6.00 x 1500.0 x 3000.0 mm
 Weight (Kg):1,485
@@ -5863,12 +5878,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="343" xml:space="preserve">
-      <c r="A343" t="str" xml:space="preserve">
+    <row r="344" xml:space="preserve">
+      <c r="A344" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 6.00 x 1500.0 x 3000.0 mm</v>
       </c>
-      <c r="B343" t="str" xml:space="preserve">
+      <c r="B344" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 6.00 x 1500.0 x 3000.0 mm
 Weight (Kg):1,940
@@ -5879,12 +5894,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="344" xml:space="preserve">
-      <c r="A344" t="str" xml:space="preserve">
+    <row r="345" xml:space="preserve">
+      <c r="A345" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 6.00 x 1500.0 x 3000.0 mm</v>
       </c>
-      <c r="B344" t="str" xml:space="preserve">
+      <c r="B345" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 6.00 x 1500.0 x 3000.0 mm
 Weight (Kg):1,762
@@ -5895,12 +5910,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="345" xml:space="preserve">
-      <c r="A345" t="str" xml:space="preserve">
+    <row r="346" xml:space="preserve">
+      <c r="A346" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 6.00 x 1500.0 x 3000.0 mm</v>
       </c>
-      <c r="B345" t="str" xml:space="preserve">
+      <c r="B346" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 6.00 x 1500.0 x 3000.0 mm
 Weight (Kg):1,918
@@ -5911,12 +5926,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="346" xml:space="preserve">
-      <c r="A346" t="str" xml:space="preserve">
+    <row r="347" xml:space="preserve">
+      <c r="A347" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 6.00 x 1500.0 x 3000.0 mm</v>
       </c>
-      <c r="B346" t="str" xml:space="preserve">
+      <c r="B347" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 6.00 x 1500.0 x 3000.0 mm
 Weight (Kg):1,306
@@ -5927,12 +5942,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="347" xml:space="preserve">
-      <c r="A347" t="str" xml:space="preserve">
+    <row r="348" xml:space="preserve">
+      <c r="A348" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 6.00 x 1500.0 x 3000.0 mm</v>
       </c>
-      <c r="B347" t="str" xml:space="preserve">
+      <c r="B348" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 6.00 x 1500.0 x 3000.0 mm
 Weight (Kg):1,066
@@ -5943,12 +5958,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="348" xml:space="preserve">
-      <c r="A348" t="str" xml:space="preserve">
+    <row r="349" xml:space="preserve">
+      <c r="A349" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 6.00 x 1500.0 x 3000.0 mm</v>
       </c>
-      <c r="B348" t="str" xml:space="preserve">
+      <c r="B349" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 6.00 x 1500.0 x 3000.0 mm
 Weight (Kg):1,936
@@ -5959,12 +5974,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="349" xml:space="preserve">
-      <c r="A349" t="str" xml:space="preserve">
+    <row r="350" xml:space="preserve">
+      <c r="A350" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 6.00 x 1500.0 x 3000.0 mm</v>
       </c>
-      <c r="B349" t="str" xml:space="preserve">
+      <c r="B350" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 6.00 x 1500.0 x 3000.0 mm
 Weight (Kg):2,390
@@ -5975,12 +5990,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="350" xml:space="preserve">
-      <c r="A350" t="str" xml:space="preserve">
+    <row r="351" xml:space="preserve">
+      <c r="A351" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 6.00 x 1500.0 x 3000.0 mm</v>
       </c>
-      <c r="B350" t="str" xml:space="preserve">
+      <c r="B351" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 6.00 x 1500.0 x 3000.0 mm
 Weight (Kg):1,728
@@ -5991,12 +6006,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="351" xml:space="preserve">
-      <c r="A351" t="str" xml:space="preserve">
+    <row r="352" xml:space="preserve">
+      <c r="A352" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 6.00 x 1500.0 x 3000.0 mm</v>
       </c>
-      <c r="B351" t="str" xml:space="preserve">
+      <c r="B352" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 6.00 x 1500.0 x 3000.0 mm
 Weight (Kg):1,514
@@ -6007,12 +6022,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="352" xml:space="preserve">
-      <c r="A352" t="str" xml:space="preserve">
+    <row r="353" xml:space="preserve">
+      <c r="A353" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 6.00 x 1500.0 x 3000.0 mm</v>
       </c>
-      <c r="B352" t="str" xml:space="preserve">
+      <c r="B353" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 6.00 x 1500.0 x 3000.0 mm
 Weight (Kg):1,922
@@ -6023,12 +6038,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="353" xml:space="preserve">
-      <c r="A353" t="str" xml:space="preserve">
+    <row r="354" xml:space="preserve">
+      <c r="A354" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 6.00 x 1500.0 x 3000.0 mm</v>
       </c>
-      <c r="B353" t="str" xml:space="preserve">
+      <c r="B354" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 6.00 x 1500.0 x 3000.0 mm
 Weight (Kg):1,942
@@ -6039,12 +6054,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="354" xml:space="preserve">
-      <c r="A354" t="str" xml:space="preserve">
+    <row r="355" xml:space="preserve">
+      <c r="A355" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 6.00 x 1500.0 x 3000.0 mm</v>
       </c>
-      <c r="B354" t="str" xml:space="preserve">
+      <c r="B355" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 6.00 x 1500.0 x 3000.0 mm
 Weight (Kg):2,114
@@ -6055,12 +6070,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="355" xml:space="preserve">
-      <c r="A355" t="str" xml:space="preserve">
+    <row r="356" xml:space="preserve">
+      <c r="A356" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 6.00 x 1500.0 x 3000.0 mm</v>
       </c>
-      <c r="B355" t="str" xml:space="preserve">
+      <c r="B356" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 6.00 x 1500.0 x 3000.0 mm
 Weight (Kg):1,088
@@ -6071,12 +6086,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="356" xml:space="preserve">
-      <c r="A356" t="str" xml:space="preserve">
+    <row r="357" xml:space="preserve">
+      <c r="A357" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 6.00 x 1500.0 x 3000.0 mm</v>
       </c>
-      <c r="B356" t="str" xml:space="preserve">
+      <c r="B357" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 6.00 x 1500.0 x 3000.0 mm
 Weight (Kg):1,274
@@ -6087,12 +6102,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="357" xml:space="preserve">
-      <c r="A357" t="str" xml:space="preserve">
+    <row r="358" xml:space="preserve">
+      <c r="A358" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 6.00 x 1500.0 x 3000.0 mm</v>
       </c>
-      <c r="B357" t="str" xml:space="preserve">
+      <c r="B358" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 6.00 x 1500.0 x 3000.0 mm
 Weight (Kg):1,718
@@ -6103,12 +6118,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="358" xml:space="preserve">
-      <c r="A358" t="str" xml:space="preserve">
+    <row r="359" xml:space="preserve">
+      <c r="A359" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 6.00 x 1500.0 x 3000.0 mm</v>
       </c>
-      <c r="B358" t="str" xml:space="preserve">
+      <c r="B359" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 6.00 x 1500.0 x 3000.0 mm
 Weight (Kg):1,922
@@ -6119,12 +6134,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="359" xml:space="preserve">
-      <c r="A359" t="str" xml:space="preserve">
+    <row r="360" xml:space="preserve">
+      <c r="A360" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 6.00 x 1500.0 x 3000.0 mm</v>
       </c>
-      <c r="B359" t="str" xml:space="preserve">
+      <c r="B360" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 6.00 x 1500.0 x 3000.0 mm
 Weight (Kg):1,878
@@ -6135,12 +6150,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="360" xml:space="preserve">
-      <c r="A360" t="str" xml:space="preserve">
+    <row r="361" xml:space="preserve">
+      <c r="A361" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 6.00 x 1500.0 x 3000.0 mm</v>
       </c>
-      <c r="B360" t="str" xml:space="preserve">
+      <c r="B361" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 6.00 x 1500.0 x 3000.0 mm
 Weight (Kg):1,714
@@ -6151,12 +6166,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="361" xml:space="preserve">
-      <c r="A361" t="str" xml:space="preserve">
+    <row r="362" xml:space="preserve">
+      <c r="A362" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 6.00 x 1500.0 x 3000.0 mm</v>
       </c>
-      <c r="B361" t="str" xml:space="preserve">
+      <c r="B362" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 6.00 x 1500.0 x 3000.0 mm
 Weight (Kg):1,918
@@ -6167,12 +6182,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="362" xml:space="preserve">
-      <c r="A362" t="str" xml:space="preserve">
+    <row r="363" xml:space="preserve">
+      <c r="A363" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 6.00 x 1500.0 x 3000.0 mm</v>
       </c>
-      <c r="B362" t="str" xml:space="preserve">
+      <c r="B363" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 6.00 x 1500.0 x 3000.0 mm
 Weight (Kg):1,754
@@ -6183,12 +6198,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="363" xml:space="preserve">
-      <c r="A363" t="str" xml:space="preserve">
+    <row r="364" xml:space="preserve">
+      <c r="A364" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 6.00 x 1500.0 x 3000.0 mm</v>
       </c>
-      <c r="B363" t="str" xml:space="preserve">
+      <c r="B364" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 6.00 x 1500.0 x 3000.0 mm
 Weight (Kg):1,528
@@ -6199,12 +6214,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="364" xml:space="preserve">
-      <c r="A364" t="str" xml:space="preserve">
+    <row r="365" xml:space="preserve">
+      <c r="A365" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 6.00 x 1500.0 x 3000.0 mm</v>
       </c>
-      <c r="B364" t="str" xml:space="preserve">
+      <c r="B365" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 6.00 x 1500.0 x 3000.0 mm
 Weight (Kg):2,136
@@ -6215,31 +6230,15 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="365" xml:space="preserve">
-      <c r="A365" t="str" xml:space="preserve">
+    <row r="366" xml:space="preserve">
+      <c r="A366" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 6.00 x 1500.0 x 3000.0 mm</v>
       </c>
-      <c r="B365" t="str" xml:space="preserve">
+      <c r="B366" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 6.00 x 1500.0 x 3000.0 mm
 Weight (Kg):1,946
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-2,225.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="366" xml:space="preserve">
-      <c r="A366" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, BA,
-0.80 x 1000.0 x 2000.0 mm</v>
-      </c>
-      <c r="B366" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, BA,
-0.80 x 1000.0 x 2000.0 mm
-Weight (Kg):1,633
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -6255,7 +6254,7 @@
       <c r="B367" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, BA,
 0.80 x 1000.0 x 2000.0 mm
-Weight (Kg):1,286
+Weight (Kg):1,633
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -6271,7 +6270,7 @@
       <c r="B368" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, BA,
 0.80 x 1000.0 x 2000.0 mm
-Weight (Kg):727
+Weight (Kg):1,286
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -6282,12 +6281,12 @@
     <row r="369" xml:space="preserve">
       <c r="A369" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, BA,
-1.00 x 1000.0 x 2000.0 mm</v>
+0.80 x 1000.0 x 2000.0 mm</v>
       </c>
       <c r="B369" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, BA,
-1.00 x 1000.0 x 2000.0 mm
-Weight (Kg):650
+0.80 x 1000.0 x 2000.0 mm
+Weight (Kg):727
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -6303,7 +6302,7 @@
       <c r="B370" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, BA,
 1.00 x 1000.0 x 2000.0 mm
-Weight (Kg):869
+Weight (Kg):650
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -6319,7 +6318,7 @@
       <c r="B371" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, BA,
 1.00 x 1000.0 x 2000.0 mm
-Weight (Kg):885
+Weight (Kg):869
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -6335,7 +6334,7 @@
       <c r="B372" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, BA,
 1.00 x 1000.0 x 2000.0 mm
-Weight (Kg):931
+Weight (Kg):885
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -6346,12 +6345,12 @@
     <row r="373" xml:space="preserve">
       <c r="A373" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, BA,
-1.00 x 1250.0 x 3000.0 mm</v>
+1.00 x 1000.0 x 2000.0 mm</v>
       </c>
       <c r="B373" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, BA,
-1.00 x 1250.0 x 3000.0 mm
-Weight (Kg):766
+1.00 x 1000.0 x 2000.0 mm
+Weight (Kg):931
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -6367,7 +6366,7 @@
       <c r="B374" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, BA,
 1.00 x 1250.0 x 3000.0 mm
-Weight (Kg):1,417
+Weight (Kg):766
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -6378,12 +6377,12 @@
     <row r="375" xml:space="preserve">
       <c r="A375" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, BA,
-1.50 x 1000.0 x 2000.0 mm</v>
+1.00 x 1250.0 x 3000.0 mm</v>
       </c>
       <c r="B375" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, BA,
-1.50 x 1000.0 x 2000.0 mm
-Weight (Kg):1,459
+1.00 x 1250.0 x 3000.0 mm
+Weight (Kg):1,417
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -6399,7 +6398,7 @@
       <c r="B376" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, BA,
 1.50 x 1000.0 x 2000.0 mm
-Weight (Kg):825
+Weight (Kg):1,459
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -6415,7 +6414,7 @@
       <c r="B377" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, BA,
 1.50 x 1000.0 x 2000.0 mm
-Weight (Kg):738
+Weight (Kg):825
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -6431,7 +6430,7 @@
       <c r="B378" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, BA,
 1.50 x 1000.0 x 2000.0 mm
-Weight (Kg):886
+Weight (Kg):738
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -6447,7 +6446,7 @@
       <c r="B379" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, BA,
 1.50 x 1000.0 x 2000.0 mm
-Weight (Kg):1,116
+Weight (Kg):886
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -6463,7 +6462,7 @@
       <c r="B380" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, BA,
 1.50 x 1000.0 x 2000.0 mm
-Weight (Kg):692
+Weight (Kg):1,116
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -6479,7 +6478,7 @@
       <c r="B381" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, BA,
 1.50 x 1000.0 x 2000.0 mm
-Weight (Kg):1,613
+Weight (Kg):692
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -6495,7 +6494,7 @@
       <c r="B382" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, BA,
 1.50 x 1000.0 x 2000.0 mm
-Weight (Kg):946
+Weight (Kg):1,613
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -6506,9 +6505,25 @@
     <row r="383" xml:space="preserve">
       <c r="A383" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, BA,
+1.50 x 1000.0 x 2000.0 mm</v>
+      </c>
+      <c r="B383" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, BA,
+1.50 x 1000.0 x 2000.0 mm
+Weight (Kg):946
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,225.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="384" xml:space="preserve">
+      <c r="A384" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, BA,
 1.50 x 1250.0 x 2500.0 mm</v>
       </c>
-      <c r="B383" t="str" xml:space="preserve">
+      <c r="B384" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, BA,
 1.50 x 1250.0 x 2500.0 mm
 Weight (Kg):1,628
@@ -6519,12 +6534,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="384" xml:space="preserve">
-      <c r="A384" t="str" xml:space="preserve">
+    <row r="385" xml:space="preserve">
+      <c r="A385" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, BA,
 1.80 x 1000.0 x 2000.0 mm</v>
       </c>
-      <c r="B384" t="str" xml:space="preserve">
+      <c r="B385" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, BA,
 1.80 x 1000.0 x 2000.0 mm
 Weight (Kg):1,405
@@ -6535,12 +6550,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="385" xml:space="preserve">
-      <c r="A385" t="str" xml:space="preserve">
+    <row r="386" xml:space="preserve">
+      <c r="A386" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, Nb. 1,
 3.00 x 1500.0 x 3000.0 mm</v>
       </c>
-      <c r="B385" t="str" xml:space="preserve">
+      <c r="B386" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, Nb. 1,
 3.00 x 1500.0 x 3000.0 mm
 Weight (Kg):1,728
@@ -6548,22 +6563,6 @@
 Help
 Location:FABRICA ALGECIRAS
 2,125.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="386" xml:space="preserve">
-      <c r="A386" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, Nb. 3 Chequered,
-4.50 x 1250.0 x 3000.0 mm</v>
-      </c>
-      <c r="B386" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, Nb. 3 Chequered,
-4.50 x 1250.0 x 3000.0 mm
-Weight (Kg):1,046
-Quality:Prime
-Help
-Location:FABRICA ALGECIRAS
-2,900.00 €/ton
 Add to cart</v>
       </c>
     </row>
@@ -6575,7 +6574,7 @@
       <c r="B387" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, Nb. 3 Chequered,
 4.50 x 1250.0 x 3000.0 mm
-Weight (Kg):1,316
+Weight (Kg):1,046
 Quality:Prime
 Help
 Location:FABRICA ALGECIRAS
@@ -6585,29 +6584,29 @@
     </row>
     <row r="388" xml:space="preserve">
       <c r="A388" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, Nb. 3 Chequered,
+4.50 x 1250.0 x 3000.0 mm</v>
+      </c>
+      <c r="B388" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, Nb. 3 Chequered,
+4.50 x 1250.0 x 3000.0 mm
+Weight (Kg):1,316
+Quality:Prime
+Help
+Location:FABRICA ALGECIRAS
+2,900.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="389" xml:space="preserve">
+      <c r="A389" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, Polished N4-G-240,
 0.80 x 1500.0 x 3000.0 mm</v>
       </c>
-      <c r="B388" t="str" xml:space="preserve">
+      <c r="B389" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, Polished N4-G-240,
 0.80 x 1500.0 x 3000.0 mm
 Weight (Kg):630
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-2,225.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="389" xml:space="preserve">
-      <c r="A389" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, Polished N4-G-240,
-0.90 x 1500.0 x 3000.0 mm</v>
-      </c>
-      <c r="B389" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, Polished N4-G-240,
-0.90 x 1500.0 x 3000.0 mm
-Weight (Kg):807
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -6623,7 +6622,7 @@
       <c r="B390" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, Polished N4-G-240,
 0.90 x 1500.0 x 3000.0 mm
-Weight (Kg):622
+Weight (Kg):807
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -6633,13 +6632,13 @@
     </row>
     <row r="391" xml:space="preserve">
       <c r="A391" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, SB-G-400,
-1.50 x 1000.0 x 2000.0 mm</v>
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, Polished N4-G-240,
+0.90 x 1500.0 x 3000.0 mm</v>
       </c>
       <c r="B391" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, SB-G-400,
-1.50 x 1000.0 x 2000.0 mm
-Weight (Kg):674
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, Polished N4-G-240,
+0.90 x 1500.0 x 3000.0 mm
+Weight (Kg):622
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -6655,7 +6654,7 @@
       <c r="B392" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, SB-G-400,
 1.50 x 1000.0 x 2000.0 mm
-Weight (Kg):535
+Weight (Kg):674
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -6666,12 +6665,12 @@
     <row r="393" xml:space="preserve">
       <c r="A393" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, SB-G-400,
-3.00 x 1500.0 x 3000.0 mm</v>
+1.50 x 1000.0 x 2000.0 mm</v>
       </c>
       <c r="B393" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, SB-G-400,
-3.00 x 1500.0 x 3000.0 mm
-Weight (Kg):1,877
+1.50 x 1000.0 x 2000.0 mm
+Weight (Kg):535
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -6687,7 +6686,7 @@
       <c r="B394" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, SB-G-400,
 3.00 x 1500.0 x 3000.0 mm
-Weight (Kg):629
+Weight (Kg):1,877
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -6703,7 +6702,7 @@
       <c r="B395" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, SB-G-400,
 3.00 x 1500.0 x 3000.0 mm
-Weight (Kg):1,887
+Weight (Kg):629
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -6713,13 +6712,13 @@
     </row>
     <row r="396" xml:space="preserve">
       <c r="A396" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, SB-G-500,
-0.70 x 1500.0 x 3000.0 mm</v>
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, SB-G-400,
+3.00 x 1500.0 x 3000.0 mm</v>
       </c>
       <c r="B396" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, SB-G-500,
-0.70 x 1500.0 x 3000.0 mm
-Weight (Kg):1,226
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, SB-G-400,
+3.00 x 1500.0 x 3000.0 mm
+Weight (Kg):1,887
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -6735,7 +6734,7 @@
       <c r="B397" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, SB-G-500,
 0.70 x 1500.0 x 3000.0 mm
-Weight (Kg):1,001
+Weight (Kg):1,226
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -6751,7 +6750,7 @@
       <c r="B398" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, SB-G-500,
 0.70 x 1500.0 x 3000.0 mm
-Weight (Kg):681
+Weight (Kg):1,001
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -6767,7 +6766,7 @@
       <c r="B399" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, SB-G-500,
 0.70 x 1500.0 x 3000.0 mm
-Weight (Kg):673
+Weight (Kg):681
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -6783,7 +6782,7 @@
       <c r="B400" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, SB-G-500,
 0.70 x 1500.0 x 3000.0 mm
-Weight (Kg):722
+Weight (Kg):673
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -6810,9 +6809,25 @@
     <row r="402" xml:space="preserve">
       <c r="A402" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, SB-G-500,
+0.70 x 1500.0 x 3000.0 mm</v>
+      </c>
+      <c r="B402" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, SB-G-500,
+0.70 x 1500.0 x 3000.0 mm
+Weight (Kg):722
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,225.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="403" xml:space="preserve">
+      <c r="A403" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, SB-G-500,
 0.80 x 1000.0 x 2000.0 mm</v>
       </c>
-      <c r="B402" t="str" xml:space="preserve">
+      <c r="B403" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, SB-G-500,
 0.80 x 1000.0 x 2000.0 mm
 Weight (Kg):1,256
@@ -6823,12 +6838,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="403" xml:space="preserve">
-      <c r="A403" t="str" xml:space="preserve">
+    <row r="404" xml:space="preserve">
+      <c r="A404" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, SB-G-500,
 0.80 x 1250.0 x 3000.0 mm</v>
       </c>
-      <c r="B403" t="str" xml:space="preserve">
+      <c r="B404" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, SB-G-500,
 0.80 x 1250.0 x 3000.0 mm
 Weight (Kg):535
@@ -6839,12 +6854,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="404" xml:space="preserve">
-      <c r="A404" t="str" xml:space="preserve">
+    <row r="405" xml:space="preserve">
+      <c r="A405" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, SB-G-500,
 3.00 x 1500.0 x 3000.0 mm</v>
       </c>
-      <c r="B404" t="str" xml:space="preserve">
+      <c r="B405" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, SB-G-500,
 3.00 x 1500.0 x 3000.0 mm
 Weight (Kg):839
@@ -6855,12 +6870,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="405" xml:space="preserve">
-      <c r="A405" t="str" xml:space="preserve">
+    <row r="406" xml:space="preserve">
+      <c r="A406" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Untrimmed, Coil,
 0.80 x 1271.0 x coil mm</v>
       </c>
-      <c r="B405" t="str" xml:space="preserve">
+      <c r="B406" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Untrimmed, Coil,
 0.80 x 1271.0 x coil mm
 Weight (Kg):2,950
@@ -6871,12 +6886,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="406" xml:space="preserve">
-      <c r="A406" t="str" xml:space="preserve">
+    <row r="407" xml:space="preserve">
+      <c r="A407" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Untrimmed, Coil, 2B,
 1.20 x 1277.0 x coil mm</v>
       </c>
-      <c r="B406" t="str" xml:space="preserve">
+      <c r="B407" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Untrimmed, Coil, 2B,
 1.20 x 1277.0 x coil mm
 Weight (Kg):2,230
@@ -6887,31 +6902,15 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="407" xml:space="preserve">
-      <c r="A407" t="str" xml:space="preserve">
+    <row r="408" xml:space="preserve">
+      <c r="A408" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Untrimmed, Coil, 2B,
 2.00 x 1275.0 x coil mm</v>
       </c>
-      <c r="B407" t="str" xml:space="preserve">
+      <c r="B408" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Untrimmed, Coil, 2B,
 2.00 x 1275.0 x coil mm
 Weight (Kg):2,619
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-2,225.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="408" xml:space="preserve">
-      <c r="A408" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Untrimmed, Coil, 2B,
-5.00 x 1540.0 x coil mm</v>
-      </c>
-      <c r="B408" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Untrimmed, Coil, 2B,
-5.00 x 1540.0 x coil mm
-Weight (Kg):7,140
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -6927,7 +6926,7 @@
       <c r="B409" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Untrimmed, Coil, 2B,
 5.00 x 1540.0 x coil mm
-Weight (Kg):13,250
+Weight (Kg):7,140
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -6937,10 +6936,26 @@
     </row>
     <row r="410" xml:space="preserve">
       <c r="A410" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Untrimmed, Coil, 2B,
+5.00 x 1540.0 x coil mm</v>
+      </c>
+      <c r="B410" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Untrimmed, Coil, 2B,
+5.00 x 1540.0 x coil mm
+Weight (Kg):13,250
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,225.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="411" xml:space="preserve">
+      <c r="A411" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Untrimmed, Coil, 2D,
 1.00 x 1027.0 x coil mm</v>
       </c>
-      <c r="B410" t="str" xml:space="preserve">
+      <c r="B411" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Untrimmed, Coil, 2D,
 1.00 x 1027.0 x coil mm
 Weight (Kg):2,410
@@ -6951,12 +6966,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="411" xml:space="preserve">
-      <c r="A411" t="str" xml:space="preserve">
+    <row r="412" xml:space="preserve">
+      <c r="A412" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Untrimmed, Coil, BA,
 0.40 x 1017.0 x coil mm</v>
       </c>
-      <c r="B411" t="str" xml:space="preserve">
+      <c r="B412" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Untrimmed, Coil, BA,
 0.40 x 1017.0 x coil mm
 Weight (Kg):5,705
@@ -6967,12 +6982,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="412" xml:space="preserve">
-      <c r="A412" t="str" xml:space="preserve">
+    <row r="413" xml:space="preserve">
+      <c r="A413" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Untrimmed, Coil, BA,
 0.90 x 1275.0 x coil mm</v>
       </c>
-      <c r="B412" t="str" xml:space="preserve">
+      <c r="B413" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Untrimmed, Coil, BA,
 0.90 x 1275.0 x coil mm
 Weight (Kg):2,500
@@ -6983,12 +6998,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="413" xml:space="preserve">
-      <c r="A413" t="str" xml:space="preserve">
+    <row r="414" xml:space="preserve">
+      <c r="A414" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Untrimmed, Coil, BA,
 0.90 x 1288.0 x coil mm</v>
       </c>
-      <c r="B413" t="str" xml:space="preserve">
+      <c r="B414" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Untrimmed, Coil, BA,
 0.90 x 1288.0 x coil mm
 Weight (Kg):7,960
@@ -6999,12 +7014,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="414" xml:space="preserve">
-      <c r="A414" t="str" xml:space="preserve">
+    <row r="415" xml:space="preserve">
+      <c r="A415" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Untrimmed, Coil, SB-G-400,
 1.20 x 1500.0 x coil mm</v>
       </c>
-      <c r="B414" t="str" xml:space="preserve">
+      <c r="B415" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Untrimmed, Coil, SB-G-400,
 1.20 x 1500.0 x coil mm
 Weight (Kg):2,640
@@ -7015,12 +7030,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="415" xml:space="preserve">
-      <c r="A415" t="str" xml:space="preserve">
+    <row r="416" xml:space="preserve">
+      <c r="A416" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Coil, 2B,
 1.20 x 1536.0 x coil mm</v>
       </c>
-      <c r="B415" t="str" xml:space="preserve">
+      <c r="B416" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Coil, 2B,
 1.20 x 1536.0 x coil mm
 Weight (Kg):1,260
@@ -7031,12 +7046,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="416" xml:space="preserve">
-      <c r="A416" t="str" xml:space="preserve">
+    <row r="417" xml:space="preserve">
+      <c r="A417" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Coil, 2B,
 1.50 x 140.0 x coil mm</v>
       </c>
-      <c r="B416" t="str" xml:space="preserve">
+      <c r="B417" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Coil, 2B,
 1.50 x 140.0 x coil mm
 Weight (Kg):758
@@ -7047,12 +7062,76 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="417" xml:space="preserve">
-      <c r="A417" t="str" xml:space="preserve">
+    <row r="418" xml:space="preserve">
+      <c r="A418" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Untrimmed, Coil,
+0.50 x 1272.0 x coil mm</v>
+      </c>
+      <c r="B418" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Untrimmed, Coil,
+0.50 x 1272.0 x coil mm
+Weight (Kg):5,960
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,225.00 €/ton
+Reserved</v>
+      </c>
+    </row>
+    <row r="419" xml:space="preserve">
+      <c r="A419" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Untrimmed, Coil, 2B,
+0.40 x 1017.0 x coil mm</v>
+      </c>
+      <c r="B419" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Untrimmed, Coil, 2B,
+0.40 x 1017.0 x coil mm
+Weight (Kg):9,900
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,225.00 €/ton
+Reserved</v>
+      </c>
+    </row>
+    <row r="420" xml:space="preserve">
+      <c r="A420" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Untrimmed, Coil, BA,
+0.80 x 1277.0 x coil mm</v>
+      </c>
+      <c r="B420" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Untrimmed, Coil, BA,
+0.80 x 1277.0 x coil mm
+Weight (Kg):5,250
+Quality:Prime
+Help
+Location:FABRICA ALGECIRAS
+2,425.00 €/ton
+Reserved</v>
+      </c>
+    </row>
+    <row r="421" xml:space="preserve">
+      <c r="A421" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Untrimmed, Coil, BA,
+1.50 x 1250.0 x coil mm</v>
+      </c>
+      <c r="B421" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Untrimmed, Coil, BA,
+1.50 x 1250.0 x coil mm
+Weight (Kg):3,285
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,050.00 €/ton
+Out of Stock</v>
+      </c>
+    </row>
+    <row r="422" xml:space="preserve">
+      <c r="A422" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Coil, 2B,
 1.50 x 160.9 x coil mm</v>
       </c>
-      <c r="B417" t="str" xml:space="preserve">
+      <c r="B422" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Coil, 2B,
 1.50 x 160.9 x coil mm
 Weight (Kg):848
@@ -7063,12 +7142,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="418" xml:space="preserve">
-      <c r="A418" t="str" xml:space="preserve">
+    <row r="423" xml:space="preserve">
+      <c r="A423" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Coil, 2B,
 1.50 x 230.9 x coil mm</v>
       </c>
-      <c r="B418" t="str" xml:space="preserve">
+      <c r="B423" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Coil, 2B,
 1.50 x 230.9 x coil mm
 Weight (Kg):1,044
@@ -7079,60 +7158,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="419" xml:space="preserve">
-      <c r="A419" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Untrimmed, Coil,
-0.50 x 1272.0 x coil mm</v>
-      </c>
-      <c r="B419" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Untrimmed, Coil,
-0.50 x 1272.0 x coil mm
-Weight (Kg):5,960
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-2,225.00 €/ton
-Reserved</v>
-      </c>
-    </row>
-    <row r="420" xml:space="preserve">
-      <c r="A420" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Untrimmed, Coil, 2B,
-0.40 x 1017.0 x coil mm</v>
-      </c>
-      <c r="B420" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Untrimmed, Coil, 2B,
-0.40 x 1017.0 x coil mm
-Weight (Kg):9,900
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-2,225.00 €/ton
-Reserved</v>
-      </c>
-    </row>
-    <row r="421" xml:space="preserve">
-      <c r="A421" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Untrimmed, Coil, BA,
-0.80 x 1277.0 x coil mm</v>
-      </c>
-      <c r="B421" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Untrimmed, Coil, BA,
-0.80 x 1277.0 x coil mm
-Weight (Kg):5,250
-Quality:Prime
-Help
-Location:FABRICA ALGECIRAS
-2,425.00 €/ton
-Reserved</v>
-      </c>
-    </row>
-    <row r="422" xml:space="preserve">
-      <c r="A422" t="str" xml:space="preserve">
+    <row r="424" xml:space="preserve">
+      <c r="A424" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Coil, 2B,
 2.00 x 1498.0 x coil mm</v>
       </c>
-      <c r="B422" t="str" xml:space="preserve">
+      <c r="B424" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Coil, 2B,
 2.00 x 1498.0 x coil mm
 Weight (Kg):2,770
@@ -7143,12 +7174,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="423" xml:space="preserve">
-      <c r="A423" t="str" xml:space="preserve">
+    <row r="425" xml:space="preserve">
+      <c r="A425" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Coil, 2B,
 5.00 x 1250.0 x coil mm</v>
       </c>
-      <c r="B423" t="str" xml:space="preserve">
+      <c r="B425" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Coil, 2B,
 5.00 x 1250.0 x coil mm
 Weight (Kg):12,055
@@ -7159,12 +7190,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="424" xml:space="preserve">
-      <c r="A424" t="str" xml:space="preserve">
+    <row r="426" xml:space="preserve">
+      <c r="A426" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Coil, 2B,
 5.00 x 240.0 x coil mm</v>
       </c>
-      <c r="B424" t="str" xml:space="preserve">
+      <c r="B426" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Coil, 2B,
 5.00 x 240.0 x coil mm
 Weight (Kg):2,314
@@ -7175,12 +7206,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="425" xml:space="preserve">
-      <c r="A425" t="str" xml:space="preserve">
+    <row r="427" xml:space="preserve">
+      <c r="A427" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Coil, 2B,
 5.00 x 240.0 x coil mm</v>
       </c>
-      <c r="B425" t="str" xml:space="preserve">
+      <c r="B427" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Coil, 2B,
 5.00 x 240.0 x coil mm
 Weight (Kg):2,237
@@ -7191,12 +7222,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="426" xml:space="preserve">
-      <c r="A426" t="str" xml:space="preserve">
+    <row r="428" xml:space="preserve">
+      <c r="A428" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Coil, 2B,
 6.00 x 1500.0 x coil mm</v>
       </c>
-      <c r="B426" t="str" xml:space="preserve">
+      <c r="B428" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Coil, 2B,
 6.00 x 1500.0 x coil mm
 Weight (Kg):2,016
@@ -7207,12 +7238,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="427" xml:space="preserve">
-      <c r="A427" t="str" xml:space="preserve">
+    <row r="429" xml:space="preserve">
+      <c r="A429" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Coil, 2B,
 6.00 x 250.9 x coil mm</v>
       </c>
-      <c r="B427" t="str" xml:space="preserve">
+      <c r="B429" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Coil, 2B,
 6.00 x 250.9 x coil mm
 Weight (Kg):548
@@ -7223,12 +7254,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="428" xml:space="preserve">
-      <c r="A428" t="str" xml:space="preserve">
+    <row r="430" xml:space="preserve">
+      <c r="A430" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Coil, 2B,
 6.00 x 250.9 x coil mm</v>
       </c>
-      <c r="B428" t="str" xml:space="preserve">
+      <c r="B430" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Coil, 2B,
 6.00 x 250.9 x coil mm
 Weight (Kg):1,880
@@ -7239,12 +7270,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="429" xml:space="preserve">
-      <c r="A429" t="str" xml:space="preserve">
+    <row r="431" xml:space="preserve">
+      <c r="A431" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Coil, 2D,
 3.30 x 112.0 x coil mm</v>
       </c>
-      <c r="B429" t="str" xml:space="preserve">
+      <c r="B431" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Coil, 2D,
 3.30 x 112.0 x coil mm
 Weight (Kg):1,017
@@ -7255,12 +7286,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="430" xml:space="preserve">
-      <c r="A430" t="str" xml:space="preserve">
+    <row r="432" xml:space="preserve">
+      <c r="A432" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Coil, 2D,
 3.30 x 112.0 x coil mm</v>
       </c>
-      <c r="B430" t="str" xml:space="preserve">
+      <c r="B432" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Coil, 2D,
 3.30 x 112.0 x coil mm
 Weight (Kg):878
@@ -7271,12 +7302,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="431" xml:space="preserve">
-      <c r="A431" t="str" xml:space="preserve">
+    <row r="433" xml:space="preserve">
+      <c r="A433" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Coil, 2D,
 3.30 x 449.0 x coil mm</v>
       </c>
-      <c r="B431" t="str" xml:space="preserve">
+      <c r="B433" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Coil, 2D,
 3.30 x 449.0 x coil mm
 Weight (Kg):1,850
@@ -7287,12 +7318,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="432" xml:space="preserve">
-      <c r="A432" t="str" xml:space="preserve">
+    <row r="434" xml:space="preserve">
+      <c r="A434" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Coil, 2D,
 3.30 x 449.0 x coil mm</v>
       </c>
-      <c r="B432" t="str" xml:space="preserve">
+      <c r="B434" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Coil, 2D,
 3.30 x 449.0 x coil mm
 Weight (Kg):1,854
@@ -7303,12 +7334,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="433" xml:space="preserve">
-      <c r="A433" t="str" xml:space="preserve">
+    <row r="435" xml:space="preserve">
+      <c r="A435" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Coil, BA,
 0.40 x 295.9 x coil mm</v>
       </c>
-      <c r="B433" t="str" xml:space="preserve">
+      <c r="B435" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Coil, BA,
 0.40 x 295.9 x coil mm
 Weight (Kg):662
@@ -7319,12 +7350,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="434" xml:space="preserve">
-      <c r="A434" t="str" xml:space="preserve">
+    <row r="436" xml:space="preserve">
+      <c r="A436" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Coil, BA,
 0.40 x 295.9 x coil mm</v>
       </c>
-      <c r="B434" t="str" xml:space="preserve">
+      <c r="B436" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Coil, BA,
 0.40 x 295.9 x coil mm
 Weight (Kg):650
@@ -7335,12 +7366,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="435" xml:space="preserve">
-      <c r="A435" t="str" xml:space="preserve">
+    <row r="437" xml:space="preserve">
+      <c r="A437" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Coil, BA,
 0.50 x 160.0 x coil mm</v>
       </c>
-      <c r="B435" t="str" xml:space="preserve">
+      <c r="B437" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Coil, BA,
 0.50 x 160.0 x coil mm
 Weight (Kg):1,066
@@ -7351,12 +7382,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="436" xml:space="preserve">
-      <c r="A436" t="str" xml:space="preserve">
+    <row r="438" xml:space="preserve">
+      <c r="A438" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Coil, Nb. 1,
 3.70 x 310.0 x coil mm</v>
       </c>
-      <c r="B436" t="str" xml:space="preserve">
+      <c r="B438" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Coil, Nb. 1,
 3.70 x 310.0 x coil mm
 Weight (Kg):5,921
@@ -7367,12 +7398,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="437" xml:space="preserve">
-      <c r="A437" t="str" xml:space="preserve">
+    <row r="439" xml:space="preserve">
+      <c r="A439" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Coil, Nb. 1,
 4.10 x 150.0 x coil mm</v>
       </c>
-      <c r="B437" t="str" xml:space="preserve">
+      <c r="B439" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Coil, Nb. 1,
 4.10 x 150.0 x coil mm
 Weight (Kg):1,593
@@ -7383,12 +7414,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="438" xml:space="preserve">
-      <c r="A438" t="str" xml:space="preserve">
+    <row r="440" xml:space="preserve">
+      <c r="A440" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Coil, Nb. 1,
 4.10 x 150.0 x coil mm</v>
       </c>
-      <c r="B438" t="str" xml:space="preserve">
+      <c r="B440" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Coil, Nb. 1,
 4.10 x 150.0 x coil mm
 Weight (Kg):1,438
@@ -7399,12 +7430,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="439" xml:space="preserve">
-      <c r="A439" t="str" xml:space="preserve">
+    <row r="441" xml:space="preserve">
+      <c r="A441" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Coil, Nb. 1,
 4.50 x 220.0 x coil mm</v>
       </c>
-      <c r="B439" t="str" xml:space="preserve">
+      <c r="B441" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Coil, Nb. 1,
 4.50 x 220.0 x coil mm
 Weight (Kg):3,869
@@ -7415,12 +7446,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="440" xml:space="preserve">
-      <c r="A440" t="str" xml:space="preserve">
+    <row r="442" xml:space="preserve">
+      <c r="A442" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Coil, SB-G-400,
 1.00 x 250.9 x coil mm</v>
       </c>
-      <c r="B440" t="str" xml:space="preserve">
+      <c r="B442" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Coil, SB-G-400,
 1.00 x 250.9 x coil mm
 Weight (Kg):1,428
@@ -7431,12 +7462,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="441" xml:space="preserve">
-      <c r="A441" t="str" xml:space="preserve">
+    <row r="443" xml:space="preserve">
+      <c r="A443" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
 0.70 x 1250.0 x 2500.0 mm</v>
       </c>
-      <c r="B441" t="str" xml:space="preserve">
+      <c r="B443" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
 0.70 x 1250.0 x 2500.0 mm
 Weight (Kg):1,756
@@ -7447,12 +7478,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="442" xml:space="preserve">
-      <c r="A442" t="str" xml:space="preserve">
+    <row r="444" xml:space="preserve">
+      <c r="A444" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
 0.80 x 1250.0 x 3000.0 mm</v>
       </c>
-      <c r="B442" t="str" xml:space="preserve">
+      <c r="B444" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
 0.80 x 1250.0 x 3000.0 mm
 Weight (Kg):695
@@ -7463,12 +7494,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="443" xml:space="preserve">
-      <c r="A443" t="str" xml:space="preserve">
+    <row r="445" xml:space="preserve">
+      <c r="A445" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
 0.80 x 1500.0 x 3000.0 mm</v>
       </c>
-      <c r="B443" t="str" xml:space="preserve">
+      <c r="B445" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
 0.80 x 1500.0 x 3000.0 mm
 Weight (Kg):978
@@ -7479,12 +7510,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="444" xml:space="preserve">
-      <c r="A444" t="str" xml:space="preserve">
+    <row r="446" xml:space="preserve">
+      <c r="A446" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
 0.80 x 1500.0 x 3000.0 mm</v>
       </c>
-      <c r="B444" t="str" xml:space="preserve">
+      <c r="B446" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
 0.80 x 1500.0 x 3000.0 mm
 Weight (Kg):1,741
@@ -7495,12 +7526,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="445" xml:space="preserve">
-      <c r="A445" t="str" xml:space="preserve">
+    <row r="447" xml:space="preserve">
+      <c r="A447" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
 0.80 x 1500.0 x 3000.0 mm</v>
       </c>
-      <c r="B445" t="str" xml:space="preserve">
+      <c r="B447" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
 0.80 x 1500.0 x 3000.0 mm
 Weight (Kg):803
@@ -7511,12 +7542,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="446" xml:space="preserve">
-      <c r="A446" t="str" xml:space="preserve">
+    <row r="448" xml:space="preserve">
+      <c r="A448" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
 0.80 x 1500.0 x 3000.0 mm</v>
       </c>
-      <c r="B446" t="str" xml:space="preserve">
+      <c r="B448" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
 0.80 x 1500.0 x 3000.0 mm
 Weight (Kg):1,136
@@ -7527,12 +7558,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="447" xml:space="preserve">
-      <c r="A447" t="str" xml:space="preserve">
+    <row r="449" xml:space="preserve">
+      <c r="A449" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
 0.90 x 1000.0 x 2000.0 mm</v>
       </c>
-      <c r="B447" t="str" xml:space="preserve">
+      <c r="B449" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
 0.90 x 1000.0 x 2000.0 mm
 Weight (Kg):576
@@ -7543,12 +7574,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="448" xml:space="preserve">
-      <c r="A448" t="str" xml:space="preserve">
+    <row r="450" xml:space="preserve">
+      <c r="A450" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
 0.90 x 1500.0 x 3000.0 mm</v>
       </c>
-      <c r="B448" t="str" xml:space="preserve">
+      <c r="B450" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
 0.90 x 1500.0 x 3000.0 mm
 Weight (Kg):553
@@ -7559,12 +7590,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="449" xml:space="preserve">
-      <c r="A449" t="str" xml:space="preserve">
+    <row r="451" xml:space="preserve">
+      <c r="A451" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
 1.10 x 1500.0 x 3000.0 mm</v>
       </c>
-      <c r="B449" t="str" xml:space="preserve">
+      <c r="B451" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
 1.10 x 1500.0 x 3000.0 mm
 Weight (Kg):1,233
@@ -7575,12 +7606,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="450" xml:space="preserve">
-      <c r="A450" t="str" xml:space="preserve">
+    <row r="452" xml:space="preserve">
+      <c r="A452" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
 1.20 x 1250.0 x 2500.0 mm</v>
       </c>
-      <c r="B450" t="str" xml:space="preserve">
+      <c r="B452" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
 1.20 x 1250.0 x 2500.0 mm
 Weight (Kg):685
@@ -7591,12 +7622,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="451" xml:space="preserve">
-      <c r="A451" t="str" xml:space="preserve">
+    <row r="453" xml:space="preserve">
+      <c r="A453" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
 1.50 x 1000.0 x 2000.0 mm</v>
       </c>
-      <c r="B451" t="str" xml:space="preserve">
+      <c r="B453" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
 1.50 x 1000.0 x 2000.0 mm
 Weight (Kg):598
@@ -7607,12 +7638,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="452" xml:space="preserve">
-      <c r="A452" t="str" xml:space="preserve">
+    <row r="454" xml:space="preserve">
+      <c r="A454" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
 1.50 x 1250.0 x 2500.0 mm</v>
       </c>
-      <c r="B452" t="str" xml:space="preserve">
+      <c r="B454" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
 1.50 x 1250.0 x 2500.0 mm
 Weight (Kg):681
@@ -7623,12 +7654,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="453" xml:space="preserve">
-      <c r="A453" t="str" xml:space="preserve">
+    <row r="455" xml:space="preserve">
+      <c r="A455" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
 2.00 x 1000.0 x 2000.0 mm</v>
       </c>
-      <c r="B453" t="str" xml:space="preserve">
+      <c r="B455" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
 2.00 x 1000.0 x 2000.0 mm
 Weight (Kg):2,359
@@ -7639,12 +7670,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="454" xml:space="preserve">
-      <c r="A454" t="str" xml:space="preserve">
+    <row r="456" xml:space="preserve">
+      <c r="A456" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
 2.00 x 1000.0 x 2000.0 mm</v>
       </c>
-      <c r="B454" t="str" xml:space="preserve">
+      <c r="B456" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
 2.00 x 1000.0 x 2000.0 mm
 Weight (Kg):529
@@ -7655,12 +7686,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="455" xml:space="preserve">
-      <c r="A455" t="str" xml:space="preserve">
+    <row r="457" xml:space="preserve">
+      <c r="A457" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
 2.00 x 1000.0 x 2000.0 mm</v>
       </c>
-      <c r="B455" t="str" xml:space="preserve">
+      <c r="B457" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
 2.00 x 1000.0 x 2000.0 mm
 Weight (Kg):889
@@ -7671,12 +7702,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="456" xml:space="preserve">
-      <c r="A456" t="str" xml:space="preserve">
+    <row r="458" xml:space="preserve">
+      <c r="A458" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
 2.00 x 1000.0 x 2000.0 mm</v>
       </c>
-      <c r="B456" t="str" xml:space="preserve">
+      <c r="B458" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
 2.00 x 1000.0 x 2000.0 mm
 Weight (Kg):628
@@ -7687,12 +7718,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="457" xml:space="preserve">
-      <c r="A457" t="str" xml:space="preserve">
+    <row r="459" xml:space="preserve">
+      <c r="A459" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
 2.00 x 1000.0 x 2000.0 mm</v>
       </c>
-      <c r="B457" t="str" xml:space="preserve">
+      <c r="B459" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
 2.00 x 1000.0 x 2000.0 mm
 Weight (Kg):1,968
@@ -7703,12 +7734,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="458" xml:space="preserve">
-      <c r="A458" t="str" xml:space="preserve">
+    <row r="460" xml:space="preserve">
+      <c r="A460" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
 2.00 x 1250.0 x 2500.0 mm</v>
       </c>
-      <c r="B458" t="str" xml:space="preserve">
+      <c r="B460" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
 2.00 x 1250.0 x 2500.0 mm
 Weight (Kg):928
@@ -7719,12 +7750,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="459" xml:space="preserve">
-      <c r="A459" t="str" xml:space="preserve">
+    <row r="461" xml:space="preserve">
+      <c r="A461" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
 2.00 x 1250.0 x 2500.0 mm</v>
       </c>
-      <c r="B459" t="str" xml:space="preserve">
+      <c r="B461" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
 2.00 x 1250.0 x 2500.0 mm
 Weight (Kg):816
@@ -7735,12 +7766,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="460" xml:space="preserve">
-      <c r="A460" t="str" xml:space="preserve">
+    <row r="462" xml:space="preserve">
+      <c r="A462" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
 2.00 x 1250.0 x 2500.0 mm</v>
       </c>
-      <c r="B460" t="str" xml:space="preserve">
+      <c r="B462" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
 2.00 x 1250.0 x 2500.0 mm
 Weight (Kg):976
@@ -7751,12 +7782,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="461" xml:space="preserve">
-      <c r="A461" t="str" xml:space="preserve">
+    <row r="463" xml:space="preserve">
+      <c r="A463" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
 2.00 x 1250.0 x 2500.0 mm</v>
       </c>
-      <c r="B461" t="str" xml:space="preserve">
+      <c r="B463" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
 2.00 x 1250.0 x 2500.0 mm
 Weight (Kg):585
@@ -7767,12 +7798,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="462" xml:space="preserve">
-      <c r="A462" t="str" xml:space="preserve">
+    <row r="464" xml:space="preserve">
+      <c r="A464" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
 2.00 x 1250.0 x 2500.0 mm</v>
       </c>
-      <c r="B462" t="str" xml:space="preserve">
+      <c r="B464" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
 2.00 x 1250.0 x 2500.0 mm
 Weight (Kg):1,956
@@ -7783,12 +7814,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="463" xml:space="preserve">
-      <c r="A463" t="str" xml:space="preserve">
+    <row r="465" xml:space="preserve">
+      <c r="A465" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
 2.00 x 1250.0 x 2500.0 mm</v>
       </c>
-      <c r="B463" t="str" xml:space="preserve">
+      <c r="B465" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
 2.00 x 1250.0 x 2500.0 mm
 Weight (Kg):1,779
@@ -7799,12 +7830,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="464" xml:space="preserve">
-      <c r="A464" t="str" xml:space="preserve">
+    <row r="466" xml:space="preserve">
+      <c r="A466" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
 2.00 x 1500.0 x 3000.0 mm</v>
       </c>
-      <c r="B464" t="str" xml:space="preserve">
+      <c r="B466" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
 2.00 x 1500.0 x 3000.0 mm
 Weight (Kg):693
@@ -7815,12 +7846,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="465" xml:space="preserve">
-      <c r="A465" t="str" xml:space="preserve">
+    <row r="467" xml:space="preserve">
+      <c r="A467" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
 2.00 x 1500.0 x 3000.0 mm</v>
       </c>
-      <c r="B465" t="str" xml:space="preserve">
+      <c r="B467" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
 2.00 x 1500.0 x 3000.0 mm
 Weight (Kg):1,122
@@ -7831,12 +7862,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="466" xml:space="preserve">
-      <c r="A466" t="str" xml:space="preserve">
+    <row r="468" xml:space="preserve">
+      <c r="A468" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
 2.00 x 1500.0 x 3000.0 mm</v>
       </c>
-      <c r="B466" t="str" xml:space="preserve">
+      <c r="B468" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
 2.00 x 1500.0 x 3000.0 mm
 Weight (Kg):1,108
@@ -7847,12 +7878,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="467" xml:space="preserve">
-      <c r="A467" t="str" xml:space="preserve">
+    <row r="469" xml:space="preserve">
+      <c r="A469" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
 2.00 x 1500.0 x 3000.0 mm</v>
       </c>
-      <c r="B467" t="str" xml:space="preserve">
+      <c r="B469" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
 2.00 x 1500.0 x 3000.0 mm
 Weight (Kg):1,836
@@ -7863,12 +7894,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="468" xml:space="preserve">
-      <c r="A468" t="str" xml:space="preserve">
+    <row r="470" xml:space="preserve">
+      <c r="A470" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
 2.00 x 1500.0 x 3000.0 mm</v>
       </c>
-      <c r="B468" t="str" xml:space="preserve">
+      <c r="B470" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
 2.00 x 1500.0 x 3000.0 mm
 Weight (Kg):630
@@ -7879,12 +7910,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="469" xml:space="preserve">
-      <c r="A469" t="str" xml:space="preserve">
+    <row r="471" xml:space="preserve">
+      <c r="A471" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
 2.00 x 1500.0 x 3000.0 mm</v>
       </c>
-      <c r="B469" t="str" xml:space="preserve">
+      <c r="B471" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
 2.00 x 1500.0 x 3000.0 mm
 Weight (Kg):726
@@ -7895,12 +7926,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="470" xml:space="preserve">
-      <c r="A470" t="str" xml:space="preserve">
+    <row r="472" xml:space="preserve">
+      <c r="A472" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
 2.00 x 1500.0 x 3000.0 mm</v>
       </c>
-      <c r="B470" t="str" xml:space="preserve">
+      <c r="B472" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
 2.00 x 1500.0 x 3000.0 mm
 Weight (Kg):565
@@ -7911,12 +7942,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="471" xml:space="preserve">
-      <c r="A471" t="str" xml:space="preserve">
+    <row r="473" xml:space="preserve">
+      <c r="A473" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
 2.00 x 1500.0 x 3000.0 mm</v>
       </c>
-      <c r="B471" t="str" xml:space="preserve">
+      <c r="B473" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
 2.00 x 1500.0 x 3000.0 mm
 Weight (Kg):729
@@ -7927,12 +7958,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="472" xml:space="preserve">
-      <c r="A472" t="str" xml:space="preserve">
+    <row r="474" xml:space="preserve">
+      <c r="A474" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
 2.00 x 1500.0 x 3000.0 mm</v>
       </c>
-      <c r="B472" t="str" xml:space="preserve">
+      <c r="B474" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
 2.00 x 1500.0 x 3000.0 mm
 Weight (Kg):792
@@ -7943,12 +7974,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="473" xml:space="preserve">
-      <c r="A473" t="str" xml:space="preserve">
+    <row r="475" xml:space="preserve">
+      <c r="A475" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
 2.00 x 1500.0 x 3000.0 mm</v>
       </c>
-      <c r="B473" t="str" xml:space="preserve">
+      <c r="B475" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
 2.00 x 1500.0 x 3000.0 mm
 Weight (Kg):637
@@ -7959,12 +7990,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="474" xml:space="preserve">
-      <c r="A474" t="str" xml:space="preserve">
+    <row r="476" xml:space="preserve">
+      <c r="A476" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
 2.00 x 1500.0 x 3000.0 mm</v>
       </c>
-      <c r="B474" t="str" xml:space="preserve">
+      <c r="B476" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
 2.00 x 1500.0 x 3000.0 mm
 Weight (Kg):1,289
@@ -7975,12 +8006,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="475" xml:space="preserve">
-      <c r="A475" t="str" xml:space="preserve">
+    <row r="477" xml:space="preserve">
+      <c r="A477" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
 2.50 x 1500.0 x 3000.0 mm</v>
       </c>
-      <c r="B475" t="str" xml:space="preserve">
+      <c r="B477" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
 2.50 x 1500.0 x 3000.0 mm
 Weight (Kg):1,826
@@ -7991,12 +8022,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="476" xml:space="preserve">
-      <c r="A476" t="str" xml:space="preserve">
+    <row r="478" xml:space="preserve">
+      <c r="A478" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
 2.50 x 1500.0 x 3000.0 mm</v>
       </c>
-      <c r="B476" t="str" xml:space="preserve">
+      <c r="B478" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
 2.50 x 1500.0 x 3000.0 mm
 Weight (Kg):1,040
@@ -8007,12 +8038,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="477" xml:space="preserve">
-      <c r="A477" t="str" xml:space="preserve">
+    <row r="479" xml:space="preserve">
+      <c r="A479" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
 2.50 x 1500.0 x 3000.0 mm</v>
       </c>
-      <c r="B477" t="str" xml:space="preserve">
+      <c r="B479" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
 2.50 x 1500.0 x 3000.0 mm
 Weight (Kg):1,328
@@ -8023,12 +8054,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="478" xml:space="preserve">
-      <c r="A478" t="str" xml:space="preserve">
+    <row r="480" xml:space="preserve">
+      <c r="A480" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
 3.00 x 1000.0 x 2000.0 mm</v>
       </c>
-      <c r="B478" t="str" xml:space="preserve">
+      <c r="B480" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
 3.00 x 1000.0 x 2000.0 mm
 Weight (Kg):940
@@ -8039,12 +8070,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="479" xml:space="preserve">
-      <c r="A479" t="str" xml:space="preserve">
+    <row r="481" xml:space="preserve">
+      <c r="A481" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
 3.00 x 1250.0 x 2500.0 mm</v>
       </c>
-      <c r="B479" t="str" xml:space="preserve">
+      <c r="B481" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
 3.00 x 1250.0 x 2500.0 mm
 Weight (Kg):1,396
@@ -8055,12 +8086,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="480" xml:space="preserve">
-      <c r="A480" t="str" xml:space="preserve">
+    <row r="482" xml:space="preserve">
+      <c r="A482" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
 3.00 x 1250.0 x 2500.0 mm</v>
       </c>
-      <c r="B480" t="str" xml:space="preserve">
+      <c r="B482" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
 3.00 x 1250.0 x 2500.0 mm
 Weight (Kg):2,318
@@ -8071,12 +8102,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="481" xml:space="preserve">
-      <c r="A481" t="str" xml:space="preserve">
+    <row r="483" xml:space="preserve">
+      <c r="A483" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
 3.00 x 1250.0 x 2500.0 mm</v>
       </c>
-      <c r="B481" t="str" xml:space="preserve">
+      <c r="B483" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
 3.00 x 1250.0 x 2500.0 mm
 Weight (Kg):1,074
@@ -8087,12 +8118,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="482" xml:space="preserve">
-      <c r="A482" t="str" xml:space="preserve">
+    <row r="484" xml:space="preserve">
+      <c r="A484" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
 3.00 x 1250.0 x 2500.0 mm</v>
       </c>
-      <c r="B482" t="str" xml:space="preserve">
+      <c r="B484" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
 3.00 x 1250.0 x 2500.0 mm
 Weight (Kg):1,584
@@ -8103,12 +8134,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="483" xml:space="preserve">
-      <c r="A483" t="str" xml:space="preserve">
+    <row r="485" xml:space="preserve">
+      <c r="A485" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
 3.00 x 1250.0 x 2500.0 mm</v>
       </c>
-      <c r="B483" t="str" xml:space="preserve">
+      <c r="B485" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
 3.00 x 1250.0 x 2500.0 mm
 Weight (Kg):1,028
@@ -8119,12 +8150,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="484" xml:space="preserve">
-      <c r="A484" t="str" xml:space="preserve">
+    <row r="486" xml:space="preserve">
+      <c r="A486" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
 3.00 x 1250.0 x 2500.0 mm</v>
       </c>
-      <c r="B484" t="str" xml:space="preserve">
+      <c r="B486" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
 3.00 x 1250.0 x 2500.0 mm
 Weight (Kg):598
@@ -8135,12 +8166,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="485" xml:space="preserve">
-      <c r="A485" t="str" xml:space="preserve">
+    <row r="487" xml:space="preserve">
+      <c r="A487" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
 3.00 x 1340.0 x 2480.0 mm</v>
       </c>
-      <c r="B485" t="str" xml:space="preserve">
+      <c r="B487" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
 3.00 x 1340.0 x 2480.0 mm
 Weight (Kg):1,174
@@ -8151,12 +8182,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="486" xml:space="preserve">
-      <c r="A486" t="str" xml:space="preserve">
+    <row r="488" xml:space="preserve">
+      <c r="A488" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
 3.00 x 1340.0 x 2480.0 mm</v>
       </c>
-      <c r="B486" t="str" xml:space="preserve">
+      <c r="B488" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
 3.00 x 1340.0 x 2480.0 mm
 Weight (Kg):1,020
@@ -8167,12 +8198,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="487" xml:space="preserve">
-      <c r="A487" t="str" xml:space="preserve">
+    <row r="489" xml:space="preserve">
+      <c r="A489" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
 3.00 x 1340.0 x 2480.0 mm</v>
       </c>
-      <c r="B487" t="str" xml:space="preserve">
+      <c r="B489" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
 3.00 x 1340.0 x 2480.0 mm
 Weight (Kg):1,169
@@ -8183,12 +8214,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="488" xml:space="preserve">
-      <c r="A488" t="str" xml:space="preserve">
+    <row r="490" xml:space="preserve">
+      <c r="A490" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
 3.00 x 1340.0 x 2480.0 mm</v>
       </c>
-      <c r="B488" t="str" xml:space="preserve">
+      <c r="B490" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
 3.00 x 1340.0 x 2480.0 mm
 Weight (Kg):1,951
@@ -8199,12 +8230,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="489" xml:space="preserve">
-      <c r="A489" t="str" xml:space="preserve">
+    <row r="491" xml:space="preserve">
+      <c r="A491" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
 5.00 x 1000.0 x 2000.0 mm</v>
       </c>
-      <c r="B489" t="str" xml:space="preserve">
+      <c r="B491" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
 5.00 x 1000.0 x 2000.0 mm
 Weight (Kg):943
@@ -8215,12 +8246,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="490" xml:space="preserve">
-      <c r="A490" t="str" xml:space="preserve">
+    <row r="492" xml:space="preserve">
+      <c r="A492" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
 5.00 x 1000.0 x 2000.0 mm</v>
       </c>
-      <c r="B490" t="str" xml:space="preserve">
+      <c r="B492" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
 5.00 x 1000.0 x 2000.0 mm
 Weight (Kg):947
@@ -8231,12 +8262,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="491" xml:space="preserve">
-      <c r="A491" t="str" xml:space="preserve">
+    <row r="493" xml:space="preserve">
+      <c r="A493" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
 5.00 x 1000.0 x 2000.0 mm</v>
       </c>
-      <c r="B491" t="str" xml:space="preserve">
+      <c r="B493" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
 5.00 x 1000.0 x 2000.0 mm
 Weight (Kg):1,588
@@ -8247,12 +8278,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="492" xml:space="preserve">
-      <c r="A492" t="str" xml:space="preserve">
+    <row r="494" xml:space="preserve">
+      <c r="A494" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
 5.00 x 1250.0 x 2500.0 mm</v>
       </c>
-      <c r="B492" t="str" xml:space="preserve">
+      <c r="B494" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
 5.00 x 1250.0 x 2500.0 mm
 Weight (Kg):742
@@ -8263,12 +8294,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="493" xml:space="preserve">
-      <c r="A493" t="str" xml:space="preserve">
+    <row r="495" xml:space="preserve">
+      <c r="A495" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
 6.00 x 1000.0 x 2000.0 mm</v>
       </c>
-      <c r="B493" t="str" xml:space="preserve">
+      <c r="B495" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
 6.00 x 1000.0 x 2000.0 mm
 Weight (Kg):1,452
@@ -8279,12 +8310,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="494" xml:space="preserve">
-      <c r="A494" t="str" xml:space="preserve">
+    <row r="496" xml:space="preserve">
+      <c r="A496" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
 6.00 x 1000.0 x 2000.0 mm</v>
       </c>
-      <c r="B494" t="str" xml:space="preserve">
+      <c r="B496" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
 6.00 x 1000.0 x 2000.0 mm
 Weight (Kg):1,624
@@ -8295,12 +8326,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="495" xml:space="preserve">
-      <c r="A495" t="str" xml:space="preserve">
+    <row r="497" xml:space="preserve">
+      <c r="A497" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
 6.00 x 1000.0 x 2000.0 mm</v>
       </c>
-      <c r="B495" t="str" xml:space="preserve">
+      <c r="B497" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
 6.00 x 1000.0 x 2000.0 mm
 Weight (Kg):1,434
@@ -8311,12 +8342,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="496" xml:space="preserve">
-      <c r="A496" t="str" xml:space="preserve">
+    <row r="498" xml:space="preserve">
+      <c r="A498" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
 6.00 x 1000.0 x 2000.0 mm</v>
       </c>
-      <c r="B496" t="str" xml:space="preserve">
+      <c r="B498" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
 6.00 x 1000.0 x 2000.0 mm
 Weight (Kg):580
@@ -8327,12 +8358,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="497" xml:space="preserve">
-      <c r="A497" t="str" xml:space="preserve">
+    <row r="499" xml:space="preserve">
+      <c r="A499" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
 6.00 x 1000.0 x 2000.0 mm</v>
       </c>
-      <c r="B497" t="str" xml:space="preserve">
+      <c r="B499" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
 6.00 x 1000.0 x 2000.0 mm
 Weight (Kg):1,054
@@ -8343,12 +8374,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="498" xml:space="preserve">
-      <c r="A498" t="str" xml:space="preserve">
+    <row r="500" xml:space="preserve">
+      <c r="A500" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
 6.00 x 1000.0 x 2000.0 mm</v>
       </c>
-      <c r="B498" t="str" xml:space="preserve">
+      <c r="B500" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
 6.00 x 1000.0 x 2000.0 mm
 Weight (Kg):1,716
@@ -8359,12 +8390,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="499" xml:space="preserve">
-      <c r="A499" t="str" xml:space="preserve">
+    <row r="501" xml:space="preserve">
+      <c r="A501" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
 6.00 x 1000.0 x 2000.0 mm</v>
       </c>
-      <c r="B499" t="str" xml:space="preserve">
+      <c r="B501" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
 6.00 x 1000.0 x 2000.0 mm
 Weight (Kg):1,148
@@ -8375,12 +8406,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="500" xml:space="preserve">
-      <c r="A500" t="str" xml:space="preserve">
+    <row r="502" xml:space="preserve">
+      <c r="A502" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
 6.00 x 1000.0 x 2000.0 mm</v>
       </c>
-      <c r="B500" t="str" xml:space="preserve">
+      <c r="B502" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
 6.00 x 1000.0 x 2000.0 mm
 Weight (Kg):960
@@ -8391,12 +8422,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="501" xml:space="preserve">
-      <c r="A501" t="str" xml:space="preserve">
+    <row r="503" xml:space="preserve">
+      <c r="A503" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
 6.00 x 1000.0 x 2000.0 mm</v>
       </c>
-      <c r="B501" t="str" xml:space="preserve">
+      <c r="B503" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
 6.00 x 1000.0 x 2000.0 mm
 Weight (Kg):772
@@ -8407,12 +8438,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="502" xml:space="preserve">
-      <c r="A502" t="str" xml:space="preserve">
+    <row r="504" xml:space="preserve">
+      <c r="A504" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
 6.00 x 1500.0 x 3000.0 mm</v>
       </c>
-      <c r="B502" t="str" xml:space="preserve">
+      <c r="B504" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
 6.00 x 1500.0 x 3000.0 mm
 Weight (Kg):2,146
@@ -8423,12 +8454,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="503" xml:space="preserve">
-      <c r="A503" t="str" xml:space="preserve">
+    <row r="505" xml:space="preserve">
+      <c r="A505" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
 6.00 x 1500.0 x 3000.0 mm</v>
       </c>
-      <c r="B503" t="str" xml:space="preserve">
+      <c r="B505" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
 6.00 x 1500.0 x 3000.0 mm
 Weight (Kg):1,994
@@ -8439,12 +8470,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="504" xml:space="preserve">
-      <c r="A504" t="str" xml:space="preserve">
+    <row r="506" xml:space="preserve">
+      <c r="A506" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
 6.00 x 1500.0 x 3000.0 mm</v>
       </c>
-      <c r="B504" t="str" xml:space="preserve">
+      <c r="B506" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
 6.00 x 1500.0 x 3000.0 mm
 Weight (Kg):1,488
@@ -8455,12 +8486,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="505" xml:space="preserve">
-      <c r="A505" t="str" xml:space="preserve">
+    <row r="507" xml:space="preserve">
+      <c r="A507" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
 6.00 x 1500.0 x 3000.0 mm</v>
       </c>
-      <c r="B505" t="str" xml:space="preserve">
+      <c r="B507" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
 6.00 x 1500.0 x 3000.0 mm
 Weight (Kg):1,278
@@ -8471,12 +8502,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="506" xml:space="preserve">
-      <c r="A506" t="str" xml:space="preserve">
+    <row r="508" xml:space="preserve">
+      <c r="A508" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
 6.00 x 1500.0 x 3000.0 mm</v>
       </c>
-      <c r="B506" t="str" xml:space="preserve">
+      <c r="B508" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
 6.00 x 1500.0 x 3000.0 mm
 Weight (Kg):1,062
@@ -8487,12 +8518,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="507" xml:space="preserve">
-      <c r="A507" t="str" xml:space="preserve">
+    <row r="509" xml:space="preserve">
+      <c r="A509" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
 6.00 x 1500.0 x 3000.0 mm</v>
       </c>
-      <c r="B507" t="str" xml:space="preserve">
+      <c r="B509" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
 6.00 x 1500.0 x 3000.0 mm
 Weight (Kg):1,526
@@ -8503,12 +8534,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="508" xml:space="preserve">
-      <c r="A508" t="str" xml:space="preserve">
+    <row r="510" xml:space="preserve">
+      <c r="A510" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
 6.00 x 1500.0 x 3000.0 mm</v>
       </c>
-      <c r="B508" t="str" xml:space="preserve">
+      <c r="B510" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
 6.00 x 1500.0 x 3000.0 mm
 Weight (Kg):1,280
@@ -8519,12 +8550,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="509" xml:space="preserve">
-      <c r="A509" t="str" xml:space="preserve">
+    <row r="511" xml:space="preserve">
+      <c r="A511" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
 6.00 x 1510.0 x 3010.0 mm</v>
       </c>
-      <c r="B509" t="str" xml:space="preserve">
+      <c r="B511" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
 6.00 x 1510.0 x 3010.0 mm
 Weight (Kg):1,986
@@ -8535,12 +8566,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="510" xml:space="preserve">
-      <c r="A510" t="str" xml:space="preserve">
+    <row r="512" xml:space="preserve">
+      <c r="A512" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
 6.00 x 1510.0 x 3010.0 mm</v>
       </c>
-      <c r="B510" t="str" xml:space="preserve">
+      <c r="B512" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
 6.00 x 1510.0 x 3010.0 mm
 Weight (Kg):1,784
@@ -8551,12 +8582,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="511" xml:space="preserve">
-      <c r="A511" t="str" xml:space="preserve">
+    <row r="513" xml:space="preserve">
+      <c r="A513" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, Nb. 1,
 6.00 x 1000.0 x 2000.0 mm</v>
       </c>
-      <c r="B511" t="str" xml:space="preserve">
+      <c r="B513" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, Nb. 1,
 6.00 x 1000.0 x 2000.0 mm
 Weight (Kg):570
@@ -8567,12 +8598,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="512" xml:space="preserve">
-      <c r="A512" t="str" xml:space="preserve">
+    <row r="514" xml:space="preserve">
+      <c r="A514" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, SB-G-400,
 1.50 x 1500.0 x 3000.0 mm</v>
       </c>
-      <c r="B512" t="str" xml:space="preserve">
+      <c r="B514" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, SB-G-400,
 1.50 x 1500.0 x 3000.0 mm
 Weight (Kg):723
@@ -8583,12 +8614,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="513" xml:space="preserve">
-      <c r="A513" t="str" xml:space="preserve">
+    <row r="515" xml:space="preserve">
+      <c r="A515" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, SB-G-400,
 2.00 x 1500.0 x 3000.0 mm</v>
       </c>
-      <c r="B513" t="str" xml:space="preserve">
+      <c r="B515" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, SB-G-400,
 2.00 x 1500.0 x 3000.0 mm
 Weight (Kg):819
@@ -8599,12 +8630,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="514" xml:space="preserve">
-      <c r="A514" t="str" xml:space="preserve">
+    <row r="516" xml:space="preserve">
+      <c r="A516" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, SB-G-400,
 2.00 x 1500.0 x 3000.0 mm</v>
       </c>
-      <c r="B514" t="str" xml:space="preserve">
+      <c r="B516" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, SB-G-400,
 2.00 x 1500.0 x 3000.0 mm
 Weight (Kg):1,935
@@ -8615,12 +8646,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="515" xml:space="preserve">
-      <c r="A515" t="str" xml:space="preserve">
+    <row r="517" xml:space="preserve">
+      <c r="A517" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Untrimmed, Coil, 2B,
 1.20 x 1537.0 x coil mm</v>
       </c>
-      <c r="B515" t="str" xml:space="preserve">
+      <c r="B517" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Untrimmed, Coil, 2B,
 1.20 x 1537.0 x coil mm
 Weight (Kg):2,125
@@ -8631,12 +8662,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="516" xml:space="preserve">
-      <c r="A516" t="str" xml:space="preserve">
+    <row r="518" xml:space="preserve">
+      <c r="A518" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Untrimmed, Coil, 2B,
 1.80 x 1530.0 x coil mm</v>
       </c>
-      <c r="B516" t="str" xml:space="preserve">
+      <c r="B518" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Untrimmed, Coil, 2B,
 1.80 x 1530.0 x coil mm
 Weight (Kg):5,263
@@ -8647,12 +8678,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="517" xml:space="preserve">
-      <c r="A517" t="str" xml:space="preserve">
+    <row r="519" xml:space="preserve">
+      <c r="A519" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Untrimmed, Coil, 2B,
 1.80 x 1535.0 x coil mm</v>
       </c>
-      <c r="B517" t="str" xml:space="preserve">
+      <c r="B519" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Untrimmed, Coil, 2B,
 1.80 x 1535.0 x coil mm
 Weight (Kg):2,726
@@ -8663,12 +8694,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="518" xml:space="preserve">
-      <c r="A518" t="str" xml:space="preserve">
+    <row r="520" xml:space="preserve">
+      <c r="A520" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Untrimmed, Coil, 2B,
 2.00 x 1023.0 x coil mm</v>
       </c>
-      <c r="B518" t="str" xml:space="preserve">
+      <c r="B520" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Untrimmed, Coil, 2B,
 2.00 x 1023.0 x coil mm
 Weight (Kg):1,825
@@ -8676,38 +8707,6 @@
 Help
 Location:FABRICA ALGECIRAS
 3,595.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="519" xml:space="preserve">
-      <c r="A519" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Untrimmed, Coil, 2B,
-3.00 x 1552.0 x coil mm</v>
-      </c>
-      <c r="B519" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Untrimmed, Coil, 2B,
-3.00 x 1552.0 x coil mm
-Weight (Kg):2,868
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-3,395.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="520" xml:space="preserve">
-      <c r="A520" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Untrimmed, Coil, 2B,
-6.00 x 1030.0 x coil mm</v>
-      </c>
-      <c r="B520" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Untrimmed, Coil, 2B,
-6.00 x 1030.0 x coil mm
-Weight (Kg):2,225
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-3,395.00 €/ton
 Add to cart</v>
       </c>
     </row>
@@ -8729,10 +8728,42 @@
     </row>
     <row r="522" xml:space="preserve">
       <c r="A522" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Untrimmed, Coil, 2B,
+3.00 x 1552.0 x coil mm</v>
+      </c>
+      <c r="B522" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Untrimmed, Coil, 2B,
+3.00 x 1552.0 x coil mm
+Weight (Kg):2,868
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+3,395.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="523" xml:space="preserve">
+      <c r="A523" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Untrimmed, Coil, 2B,
+6.00 x 1030.0 x coil mm</v>
+      </c>
+      <c r="B523" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Untrimmed, Coil, 2B,
+6.00 x 1030.0 x coil mm
+Weight (Kg):2,225
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+3,395.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="524" xml:space="preserve">
+      <c r="A524" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4571 316Ti-Coil, 2B,
 4.00 x 210.0 x coil mm</v>
       </c>
-      <c r="B522" t="str" xml:space="preserve">
+      <c r="B524" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4571 316Ti-Coil, 2B,
 4.00 x 210.0 x coil mm
 Weight (Kg):3,817
@@ -8740,38 +8771,6 @@
 Help
 Location:FABRICA ALGECIRAS
 3,370.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="523" xml:space="preserve">
-      <c r="A523" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4571 316Ti-Coil, Nb. 1,
-3.00 x 184.0 x coil mm</v>
-      </c>
-      <c r="B523" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4571 316Ti-Coil, Nb. 1,
-3.00 x 184.0 x coil mm
-Weight (Kg):1,794
-Quality:Prime
-Help
-Location:FABRICA ALGECIRAS
-3,270.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="524" xml:space="preserve">
-      <c r="A524" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4571 316Ti-Coil, Nb. 1,
-3.00 x 184.0 x coil mm</v>
-      </c>
-      <c r="B524" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4571 316Ti-Coil, Nb. 1,
-3.00 x 184.0 x coil mm
-Weight (Kg):1,806
-Quality:Prime
-Help
-Location:FABRICA ALGECIRAS
-3,270.00 €/ton
 Add to cart</v>
       </c>
     </row>
@@ -8783,7 +8782,7 @@
       <c r="B525" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4571 316Ti-Coil, Nb. 1,
 3.00 x 184.0 x coil mm
-Weight (Kg):1,808
+Weight (Kg):1,794
 Quality:Prime
 Help
 Location:FABRICA ALGECIRAS
@@ -8794,9 +8793,41 @@
     <row r="526" xml:space="preserve">
       <c r="A526" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4571 316Ti-Coil, Nb. 1,
+3.00 x 184.0 x coil mm</v>
+      </c>
+      <c r="B526" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4571 316Ti-Coil, Nb. 1,
+3.00 x 184.0 x coil mm
+Weight (Kg):1,806
+Quality:Prime
+Help
+Location:FABRICA ALGECIRAS
+3,270.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="527" xml:space="preserve">
+      <c r="A527" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4571 316Ti-Coil, Nb. 1,
+3.00 x 184.0 x coil mm</v>
+      </c>
+      <c r="B527" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4571 316Ti-Coil, Nb. 1,
+3.00 x 184.0 x coil mm
+Weight (Kg):1,808
+Quality:Prime
+Help
+Location:FABRICA ALGECIRAS
+3,270.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="528" xml:space="preserve">
+      <c r="A528" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4571 316Ti-Coil, Nb. 1,
 4.00 x 200.0 x coil mm</v>
       </c>
-      <c r="B526" t="str" xml:space="preserve">
+      <c r="B528" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4571 316Ti-Coil, Nb. 1,
 4.00 x 200.0 x coil mm
 Weight (Kg):1,918
@@ -8807,12 +8838,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="527" xml:space="preserve">
-      <c r="A527" t="str" xml:space="preserve">
+    <row r="529" xml:space="preserve">
+      <c r="A529" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4571 316Ti-Plate, Nb. 1,
 45.00 x 1500.0 x 3000.0 mm</v>
       </c>
-      <c r="B527" t="str" xml:space="preserve">
+      <c r="B529" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4571 316Ti-Plate, Nb. 1,
 45.00 x 1500.0 x 3000.0 mm
 Weight (Kg):1,640
@@ -8820,38 +8851,6 @@
 Help
 Location:FABRICA ALGECIRAS
 4,600.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="528" xml:space="preserve">
-      <c r="A528" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4571 316Ti-Sheet, 2B,
-3.00 x 1000.0 x 2000.0 mm</v>
-      </c>
-      <c r="B528" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4571 316Ti-Sheet, 2B,
-3.00 x 1000.0 x 2000.0 mm
-Weight (Kg):918
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-3,495.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="529" xml:space="preserve">
-      <c r="A529" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4571 316Ti-Sheet, 2B,
-3.00 x 1000.0 x 2000.0 mm</v>
-      </c>
-      <c r="B529" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4571 316Ti-Sheet, 2B,
-3.00 x 1000.0 x 2000.0 mm
-Weight (Kg):518
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-3,495.00 €/ton
 Add to cart</v>
       </c>
     </row>
@@ -8863,7 +8862,7 @@
       <c r="B530" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4571 316Ti-Sheet, 2B,
 3.00 x 1000.0 x 2000.0 mm
-Weight (Kg):848
+Weight (Kg):918
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -8874,9 +8873,41 @@
     <row r="531" xml:space="preserve">
       <c r="A531" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4571 316Ti-Sheet, 2B,
+3.00 x 1000.0 x 2000.0 mm</v>
+      </c>
+      <c r="B531" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4571 316Ti-Sheet, 2B,
+3.00 x 1000.0 x 2000.0 mm
+Weight (Kg):518
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+3,495.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="532" xml:space="preserve">
+      <c r="A532" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4571 316Ti-Sheet, 2B,
+3.00 x 1000.0 x 2000.0 mm</v>
+      </c>
+      <c r="B532" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4571 316Ti-Sheet, 2B,
+3.00 x 1000.0 x 2000.0 mm
+Weight (Kg):848
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+3,495.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="533" xml:space="preserve">
+      <c r="A533" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4571 316Ti-Sheet, 2B,
 5.00 x 1000.0 x 2000.0 mm</v>
       </c>
-      <c r="B531" t="str" xml:space="preserve">
+      <c r="B533" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4571 316Ti-Sheet, 2B,
 5.00 x 1000.0 x 2000.0 mm
 Weight (Kg):1,102
@@ -8887,12 +8918,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="532" xml:space="preserve">
-      <c r="A532" t="str" xml:space="preserve">
+    <row r="534" xml:space="preserve">
+      <c r="A534" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4571 316Ti-Sheet, 2B,
 6.00 x 1000.0 x 2000.0 mm</v>
       </c>
-      <c r="B532" t="str" xml:space="preserve">
+      <c r="B534" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4571 316Ti-Sheet, 2B,
 6.00 x 1000.0 x 2000.0 mm
 Weight (Kg):1,050
@@ -8903,12 +8934,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="533" xml:space="preserve">
-      <c r="A533" t="str" xml:space="preserve">
+    <row r="535" xml:space="preserve">
+      <c r="A535" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4571 316Ti-Sheet, 2B,
 6.00 x 1000.0 x 2000.0 mm</v>
       </c>
-      <c r="B533" t="str" xml:space="preserve">
+      <c r="B535" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4571 316Ti-Sheet, 2B,
 6.00 x 1000.0 x 2000.0 mm
 Weight (Kg):952
@@ -8919,12 +8950,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="534" xml:space="preserve">
-      <c r="A534" t="str" xml:space="preserve">
+    <row r="536" xml:space="preserve">
+      <c r="A536" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4571 316Ti-Sheet, Nb. 1,
 8.00 x 1500.0 x 3000.0 mm</v>
       </c>
-      <c r="B534" t="str" xml:space="preserve">
+      <c r="B536" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4571 316Ti-Sheet, Nb. 1,
 8.00 x 1500.0 x 3000.0 mm
 Weight (Kg):1,136
@@ -8932,38 +8963,6 @@
 Help
 Location:FABRICA ALGECIRAS
 3,495.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="535" xml:space="preserve">
-      <c r="A535" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4541 321-Coil, 2B,
-1.90 x 217.0 x coil mm</v>
-      </c>
-      <c r="B535" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4541 321-Coil, 2B,
-1.90 x 217.0 x coil mm
-Weight (Kg):3,537
-Quality:Prime
-Help
-Location:FABRICA ALGECIRAS
-2,235.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="536" xml:space="preserve">
-      <c r="A536" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4541 321-Coil, 2B,
-1.90 x 217.0 x coil mm</v>
-      </c>
-      <c r="B536" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4541 321-Coil, 2B,
-1.90 x 217.0 x coil mm
-Weight (Kg):3,484
-Quality:Prime
-Help
-Location:FABRICA ALGECIRAS
-2,235.00 €/ton
 Add to cart</v>
       </c>
     </row>
@@ -8991,7 +8990,7 @@
       <c r="B538" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4541 321-Coil, 2B,
 1.90 x 217.0 x coil mm
-Weight (Kg):3,490
+Weight (Kg):3,484
 Quality:Prime
 Help
 Location:FABRICA ALGECIRAS
@@ -9023,7 +9022,7 @@
       <c r="B540" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4541 321-Coil, 2B,
 1.90 x 217.0 x coil mm
-Weight (Kg):3,492
+Weight (Kg):3,490
 Quality:Prime
 Help
 Location:FABRICA ALGECIRAS
@@ -9039,7 +9038,7 @@
       <c r="B541" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4541 321-Coil, 2B,
 1.90 x 217.0 x coil mm
-Weight (Kg):3,480
+Weight (Kg):3,537
 Quality:Prime
 Help
 Location:FABRICA ALGECIRAS
@@ -9050,9 +9049,41 @@
     <row r="542" xml:space="preserve">
       <c r="A542" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4541 321-Coil, 2B,
+1.90 x 217.0 x coil mm</v>
+      </c>
+      <c r="B542" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4541 321-Coil, 2B,
+1.90 x 217.0 x coil mm
+Weight (Kg):3,492
+Quality:Prime
+Help
+Location:FABRICA ALGECIRAS
+2,235.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="543" xml:space="preserve">
+      <c r="A543" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4541 321-Coil, 2B,
+1.90 x 217.0 x coil mm</v>
+      </c>
+      <c r="B543" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4541 321-Coil, 2B,
+1.90 x 217.0 x coil mm
+Weight (Kg):3,480
+Quality:Prime
+Help
+Location:FABRICA ALGECIRAS
+2,235.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="544" xml:space="preserve">
+      <c r="A544" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4541 321-Coil, 2B,
 4.00 x 520.0 x coil mm</v>
       </c>
-      <c r="B542" t="str" xml:space="preserve">
+      <c r="B544" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4541 321-Coil, 2B,
 4.00 x 520.0 x coil mm
 Weight (Kg):7,263
@@ -9063,12 +9094,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="543" xml:space="preserve">
-      <c r="A543" t="str" xml:space="preserve">
+    <row r="545" xml:space="preserve">
+      <c r="A545" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4541 321-Coil, Nb. 1,
 5.00 x 1542.0 x coil mm</v>
       </c>
-      <c r="B543" t="str" xml:space="preserve">
+      <c r="B545" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4541 321-Coil, Nb. 1,
 5.00 x 1542.0 x coil mm
 Weight (Kg):4,890
@@ -9079,12 +9110,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="544" xml:space="preserve">
-      <c r="A544" t="str" xml:space="preserve">
+    <row r="546" xml:space="preserve">
+      <c r="A546" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4541 321-Coil, Nb. 1,
 5.00 x 230.9 x coil mm</v>
       </c>
-      <c r="B544" t="str" xml:space="preserve">
+      <c r="B546" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4541 321-Coil, Nb. 1,
 5.00 x 230.9 x coil mm
 Weight (Kg):4,198
@@ -9095,12 +9126,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="545" xml:space="preserve">
-      <c r="A545" t="str" xml:space="preserve">
+    <row r="547" xml:space="preserve">
+      <c r="A547" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4541 321-Sheet, 2B,
 3.00 x 1000.0 x 2000.0 mm</v>
       </c>
-      <c r="B545" t="str" xml:space="preserve">
+      <c r="B547" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4541 321-Sheet, 2B,
 3.00 x 1000.0 x 2000.0 mm
 Weight (Kg):1,104
@@ -9111,12 +9142,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="546" xml:space="preserve">
-      <c r="A546" t="str" xml:space="preserve">
+    <row r="548" xml:space="preserve">
+      <c r="A548" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4541 321-Sheet, 2B,
 4.00 x 1000.0 x 2000.0 mm</v>
       </c>
-      <c r="B546" t="str" xml:space="preserve">
+      <c r="B548" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4541 321-Sheet, 2B,
 4.00 x 1000.0 x 2000.0 mm
 Weight (Kg):1,552
@@ -9127,12 +9158,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="547" xml:space="preserve">
-      <c r="A547" t="str" xml:space="preserve">
+    <row r="549" xml:space="preserve">
+      <c r="A549" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4541 321-Sheet, 2B,
 6.00 x 1250.0 x 2500.0 mm</v>
       </c>
-      <c r="B547" t="str" xml:space="preserve">
+      <c r="B549" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4541 321-Sheet, 2B,
 6.00 x 1250.0 x 2500.0 mm
 Weight (Kg):1,296
@@ -9143,12 +9174,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="548" xml:space="preserve">
-      <c r="A548" t="str" xml:space="preserve">
+    <row r="550" xml:space="preserve">
+      <c r="A550" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4541 321-Sheet, Nb. 1,
 8.00 x 1000.0 x 2000.0 mm</v>
       </c>
-      <c r="B548" t="str" xml:space="preserve">
+      <c r="B550" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4541 321-Sheet, Nb. 1,
 8.00 x 1000.0 x 2000.0 mm
 Weight (Kg):640
@@ -9159,12 +9190,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="549" xml:space="preserve">
-      <c r="A549" t="str" xml:space="preserve">
+    <row r="551" xml:space="preserve">
+      <c r="A551" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4512 409L-Coil, 2B,
 1.00 x 1304.0 x coil mm</v>
       </c>
-      <c r="B549" t="str" xml:space="preserve">
+      <c r="B551" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4512 409L-Coil, 2B,
 1.00 x 1304.0 x coil mm
 Weight (Kg):10,360
@@ -9175,12 +9206,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="550" xml:space="preserve">
-      <c r="A550" t="str" xml:space="preserve">
+    <row r="552" xml:space="preserve">
+      <c r="A552" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4512 409L-Coil, 2B,
 1.00 x 625.0 x coil mm</v>
       </c>
-      <c r="B550" t="str" xml:space="preserve">
+      <c r="B552" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4512 409L-Coil, 2B,
 1.00 x 625.0 x coil mm
 Weight (Kg):6,700
@@ -9191,12 +9222,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="551" xml:space="preserve">
-      <c r="A551" t="str" xml:space="preserve">
+    <row r="553" xml:space="preserve">
+      <c r="A553" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4512 409L-Coil, 2D,
 2.00 x 1291.0 x coil mm</v>
       </c>
-      <c r="B551" t="str" xml:space="preserve">
+      <c r="B553" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4512 409L-Coil, 2D,
 2.00 x 1291.0 x coil mm
 Weight (Kg):3,579
@@ -9207,12 +9238,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="552" xml:space="preserve">
-      <c r="A552" t="str" xml:space="preserve">
+    <row r="554" xml:space="preserve">
+      <c r="A554" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4512 409L-Coil, 2D,
 2.00 x 150.0 x coil mm</v>
       </c>
-      <c r="B552" t="str" xml:space="preserve">
+      <c r="B554" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4512 409L-Coil, 2D,
 2.00 x 150.0 x coil mm
 Weight (Kg):2,270
@@ -9223,12 +9254,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="553" xml:space="preserve">
-      <c r="A553" t="str" xml:space="preserve">
+    <row r="555" xml:space="preserve">
+      <c r="A555" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4512 409L-Coil, Nb. 1,
 4.00 x 140.0 x coil mm</v>
       </c>
-      <c r="B553" t="str" xml:space="preserve">
+      <c r="B555" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4512 409L-Coil, Nb. 1,
 4.00 x 140.0 x coil mm
 Weight (Kg):2,354
@@ -9239,12 +9270,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="554" xml:space="preserve">
-      <c r="A554" t="str" xml:space="preserve">
+    <row r="556" xml:space="preserve">
+      <c r="A556" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4512 409L-Coil, Nb. 1,
 5.00 x 190.0 x coil mm</v>
       </c>
-      <c r="B554" t="str" xml:space="preserve">
+      <c r="B556" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4512 409L-Coil, Nb. 1,
 5.00 x 190.0 x coil mm
 Weight (Kg):2,447
@@ -9255,12 +9286,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="555" xml:space="preserve">
-      <c r="A555" t="str" xml:space="preserve">
+    <row r="557" xml:space="preserve">
+      <c r="A557" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4512 409L-Coil, Nb. 1,
 6.00 x 270.0 x coil mm</v>
       </c>
-      <c r="B555" t="str" xml:space="preserve">
+      <c r="B557" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4512 409L-Coil, Nb. 1,
 6.00 x 270.0 x coil mm
 Weight (Kg):2,116
@@ -9271,12 +9302,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="556" xml:space="preserve">
-      <c r="A556" t="str" xml:space="preserve">
+    <row r="558" xml:space="preserve">
+      <c r="A558" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4512 409L-Coil, Nb. 1,
 6.00 x 270.0 x coil mm</v>
       </c>
-      <c r="B556" t="str" xml:space="preserve">
+      <c r="B558" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4512 409L-Coil, Nb. 1,
 6.00 x 270.0 x coil mm
 Weight (Kg):1,780
@@ -9287,12 +9318,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="557" xml:space="preserve">
-      <c r="A557" t="str" xml:space="preserve">
+    <row r="559" xml:space="preserve">
+      <c r="A559" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4512 409L-Coil, Nb. 1,
 8.00 x 115.9 x coil mm</v>
       </c>
-      <c r="B557" t="str" xml:space="preserve">
+      <c r="B559" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4512 409L-Coil, Nb. 1,
 8.00 x 115.9 x coil mm
 Weight (Kg):1,238
@@ -9303,12 +9334,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="558" xml:space="preserve">
-      <c r="A558" t="str" xml:space="preserve">
+    <row r="560" xml:space="preserve">
+      <c r="A560" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4512 409L-Coil, Nb. 1,
 8.00 x 125.9 x coil mm</v>
       </c>
-      <c r="B558" t="str" xml:space="preserve">
+      <c r="B560" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4512 409L-Coil, Nb. 1,
 8.00 x 125.9 x coil mm
 Weight (Kg):1,214
@@ -9319,12 +9350,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="559" xml:space="preserve">
-      <c r="A559" t="str" xml:space="preserve">
+    <row r="561" xml:space="preserve">
+      <c r="A561" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4512 409L-Coil, Nb. 1,
 8.00 x 230.9 x coil mm</v>
       </c>
-      <c r="B559" t="str" xml:space="preserve">
+      <c r="B561" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4512 409L-Coil, Nb. 1,
 8.00 x 230.9 x coil mm
 Weight (Kg):2,960
@@ -9335,12 +9366,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="560" xml:space="preserve">
-      <c r="A560" t="str" xml:space="preserve">
+    <row r="562" xml:space="preserve">
+      <c r="A562" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4512 409L-Untrimmed, Coil, 2B,
 1.00 x 625.0 x coil mm</v>
       </c>
-      <c r="B560" t="str" xml:space="preserve">
+      <c r="B562" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4512 409L-Untrimmed, Coil, 2B,
 1.00 x 625.0 x coil mm
 Weight (Kg):3,441
@@ -9351,12 +9382,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="561" xml:space="preserve">
-      <c r="A561" t="str" xml:space="preserve">
+    <row r="563" xml:space="preserve">
+      <c r="A563" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4512 409L-Untrimmed, Coil, 2D,
 1.50 x 1295.0 x coil mm</v>
       </c>
-      <c r="B561" t="str" xml:space="preserve">
+      <c r="B563" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4512 409L-Untrimmed, Coil, 2D,
 1.50 x 1295.0 x coil mm
 Weight (Kg):2,445
@@ -9367,12 +9398,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="562" xml:space="preserve">
-      <c r="A562" t="str" xml:space="preserve">
+    <row r="564" xml:space="preserve">
+      <c r="A564" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, 2B,
 0.70 x 299.9 x coil mm</v>
       </c>
-      <c r="B562" t="str" xml:space="preserve">
+      <c r="B564" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, 2B,
 0.70 x 299.9 x coil mm
 Weight (Kg):2,518
@@ -9383,12 +9414,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="563" xml:space="preserve">
-      <c r="A563" t="str" xml:space="preserve">
+    <row r="565" xml:space="preserve">
+      <c r="A565" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, 2B,
 2.00 x 220.0 x coil mm</v>
       </c>
-      <c r="B563" t="str" xml:space="preserve">
+      <c r="B565" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, 2B,
 2.00 x 220.0 x coil mm
 Weight (Kg):776
@@ -9399,12 +9430,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="564" xml:space="preserve">
-      <c r="A564" t="str" xml:space="preserve">
+    <row r="566" xml:space="preserve">
+      <c r="A566" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, 2D,
 0.50 x 1518.0 x coil mm</v>
       </c>
-      <c r="B564" t="str" xml:space="preserve">
+      <c r="B566" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, 2D,
 0.50 x 1518.0 x coil mm
 Weight (Kg):4,480
@@ -9415,12 +9446,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="565" xml:space="preserve">
-      <c r="A565" t="str" xml:space="preserve">
+    <row r="567" xml:space="preserve">
+      <c r="A567" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, 2D,
 0.70 x 1007.0 x coil mm</v>
       </c>
-      <c r="B565" t="str" xml:space="preserve">
+      <c r="B567" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, 2D,
 0.70 x 1007.0 x coil mm
 Weight (Kg):14,970
@@ -9431,12 +9462,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="566" xml:space="preserve">
-      <c r="A566" t="str" xml:space="preserve">
+    <row r="568" xml:space="preserve">
+      <c r="A568" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, 2D,
 0.70 x 1450.0 x coil mm</v>
       </c>
-      <c r="B566" t="str" xml:space="preserve">
+      <c r="B568" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, 2D,
 0.70 x 1450.0 x coil mm
 Weight (Kg):4,780
@@ -9447,12 +9478,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="567" xml:space="preserve">
-      <c r="A567" t="str" xml:space="preserve">
+    <row r="569" xml:space="preserve">
+      <c r="A569" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, 2D,
 0.70 x 869.0 x coil mm</v>
       </c>
-      <c r="B567" t="str" xml:space="preserve">
+      <c r="B569" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, 2D,
 0.70 x 869.0 x coil mm
 Weight (Kg):13,570
@@ -9463,12 +9494,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="568" xml:space="preserve">
-      <c r="A568" t="str" xml:space="preserve">
+    <row r="570" xml:space="preserve">
+      <c r="A570" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, BA,
 0.70 x 100.9 x coil mm</v>
       </c>
-      <c r="B568" t="str" xml:space="preserve">
+      <c r="B570" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, BA,
 0.70 x 100.9 x coil mm
 Weight (Kg):778
@@ -9479,12 +9510,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="569" xml:space="preserve">
-      <c r="A569" t="str" xml:space="preserve">
+    <row r="571" xml:space="preserve">
+      <c r="A571" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, BA,
 0.70 x 110.9 x coil mm</v>
       </c>
-      <c r="B569" t="str" xml:space="preserve">
+      <c r="B571" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, BA,
 0.70 x 110.9 x coil mm
 Weight (Kg):634
@@ -9495,12 +9526,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="570" xml:space="preserve">
-      <c r="A570" t="str" xml:space="preserve">
+    <row r="572" xml:space="preserve">
+      <c r="A572" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, BA,
 0.70 x 110.9 x coil mm</v>
       </c>
-      <c r="B570" t="str" xml:space="preserve">
+      <c r="B572" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, BA,
 0.70 x 110.9 x coil mm
 Weight (Kg):658
@@ -9511,12 +9542,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="571" xml:space="preserve">
-      <c r="A571" t="str" xml:space="preserve">
+    <row r="573" xml:space="preserve">
+      <c r="A573" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, BA,
 0.70 x 120.0 x coil mm</v>
       </c>
-      <c r="B571" t="str" xml:space="preserve">
+      <c r="B573" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, BA,
 0.70 x 120.0 x coil mm
 Weight (Kg):836
@@ -9527,12 +9558,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="572" xml:space="preserve">
-      <c r="A572" t="str" xml:space="preserve">
+    <row r="574" xml:space="preserve">
+      <c r="A574" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, BA,
 0.70 x 125.0 x coil mm</v>
       </c>
-      <c r="B572" t="str" xml:space="preserve">
+      <c r="B574" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, BA,
 0.70 x 125.0 x coil mm
 Weight (Kg):1,288
@@ -9543,12 +9574,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="573" xml:space="preserve">
-      <c r="A573" t="str" xml:space="preserve">
+    <row r="575" xml:space="preserve">
+      <c r="A575" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, BA,
 0.70 x 125.9 x coil mm</v>
       </c>
-      <c r="B573" t="str" xml:space="preserve">
+      <c r="B575" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, BA,
 0.70 x 125.9 x coil mm
 Weight (Kg):708
@@ -9559,47 +9590,15 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="574" xml:space="preserve">
-      <c r="A574" t="str" xml:space="preserve">
+    <row r="576" xml:space="preserve">
+      <c r="A576" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, BA,
 0.70 x 126.0 x coil mm</v>
       </c>
-      <c r="B574" t="str" xml:space="preserve">
+      <c r="B576" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, BA,
 0.70 x 126.0 x coil mm
 Weight (Kg):804
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-1,000.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="575" xml:space="preserve">
-      <c r="A575" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, BA,
-0.70 x 155.9 x coil mm</v>
-      </c>
-      <c r="B575" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, BA,
-0.70 x 155.9 x coil mm
-Weight (Kg):1,148
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-1,000.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="576" xml:space="preserve">
-      <c r="A576" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, BA,
-0.70 x 175.9 x coil mm</v>
-      </c>
-      <c r="B576" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, BA,
-0.70 x 175.9 x coil mm
-Weight (Kg):944
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -9690,9 +9689,41 @@
     <row r="582" xml:space="preserve">
       <c r="A582" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, BA,
+0.70 x 155.9 x coil mm</v>
+      </c>
+      <c r="B582" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, BA,
+0.70 x 155.9 x coil mm
+Weight (Kg):1,148
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+1,000.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="583" xml:space="preserve">
+      <c r="A583" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, BA,
 0.70 x 175.9 x coil mm</v>
       </c>
-      <c r="B582" t="str" xml:space="preserve">
+      <c r="B583" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, BA,
+0.70 x 175.9 x coil mm
+Weight (Kg):944
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+1,000.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="584" xml:space="preserve">
+      <c r="A584" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, BA,
+0.70 x 175.9 x coil mm</v>
+      </c>
+      <c r="B584" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, BA,
 0.70 x 175.9 x coil mm
 Weight (Kg):1,054
@@ -9703,12 +9734,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="583" xml:space="preserve">
-      <c r="A583" t="str" xml:space="preserve">
+    <row r="585" xml:space="preserve">
+      <c r="A585" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, BA,
 0.70 x 181.9 x coil mm</v>
       </c>
-      <c r="B583" t="str" xml:space="preserve">
+      <c r="B585" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, BA,
 0.70 x 181.9 x coil mm
 Weight (Kg):1,632
@@ -9719,12 +9750,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="584" xml:space="preserve">
-      <c r="A584" t="str" xml:space="preserve">
+    <row r="586" xml:space="preserve">
+      <c r="A586" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, BA,
 0.70 x 195.9 x coil mm</v>
       </c>
-      <c r="B584" t="str" xml:space="preserve">
+      <c r="B586" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, BA,
 0.70 x 195.9 x coil mm
 Weight (Kg):1,174
@@ -9735,12 +9766,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="585" xml:space="preserve">
-      <c r="A585" t="str" xml:space="preserve">
+    <row r="587" xml:space="preserve">
+      <c r="A587" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, BA,
 0.70 x 195.9 x coil mm</v>
       </c>
-      <c r="B585" t="str" xml:space="preserve">
+      <c r="B587" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, BA,
 0.70 x 195.9 x coil mm
 Weight (Kg):1,541
@@ -9751,12 +9782,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="586" xml:space="preserve">
-      <c r="A586" t="str" xml:space="preserve">
+    <row r="588" xml:space="preserve">
+      <c r="A588" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, BA,
 0.70 x 200.9 x coil mm</v>
       </c>
-      <c r="B586" t="str" xml:space="preserve">
+      <c r="B588" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, BA,
 0.70 x 200.9 x coil mm
 Weight (Kg):1,098
@@ -9767,12 +9798,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="587" xml:space="preserve">
-      <c r="A587" t="str" xml:space="preserve">
+    <row r="589" xml:space="preserve">
+      <c r="A589" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, BA,
 0.70 x 260.9 x coil mm</v>
       </c>
-      <c r="B587" t="str" xml:space="preserve">
+      <c r="B589" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, BA,
 0.70 x 260.9 x coil mm
 Weight (Kg):2,121
@@ -9783,12 +9814,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="588" xml:space="preserve">
-      <c r="A588" t="str" xml:space="preserve">
+    <row r="590" xml:space="preserve">
+      <c r="A590" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, BA,
 0.70 x 825.0 x coil mm</v>
       </c>
-      <c r="B588" t="str" xml:space="preserve">
+      <c r="B590" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, BA,
 0.70 x 825.0 x coil mm
 Weight (Kg):5,270
@@ -9799,12 +9830,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="589" xml:space="preserve">
-      <c r="A589" t="str" xml:space="preserve">
+    <row r="591" xml:space="preserve">
+      <c r="A591" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, BA,
 0.70 x 842.0 x coil mm</v>
       </c>
-      <c r="B589" t="str" xml:space="preserve">
+      <c r="B591" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, BA,
 0.70 x 842.0 x coil mm
 Weight (Kg):10,370
@@ -9815,12 +9846,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="590" xml:space="preserve">
-      <c r="A590" t="str" xml:space="preserve">
+    <row r="592" xml:space="preserve">
+      <c r="A592" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, BA,
 0.70 x 855.0 x coil mm</v>
       </c>
-      <c r="B590" t="str" xml:space="preserve">
+      <c r="B592" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, BA,
 0.70 x 855.0 x coil mm
 Weight (Kg):3,990
@@ -9831,12 +9862,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="591" xml:space="preserve">
-      <c r="A591" t="str" xml:space="preserve">
+    <row r="593" xml:space="preserve">
+      <c r="A593" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, BA,
 0.70 x 870.0 x coil mm</v>
       </c>
-      <c r="B591" t="str" xml:space="preserve">
+      <c r="B593" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, BA,
 0.70 x 870.0 x coil mm
 Weight (Kg):13,910
@@ -9847,12 +9878,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="592" xml:space="preserve">
-      <c r="A592" t="str" xml:space="preserve">
+    <row r="594" xml:space="preserve">
+      <c r="A594" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, BA,
 0.70 x 953.0 x coil mm</v>
       </c>
-      <c r="B592" t="str" xml:space="preserve">
+      <c r="B594" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, BA,
 0.70 x 953.0 x coil mm
 Weight (Kg):6,970
@@ -9863,12 +9894,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="593" xml:space="preserve">
-      <c r="A593" t="str" xml:space="preserve">
+    <row r="595" xml:space="preserve">
+      <c r="A595" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, BA,
 1.00 x 530.0 x coil mm</v>
       </c>
-      <c r="B593" t="str" xml:space="preserve">
+      <c r="B595" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, BA,
 1.00 x 530.0 x coil mm
 Weight (Kg):880
@@ -9879,12 +9910,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="594" xml:space="preserve">
-      <c r="A594" t="str" xml:space="preserve">
+    <row r="596" xml:space="preserve">
+      <c r="A596" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, Polished N4-G-180,
 0.90 x 1250.0 x coil mm</v>
       </c>
-      <c r="B594" t="str" xml:space="preserve">
+      <c r="B596" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, Polished N4-G-180,
 0.90 x 1250.0 x coil mm
 Weight (Kg):2,218
@@ -9895,12 +9926,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="595" xml:space="preserve">
-      <c r="A595" t="str" xml:space="preserve">
+    <row r="597" xml:space="preserve">
+      <c r="A597" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, Polished N4-G-180,
 1.20 x 120.0 x coil mm</v>
       </c>
-      <c r="B595" t="str" xml:space="preserve">
+      <c r="B597" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, Polished N4-G-180,
 1.20 x 120.0 x coil mm
 Weight (Kg):1,430
@@ -9911,12 +9942,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="596" xml:space="preserve">
-      <c r="A596" t="str" xml:space="preserve">
+    <row r="598" xml:space="preserve">
+      <c r="A598" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, Polished N4-G-180,
 1.20 x 250.0 x coil mm</v>
       </c>
-      <c r="B596" t="str" xml:space="preserve">
+      <c r="B598" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, Polished N4-G-180,
 1.20 x 250.0 x coil mm
 Weight (Kg):1,902
@@ -9927,12 +9958,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="597" xml:space="preserve">
-      <c r="A597" t="str" xml:space="preserve">
+    <row r="599" xml:space="preserve">
+      <c r="A599" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, Polished N4-G-180,
 1.20 x 250.9 x coil mm</v>
       </c>
-      <c r="B597" t="str" xml:space="preserve">
+      <c r="B599" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, Polished N4-G-180,
 1.20 x 250.9 x coil mm
 Weight (Kg):1,960
@@ -9943,47 +9974,15 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="598" xml:space="preserve">
-      <c r="A598" t="str" xml:space="preserve">
+    <row r="600" xml:space="preserve">
+      <c r="A600" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, Polished N4-G-180,
 1.20 x 250.9 x coil mm</v>
       </c>
-      <c r="B598" t="str" xml:space="preserve">
+      <c r="B600" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, Polished N4-G-180,
 1.20 x 250.9 x coil mm
 Weight (Kg):1,918
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-1,000.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="599" xml:space="preserve">
-      <c r="A599" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, Polished N4-G-180,
-1.20 x 260.9 x coil mm</v>
-      </c>
-      <c r="B599" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, Polished N4-G-180,
-1.20 x 260.9 x coil mm
-Weight (Kg):1,524
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-1,000.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="600" xml:space="preserve">
-      <c r="A600" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, Polished N4-G-180,
-1.20 x 260.9 x coil mm</v>
-      </c>
-      <c r="B600" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, Polished N4-G-180,
-1.20 x 260.9 x coil mm
-Weight (Kg):1,934
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -10009,10 +10008,42 @@
     </row>
     <row r="602" xml:space="preserve">
       <c r="A602" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, Polished N4-G-180,
+1.20 x 260.9 x coil mm</v>
+      </c>
+      <c r="B602" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, Polished N4-G-180,
+1.20 x 260.9 x coil mm
+Weight (Kg):1,524
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+1,000.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="603" xml:space="preserve">
+      <c r="A603" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, Polished N4-G-180,
+1.20 x 260.9 x coil mm</v>
+      </c>
+      <c r="B603" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, Polished N4-G-180,
+1.20 x 260.9 x coil mm
+Weight (Kg):1,934
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+1,000.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="604" xml:space="preserve">
+      <c r="A604" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, SB-G-400,
 0.60 x 134.9 x coil mm</v>
       </c>
-      <c r="B602" t="str" xml:space="preserve">
+      <c r="B604" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, SB-G-400,
 0.60 x 134.9 x coil mm
 Weight (Kg):1,134
@@ -10023,12 +10054,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="603" xml:space="preserve">
-      <c r="A603" t="str" xml:space="preserve">
+    <row r="605" xml:space="preserve">
+      <c r="A605" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, SB-G-400,
 0.60 x 134.9 x coil mm</v>
       </c>
-      <c r="B603" t="str" xml:space="preserve">
+      <c r="B605" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, SB-G-400,
 0.60 x 134.9 x coil mm
 Weight (Kg):962
@@ -10039,12 +10070,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="604" xml:space="preserve">
-      <c r="A604" t="str" xml:space="preserve">
+    <row r="606" xml:space="preserve">
+      <c r="A606" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, SB-G-400,
 0.60 x 245.9 x coil mm</v>
       </c>
-      <c r="B604" t="str" xml:space="preserve">
+      <c r="B606" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, SB-G-400,
 0.60 x 245.9 x coil mm
 Weight (Kg):1,778
@@ -10055,12 +10086,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="605" xml:space="preserve">
-      <c r="A605" t="str" xml:space="preserve">
+    <row r="607" xml:space="preserve">
+      <c r="A607" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, SB-G-400,
 1.00 x 118.9 x coil mm</v>
       </c>
-      <c r="B605" t="str" xml:space="preserve">
+      <c r="B607" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, SB-G-400,
 1.00 x 118.9 x coil mm
 Weight (Kg):754
@@ -10071,12 +10102,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="606" xml:space="preserve">
-      <c r="A606" t="str" xml:space="preserve">
+    <row r="608" xml:space="preserve">
+      <c r="A608" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, SB-G-400,
 1.00 x 118.9 x coil mm</v>
       </c>
-      <c r="B606" t="str" xml:space="preserve">
+      <c r="B608" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, SB-G-400,
 1.00 x 118.9 x coil mm
 Weight (Kg):802
@@ -10087,12 +10118,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="607" xml:space="preserve">
-      <c r="A607" t="str" xml:space="preserve">
+    <row r="609" xml:space="preserve">
+      <c r="A609" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, SB-G-400,
 1.00 x 266.9 x coil mm</v>
       </c>
-      <c r="B607" t="str" xml:space="preserve">
+      <c r="B609" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, SB-G-400,
 1.00 x 266.9 x coil mm
 Weight (Kg):1,322
@@ -10103,12 +10134,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="608" xml:space="preserve">
-      <c r="A608" t="str" xml:space="preserve">
+    <row r="610" xml:space="preserve">
+      <c r="A610" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, SB-G-500,
 0.70 x 245.9 x coil mm</v>
       </c>
-      <c r="B608" t="str" xml:space="preserve">
+      <c r="B610" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, SB-G-500,
 0.70 x 245.9 x coil mm
 Weight (Kg):1,496
@@ -10119,12 +10150,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="609" xml:space="preserve">
-      <c r="A609" t="str" xml:space="preserve">
+    <row r="611" xml:space="preserve">
+      <c r="A611" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, SBA,
 0.70 x 1056.0 x coil mm</v>
       </c>
-      <c r="B609" t="str" xml:space="preserve">
+      <c r="B611" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, SBA,
 0.70 x 1056.0 x coil mm
 Weight (Kg):15,197
@@ -10135,12 +10166,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="610" xml:space="preserve">
-      <c r="A610" t="str" xml:space="preserve">
+    <row r="612" xml:space="preserve">
+      <c r="A612" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, SBA,
 0.70 x 150.9 x coil mm</v>
       </c>
-      <c r="B610" t="str" xml:space="preserve">
+      <c r="B612" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, SBA,
 0.70 x 150.9 x coil mm
 Weight (Kg):1,268
@@ -10151,12 +10182,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="611" xml:space="preserve">
-      <c r="A611" t="str" xml:space="preserve">
+    <row r="613" xml:space="preserve">
+      <c r="A613" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, SBA,
 0.70 x 173.0 x coil mm</v>
       </c>
-      <c r="B611" t="str" xml:space="preserve">
+      <c r="B613" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, SBA,
 0.70 x 173.0 x coil mm
 Weight (Kg):890
@@ -10167,12 +10198,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="612" xml:space="preserve">
-      <c r="A612" t="str" xml:space="preserve">
+    <row r="614" xml:space="preserve">
+      <c r="A614" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, SBA,
 0.70 x 195.9 x coil mm</v>
       </c>
-      <c r="B612" t="str" xml:space="preserve">
+      <c r="B614" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, SBA,
 0.70 x 195.9 x coil mm
 Weight (Kg):962
@@ -10183,12 +10214,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="613" xml:space="preserve">
-      <c r="A613" t="str" xml:space="preserve">
+    <row r="615" xml:space="preserve">
+      <c r="A615" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, SBA,
 0.70 x 682.0 x coil mm</v>
       </c>
-      <c r="B613" t="str" xml:space="preserve">
+      <c r="B615" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, SBA,
 0.70 x 682.0 x coil mm
 Weight (Kg):3,870
@@ -10199,12 +10230,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="614" xml:space="preserve">
-      <c r="A614" t="str" xml:space="preserve">
+    <row r="616" xml:space="preserve">
+      <c r="A616" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, SBA,
 0.70 x 825.0 x coil mm</v>
       </c>
-      <c r="B614" t="str" xml:space="preserve">
+      <c r="B616" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, SBA,
 0.70 x 825.0 x coil mm
 Weight (Kg):6,448
@@ -10215,12 +10246,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="615" xml:space="preserve">
-      <c r="A615" t="str" xml:space="preserve">
+    <row r="617" xml:space="preserve">
+      <c r="A617" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, SBA,
 0.70 x 942.0 x coil mm</v>
       </c>
-      <c r="B615" t="str" xml:space="preserve">
+      <c r="B617" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, SBA,
 0.70 x 942.0 x coil mm
 Weight (Kg):1,810
@@ -10231,12 +10262,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="616" xml:space="preserve">
-      <c r="A616" t="str" xml:space="preserve">
+    <row r="618" xml:space="preserve">
+      <c r="A618" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, SBA,
 0.70 x 948.0 x coil mm</v>
       </c>
-      <c r="B616" t="str" xml:space="preserve">
+      <c r="B618" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, SBA,
 0.70 x 948.0 x coil mm
 Weight (Kg):3,410
@@ -10247,12 +10278,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="617" xml:space="preserve">
-      <c r="A617" t="str" xml:space="preserve">
+    <row r="619" xml:space="preserve">
+      <c r="A619" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, SBA,
 0.70 x 960.0 x coil mm</v>
       </c>
-      <c r="B617" t="str" xml:space="preserve">
+      <c r="B619" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, SBA,
 0.70 x 960.0 x coil mm
 Weight (Kg):2,780
@@ -10263,12 +10294,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="618" xml:space="preserve">
-      <c r="A618" t="str" xml:space="preserve">
+    <row r="620" xml:space="preserve">
+      <c r="A620" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, SBA,
 0.70 x 963.0 x coil mm</v>
       </c>
-      <c r="B618" t="str" xml:space="preserve">
+      <c r="B620" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, SBA,
 0.70 x 963.0 x coil mm
 Weight (Kg):4,570
@@ -10276,38 +10307,6 @@
 Help
 Location:FABRICA ALGECIRAS
 1,325.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="619" xml:space="preserve">
-      <c r="A619" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Disk, BA,
-0.60 x 550.0 x 0.0 mm</v>
-      </c>
-      <c r="B619" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Disk, BA,
-0.60 x 550.0 x 0.0 mm
-Weight (Kg):578
-Quality:Prime
-Help
-Location:FABRICA ALGECIRAS
-1,900.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="620" xml:space="preserve">
-      <c r="A620" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Disk, BA,
-0.60 x 550.0 x 0.0 mm</v>
-      </c>
-      <c r="B620" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Disk, BA,
-0.60 x 550.0 x 0.0 mm
-Weight (Kg):572
-Quality:Prime
-Help
-Location:FABRICA ALGECIRAS
-1,900.00 €/ton
 Add to cart</v>
       </c>
     </row>
@@ -10319,7 +10318,7 @@
       <c r="B621" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Disk, BA,
 0.60 x 550.0 x 0.0 mm
-Weight (Kg):576
+Weight (Kg):578
 Quality:Prime
 Help
 Location:FABRICA ALGECIRAS
@@ -10335,7 +10334,7 @@
       <c r="B622" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Disk, BA,
 0.60 x 550.0 x 0.0 mm
-Weight (Kg):578
+Weight (Kg):572
 Quality:Prime
 Help
 Location:FABRICA ALGECIRAS
@@ -10351,7 +10350,7 @@
       <c r="B623" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Disk, BA,
 0.60 x 550.0 x 0.0 mm
-Weight (Kg):582
+Weight (Kg):576
 Quality:Prime
 Help
 Location:FABRICA ALGECIRAS
@@ -10361,10 +10360,42 @@
     </row>
     <row r="624" xml:space="preserve">
       <c r="A624" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Disk, BA,
+0.60 x 550.0 x 0.0 mm</v>
+      </c>
+      <c r="B624" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Disk, BA,
+0.60 x 550.0 x 0.0 mm
+Weight (Kg):578
+Quality:Prime
+Help
+Location:FABRICA ALGECIRAS
+1,900.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="625" xml:space="preserve">
+      <c r="A625" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Disk, BA,
+0.60 x 550.0 x 0.0 mm</v>
+      </c>
+      <c r="B625" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Disk, BA,
+0.60 x 550.0 x 0.0 mm
+Weight (Kg):582
+Quality:Prime
+Help
+Location:FABRICA ALGECIRAS
+1,900.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="626" xml:space="preserve">
+      <c r="A626" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Sheet, 2B,
 2.00 x 1250.0 x 2500.0 mm</v>
       </c>
-      <c r="B624" t="str" xml:space="preserve">
+      <c r="B626" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Sheet, 2B,
 2.00 x 1250.0 x 2500.0 mm
 Weight (Kg):619
@@ -10375,12 +10406,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="625" xml:space="preserve">
-      <c r="A625" t="str" xml:space="preserve">
+    <row r="627" xml:space="preserve">
+      <c r="A627" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Sheet, 2B,
 3.00 x 1250.0 x 2500.0 mm</v>
       </c>
-      <c r="B625" t="str" xml:space="preserve">
+      <c r="B627" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Sheet, 2B,
 3.00 x 1250.0 x 2500.0 mm
 Weight (Kg):566
@@ -10391,12 +10422,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="626" xml:space="preserve">
-      <c r="A626" t="str" xml:space="preserve">
+    <row r="628" xml:space="preserve">
+      <c r="A628" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Sheet, 2B,
 3.00 x 1250.0 x 2500.0 mm</v>
       </c>
-      <c r="B626" t="str" xml:space="preserve">
+      <c r="B628" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Sheet, 2B,
 3.00 x 1250.0 x 2500.0 mm
 Weight (Kg):640
@@ -10407,12 +10438,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="627" xml:space="preserve">
-      <c r="A627" t="str" xml:space="preserve">
+    <row r="629" xml:space="preserve">
+      <c r="A629" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Sheet, BA,
 0.70 x 1250.0 x 2500.0 mm</v>
       </c>
-      <c r="B627" t="str" xml:space="preserve">
+      <c r="B629" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Sheet, BA,
 0.70 x 1250.0 x 2500.0 mm
 Weight (Kg):766
@@ -10423,12 +10454,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="628" xml:space="preserve">
-      <c r="A628" t="str" xml:space="preserve">
+    <row r="630" xml:space="preserve">
+      <c r="A630" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Sheet, SB-G-400,
 1.00 x 1500.0 x 3000.0 mm</v>
       </c>
-      <c r="B628" t="str" xml:space="preserve">
+      <c r="B630" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Sheet, SB-G-400,
 1.00 x 1500.0 x 3000.0 mm
 Weight (Kg):1,940
@@ -10439,12 +10470,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="629" xml:space="preserve">
-      <c r="A629" t="str" xml:space="preserve">
+    <row r="631" xml:space="preserve">
+      <c r="A631" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Untrimmed, Coil, 1/4 HT,
 3.00 x 1292.0 x coil mm</v>
       </c>
-      <c r="B629" t="str" xml:space="preserve">
+      <c r="B631" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Untrimmed, Coil, 1/4 HT,
 3.00 x 1292.0 x coil mm
 Weight (Kg):3,641
@@ -10455,12 +10486,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="630" xml:space="preserve">
-      <c r="A630" t="str" xml:space="preserve">
+    <row r="632" xml:space="preserve">
+      <c r="A632" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Untrimmed, Coil, 2B,
 1.20 x 1500.0 x coil mm</v>
       </c>
-      <c r="B630" t="str" xml:space="preserve">
+      <c r="B632" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Untrimmed, Coil, 2B,
 1.20 x 1500.0 x coil mm
 Weight (Kg):4,750
@@ -10471,12 +10502,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="631" xml:space="preserve">
-      <c r="A631" t="str" xml:space="preserve">
+    <row r="633" xml:space="preserve">
+      <c r="A633" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Untrimmed, Coil, 2D, ET-100
 0.50 x 1250.0 x coil mm</v>
       </c>
-      <c r="B631" t="str" xml:space="preserve">
+      <c r="B633" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Untrimmed, Coil, 2D, ET-100
 0.50 x 1250.0 x coil mm
 Weight (Kg):5,160
@@ -10487,12 +10518,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="632" xml:space="preserve">
-      <c r="A632" t="str" xml:space="preserve">
+    <row r="634" xml:space="preserve">
+      <c r="A634" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Untrimmed, Coil, 2D, ET-100
 0.50 x 1250.0 x coil mm</v>
       </c>
-      <c r="B632" t="str" xml:space="preserve">
+      <c r="B634" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Untrimmed, Coil, 2D, ET-100
 0.50 x 1250.0 x coil mm
 Weight (Kg):3,695
@@ -10503,12 +10534,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="633" xml:space="preserve">
-      <c r="A633" t="str" xml:space="preserve">
+    <row r="635" xml:space="preserve">
+      <c r="A635" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Untrimmed, Coil, BA,
 0.60 x 1246.0 x coil mm</v>
       </c>
-      <c r="B633" t="str" xml:space="preserve">
+      <c r="B635" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Untrimmed, Coil, BA,
 0.60 x 1246.0 x coil mm
 Weight (Kg):2,585
@@ -10519,12 +10550,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="634" xml:space="preserve">
-      <c r="A634" t="str" xml:space="preserve">
+    <row r="636" xml:space="preserve">
+      <c r="A636" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Untrimmed, Coil, BA,
 1.00 x 1028.0 x coil mm</v>
       </c>
-      <c r="B634" t="str" xml:space="preserve">
+      <c r="B636" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Untrimmed, Coil, BA,
 1.00 x 1028.0 x coil mm
 Weight (Kg):2,430
@@ -10535,28 +10566,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="635" xml:space="preserve">
-      <c r="A635" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Untrimmed, Coil, 2B,
-0.40 x 1264.0 x coil mm</v>
-      </c>
-      <c r="B635" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Untrimmed, Coil, 2B,
-0.40 x 1264.0 x coil mm
-Weight (Kg):5,720
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-1,125.00 €/ton
-Out of Stock</v>
-      </c>
-    </row>
-    <row r="636" xml:space="preserve">
-      <c r="A636" t="str" xml:space="preserve">
+    <row r="637" xml:space="preserve">
+      <c r="A637" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Untrimmed, Coil, 2B,
 0.40 x 1273.0 x coil mm</v>
       </c>
-      <c r="B636" t="str" xml:space="preserve">
+      <c r="B637" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Untrimmed, Coil, 2B,
 0.40 x 1273.0 x coil mm
 Weight (Kg):5,176
@@ -10565,22 +10580,6 @@
 Location:FABRICA ALGECIRAS
 1,325.00 €/ton
 Reserved</v>
-      </c>
-    </row>
-    <row r="637" xml:space="preserve">
-      <c r="A637" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Untrimmed, Coil, BA,
-0.50 x 1015.0 x coil mm</v>
-      </c>
-      <c r="B637" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Untrimmed, Coil, BA,
-0.50 x 1015.0 x coil mm
-Weight (Kg):2,340
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-1,125.00 €/ton
-Out of Stock</v>
       </c>
     </row>
     <row r="638" xml:space="preserve">

--- a/scraped_data.xlsx
+++ b/scraped_data.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B757"/>
+  <dimension ref="A1:B756"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -2904,10 +2904,26 @@
     </row>
     <row r="158" xml:space="preserve">
       <c r="A158" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4301 304DDQ-Coil, BA,
+0.70 x 265.9 x coil mm</v>
+      </c>
+      <c r="B158" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4301 304DDQ-Coil, BA,
+0.70 x 265.9 x coil mm
+Weight (Kg):2,906
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,075.00 €/ton
+Out of Stock</v>
+      </c>
+    </row>
+    <row r="159" xml:space="preserve">
+      <c r="A159" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Coil, 2B,
 0.80 x 150.9 x coil mm</v>
       </c>
-      <c r="B158" t="str" xml:space="preserve">
+      <c r="B159" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Coil, 2B,
 0.80 x 150.9 x coil mm
 Weight (Kg):670
@@ -2915,15 +2931,15 @@
 Help
 Location:FABRICA ALGECIRAS
 2,075.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="159" xml:space="preserve">
-      <c r="A159" t="str" xml:space="preserve">
+Reserved</v>
+      </c>
+    </row>
+    <row r="160" xml:space="preserve">
+      <c r="A160" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Coil, 2B,
 1.00 x 125.9 x coil mm</v>
       </c>
-      <c r="B159" t="str" xml:space="preserve">
+      <c r="B160" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Coil, 2B,
 1.00 x 125.9 x coil mm
 Weight (Kg):568
@@ -2931,15 +2947,15 @@
 Help
 Location:FABRICA ALGECIRAS
 2,075.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="160" xml:space="preserve">
-      <c r="A160" t="str" xml:space="preserve">
+Reserved</v>
+      </c>
+    </row>
+    <row r="161" xml:space="preserve">
+      <c r="A161" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Coil, 2B,
 1.00 x 135.9 x coil mm</v>
       </c>
-      <c r="B160" t="str" xml:space="preserve">
+      <c r="B161" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Coil, 2B,
 1.00 x 135.9 x coil mm
 Weight (Kg):538
@@ -2947,23 +2963,7 @@
 Help
 Location:FABRICA ALGECIRAS
 2,075.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="161" xml:space="preserve">
-      <c r="A161" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4301 304DDQ-Coil, BA,
-0.70 x 265.9 x coil mm</v>
-      </c>
-      <c r="B161" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4301 304DDQ-Coil, BA,
-0.70 x 265.9 x coil mm
-Weight (Kg):2,906
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-2,075.00 €/ton
-Out of Stock</v>
+Reserved</v>
       </c>
     </row>
     <row r="162" xml:space="preserve">
@@ -7064,10 +7064,26 @@
     </row>
     <row r="418" xml:space="preserve">
       <c r="A418" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Coil, 2B,
+1.50 x 160.9 x coil mm</v>
+      </c>
+      <c r="B418" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Coil, 2B,
+1.50 x 160.9 x coil mm
+Weight (Kg):848
+Quality:Prime
+Help
+Location:FABRICA ALGECIRAS
+3,270.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="419" xml:space="preserve">
+      <c r="A419" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Untrimmed, Coil,
 0.50 x 1272.0 x coil mm</v>
       </c>
-      <c r="B418" t="str" xml:space="preserve">
+      <c r="B419" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Untrimmed, Coil,
 0.50 x 1272.0 x coil mm
 Weight (Kg):5,960
@@ -7078,12 +7094,12 @@
 Reserved</v>
       </c>
     </row>
-    <row r="419" xml:space="preserve">
-      <c r="A419" t="str" xml:space="preserve">
+    <row r="420" xml:space="preserve">
+      <c r="A420" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Untrimmed, Coil, 2B,
 0.40 x 1017.0 x coil mm</v>
       </c>
-      <c r="B419" t="str" xml:space="preserve">
+      <c r="B420" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Untrimmed, Coil, 2B,
 0.40 x 1017.0 x coil mm
 Weight (Kg):9,900
@@ -7094,12 +7110,12 @@
 Reserved</v>
       </c>
     </row>
-    <row r="420" xml:space="preserve">
-      <c r="A420" t="str" xml:space="preserve">
+    <row r="421" xml:space="preserve">
+      <c r="A421" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Untrimmed, Coil, BA,
 0.80 x 1277.0 x coil mm</v>
       </c>
-      <c r="B420" t="str" xml:space="preserve">
+      <c r="B421" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Untrimmed, Coil, BA,
 0.80 x 1277.0 x coil mm
 Weight (Kg):5,250
@@ -7110,32 +7126,16 @@
 Reserved</v>
       </c>
     </row>
-    <row r="421" xml:space="preserve">
-      <c r="A421" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Untrimmed, Coil, BA,
-1.50 x 1250.0 x coil mm</v>
-      </c>
-      <c r="B421" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Untrimmed, Coil, BA,
-1.50 x 1250.0 x coil mm
-Weight (Kg):3,285
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-2,050.00 €/ton
-Out of Stock</v>
-      </c>
-    </row>
     <row r="422" xml:space="preserve">
       <c r="A422" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Coil, 2B,
-1.50 x 160.9 x coil mm</v>
+1.50 x 230.9 x coil mm</v>
       </c>
       <c r="B422" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Coil, 2B,
-1.50 x 160.9 x coil mm
-Weight (Kg):848
-Quality:Prime
+1.50 x 230.9 x coil mm
+Weight (Kg):1,044
+Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
 3,270.00 €/ton
@@ -7145,48 +7145,48 @@
     <row r="423" xml:space="preserve">
       <c r="A423" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Coil, 2B,
-1.50 x 230.9 x coil mm</v>
+2.00 x 1498.0 x coil mm</v>
       </c>
       <c r="B423" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Coil, 2B,
-1.50 x 230.9 x coil mm
-Weight (Kg):1,044
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-3,270.00 €/ton
+2.00 x 1498.0 x coil mm
+Weight (Kg):2,770
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+3,395.00 €/ton
 Add to cart</v>
       </c>
     </row>
     <row r="424" xml:space="preserve">
       <c r="A424" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Coil, 2B,
-2.00 x 1498.0 x coil mm</v>
+5.00 x 1250.0 x coil mm</v>
       </c>
       <c r="B424" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Coil, 2B,
-2.00 x 1498.0 x coil mm
-Weight (Kg):2,770
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-3,395.00 €/ton
+5.00 x 1250.0 x coil mm
+Weight (Kg):12,055
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+3,375.00 €/ton
 Add to cart</v>
       </c>
     </row>
     <row r="425" xml:space="preserve">
       <c r="A425" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Coil, 2B,
-5.00 x 1250.0 x coil mm</v>
+5.00 x 240.0 x coil mm</v>
       </c>
       <c r="B425" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Coil, 2B,
-5.00 x 1250.0 x coil mm
-Weight (Kg):12,055
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-3,375.00 €/ton
+5.00 x 240.0 x coil mm
+Weight (Kg):2,314
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+3,270.00 €/ton
 Add to cart</v>
       </c>
     </row>
@@ -7198,7 +7198,7 @@
       <c r="B426" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Coil, 2B,
 5.00 x 240.0 x coil mm
-Weight (Kg):2,314
+Weight (Kg):2,237
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -7209,32 +7209,32 @@
     <row r="427" xml:space="preserve">
       <c r="A427" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Coil, 2B,
-5.00 x 240.0 x coil mm</v>
+6.00 x 1500.0 x coil mm</v>
       </c>
       <c r="B427" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Coil, 2B,
-5.00 x 240.0 x coil mm
-Weight (Kg):2,237
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-3,270.00 €/ton
+6.00 x 1500.0 x coil mm
+Weight (Kg):2,016
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+3,395.00 €/ton
 Add to cart</v>
       </c>
     </row>
     <row r="428" xml:space="preserve">
       <c r="A428" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Coil, 2B,
-6.00 x 1500.0 x coil mm</v>
+6.00 x 250.9 x coil mm</v>
       </c>
       <c r="B428" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Coil, 2B,
-6.00 x 1500.0 x coil mm
-Weight (Kg):2,016
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-3,395.00 €/ton
+6.00 x 250.9 x coil mm
+Weight (Kg):548
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+3,270.00 €/ton
 Add to cart</v>
       </c>
     </row>
@@ -7246,7 +7246,7 @@
       <c r="B429" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Coil, 2B,
 6.00 x 250.9 x coil mm
-Weight (Kg):548
+Weight (Kg):1,880
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -7256,13 +7256,13 @@
     </row>
     <row r="430" xml:space="preserve">
       <c r="A430" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Coil, 2B,
-6.00 x 250.9 x coil mm</v>
+        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Coil, 2D,
+3.30 x 112.0 x coil mm</v>
       </c>
       <c r="B430" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Coil, 2B,
-6.00 x 250.9 x coil mm
-Weight (Kg):1,880
+        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Coil, 2D,
+3.30 x 112.0 x coil mm
+Weight (Kg):1,017
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -7278,8 +7278,8 @@
       <c r="B431" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Coil, 2D,
 3.30 x 112.0 x coil mm
-Weight (Kg):1,017
-Quality:Prime-2
+Weight (Kg):878
+Quality:Prime
 Help
 Location:FABRICA ALGECIRAS
 3,270.00 €/ton
@@ -7289,13 +7289,13 @@
     <row r="432" xml:space="preserve">
       <c r="A432" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Coil, 2D,
-3.30 x 112.0 x coil mm</v>
+3.30 x 449.0 x coil mm</v>
       </c>
       <c r="B432" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Coil, 2D,
-3.30 x 112.0 x coil mm
-Weight (Kg):878
-Quality:Prime
+3.30 x 449.0 x coil mm
+Weight (Kg):1,850
+Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
 3,270.00 €/ton
@@ -7310,7 +7310,7 @@
       <c r="B433" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Coil, 2D,
 3.30 x 449.0 x coil mm
-Weight (Kg):1,850
+Weight (Kg):1,854
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -7320,14 +7320,14 @@
     </row>
     <row r="434" xml:space="preserve">
       <c r="A434" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Coil, 2D,
-3.30 x 449.0 x coil mm</v>
+        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Coil, BA,
+0.40 x 295.9 x coil mm</v>
       </c>
       <c r="B434" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Coil, 2D,
-3.30 x 449.0 x coil mm
-Weight (Kg):1,854
-Quality:Prime-2
+        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Coil, BA,
+0.40 x 295.9 x coil mm
+Weight (Kg):662
+Quality:Prime
 Help
 Location:FABRICA ALGECIRAS
 3,270.00 €/ton
@@ -7342,7 +7342,7 @@
       <c r="B435" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Coil, BA,
 0.40 x 295.9 x coil mm
-Weight (Kg):662
+Weight (Kg):650
 Quality:Prime
 Help
 Location:FABRICA ALGECIRAS
@@ -7353,25 +7353,9 @@
     <row r="436" xml:space="preserve">
       <c r="A436" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Coil, BA,
-0.40 x 295.9 x coil mm</v>
+0.50 x 160.0 x coil mm</v>
       </c>
       <c r="B436" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Coil, BA,
-0.40 x 295.9 x coil mm
-Weight (Kg):650
-Quality:Prime
-Help
-Location:FABRICA ALGECIRAS
-3,270.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="437" xml:space="preserve">
-      <c r="A437" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Coil, BA,
-0.50 x 160.0 x coil mm</v>
-      </c>
-      <c r="B437" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Coil, BA,
 0.50 x 160.0 x coil mm
 Weight (Kg):1,066
@@ -7382,16 +7366,32 @@
 Add to cart</v>
       </c>
     </row>
+    <row r="437" xml:space="preserve">
+      <c r="A437" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Coil, Nb. 1,
+3.70 x 310.0 x coil mm</v>
+      </c>
+      <c r="B437" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Coil, Nb. 1,
+3.70 x 310.0 x coil mm
+Weight (Kg):5,921
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+3,170.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
     <row r="438" xml:space="preserve">
       <c r="A438" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Coil, Nb. 1,
-3.70 x 310.0 x coil mm</v>
+4.10 x 150.0 x coil mm</v>
       </c>
       <c r="B438" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Coil, Nb. 1,
-3.70 x 310.0 x coil mm
-Weight (Kg):5,921
-Quality:Prime-2
+4.10 x 150.0 x coil mm
+Weight (Kg):1,593
+Quality:Prime
 Help
 Location:FABRICA ALGECIRAS
 3,170.00 €/ton
@@ -7406,7 +7406,7 @@
       <c r="B439" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Coil, Nb. 1,
 4.10 x 150.0 x coil mm
-Weight (Kg):1,593
+Weight (Kg):1,438
 Quality:Prime
 Help
 Location:FABRICA ALGECIRAS
@@ -7417,25 +7417,9 @@
     <row r="440" xml:space="preserve">
       <c r="A440" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Coil, Nb. 1,
-4.10 x 150.0 x coil mm</v>
+4.50 x 220.0 x coil mm</v>
       </c>
       <c r="B440" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Coil, Nb. 1,
-4.10 x 150.0 x coil mm
-Weight (Kg):1,438
-Quality:Prime
-Help
-Location:FABRICA ALGECIRAS
-3,170.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="441" xml:space="preserve">
-      <c r="A441" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Coil, Nb. 1,
-4.50 x 220.0 x coil mm</v>
-      </c>
-      <c r="B441" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Coil, Nb. 1,
 4.50 x 220.0 x coil mm
 Weight (Kg):3,869
@@ -7446,12 +7430,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="442" xml:space="preserve">
-      <c r="A442" t="str" xml:space="preserve">
+    <row r="441" xml:space="preserve">
+      <c r="A441" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Coil, SB-G-400,
 1.00 x 250.9 x coil mm</v>
       </c>
-      <c r="B442" t="str" xml:space="preserve">
+      <c r="B441" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Coil, SB-G-400,
 1.00 x 250.9 x coil mm
 Weight (Kg):1,428
@@ -7462,15 +7446,31 @@
 Add to cart</v>
       </c>
     </row>
+    <row r="442" xml:space="preserve">
+      <c r="A442" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
+0.70 x 1250.0 x 2500.0 mm</v>
+      </c>
+      <c r="B442" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
+0.70 x 1250.0 x 2500.0 mm
+Weight (Kg):1,756
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+3,395.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
     <row r="443" xml:space="preserve">
       <c r="A443" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
-0.70 x 1250.0 x 2500.0 mm</v>
+0.80 x 1250.0 x 3000.0 mm</v>
       </c>
       <c r="B443" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
-0.70 x 1250.0 x 2500.0 mm
-Weight (Kg):1,756
+0.80 x 1250.0 x 3000.0 mm
+Weight (Kg):695
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -7481,12 +7481,12 @@
     <row r="444" xml:space="preserve">
       <c r="A444" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
-0.80 x 1250.0 x 3000.0 mm</v>
+0.80 x 1500.0 x 3000.0 mm</v>
       </c>
       <c r="B444" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
-0.80 x 1250.0 x 3000.0 mm
-Weight (Kg):695
+0.80 x 1500.0 x 3000.0 mm
+Weight (Kg):978
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -7502,7 +7502,7 @@
       <c r="B445" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
 0.80 x 1500.0 x 3000.0 mm
-Weight (Kg):978
+Weight (Kg):1,741
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -7518,7 +7518,7 @@
       <c r="B446" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
 0.80 x 1500.0 x 3000.0 mm
-Weight (Kg):1,741
+Weight (Kg):803
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -7534,7 +7534,7 @@
       <c r="B447" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
 0.80 x 1500.0 x 3000.0 mm
-Weight (Kg):803
+Weight (Kg):1,136
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -7545,12 +7545,12 @@
     <row r="448" xml:space="preserve">
       <c r="A448" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
-0.80 x 1500.0 x 3000.0 mm</v>
+0.90 x 1000.0 x 2000.0 mm</v>
       </c>
       <c r="B448" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
-0.80 x 1500.0 x 3000.0 mm
-Weight (Kg):1,136
+0.90 x 1000.0 x 2000.0 mm
+Weight (Kg):576
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -7561,12 +7561,12 @@
     <row r="449" xml:space="preserve">
       <c r="A449" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
-0.90 x 1000.0 x 2000.0 mm</v>
+0.90 x 1500.0 x 3000.0 mm</v>
       </c>
       <c r="B449" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
-0.90 x 1000.0 x 2000.0 mm
-Weight (Kg):576
+0.90 x 1500.0 x 3000.0 mm
+Weight (Kg):553
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -7577,12 +7577,12 @@
     <row r="450" xml:space="preserve">
       <c r="A450" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
-0.90 x 1500.0 x 3000.0 mm</v>
+1.10 x 1500.0 x 3000.0 mm</v>
       </c>
       <c r="B450" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
-0.90 x 1500.0 x 3000.0 mm
-Weight (Kg):553
+1.10 x 1500.0 x 3000.0 mm
+Weight (Kg):1,233
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -7593,12 +7593,12 @@
     <row r="451" xml:space="preserve">
       <c r="A451" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
-1.10 x 1500.0 x 3000.0 mm</v>
+1.20 x 1250.0 x 2500.0 mm</v>
       </c>
       <c r="B451" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
-1.10 x 1500.0 x 3000.0 mm
-Weight (Kg):1,233
+1.20 x 1250.0 x 2500.0 mm
+Weight (Kg):685
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -7609,12 +7609,12 @@
     <row r="452" xml:space="preserve">
       <c r="A452" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
-1.20 x 1250.0 x 2500.0 mm</v>
+1.50 x 1000.0 x 2000.0 mm</v>
       </c>
       <c r="B452" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
-1.20 x 1250.0 x 2500.0 mm
-Weight (Kg):685
+1.50 x 1000.0 x 2000.0 mm
+Weight (Kg):598
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -7625,12 +7625,12 @@
     <row r="453" xml:space="preserve">
       <c r="A453" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
-1.50 x 1000.0 x 2000.0 mm</v>
+1.50 x 1250.0 x 2500.0 mm</v>
       </c>
       <c r="B453" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
-1.50 x 1000.0 x 2000.0 mm
-Weight (Kg):598
+1.50 x 1250.0 x 2500.0 mm
+Weight (Kg):681
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -7641,12 +7641,12 @@
     <row r="454" xml:space="preserve">
       <c r="A454" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
-1.50 x 1250.0 x 2500.0 mm</v>
+2.00 x 1000.0 x 2000.0 mm</v>
       </c>
       <c r="B454" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
-1.50 x 1250.0 x 2500.0 mm
-Weight (Kg):681
+2.00 x 1000.0 x 2000.0 mm
+Weight (Kg):2,359
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -7662,7 +7662,7 @@
       <c r="B455" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
 2.00 x 1000.0 x 2000.0 mm
-Weight (Kg):2,359
+Weight (Kg):529
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -7678,7 +7678,7 @@
       <c r="B456" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
 2.00 x 1000.0 x 2000.0 mm
-Weight (Kg):529
+Weight (Kg):889
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -7694,7 +7694,7 @@
       <c r="B457" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
 2.00 x 1000.0 x 2000.0 mm
-Weight (Kg):889
+Weight (Kg):628
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -7710,7 +7710,7 @@
       <c r="B458" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
 2.00 x 1000.0 x 2000.0 mm
-Weight (Kg):628
+Weight (Kg):1,968
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -7721,12 +7721,12 @@
     <row r="459" xml:space="preserve">
       <c r="A459" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
-2.00 x 1000.0 x 2000.0 mm</v>
+2.00 x 1250.0 x 2500.0 mm</v>
       </c>
       <c r="B459" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
-2.00 x 1000.0 x 2000.0 mm
-Weight (Kg):1,968
+2.00 x 1250.0 x 2500.0 mm
+Weight (Kg):928
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -7742,7 +7742,7 @@
       <c r="B460" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
 2.00 x 1250.0 x 2500.0 mm
-Weight (Kg):928
+Weight (Kg):816
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -7758,7 +7758,7 @@
       <c r="B461" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
 2.00 x 1250.0 x 2500.0 mm
-Weight (Kg):816
+Weight (Kg):976
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -7774,7 +7774,7 @@
       <c r="B462" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
 2.00 x 1250.0 x 2500.0 mm
-Weight (Kg):976
+Weight (Kg):585
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -7790,7 +7790,7 @@
       <c r="B463" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
 2.00 x 1250.0 x 2500.0 mm
-Weight (Kg):585
+Weight (Kg):1,956
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -7806,7 +7806,7 @@
       <c r="B464" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
 2.00 x 1250.0 x 2500.0 mm
-Weight (Kg):1,956
+Weight (Kg):1,779
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -7817,12 +7817,12 @@
     <row r="465" xml:space="preserve">
       <c r="A465" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
-2.00 x 1250.0 x 2500.0 mm</v>
+2.00 x 1500.0 x 3000.0 mm</v>
       </c>
       <c r="B465" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
-2.00 x 1250.0 x 2500.0 mm
-Weight (Kg):1,779
+2.00 x 1500.0 x 3000.0 mm
+Weight (Kg):693
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -7838,7 +7838,7 @@
       <c r="B466" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
 2.00 x 1500.0 x 3000.0 mm
-Weight (Kg):693
+Weight (Kg):1,122
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -7854,7 +7854,7 @@
       <c r="B467" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
 2.00 x 1500.0 x 3000.0 mm
-Weight (Kg):1,122
+Weight (Kg):1,108
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -7870,7 +7870,7 @@
       <c r="B468" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
 2.00 x 1500.0 x 3000.0 mm
-Weight (Kg):1,108
+Weight (Kg):1,836
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -7886,7 +7886,7 @@
       <c r="B469" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
 2.00 x 1500.0 x 3000.0 mm
-Weight (Kg):1,836
+Weight (Kg):630
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -7902,7 +7902,7 @@
       <c r="B470" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
 2.00 x 1500.0 x 3000.0 mm
-Weight (Kg):630
+Weight (Kg):726
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -7918,7 +7918,7 @@
       <c r="B471" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
 2.00 x 1500.0 x 3000.0 mm
-Weight (Kg):726
+Weight (Kg):565
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -7934,7 +7934,7 @@
       <c r="B472" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
 2.00 x 1500.0 x 3000.0 mm
-Weight (Kg):565
+Weight (Kg):729
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -7950,7 +7950,7 @@
       <c r="B473" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
 2.00 x 1500.0 x 3000.0 mm
-Weight (Kg):729
+Weight (Kg):792
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -7966,7 +7966,7 @@
       <c r="B474" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
 2.00 x 1500.0 x 3000.0 mm
-Weight (Kg):792
+Weight (Kg):637
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -7982,7 +7982,7 @@
       <c r="B475" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
 2.00 x 1500.0 x 3000.0 mm
-Weight (Kg):637
+Weight (Kg):1,289
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -7993,12 +7993,12 @@
     <row r="476" xml:space="preserve">
       <c r="A476" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
-2.00 x 1500.0 x 3000.0 mm</v>
+2.50 x 1500.0 x 3000.0 mm</v>
       </c>
       <c r="B476" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
-2.00 x 1500.0 x 3000.0 mm
-Weight (Kg):1,289
+2.50 x 1500.0 x 3000.0 mm
+Weight (Kg):1,826
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -8014,7 +8014,7 @@
       <c r="B477" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
 2.50 x 1500.0 x 3000.0 mm
-Weight (Kg):1,826
+Weight (Kg):1,040
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -8030,7 +8030,7 @@
       <c r="B478" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
 2.50 x 1500.0 x 3000.0 mm
-Weight (Kg):1,040
+Weight (Kg):1,328
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -8041,12 +8041,12 @@
     <row r="479" xml:space="preserve">
       <c r="A479" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
-2.50 x 1500.0 x 3000.0 mm</v>
+3.00 x 1000.0 x 2000.0 mm</v>
       </c>
       <c r="B479" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
-2.50 x 1500.0 x 3000.0 mm
-Weight (Kg):1,328
+3.00 x 1000.0 x 2000.0 mm
+Weight (Kg):940
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -8057,12 +8057,12 @@
     <row r="480" xml:space="preserve">
       <c r="A480" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
-3.00 x 1000.0 x 2000.0 mm</v>
+3.00 x 1250.0 x 2500.0 mm</v>
       </c>
       <c r="B480" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
-3.00 x 1000.0 x 2000.0 mm
-Weight (Kg):940
+3.00 x 1250.0 x 2500.0 mm
+Weight (Kg):1,396
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -8078,7 +8078,7 @@
       <c r="B481" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
 3.00 x 1250.0 x 2500.0 mm
-Weight (Kg):1,396
+Weight (Kg):2,318
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -8094,7 +8094,7 @@
       <c r="B482" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
 3.00 x 1250.0 x 2500.0 mm
-Weight (Kg):2,318
+Weight (Kg):1,074
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -8110,7 +8110,7 @@
       <c r="B483" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
 3.00 x 1250.0 x 2500.0 mm
-Weight (Kg):1,074
+Weight (Kg):1,584
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -8126,7 +8126,7 @@
       <c r="B484" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
 3.00 x 1250.0 x 2500.0 mm
-Weight (Kg):1,584
+Weight (Kg):1,028
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -8142,7 +8142,7 @@
       <c r="B485" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
 3.00 x 1250.0 x 2500.0 mm
-Weight (Kg):1,028
+Weight (Kg):598
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -8153,12 +8153,12 @@
     <row r="486" xml:space="preserve">
       <c r="A486" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
-3.00 x 1250.0 x 2500.0 mm</v>
+3.00 x 1340.0 x 2480.0 mm</v>
       </c>
       <c r="B486" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
-3.00 x 1250.0 x 2500.0 mm
-Weight (Kg):598
+3.00 x 1340.0 x 2480.0 mm
+Weight (Kg):1,174
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -8174,7 +8174,7 @@
       <c r="B487" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
 3.00 x 1340.0 x 2480.0 mm
-Weight (Kg):1,174
+Weight (Kg):1,020
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -8190,7 +8190,7 @@
       <c r="B488" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
 3.00 x 1340.0 x 2480.0 mm
-Weight (Kg):1,020
+Weight (Kg):1,169
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -8206,7 +8206,7 @@
       <c r="B489" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
 3.00 x 1340.0 x 2480.0 mm
-Weight (Kg):1,169
+Weight (Kg):1,951
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -8217,12 +8217,12 @@
     <row r="490" xml:space="preserve">
       <c r="A490" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
-3.00 x 1340.0 x 2480.0 mm</v>
+5.00 x 1000.0 x 2000.0 mm</v>
       </c>
       <c r="B490" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
-3.00 x 1340.0 x 2480.0 mm
-Weight (Kg):1,951
+5.00 x 1000.0 x 2000.0 mm
+Weight (Kg):943
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -8238,7 +8238,7 @@
       <c r="B491" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
 5.00 x 1000.0 x 2000.0 mm
-Weight (Kg):943
+Weight (Kg):947
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -8254,7 +8254,7 @@
       <c r="B492" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
 5.00 x 1000.0 x 2000.0 mm
-Weight (Kg):947
+Weight (Kg):1,588
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -8265,12 +8265,12 @@
     <row r="493" xml:space="preserve">
       <c r="A493" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
-5.00 x 1000.0 x 2000.0 mm</v>
+5.00 x 1250.0 x 2500.0 mm</v>
       </c>
       <c r="B493" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
-5.00 x 1000.0 x 2000.0 mm
-Weight (Kg):1,588
+5.00 x 1250.0 x 2500.0 mm
+Weight (Kg):742
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -8281,12 +8281,12 @@
     <row r="494" xml:space="preserve">
       <c r="A494" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
-5.00 x 1250.0 x 2500.0 mm</v>
+6.00 x 1000.0 x 2000.0 mm</v>
       </c>
       <c r="B494" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
-5.00 x 1250.0 x 2500.0 mm
-Weight (Kg):742
+6.00 x 1000.0 x 2000.0 mm
+Weight (Kg):1,452
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -8302,7 +8302,7 @@
       <c r="B495" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
 6.00 x 1000.0 x 2000.0 mm
-Weight (Kg):1,452
+Weight (Kg):1,624
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -8318,7 +8318,7 @@
       <c r="B496" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
 6.00 x 1000.0 x 2000.0 mm
-Weight (Kg):1,624
+Weight (Kg):1,434
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -8334,7 +8334,7 @@
       <c r="B497" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
 6.00 x 1000.0 x 2000.0 mm
-Weight (Kg):1,434
+Weight (Kg):580
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -8350,7 +8350,7 @@
       <c r="B498" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
 6.00 x 1000.0 x 2000.0 mm
-Weight (Kg):580
+Weight (Kg):1,054
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -8366,7 +8366,7 @@
       <c r="B499" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
 6.00 x 1000.0 x 2000.0 mm
-Weight (Kg):1,054
+Weight (Kg):1,716
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -8382,7 +8382,7 @@
       <c r="B500" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
 6.00 x 1000.0 x 2000.0 mm
-Weight (Kg):1,716
+Weight (Kg):1,148
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -8398,7 +8398,7 @@
       <c r="B501" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
 6.00 x 1000.0 x 2000.0 mm
-Weight (Kg):1,148
+Weight (Kg):960
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -8414,7 +8414,7 @@
       <c r="B502" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
 6.00 x 1000.0 x 2000.0 mm
-Weight (Kg):960
+Weight (Kg):772
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -8425,12 +8425,12 @@
     <row r="503" xml:space="preserve">
       <c r="A503" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
-6.00 x 1000.0 x 2000.0 mm</v>
+6.00 x 1500.0 x 3000.0 mm</v>
       </c>
       <c r="B503" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
-6.00 x 1000.0 x 2000.0 mm
-Weight (Kg):772
+6.00 x 1500.0 x 3000.0 mm
+Weight (Kg):2,146
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -8446,7 +8446,7 @@
       <c r="B504" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
 6.00 x 1500.0 x 3000.0 mm
-Weight (Kg):2,146
+Weight (Kg):1,994
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -8462,7 +8462,7 @@
       <c r="B505" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
 6.00 x 1500.0 x 3000.0 mm
-Weight (Kg):1,994
+Weight (Kg):1,488
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -8478,7 +8478,7 @@
       <c r="B506" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
 6.00 x 1500.0 x 3000.0 mm
-Weight (Kg):1,488
+Weight (Kg):1,278
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -8494,7 +8494,7 @@
       <c r="B507" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
 6.00 x 1500.0 x 3000.0 mm
-Weight (Kg):1,278
+Weight (Kg):1,062
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -8510,7 +8510,7 @@
       <c r="B508" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
 6.00 x 1500.0 x 3000.0 mm
-Weight (Kg):1,062
+Weight (Kg):1,526
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -8526,7 +8526,7 @@
       <c r="B509" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
 6.00 x 1500.0 x 3000.0 mm
-Weight (Kg):1,526
+Weight (Kg):1,280
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -8537,12 +8537,12 @@
     <row r="510" xml:space="preserve">
       <c r="A510" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
-6.00 x 1500.0 x 3000.0 mm</v>
+6.00 x 1510.0 x 3010.0 mm</v>
       </c>
       <c r="B510" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
-6.00 x 1500.0 x 3000.0 mm
-Weight (Kg):1,280
+6.00 x 1510.0 x 3010.0 mm
+Weight (Kg):1,986
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -8558,7 +8558,7 @@
       <c r="B511" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
 6.00 x 1510.0 x 3010.0 mm
-Weight (Kg):1,986
+Weight (Kg):1,784
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -8568,26 +8568,10 @@
     </row>
     <row r="512" xml:space="preserve">
       <c r="A512" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
-6.00 x 1510.0 x 3010.0 mm</v>
-      </c>
-      <c r="B512" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
-6.00 x 1510.0 x 3010.0 mm
-Weight (Kg):1,784
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-3,395.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="513" xml:space="preserve">
-      <c r="A513" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, Nb. 1,
 6.00 x 1000.0 x 2000.0 mm</v>
       </c>
-      <c r="B513" t="str" xml:space="preserve">
+      <c r="B512" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, Nb. 1,
 6.00 x 1000.0 x 2000.0 mm
 Weight (Kg):570
@@ -8598,15 +8582,31 @@
 Add to cart</v>
       </c>
     </row>
+    <row r="513" xml:space="preserve">
+      <c r="A513" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, SB-G-400,
+1.50 x 1500.0 x 3000.0 mm</v>
+      </c>
+      <c r="B513" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, SB-G-400,
+1.50 x 1500.0 x 3000.0 mm
+Weight (Kg):723
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+3,395.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
     <row r="514" xml:space="preserve">
       <c r="A514" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, SB-G-400,
-1.50 x 1500.0 x 3000.0 mm</v>
+2.00 x 1500.0 x 3000.0 mm</v>
       </c>
       <c r="B514" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, SB-G-400,
-1.50 x 1500.0 x 3000.0 mm
-Weight (Kg):723
+2.00 x 1500.0 x 3000.0 mm
+Weight (Kg):819
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -8622,7 +8622,7 @@
       <c r="B515" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, SB-G-400,
 2.00 x 1500.0 x 3000.0 mm
-Weight (Kg):819
+Weight (Kg):1,935
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -8632,13 +8632,13 @@
     </row>
     <row r="516" xml:space="preserve">
       <c r="A516" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, SB-G-400,
-2.00 x 1500.0 x 3000.0 mm</v>
+        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Untrimmed, Coil, 2B,
+1.20 x 1537.0 x coil mm</v>
       </c>
       <c r="B516" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, SB-G-400,
-2.00 x 1500.0 x 3000.0 mm
-Weight (Kg):1,935
+        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Untrimmed, Coil, 2B,
+1.20 x 1537.0 x coil mm
+Weight (Kg):2,125
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -8649,12 +8649,12 @@
     <row r="517" xml:space="preserve">
       <c r="A517" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Untrimmed, Coil, 2B,
-1.20 x 1537.0 x coil mm</v>
+1.80 x 1530.0 x coil mm</v>
       </c>
       <c r="B517" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Untrimmed, Coil, 2B,
-1.20 x 1537.0 x coil mm
-Weight (Kg):2,125
+1.80 x 1530.0 x coil mm
+Weight (Kg):5,263
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -8665,12 +8665,12 @@
     <row r="518" xml:space="preserve">
       <c r="A518" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Untrimmed, Coil, 2B,
-1.80 x 1530.0 x coil mm</v>
+1.80 x 1535.0 x coil mm</v>
       </c>
       <c r="B518" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Untrimmed, Coil, 2B,
-1.80 x 1530.0 x coil mm
-Weight (Kg):5,263
+1.80 x 1535.0 x coil mm
+Weight (Kg):2,726
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -8681,32 +8681,32 @@
     <row r="519" xml:space="preserve">
       <c r="A519" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Untrimmed, Coil, 2B,
-1.80 x 1535.0 x coil mm</v>
+2.00 x 1023.0 x coil mm</v>
       </c>
       <c r="B519" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Untrimmed, Coil, 2B,
-1.80 x 1535.0 x coil mm
-Weight (Kg):2,726
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-3,395.00 €/ton
+2.00 x 1023.0 x coil mm
+Weight (Kg):1,825
+Quality:Prime
+Help
+Location:FABRICA ALGECIRAS
+3,595.00 €/ton
 Add to cart</v>
       </c>
     </row>
     <row r="520" xml:space="preserve">
       <c r="A520" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Untrimmed, Coil, 2B,
-2.00 x 1023.0 x coil mm</v>
+3.00 x 1552.0 x coil mm</v>
       </c>
       <c r="B520" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Untrimmed, Coil, 2B,
-2.00 x 1023.0 x coil mm
-Weight (Kg):1,825
-Quality:Prime
-Help
-Location:FABRICA ALGECIRAS
-3,595.00 €/ton
+3.00 x 1552.0 x coil mm
+Weight (Kg):2,868
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+3,395.00 €/ton
 Add to cart</v>
       </c>
     </row>
@@ -8729,25 +8729,9 @@
     <row r="522" xml:space="preserve">
       <c r="A522" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Untrimmed, Coil, 2B,
-3.00 x 1552.0 x coil mm</v>
+6.00 x 1030.0 x coil mm</v>
       </c>
       <c r="B522" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Untrimmed, Coil, 2B,
-3.00 x 1552.0 x coil mm
-Weight (Kg):2,868
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-3,395.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="523" xml:space="preserve">
-      <c r="A523" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Untrimmed, Coil, 2B,
-6.00 x 1030.0 x coil mm</v>
-      </c>
-      <c r="B523" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Untrimmed, Coil, 2B,
 6.00 x 1030.0 x coil mm
 Weight (Kg):2,225
@@ -8758,12 +8742,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="524" xml:space="preserve">
-      <c r="A524" t="str" xml:space="preserve">
+    <row r="523" xml:space="preserve">
+      <c r="A523" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4571 316Ti-Coil, 2B,
 4.00 x 210.0 x coil mm</v>
       </c>
-      <c r="B524" t="str" xml:space="preserve">
+      <c r="B523" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4571 316Ti-Coil, 2B,
 4.00 x 210.0 x coil mm
 Weight (Kg):3,817
@@ -8771,6 +8755,22 @@
 Help
 Location:FABRICA ALGECIRAS
 3,370.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="524" xml:space="preserve">
+      <c r="A524" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4571 316Ti-Coil, Nb. 1,
+3.00 x 184.0 x coil mm</v>
+      </c>
+      <c r="B524" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4571 316Ti-Coil, Nb. 1,
+3.00 x 184.0 x coil mm
+Weight (Kg):1,794
+Quality:Prime
+Help
+Location:FABRICA ALGECIRAS
+3,270.00 €/ton
 Add to cart</v>
       </c>
     </row>
@@ -8782,7 +8782,7 @@
       <c r="B525" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4571 316Ti-Coil, Nb. 1,
 3.00 x 184.0 x coil mm
-Weight (Kg):1,794
+Weight (Kg):1,806
 Quality:Prime
 Help
 Location:FABRICA ALGECIRAS
@@ -8798,7 +8798,7 @@
       <c r="B526" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4571 316Ti-Coil, Nb. 1,
 3.00 x 184.0 x coil mm
-Weight (Kg):1,806
+Weight (Kg):1,808
 Quality:Prime
 Help
 Location:FABRICA ALGECIRAS
@@ -8809,25 +8809,9 @@
     <row r="527" xml:space="preserve">
       <c r="A527" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4571 316Ti-Coil, Nb. 1,
-3.00 x 184.0 x coil mm</v>
+4.00 x 200.0 x coil mm</v>
       </c>
       <c r="B527" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4571 316Ti-Coil, Nb. 1,
-3.00 x 184.0 x coil mm
-Weight (Kg):1,808
-Quality:Prime
-Help
-Location:FABRICA ALGECIRAS
-3,270.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="528" xml:space="preserve">
-      <c r="A528" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4571 316Ti-Coil, Nb. 1,
-4.00 x 200.0 x coil mm</v>
-      </c>
-      <c r="B528" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4571 316Ti-Coil, Nb. 1,
 4.00 x 200.0 x coil mm
 Weight (Kg):1,918
@@ -8838,12 +8822,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="529" xml:space="preserve">
-      <c r="A529" t="str" xml:space="preserve">
+    <row r="528" xml:space="preserve">
+      <c r="A528" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4571 316Ti-Plate, Nb. 1,
 45.00 x 1500.0 x 3000.0 mm</v>
       </c>
-      <c r="B529" t="str" xml:space="preserve">
+      <c r="B528" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4571 316Ti-Plate, Nb. 1,
 45.00 x 1500.0 x 3000.0 mm
 Weight (Kg):1,640
@@ -8851,6 +8835,22 @@
 Help
 Location:FABRICA ALGECIRAS
 4,600.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="529" xml:space="preserve">
+      <c r="A529" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4571 316Ti-Sheet, 2B,
+3.00 x 1000.0 x 2000.0 mm</v>
+      </c>
+      <c r="B529" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4571 316Ti-Sheet, 2B,
+3.00 x 1000.0 x 2000.0 mm
+Weight (Kg):918
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+3,495.00 €/ton
 Add to cart</v>
       </c>
     </row>
@@ -8862,7 +8862,7 @@
       <c r="B530" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4571 316Ti-Sheet, 2B,
 3.00 x 1000.0 x 2000.0 mm
-Weight (Kg):918
+Weight (Kg):518
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -8878,7 +8878,7 @@
       <c r="B531" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4571 316Ti-Sheet, 2B,
 3.00 x 1000.0 x 2000.0 mm
-Weight (Kg):518
+Weight (Kg):848
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -8889,12 +8889,12 @@
     <row r="532" xml:space="preserve">
       <c r="A532" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4571 316Ti-Sheet, 2B,
-3.00 x 1000.0 x 2000.0 mm</v>
+5.00 x 1000.0 x 2000.0 mm</v>
       </c>
       <c r="B532" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4571 316Ti-Sheet, 2B,
-3.00 x 1000.0 x 2000.0 mm
-Weight (Kg):848
+5.00 x 1000.0 x 2000.0 mm
+Weight (Kg):1,102
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -8905,12 +8905,12 @@
     <row r="533" xml:space="preserve">
       <c r="A533" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4571 316Ti-Sheet, 2B,
-5.00 x 1000.0 x 2000.0 mm</v>
+6.00 x 1000.0 x 2000.0 mm</v>
       </c>
       <c r="B533" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4571 316Ti-Sheet, 2B,
-5.00 x 1000.0 x 2000.0 mm
-Weight (Kg):1,102
+6.00 x 1000.0 x 2000.0 mm
+Weight (Kg):1,050
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -8926,7 +8926,7 @@
       <c r="B534" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4571 316Ti-Sheet, 2B,
 6.00 x 1000.0 x 2000.0 mm
-Weight (Kg):1,050
+Weight (Kg):952
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -8936,26 +8936,10 @@
     </row>
     <row r="535" xml:space="preserve">
       <c r="A535" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4571 316Ti-Sheet, 2B,
-6.00 x 1000.0 x 2000.0 mm</v>
-      </c>
-      <c r="B535" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4571 316Ti-Sheet, 2B,
-6.00 x 1000.0 x 2000.0 mm
-Weight (Kg):952
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-3,495.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="536" xml:space="preserve">
-      <c r="A536" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4571 316Ti-Sheet, Nb. 1,
 8.00 x 1500.0 x 3000.0 mm</v>
       </c>
-      <c r="B536" t="str" xml:space="preserve">
+      <c r="B535" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4571 316Ti-Sheet, Nb. 1,
 8.00 x 1500.0 x 3000.0 mm
 Weight (Kg):1,136
@@ -8963,6 +8947,22 @@
 Help
 Location:FABRICA ALGECIRAS
 3,495.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="536" xml:space="preserve">
+      <c r="A536" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4541 321-Coil, 2B,
+1.90 x 217.0 x coil mm</v>
+      </c>
+      <c r="B536" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4541 321-Coil, 2B,
+1.90 x 217.0 x coil mm
+Weight (Kg):3,537
+Quality:Prime
+Help
+Location:FABRICA ALGECIRAS
+2,235.00 €/ton
 Add to cart</v>
       </c>
     </row>
@@ -8974,7 +8974,7 @@
       <c r="B537" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4541 321-Coil, 2B,
 1.90 x 217.0 x coil mm
-Weight (Kg):3,537
+Weight (Kg):3,484
 Quality:Prime
 Help
 Location:FABRICA ALGECIRAS
@@ -8990,7 +8990,7 @@
       <c r="B538" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4541 321-Coil, 2B,
 1.90 x 217.0 x coil mm
-Weight (Kg):3,484
+Weight (Kg):3,537
 Quality:Prime
 Help
 Location:FABRICA ALGECIRAS
@@ -9006,7 +9006,7 @@
       <c r="B539" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4541 321-Coil, 2B,
 1.90 x 217.0 x coil mm
-Weight (Kg):3,537
+Weight (Kg):3,490
 Quality:Prime
 Help
 Location:FABRICA ALGECIRAS
@@ -9022,7 +9022,7 @@
       <c r="B540" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4541 321-Coil, 2B,
 1.90 x 217.0 x coil mm
-Weight (Kg):3,490
+Weight (Kg):3,537
 Quality:Prime
 Help
 Location:FABRICA ALGECIRAS
@@ -9038,7 +9038,7 @@
       <c r="B541" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4541 321-Coil, 2B,
 1.90 x 217.0 x coil mm
-Weight (Kg):3,537
+Weight (Kg):3,492
 Quality:Prime
 Help
 Location:FABRICA ALGECIRAS
@@ -9054,7 +9054,7 @@
       <c r="B542" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4541 321-Coil, 2B,
 1.90 x 217.0 x coil mm
-Weight (Kg):3,492
+Weight (Kg):3,480
 Quality:Prime
 Help
 Location:FABRICA ALGECIRAS
@@ -9065,25 +9065,9 @@
     <row r="543" xml:space="preserve">
       <c r="A543" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4541 321-Coil, 2B,
-1.90 x 217.0 x coil mm</v>
+4.00 x 520.0 x coil mm</v>
       </c>
       <c r="B543" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4541 321-Coil, 2B,
-1.90 x 217.0 x coil mm
-Weight (Kg):3,480
-Quality:Prime
-Help
-Location:FABRICA ALGECIRAS
-2,235.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="544" xml:space="preserve">
-      <c r="A544" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4541 321-Coil, 2B,
-4.00 x 520.0 x coil mm</v>
-      </c>
-      <c r="B544" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4541 321-Coil, 2B,
 4.00 x 520.0 x coil mm
 Weight (Kg):7,263
@@ -9094,28 +9078,28 @@
 Add to cart</v>
       </c>
     </row>
+    <row r="544" xml:space="preserve">
+      <c r="A544" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4541 321-Coil, Nb. 1,
+5.00 x 1542.0 x coil mm</v>
+      </c>
+      <c r="B544" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4541 321-Coil, Nb. 1,
+5.00 x 1542.0 x coil mm
+Weight (Kg):4,890
+Quality:Prime
+Help
+Location:FABRICA ALGECIRAS
+2,875.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
     <row r="545" xml:space="preserve">
       <c r="A545" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4541 321-Coil, Nb. 1,
-5.00 x 1542.0 x coil mm</v>
+5.00 x 230.9 x coil mm</v>
       </c>
       <c r="B545" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4541 321-Coil, Nb. 1,
-5.00 x 1542.0 x coil mm
-Weight (Kg):4,890
-Quality:Prime
-Help
-Location:FABRICA ALGECIRAS
-2,875.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="546" xml:space="preserve">
-      <c r="A546" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4541 321-Coil, Nb. 1,
-5.00 x 230.9 x coil mm</v>
-      </c>
-      <c r="B546" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4541 321-Coil, Nb. 1,
 5.00 x 230.9 x coil mm
 Weight (Kg):4,198
@@ -9126,15 +9110,31 @@
 Add to cart</v>
       </c>
     </row>
+    <row r="546" xml:space="preserve">
+      <c r="A546" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4541 321-Sheet, 2B,
+3.00 x 1000.0 x 2000.0 mm</v>
+      </c>
+      <c r="B546" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4541 321-Sheet, 2B,
+3.00 x 1000.0 x 2000.0 mm
+Weight (Kg):1,104
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,385.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
     <row r="547" xml:space="preserve">
       <c r="A547" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4541 321-Sheet, 2B,
-3.00 x 1000.0 x 2000.0 mm</v>
+4.00 x 1000.0 x 2000.0 mm</v>
       </c>
       <c r="B547" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4541 321-Sheet, 2B,
-3.00 x 1000.0 x 2000.0 mm
-Weight (Kg):1,104
+4.00 x 1000.0 x 2000.0 mm
+Weight (Kg):1,552
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -9145,25 +9145,9 @@
     <row r="548" xml:space="preserve">
       <c r="A548" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4541 321-Sheet, 2B,
-4.00 x 1000.0 x 2000.0 mm</v>
+6.00 x 1250.0 x 2500.0 mm</v>
       </c>
       <c r="B548" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4541 321-Sheet, 2B,
-4.00 x 1000.0 x 2000.0 mm
-Weight (Kg):1,552
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-2,385.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="549" xml:space="preserve">
-      <c r="A549" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4541 321-Sheet, 2B,
-6.00 x 1250.0 x 2500.0 mm</v>
-      </c>
-      <c r="B549" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4541 321-Sheet, 2B,
 6.00 x 1250.0 x 2500.0 mm
 Weight (Kg):1,296
@@ -9174,12 +9158,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="550" xml:space="preserve">
-      <c r="A550" t="str" xml:space="preserve">
+    <row r="549" xml:space="preserve">
+      <c r="A549" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4541 321-Sheet, Nb. 1,
 8.00 x 1000.0 x 2000.0 mm</v>
       </c>
-      <c r="B550" t="str" xml:space="preserve">
+      <c r="B549" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4541 321-Sheet, Nb. 1,
 8.00 x 1000.0 x 2000.0 mm
 Weight (Kg):640
@@ -9190,28 +9174,28 @@
 Add to cart</v>
       </c>
     </row>
+    <row r="550" xml:space="preserve">
+      <c r="A550" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4512 409L-Coil, 2B,
+1.00 x 1304.0 x coil mm</v>
+      </c>
+      <c r="B550" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4512 409L-Coil, 2B,
+1.00 x 1304.0 x coil mm
+Weight (Kg):10,360
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+1,125.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
     <row r="551" xml:space="preserve">
       <c r="A551" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4512 409L-Coil, 2B,
-1.00 x 1304.0 x coil mm</v>
+1.00 x 625.0 x coil mm</v>
       </c>
       <c r="B551" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4512 409L-Coil, 2B,
-1.00 x 1304.0 x coil mm
-Weight (Kg):10,360
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-1,125.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="552" xml:space="preserve">
-      <c r="A552" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4512 409L-Coil, 2B,
-1.00 x 625.0 x coil mm</v>
-      </c>
-      <c r="B552" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4512 409L-Coil, 2B,
 1.00 x 625.0 x coil mm
 Weight (Kg):6,700
@@ -9222,28 +9206,28 @@
 Add to cart</v>
       </c>
     </row>
+    <row r="552" xml:space="preserve">
+      <c r="A552" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4512 409L-Coil, 2D,
+2.00 x 1291.0 x coil mm</v>
+      </c>
+      <c r="B552" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4512 409L-Coil, 2D,
+2.00 x 1291.0 x coil mm
+Weight (Kg):3,579
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+1,125.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
     <row r="553" xml:space="preserve">
       <c r="A553" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4512 409L-Coil, 2D,
-2.00 x 1291.0 x coil mm</v>
+2.00 x 150.0 x coil mm</v>
       </c>
       <c r="B553" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4512 409L-Coil, 2D,
-2.00 x 1291.0 x coil mm
-Weight (Kg):3,579
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-1,125.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="554" xml:space="preserve">
-      <c r="A554" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4512 409L-Coil, 2D,
-2.00 x 150.0 x coil mm</v>
-      </c>
-      <c r="B554" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4512 409L-Coil, 2D,
 2.00 x 150.0 x coil mm
 Weight (Kg):2,270
@@ -9254,15 +9238,31 @@
 Add to cart</v>
       </c>
     </row>
+    <row r="554" xml:space="preserve">
+      <c r="A554" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4512 409L-Coil, Nb. 1,
+4.00 x 140.0 x coil mm</v>
+      </c>
+      <c r="B554" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4512 409L-Coil, Nb. 1,
+4.00 x 140.0 x coil mm
+Weight (Kg):2,354
+Quality:Prime
+Help
+Location:FABRICA ALGECIRAS
+900.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
     <row r="555" xml:space="preserve">
       <c r="A555" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4512 409L-Coil, Nb. 1,
-4.00 x 140.0 x coil mm</v>
+5.00 x 190.0 x coil mm</v>
       </c>
       <c r="B555" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4512 409L-Coil, Nb. 1,
-4.00 x 140.0 x coil mm
-Weight (Kg):2,354
+5.00 x 190.0 x coil mm
+Weight (Kg):2,447
 Quality:Prime
 Help
 Location:FABRICA ALGECIRAS
@@ -9273,13 +9273,13 @@
     <row r="556" xml:space="preserve">
       <c r="A556" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4512 409L-Coil, Nb. 1,
-5.00 x 190.0 x coil mm</v>
+6.00 x 270.0 x coil mm</v>
       </c>
       <c r="B556" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4512 409L-Coil, Nb. 1,
-5.00 x 190.0 x coil mm
-Weight (Kg):2,447
-Quality:Prime
+6.00 x 270.0 x coil mm
+Weight (Kg):2,116
+Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
 900.00 €/ton
@@ -9294,7 +9294,7 @@
       <c r="B557" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4512 409L-Coil, Nb. 1,
 6.00 x 270.0 x coil mm
-Weight (Kg):2,116
+Weight (Kg):1,780
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -9305,13 +9305,13 @@
     <row r="558" xml:space="preserve">
       <c r="A558" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4512 409L-Coil, Nb. 1,
-6.00 x 270.0 x coil mm</v>
+8.00 x 115.9 x coil mm</v>
       </c>
       <c r="B558" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4512 409L-Coil, Nb. 1,
-6.00 x 270.0 x coil mm
-Weight (Kg):1,780
-Quality:Prime-2
+8.00 x 115.9 x coil mm
+Weight (Kg):1,238
+Quality:Prime
 Help
 Location:FABRICA ALGECIRAS
 900.00 €/ton
@@ -9321,12 +9321,12 @@
     <row r="559" xml:space="preserve">
       <c r="A559" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4512 409L-Coil, Nb. 1,
-8.00 x 115.9 x coil mm</v>
+8.00 x 125.9 x coil mm</v>
       </c>
       <c r="B559" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4512 409L-Coil, Nb. 1,
-8.00 x 115.9 x coil mm
-Weight (Kg):1,238
+8.00 x 125.9 x coil mm
+Weight (Kg):1,214
 Quality:Prime
 Help
 Location:FABRICA ALGECIRAS
@@ -9337,25 +9337,9 @@
     <row r="560" xml:space="preserve">
       <c r="A560" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4512 409L-Coil, Nb. 1,
-8.00 x 125.9 x coil mm</v>
+8.00 x 230.9 x coil mm</v>
       </c>
       <c r="B560" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4512 409L-Coil, Nb. 1,
-8.00 x 125.9 x coil mm
-Weight (Kg):1,214
-Quality:Prime
-Help
-Location:FABRICA ALGECIRAS
-900.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="561" xml:space="preserve">
-      <c r="A561" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4512 409L-Coil, Nb. 1,
-8.00 x 230.9 x coil mm</v>
-      </c>
-      <c r="B561" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4512 409L-Coil, Nb. 1,
 8.00 x 230.9 x coil mm
 Weight (Kg):2,960
@@ -9366,12 +9350,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="562" xml:space="preserve">
-      <c r="A562" t="str" xml:space="preserve">
+    <row r="561" xml:space="preserve">
+      <c r="A561" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4512 409L-Untrimmed, Coil, 2B,
 1.00 x 625.0 x coil mm</v>
       </c>
-      <c r="B562" t="str" xml:space="preserve">
+      <c r="B561" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4512 409L-Untrimmed, Coil, 2B,
 1.00 x 625.0 x coil mm
 Weight (Kg):3,441
@@ -9382,12 +9366,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="563" xml:space="preserve">
-      <c r="A563" t="str" xml:space="preserve">
+    <row r="562" xml:space="preserve">
+      <c r="A562" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4512 409L-Untrimmed, Coil, 2D,
 1.50 x 1295.0 x coil mm</v>
       </c>
-      <c r="B563" t="str" xml:space="preserve">
+      <c r="B562" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4512 409L-Untrimmed, Coil, 2D,
 1.50 x 1295.0 x coil mm
 Weight (Kg):2,445
@@ -9398,28 +9382,28 @@
 Add to cart</v>
       </c>
     </row>
+    <row r="563" xml:space="preserve">
+      <c r="A563" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, 2B,
+0.70 x 299.9 x coil mm</v>
+      </c>
+      <c r="B563" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, 2B,
+0.70 x 299.9 x coil mm
+Weight (Kg):2,518
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+1,000.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
     <row r="564" xml:space="preserve">
       <c r="A564" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, 2B,
-0.70 x 299.9 x coil mm</v>
+2.00 x 220.0 x coil mm</v>
       </c>
       <c r="B564" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, 2B,
-0.70 x 299.9 x coil mm
-Weight (Kg):2,518
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-1,000.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="565" xml:space="preserve">
-      <c r="A565" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, 2B,
-2.00 x 220.0 x coil mm</v>
-      </c>
-      <c r="B565" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, 2B,
 2.00 x 220.0 x coil mm
 Weight (Kg):776
@@ -9430,60 +9414,60 @@
 Add to cart</v>
       </c>
     </row>
+    <row r="565" xml:space="preserve">
+      <c r="A565" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, 2D,
+0.50 x 1518.0 x coil mm</v>
+      </c>
+      <c r="B565" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, 2D,
+0.50 x 1518.0 x coil mm
+Weight (Kg):4,480
+Quality:Prime
+Help
+Location:FABRICA ALGECIRAS
+1,325.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
     <row r="566" xml:space="preserve">
       <c r="A566" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, 2D,
-0.50 x 1518.0 x coil mm</v>
+0.70 x 1007.0 x coil mm</v>
       </c>
       <c r="B566" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, 2D,
-0.50 x 1518.0 x coil mm
-Weight (Kg):4,480
-Quality:Prime
-Help
-Location:FABRICA ALGECIRAS
-1,325.00 €/ton
+0.70 x 1007.0 x coil mm
+Weight (Kg):14,970
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+1,125.00 €/ton
 Add to cart</v>
       </c>
     </row>
     <row r="567" xml:space="preserve">
       <c r="A567" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, 2D,
-0.70 x 1007.0 x coil mm</v>
+0.70 x 1450.0 x coil mm</v>
       </c>
       <c r="B567" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, 2D,
-0.70 x 1007.0 x coil mm
-Weight (Kg):14,970
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-1,125.00 €/ton
+0.70 x 1450.0 x coil mm
+Weight (Kg):4,780
+Quality:Prime
+Help
+Location:FABRICA ALGECIRAS
+1,325.00 €/ton
 Add to cart</v>
       </c>
     </row>
     <row r="568" xml:space="preserve">
       <c r="A568" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, 2D,
-0.70 x 1450.0 x coil mm</v>
+0.70 x 869.0 x coil mm</v>
       </c>
       <c r="B568" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, 2D,
-0.70 x 1450.0 x coil mm
-Weight (Kg):4,780
-Quality:Prime
-Help
-Location:FABRICA ALGECIRAS
-1,325.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="569" xml:space="preserve">
-      <c r="A569" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, 2D,
-0.70 x 869.0 x coil mm</v>
-      </c>
-      <c r="B569" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, 2D,
 0.70 x 869.0 x coil mm
 Weight (Kg):13,570
@@ -9494,15 +9478,31 @@
 Add to cart</v>
       </c>
     </row>
+    <row r="569" xml:space="preserve">
+      <c r="A569" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, BA,
+0.70 x 100.9 x coil mm</v>
+      </c>
+      <c r="B569" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, BA,
+0.70 x 100.9 x coil mm
+Weight (Kg):778
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+1,000.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
     <row r="570" xml:space="preserve">
       <c r="A570" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, BA,
-0.70 x 100.9 x coil mm</v>
+0.70 x 110.9 x coil mm</v>
       </c>
       <c r="B570" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, BA,
-0.70 x 100.9 x coil mm
-Weight (Kg):778
+0.70 x 110.9 x coil mm
+Weight (Kg):634
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -9518,8 +9518,8 @@
       <c r="B571" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, BA,
 0.70 x 110.9 x coil mm
-Weight (Kg):634
-Quality:Prime-2
+Weight (Kg):658
+Quality:Prime
 Help
 Location:FABRICA ALGECIRAS
 1,000.00 €/ton
@@ -9529,12 +9529,12 @@
     <row r="572" xml:space="preserve">
       <c r="A572" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, BA,
-0.70 x 110.9 x coil mm</v>
+0.70 x 120.0 x coil mm</v>
       </c>
       <c r="B572" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, BA,
-0.70 x 110.9 x coil mm
-Weight (Kg):658
+0.70 x 120.0 x coil mm
+Weight (Kg):836
 Quality:Prime
 Help
 Location:FABRICA ALGECIRAS
@@ -9545,12 +9545,12 @@
     <row r="573" xml:space="preserve">
       <c r="A573" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, BA,
-0.70 x 120.0 x coil mm</v>
+0.70 x 125.0 x coil mm</v>
       </c>
       <c r="B573" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, BA,
-0.70 x 120.0 x coil mm
-Weight (Kg):836
+0.70 x 125.0 x coil mm
+Weight (Kg):1,288
 Quality:Prime
 Help
 Location:FABRICA ALGECIRAS
@@ -9561,12 +9561,12 @@
     <row r="574" xml:space="preserve">
       <c r="A574" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, BA,
-0.70 x 125.0 x coil mm</v>
+0.70 x 125.9 x coil mm</v>
       </c>
       <c r="B574" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, BA,
-0.70 x 125.0 x coil mm
-Weight (Kg):1,288
+0.70 x 125.9 x coil mm
+Weight (Kg):708
 Quality:Prime
 Help
 Location:FABRICA ALGECIRAS
@@ -9577,13 +9577,13 @@
     <row r="575" xml:space="preserve">
       <c r="A575" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, BA,
-0.70 x 125.9 x coil mm</v>
+0.70 x 126.0 x coil mm</v>
       </c>
       <c r="B575" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, BA,
-0.70 x 125.9 x coil mm
-Weight (Kg):708
-Quality:Prime
+0.70 x 126.0 x coil mm
+Weight (Kg):804
+Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
 1,000.00 €/ton
@@ -9593,12 +9593,12 @@
     <row r="576" xml:space="preserve">
       <c r="A576" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, BA,
-0.70 x 126.0 x coil mm</v>
+0.70 x 155.9 x coil mm</v>
       </c>
       <c r="B576" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, BA,
-0.70 x 126.0 x coil mm
-Weight (Kg):804
+0.70 x 155.9 x coil mm
+Weight (Kg):1,148
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -9689,12 +9689,12 @@
     <row r="582" xml:space="preserve">
       <c r="A582" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, BA,
-0.70 x 155.9 x coil mm</v>
+0.70 x 175.9 x coil mm</v>
       </c>
       <c r="B582" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, BA,
-0.70 x 155.9 x coil mm
-Weight (Kg):1,148
+0.70 x 175.9 x coil mm
+Weight (Kg):944
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -9710,7 +9710,7 @@
       <c r="B583" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, BA,
 0.70 x 175.9 x coil mm
-Weight (Kg):944
+Weight (Kg):1,054
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -9721,13 +9721,13 @@
     <row r="584" xml:space="preserve">
       <c r="A584" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, BA,
-0.70 x 175.9 x coil mm</v>
+0.70 x 181.9 x coil mm</v>
       </c>
       <c r="B584" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, BA,
-0.70 x 175.9 x coil mm
-Weight (Kg):1,054
-Quality:Prime-2
+0.70 x 181.9 x coil mm
+Weight (Kg):1,632
+Quality:Prime
 Help
 Location:FABRICA ALGECIRAS
 1,000.00 €/ton
@@ -9737,13 +9737,13 @@
     <row r="585" xml:space="preserve">
       <c r="A585" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, BA,
-0.70 x 181.9 x coil mm</v>
+0.70 x 195.9 x coil mm</v>
       </c>
       <c r="B585" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, BA,
-0.70 x 181.9 x coil mm
-Weight (Kg):1,632
-Quality:Prime
+0.70 x 195.9 x coil mm
+Weight (Kg):1,174
+Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
 1,000.00 €/ton
@@ -9758,7 +9758,7 @@
       <c r="B586" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, BA,
 0.70 x 195.9 x coil mm
-Weight (Kg):1,174
+Weight (Kg):1,541
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -9769,12 +9769,12 @@
     <row r="587" xml:space="preserve">
       <c r="A587" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, BA,
-0.70 x 195.9 x coil mm</v>
+0.70 x 200.9 x coil mm</v>
       </c>
       <c r="B587" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, BA,
-0.70 x 195.9 x coil mm
-Weight (Kg):1,541
+0.70 x 200.9 x coil mm
+Weight (Kg):1,098
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -9785,12 +9785,12 @@
     <row r="588" xml:space="preserve">
       <c r="A588" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, BA,
-0.70 x 200.9 x coil mm</v>
+0.70 x 260.9 x coil mm</v>
       </c>
       <c r="B588" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, BA,
-0.70 x 200.9 x coil mm
-Weight (Kg):1,098
+0.70 x 260.9 x coil mm
+Weight (Kg):2,121
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -9801,105 +9801,89 @@
     <row r="589" xml:space="preserve">
       <c r="A589" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, BA,
-0.70 x 260.9 x coil mm</v>
+0.70 x 825.0 x coil mm</v>
       </c>
       <c r="B589" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, BA,
-0.70 x 260.9 x coil mm
-Weight (Kg):2,121
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-1,000.00 €/ton
+0.70 x 825.0 x coil mm
+Weight (Kg):5,270
+Quality:Prime
+Help
+Location:FABRICA ALGECIRAS
+1,325.00 €/ton
 Add to cart</v>
       </c>
     </row>
     <row r="590" xml:space="preserve">
       <c r="A590" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, BA,
-0.70 x 825.0 x coil mm</v>
+0.70 x 842.0 x coil mm</v>
       </c>
       <c r="B590" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, BA,
-0.70 x 825.0 x coil mm
-Weight (Kg):5,270
-Quality:Prime
-Help
-Location:FABRICA ALGECIRAS
-1,325.00 €/ton
+0.70 x 842.0 x coil mm
+Weight (Kg):10,370
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+1,125.00 €/ton
 Add to cart</v>
       </c>
     </row>
     <row r="591" xml:space="preserve">
       <c r="A591" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, BA,
-0.70 x 842.0 x coil mm</v>
+0.70 x 855.0 x coil mm</v>
       </c>
       <c r="B591" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, BA,
-0.70 x 842.0 x coil mm
-Weight (Kg):10,370
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-1,125.00 €/ton
+0.70 x 855.0 x coil mm
+Weight (Kg):3,990
+Quality:Prime
+Help
+Location:FABRICA ALGECIRAS
+1,325.00 €/ton
 Add to cart</v>
       </c>
     </row>
     <row r="592" xml:space="preserve">
       <c r="A592" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, BA,
-0.70 x 855.0 x coil mm</v>
+0.70 x 870.0 x coil mm</v>
       </c>
       <c r="B592" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, BA,
-0.70 x 855.0 x coil mm
-Weight (Kg):3,990
-Quality:Prime
-Help
-Location:FABRICA ALGECIRAS
-1,325.00 €/ton
+0.70 x 870.0 x coil mm
+Weight (Kg):13,910
+Quality:Prime
+Help
+Location:FABRICA ALGECIRAS
+1,900.00 €/ton
 Add to cart</v>
       </c>
     </row>
     <row r="593" xml:space="preserve">
       <c r="A593" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, BA,
-0.70 x 870.0 x coil mm</v>
+0.70 x 953.0 x coil mm</v>
       </c>
       <c r="B593" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, BA,
-0.70 x 870.0 x coil mm
-Weight (Kg):13,910
-Quality:Prime
-Help
-Location:FABRICA ALGECIRAS
-1,900.00 €/ton
+0.70 x 953.0 x coil mm
+Weight (Kg):6,970
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+1,125.00 €/ton
 Add to cart</v>
       </c>
     </row>
     <row r="594" xml:space="preserve">
       <c r="A594" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, BA,
-0.70 x 953.0 x coil mm</v>
+1.00 x 530.0 x coil mm</v>
       </c>
       <c r="B594" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, BA,
-0.70 x 953.0 x coil mm
-Weight (Kg):6,970
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-1,125.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="595" xml:space="preserve">
-      <c r="A595" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, BA,
-1.00 x 530.0 x coil mm</v>
-      </c>
-      <c r="B595" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, BA,
 1.00 x 530.0 x coil mm
 Weight (Kg):880
@@ -9910,32 +9894,48 @@
 Add to cart</v>
       </c>
     </row>
+    <row r="595" xml:space="preserve">
+      <c r="A595" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, Polished N4-G-180,
+0.90 x 1250.0 x coil mm</v>
+      </c>
+      <c r="B595" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, Polished N4-G-180,
+0.90 x 1250.0 x coil mm
+Weight (Kg):2,218
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+1,125.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
     <row r="596" xml:space="preserve">
       <c r="A596" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, Polished N4-G-180,
-0.90 x 1250.0 x coil mm</v>
+1.20 x 120.0 x coil mm</v>
       </c>
       <c r="B596" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, Polished N4-G-180,
-0.90 x 1250.0 x coil mm
-Weight (Kg):2,218
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-1,125.00 €/ton
+1.20 x 120.0 x coil mm
+Weight (Kg):1,430
+Quality:Prime
+Help
+Location:FABRICA ALGECIRAS
+1,000.00 €/ton
 Add to cart</v>
       </c>
     </row>
     <row r="597" xml:space="preserve">
       <c r="A597" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, Polished N4-G-180,
-1.20 x 120.0 x coil mm</v>
+1.20 x 250.0 x coil mm</v>
       </c>
       <c r="B597" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, Polished N4-G-180,
-1.20 x 120.0 x coil mm
-Weight (Kg):1,430
-Quality:Prime
+1.20 x 250.0 x coil mm
+Weight (Kg):1,902
+Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
 1,000.00 €/ton
@@ -9945,13 +9945,13 @@
     <row r="598" xml:space="preserve">
       <c r="A598" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, Polished N4-G-180,
-1.20 x 250.0 x coil mm</v>
+1.20 x 250.9 x coil mm</v>
       </c>
       <c r="B598" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, Polished N4-G-180,
-1.20 x 250.0 x coil mm
-Weight (Kg):1,902
-Quality:Prime-2
+1.20 x 250.9 x coil mm
+Weight (Kg):1,960
+Quality:Prime
 Help
 Location:FABRICA ALGECIRAS
 1,000.00 €/ton
@@ -9966,8 +9966,8 @@
       <c r="B599" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, Polished N4-G-180,
 1.20 x 250.9 x coil mm
-Weight (Kg):1,960
-Quality:Prime
+Weight (Kg):1,918
+Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
 1,000.00 €/ton
@@ -9977,12 +9977,12 @@
     <row r="600" xml:space="preserve">
       <c r="A600" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, Polished N4-G-180,
-1.20 x 250.9 x coil mm</v>
+1.20 x 260.9 x coil mm</v>
       </c>
       <c r="B600" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, Polished N4-G-180,
-1.20 x 250.9 x coil mm
-Weight (Kg):1,918
+1.20 x 260.9 x coil mm
+Weight (Kg):1,524
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -10014,7 +10014,7 @@
       <c r="B602" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, Polished N4-G-180,
 1.20 x 260.9 x coil mm
-Weight (Kg):1,524
+Weight (Kg):1,934
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -10024,13 +10024,13 @@
     </row>
     <row r="603" xml:space="preserve">
       <c r="A603" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, Polished N4-G-180,
-1.20 x 260.9 x coil mm</v>
+        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, SB-G-400,
+0.60 x 134.9 x coil mm</v>
       </c>
       <c r="B603" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, Polished N4-G-180,
-1.20 x 260.9 x coil mm
-Weight (Kg):1,934
+        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, SB-G-400,
+0.60 x 134.9 x coil mm
+Weight (Kg):1,134
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -10046,7 +10046,7 @@
       <c r="B604" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, SB-G-400,
 0.60 x 134.9 x coil mm
-Weight (Kg):1,134
+Weight (Kg):962
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -10057,12 +10057,12 @@
     <row r="605" xml:space="preserve">
       <c r="A605" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, SB-G-400,
-0.60 x 134.9 x coil mm</v>
+0.60 x 245.9 x coil mm</v>
       </c>
       <c r="B605" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, SB-G-400,
-0.60 x 134.9 x coil mm
-Weight (Kg):962
+0.60 x 245.9 x coil mm
+Weight (Kg):1,778
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -10073,12 +10073,12 @@
     <row r="606" xml:space="preserve">
       <c r="A606" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, SB-G-400,
-0.60 x 245.9 x coil mm</v>
+1.00 x 118.9 x coil mm</v>
       </c>
       <c r="B606" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, SB-G-400,
-0.60 x 245.9 x coil mm
-Weight (Kg):1,778
+1.00 x 118.9 x coil mm
+Weight (Kg):754
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -10094,7 +10094,7 @@
       <c r="B607" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, SB-G-400,
 1.00 x 118.9 x coil mm
-Weight (Kg):754
+Weight (Kg):802
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -10105,25 +10105,9 @@
     <row r="608" xml:space="preserve">
       <c r="A608" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, SB-G-400,
-1.00 x 118.9 x coil mm</v>
+1.00 x 266.9 x coil mm</v>
       </c>
       <c r="B608" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, SB-G-400,
-1.00 x 118.9 x coil mm
-Weight (Kg):802
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-1,000.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="609" xml:space="preserve">
-      <c r="A609" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, SB-G-400,
-1.00 x 266.9 x coil mm</v>
-      </c>
-      <c r="B609" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, SB-G-400,
 1.00 x 266.9 x coil mm
 Weight (Kg):1,322
@@ -10134,12 +10118,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="610" xml:space="preserve">
-      <c r="A610" t="str" xml:space="preserve">
+    <row r="609" xml:space="preserve">
+      <c r="A609" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, SB-G-500,
 0.70 x 245.9 x coil mm</v>
       </c>
-      <c r="B610" t="str" xml:space="preserve">
+      <c r="B609" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, SB-G-500,
 0.70 x 245.9 x coil mm
 Weight (Kg):1,496
@@ -10150,32 +10134,48 @@
 Add to cart</v>
       </c>
     </row>
+    <row r="610" xml:space="preserve">
+      <c r="A610" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, SBA,
+0.70 x 1056.0 x coil mm</v>
+      </c>
+      <c r="B610" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, SBA,
+0.70 x 1056.0 x coil mm
+Weight (Kg):15,197
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+1,125.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
     <row r="611" xml:space="preserve">
       <c r="A611" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, SBA,
-0.70 x 1056.0 x coil mm</v>
+0.70 x 150.9 x coil mm</v>
       </c>
       <c r="B611" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, SBA,
-0.70 x 1056.0 x coil mm
-Weight (Kg):15,197
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-1,125.00 €/ton
+0.70 x 150.9 x coil mm
+Weight (Kg):1,268
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+1,000.00 €/ton
 Add to cart</v>
       </c>
     </row>
     <row r="612" xml:space="preserve">
       <c r="A612" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, SBA,
-0.70 x 150.9 x coil mm</v>
+0.70 x 173.0 x coil mm</v>
       </c>
       <c r="B612" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, SBA,
-0.70 x 150.9 x coil mm
-Weight (Kg):1,268
-Quality:Prime-2
+0.70 x 173.0 x coil mm
+Weight (Kg):890
+Quality:Prime
 Help
 Location:FABRICA ALGECIRAS
 1,000.00 €/ton
@@ -10185,13 +10185,13 @@
     <row r="613" xml:space="preserve">
       <c r="A613" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, SBA,
-0.70 x 173.0 x coil mm</v>
+0.70 x 195.9 x coil mm</v>
       </c>
       <c r="B613" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, SBA,
-0.70 x 173.0 x coil mm
-Weight (Kg):890
-Quality:Prime
+0.70 x 195.9 x coil mm
+Weight (Kg):962
+Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
 1,000.00 €/ton
@@ -10201,44 +10201,44 @@
     <row r="614" xml:space="preserve">
       <c r="A614" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, SBA,
-0.70 x 195.9 x coil mm</v>
+0.70 x 682.0 x coil mm</v>
       </c>
       <c r="B614" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, SBA,
-0.70 x 195.9 x coil mm
-Weight (Kg):962
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-1,000.00 €/ton
+0.70 x 682.0 x coil mm
+Weight (Kg):3,870
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+1,025.00 €/ton
 Add to cart</v>
       </c>
     </row>
     <row r="615" xml:space="preserve">
       <c r="A615" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, SBA,
-0.70 x 682.0 x coil mm</v>
+0.70 x 825.0 x coil mm</v>
       </c>
       <c r="B615" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, SBA,
-0.70 x 682.0 x coil mm
-Weight (Kg):3,870
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-1,025.00 €/ton
+0.70 x 825.0 x coil mm
+Weight (Kg):6,448
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+1,125.00 €/ton
 Add to cart</v>
       </c>
     </row>
     <row r="616" xml:space="preserve">
       <c r="A616" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, SBA,
-0.70 x 825.0 x coil mm</v>
+0.70 x 942.0 x coil mm</v>
       </c>
       <c r="B616" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, SBA,
-0.70 x 825.0 x coil mm
-Weight (Kg):6,448
+0.70 x 942.0 x coil mm
+Weight (Kg):1,810
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -10249,12 +10249,12 @@
     <row r="617" xml:space="preserve">
       <c r="A617" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, SBA,
-0.70 x 942.0 x coil mm</v>
+0.70 x 948.0 x coil mm</v>
       </c>
       <c r="B617" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, SBA,
-0.70 x 942.0 x coil mm
-Weight (Kg):1,810
+0.70 x 948.0 x coil mm
+Weight (Kg):3,410
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -10265,12 +10265,12 @@
     <row r="618" xml:space="preserve">
       <c r="A618" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, SBA,
-0.70 x 948.0 x coil mm</v>
+0.70 x 960.0 x coil mm</v>
       </c>
       <c r="B618" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, SBA,
-0.70 x 948.0 x coil mm
-Weight (Kg):3,410
+0.70 x 960.0 x coil mm
+Weight (Kg):2,780
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -10281,25 +10281,9 @@
     <row r="619" xml:space="preserve">
       <c r="A619" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, SBA,
-0.70 x 960.0 x coil mm</v>
+0.70 x 963.0 x coil mm</v>
       </c>
       <c r="B619" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, SBA,
-0.70 x 960.0 x coil mm
-Weight (Kg):2,780
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-1,125.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="620" xml:space="preserve">
-      <c r="A620" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, SBA,
-0.70 x 963.0 x coil mm</v>
-      </c>
-      <c r="B620" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, SBA,
 0.70 x 963.0 x coil mm
 Weight (Kg):4,570
@@ -10307,6 +10291,22 @@
 Help
 Location:FABRICA ALGECIRAS
 1,325.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="620" xml:space="preserve">
+      <c r="A620" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Disk, BA,
+0.60 x 550.0 x 0.0 mm</v>
+      </c>
+      <c r="B620" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Disk, BA,
+0.60 x 550.0 x 0.0 mm
+Weight (Kg):578
+Quality:Prime
+Help
+Location:FABRICA ALGECIRAS
+1,900.00 €/ton
 Add to cart</v>
       </c>
     </row>
@@ -10318,7 +10318,7 @@
       <c r="B621" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Disk, BA,
 0.60 x 550.0 x 0.0 mm
-Weight (Kg):578
+Weight (Kg):572
 Quality:Prime
 Help
 Location:FABRICA ALGECIRAS
@@ -10334,7 +10334,7 @@
       <c r="B622" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Disk, BA,
 0.60 x 550.0 x 0.0 mm
-Weight (Kg):572
+Weight (Kg):576
 Quality:Prime
 Help
 Location:FABRICA ALGECIRAS
@@ -10350,7 +10350,7 @@
       <c r="B623" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Disk, BA,
 0.60 x 550.0 x 0.0 mm
-Weight (Kg):576
+Weight (Kg):578
 Quality:Prime
 Help
 Location:FABRICA ALGECIRAS
@@ -10366,7 +10366,7 @@
       <c r="B624" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Disk, BA,
 0.60 x 550.0 x 0.0 mm
-Weight (Kg):578
+Weight (Kg):582
 Quality:Prime
 Help
 Location:FABRICA ALGECIRAS
@@ -10376,29 +10376,29 @@
     </row>
     <row r="625" xml:space="preserve">
       <c r="A625" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Disk, BA,
-0.60 x 550.0 x 0.0 mm</v>
+        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Sheet, 2B,
+2.00 x 1250.0 x 2500.0 mm</v>
       </c>
       <c r="B625" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Disk, BA,
-0.60 x 550.0 x 0.0 mm
-Weight (Kg):582
-Quality:Prime
-Help
-Location:FABRICA ALGECIRAS
-1,900.00 €/ton
+        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Sheet, 2B,
+2.00 x 1250.0 x 2500.0 mm
+Weight (Kg):619
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+1,125.00 €/ton
 Add to cart</v>
       </c>
     </row>
     <row r="626" xml:space="preserve">
       <c r="A626" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Sheet, 2B,
-2.00 x 1250.0 x 2500.0 mm</v>
+3.00 x 1250.0 x 2500.0 mm</v>
       </c>
       <c r="B626" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Sheet, 2B,
-2.00 x 1250.0 x 2500.0 mm
-Weight (Kg):619
+3.00 x 1250.0 x 2500.0 mm
+Weight (Kg):566
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -10414,7 +10414,7 @@
       <c r="B627" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Sheet, 2B,
 3.00 x 1250.0 x 2500.0 mm
-Weight (Kg):566
+Weight (Kg):640
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -10424,26 +10424,10 @@
     </row>
     <row r="628" xml:space="preserve">
       <c r="A628" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Sheet, 2B,
-3.00 x 1250.0 x 2500.0 mm</v>
-      </c>
-      <c r="B628" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Sheet, 2B,
-3.00 x 1250.0 x 2500.0 mm
-Weight (Kg):640
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-1,125.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="629" xml:space="preserve">
-      <c r="A629" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Sheet, BA,
 0.70 x 1250.0 x 2500.0 mm</v>
       </c>
-      <c r="B629" t="str" xml:space="preserve">
+      <c r="B628" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Sheet, BA,
 0.70 x 1250.0 x 2500.0 mm
 Weight (Kg):766
@@ -10454,12 +10438,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="630" xml:space="preserve">
-      <c r="A630" t="str" xml:space="preserve">
+    <row r="629" xml:space="preserve">
+      <c r="A629" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Sheet, SB-G-400,
 1.00 x 1500.0 x 3000.0 mm</v>
       </c>
-      <c r="B630" t="str" xml:space="preserve">
+      <c r="B629" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Sheet, SB-G-400,
 1.00 x 1500.0 x 3000.0 mm
 Weight (Kg):1,940
@@ -10470,12 +10454,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="631" xml:space="preserve">
-      <c r="A631" t="str" xml:space="preserve">
+    <row r="630" xml:space="preserve">
+      <c r="A630" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Untrimmed, Coil, 1/4 HT,
 3.00 x 1292.0 x coil mm</v>
       </c>
-      <c r="B631" t="str" xml:space="preserve">
+      <c r="B630" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Untrimmed, Coil, 1/4 HT,
 3.00 x 1292.0 x coil mm
 Weight (Kg):3,641
@@ -10486,12 +10470,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="632" xml:space="preserve">
-      <c r="A632" t="str" xml:space="preserve">
+    <row r="631" xml:space="preserve">
+      <c r="A631" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Untrimmed, Coil, 2B,
 1.20 x 1500.0 x coil mm</v>
       </c>
-      <c r="B632" t="str" xml:space="preserve">
+      <c r="B631" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Untrimmed, Coil, 2B,
 1.20 x 1500.0 x coil mm
 Weight (Kg):4,750
@@ -10502,6 +10486,22 @@
 Add to cart</v>
       </c>
     </row>
+    <row r="632" xml:space="preserve">
+      <c r="A632" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Untrimmed, Coil, 2D, ET-100
+0.50 x 1250.0 x coil mm</v>
+      </c>
+      <c r="B632" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Untrimmed, Coil, 2D, ET-100
+0.50 x 1250.0 x coil mm
+Weight (Kg):5,160
+Quality:Prime
+Help
+Location:FABRICA ALGECIRAS
+1,325.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
     <row r="633" xml:space="preserve">
       <c r="A633" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Untrimmed, Coil, 2D, ET-100
@@ -10510,7 +10510,7 @@
       <c r="B633" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Untrimmed, Coil, 2D, ET-100
 0.50 x 1250.0 x coil mm
-Weight (Kg):5,160
+Weight (Kg):3,695
 Quality:Prime
 Help
 Location:FABRICA ALGECIRAS
@@ -10520,45 +10520,45 @@
     </row>
     <row r="634" xml:space="preserve">
       <c r="A634" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Untrimmed, Coil, 2D, ET-100
-0.50 x 1250.0 x coil mm</v>
+        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Untrimmed, Coil, BA,
+0.60 x 1246.0 x coil mm</v>
       </c>
       <c r="B634" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Untrimmed, Coil, 2D, ET-100
-0.50 x 1250.0 x coil mm
-Weight (Kg):3,695
-Quality:Prime
-Help
-Location:FABRICA ALGECIRAS
-1,325.00 €/ton
+        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Untrimmed, Coil, BA,
+0.60 x 1246.0 x coil mm
+Weight (Kg):2,585
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+1,125.00 €/ton
 Add to cart</v>
       </c>
     </row>
     <row r="635" xml:space="preserve">
       <c r="A635" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Untrimmed, Coil, BA,
-0.60 x 1246.0 x coil mm</v>
+1.00 x 1028.0 x coil mm</v>
       </c>
       <c r="B635" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Untrimmed, Coil, BA,
-0.60 x 1246.0 x coil mm
-Weight (Kg):2,585
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-1,125.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="636" xml:space="preserve">
-      <c r="A636" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Untrimmed, Coil, BA,
-1.00 x 1028.0 x coil mm</v>
-      </c>
-      <c r="B636" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Untrimmed, Coil, BA,
 1.00 x 1028.0 x coil mm
 Weight (Kg):2,430
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+1,125.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="636" xml:space="preserve">
+      <c r="A636" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Untrimmed, Coil, SBA,
+0.70 x 825.0 x coil mm</v>
+      </c>
+      <c r="B636" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Untrimmed, Coil, SBA,
+0.70 x 825.0 x coil mm
+Weight (Kg):7,260
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -10649,25 +10649,9 @@
     <row r="642" xml:space="preserve">
       <c r="A642" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Untrimmed, Coil, SBA,
-0.70 x 825.0 x coil mm</v>
+0.70 x 873.0 x coil mm</v>
       </c>
       <c r="B642" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Untrimmed, Coil, SBA,
-0.70 x 825.0 x coil mm
-Weight (Kg):7,260
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-1,125.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="643" xml:space="preserve">
-      <c r="A643" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Untrimmed, Coil, SBA,
-0.70 x 873.0 x coil mm</v>
-      </c>
-      <c r="B643" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Untrimmed, Coil, SBA,
 0.70 x 873.0 x coil mm
 Weight (Kg):4,020
@@ -10678,12 +10662,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="644" xml:space="preserve">
-      <c r="A644" t="str" xml:space="preserve">
+    <row r="643" xml:space="preserve">
+      <c r="A643" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4510 430Ti-Coil, 2B,
 2.00 x 100.9 x coil mm</v>
       </c>
-      <c r="B644" t="str" xml:space="preserve">
+      <c r="B643" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4510 430Ti-Coil, 2B,
 2.00 x 100.9 x coil mm
 Weight (Kg):1,710
@@ -10694,16 +10678,32 @@
 Add to cart</v>
       </c>
     </row>
+    <row r="644" xml:space="preserve">
+      <c r="A644" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4510 430Ti-Coil, BA,
+0.50 x 170.0 x coil mm</v>
+      </c>
+      <c r="B644" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4510 430Ti-Coil, BA,
+0.50 x 170.0 x coil mm
+Weight (Kg):914
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+1,000.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
     <row r="645" xml:space="preserve">
       <c r="A645" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4510 430Ti-Coil, BA,
-0.50 x 170.0 x coil mm</v>
+0.70 x 100.9 x coil mm</v>
       </c>
       <c r="B645" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4510 430Ti-Coil, BA,
-0.50 x 170.0 x coil mm
-Weight (Kg):914
-Quality:Prime-2
+0.70 x 100.9 x coil mm
+Weight (Kg):638
+Quality:Prime
 Help
 Location:FABRICA ALGECIRAS
 1,000.00 €/ton
@@ -10713,44 +10713,44 @@
     <row r="646" xml:space="preserve">
       <c r="A646" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4510 430Ti-Coil, BA,
-0.70 x 100.9 x coil mm</v>
+0.70 x 1020.0 x coil mm</v>
       </c>
       <c r="B646" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4510 430Ti-Coil, BA,
-0.70 x 100.9 x coil mm
-Weight (Kg):638
-Quality:Prime
-Help
-Location:FABRICA ALGECIRAS
-1,000.00 €/ton
+0.70 x 1020.0 x coil mm
+Weight (Kg):16,000
+Quality:Prime
+Help
+Location:FABRICA ALGECIRAS
+1,900.00 €/ton
 Add to cart</v>
       </c>
     </row>
     <row r="647" xml:space="preserve">
       <c r="A647" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4510 430Ti-Coil, BA,
-0.70 x 1020.0 x coil mm</v>
+0.70 x 108.0 x coil mm</v>
       </c>
       <c r="B647" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4510 430Ti-Coil, BA,
-0.70 x 1020.0 x coil mm
-Weight (Kg):16,000
-Quality:Prime
-Help
-Location:FABRICA ALGECIRAS
-1,900.00 €/ton
+0.70 x 108.0 x coil mm
+Weight (Kg):714
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+1,000.00 €/ton
 Add to cart</v>
       </c>
     </row>
     <row r="648" xml:space="preserve">
       <c r="A648" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4510 430Ti-Coil, BA,
-0.70 x 108.0 x coil mm</v>
+0.70 x 120.9 x coil mm</v>
       </c>
       <c r="B648" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4510 430Ti-Coil, BA,
-0.70 x 108.0 x coil mm
-Weight (Kg):714
+0.70 x 120.9 x coil mm
+Weight (Kg):976
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -10761,12 +10761,12 @@
     <row r="649" xml:space="preserve">
       <c r="A649" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4510 430Ti-Coil, BA,
-0.70 x 120.9 x coil mm</v>
+0.70 x 325.0 x coil mm</v>
       </c>
       <c r="B649" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4510 430Ti-Coil, BA,
-0.70 x 120.9 x coil mm
-Weight (Kg):976
+0.70 x 325.0 x coil mm
+Weight (Kg):4,156
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -10777,16 +10777,16 @@
     <row r="650" xml:space="preserve">
       <c r="A650" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4510 430Ti-Coil, BA,
-0.70 x 325.0 x coil mm</v>
+0.70 x 900.0 x coil mm</v>
       </c>
       <c r="B650" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4510 430Ti-Coil, BA,
-0.70 x 325.0 x coil mm
-Weight (Kg):4,156
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-1,000.00 €/ton
+0.70 x 900.0 x coil mm
+Weight (Kg):2,800
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+1,125.00 €/ton
 Add to cart</v>
       </c>
     </row>
@@ -10798,7 +10798,7 @@
       <c r="B651" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4510 430Ti-Coil, BA,
 0.70 x 900.0 x coil mm
-Weight (Kg):2,800
+Weight (Kg):6,570
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -10809,12 +10809,12 @@
     <row r="652" xml:space="preserve">
       <c r="A652" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4510 430Ti-Coil, BA,
-0.70 x 900.0 x coil mm</v>
+0.70 x 905.0 x coil mm</v>
       </c>
       <c r="B652" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4510 430Ti-Coil, BA,
-0.70 x 900.0 x coil mm
-Weight (Kg):6,570
+0.70 x 905.0 x coil mm
+Weight (Kg):9,410
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -10825,12 +10825,12 @@
     <row r="653" xml:space="preserve">
       <c r="A653" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4510 430Ti-Coil, BA,
-0.70 x 905.0 x coil mm</v>
+0.70 x 932.0 x coil mm</v>
       </c>
       <c r="B653" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4510 430Ti-Coil, BA,
-0.70 x 905.0 x coil mm
-Weight (Kg):9,410
+0.70 x 932.0 x coil mm
+Weight (Kg):2,270
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -10841,25 +10841,9 @@
     <row r="654" xml:space="preserve">
       <c r="A654" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4510 430Ti-Coil, BA,
-0.70 x 932.0 x coil mm</v>
+0.70 x 940.0 x coil mm</v>
       </c>
       <c r="B654" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4510 430Ti-Coil, BA,
-0.70 x 932.0 x coil mm
-Weight (Kg):2,270
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-1,125.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="655" xml:space="preserve">
-      <c r="A655" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4510 430Ti-Coil, BA,
-0.70 x 940.0 x coil mm</v>
-      </c>
-      <c r="B655" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4510 430Ti-Coil, BA,
 0.70 x 940.0 x coil mm
 Weight (Kg):14,920
@@ -10870,28 +10854,28 @@
 Add to cart</v>
       </c>
     </row>
+    <row r="655" xml:space="preserve">
+      <c r="A655" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4510 430Ti-Untrimmed, Coil, BA,
+0.50 x 1275.0 x coil mm</v>
+      </c>
+      <c r="B655" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4510 430Ti-Untrimmed, Coil, BA,
+0.50 x 1275.0 x coil mm
+Weight (Kg):2,258
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+1,125.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
     <row r="656" xml:space="preserve">
       <c r="A656" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4510 430Ti-Untrimmed, Coil, BA,
-0.50 x 1275.0 x coil mm</v>
+0.70 x 928.0 x coil mm</v>
       </c>
       <c r="B656" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4510 430Ti-Untrimmed, Coil, BA,
-0.50 x 1275.0 x coil mm
-Weight (Kg):2,258
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-1,125.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="657" xml:space="preserve">
-      <c r="A657" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4510 430Ti-Untrimmed, Coil, BA,
-0.70 x 928.0 x coil mm</v>
-      </c>
-      <c r="B657" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4510 430Ti-Untrimmed, Coil, BA,
 0.70 x 928.0 x coil mm
 Weight (Kg):4,257
@@ -10902,12 +10886,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="658" xml:space="preserve">
-      <c r="A658" t="str" xml:space="preserve">
+    <row r="657" xml:space="preserve">
+      <c r="A657" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4509 441-Coil, 2B,
 1.20 x 275.9 x coil mm</v>
       </c>
-      <c r="B658" t="str" xml:space="preserve">
+      <c r="B657" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4509 441-Coil, 2B,
 1.20 x 275.9 x coil mm
 Weight (Kg):2,416
@@ -10918,15 +10902,31 @@
 Add to cart</v>
       </c>
     </row>
+    <row r="658" xml:space="preserve">
+      <c r="A658" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4509 441-Coil, 2D,
+1.20 x 196.0 x coil mm</v>
+      </c>
+      <c r="B658" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4509 441-Coil, 2D,
+1.20 x 196.0 x coil mm
+Weight (Kg):2,970
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+1,100.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
     <row r="659" xml:space="preserve">
       <c r="A659" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4509 441-Coil, 2D,
-1.20 x 196.0 x coil mm</v>
+1.20 x 200.0 x coil mm</v>
       </c>
       <c r="B659" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4509 441-Coil, 2D,
-1.20 x 196.0 x coil mm
-Weight (Kg):2,970
+1.20 x 200.0 x coil mm
+Weight (Kg):3,310
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -10937,12 +10937,12 @@
     <row r="660" xml:space="preserve">
       <c r="A660" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4509 441-Coil, 2D,
-1.20 x 200.0 x coil mm</v>
+1.20 x 214.9 x coil mm</v>
       </c>
       <c r="B660" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4509 441-Coil, 2D,
-1.20 x 200.0 x coil mm
-Weight (Kg):3,310
+1.20 x 214.9 x coil mm
+Weight (Kg):3,220
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -10969,12 +10969,12 @@
     <row r="662" xml:space="preserve">
       <c r="A662" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4509 441-Coil, 2D,
-1.20 x 214.9 x coil mm</v>
+1.20 x 223.9 x coil mm</v>
       </c>
       <c r="B662" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4509 441-Coil, 2D,
-1.20 x 214.9 x coil mm
-Weight (Kg):3,220
+1.20 x 223.9 x coil mm
+Weight (Kg):3,798
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -10985,28 +10985,28 @@
     <row r="663" xml:space="preserve">
       <c r="A663" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4509 441-Coil, 2D,
-1.20 x 223.9 x coil mm</v>
+1.20 x 224.0 x coil mm</v>
       </c>
       <c r="B663" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4509 441-Coil, 2D,
-1.20 x 223.9 x coil mm
-Weight (Kg):3,798
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-1,100.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="664" xml:space="preserve">
-      <c r="A664" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4509 441-Coil, 2D,
-1.20 x 224.0 x coil mm</v>
-      </c>
-      <c r="B664" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4509 441-Coil, 2D,
 1.20 x 224.0 x coil mm
 Weight (Kg):3,808
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+1,100.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="664" xml:space="preserve">
+      <c r="A664" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4509 441-Coil, BA,
+0.80 x 130.9 x coil mm</v>
+      </c>
+      <c r="B664" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4509 441-Coil, BA,
+0.80 x 130.9 x coil mm
+Weight (Kg):245
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -11038,7 +11038,7 @@
       <c r="B666" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4509 441-Coil, BA,
 0.80 x 130.9 x coil mm
-Weight (Kg):245
+Weight (Kg):213
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -11054,7 +11054,7 @@
       <c r="B667" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4509 441-Coil, BA,
 0.80 x 130.9 x coil mm
-Weight (Kg):213
+Weight (Kg):244
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -11064,45 +11064,45 @@
     </row>
     <row r="668" xml:space="preserve">
       <c r="A668" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4509 441-Coil, BA,
-0.80 x 130.9 x coil mm</v>
+        <v xml:space="preserve">Acerinox Europa, 1.4509 441-Coil, SB-G-400,
+1.00 x 1000.0 x coil mm</v>
       </c>
       <c r="B668" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4509 441-Coil, BA,
-0.80 x 130.9 x coil mm
-Weight (Kg):244
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-1,100.00 €/ton
+        <v xml:space="preserve">Acerinox Europa, 1.4509 441-Coil, SB-G-400,
+1.00 x 1000.0 x coil mm
+Weight (Kg):7,550
+Quality:Prime
+Help
+Location:FABRICA ALGECIRAS
+1,625.00 €/ton
 Add to cart</v>
       </c>
     </row>
     <row r="669" xml:space="preserve">
       <c r="A669" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4509 441-Coil, SB-G-400,
-1.00 x 1000.0 x coil mm</v>
+1.00 x 255.0 x coil mm</v>
       </c>
       <c r="B669" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4509 441-Coil, SB-G-400,
-1.00 x 1000.0 x coil mm
-Weight (Kg):7,550
-Quality:Prime
-Help
-Location:FABRICA ALGECIRAS
-1,625.00 €/ton
+1.00 x 255.0 x coil mm
+Weight (Kg):2,182
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+1,100.00 €/ton
 Add to cart</v>
       </c>
     </row>
     <row r="670" xml:space="preserve">
       <c r="A670" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4509 441-Coil, SB-G-400,
-1.00 x 255.0 x coil mm</v>
+1.00 x 290.9 x coil mm</v>
       </c>
       <c r="B670" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4509 441-Coil, SB-G-400,
-1.00 x 255.0 x coil mm
-Weight (Kg):2,182
+1.00 x 290.9 x coil mm
+Weight (Kg):2,370
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -11113,12 +11113,12 @@
     <row r="671" xml:space="preserve">
       <c r="A671" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4509 441-Coil, SB-G-400,
-1.00 x 290.9 x coil mm</v>
+1.20 x 110.9 x coil mm</v>
       </c>
       <c r="B671" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4509 441-Coil, SB-G-400,
-1.00 x 290.9 x coil mm
-Weight (Kg):2,370
+1.20 x 110.9 x coil mm
+Weight (Kg):856
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -11129,12 +11129,12 @@
     <row r="672" xml:space="preserve">
       <c r="A672" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4509 441-Coil, SB-G-400,
-1.20 x 110.9 x coil mm</v>
+1.20 x 130.9 x coil mm</v>
       </c>
       <c r="B672" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4509 441-Coil, SB-G-400,
-1.20 x 110.9 x coil mm
-Weight (Kg):856
+1.20 x 130.9 x coil mm
+Weight (Kg):564
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -11150,8 +11150,8 @@
       <c r="B673" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4509 441-Coil, SB-G-400,
 1.20 x 130.9 x coil mm
-Weight (Kg):564
-Quality:Prime-2
+Weight (Kg):532
+Quality:Prime
 Help
 Location:FABRICA ALGECIRAS
 1,100.00 €/ton
@@ -11161,13 +11161,13 @@
     <row r="674" xml:space="preserve">
       <c r="A674" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4509 441-Coil, SB-G-400,
-1.20 x 130.9 x coil mm</v>
+1.50 x 130.9 x coil mm</v>
       </c>
       <c r="B674" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4509 441-Coil, SB-G-400,
-1.20 x 130.9 x coil mm
-Weight (Kg):532
-Quality:Prime
+1.50 x 130.9 x coil mm
+Weight (Kg):640
+Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
 1,100.00 €/ton
@@ -11177,25 +11177,9 @@
     <row r="675" xml:space="preserve">
       <c r="A675" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4509 441-Coil, SB-G-400,
-1.50 x 130.9 x coil mm</v>
+1.50 x 360.0 x coil mm</v>
       </c>
       <c r="B675" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4509 441-Coil, SB-G-400,
-1.50 x 130.9 x coil mm
-Weight (Kg):640
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-1,100.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="676" xml:space="preserve">
-      <c r="A676" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4509 441-Coil, SB-G-400,
-1.50 x 360.0 x coil mm</v>
-      </c>
-      <c r="B676" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4509 441-Coil, SB-G-400,
 1.50 x 360.0 x coil mm
 Weight (Kg):1,488
@@ -11206,12 +11190,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="677" xml:space="preserve">
-      <c r="A677" t="str" xml:space="preserve">
+    <row r="676" xml:space="preserve">
+      <c r="A676" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4509 441-Untrimmed, Coil, 2B,
 1.50 x 1539.0 x coil mm</v>
       </c>
-      <c r="B677" t="str" xml:space="preserve">
+      <c r="B676" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4509 441-Untrimmed, Coil, 2B,
 1.50 x 1539.0 x coil mm
 Weight (Kg):14,230
@@ -11222,12 +11206,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="678" xml:space="preserve">
-      <c r="A678" t="str" xml:space="preserve">
+    <row r="677" xml:space="preserve">
+      <c r="A677" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4509 441-Untrimmed, Coil, BA,
 0.40 x 1075.0 x coil mm</v>
       </c>
-      <c r="B678" t="str" xml:space="preserve">
+      <c r="B677" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4509 441-Untrimmed, Coil, BA,
 0.40 x 1075.0 x coil mm
 Weight (Kg):9,750
@@ -11238,12 +11222,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="679" xml:space="preserve">
-      <c r="A679" t="str" xml:space="preserve">
+    <row r="678" xml:space="preserve">
+      <c r="A678" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4509 441-Untrimmed, Coil, Nb. 1,
 5.00 x 1045.0 x coil mm</v>
       </c>
-      <c r="B679" t="str" xml:space="preserve">
+      <c r="B678" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4509 441-Untrimmed, Coil, Nb. 1,
 5.00 x 1045.0 x coil mm
 Weight (Kg):7,880
@@ -11254,12 +11238,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="680" xml:space="preserve">
-      <c r="A680" t="str" xml:space="preserve">
+    <row r="679" xml:space="preserve">
+      <c r="A679" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 441-1.4509 Coil, 2B,
 1.20 x 240.9 x coil mm</v>
       </c>
-      <c r="B680" t="str" xml:space="preserve">
+      <c r="B679" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 441-1.4509 Coil, 2B,
 1.20 x 240.9 x coil mm
 Weight (Kg):3,882
@@ -11270,12 +11254,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="681" xml:space="preserve">
-      <c r="A681" t="str" xml:space="preserve">
+    <row r="680" xml:space="preserve">
+      <c r="A680" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 304-1.4301 Coil,
 0.70 x 270.9 x coil mm</v>
       </c>
-      <c r="B681" t="str" xml:space="preserve">
+      <c r="B680" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 304-1.4301 Coil,
 0.70 x 270.9 x coil mm
 Weight (Kg):2,704
@@ -11286,12 +11270,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="682" xml:space="preserve">
-      <c r="A682" t="str" xml:space="preserve">
+    <row r="681" xml:space="preserve">
+      <c r="A681" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 316L-1.4404 Coil,
 1.20 x 136.0 x coil mm</v>
       </c>
-      <c r="B682" t="str" xml:space="preserve">
+      <c r="B681" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 316L-1.4404 Coil,
 1.20 x 136.0 x coil mm
 Weight (Kg):2,300
@@ -11302,12 +11286,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="683" xml:space="preserve">
-      <c r="A683" t="str" xml:space="preserve">
+    <row r="682" xml:space="preserve">
+      <c r="A682" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 304L/304-4301/4307 Coil, 2B,
 6.00 x 245.0 x coil mm</v>
       </c>
-      <c r="B683" t="str" xml:space="preserve">
+      <c r="B682" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 304L/304-4301/4307 Coil, 2B,
 6.00 x 245.0 x coil mm
 Weight (Kg):2,394
@@ -11318,12 +11302,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="684" xml:space="preserve">
-      <c r="A684" t="str" xml:space="preserve">
+    <row r="683" xml:space="preserve">
+      <c r="A683" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, 2B,
 0.70 x 197.5 x coil mm</v>
       </c>
-      <c r="B684" t="str" xml:space="preserve">
+      <c r="B683" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, 2B,
 0.70 x 197.5 x coil mm
 Weight (Kg):2,442
@@ -11334,12 +11318,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="685" xml:space="preserve">
-      <c r="A685" t="str" xml:space="preserve">
+    <row r="684" xml:space="preserve">
+      <c r="A684" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 441-1.4509 Coil, 2B,
 2.00 x 120.9 x coil mm</v>
       </c>
-      <c r="B685" t="str" xml:space="preserve">
+      <c r="B684" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 441-1.4509 Coil, 2B,
 2.00 x 120.9 x coil mm
 Weight (Kg):1,956
@@ -11347,6 +11331,22 @@
 Help
 Location:FABRICA ALGECIRAS
 1,100.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="685" xml:space="preserve">
+      <c r="A685" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 304-1.4301 Coil, 2B,
+1.20 x 119.9 x coil mm</v>
+      </c>
+      <c r="B685" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 304-1.4301 Coil, 2B,
+1.20 x 119.9 x coil mm
+Weight (Kg):1,500
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,075.00 €/ton
 Add to cart</v>
       </c>
     </row>
@@ -11358,7 +11358,7 @@
       <c r="B686" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 304-1.4301 Coil, 2B,
 1.20 x 119.9 x coil mm
-Weight (Kg):1,500
+Weight (Kg):1,400
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -11368,29 +11368,29 @@
     </row>
     <row r="687" xml:space="preserve">
       <c r="A687" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 304-1.4301 Coil, 2B,
-1.20 x 119.9 x coil mm</v>
+        <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, BA,
+0.70 x 125.0 x coil mm</v>
       </c>
       <c r="B687" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 304-1.4301 Coil, 2B,
-1.20 x 119.9 x coil mm
-Weight (Kg):1,400
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-2,075.00 €/ton
+        <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, BA,
+0.70 x 125.0 x coil mm
+Weight (Kg):1,764
+Quality:Prime
+Help
+Location:FABRICA ALGECIRAS
+1,000.00 €/ton
 Add to cart</v>
       </c>
     </row>
     <row r="688" xml:space="preserve">
       <c r="A688" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, BA,
-0.70 x 125.0 x coil mm</v>
+0.70 x 104.9 x coil mm</v>
       </c>
       <c r="B688" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, BA,
-0.70 x 125.0 x coil mm
-Weight (Kg):1,764
+0.70 x 104.9 x coil mm
+Weight (Kg):1,240
 Quality:Prime
 Help
 Location:FABRICA ALGECIRAS
@@ -11401,12 +11401,12 @@
     <row r="689" xml:space="preserve">
       <c r="A689" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, BA,
-0.70 x 104.9 x coil mm</v>
+0.70 x 118.9 x coil mm</v>
       </c>
       <c r="B689" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, BA,
-0.70 x 104.9 x coil mm
-Weight (Kg):1,240
+0.70 x 118.9 x coil mm
+Weight (Kg):1,802
 Quality:Prime
 Help
 Location:FABRICA ALGECIRAS
@@ -11417,12 +11417,12 @@
     <row r="690" xml:space="preserve">
       <c r="A690" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, BA,
-0.70 x 118.9 x coil mm</v>
+0.70 x 115.9 x coil mm</v>
       </c>
       <c r="B690" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, BA,
-0.70 x 118.9 x coil mm
-Weight (Kg):1,802
+0.70 x 115.9 x coil mm
+Weight (Kg):1,368
 Quality:Prime
 Help
 Location:FABRICA ALGECIRAS
@@ -11433,25 +11433,9 @@
     <row r="691" xml:space="preserve">
       <c r="A691" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, BA,
-0.70 x 115.9 x coil mm</v>
+0.70 x 119.0 x coil mm</v>
       </c>
       <c r="B691" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, BA,
-0.70 x 115.9 x coil mm
-Weight (Kg):1,368
-Quality:Prime
-Help
-Location:FABRICA ALGECIRAS
-1,000.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="692" xml:space="preserve">
-      <c r="A692" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, BA,
-0.70 x 119.0 x coil mm</v>
-      </c>
-      <c r="B692" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, BA,
 0.70 x 119.0 x coil mm
 Weight (Kg):1,622
@@ -11462,12 +11446,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="693" xml:space="preserve">
-      <c r="A693" t="str" xml:space="preserve">
+    <row r="692" xml:space="preserve">
+      <c r="A692" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 304L/304-4301/4307 Coil, 2B,
 1.40 x 110.9 x coil mm</v>
       </c>
-      <c r="B693" t="str" xml:space="preserve">
+      <c r="B692" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 304L/304-4301/4307 Coil, 2B,
 1.40 x 110.9 x coil mm
 Weight (Kg):1,240
@@ -11475,6 +11459,22 @@
 Help
 Location:FABRICA ALGECIRAS
 2,075.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="693" xml:space="preserve">
+      <c r="A693" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, BA,
+0.70 x 104.0 x coil mm</v>
+      </c>
+      <c r="B693" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, BA,
+0.70 x 104.0 x coil mm
+Weight (Kg):1,622
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+1,000.00 €/ton
 Add to cart</v>
       </c>
     </row>
@@ -11486,7 +11486,7 @@
       <c r="B694" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, BA,
 0.70 x 104.0 x coil mm
-Weight (Kg):1,622
+Weight (Kg):1,688
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -11496,26 +11496,10 @@
     </row>
     <row r="695" xml:space="preserve">
       <c r="A695" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, BA,
-0.70 x 104.0 x coil mm</v>
-      </c>
-      <c r="B695" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, BA,
-0.70 x 104.0 x coil mm
-Weight (Kg):1,688
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-1,000.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="696" xml:space="preserve">
-      <c r="A696" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 304L/304-4301/4307 Coil, 2B,
 1.40 x 110.9 x coil mm</v>
       </c>
-      <c r="B696" t="str" xml:space="preserve">
+      <c r="B695" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 304L/304-4301/4307 Coil, 2B,
 1.40 x 110.9 x coil mm
 Weight (Kg):1,162
@@ -11523,6 +11507,22 @@
 Help
 Location:FABRICA ALGECIRAS
 2,075.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="696" xml:space="preserve">
+      <c r="A696" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 430Ti-1.4510 Coil, BA,
+0.70 x 165.9 x coil mm</v>
+      </c>
+      <c r="B696" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 430Ti-1.4510 Coil, BA,
+0.70 x 165.9 x coil mm
+Weight (Kg):2,692
+Quality:Prime
+Help
+Location:FABRICA ALGECIRAS
+1,000.00 €/ton
 Add to cart</v>
       </c>
     </row>
@@ -11534,8 +11534,8 @@
       <c r="B697" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 430Ti-1.4510 Coil, BA,
 0.70 x 165.9 x coil mm
-Weight (Kg):2,692
-Quality:Prime
+Weight (Kg):2,756
+Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
 1,000.00 €/ton
@@ -11544,13 +11544,13 @@
     </row>
     <row r="698" xml:space="preserve">
       <c r="A698" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 430Ti-1.4510 Coil, BA,
-0.70 x 165.9 x coil mm</v>
+        <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, BA,
+0.70 x 140.9 x coil mm</v>
       </c>
       <c r="B698" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 430Ti-1.4510 Coil, BA,
-0.70 x 165.9 x coil mm
-Weight (Kg):2,756
+        <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, BA,
+0.70 x 140.9 x coil mm
+Weight (Kg):1,676
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -11561,12 +11561,12 @@
     <row r="699" xml:space="preserve">
       <c r="A699" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, BA,
-0.70 x 140.9 x coil mm</v>
+0.70 x 100.9 x coil mm</v>
       </c>
       <c r="B699" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, BA,
-0.70 x 140.9 x coil mm
-Weight (Kg):1,676
+0.70 x 100.9 x coil mm
+Weight (Kg):1,340
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -11577,12 +11577,12 @@
     <row r="700" xml:space="preserve">
       <c r="A700" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, BA,
-0.70 x 100.9 x coil mm</v>
+0.70 x 125.0 x coil mm</v>
       </c>
       <c r="B700" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, BA,
-0.70 x 100.9 x coil mm
-Weight (Kg):1,340
+0.70 x 125.0 x coil mm
+Weight (Kg):1,550
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -11598,7 +11598,7 @@
       <c r="B701" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, BA,
 0.70 x 125.0 x coil mm
-Weight (Kg):1,550
+Weight (Kg):1,414
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -11609,25 +11609,9 @@
     <row r="702" xml:space="preserve">
       <c r="A702" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, BA,
-0.70 x 125.0 x coil mm</v>
+0.70 x 100.9 x coil mm</v>
       </c>
       <c r="B702" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, BA,
-0.70 x 125.0 x coil mm
-Weight (Kg):1,414
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-1,000.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="703" xml:space="preserve">
-      <c r="A703" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, BA,
-0.70 x 100.9 x coil mm</v>
-      </c>
-      <c r="B703" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, BA,
 0.70 x 100.9 x coil mm
 Weight (Kg):2,188
@@ -11635,6 +11619,22 @@
 Help
 Location:FABRICA ALGECIRAS
 1,000.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="703" xml:space="preserve">
+      <c r="A703" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 304L/304-4301/4307 Coil, Nb. 1,
+4.70 x 110.0 x coil mm</v>
+      </c>
+      <c r="B703" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 304L/304-4301/4307 Coil, Nb. 1,
+4.70 x 110.0 x coil mm
+Weight (Kg):1,796
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+1,975.00 €/ton
 Add to cart</v>
       </c>
     </row>
@@ -11646,7 +11646,7 @@
       <c r="B704" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 304L/304-4301/4307 Coil, Nb. 1,
 4.70 x 110.0 x coil mm
-Weight (Kg):1,796
+Weight (Kg):2,038
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -11656,26 +11656,10 @@
     </row>
     <row r="705" xml:space="preserve">
       <c r="A705" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 304L/304-4301/4307 Coil, Nb. 1,
-4.70 x 110.0 x coil mm</v>
-      </c>
-      <c r="B705" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 304L/304-4301/4307 Coil, Nb. 1,
-4.70 x 110.0 x coil mm
-Weight (Kg):2,038
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-1,975.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="706" xml:space="preserve">
-      <c r="A706" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, BA,
 0.70 x 165.9 x coil mm</v>
       </c>
-      <c r="B706" t="str" xml:space="preserve">
+      <c r="B705" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, BA,
 0.70 x 165.9 x coil mm
 Weight (Kg):2,620
@@ -11683,6 +11667,22 @@
 Help
 Location:FABRICA ALGECIRAS
 1,000.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="706" xml:space="preserve">
+      <c r="A706" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 304-1.4301 Coil,
+0.70 x 260.9 x coil mm</v>
+      </c>
+      <c r="B706" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 304-1.4301 Coil,
+0.70 x 260.9 x coil mm
+Weight (Kg):1,330
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,075.00 €/ton
 Add to cart</v>
       </c>
     </row>
@@ -11694,7 +11694,7 @@
       <c r="B707" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 304-1.4301 Coil,
 0.70 x 260.9 x coil mm
-Weight (Kg):1,330
+Weight (Kg):1,264
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -11704,42 +11704,26 @@
     </row>
     <row r="708" xml:space="preserve">
       <c r="A708" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 304-1.4301 Coil,
-0.70 x 260.9 x coil mm</v>
+        <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, BA,
+0.70 x 110.0 x coil mm</v>
       </c>
       <c r="B708" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 304-1.4301 Coil,
-0.70 x 260.9 x coil mm
-Weight (Kg):1,264
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-2,075.00 €/ton
+        <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, BA,
+0.70 x 110.0 x coil mm
+Weight (Kg):1,250
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+1,000.00 €/ton
 Add to cart</v>
       </c>
     </row>
     <row r="709" xml:space="preserve">
       <c r="A709" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, BA,
-0.70 x 110.0 x coil mm</v>
+0.70 x 122.9 x coil mm</v>
       </c>
       <c r="B709" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, BA,
-0.70 x 110.0 x coil mm
-Weight (Kg):1,250
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-1,000.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="710" xml:space="preserve">
-      <c r="A710" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, BA,
-0.70 x 122.9 x coil mm</v>
-      </c>
-      <c r="B710" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, BA,
 0.70 x 122.9 x coil mm
 Weight (Kg):1,460
@@ -11747,6 +11731,22 @@
 Help
 Location:FABRICA ALGECIRAS
 1,000.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="710" xml:space="preserve">
+      <c r="A710" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 304L/304-4301/4307 Coil, 2B,
+1.40 x 110.0 x coil mm</v>
+      </c>
+      <c r="B710" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 304L/304-4301/4307 Coil, 2B,
+1.40 x 110.0 x coil mm
+Weight (Kg):1,554
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,075.00 €/ton
 Add to cart</v>
       </c>
     </row>
@@ -11758,7 +11758,7 @@
       <c r="B711" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 304L/304-4301/4307 Coil, 2B,
 1.40 x 110.0 x coil mm
-Weight (Kg):1,554
+Weight (Kg):1,586
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -11769,25 +11769,9 @@
     <row r="712" xml:space="preserve">
       <c r="A712" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 304L/304-4301/4307 Coil, 2B,
-1.40 x 110.0 x coil mm</v>
+1.40 x 104.0 x coil mm</v>
       </c>
       <c r="B712" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 304L/304-4301/4307 Coil, 2B,
-1.40 x 110.0 x coil mm
-Weight (Kg):1,586
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-2,075.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="713" xml:space="preserve">
-      <c r="A713" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 304L/304-4301/4307 Coil, 2B,
-1.40 x 104.0 x coil mm</v>
-      </c>
-      <c r="B713" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 304L/304-4301/4307 Coil, 2B,
 1.40 x 104.0 x coil mm
 Weight (Kg):1,030
@@ -11798,12 +11782,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="714" xml:space="preserve">
-      <c r="A714" t="str" xml:space="preserve">
+    <row r="713" xml:space="preserve">
+      <c r="A713" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 304DDQ-1.4301 Coil, BA,
 0.70 x 181.9 x coil mm</v>
       </c>
-      <c r="B714" t="str" xml:space="preserve">
+      <c r="B713" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 304DDQ-1.4301 Coil, BA,
 0.70 x 181.9 x coil mm
 Weight (Kg):2,912
@@ -11814,12 +11798,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="715" xml:space="preserve">
-      <c r="A715" t="str" xml:space="preserve">
+    <row r="714" xml:space="preserve">
+      <c r="A714" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 304-1.4301 Coil,
 1.50 x 136.0 x coil mm</v>
       </c>
-      <c r="B715" t="str" xml:space="preserve">
+      <c r="B714" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 304-1.4301 Coil,
 1.50 x 136.0 x coil mm
 Weight (Kg):3,450
@@ -11830,12 +11814,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="716" xml:space="preserve">
-      <c r="A716" t="str" xml:space="preserve">
+    <row r="715" xml:space="preserve">
+      <c r="A715" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 304-1.4301 Coil, BA,
 0.40 x 200.0 x coil mm</v>
       </c>
-      <c r="B716" t="str" xml:space="preserve">
+      <c r="B715" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 304-1.4301 Coil, BA,
 0.40 x 200.0 x coil mm
 Weight (Kg):1,964
@@ -11846,12 +11830,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="717" xml:space="preserve">
-      <c r="A717" t="str" xml:space="preserve">
+    <row r="716" xml:space="preserve">
+      <c r="A716" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 304-1.4301 Coil, BA, ET-60
 0.60 x 120.0 x coil mm</v>
       </c>
-      <c r="B717" t="str" xml:space="preserve">
+      <c r="B716" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 304-1.4301 Coil, BA, ET-60
 0.60 x 120.0 x coil mm
 Weight (Kg):1,302
@@ -11859,6 +11843,22 @@
 Help
 Location:FABRICA ALGECIRAS
 2,075.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="717" xml:space="preserve">
+      <c r="A717" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, ET-100
+0.70 x 124.9 x coil mm</v>
+      </c>
+      <c r="B717" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, ET-100
+0.70 x 124.9 x coil mm
+Weight (Kg):2,106
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+1,000.00 €/ton
 Add to cart</v>
       </c>
     </row>
@@ -11870,7 +11870,7 @@
       <c r="B718" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, ET-100
 0.70 x 124.9 x coil mm
-Weight (Kg):2,106
+Weight (Kg):1,972
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -11880,26 +11880,10 @@
     </row>
     <row r="719" xml:space="preserve">
       <c r="A719" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, ET-100
-0.70 x 124.9 x coil mm</v>
-      </c>
-      <c r="B719" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, ET-100
-0.70 x 124.9 x coil mm
-Weight (Kg):1,972
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-1,000.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="720" xml:space="preserve">
-      <c r="A720" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 430Ti-1.4510 Coil, 2B,
 0.80 x 155.9 x coil mm</v>
       </c>
-      <c r="B720" t="str" xml:space="preserve">
+      <c r="B719" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 430Ti-1.4510 Coil, 2B,
 0.80 x 155.9 x coil mm
 Weight (Kg):1,586
@@ -11910,12 +11894,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="721" xml:space="preserve">
-      <c r="A721" t="str" xml:space="preserve">
+    <row r="720" xml:space="preserve">
+      <c r="A720" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 304-1.4301 Coil, BA,
 0.40 x 270.0 x coil mm</v>
       </c>
-      <c r="B721" t="str" xml:space="preserve">
+      <c r="B720" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 304-1.4301 Coil, BA,
 0.40 x 270.0 x coil mm
 Weight (Kg):2,572
@@ -11926,12 +11910,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="722" xml:space="preserve">
-      <c r="A722" t="str" xml:space="preserve">
+    <row r="721" xml:space="preserve">
+      <c r="A721" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, BA,
 0.60 x 130.0 x coil mm</v>
       </c>
-      <c r="B722" t="str" xml:space="preserve">
+      <c r="B721" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, BA,
 0.60 x 130.0 x coil mm
 Weight (Kg):1,490
@@ -11939,6 +11923,22 @@
 Help
 Location:FABRICA ALGECIRAS
 1,000.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="722" xml:space="preserve">
+      <c r="A722" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 441-1.4509 Coil, BA,
+0.40 x 110.0 x coil mm</v>
+      </c>
+      <c r="B722" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 441-1.4509 Coil, BA,
+0.40 x 110.0 x coil mm
+Weight (Kg):1,870
+Quality:Prime
+Help
+Location:FABRICA ALGECIRAS
+1,100.00 €/ton
 Add to cart</v>
       </c>
     </row>
@@ -11950,7 +11950,7 @@
       <c r="B723" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 441-1.4509 Coil, BA,
 0.40 x 110.0 x coil mm
-Weight (Kg):1,870
+Weight (Kg):1,882
 Quality:Prime
 Help
 Location:FABRICA ALGECIRAS
@@ -11960,17 +11960,17 @@
     </row>
     <row r="724" xml:space="preserve">
       <c r="A724" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 441-1.4509 Coil, BA,
+        <v xml:space="preserve">Acerinox Europa, 301-1.4310 Coil, BA,
 0.40 x 110.0 x coil mm</v>
       </c>
       <c r="B724" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 441-1.4509 Coil, BA,
+        <v xml:space="preserve">Acerinox Europa, 301-1.4310 Coil, BA,
 0.40 x 110.0 x coil mm
-Weight (Kg):1,882
-Quality:Prime
-Help
-Location:FABRICA ALGECIRAS
-1,100.00 €/ton
+Weight (Kg):1,934
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+1,925.00 €/ton
 Add to cart</v>
       </c>
     </row>
@@ -11982,7 +11982,7 @@
       <c r="B725" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 301-1.4310 Coil, BA,
 0.40 x 110.0 x coil mm
-Weight (Kg):1,934
+Weight (Kg):1,860
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -11992,26 +11992,10 @@
     </row>
     <row r="726" xml:space="preserve">
       <c r="A726" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 301-1.4310 Coil, BA,
-0.40 x 110.0 x coil mm</v>
-      </c>
-      <c r="B726" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 301-1.4310 Coil, BA,
-0.40 x 110.0 x coil mm
-Weight (Kg):1,860
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-1,925.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="727" xml:space="preserve">
-      <c r="A727" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 321-1.4541 Coil, 2B,
 1.90 x 104.5 x coil mm</v>
       </c>
-      <c r="B727" t="str" xml:space="preserve">
+      <c r="B726" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 321-1.4541 Coil, 2B,
 1.90 x 104.5 x coil mm
 Weight (Kg):2,304
@@ -12022,12 +12006,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="728" xml:space="preserve">
-      <c r="A728" t="str" xml:space="preserve">
+    <row r="727" xml:space="preserve">
+      <c r="A727" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 304L/304-4301/4307 Coil, Polished N4-G-180,
 1.20 x 255.9 x coil mm</v>
       </c>
-      <c r="B728" t="str" xml:space="preserve">
+      <c r="B727" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 304L/304-4301/4307 Coil, Polished N4-G-180,
 1.20 x 255.9 x coil mm
 Weight (Kg):4,298
@@ -12038,12 +12022,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="729" xml:space="preserve">
-      <c r="A729" t="str" xml:space="preserve">
+    <row r="728" xml:space="preserve">
+      <c r="A728" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 301-1.4310 Coil, BA,
 0.40 x 110.0 x coil mm</v>
       </c>
-      <c r="B729" t="str" xml:space="preserve">
+      <c r="B728" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 301-1.4310 Coil, BA,
 0.40 x 110.0 x coil mm
 Weight (Kg):1,698
@@ -12054,15 +12038,31 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="730" xml:space="preserve">
-      <c r="A730" t="str" xml:space="preserve">
+    <row r="729" xml:space="preserve">
+      <c r="A729" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, BA,
 0.40 x 130.0 x coil mm</v>
       </c>
-      <c r="B730" t="str" xml:space="preserve">
+      <c r="B729" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, BA,
 0.40 x 130.0 x coil mm
 Weight (Kg):1,916
+Quality:Prime
+Help
+Location:FABRICA ALGECIRAS
+1,000.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="730" xml:space="preserve">
+      <c r="A730" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 430Ti-1.4510 Coil, BA,
+0.50 x 140.0 x coil mm</v>
+      </c>
+      <c r="B730" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 430Ti-1.4510 Coil, BA,
+0.50 x 140.0 x coil mm
+Weight (Kg):3,054
 Quality:Prime
 Help
 Location:FABRICA ALGECIRAS
@@ -12078,7 +12078,7 @@
       <c r="B731" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 430Ti-1.4510 Coil, BA,
 0.50 x 140.0 x coil mm
-Weight (Kg):3,054
+Weight (Kg):3,060
 Quality:Prime
 Help
 Location:FABRICA ALGECIRAS
@@ -12094,7 +12094,7 @@
       <c r="B732" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 430Ti-1.4510 Coil, BA,
 0.50 x 140.0 x coil mm
-Weight (Kg):3,060
+Weight (Kg):2,220
 Quality:Prime
 Help
 Location:FABRICA ALGECIRAS
@@ -12110,7 +12110,7 @@
       <c r="B733" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 430Ti-1.4510 Coil, BA,
 0.50 x 140.0 x coil mm
-Weight (Kg):2,220
+Weight (Kg):2,224
 Quality:Prime
 Help
 Location:FABRICA ALGECIRAS
@@ -12120,17 +12120,17 @@
     </row>
     <row r="734" xml:space="preserve">
       <c r="A734" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 430Ti-1.4510 Coil, BA,
-0.50 x 140.0 x coil mm</v>
+        <v xml:space="preserve">Acerinox Europa, 304L/304-4301/4307 Coil, 2B,
+1.40 x 100.9 x coil mm</v>
       </c>
       <c r="B734" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 430Ti-1.4510 Coil, BA,
-0.50 x 140.0 x coil mm
-Weight (Kg):2,224
-Quality:Prime
-Help
-Location:FABRICA ALGECIRAS
-1,000.00 €/ton
+        <v xml:space="preserve">Acerinox Europa, 304L/304-4301/4307 Coil, 2B,
+1.40 x 100.9 x coil mm
+Weight (Kg):1,612
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,075.00 €/ton
 Add to cart</v>
       </c>
     </row>
@@ -12142,7 +12142,7 @@
       <c r="B735" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 304L/304-4301/4307 Coil, 2B,
 1.40 x 100.9 x coil mm
-Weight (Kg):1,612
+Weight (Kg):1,600
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -12152,14 +12152,14 @@
     </row>
     <row r="736" xml:space="preserve">
       <c r="A736" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 304L/304-4301/4307 Coil, 2B,
-1.40 x 100.9 x coil mm</v>
+        <v xml:space="preserve">Acerinox Europa, 304-1.4301 Coil, Emboss Chequered,
+0.70 x 174.9 x coil mm</v>
       </c>
       <c r="B736" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 304L/304-4301/4307 Coil, 2B,
-1.40 x 100.9 x coil mm
-Weight (Kg):1,600
-Quality:Prime-2
+        <v xml:space="preserve">Acerinox Europa, 304-1.4301 Coil, Emboss Chequered,
+0.70 x 174.9 x coil mm
+Weight (Kg):1,494
+Quality:Prime
 Help
 Location:FABRICA ALGECIRAS
 2,075.00 €/ton
@@ -12174,7 +12174,7 @@
       <c r="B737" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 304-1.4301 Coil, Emboss Chequered,
 0.70 x 174.9 x coil mm
-Weight (Kg):1,494
+Weight (Kg):1,472
 Quality:Prime
 Help
 Location:FABRICA ALGECIRAS
@@ -12184,26 +12184,10 @@
     </row>
     <row r="738" xml:space="preserve">
       <c r="A738" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 304-1.4301 Coil, Emboss Chequered,
-0.70 x 174.9 x coil mm</v>
-      </c>
-      <c r="B738" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 304-1.4301 Coil, Emboss Chequered,
-0.70 x 174.9 x coil mm
-Weight (Kg):1,472
-Quality:Prime
-Help
-Location:FABRICA ALGECIRAS
-2,075.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="739" xml:space="preserve">
-      <c r="A739" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, SB-G-240,
 0.50 x 290.9 x coil mm</v>
       </c>
-      <c r="B739" t="str" xml:space="preserve">
+      <c r="B738" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, SB-G-240,
 0.50 x 290.9 x coil mm
 Weight (Kg):4,408
@@ -12214,15 +12198,31 @@
 Add to cart</v>
       </c>
     </row>
+    <row r="739" xml:space="preserve">
+      <c r="A739" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 304-1.4301 Coil, BA,
+0.60 x 110.0 x coil mm</v>
+      </c>
+      <c r="B739" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 304-1.4301 Coil, BA,
+0.60 x 110.0 x coil mm
+Weight (Kg):1,032
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,075.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
     <row r="740" xml:space="preserve">
       <c r="A740" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 304-1.4301 Coil, BA,
-0.60 x 110.0 x coil mm</v>
+0.40 x 270.0 x coil mm</v>
       </c>
       <c r="B740" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 304-1.4301 Coil, BA,
-0.60 x 110.0 x coil mm
-Weight (Kg):1,032
+0.40 x 270.0 x coil mm
+Weight (Kg):3,124
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -12233,25 +12233,9 @@
     <row r="741" xml:space="preserve">
       <c r="A741" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 304-1.4301 Coil, BA,
-0.40 x 270.0 x coil mm</v>
+0.60 x 135.0 x coil mm</v>
       </c>
       <c r="B741" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 304-1.4301 Coil, BA,
-0.40 x 270.0 x coil mm
-Weight (Kg):3,124
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-2,075.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="742" xml:space="preserve">
-      <c r="A742" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 304-1.4301 Coil, BA,
-0.60 x 135.0 x coil mm</v>
-      </c>
-      <c r="B742" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 304-1.4301 Coil, BA,
 0.60 x 135.0 x coil mm
 Weight (Kg):2,078
@@ -12262,12 +12246,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="743" xml:space="preserve">
-      <c r="A743" t="str" xml:space="preserve">
+    <row r="742" xml:space="preserve">
+      <c r="A742" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 441-1.4509 Coil, 2B,
 2.00 x 245.9 x coil mm</v>
       </c>
-      <c r="B743" t="str" xml:space="preserve">
+      <c r="B742" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 441-1.4509 Coil, 2B,
 2.00 x 245.9 x coil mm
 Weight (Kg):3,492
@@ -12278,12 +12262,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="744" xml:space="preserve">
-      <c r="A744" t="str" xml:space="preserve">
+    <row r="743" xml:space="preserve">
+      <c r="A743" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 304-1.4301 Coil, 2B,
 0.60 x 101.9 x coil mm</v>
       </c>
-      <c r="B744" t="str" xml:space="preserve">
+      <c r="B743" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 304-1.4301 Coil, 2B,
 0.60 x 101.9 x coil mm
 Weight (Kg):1,350
@@ -12294,12 +12278,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="745" xml:space="preserve">
-      <c r="A745" t="str" xml:space="preserve">
+    <row r="744" xml:space="preserve">
+      <c r="A744" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 430Ti-1.4510 Coil, BA,
 0.70 x 118.9 x coil mm</v>
       </c>
-      <c r="B745" t="str" xml:space="preserve">
+      <c r="B744" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 430Ti-1.4510 Coil, BA,
 0.70 x 118.9 x coil mm
 Weight (Kg):1,768
@@ -12310,28 +12294,28 @@
 Add to cart</v>
       </c>
     </row>
+    <row r="745" xml:space="preserve">
+      <c r="A745" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 304L/304-4301/4307 Coil, 2B,
+1.00 x 135.9 x coil mm</v>
+      </c>
+      <c r="B745" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 304L/304-4301/4307 Coil, 2B,
+1.00 x 135.9 x coil mm
+Weight (Kg):1,056
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,075.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
     <row r="746" xml:space="preserve">
       <c r="A746" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 304L/304-4301/4307 Coil, 2B,
-1.00 x 135.9 x coil mm</v>
+2.00 x 250.0 x coil mm</v>
       </c>
       <c r="B746" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 304L/304-4301/4307 Coil, 2B,
-1.00 x 135.9 x coil mm
-Weight (Kg):1,056
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-2,075.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="747" xml:space="preserve">
-      <c r="A747" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 304L/304-4301/4307 Coil, 2B,
-2.00 x 250.0 x coil mm</v>
-      </c>
-      <c r="B747" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 304L/304-4301/4307 Coil, 2B,
 2.00 x 250.0 x coil mm
 Weight (Kg):2,388
@@ -12339,6 +12323,22 @@
 Help
 Location:FABRICA ALGECIRAS
 2,075.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="747" xml:space="preserve">
+      <c r="A747" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, BA,
+0.70 x 125.9 x coil mm</v>
+      </c>
+      <c r="B747" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, BA,
+0.70 x 125.9 x coil mm
+Weight (Kg):1,788
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+1,000.00 €/ton
 Add to cart</v>
       </c>
     </row>
@@ -12350,7 +12350,7 @@
       <c r="B748" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, BA,
 0.70 x 125.9 x coil mm
-Weight (Kg):1,788
+Weight (Kg):1,794
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -12360,26 +12360,10 @@
     </row>
     <row r="749" xml:space="preserve">
       <c r="A749" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, BA,
-0.70 x 125.9 x coil mm</v>
-      </c>
-      <c r="B749" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, BA,
-0.70 x 125.9 x coil mm
-Weight (Kg):1,794
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-1,000.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="750" xml:space="preserve">
-      <c r="A750" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 430Ti-1.4510 Coil, BA,
 0.70 x 112.0 x coil mm</v>
       </c>
-      <c r="B750" t="str" xml:space="preserve">
+      <c r="B749" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 430Ti-1.4510 Coil, BA,
 0.70 x 112.0 x coil mm
 Weight (Kg):1,550
@@ -12387,6 +12371,22 @@
 Help
 Location:FABRICA ALGECIRAS
 1,000.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="750" xml:space="preserve">
+      <c r="A750" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 304-1.4301 Coil, BA,
+0.60 x 320.0 x coil mm</v>
+      </c>
+      <c r="B750" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 304-1.4301 Coil, BA,
+0.60 x 320.0 x coil mm
+Weight (Kg):2,534
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,075.00 €/ton
 Add to cart</v>
       </c>
     </row>
@@ -12398,7 +12398,7 @@
       <c r="B751" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 304-1.4301 Coil, BA,
 0.60 x 320.0 x coil mm
-Weight (Kg):2,534
+Weight (Kg):3,148
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -12408,26 +12408,10 @@
     </row>
     <row r="752" xml:space="preserve">
       <c r="A752" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 304-1.4301 Coil, BA,
-0.60 x 320.0 x coil mm</v>
-      </c>
-      <c r="B752" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 304-1.4301 Coil, BA,
-0.60 x 320.0 x coil mm
-Weight (Kg):3,148
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-2,075.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="753" xml:space="preserve">
-      <c r="A753" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 304-1.4301 Coil, 2B,
 0.80 x 199.9 x coil mm</v>
       </c>
-      <c r="B753" t="str" xml:space="preserve">
+      <c r="B752" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 304-1.4301 Coil, 2B,
 0.80 x 199.9 x coil mm
 Weight (Kg):2,602
@@ -12438,12 +12422,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="754" xml:space="preserve">
-      <c r="A754" t="str" xml:space="preserve">
+    <row r="753" xml:space="preserve">
+      <c r="A753" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 304L/304-4301/4307 Coil, 2B,
 1.00 x 125.9 x coil mm</v>
       </c>
-      <c r="B754" t="str" xml:space="preserve">
+      <c r="B753" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 304L/304-4301/4307 Coil, 2B,
 1.00 x 125.9 x coil mm
 Weight (Kg):1,726
@@ -12454,12 +12438,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="755" xml:space="preserve">
-      <c r="A755" t="str" xml:space="preserve">
+    <row r="754" xml:space="preserve">
+      <c r="A754" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 316L-1.4404 Coil, 2B,
 1.50 x 230.9 x coil mm</v>
       </c>
-      <c r="B755" t="str" xml:space="preserve">
+      <c r="B754" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 316L-1.4404 Coil, 2B,
 1.50 x 230.9 x coil mm
 Weight (Kg):1,956
@@ -12470,12 +12454,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="756" xml:space="preserve">
-      <c r="A756" t="str" xml:space="preserve">
+    <row r="755" xml:space="preserve">
+      <c r="A755" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, SBA,
 0.70 x 180.9 x coil mm</v>
       </c>
-      <c r="B756" t="str" xml:space="preserve">
+      <c r="B755" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, SBA,
 0.70 x 180.9 x coil mm
 Weight (Kg):2,402
@@ -12486,12 +12470,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="757" xml:space="preserve">
-      <c r="A757" t="str" xml:space="preserve">
+    <row r="756" xml:space="preserve">
+      <c r="A756" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 301-1.4310 Coil, BA,
 0.40 x 110.0 x coil mm</v>
       </c>
-      <c r="B757" t="str" xml:space="preserve">
+      <c r="B756" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 301-1.4310 Coil, BA,
 0.40 x 110.0 x coil mm
 Weight (Kg):1,734
@@ -12504,7 +12488,7 @@
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B757"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B756"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/scraped_data.xlsx
+++ b/scraped_data.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B746"/>
+  <dimension ref="A1:B745"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -9610,17 +9610,17 @@
     <row r="577" xml:space="preserve">
       <c r="A577" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, BA,
-0.40 x 596.2 x coil mm</v>
+0.70 x 825.0 x coil mm</v>
       </c>
       <c r="B577" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, BA,
-0.40 x 596.2 x coil mm
-Weight (Kg):4,371
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-1,050.00 €/ton
-Out of Stock</v>
+0.70 x 825.0 x coil mm
+Weight (Kg):5,270
+Quality:Prime
+Help
+Location:FABRICA ALGECIRAS
+1,325.00 €/ton
+Add to cart</v>
       </c>
     </row>
     <row r="578" xml:space="preserve">
@@ -9690,89 +9690,73 @@
     <row r="582" xml:space="preserve">
       <c r="A582" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, BA,
-0.70 x 825.0 x coil mm</v>
+0.70 x 842.0 x coil mm</v>
       </c>
       <c r="B582" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, BA,
-0.70 x 825.0 x coil mm
-Weight (Kg):5,270
-Quality:Prime
-Help
-Location:FABRICA ALGECIRAS
-1,325.00 €/ton
+0.70 x 842.0 x coil mm
+Weight (Kg):10,370
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+1,125.00 €/ton
 Add to cart</v>
       </c>
     </row>
     <row r="583" xml:space="preserve">
       <c r="A583" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, BA,
-0.70 x 842.0 x coil mm</v>
+0.70 x 855.0 x coil mm</v>
       </c>
       <c r="B583" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, BA,
-0.70 x 842.0 x coil mm
-Weight (Kg):10,370
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-1,125.00 €/ton
+0.70 x 855.0 x coil mm
+Weight (Kg):3,990
+Quality:Prime
+Help
+Location:FABRICA ALGECIRAS
+1,325.00 €/ton
 Add to cart</v>
       </c>
     </row>
     <row r="584" xml:space="preserve">
       <c r="A584" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, BA,
-0.70 x 855.0 x coil mm</v>
+0.70 x 870.0 x coil mm</v>
       </c>
       <c r="B584" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, BA,
-0.70 x 855.0 x coil mm
-Weight (Kg):3,990
-Quality:Prime
-Help
-Location:FABRICA ALGECIRAS
-1,325.00 €/ton
+0.70 x 870.0 x coil mm
+Weight (Kg):13,910
+Quality:Prime
+Help
+Location:FABRICA ALGECIRAS
+1,900.00 €/ton
 Add to cart</v>
       </c>
     </row>
     <row r="585" xml:space="preserve">
       <c r="A585" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, BA,
-0.70 x 870.0 x coil mm</v>
+0.70 x 953.0 x coil mm</v>
       </c>
       <c r="B585" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, BA,
-0.70 x 870.0 x coil mm
-Weight (Kg):13,910
-Quality:Prime
-Help
-Location:FABRICA ALGECIRAS
-1,900.00 €/ton
+0.70 x 953.0 x coil mm
+Weight (Kg):6,970
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+1,125.00 €/ton
 Add to cart</v>
       </c>
     </row>
     <row r="586" xml:space="preserve">
       <c r="A586" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, BA,
-0.70 x 953.0 x coil mm</v>
+1.00 x 530.0 x coil mm</v>
       </c>
       <c r="B586" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, BA,
-0.70 x 953.0 x coil mm
-Weight (Kg):6,970
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-1,125.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="587" xml:space="preserve">
-      <c r="A587" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, BA,
-1.00 x 530.0 x coil mm</v>
-      </c>
-      <c r="B587" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, BA,
 1.00 x 530.0 x coil mm
 Weight (Kg):880
@@ -9783,32 +9767,48 @@
 Add to cart</v>
       </c>
     </row>
+    <row r="587" xml:space="preserve">
+      <c r="A587" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, Polished N4-G-180,
+0.90 x 1250.0 x coil mm</v>
+      </c>
+      <c r="B587" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, Polished N4-G-180,
+0.90 x 1250.0 x coil mm
+Weight (Kg):2,218
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+1,125.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
     <row r="588" xml:space="preserve">
       <c r="A588" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, Polished N4-G-180,
-0.90 x 1250.0 x coil mm</v>
+1.20 x 120.0 x coil mm</v>
       </c>
       <c r="B588" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, Polished N4-G-180,
-0.90 x 1250.0 x coil mm
-Weight (Kg):2,218
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-1,125.00 €/ton
+1.20 x 120.0 x coil mm
+Weight (Kg):1,430
+Quality:Prime
+Help
+Location:FABRICA ALGECIRAS
+1,000.00 €/ton
 Add to cart</v>
       </c>
     </row>
     <row r="589" xml:space="preserve">
       <c r="A589" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, Polished N4-G-180,
-1.20 x 120.0 x coil mm</v>
+1.20 x 250.0 x coil mm</v>
       </c>
       <c r="B589" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, Polished N4-G-180,
-1.20 x 120.0 x coil mm
-Weight (Kg):1,430
-Quality:Prime
+1.20 x 250.0 x coil mm
+Weight (Kg):1,902
+Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
 1,000.00 €/ton
@@ -9818,13 +9818,13 @@
     <row r="590" xml:space="preserve">
       <c r="A590" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, Polished N4-G-180,
-1.20 x 250.0 x coil mm</v>
+1.20 x 250.9 x coil mm</v>
       </c>
       <c r="B590" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, Polished N4-G-180,
-1.20 x 250.0 x coil mm
-Weight (Kg):1,902
-Quality:Prime-2
+1.20 x 250.9 x coil mm
+Weight (Kg):1,960
+Quality:Prime
 Help
 Location:FABRICA ALGECIRAS
 1,000.00 €/ton
@@ -9839,8 +9839,8 @@
       <c r="B591" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, Polished N4-G-180,
 1.20 x 250.9 x coil mm
-Weight (Kg):1,960
-Quality:Prime
+Weight (Kg):1,918
+Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
 1,000.00 €/ton
@@ -9850,12 +9850,12 @@
     <row r="592" xml:space="preserve">
       <c r="A592" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, Polished N4-G-180,
-1.20 x 250.9 x coil mm</v>
+1.20 x 260.9 x coil mm</v>
       </c>
       <c r="B592" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, Polished N4-G-180,
-1.20 x 250.9 x coil mm
-Weight (Kg):1,918
+1.20 x 260.9 x coil mm
+Weight (Kg):1,524
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -9871,7 +9871,7 @@
       <c r="B593" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, Polished N4-G-180,
 1.20 x 260.9 x coil mm
-Weight (Kg):1,524
+Weight (Kg):1,934
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -9881,13 +9881,13 @@
     </row>
     <row r="594" xml:space="preserve">
       <c r="A594" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, Polished N4-G-180,
-1.20 x 260.9 x coil mm</v>
+        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, SB-G-400,
+0.60 x 134.9 x coil mm</v>
       </c>
       <c r="B594" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, Polished N4-G-180,
-1.20 x 260.9 x coil mm
-Weight (Kg):1,934
+        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, SB-G-400,
+0.60 x 134.9 x coil mm
+Weight (Kg):1,134
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -9903,7 +9903,7 @@
       <c r="B595" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, SB-G-400,
 0.60 x 134.9 x coil mm
-Weight (Kg):1,134
+Weight (Kg):962
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -9914,12 +9914,12 @@
     <row r="596" xml:space="preserve">
       <c r="A596" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, SB-G-400,
-0.60 x 134.9 x coil mm</v>
+0.60 x 245.9 x coil mm</v>
       </c>
       <c r="B596" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, SB-G-400,
-0.60 x 134.9 x coil mm
-Weight (Kg):962
+0.60 x 245.9 x coil mm
+Weight (Kg):1,778
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -9930,12 +9930,12 @@
     <row r="597" xml:space="preserve">
       <c r="A597" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, SB-G-400,
-0.60 x 245.9 x coil mm</v>
+1.00 x 118.9 x coil mm</v>
       </c>
       <c r="B597" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, SB-G-400,
-0.60 x 245.9 x coil mm
-Weight (Kg):1,778
+1.00 x 118.9 x coil mm
+Weight (Kg):754
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -9951,7 +9951,7 @@
       <c r="B598" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, SB-G-400,
 1.00 x 118.9 x coil mm
-Weight (Kg):754
+Weight (Kg):802
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -9962,25 +9962,9 @@
     <row r="599" xml:space="preserve">
       <c r="A599" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, SB-G-400,
-1.00 x 118.9 x coil mm</v>
+1.00 x 266.9 x coil mm</v>
       </c>
       <c r="B599" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, SB-G-400,
-1.00 x 118.9 x coil mm
-Weight (Kg):802
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-1,000.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="600" xml:space="preserve">
-      <c r="A600" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, SB-G-400,
-1.00 x 266.9 x coil mm</v>
-      </c>
-      <c r="B600" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, SB-G-400,
 1.00 x 266.9 x coil mm
 Weight (Kg):1,322
@@ -9991,12 +9975,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="601" xml:space="preserve">
-      <c r="A601" t="str" xml:space="preserve">
+    <row r="600" xml:space="preserve">
+      <c r="A600" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, SB-G-500,
 0.70 x 245.9 x coil mm</v>
       </c>
-      <c r="B601" t="str" xml:space="preserve">
+      <c r="B600" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, SB-G-500,
 0.70 x 245.9 x coil mm
 Weight (Kg):1,496
@@ -10007,32 +9991,48 @@
 Add to cart</v>
       </c>
     </row>
+    <row r="601" xml:space="preserve">
+      <c r="A601" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, SBA,
+0.70 x 1056.0 x coil mm</v>
+      </c>
+      <c r="B601" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, SBA,
+0.70 x 1056.0 x coil mm
+Weight (Kg):15,197
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+1,125.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
     <row r="602" xml:space="preserve">
       <c r="A602" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, SBA,
-0.70 x 1056.0 x coil mm</v>
+0.70 x 150.9 x coil mm</v>
       </c>
       <c r="B602" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, SBA,
-0.70 x 1056.0 x coil mm
-Weight (Kg):15,197
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-1,125.00 €/ton
+0.70 x 150.9 x coil mm
+Weight (Kg):1,268
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+1,000.00 €/ton
 Add to cart</v>
       </c>
     </row>
     <row r="603" xml:space="preserve">
       <c r="A603" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, SBA,
-0.70 x 150.9 x coil mm</v>
+0.70 x 173.0 x coil mm</v>
       </c>
       <c r="B603" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, SBA,
-0.70 x 150.9 x coil mm
-Weight (Kg):1,268
-Quality:Prime-2
+0.70 x 173.0 x coil mm
+Weight (Kg):890
+Quality:Prime
 Help
 Location:FABRICA ALGECIRAS
 1,000.00 €/ton
@@ -10042,13 +10042,13 @@
     <row r="604" xml:space="preserve">
       <c r="A604" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, SBA,
-0.70 x 173.0 x coil mm</v>
+0.70 x 195.9 x coil mm</v>
       </c>
       <c r="B604" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, SBA,
-0.70 x 173.0 x coil mm
-Weight (Kg):890
-Quality:Prime
+0.70 x 195.9 x coil mm
+Weight (Kg):962
+Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
 1,000.00 €/ton
@@ -10058,44 +10058,44 @@
     <row r="605" xml:space="preserve">
       <c r="A605" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, SBA,
-0.70 x 195.9 x coil mm</v>
+0.70 x 682.0 x coil mm</v>
       </c>
       <c r="B605" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, SBA,
-0.70 x 195.9 x coil mm
-Weight (Kg):962
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-1,000.00 €/ton
+0.70 x 682.0 x coil mm
+Weight (Kg):3,870
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+1,025.00 €/ton
 Add to cart</v>
       </c>
     </row>
     <row r="606" xml:space="preserve">
       <c r="A606" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, SBA,
-0.70 x 682.0 x coil mm</v>
+0.70 x 825.0 x coil mm</v>
       </c>
       <c r="B606" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, SBA,
-0.70 x 682.0 x coil mm
-Weight (Kg):3,870
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-1,025.00 €/ton
+0.70 x 825.0 x coil mm
+Weight (Kg):6,448
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+1,125.00 €/ton
 Add to cart</v>
       </c>
     </row>
     <row r="607" xml:space="preserve">
       <c r="A607" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, SBA,
-0.70 x 825.0 x coil mm</v>
+0.70 x 942.0 x coil mm</v>
       </c>
       <c r="B607" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, SBA,
-0.70 x 825.0 x coil mm
-Weight (Kg):6,448
+0.70 x 942.0 x coil mm
+Weight (Kg):1,810
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -10106,12 +10106,12 @@
     <row r="608" xml:space="preserve">
       <c r="A608" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, SBA,
-0.70 x 942.0 x coil mm</v>
+0.70 x 948.0 x coil mm</v>
       </c>
       <c r="B608" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, SBA,
-0.70 x 942.0 x coil mm
-Weight (Kg):1,810
+0.70 x 948.0 x coil mm
+Weight (Kg):3,410
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -10122,12 +10122,12 @@
     <row r="609" xml:space="preserve">
       <c r="A609" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, SBA,
-0.70 x 948.0 x coil mm</v>
+0.70 x 960.0 x coil mm</v>
       </c>
       <c r="B609" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, SBA,
-0.70 x 948.0 x coil mm
-Weight (Kg):3,410
+0.70 x 960.0 x coil mm
+Weight (Kg):2,780
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -10138,25 +10138,9 @@
     <row r="610" xml:space="preserve">
       <c r="A610" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, SBA,
-0.70 x 960.0 x coil mm</v>
+0.70 x 963.0 x coil mm</v>
       </c>
       <c r="B610" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, SBA,
-0.70 x 960.0 x coil mm
-Weight (Kg):2,780
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-1,125.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="611" xml:space="preserve">
-      <c r="A611" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, SBA,
-0.70 x 963.0 x coil mm</v>
-      </c>
-      <c r="B611" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, SBA,
 0.70 x 963.0 x coil mm
 Weight (Kg):4,570
@@ -10164,6 +10148,22 @@
 Help
 Location:FABRICA ALGECIRAS
 1,325.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="611" xml:space="preserve">
+      <c r="A611" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Disk, BA,
+0.60 x 550.0 x 0.0 mm</v>
+      </c>
+      <c r="B611" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Disk, BA,
+0.60 x 550.0 x 0.0 mm
+Weight (Kg):578
+Quality:Prime
+Help
+Location:FABRICA ALGECIRAS
+1,900.00 €/ton
 Add to cart</v>
       </c>
     </row>
@@ -10175,7 +10175,7 @@
       <c r="B612" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Disk, BA,
 0.60 x 550.0 x 0.0 mm
-Weight (Kg):578
+Weight (Kg):572
 Quality:Prime
 Help
 Location:FABRICA ALGECIRAS
@@ -10191,7 +10191,7 @@
       <c r="B613" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Disk, BA,
 0.60 x 550.0 x 0.0 mm
-Weight (Kg):572
+Weight (Kg):576
 Quality:Prime
 Help
 Location:FABRICA ALGECIRAS
@@ -10207,7 +10207,7 @@
       <c r="B614" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Disk, BA,
 0.60 x 550.0 x 0.0 mm
-Weight (Kg):576
+Weight (Kg):578
 Quality:Prime
 Help
 Location:FABRICA ALGECIRAS
@@ -10223,7 +10223,7 @@
       <c r="B615" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Disk, BA,
 0.60 x 550.0 x 0.0 mm
-Weight (Kg):578
+Weight (Kg):582
 Quality:Prime
 Help
 Location:FABRICA ALGECIRAS
@@ -10233,29 +10233,29 @@
     </row>
     <row r="616" xml:space="preserve">
       <c r="A616" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Disk, BA,
-0.60 x 550.0 x 0.0 mm</v>
+        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Sheet, 2B,
+2.00 x 1250.0 x 2500.0 mm</v>
       </c>
       <c r="B616" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Disk, BA,
-0.60 x 550.0 x 0.0 mm
-Weight (Kg):582
-Quality:Prime
-Help
-Location:FABRICA ALGECIRAS
-1,900.00 €/ton
+        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Sheet, 2B,
+2.00 x 1250.0 x 2500.0 mm
+Weight (Kg):619
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+1,125.00 €/ton
 Add to cart</v>
       </c>
     </row>
     <row r="617" xml:space="preserve">
       <c r="A617" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Sheet, 2B,
-2.00 x 1250.0 x 2500.0 mm</v>
+3.00 x 1250.0 x 2500.0 mm</v>
       </c>
       <c r="B617" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Sheet, 2B,
-2.00 x 1250.0 x 2500.0 mm
-Weight (Kg):619
+3.00 x 1250.0 x 2500.0 mm
+Weight (Kg):566
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -10271,7 +10271,7 @@
       <c r="B618" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Sheet, 2B,
 3.00 x 1250.0 x 2500.0 mm
-Weight (Kg):566
+Weight (Kg):640
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -10281,26 +10281,10 @@
     </row>
     <row r="619" xml:space="preserve">
       <c r="A619" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Sheet, 2B,
-3.00 x 1250.0 x 2500.0 mm</v>
-      </c>
-      <c r="B619" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Sheet, 2B,
-3.00 x 1250.0 x 2500.0 mm
-Weight (Kg):640
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-1,125.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="620" xml:space="preserve">
-      <c r="A620" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Sheet, BA,
 0.70 x 1250.0 x 2500.0 mm</v>
       </c>
-      <c r="B620" t="str" xml:space="preserve">
+      <c r="B619" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Sheet, BA,
 0.70 x 1250.0 x 2500.0 mm
 Weight (Kg):766
@@ -10311,12 +10295,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="621" xml:space="preserve">
-      <c r="A621" t="str" xml:space="preserve">
+    <row r="620" xml:space="preserve">
+      <c r="A620" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Sheet, SB-G-400,
 1.00 x 1500.0 x 3000.0 mm</v>
       </c>
-      <c r="B621" t="str" xml:space="preserve">
+      <c r="B620" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Sheet, SB-G-400,
 1.00 x 1500.0 x 3000.0 mm
 Weight (Kg):1,940
@@ -10327,12 +10311,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="622" xml:space="preserve">
-      <c r="A622" t="str" xml:space="preserve">
+    <row r="621" xml:space="preserve">
+      <c r="A621" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Untrimmed, Coil, 1/4 HT,
 3.00 x 1292.0 x coil mm</v>
       </c>
-      <c r="B622" t="str" xml:space="preserve">
+      <c r="B621" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Untrimmed, Coil, 1/4 HT,
 3.00 x 1292.0 x coil mm
 Weight (Kg):3,641
@@ -10343,12 +10327,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="623" xml:space="preserve">
-      <c r="A623" t="str" xml:space="preserve">
+    <row r="622" xml:space="preserve">
+      <c r="A622" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Untrimmed, Coil, 2B,
 1.20 x 1500.0 x coil mm</v>
       </c>
-      <c r="B623" t="str" xml:space="preserve">
+      <c r="B622" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Untrimmed, Coil, 2B,
 1.20 x 1500.0 x coil mm
 Weight (Kg):4,750
@@ -10359,6 +10343,22 @@
 Add to cart</v>
       </c>
     </row>
+    <row r="623" xml:space="preserve">
+      <c r="A623" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Untrimmed, Coil, 2D, ET-100
+0.50 x 1250.0 x coil mm</v>
+      </c>
+      <c r="B623" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Untrimmed, Coil, 2D, ET-100
+0.50 x 1250.0 x coil mm
+Weight (Kg):5,160
+Quality:Prime
+Help
+Location:FABRICA ALGECIRAS
+1,325.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
     <row r="624" xml:space="preserve">
       <c r="A624" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Untrimmed, Coil, 2D, ET-100
@@ -10367,7 +10367,7 @@
       <c r="B624" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Untrimmed, Coil, 2D, ET-100
 0.50 x 1250.0 x coil mm
-Weight (Kg):5,160
+Weight (Kg):3,695
 Quality:Prime
 Help
 Location:FABRICA ALGECIRAS
@@ -10377,42 +10377,26 @@
     </row>
     <row r="625" xml:space="preserve">
       <c r="A625" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Untrimmed, Coil, 2D, ET-100
-0.50 x 1250.0 x coil mm</v>
+        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Untrimmed, Coil, BA,
+0.60 x 1246.0 x coil mm</v>
       </c>
       <c r="B625" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Untrimmed, Coil, 2D, ET-100
-0.50 x 1250.0 x coil mm
-Weight (Kg):3,695
-Quality:Prime
-Help
-Location:FABRICA ALGECIRAS
-1,325.00 €/ton
+        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Untrimmed, Coil, BA,
+0.60 x 1246.0 x coil mm
+Weight (Kg):2,585
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+1,125.00 €/ton
 Add to cart</v>
       </c>
     </row>
     <row r="626" xml:space="preserve">
       <c r="A626" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Untrimmed, Coil, BA,
-0.60 x 1246.0 x coil mm</v>
+1.00 x 1028.0 x coil mm</v>
       </c>
       <c r="B626" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Untrimmed, Coil, BA,
-0.60 x 1246.0 x coil mm
-Weight (Kg):2,585
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-1,125.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="627" xml:space="preserve">
-      <c r="A627" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Untrimmed, Coil, BA,
-1.00 x 1028.0 x coil mm</v>
-      </c>
-      <c r="B627" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Untrimmed, Coil, BA,
 1.00 x 1028.0 x coil mm
 Weight (Kg):2,430
@@ -10423,28 +10407,28 @@
 Add to cart</v>
       </c>
     </row>
+    <row r="627" xml:space="preserve">
+      <c r="A627" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Untrimmed, Coil, SBA,
+0.70 x 825.0 x coil mm</v>
+      </c>
+      <c r="B627" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Untrimmed, Coil, SBA,
+0.70 x 825.0 x coil mm
+Weight (Kg):7,260
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+1,125.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
     <row r="628" xml:space="preserve">
       <c r="A628" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Untrimmed, Coil, SBA,
-0.70 x 825.0 x coil mm</v>
+0.70 x 873.0 x coil mm</v>
       </c>
       <c r="B628" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Untrimmed, Coil, SBA,
-0.70 x 825.0 x coil mm
-Weight (Kg):7,260
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-1,125.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="629" xml:space="preserve">
-      <c r="A629" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Untrimmed, Coil, SBA,
-0.70 x 873.0 x coil mm</v>
-      </c>
-      <c r="B629" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Untrimmed, Coil, SBA,
 0.70 x 873.0 x coil mm
 Weight (Kg):4,020
@@ -10455,12 +10439,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="630" xml:space="preserve">
-      <c r="A630" t="str" xml:space="preserve">
+    <row r="629" xml:space="preserve">
+      <c r="A629" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4510 430Ti-Coil, 2B,
 2.00 x 100.9 x coil mm</v>
       </c>
-      <c r="B630" t="str" xml:space="preserve">
+      <c r="B629" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4510 430Ti-Coil, 2B,
 2.00 x 100.9 x coil mm
 Weight (Kg):1,710
@@ -10471,16 +10455,32 @@
 Add to cart</v>
       </c>
     </row>
+    <row r="630" xml:space="preserve">
+      <c r="A630" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4510 430Ti-Coil, BA,
+0.50 x 170.0 x coil mm</v>
+      </c>
+      <c r="B630" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4510 430Ti-Coil, BA,
+0.50 x 170.0 x coil mm
+Weight (Kg):914
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+1,000.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
     <row r="631" xml:space="preserve">
       <c r="A631" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4510 430Ti-Coil, BA,
-0.50 x 170.0 x coil mm</v>
+0.70 x 100.9 x coil mm</v>
       </c>
       <c r="B631" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4510 430Ti-Coil, BA,
-0.50 x 170.0 x coil mm
-Weight (Kg):914
-Quality:Prime-2
+0.70 x 100.9 x coil mm
+Weight (Kg):638
+Quality:Prime
 Help
 Location:FABRICA ALGECIRAS
 1,000.00 €/ton
@@ -10490,44 +10490,44 @@
     <row r="632" xml:space="preserve">
       <c r="A632" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4510 430Ti-Coil, BA,
-0.70 x 100.9 x coil mm</v>
+0.70 x 1020.0 x coil mm</v>
       </c>
       <c r="B632" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4510 430Ti-Coil, BA,
-0.70 x 100.9 x coil mm
-Weight (Kg):638
-Quality:Prime
-Help
-Location:FABRICA ALGECIRAS
-1,000.00 €/ton
+0.70 x 1020.0 x coil mm
+Weight (Kg):16,000
+Quality:Prime
+Help
+Location:FABRICA ALGECIRAS
+1,900.00 €/ton
 Add to cart</v>
       </c>
     </row>
     <row r="633" xml:space="preserve">
       <c r="A633" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4510 430Ti-Coil, BA,
-0.70 x 1020.0 x coil mm</v>
+0.70 x 108.0 x coil mm</v>
       </c>
       <c r="B633" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4510 430Ti-Coil, BA,
-0.70 x 1020.0 x coil mm
-Weight (Kg):16,000
-Quality:Prime
-Help
-Location:FABRICA ALGECIRAS
-1,900.00 €/ton
+0.70 x 108.0 x coil mm
+Weight (Kg):714
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+1,000.00 €/ton
 Add to cart</v>
       </c>
     </row>
     <row r="634" xml:space="preserve">
       <c r="A634" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4510 430Ti-Coil, BA,
-0.70 x 108.0 x coil mm</v>
+0.70 x 120.9 x coil mm</v>
       </c>
       <c r="B634" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4510 430Ti-Coil, BA,
-0.70 x 108.0 x coil mm
-Weight (Kg):714
+0.70 x 120.9 x coil mm
+Weight (Kg):976
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -10538,12 +10538,12 @@
     <row r="635" xml:space="preserve">
       <c r="A635" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4510 430Ti-Coil, BA,
-0.70 x 120.9 x coil mm</v>
+0.70 x 325.0 x coil mm</v>
       </c>
       <c r="B635" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4510 430Ti-Coil, BA,
-0.70 x 120.9 x coil mm
-Weight (Kg):976
+0.70 x 325.0 x coil mm
+Weight (Kg):4,156
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -10554,16 +10554,16 @@
     <row r="636" xml:space="preserve">
       <c r="A636" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4510 430Ti-Coil, BA,
-0.70 x 325.0 x coil mm</v>
+0.70 x 900.0 x coil mm</v>
       </c>
       <c r="B636" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4510 430Ti-Coil, BA,
-0.70 x 325.0 x coil mm
-Weight (Kg):4,156
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-1,000.00 €/ton
+0.70 x 900.0 x coil mm
+Weight (Kg):2,800
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+1,125.00 €/ton
 Add to cart</v>
       </c>
     </row>
@@ -10575,7 +10575,7 @@
       <c r="B637" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4510 430Ti-Coil, BA,
 0.70 x 900.0 x coil mm
-Weight (Kg):2,800
+Weight (Kg):6,570
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -10650,12 +10650,12 @@
     <row r="642" xml:space="preserve">
       <c r="A642" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4510 430Ti-Coil, BA,
-0.70 x 900.0 x coil mm</v>
+0.70 x 905.0 x coil mm</v>
       </c>
       <c r="B642" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4510 430Ti-Coil, BA,
-0.70 x 900.0 x coil mm
-Weight (Kg):6,570
+0.70 x 905.0 x coil mm
+Weight (Kg):9,410
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -10666,12 +10666,12 @@
     <row r="643" xml:space="preserve">
       <c r="A643" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4510 430Ti-Coil, BA,
-0.70 x 905.0 x coil mm</v>
+0.70 x 932.0 x coil mm</v>
       </c>
       <c r="B643" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4510 430Ti-Coil, BA,
-0.70 x 905.0 x coil mm
-Weight (Kg):9,410
+0.70 x 932.0 x coil mm
+Weight (Kg):2,270
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -10682,25 +10682,9 @@
     <row r="644" xml:space="preserve">
       <c r="A644" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4510 430Ti-Coil, BA,
-0.70 x 932.0 x coil mm</v>
+0.70 x 940.0 x coil mm</v>
       </c>
       <c r="B644" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4510 430Ti-Coil, BA,
-0.70 x 932.0 x coil mm
-Weight (Kg):2,270
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-1,125.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="645" xml:space="preserve">
-      <c r="A645" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4510 430Ti-Coil, BA,
-0.70 x 940.0 x coil mm</v>
-      </c>
-      <c r="B645" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4510 430Ti-Coil, BA,
 0.70 x 940.0 x coil mm
 Weight (Kg):14,920
@@ -10711,28 +10695,28 @@
 Add to cart</v>
       </c>
     </row>
+    <row r="645" xml:space="preserve">
+      <c r="A645" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4510 430Ti-Untrimmed, Coil, BA,
+0.50 x 1275.0 x coil mm</v>
+      </c>
+      <c r="B645" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4510 430Ti-Untrimmed, Coil, BA,
+0.50 x 1275.0 x coil mm
+Weight (Kg):2,258
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+1,125.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
     <row r="646" xml:space="preserve">
       <c r="A646" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4510 430Ti-Untrimmed, Coil, BA,
-0.50 x 1275.0 x coil mm</v>
+0.70 x 928.0 x coil mm</v>
       </c>
       <c r="B646" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4510 430Ti-Untrimmed, Coil, BA,
-0.50 x 1275.0 x coil mm
-Weight (Kg):2,258
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-1,125.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="647" xml:space="preserve">
-      <c r="A647" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4510 430Ti-Untrimmed, Coil, BA,
-0.70 x 928.0 x coil mm</v>
-      </c>
-      <c r="B647" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4510 430Ti-Untrimmed, Coil, BA,
 0.70 x 928.0 x coil mm
 Weight (Kg):4,257
@@ -10743,12 +10727,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="648" xml:space="preserve">
-      <c r="A648" t="str" xml:space="preserve">
+    <row r="647" xml:space="preserve">
+      <c r="A647" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4509 441-Coil, 2B,
 1.20 x 275.9 x coil mm</v>
       </c>
-      <c r="B648" t="str" xml:space="preserve">
+      <c r="B647" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4509 441-Coil, 2B,
 1.20 x 275.9 x coil mm
 Weight (Kg):2,416
@@ -10759,15 +10743,31 @@
 Add to cart</v>
       </c>
     </row>
+    <row r="648" xml:space="preserve">
+      <c r="A648" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4509 441-Coil, 2D,
+1.20 x 196.0 x coil mm</v>
+      </c>
+      <c r="B648" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4509 441-Coil, 2D,
+1.20 x 196.0 x coil mm
+Weight (Kg):2,970
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+1,100.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
     <row r="649" xml:space="preserve">
       <c r="A649" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4509 441-Coil, 2D,
-1.20 x 196.0 x coil mm</v>
+1.20 x 200.0 x coil mm</v>
       </c>
       <c r="B649" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4509 441-Coil, 2D,
-1.20 x 196.0 x coil mm
-Weight (Kg):2,970
+1.20 x 200.0 x coil mm
+Weight (Kg):3,310
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -10778,12 +10778,12 @@
     <row r="650" xml:space="preserve">
       <c r="A650" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4509 441-Coil, 2D,
-1.20 x 200.0 x coil mm</v>
+1.20 x 214.9 x coil mm</v>
       </c>
       <c r="B650" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4509 441-Coil, 2D,
-1.20 x 200.0 x coil mm
-Weight (Kg):3,310
+1.20 x 214.9 x coil mm
+Weight (Kg):3,220
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -10794,12 +10794,12 @@
     <row r="651" xml:space="preserve">
       <c r="A651" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4509 441-Coil, 2D,
-1.20 x 214.9 x coil mm</v>
+1.20 x 223.9 x coil mm</v>
       </c>
       <c r="B651" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4509 441-Coil, 2D,
-1.20 x 214.9 x coil mm
-Weight (Kg):3,220
+1.20 x 223.9 x coil mm
+Weight (Kg):3,798
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -10810,28 +10810,28 @@
     <row r="652" xml:space="preserve">
       <c r="A652" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4509 441-Coil, 2D,
-1.20 x 223.9 x coil mm</v>
+1.20 x 224.0 x coil mm</v>
       </c>
       <c r="B652" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4509 441-Coil, 2D,
-1.20 x 223.9 x coil mm
-Weight (Kg):3,798
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-1,100.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="653" xml:space="preserve">
-      <c r="A653" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4509 441-Coil, 2D,
-1.20 x 224.0 x coil mm</v>
-      </c>
-      <c r="B653" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4509 441-Coil, 2D,
 1.20 x 224.0 x coil mm
 Weight (Kg):3,808
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+1,100.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="653" xml:space="preserve">
+      <c r="A653" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4509 441-Coil, BA,
+0.80 x 130.9 x coil mm</v>
+      </c>
+      <c r="B653" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4509 441-Coil, BA,
+0.80 x 130.9 x coil mm
+Weight (Kg):245
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -10863,7 +10863,7 @@
       <c r="B655" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4509 441-Coil, BA,
 0.80 x 130.9 x coil mm
-Weight (Kg):245
+Weight (Kg):213
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -10879,7 +10879,7 @@
       <c r="B656" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4509 441-Coil, BA,
 0.80 x 130.9 x coil mm
-Weight (Kg):213
+Weight (Kg):244
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -10889,45 +10889,45 @@
     </row>
     <row r="657" xml:space="preserve">
       <c r="A657" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4509 441-Coil, BA,
-0.80 x 130.9 x coil mm</v>
+        <v xml:space="preserve">Acerinox Europa, 1.4509 441-Coil, SB-G-400,
+1.00 x 1000.0 x coil mm</v>
       </c>
       <c r="B657" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4509 441-Coil, BA,
-0.80 x 130.9 x coil mm
-Weight (Kg):244
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-1,100.00 €/ton
+        <v xml:space="preserve">Acerinox Europa, 1.4509 441-Coil, SB-G-400,
+1.00 x 1000.0 x coil mm
+Weight (Kg):7,550
+Quality:Prime
+Help
+Location:FABRICA ALGECIRAS
+1,625.00 €/ton
 Add to cart</v>
       </c>
     </row>
     <row r="658" xml:space="preserve">
       <c r="A658" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4509 441-Coil, SB-G-400,
-1.00 x 1000.0 x coil mm</v>
+1.00 x 255.0 x coil mm</v>
       </c>
       <c r="B658" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4509 441-Coil, SB-G-400,
-1.00 x 1000.0 x coil mm
-Weight (Kg):7,550
-Quality:Prime
-Help
-Location:FABRICA ALGECIRAS
-1,625.00 €/ton
+1.00 x 255.0 x coil mm
+Weight (Kg):2,182
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+1,100.00 €/ton
 Add to cart</v>
       </c>
     </row>
     <row r="659" xml:space="preserve">
       <c r="A659" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4509 441-Coil, SB-G-400,
-1.00 x 255.0 x coil mm</v>
+1.00 x 290.9 x coil mm</v>
       </c>
       <c r="B659" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4509 441-Coil, SB-G-400,
-1.00 x 255.0 x coil mm
-Weight (Kg):2,182
+1.00 x 290.9 x coil mm
+Weight (Kg):2,370
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -10938,12 +10938,12 @@
     <row r="660" xml:space="preserve">
       <c r="A660" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4509 441-Coil, SB-G-400,
-1.00 x 290.9 x coil mm</v>
+1.20 x 110.9 x coil mm</v>
       </c>
       <c r="B660" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4509 441-Coil, SB-G-400,
-1.00 x 290.9 x coil mm
-Weight (Kg):2,370
+1.20 x 110.9 x coil mm
+Weight (Kg):856
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -10954,12 +10954,12 @@
     <row r="661" xml:space="preserve">
       <c r="A661" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4509 441-Coil, SB-G-400,
-1.20 x 110.9 x coil mm</v>
+1.20 x 130.9 x coil mm</v>
       </c>
       <c r="B661" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4509 441-Coil, SB-G-400,
-1.20 x 110.9 x coil mm
-Weight (Kg):856
+1.20 x 130.9 x coil mm
+Weight (Kg):564
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -10975,8 +10975,8 @@
       <c r="B662" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4509 441-Coil, SB-G-400,
 1.20 x 130.9 x coil mm
-Weight (Kg):564
-Quality:Prime-2
+Weight (Kg):532
+Quality:Prime
 Help
 Location:FABRICA ALGECIRAS
 1,100.00 €/ton
@@ -10986,13 +10986,13 @@
     <row r="663" xml:space="preserve">
       <c r="A663" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4509 441-Coil, SB-G-400,
-1.20 x 130.9 x coil mm</v>
+1.50 x 130.9 x coil mm</v>
       </c>
       <c r="B663" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4509 441-Coil, SB-G-400,
-1.20 x 130.9 x coil mm
-Weight (Kg):532
-Quality:Prime
+1.50 x 130.9 x coil mm
+Weight (Kg):640
+Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
 1,100.00 €/ton
@@ -11002,25 +11002,9 @@
     <row r="664" xml:space="preserve">
       <c r="A664" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4509 441-Coil, SB-G-400,
-1.50 x 130.9 x coil mm</v>
+1.50 x 360.0 x coil mm</v>
       </c>
       <c r="B664" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4509 441-Coil, SB-G-400,
-1.50 x 130.9 x coil mm
-Weight (Kg):640
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-1,100.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="665" xml:space="preserve">
-      <c r="A665" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4509 441-Coil, SB-G-400,
-1.50 x 360.0 x coil mm</v>
-      </c>
-      <c r="B665" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4509 441-Coil, SB-G-400,
 1.50 x 360.0 x coil mm
 Weight (Kg):1,488
@@ -11031,12 +11015,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="666" xml:space="preserve">
-      <c r="A666" t="str" xml:space="preserve">
+    <row r="665" xml:space="preserve">
+      <c r="A665" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4509 441-Untrimmed, Coil, 2B,
 1.50 x 1539.0 x coil mm</v>
       </c>
-      <c r="B666" t="str" xml:space="preserve">
+      <c r="B665" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4509 441-Untrimmed, Coil, 2B,
 1.50 x 1539.0 x coil mm
 Weight (Kg):14,230
@@ -11047,12 +11031,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="667" xml:space="preserve">
-      <c r="A667" t="str" xml:space="preserve">
+    <row r="666" xml:space="preserve">
+      <c r="A666" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4509 441-Untrimmed, Coil, BA,
 0.40 x 1075.0 x coil mm</v>
       </c>
-      <c r="B667" t="str" xml:space="preserve">
+      <c r="B666" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4509 441-Untrimmed, Coil, BA,
 0.40 x 1075.0 x coil mm
 Weight (Kg):9,750
@@ -11063,12 +11047,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="668" xml:space="preserve">
-      <c r="A668" t="str" xml:space="preserve">
+    <row r="667" xml:space="preserve">
+      <c r="A667" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4509 441-Untrimmed, Coil, Nb. 1,
 5.00 x 1045.0 x coil mm</v>
       </c>
-      <c r="B668" t="str" xml:space="preserve">
+      <c r="B667" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4509 441-Untrimmed, Coil, Nb. 1,
 5.00 x 1045.0 x coil mm
 Weight (Kg):7,880
@@ -11079,12 +11063,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="669" xml:space="preserve">
-      <c r="A669" t="str" xml:space="preserve">
+    <row r="668" xml:space="preserve">
+      <c r="A668" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 441-1.4509 Coil, 2B,
 1.20 x 240.9 x coil mm</v>
       </c>
-      <c r="B669" t="str" xml:space="preserve">
+      <c r="B668" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 441-1.4509 Coil, 2B,
 1.20 x 240.9 x coil mm
 Weight (Kg):3,882
@@ -11095,12 +11079,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="670" xml:space="preserve">
-      <c r="A670" t="str" xml:space="preserve">
+    <row r="669" xml:space="preserve">
+      <c r="A669" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 304-1.4301 Coil,
 0.70 x 270.9 x coil mm</v>
       </c>
-      <c r="B670" t="str" xml:space="preserve">
+      <c r="B669" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 304-1.4301 Coil,
 0.70 x 270.9 x coil mm
 Weight (Kg):2,704
@@ -11111,12 +11095,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="671" xml:space="preserve">
-      <c r="A671" t="str" xml:space="preserve">
+    <row r="670" xml:space="preserve">
+      <c r="A670" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 316L-1.4404 Coil,
 1.20 x 136.0 x coil mm</v>
       </c>
-      <c r="B671" t="str" xml:space="preserve">
+      <c r="B670" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 316L-1.4404 Coil,
 1.20 x 136.0 x coil mm
 Weight (Kg):2,300
@@ -11127,12 +11111,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="672" xml:space="preserve">
-      <c r="A672" t="str" xml:space="preserve">
+    <row r="671" xml:space="preserve">
+      <c r="A671" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 304L/304-4301/4307 Coil, 2B,
 6.00 x 245.0 x coil mm</v>
       </c>
-      <c r="B672" t="str" xml:space="preserve">
+      <c r="B671" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 304L/304-4301/4307 Coil, 2B,
 6.00 x 245.0 x coil mm
 Weight (Kg):2,394
@@ -11143,12 +11127,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="673" xml:space="preserve">
-      <c r="A673" t="str" xml:space="preserve">
+    <row r="672" xml:space="preserve">
+      <c r="A672" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, 2B,
 0.70 x 197.5 x coil mm</v>
       </c>
-      <c r="B673" t="str" xml:space="preserve">
+      <c r="B672" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, 2B,
 0.70 x 197.5 x coil mm
 Weight (Kg):2,442
@@ -11159,12 +11143,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="674" xml:space="preserve">
-      <c r="A674" t="str" xml:space="preserve">
+    <row r="673" xml:space="preserve">
+      <c r="A673" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 441-1.4509 Coil, 2B,
 2.00 x 120.9 x coil mm</v>
       </c>
-      <c r="B674" t="str" xml:space="preserve">
+      <c r="B673" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 441-1.4509 Coil, 2B,
 2.00 x 120.9 x coil mm
 Weight (Kg):1,956
@@ -11172,6 +11156,22 @@
 Help
 Location:FABRICA ALGECIRAS
 1,100.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="674" xml:space="preserve">
+      <c r="A674" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 304-1.4301 Coil, 2B,
+1.20 x 119.9 x coil mm</v>
+      </c>
+      <c r="B674" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 304-1.4301 Coil, 2B,
+1.20 x 119.9 x coil mm
+Weight (Kg):1,500
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,075.00 €/ton
 Add to cart</v>
       </c>
     </row>
@@ -11183,7 +11183,7 @@
       <c r="B675" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 304-1.4301 Coil, 2B,
 1.20 x 119.9 x coil mm
-Weight (Kg):1,500
+Weight (Kg):1,400
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -11193,29 +11193,29 @@
     </row>
     <row r="676" xml:space="preserve">
       <c r="A676" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 304-1.4301 Coil, 2B,
-1.20 x 119.9 x coil mm</v>
+        <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, BA,
+0.70 x 125.0 x coil mm</v>
       </c>
       <c r="B676" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 304-1.4301 Coil, 2B,
-1.20 x 119.9 x coil mm
-Weight (Kg):1,400
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-2,075.00 €/ton
+        <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, BA,
+0.70 x 125.0 x coil mm
+Weight (Kg):1,764
+Quality:Prime
+Help
+Location:FABRICA ALGECIRAS
+1,000.00 €/ton
 Add to cart</v>
       </c>
     </row>
     <row r="677" xml:space="preserve">
       <c r="A677" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, BA,
-0.70 x 125.0 x coil mm</v>
+0.70 x 104.9 x coil mm</v>
       </c>
       <c r="B677" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, BA,
-0.70 x 125.0 x coil mm
-Weight (Kg):1,764
+0.70 x 104.9 x coil mm
+Weight (Kg):1,240
 Quality:Prime
 Help
 Location:FABRICA ALGECIRAS
@@ -11226,12 +11226,12 @@
     <row r="678" xml:space="preserve">
       <c r="A678" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, BA,
-0.70 x 104.9 x coil mm</v>
+0.70 x 118.9 x coil mm</v>
       </c>
       <c r="B678" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, BA,
-0.70 x 104.9 x coil mm
-Weight (Kg):1,240
+0.70 x 118.9 x coil mm
+Weight (Kg):1,802
 Quality:Prime
 Help
 Location:FABRICA ALGECIRAS
@@ -11242,12 +11242,12 @@
     <row r="679" xml:space="preserve">
       <c r="A679" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, BA,
-0.70 x 118.9 x coil mm</v>
+0.70 x 115.9 x coil mm</v>
       </c>
       <c r="B679" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, BA,
-0.70 x 118.9 x coil mm
-Weight (Kg):1,802
+0.70 x 115.9 x coil mm
+Weight (Kg):1,368
 Quality:Prime
 Help
 Location:FABRICA ALGECIRAS
@@ -11258,25 +11258,9 @@
     <row r="680" xml:space="preserve">
       <c r="A680" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, BA,
-0.70 x 115.9 x coil mm</v>
+0.70 x 119.0 x coil mm</v>
       </c>
       <c r="B680" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, BA,
-0.70 x 115.9 x coil mm
-Weight (Kg):1,368
-Quality:Prime
-Help
-Location:FABRICA ALGECIRAS
-1,000.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="681" xml:space="preserve">
-      <c r="A681" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, BA,
-0.70 x 119.0 x coil mm</v>
-      </c>
-      <c r="B681" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, BA,
 0.70 x 119.0 x coil mm
 Weight (Kg):1,622
@@ -11287,12 +11271,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="682" xml:space="preserve">
-      <c r="A682" t="str" xml:space="preserve">
+    <row r="681" xml:space="preserve">
+      <c r="A681" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 304L/304-4301/4307 Coil, 2B,
 1.40 x 110.9 x coil mm</v>
       </c>
-      <c r="B682" t="str" xml:space="preserve">
+      <c r="B681" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 304L/304-4301/4307 Coil, 2B,
 1.40 x 110.9 x coil mm
 Weight (Kg):1,240
@@ -11300,6 +11284,22 @@
 Help
 Location:FABRICA ALGECIRAS
 2,075.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="682" xml:space="preserve">
+      <c r="A682" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, BA,
+0.70 x 104.0 x coil mm</v>
+      </c>
+      <c r="B682" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, BA,
+0.70 x 104.0 x coil mm
+Weight (Kg):1,622
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+1,000.00 €/ton
 Add to cart</v>
       </c>
     </row>
@@ -11311,7 +11311,7 @@
       <c r="B683" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, BA,
 0.70 x 104.0 x coil mm
-Weight (Kg):1,622
+Weight (Kg):1,688
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -11321,26 +11321,10 @@
     </row>
     <row r="684" xml:space="preserve">
       <c r="A684" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, BA,
-0.70 x 104.0 x coil mm</v>
-      </c>
-      <c r="B684" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, BA,
-0.70 x 104.0 x coil mm
-Weight (Kg):1,688
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-1,000.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="685" xml:space="preserve">
-      <c r="A685" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 304L/304-4301/4307 Coil, 2B,
 1.40 x 110.9 x coil mm</v>
       </c>
-      <c r="B685" t="str" xml:space="preserve">
+      <c r="B684" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 304L/304-4301/4307 Coil, 2B,
 1.40 x 110.9 x coil mm
 Weight (Kg):1,162
@@ -11348,6 +11332,22 @@
 Help
 Location:FABRICA ALGECIRAS
 2,075.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="685" xml:space="preserve">
+      <c r="A685" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 430Ti-1.4510 Coil, BA,
+0.70 x 165.9 x coil mm</v>
+      </c>
+      <c r="B685" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 430Ti-1.4510 Coil, BA,
+0.70 x 165.9 x coil mm
+Weight (Kg):2,692
+Quality:Prime
+Help
+Location:FABRICA ALGECIRAS
+1,000.00 €/ton
 Add to cart</v>
       </c>
     </row>
@@ -11359,8 +11359,8 @@
       <c r="B686" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 430Ti-1.4510 Coil, BA,
 0.70 x 165.9 x coil mm
-Weight (Kg):2,692
-Quality:Prime
+Weight (Kg):2,756
+Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
 1,000.00 €/ton
@@ -11369,13 +11369,13 @@
     </row>
     <row r="687" xml:space="preserve">
       <c r="A687" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 430Ti-1.4510 Coil, BA,
-0.70 x 165.9 x coil mm</v>
+        <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, BA,
+0.70 x 140.9 x coil mm</v>
       </c>
       <c r="B687" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 430Ti-1.4510 Coil, BA,
-0.70 x 165.9 x coil mm
-Weight (Kg):2,756
+        <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, BA,
+0.70 x 140.9 x coil mm
+Weight (Kg):1,676
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -11386,12 +11386,12 @@
     <row r="688" xml:space="preserve">
       <c r="A688" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, BA,
-0.70 x 140.9 x coil mm</v>
+0.70 x 100.9 x coil mm</v>
       </c>
       <c r="B688" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, BA,
-0.70 x 140.9 x coil mm
-Weight (Kg):1,676
+0.70 x 100.9 x coil mm
+Weight (Kg):1,340
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -11402,12 +11402,12 @@
     <row r="689" xml:space="preserve">
       <c r="A689" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, BA,
-0.70 x 100.9 x coil mm</v>
+0.70 x 125.0 x coil mm</v>
       </c>
       <c r="B689" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, BA,
-0.70 x 100.9 x coil mm
-Weight (Kg):1,340
+0.70 x 125.0 x coil mm
+Weight (Kg):1,550
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -11423,7 +11423,7 @@
       <c r="B690" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, BA,
 0.70 x 125.0 x coil mm
-Weight (Kg):1,550
+Weight (Kg):1,414
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -11434,25 +11434,9 @@
     <row r="691" xml:space="preserve">
       <c r="A691" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, BA,
-0.70 x 125.0 x coil mm</v>
+0.70 x 100.9 x coil mm</v>
       </c>
       <c r="B691" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, BA,
-0.70 x 125.0 x coil mm
-Weight (Kg):1,414
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-1,000.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="692" xml:space="preserve">
-      <c r="A692" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, BA,
-0.70 x 100.9 x coil mm</v>
-      </c>
-      <c r="B692" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, BA,
 0.70 x 100.9 x coil mm
 Weight (Kg):2,188
@@ -11460,6 +11444,22 @@
 Help
 Location:FABRICA ALGECIRAS
 1,000.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="692" xml:space="preserve">
+      <c r="A692" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 304L/304-4301/4307 Coil, Nb. 1,
+4.70 x 110.0 x coil mm</v>
+      </c>
+      <c r="B692" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 304L/304-4301/4307 Coil, Nb. 1,
+4.70 x 110.0 x coil mm
+Weight (Kg):1,796
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+1,975.00 €/ton
 Add to cart</v>
       </c>
     </row>
@@ -11471,7 +11471,7 @@
       <c r="B693" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 304L/304-4301/4307 Coil, Nb. 1,
 4.70 x 110.0 x coil mm
-Weight (Kg):1,796
+Weight (Kg):2,038
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -11481,26 +11481,10 @@
     </row>
     <row r="694" xml:space="preserve">
       <c r="A694" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 304L/304-4301/4307 Coil, Nb. 1,
-4.70 x 110.0 x coil mm</v>
-      </c>
-      <c r="B694" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 304L/304-4301/4307 Coil, Nb. 1,
-4.70 x 110.0 x coil mm
-Weight (Kg):2,038
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-1,975.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="695" xml:space="preserve">
-      <c r="A695" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, BA,
 0.70 x 165.9 x coil mm</v>
       </c>
-      <c r="B695" t="str" xml:space="preserve">
+      <c r="B694" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, BA,
 0.70 x 165.9 x coil mm
 Weight (Kg):2,620
@@ -11508,6 +11492,22 @@
 Help
 Location:FABRICA ALGECIRAS
 1,000.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="695" xml:space="preserve">
+      <c r="A695" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 304-1.4301 Coil,
+0.70 x 260.9 x coil mm</v>
+      </c>
+      <c r="B695" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 304-1.4301 Coil,
+0.70 x 260.9 x coil mm
+Weight (Kg):1,330
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,075.00 €/ton
 Add to cart</v>
       </c>
     </row>
@@ -11519,7 +11519,7 @@
       <c r="B696" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 304-1.4301 Coil,
 0.70 x 260.9 x coil mm
-Weight (Kg):1,330
+Weight (Kg):1,264
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -11529,42 +11529,26 @@
     </row>
     <row r="697" xml:space="preserve">
       <c r="A697" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 304-1.4301 Coil,
-0.70 x 260.9 x coil mm</v>
+        <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, BA,
+0.70 x 110.0 x coil mm</v>
       </c>
       <c r="B697" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 304-1.4301 Coil,
-0.70 x 260.9 x coil mm
-Weight (Kg):1,264
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-2,075.00 €/ton
+        <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, BA,
+0.70 x 110.0 x coil mm
+Weight (Kg):1,250
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+1,000.00 €/ton
 Add to cart</v>
       </c>
     </row>
     <row r="698" xml:space="preserve">
       <c r="A698" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, BA,
-0.70 x 110.0 x coil mm</v>
+0.70 x 122.9 x coil mm</v>
       </c>
       <c r="B698" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, BA,
-0.70 x 110.0 x coil mm
-Weight (Kg):1,250
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-1,000.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="699" xml:space="preserve">
-      <c r="A699" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, BA,
-0.70 x 122.9 x coil mm</v>
-      </c>
-      <c r="B699" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, BA,
 0.70 x 122.9 x coil mm
 Weight (Kg):1,460
@@ -11572,6 +11556,22 @@
 Help
 Location:FABRICA ALGECIRAS
 1,000.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="699" xml:space="preserve">
+      <c r="A699" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 304L/304-4301/4307 Coil, 2B,
+1.40 x 110.0 x coil mm</v>
+      </c>
+      <c r="B699" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 304L/304-4301/4307 Coil, 2B,
+1.40 x 110.0 x coil mm
+Weight (Kg):1,554
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,075.00 €/ton
 Add to cart</v>
       </c>
     </row>
@@ -11583,7 +11583,7 @@
       <c r="B700" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 304L/304-4301/4307 Coil, 2B,
 1.40 x 110.0 x coil mm
-Weight (Kg):1,554
+Weight (Kg):1,586
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -11594,25 +11594,9 @@
     <row r="701" xml:space="preserve">
       <c r="A701" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 304L/304-4301/4307 Coil, 2B,
-1.40 x 110.0 x coil mm</v>
+1.40 x 104.0 x coil mm</v>
       </c>
       <c r="B701" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 304L/304-4301/4307 Coil, 2B,
-1.40 x 110.0 x coil mm
-Weight (Kg):1,586
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-2,075.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="702" xml:space="preserve">
-      <c r="A702" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 304L/304-4301/4307 Coil, 2B,
-1.40 x 104.0 x coil mm</v>
-      </c>
-      <c r="B702" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 304L/304-4301/4307 Coil, 2B,
 1.40 x 104.0 x coil mm
 Weight (Kg):1,030
@@ -11623,12 +11607,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="703" xml:space="preserve">
-      <c r="A703" t="str" xml:space="preserve">
+    <row r="702" xml:space="preserve">
+      <c r="A702" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 304DDQ-1.4301 Coil, BA,
 0.70 x 181.9 x coil mm</v>
       </c>
-      <c r="B703" t="str" xml:space="preserve">
+      <c r="B702" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 304DDQ-1.4301 Coil, BA,
 0.70 x 181.9 x coil mm
 Weight (Kg):2,912
@@ -11639,12 +11623,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="704" xml:space="preserve">
-      <c r="A704" t="str" xml:space="preserve">
+    <row r="703" xml:space="preserve">
+      <c r="A703" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 304-1.4301 Coil,
 1.50 x 136.0 x coil mm</v>
       </c>
-      <c r="B704" t="str" xml:space="preserve">
+      <c r="B703" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 304-1.4301 Coil,
 1.50 x 136.0 x coil mm
 Weight (Kg):3,450
@@ -11655,12 +11639,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="705" xml:space="preserve">
-      <c r="A705" t="str" xml:space="preserve">
+    <row r="704" xml:space="preserve">
+      <c r="A704" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 304-1.4301 Coil, BA,
 0.40 x 200.0 x coil mm</v>
       </c>
-      <c r="B705" t="str" xml:space="preserve">
+      <c r="B704" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 304-1.4301 Coil, BA,
 0.40 x 200.0 x coil mm
 Weight (Kg):1,964
@@ -11671,12 +11655,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="706" xml:space="preserve">
-      <c r="A706" t="str" xml:space="preserve">
+    <row r="705" xml:space="preserve">
+      <c r="A705" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 304-1.4301 Coil, BA, ET-60
 0.60 x 120.0 x coil mm</v>
       </c>
-      <c r="B706" t="str" xml:space="preserve">
+      <c r="B705" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 304-1.4301 Coil, BA, ET-60
 0.60 x 120.0 x coil mm
 Weight (Kg):1,302
@@ -11684,6 +11668,22 @@
 Help
 Location:FABRICA ALGECIRAS
 2,075.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="706" xml:space="preserve">
+      <c r="A706" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, ET-100
+0.70 x 124.9 x coil mm</v>
+      </c>
+      <c r="B706" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, ET-100
+0.70 x 124.9 x coil mm
+Weight (Kg):2,106
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+1,000.00 €/ton
 Add to cart</v>
       </c>
     </row>
@@ -11695,7 +11695,7 @@
       <c r="B707" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, ET-100
 0.70 x 124.9 x coil mm
-Weight (Kg):2,106
+Weight (Kg):1,972
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -11705,26 +11705,10 @@
     </row>
     <row r="708" xml:space="preserve">
       <c r="A708" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, ET-100
-0.70 x 124.9 x coil mm</v>
-      </c>
-      <c r="B708" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, ET-100
-0.70 x 124.9 x coil mm
-Weight (Kg):1,972
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-1,000.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="709" xml:space="preserve">
-      <c r="A709" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 430Ti-1.4510 Coil, 2B,
 0.80 x 155.9 x coil mm</v>
       </c>
-      <c r="B709" t="str" xml:space="preserve">
+      <c r="B708" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 430Ti-1.4510 Coil, 2B,
 0.80 x 155.9 x coil mm
 Weight (Kg):1,586
@@ -11735,12 +11719,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="710" xml:space="preserve">
-      <c r="A710" t="str" xml:space="preserve">
+    <row r="709" xml:space="preserve">
+      <c r="A709" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 304-1.4301 Coil, BA,
 0.40 x 270.0 x coil mm</v>
       </c>
-      <c r="B710" t="str" xml:space="preserve">
+      <c r="B709" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 304-1.4301 Coil, BA,
 0.40 x 270.0 x coil mm
 Weight (Kg):2,572
@@ -11751,12 +11735,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="711" xml:space="preserve">
-      <c r="A711" t="str" xml:space="preserve">
+    <row r="710" xml:space="preserve">
+      <c r="A710" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, BA,
 0.60 x 130.0 x coil mm</v>
       </c>
-      <c r="B711" t="str" xml:space="preserve">
+      <c r="B710" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, BA,
 0.60 x 130.0 x coil mm
 Weight (Kg):1,490
@@ -11764,6 +11748,22 @@
 Help
 Location:FABRICA ALGECIRAS
 1,000.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="711" xml:space="preserve">
+      <c r="A711" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 441-1.4509 Coil, BA,
+0.40 x 110.0 x coil mm</v>
+      </c>
+      <c r="B711" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 441-1.4509 Coil, BA,
+0.40 x 110.0 x coil mm
+Weight (Kg):1,870
+Quality:Prime
+Help
+Location:FABRICA ALGECIRAS
+1,100.00 €/ton
 Add to cart</v>
       </c>
     </row>
@@ -11775,7 +11775,7 @@
       <c r="B712" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 441-1.4509 Coil, BA,
 0.40 x 110.0 x coil mm
-Weight (Kg):1,870
+Weight (Kg):1,882
 Quality:Prime
 Help
 Location:FABRICA ALGECIRAS
@@ -11785,17 +11785,17 @@
     </row>
     <row r="713" xml:space="preserve">
       <c r="A713" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 441-1.4509 Coil, BA,
+        <v xml:space="preserve">Acerinox Europa, 301-1.4310 Coil, BA,
 0.40 x 110.0 x coil mm</v>
       </c>
       <c r="B713" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 441-1.4509 Coil, BA,
+        <v xml:space="preserve">Acerinox Europa, 301-1.4310 Coil, BA,
 0.40 x 110.0 x coil mm
-Weight (Kg):1,882
-Quality:Prime
-Help
-Location:FABRICA ALGECIRAS
-1,100.00 €/ton
+Weight (Kg):1,934
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+1,925.00 €/ton
 Add to cart</v>
       </c>
     </row>
@@ -11807,7 +11807,7 @@
       <c r="B714" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 301-1.4310 Coil, BA,
 0.40 x 110.0 x coil mm
-Weight (Kg):1,934
+Weight (Kg):1,860
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -11817,26 +11817,10 @@
     </row>
     <row r="715" xml:space="preserve">
       <c r="A715" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 301-1.4310 Coil, BA,
-0.40 x 110.0 x coil mm</v>
-      </c>
-      <c r="B715" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 301-1.4310 Coil, BA,
-0.40 x 110.0 x coil mm
-Weight (Kg):1,860
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-1,925.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="716" xml:space="preserve">
-      <c r="A716" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 321-1.4541 Coil, 2B,
 1.90 x 104.5 x coil mm</v>
       </c>
-      <c r="B716" t="str" xml:space="preserve">
+      <c r="B715" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 321-1.4541 Coil, 2B,
 1.90 x 104.5 x coil mm
 Weight (Kg):2,304
@@ -11847,12 +11831,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="717" xml:space="preserve">
-      <c r="A717" t="str" xml:space="preserve">
+    <row r="716" xml:space="preserve">
+      <c r="A716" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 304L/304-4301/4307 Coil, Polished N4-G-180,
 1.20 x 255.9 x coil mm</v>
       </c>
-      <c r="B717" t="str" xml:space="preserve">
+      <c r="B716" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 304L/304-4301/4307 Coil, Polished N4-G-180,
 1.20 x 255.9 x coil mm
 Weight (Kg):4,298
@@ -11863,12 +11847,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="718" xml:space="preserve">
-      <c r="A718" t="str" xml:space="preserve">
+    <row r="717" xml:space="preserve">
+      <c r="A717" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 301-1.4310 Coil, BA,
 0.40 x 110.0 x coil mm</v>
       </c>
-      <c r="B718" t="str" xml:space="preserve">
+      <c r="B717" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 301-1.4310 Coil, BA,
 0.40 x 110.0 x coil mm
 Weight (Kg):1,698
@@ -11879,15 +11863,31 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="719" xml:space="preserve">
-      <c r="A719" t="str" xml:space="preserve">
+    <row r="718" xml:space="preserve">
+      <c r="A718" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, BA,
 0.40 x 130.0 x coil mm</v>
       </c>
-      <c r="B719" t="str" xml:space="preserve">
+      <c r="B718" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, BA,
 0.40 x 130.0 x coil mm
 Weight (Kg):1,916
+Quality:Prime
+Help
+Location:FABRICA ALGECIRAS
+1,000.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="719" xml:space="preserve">
+      <c r="A719" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 430Ti-1.4510 Coil, BA,
+0.50 x 140.0 x coil mm</v>
+      </c>
+      <c r="B719" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 430Ti-1.4510 Coil, BA,
+0.50 x 140.0 x coil mm
+Weight (Kg):3,054
 Quality:Prime
 Help
 Location:FABRICA ALGECIRAS
@@ -11903,7 +11903,7 @@
       <c r="B720" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 430Ti-1.4510 Coil, BA,
 0.50 x 140.0 x coil mm
-Weight (Kg):3,054
+Weight (Kg):3,060
 Quality:Prime
 Help
 Location:FABRICA ALGECIRAS
@@ -11919,7 +11919,7 @@
       <c r="B721" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 430Ti-1.4510 Coil, BA,
 0.50 x 140.0 x coil mm
-Weight (Kg):3,060
+Weight (Kg):2,220
 Quality:Prime
 Help
 Location:FABRICA ALGECIRAS
@@ -11935,7 +11935,7 @@
       <c r="B722" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 430Ti-1.4510 Coil, BA,
 0.50 x 140.0 x coil mm
-Weight (Kg):2,220
+Weight (Kg):2,224
 Quality:Prime
 Help
 Location:FABRICA ALGECIRAS
@@ -11945,17 +11945,17 @@
     </row>
     <row r="723" xml:space="preserve">
       <c r="A723" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 430Ti-1.4510 Coil, BA,
-0.50 x 140.0 x coil mm</v>
+        <v xml:space="preserve">Acerinox Europa, 304L/304-4301/4307 Coil, 2B,
+1.40 x 100.9 x coil mm</v>
       </c>
       <c r="B723" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 430Ti-1.4510 Coil, BA,
-0.50 x 140.0 x coil mm
-Weight (Kg):2,224
-Quality:Prime
-Help
-Location:FABRICA ALGECIRAS
-1,000.00 €/ton
+        <v xml:space="preserve">Acerinox Europa, 304L/304-4301/4307 Coil, 2B,
+1.40 x 100.9 x coil mm
+Weight (Kg):1,612
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,075.00 €/ton
 Add to cart</v>
       </c>
     </row>
@@ -11967,7 +11967,7 @@
       <c r="B724" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 304L/304-4301/4307 Coil, 2B,
 1.40 x 100.9 x coil mm
-Weight (Kg):1,612
+Weight (Kg):1,600
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -11977,14 +11977,14 @@
     </row>
     <row r="725" xml:space="preserve">
       <c r="A725" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 304L/304-4301/4307 Coil, 2B,
-1.40 x 100.9 x coil mm</v>
+        <v xml:space="preserve">Acerinox Europa, 304-1.4301 Coil, Emboss Chequered,
+0.70 x 174.9 x coil mm</v>
       </c>
       <c r="B725" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 304L/304-4301/4307 Coil, 2B,
-1.40 x 100.9 x coil mm
-Weight (Kg):1,600
-Quality:Prime-2
+        <v xml:space="preserve">Acerinox Europa, 304-1.4301 Coil, Emboss Chequered,
+0.70 x 174.9 x coil mm
+Weight (Kg):1,494
+Quality:Prime
 Help
 Location:FABRICA ALGECIRAS
 2,075.00 €/ton
@@ -11999,7 +11999,7 @@
       <c r="B726" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 304-1.4301 Coil, Emboss Chequered,
 0.70 x 174.9 x coil mm
-Weight (Kg):1,494
+Weight (Kg):1,472
 Quality:Prime
 Help
 Location:FABRICA ALGECIRAS
@@ -12009,26 +12009,10 @@
     </row>
     <row r="727" xml:space="preserve">
       <c r="A727" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 304-1.4301 Coil, Emboss Chequered,
-0.70 x 174.9 x coil mm</v>
-      </c>
-      <c r="B727" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 304-1.4301 Coil, Emboss Chequered,
-0.70 x 174.9 x coil mm
-Weight (Kg):1,472
-Quality:Prime
-Help
-Location:FABRICA ALGECIRAS
-2,075.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="728" xml:space="preserve">
-      <c r="A728" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, SB-G-240,
 0.50 x 290.9 x coil mm</v>
       </c>
-      <c r="B728" t="str" xml:space="preserve">
+      <c r="B727" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, SB-G-240,
 0.50 x 290.9 x coil mm
 Weight (Kg):4,408
@@ -12039,15 +12023,31 @@
 Add to cart</v>
       </c>
     </row>
+    <row r="728" xml:space="preserve">
+      <c r="A728" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 304-1.4301 Coil, BA,
+0.60 x 110.0 x coil mm</v>
+      </c>
+      <c r="B728" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 304-1.4301 Coil, BA,
+0.60 x 110.0 x coil mm
+Weight (Kg):1,032
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,075.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
     <row r="729" xml:space="preserve">
       <c r="A729" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 304-1.4301 Coil, BA,
-0.60 x 110.0 x coil mm</v>
+0.40 x 270.0 x coil mm</v>
       </c>
       <c r="B729" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 304-1.4301 Coil, BA,
-0.60 x 110.0 x coil mm
-Weight (Kg):1,032
+0.40 x 270.0 x coil mm
+Weight (Kg):3,124
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -12058,25 +12058,9 @@
     <row r="730" xml:space="preserve">
       <c r="A730" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 304-1.4301 Coil, BA,
-0.40 x 270.0 x coil mm</v>
+0.60 x 135.0 x coil mm</v>
       </c>
       <c r="B730" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 304-1.4301 Coil, BA,
-0.40 x 270.0 x coil mm
-Weight (Kg):3,124
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-2,075.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="731" xml:space="preserve">
-      <c r="A731" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 304-1.4301 Coil, BA,
-0.60 x 135.0 x coil mm</v>
-      </c>
-      <c r="B731" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 304-1.4301 Coil, BA,
 0.60 x 135.0 x coil mm
 Weight (Kg):2,078
@@ -12087,12 +12071,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="732" xml:space="preserve">
-      <c r="A732" t="str" xml:space="preserve">
+    <row r="731" xml:space="preserve">
+      <c r="A731" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 441-1.4509 Coil, 2B,
 2.00 x 245.9 x coil mm</v>
       </c>
-      <c r="B732" t="str" xml:space="preserve">
+      <c r="B731" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 441-1.4509 Coil, 2B,
 2.00 x 245.9 x coil mm
 Weight (Kg):3,492
@@ -12103,12 +12087,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="733" xml:space="preserve">
-      <c r="A733" t="str" xml:space="preserve">
+    <row r="732" xml:space="preserve">
+      <c r="A732" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 304-1.4301 Coil, 2B,
 0.60 x 101.9 x coil mm</v>
       </c>
-      <c r="B733" t="str" xml:space="preserve">
+      <c r="B732" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 304-1.4301 Coil, 2B,
 0.60 x 101.9 x coil mm
 Weight (Kg):1,350
@@ -12119,12 +12103,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="734" xml:space="preserve">
-      <c r="A734" t="str" xml:space="preserve">
+    <row r="733" xml:space="preserve">
+      <c r="A733" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 430Ti-1.4510 Coil, BA,
 0.70 x 118.9 x coil mm</v>
       </c>
-      <c r="B734" t="str" xml:space="preserve">
+      <c r="B733" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 430Ti-1.4510 Coil, BA,
 0.70 x 118.9 x coil mm
 Weight (Kg):1,768
@@ -12135,28 +12119,28 @@
 Add to cart</v>
       </c>
     </row>
+    <row r="734" xml:space="preserve">
+      <c r="A734" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 304L/304-4301/4307 Coil, 2B,
+1.00 x 135.9 x coil mm</v>
+      </c>
+      <c r="B734" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 304L/304-4301/4307 Coil, 2B,
+1.00 x 135.9 x coil mm
+Weight (Kg):1,056
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,075.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
     <row r="735" xml:space="preserve">
       <c r="A735" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 304L/304-4301/4307 Coil, 2B,
-1.00 x 135.9 x coil mm</v>
+2.00 x 250.0 x coil mm</v>
       </c>
       <c r="B735" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 304L/304-4301/4307 Coil, 2B,
-1.00 x 135.9 x coil mm
-Weight (Kg):1,056
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-2,075.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="736" xml:space="preserve">
-      <c r="A736" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 304L/304-4301/4307 Coil, 2B,
-2.00 x 250.0 x coil mm</v>
-      </c>
-      <c r="B736" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 304L/304-4301/4307 Coil, 2B,
 2.00 x 250.0 x coil mm
 Weight (Kg):2,388
@@ -12164,6 +12148,22 @@
 Help
 Location:FABRICA ALGECIRAS
 2,075.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="736" xml:space="preserve">
+      <c r="A736" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, BA,
+0.70 x 125.9 x coil mm</v>
+      </c>
+      <c r="B736" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, BA,
+0.70 x 125.9 x coil mm
+Weight (Kg):1,788
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+1,000.00 €/ton
 Add to cart</v>
       </c>
     </row>
@@ -12175,7 +12175,7 @@
       <c r="B737" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, BA,
 0.70 x 125.9 x coil mm
-Weight (Kg):1,788
+Weight (Kg):1,794
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -12185,26 +12185,10 @@
     </row>
     <row r="738" xml:space="preserve">
       <c r="A738" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, BA,
-0.70 x 125.9 x coil mm</v>
-      </c>
-      <c r="B738" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, BA,
-0.70 x 125.9 x coil mm
-Weight (Kg):1,794
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-1,000.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="739" xml:space="preserve">
-      <c r="A739" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 430Ti-1.4510 Coil, BA,
 0.70 x 112.0 x coil mm</v>
       </c>
-      <c r="B739" t="str" xml:space="preserve">
+      <c r="B738" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 430Ti-1.4510 Coil, BA,
 0.70 x 112.0 x coil mm
 Weight (Kg):1,550
@@ -12212,6 +12196,22 @@
 Help
 Location:FABRICA ALGECIRAS
 1,000.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="739" xml:space="preserve">
+      <c r="A739" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 304-1.4301 Coil, BA,
+0.60 x 320.0 x coil mm</v>
+      </c>
+      <c r="B739" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 304-1.4301 Coil, BA,
+0.60 x 320.0 x coil mm
+Weight (Kg):2,534
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,075.00 €/ton
 Add to cart</v>
       </c>
     </row>
@@ -12223,7 +12223,7 @@
       <c r="B740" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 304-1.4301 Coil, BA,
 0.60 x 320.0 x coil mm
-Weight (Kg):2,534
+Weight (Kg):3,148
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -12233,26 +12233,10 @@
     </row>
     <row r="741" xml:space="preserve">
       <c r="A741" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 304-1.4301 Coil, BA,
-0.60 x 320.0 x coil mm</v>
-      </c>
-      <c r="B741" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 304-1.4301 Coil, BA,
-0.60 x 320.0 x coil mm
-Weight (Kg):3,148
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-2,075.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="742" xml:space="preserve">
-      <c r="A742" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 304-1.4301 Coil, 2B,
 0.80 x 199.9 x coil mm</v>
       </c>
-      <c r="B742" t="str" xml:space="preserve">
+      <c r="B741" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 304-1.4301 Coil, 2B,
 0.80 x 199.9 x coil mm
 Weight (Kg):2,602
@@ -12263,12 +12247,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="743" xml:space="preserve">
-      <c r="A743" t="str" xml:space="preserve">
+    <row r="742" xml:space="preserve">
+      <c r="A742" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 304L/304-4301/4307 Coil, 2B,
 1.00 x 125.9 x coil mm</v>
       </c>
-      <c r="B743" t="str" xml:space="preserve">
+      <c r="B742" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 304L/304-4301/4307 Coil, 2B,
 1.00 x 125.9 x coil mm
 Weight (Kg):1,726
@@ -12279,12 +12263,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="744" xml:space="preserve">
-      <c r="A744" t="str" xml:space="preserve">
+    <row r="743" xml:space="preserve">
+      <c r="A743" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 316L-1.4404 Coil, 2B,
 1.50 x 230.9 x coil mm</v>
       </c>
-      <c r="B744" t="str" xml:space="preserve">
+      <c r="B743" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 316L-1.4404 Coil, 2B,
 1.50 x 230.9 x coil mm
 Weight (Kg):1,956
@@ -12295,12 +12279,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="745" xml:space="preserve">
-      <c r="A745" t="str" xml:space="preserve">
+    <row r="744" xml:space="preserve">
+      <c r="A744" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, SBA,
 0.70 x 180.9 x coil mm</v>
       </c>
-      <c r="B745" t="str" xml:space="preserve">
+      <c r="B744" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, SBA,
 0.70 x 180.9 x coil mm
 Weight (Kg):2,402
@@ -12311,12 +12295,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="746" xml:space="preserve">
-      <c r="A746" t="str" xml:space="preserve">
+    <row r="745" xml:space="preserve">
+      <c r="A745" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 301-1.4310 Coil, BA,
 0.40 x 110.0 x coil mm</v>
       </c>
-      <c r="B746" t="str" xml:space="preserve">
+      <c r="B745" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 301-1.4310 Coil, BA,
 0.40 x 110.0 x coil mm
 Weight (Kg):1,734
@@ -12329,7 +12313,7 @@
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B746"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B745"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/scraped_data.xlsx
+++ b/scraped_data.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B745"/>
+  <dimension ref="A1:B742"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -3018,12 +3018,12 @@
     <row r="165" xml:space="preserve">
       <c r="A165" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Coil, 2B,
-1.50 x 230.9 x coil mm</v>
+1.80 x 102.0 x coil mm</v>
       </c>
       <c r="B165" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Coil, 2B,
-1.50 x 230.9 x coil mm
-Weight (Kg):4,140
+1.80 x 102.0 x coil mm
+Weight (Kg):794
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -3034,32 +3034,32 @@
     <row r="166" xml:space="preserve">
       <c r="A166" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Coil, 2B,
-1.80 x 102.0 x coil mm</v>
+2.00 x 1277.0 x coil mm</v>
       </c>
       <c r="B166" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Coil, 2B,
-1.80 x 102.0 x coil mm
-Weight (Kg):794
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-2,075.00 €/ton
+2.00 x 1277.0 x coil mm
+Weight (Kg):2,940
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,225.00 €/ton
 Add to cart</v>
       </c>
     </row>
     <row r="167" xml:space="preserve">
       <c r="A167" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Coil, 2B,
-2.00 x 1277.0 x coil mm</v>
+2.00 x 553.0 x coil mm</v>
       </c>
       <c r="B167" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Coil, 2B,
-2.00 x 1277.0 x coil mm
-Weight (Kg):2,940
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-2,225.00 €/ton
+2.00 x 553.0 x coil mm
+Weight (Kg):385
+Quality:Downgraded
+Help
+Location:FABRICA ALGECIRAS
+2,025.00 €/ton
 Add to cart</v>
       </c>
     </row>
@@ -3082,44 +3082,44 @@
     <row r="169" xml:space="preserve">
       <c r="A169" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Coil, 2B,
-2.00 x 553.0 x coil mm</v>
+2.50 x 1000.0 x coil mm</v>
       </c>
       <c r="B169" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Coil, 2B,
-2.00 x 553.0 x coil mm
-Weight (Kg):385
-Quality:Downgraded
-Help
-Location:FABRICA ALGECIRAS
-2,025.00 €/ton
+2.50 x 1000.0 x coil mm
+Weight (Kg):2,280
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,225.00 €/ton
 Add to cart</v>
       </c>
     </row>
     <row r="170" xml:space="preserve">
       <c r="A170" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Coil, 2B,
-2.50 x 1000.0 x coil mm</v>
+5.00 x 265.9 x coil mm</v>
       </c>
       <c r="B170" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Coil, 2B,
-2.50 x 1000.0 x coil mm
-Weight (Kg):2,280
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-2,225.00 €/ton
+5.00 x 265.9 x coil mm
+Weight (Kg):1,596
+Quality:Prime
+Help
+Location:FABRICA ALGECIRAS
+2,075.00 €/ton
 Add to cart</v>
       </c>
     </row>
     <row r="171" xml:space="preserve">
       <c r="A171" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Coil, 2B,
-5.00 x 265.9 x coil mm</v>
+5.00 x 286.0 x coil mm</v>
       </c>
       <c r="B171" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Coil, 2B,
-5.00 x 265.9 x coil mm
-Weight (Kg):1,596
+5.00 x 286.0 x coil mm
+Weight (Kg):2,451
 Quality:Prime
 Help
 Location:FABRICA ALGECIRAS
@@ -3136,7 +3136,7 @@
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Coil, 2B,
 5.00 x 286.0 x coil mm
 Weight (Kg):2,451
-Quality:Prime
+Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
 2,075.00 €/ton
@@ -3146,16 +3146,16 @@
     <row r="173" xml:space="preserve">
       <c r="A173" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Coil, 2B,
-5.00 x 286.0 x coil mm</v>
+6.00 x 1500.0 x coil mm</v>
       </c>
       <c r="B173" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Coil, 2B,
-5.00 x 286.0 x coil mm
-Weight (Kg):2,451
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-2,075.00 €/ton
+6.00 x 1500.0 x coil mm
+Weight (Kg):1,700
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,225.00 €/ton
 Add to cart</v>
       </c>
     </row>
@@ -3167,7 +3167,7 @@
       <c r="B174" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Coil, 2B,
 6.00 x 1500.0 x coil mm
-Weight (Kg):1,700
+Weight (Kg):2,355
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -3183,7 +3183,7 @@
       <c r="B175" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Coil, 2B,
 6.00 x 1500.0 x coil mm
-Weight (Kg):2,355
+Weight (Kg):2,375
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -3199,7 +3199,7 @@
       <c r="B176" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Coil, 2B,
 6.00 x 1500.0 x coil mm
-Weight (Kg):2,375
+Weight (Kg):2,204
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -3231,7 +3231,7 @@
       <c r="B178" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Coil, 2B,
 6.00 x 1500.0 x coil mm
-Weight (Kg):2,204
+Weight (Kg):2,844
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -3242,41 +3242,25 @@
     <row r="179" xml:space="preserve">
       <c r="A179" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Coil, 2B,
-6.00 x 1500.0 x coil mm</v>
+6.00 x 220.0 x coil mm</v>
       </c>
       <c r="B179" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Coil, 2B,
-6.00 x 1500.0 x coil mm
-Weight (Kg):2,844
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-2,225.00 €/ton
+6.00 x 220.0 x coil mm
+Weight (Kg):4,046
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,075.00 €/ton
 Add to cart</v>
       </c>
     </row>
     <row r="180" xml:space="preserve">
       <c r="A180" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Coil, 2B,
-6.00 x 220.0 x coil mm</v>
+6.00 x 250.0 x coil mm</v>
       </c>
       <c r="B180" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Coil, 2B,
-6.00 x 220.0 x coil mm
-Weight (Kg):4,046
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-2,075.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="181" xml:space="preserve">
-      <c r="A181" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Coil, 2B,
-6.00 x 250.0 x coil mm</v>
-      </c>
-      <c r="B181" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Coil, 2B,
 6.00 x 250.0 x coil mm
 Weight (Kg):3,086
@@ -3287,12 +3271,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="182" xml:space="preserve">
-      <c r="A182" t="str" xml:space="preserve">
+    <row r="181" xml:space="preserve">
+      <c r="A181" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Coil, BA,
 0.70 x 1268.0 x coil mm</v>
       </c>
-      <c r="B182" t="str" xml:space="preserve">
+      <c r="B181" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Coil, BA,
 0.70 x 1268.0 x coil mm
 Weight (Kg):20,010
@@ -3303,28 +3287,28 @@
 Add to cart</v>
       </c>
     </row>
+    <row r="182" xml:space="preserve">
+      <c r="A182" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Coil, Emboss Skin,
+0.50 x 1250.0 x coil mm</v>
+      </c>
+      <c r="B182" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Coil, Emboss Skin,
+0.50 x 1250.0 x coil mm
+Weight (Kg):3,950
+Quality:Prime
+Help
+Location:FABRICA ALGECIRAS
+2,425.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
     <row r="183" xml:space="preserve">
       <c r="A183" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Coil, Emboss Skin,
-0.50 x 1250.0 x coil mm</v>
+0.50 x 1261.0 x coil mm</v>
       </c>
       <c r="B183" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Coil, Emboss Skin,
-0.50 x 1250.0 x coil mm
-Weight (Kg):3,950
-Quality:Prime
-Help
-Location:FABRICA ALGECIRAS
-2,425.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="184" xml:space="preserve">
-      <c r="A184" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Coil, Emboss Skin,
-0.50 x 1261.0 x coil mm</v>
-      </c>
-      <c r="B184" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Coil, Emboss Skin,
 0.50 x 1261.0 x coil mm
 Weight (Kg):10,590
@@ -3335,19 +3319,35 @@
 Add to cart</v>
       </c>
     </row>
+    <row r="184" xml:space="preserve">
+      <c r="A184" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Coil, Nb. 1,
+4.70 x 220.0 x coil mm</v>
+      </c>
+      <c r="B184" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Coil, Nb. 1,
+4.70 x 220.0 x coil mm
+Weight (Kg):3,704
+Quality:Prime
+Help
+Location:FABRICA ALGECIRAS
+1,975.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
     <row r="185" xml:space="preserve">
       <c r="A185" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Coil, Nb. 1,
-4.70 x 220.0 x coil mm</v>
+8.00 x 1500.0 x coil mm</v>
       </c>
       <c r="B185" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Coil, Nb. 1,
-4.70 x 220.0 x coil mm
-Weight (Kg):3,704
-Quality:Prime
-Help
-Location:FABRICA ALGECIRAS
-1,975.00 €/ton
+8.00 x 1500.0 x coil mm
+Weight (Kg):4,076
+Quality:Prime
+Help
+Location:FABRICA ALGECIRAS
+2,325.00 €/ton
 Add to cart</v>
       </c>
     </row>
@@ -3359,7 +3359,7 @@
       <c r="B186" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Coil, Nb. 1,
 8.00 x 1500.0 x coil mm
-Weight (Kg):4,076
+Weight (Kg):2,749
 Quality:Prime
 Help
 Location:FABRICA ALGECIRAS
@@ -3369,26 +3369,10 @@
     </row>
     <row r="187" xml:space="preserve">
       <c r="A187" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Coil, Nb. 1,
-8.00 x 1500.0 x coil mm</v>
-      </c>
-      <c r="B187" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Coil, Nb. 1,
-8.00 x 1500.0 x coil mm
-Weight (Kg):2,749
-Quality:Prime
-Help
-Location:FABRICA ALGECIRAS
-2,325.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="188" xml:space="preserve">
-      <c r="A188" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Coil, Nb. 2 Chequered,
 6.00 x 1250.0 x coil mm</v>
       </c>
-      <c r="B188" t="str" xml:space="preserve">
+      <c r="B187" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Coil, Nb. 2 Chequered,
 6.00 x 1250.0 x coil mm
 Weight (Kg):19,244
@@ -3399,12 +3383,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="189" xml:space="preserve">
-      <c r="A189" t="str" xml:space="preserve">
+    <row r="188" xml:space="preserve">
+      <c r="A188" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Coil, Nb. 3 Chequered,
 4.00 x 1548.0 x coil mm</v>
       </c>
-      <c r="B189" t="str" xml:space="preserve">
+      <c r="B188" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Coil, Nb. 3 Chequered,
 4.00 x 1548.0 x coil mm
 Weight (Kg):3,000
@@ -3415,28 +3399,28 @@
 Add to cart</v>
       </c>
     </row>
+    <row r="189" xml:space="preserve">
+      <c r="A189" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Coil, Polished N4-G-180,
+0.90 x 190.0 x coil mm</v>
+      </c>
+      <c r="B189" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Coil, Polished N4-G-180,
+0.90 x 190.0 x coil mm
+Weight (Kg):1,424
+Quality:Prime
+Help
+Location:FABRICA ALGECIRAS
+2,075.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
     <row r="190" xml:space="preserve">
       <c r="A190" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Coil, Polished N4-G-180,
-0.90 x 190.0 x coil mm</v>
+0.90 x 205.9 x coil mm</v>
       </c>
       <c r="B190" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Coil, Polished N4-G-180,
-0.90 x 190.0 x coil mm
-Weight (Kg):1,424
-Quality:Prime
-Help
-Location:FABRICA ALGECIRAS
-2,075.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="191" xml:space="preserve">
-      <c r="A191" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Coil, Polished N4-G-180,
-0.90 x 205.9 x coil mm</v>
-      </c>
-      <c r="B191" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Coil, Polished N4-G-180,
 0.90 x 205.9 x coil mm
 Weight (Kg):802
@@ -3447,12 +3431,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="192" xml:space="preserve">
-      <c r="A192" t="str" xml:space="preserve">
+    <row r="191" xml:space="preserve">
+      <c r="A191" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Coil, SB-G-400,
 1.00 x 154.9 x coil mm</v>
       </c>
-      <c r="B192" t="str" xml:space="preserve">
+      <c r="B191" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Coil, SB-G-400,
 1.00 x 154.9 x coil mm
 Weight (Kg):1,152
@@ -3463,12 +3447,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="193" xml:space="preserve">
-      <c r="A193" t="str" xml:space="preserve">
+    <row r="192" xml:space="preserve">
+      <c r="A192" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Coil, SB-G-500,
 0.90 x 1250.0 x coil mm</v>
       </c>
-      <c r="B193" t="str" xml:space="preserve">
+      <c r="B192" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Coil, SB-G-500,
 0.90 x 1250.0 x coil mm
 Weight (Kg):2,329
@@ -3479,6 +3463,22 @@
 Add to cart</v>
       </c>
     </row>
+    <row r="193" xml:space="preserve">
+      <c r="A193" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
+0.70 x 1500.0 x 3000.0 mm</v>
+      </c>
+      <c r="B193" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
+0.70 x 1500.0 x 3000.0 mm
+Weight (Kg):612
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,225.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
     <row r="194" xml:space="preserve">
       <c r="A194" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
@@ -3487,7 +3487,7 @@
       <c r="B194" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 0.70 x 1500.0 x 3000.0 mm
-Weight (Kg):612
+Weight (Kg):702
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -3498,12 +3498,12 @@
     <row r="195" xml:space="preserve">
       <c r="A195" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
-0.70 x 1500.0 x 3000.0 mm</v>
+0.80 x 1000.0 x 2000.0 mm</v>
       </c>
       <c r="B195" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
-0.70 x 1500.0 x 3000.0 mm
-Weight (Kg):702
+0.80 x 1000.0 x 2000.0 mm
+Weight (Kg):580
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -3514,12 +3514,12 @@
     <row r="196" xml:space="preserve">
       <c r="A196" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
-0.80 x 1000.0 x 2000.0 mm</v>
+1.00 x 1500.0 x 3000.0 mm</v>
       </c>
       <c r="B196" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
-0.80 x 1000.0 x 2000.0 mm
-Weight (Kg):580
+1.00 x 1500.0 x 3000.0 mm
+Weight (Kg):959
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -3535,7 +3535,7 @@
       <c r="B197" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 1.00 x 1500.0 x 3000.0 mm
-Weight (Kg):959
+Weight (Kg):794
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -3551,7 +3551,7 @@
       <c r="B198" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 1.00 x 1500.0 x 3000.0 mm
-Weight (Kg):794
+Weight (Kg):659
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -3615,7 +3615,7 @@
       <c r="B202" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 1.00 x 1500.0 x 3000.0 mm
-Weight (Kg):659
+Weight (Kg):1,508
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -3631,7 +3631,7 @@
       <c r="B203" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 1.00 x 1500.0 x 3000.0 mm
-Weight (Kg):1,508
+Weight (Kg):1,921
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -3647,7 +3647,7 @@
       <c r="B204" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 1.00 x 1500.0 x 3000.0 mm
-Weight (Kg):1,921
+Weight (Kg):894
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -3663,7 +3663,7 @@
       <c r="B205" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 1.00 x 1500.0 x 3000.0 mm
-Weight (Kg):894
+Weight (Kg):700
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -3679,7 +3679,7 @@
       <c r="B206" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 1.00 x 1500.0 x 3000.0 mm
-Weight (Kg):700
+Weight (Kg):842
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -3690,12 +3690,12 @@
     <row r="207" xml:space="preserve">
       <c r="A207" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
-1.00 x 1500.0 x 3000.0 mm</v>
+2.00 x 1000.0 x 2000.0 mm</v>
       </c>
       <c r="B207" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
-1.00 x 1500.0 x 3000.0 mm
-Weight (Kg):842
+2.00 x 1000.0 x 2000.0 mm
+Weight (Kg):512
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -3711,7 +3711,7 @@
       <c r="B208" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 2.00 x 1000.0 x 2000.0 mm
-Weight (Kg):512
+Weight (Kg):949
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -3722,12 +3722,12 @@
     <row r="209" xml:space="preserve">
       <c r="A209" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
-2.00 x 1000.0 x 2000.0 mm</v>
+2.00 x 1250.0 x 2500.0 mm</v>
       </c>
       <c r="B209" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
-2.00 x 1000.0 x 2000.0 mm
-Weight (Kg):949
+2.00 x 1250.0 x 2500.0 mm
+Weight (Kg):735
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -3743,7 +3743,7 @@
       <c r="B210" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 2.00 x 1250.0 x 2500.0 mm
-Weight (Kg):735
+Weight (Kg):805
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -3759,7 +3759,7 @@
       <c r="B211" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 2.00 x 1250.0 x 2500.0 mm
-Weight (Kg):805
+Weight (Kg):777
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -3775,7 +3775,7 @@
       <c r="B212" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 2.00 x 1250.0 x 2500.0 mm
-Weight (Kg):777
+Weight (Kg):576
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -3791,7 +3791,7 @@
       <c r="B213" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 2.00 x 1250.0 x 2500.0 mm
-Weight (Kg):576
+Weight (Kg):622
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -3807,7 +3807,7 @@
       <c r="B214" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 2.00 x 1250.0 x 2500.0 mm
-Weight (Kg):622
+Weight (Kg):862
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -3823,7 +3823,7 @@
       <c r="B215" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 2.00 x 1250.0 x 2500.0 mm
-Weight (Kg):862
+Weight (Kg):619
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -3839,7 +3839,7 @@
       <c r="B216" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 2.00 x 1250.0 x 2500.0 mm
-Weight (Kg):619
+Weight (Kg):867
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -3855,7 +3855,7 @@
       <c r="B217" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 2.00 x 1250.0 x 2500.0 mm
-Weight (Kg):867
+Weight (Kg):774
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -3866,12 +3866,12 @@
     <row r="218" xml:space="preserve">
       <c r="A218" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
-2.00 x 1250.0 x 2500.0 mm</v>
+2.00 x 1250.0 x 3000.0 mm</v>
       </c>
       <c r="B218" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
-2.00 x 1250.0 x 2500.0 mm
-Weight (Kg):774
+2.00 x 1250.0 x 3000.0 mm
+Weight (Kg):877
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -3882,12 +3882,12 @@
     <row r="219" xml:space="preserve">
       <c r="A219" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
-2.00 x 1250.0 x 3000.0 mm</v>
+2.50 x 1000.0 x 2000.0 mm</v>
       </c>
       <c r="B219" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
-2.00 x 1250.0 x 3000.0 mm
-Weight (Kg):877
+2.50 x 1000.0 x 2000.0 mm
+Weight (Kg):781
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -3903,7 +3903,7 @@
       <c r="B220" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 2.50 x 1000.0 x 2000.0 mm
-Weight (Kg):781
+Weight (Kg):590
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -3914,12 +3914,12 @@
     <row r="221" xml:space="preserve">
       <c r="A221" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
-2.50 x 1000.0 x 2000.0 mm</v>
+2.50 x 1250.0 x 2500.0 mm</v>
       </c>
       <c r="B221" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
-2.50 x 1000.0 x 2000.0 mm
-Weight (Kg):590
+2.50 x 1250.0 x 2500.0 mm
+Weight (Kg):660
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -3935,7 +3935,7 @@
       <c r="B222" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 2.50 x 1250.0 x 2500.0 mm
-Weight (Kg):660
+Weight (Kg):852
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -3946,12 +3946,12 @@
     <row r="223" xml:space="preserve">
       <c r="A223" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
-2.50 x 1250.0 x 2500.0 mm</v>
+2.50 x 1500.0 x 3000.0 mm</v>
       </c>
       <c r="B223" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
-2.50 x 1250.0 x 2500.0 mm
-Weight (Kg):852
+2.50 x 1500.0 x 3000.0 mm
+Weight (Kg):792
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -3967,7 +3967,7 @@
       <c r="B224" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 2.50 x 1500.0 x 3000.0 mm
-Weight (Kg):792
+Weight (Kg):1,390
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -3983,7 +3983,7 @@
       <c r="B225" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 2.50 x 1500.0 x 3000.0 mm
-Weight (Kg):1,390
+Weight (Kg):1,224
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -3999,7 +3999,7 @@
       <c r="B226" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 2.50 x 1500.0 x 3000.0 mm
-Weight (Kg):1,224
+Weight (Kg):2,098
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -4015,7 +4015,7 @@
       <c r="B227" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 2.50 x 1500.0 x 3000.0 mm
-Weight (Kg):2,098
+Weight (Kg):1,238
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -4031,7 +4031,7 @@
       <c r="B228" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 2.50 x 1500.0 x 3000.0 mm
-Weight (Kg):1,238
+Weight (Kg):856
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -4047,7 +4047,7 @@
       <c r="B229" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 2.50 x 1500.0 x 3000.0 mm
-Weight (Kg):856
+Weight (Kg):605
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -4063,7 +4063,7 @@
       <c r="B230" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 2.50 x 1500.0 x 3000.0 mm
-Weight (Kg):605
+Weight (Kg):521
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -4079,7 +4079,7 @@
       <c r="B231" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 2.50 x 1500.0 x 3000.0 mm
-Weight (Kg):521
+Weight (Kg):527
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -4095,7 +4095,7 @@
       <c r="B232" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 2.50 x 1500.0 x 3000.0 mm
-Weight (Kg):527
+Weight (Kg):862
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -4106,12 +4106,12 @@
     <row r="233" xml:space="preserve">
       <c r="A233" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
-2.50 x 1500.0 x 3000.0 mm</v>
+3.00 x 1000.0 x 2000.0 mm</v>
       </c>
       <c r="B233" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
-2.50 x 1500.0 x 3000.0 mm
-Weight (Kg):862
+3.00 x 1000.0 x 2000.0 mm
+Weight (Kg):992
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -4127,7 +4127,7 @@
       <c r="B234" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 3.00 x 1000.0 x 2000.0 mm
-Weight (Kg):992
+Weight (Kg):1,038
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -4143,7 +4143,7 @@
       <c r="B235" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 3.00 x 1000.0 x 2000.0 mm
-Weight (Kg):1,038
+Weight (Kg):946
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -4159,7 +4159,7 @@
       <c r="B236" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 3.00 x 1000.0 x 2000.0 mm
-Weight (Kg):946
+Weight (Kg):503
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -4175,7 +4175,7 @@
       <c r="B237" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 3.00 x 1000.0 x 2000.0 mm
-Weight (Kg):503
+Weight (Kg):880
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -4191,7 +4191,7 @@
       <c r="B238" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 3.00 x 1000.0 x 2000.0 mm
-Weight (Kg):880
+Weight (Kg):796
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -4207,7 +4207,7 @@
       <c r="B239" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 3.00 x 1000.0 x 2000.0 mm
-Weight (Kg):796
+Weight (Kg):578
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -4223,7 +4223,7 @@
       <c r="B240" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 3.00 x 1000.0 x 2000.0 mm
-Weight (Kg):578
+Weight (Kg):1,506
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -4239,7 +4239,7 @@
       <c r="B241" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 3.00 x 1000.0 x 2000.0 mm
-Weight (Kg):1,506
+Weight (Kg):1,538
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -4255,7 +4255,7 @@
       <c r="B242" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 3.00 x 1000.0 x 2000.0 mm
-Weight (Kg):1,538
+Weight (Kg):520
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -4266,12 +4266,12 @@
     <row r="243" xml:space="preserve">
       <c r="A243" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
-3.00 x 1000.0 x 2000.0 mm</v>
+3.00 x 1250.0 x 2500.0 mm</v>
       </c>
       <c r="B243" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
-3.00 x 1000.0 x 2000.0 mm
-Weight (Kg):520
+3.00 x 1250.0 x 2500.0 mm
+Weight (Kg):886
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -4287,7 +4287,7 @@
       <c r="B244" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 3.00 x 1250.0 x 2500.0 mm
-Weight (Kg):886
+Weight (Kg):1,233
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -4303,7 +4303,7 @@
       <c r="B245" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 3.00 x 1250.0 x 2500.0 mm
-Weight (Kg):1,233
+Weight (Kg):742
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -4319,7 +4319,7 @@
       <c r="B246" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 3.00 x 1250.0 x 2500.0 mm
-Weight (Kg):742
+Weight (Kg):858
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -4335,7 +4335,7 @@
       <c r="B247" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 3.00 x 1250.0 x 2500.0 mm
-Weight (Kg):858
+Weight (Kg):1,450
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -4351,7 +4351,7 @@
       <c r="B248" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 3.00 x 1250.0 x 2500.0 mm
-Weight (Kg):1,450
+Weight (Kg):1,818
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -4367,7 +4367,7 @@
       <c r="B249" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 3.00 x 1250.0 x 2500.0 mm
-Weight (Kg):1,818
+Weight (Kg):1,220
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -4383,7 +4383,7 @@
       <c r="B250" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 3.00 x 1250.0 x 2500.0 mm
-Weight (Kg):1,220
+Weight (Kg):812
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -4399,7 +4399,7 @@
       <c r="B251" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 3.00 x 1250.0 x 2500.0 mm
-Weight (Kg):812
+Weight (Kg):816
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -4415,7 +4415,7 @@
       <c r="B252" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 3.00 x 1250.0 x 2500.0 mm
-Weight (Kg):816
+Weight (Kg):1,320
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -4431,7 +4431,7 @@
       <c r="B253" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 3.00 x 1250.0 x 2500.0 mm
-Weight (Kg):1,320
+Weight (Kg):830
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -4447,7 +4447,7 @@
       <c r="B254" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 3.00 x 1250.0 x 2500.0 mm
-Weight (Kg):830
+Weight (Kg):1,446
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -4463,7 +4463,7 @@
       <c r="B255" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 3.00 x 1250.0 x 2500.0 mm
-Weight (Kg):1,446
+Weight (Kg):670
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -4479,7 +4479,7 @@
       <c r="B256" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 3.00 x 1250.0 x 2500.0 mm
-Weight (Kg):670
+Weight (Kg):884
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -4495,7 +4495,7 @@
       <c r="B257" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 3.00 x 1250.0 x 2500.0 mm
-Weight (Kg):884
+Weight (Kg):762
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -4506,12 +4506,12 @@
     <row r="258" xml:space="preserve">
       <c r="A258" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
-3.00 x 1250.0 x 2500.0 mm</v>
+3.00 x 1500.0 x 3000.0 mm</v>
       </c>
       <c r="B258" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
-3.00 x 1250.0 x 2500.0 mm
-Weight (Kg):762
+3.00 x 1500.0 x 3000.0 mm
+Weight (Kg):744
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -4527,7 +4527,7 @@
       <c r="B259" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 3.00 x 1500.0 x 3000.0 mm
-Weight (Kg):744
+Weight (Kg):1,394
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -4543,7 +4543,7 @@
       <c r="B260" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 3.00 x 1500.0 x 3000.0 mm
-Weight (Kg):1,394
+Weight (Kg):2,224
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -4559,7 +4559,7 @@
       <c r="B261" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 3.00 x 1500.0 x 3000.0 mm
-Weight (Kg):2,224
+Weight (Kg):1,156
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -4575,7 +4575,7 @@
       <c r="B262" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 3.00 x 1500.0 x 3000.0 mm
-Weight (Kg):1,156
+Weight (Kg):632
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -4591,7 +4591,7 @@
       <c r="B263" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 3.00 x 1500.0 x 3000.0 mm
-Weight (Kg):632
+Weight (Kg):950
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -4607,7 +4607,7 @@
       <c r="B264" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 3.00 x 1500.0 x 3000.0 mm
-Weight (Kg):950
+Weight (Kg):750
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -4623,7 +4623,7 @@
       <c r="B265" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 3.00 x 1500.0 x 3000.0 mm
-Weight (Kg):750
+Weight (Kg):1,906
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -4639,7 +4639,7 @@
       <c r="B266" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 3.00 x 1500.0 x 3000.0 mm
-Weight (Kg):1,906
+Weight (Kg):640
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -4655,7 +4655,7 @@
       <c r="B267" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 3.00 x 1500.0 x 3000.0 mm
-Weight (Kg):640
+Weight (Kg):1,496
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -4666,12 +4666,12 @@
     <row r="268" xml:space="preserve">
       <c r="A268" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
-3.00 x 1500.0 x 3000.0 mm</v>
+4.00 x 1000.0 x 2000.0 mm</v>
       </c>
       <c r="B268" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
-3.00 x 1500.0 x 3000.0 mm
-Weight (Kg):1,496
+4.00 x 1000.0 x 2000.0 mm
+Weight (Kg):1,348
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -4682,12 +4682,12 @@
     <row r="269" xml:space="preserve">
       <c r="A269" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
-4.00 x 1000.0 x 2000.0 mm</v>
+4.00 x 1500.0 x 3000.0 mm</v>
       </c>
       <c r="B269" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
-4.00 x 1000.0 x 2000.0 mm
-Weight (Kg):1,348
+4.00 x 1500.0 x 3000.0 mm
+Weight (Kg):1,574
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -4703,7 +4703,7 @@
       <c r="B270" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 4.00 x 1500.0 x 3000.0 mm
-Weight (Kg):1,574
+Weight (Kg):1,861
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -4719,7 +4719,7 @@
       <c r="B271" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 4.00 x 1500.0 x 3000.0 mm
-Weight (Kg):1,861
+Weight (Kg):1,722
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -4735,7 +4735,7 @@
       <c r="B272" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 4.00 x 1500.0 x 3000.0 mm
-Weight (Kg):1,722
+Weight (Kg):1,726
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -4751,7 +4751,7 @@
       <c r="B273" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 4.00 x 1500.0 x 3000.0 mm
-Weight (Kg):1,726
+Weight (Kg):999
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -4767,7 +4767,7 @@
       <c r="B274" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 4.00 x 1500.0 x 3000.0 mm
-Weight (Kg):999
+Weight (Kg):724
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -4783,7 +4783,7 @@
       <c r="B275" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 4.00 x 1500.0 x 3000.0 mm
-Weight (Kg):724
+Weight (Kg):854
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -4799,7 +4799,7 @@
       <c r="B276" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 4.00 x 1500.0 x 3000.0 mm
-Weight (Kg):854
+Weight (Kg):1,987
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -4815,7 +4815,7 @@
       <c r="B277" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 4.00 x 1500.0 x 3000.0 mm
-Weight (Kg):1,987
+Weight (Kg):1,708
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -4831,7 +4831,7 @@
       <c r="B278" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 4.00 x 1500.0 x 3000.0 mm
-Weight (Kg):1,708
+Weight (Kg):1,562
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -4842,12 +4842,12 @@
     <row r="279" xml:space="preserve">
       <c r="A279" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
-4.00 x 1500.0 x 3000.0 mm</v>
+5.00 x 1250.0 x 2500.0 mm</v>
       </c>
       <c r="B279" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
-4.00 x 1500.0 x 3000.0 mm
-Weight (Kg):1,562
+5.00 x 1250.0 x 2500.0 mm
+Weight (Kg):2,220
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -4863,7 +4863,7 @@
       <c r="B280" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 5.00 x 1250.0 x 2500.0 mm
-Weight (Kg):2,220
+Weight (Kg):1,580
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -4879,7 +4879,7 @@
       <c r="B281" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 5.00 x 1250.0 x 2500.0 mm
-Weight (Kg):1,580
+Weight (Kg):750
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -4890,12 +4890,12 @@
     <row r="282" xml:space="preserve">
       <c r="A282" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
-5.00 x 1250.0 x 2500.0 mm</v>
+5.00 x 1500.0 x 3000.0 mm</v>
       </c>
       <c r="B282" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
-5.00 x 1250.0 x 2500.0 mm
-Weight (Kg):750
+5.00 x 1500.0 x 3000.0 mm
+Weight (Kg):1,777
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -4911,7 +4911,7 @@
       <c r="B283" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 5.00 x 1500.0 x 3000.0 mm
-Weight (Kg):1,777
+Weight (Kg):1,436
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -4927,7 +4927,7 @@
       <c r="B284" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 5.00 x 1500.0 x 3000.0 mm
-Weight (Kg):1,436
+Weight (Kg):890
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -4943,7 +4943,7 @@
       <c r="B285" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 5.00 x 1500.0 x 3000.0 mm
-Weight (Kg):890
+Weight (Kg):1,252
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -4959,7 +4959,7 @@
       <c r="B286" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 5.00 x 1500.0 x 3000.0 mm
-Weight (Kg):1,252
+Weight (Kg):1,646
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -4975,7 +4975,7 @@
       <c r="B287" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 5.00 x 1500.0 x 3000.0 mm
-Weight (Kg):1,646
+Weight (Kg):1,434
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -4991,7 +4991,7 @@
       <c r="B288" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 5.00 x 1500.0 x 3000.0 mm
-Weight (Kg):1,434
+Weight (Kg):1,778
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -5007,7 +5007,7 @@
       <c r="B289" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 5.00 x 1500.0 x 3000.0 mm
-Weight (Kg):1,778
+Weight (Kg):1,818
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -5023,7 +5023,7 @@
       <c r="B290" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 5.00 x 1500.0 x 3000.0 mm
-Weight (Kg):1,818
+Weight (Kg):1,807
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -5039,7 +5039,7 @@
       <c r="B291" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 5.00 x 1500.0 x 3000.0 mm
-Weight (Kg):1,807
+Weight (Kg):1,978
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -5055,7 +5055,7 @@
       <c r="B292" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 5.00 x 1500.0 x 3000.0 mm
-Weight (Kg):1,978
+Weight (Kg):1,760
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -5071,7 +5071,7 @@
       <c r="B293" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 5.00 x 1500.0 x 3000.0 mm
-Weight (Kg):1,760
+Weight (Kg):1,976
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -5087,7 +5087,7 @@
       <c r="B294" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 5.00 x 1500.0 x 3000.0 mm
-Weight (Kg):1,976
+Weight (Kg):1,236
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -5103,7 +5103,7 @@
       <c r="B295" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 5.00 x 1500.0 x 3000.0 mm
-Weight (Kg):1,236
+Weight (Kg):1,968
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -5119,7 +5119,7 @@
       <c r="B296" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 5.00 x 1500.0 x 3000.0 mm
-Weight (Kg):1,968
+Weight (Kg):1,240
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -5135,7 +5135,7 @@
       <c r="B297" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 5.00 x 1500.0 x 3000.0 mm
-Weight (Kg):1,240
+Weight (Kg):1,070
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -5151,7 +5151,7 @@
       <c r="B298" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 5.00 x 1500.0 x 3000.0 mm
-Weight (Kg):1,070
+Weight (Kg):1,960
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -5167,7 +5167,7 @@
       <c r="B299" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 5.00 x 1500.0 x 3000.0 mm
-Weight (Kg):1,960
+Weight (Kg):1,734
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -5183,7 +5183,7 @@
       <c r="B300" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 5.00 x 1500.0 x 3000.0 mm
-Weight (Kg):1,734
+Weight (Kg):1,874
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -5199,7 +5199,7 @@
       <c r="B301" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 5.00 x 1500.0 x 3000.0 mm
-Weight (Kg):1,874
+Weight (Kg):884
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -5215,7 +5215,7 @@
       <c r="B302" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 5.00 x 1500.0 x 3000.0 mm
-Weight (Kg):884
+Weight (Kg):1,578
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -5231,7 +5231,7 @@
       <c r="B303" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 5.00 x 1500.0 x 3000.0 mm
-Weight (Kg):1,578
+Weight (Kg):852
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -5247,7 +5247,7 @@
       <c r="B304" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 5.00 x 1500.0 x 3000.0 mm
-Weight (Kg):852
+Weight (Kg):1,942
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -5258,12 +5258,12 @@
     <row r="305" xml:space="preserve">
       <c r="A305" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
-5.00 x 1500.0 x 3000.0 mm</v>
+6.00 x 1000.0 x 2000.0 mm</v>
       </c>
       <c r="B305" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
-5.00 x 1500.0 x 3000.0 mm
-Weight (Kg):1,942
+6.00 x 1000.0 x 2000.0 mm
+Weight (Kg):1,906
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -5279,7 +5279,7 @@
       <c r="B306" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 6.00 x 1000.0 x 2000.0 mm
-Weight (Kg):1,906
+Weight (Kg):1,886
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -5295,7 +5295,7 @@
       <c r="B307" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 6.00 x 1000.0 x 2000.0 mm
-Weight (Kg):1,886
+Weight (Kg):1,414
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -5311,7 +5311,7 @@
       <c r="B308" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 6.00 x 1000.0 x 2000.0 mm
-Weight (Kg):1,414
+Weight (Kg):1,620
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -5327,7 +5327,7 @@
       <c r="B309" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 6.00 x 1000.0 x 2000.0 mm
-Weight (Kg):1,620
+Weight (Kg):938
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -5343,7 +5343,7 @@
       <c r="B310" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 6.00 x 1000.0 x 2000.0 mm
-Weight (Kg):938
+Weight (Kg):1,406
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -5359,7 +5359,7 @@
       <c r="B311" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 6.00 x 1000.0 x 2000.0 mm
-Weight (Kg):1,406
+Weight (Kg):1,140
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -5370,12 +5370,12 @@
     <row r="312" xml:space="preserve">
       <c r="A312" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
-6.00 x 1000.0 x 2000.0 mm</v>
+6.00 x 1250.0 x 2500.0 mm</v>
       </c>
       <c r="B312" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
-6.00 x 1000.0 x 2000.0 mm
-Weight (Kg):1,140
+6.00 x 1250.0 x 2500.0 mm
+Weight (Kg):1,494
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -5391,7 +5391,7 @@
       <c r="B313" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 6.00 x 1250.0 x 2500.0 mm
-Weight (Kg):1,494
+Weight (Kg):1,652
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -5407,7 +5407,7 @@
       <c r="B314" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 6.00 x 1250.0 x 2500.0 mm
-Weight (Kg):1,652
+Weight (Kg):1,610
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -5423,7 +5423,7 @@
       <c r="B315" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 6.00 x 1250.0 x 2500.0 mm
-Weight (Kg):1,610
+Weight (Kg):1,900
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -5439,7 +5439,7 @@
       <c r="B316" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 6.00 x 1250.0 x 2500.0 mm
-Weight (Kg):1,900
+Weight (Kg):2,346
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -5455,7 +5455,7 @@
       <c r="B317" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 6.00 x 1250.0 x 2500.0 mm
-Weight (Kg):2,346
+Weight (Kg):1,624
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -5466,12 +5466,12 @@
     <row r="318" xml:space="preserve">
       <c r="A318" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
-6.00 x 1250.0 x 2500.0 mm</v>
+6.00 x 1500.0 x 3000.0 mm</v>
       </c>
       <c r="B318" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
-6.00 x 1250.0 x 2500.0 mm
-Weight (Kg):1,624
+6.00 x 1500.0 x 3000.0 mm
+Weight (Kg):1,296
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -5487,7 +5487,7 @@
       <c r="B319" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 6.00 x 1500.0 x 3000.0 mm
-Weight (Kg):1,296
+Weight (Kg):1,716
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -5503,7 +5503,7 @@
       <c r="B320" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 6.00 x 1500.0 x 3000.0 mm
-Weight (Kg):1,716
+Weight (Kg):1,917
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -5519,7 +5519,7 @@
       <c r="B321" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 6.00 x 1500.0 x 3000.0 mm
-Weight (Kg):1,917
+Weight (Kg):1,922
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -5535,7 +5535,7 @@
       <c r="B322" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 6.00 x 1500.0 x 3000.0 mm
-Weight (Kg):1,922
+Weight (Kg):1,728
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -5551,7 +5551,7 @@
       <c r="B323" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 6.00 x 1500.0 x 3000.0 mm
-Weight (Kg):1,728
+Weight (Kg):864
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -5567,7 +5567,7 @@
       <c r="B324" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 6.00 x 1500.0 x 3000.0 mm
-Weight (Kg):864
+Weight (Kg):1,302
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -5583,7 +5583,7 @@
       <c r="B325" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 6.00 x 1500.0 x 3000.0 mm
-Weight (Kg):1,302
+Weight (Kg):1,062
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -5599,7 +5599,7 @@
       <c r="B326" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 6.00 x 1500.0 x 3000.0 mm
-Weight (Kg):1,062
+Weight (Kg):1,966
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -5615,7 +5615,7 @@
       <c r="B327" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 6.00 x 1500.0 x 3000.0 mm
-Weight (Kg):1,966
+Weight (Kg):1,496
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -5631,7 +5631,7 @@
       <c r="B328" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 6.00 x 1500.0 x 3000.0 mm
-Weight (Kg):1,496
+Weight (Kg):1,320
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -5647,7 +5647,7 @@
       <c r="B329" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 6.00 x 1500.0 x 3000.0 mm
-Weight (Kg):1,320
+Weight (Kg):1,071
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -5663,7 +5663,7 @@
       <c r="B330" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 6.00 x 1500.0 x 3000.0 mm
-Weight (Kg):1,071
+Weight (Kg):1,264
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -5679,7 +5679,7 @@
       <c r="B331" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 6.00 x 1500.0 x 3000.0 mm
-Weight (Kg):1,264
+Weight (Kg):1,916
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -5695,7 +5695,7 @@
       <c r="B332" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 6.00 x 1500.0 x 3000.0 mm
-Weight (Kg):1,916
+Weight (Kg):1,908
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -5711,7 +5711,7 @@
       <c r="B333" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 6.00 x 1500.0 x 3000.0 mm
-Weight (Kg):1,908
+Weight (Kg):1,928
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -5727,7 +5727,7 @@
       <c r="B334" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 6.00 x 1500.0 x 3000.0 mm
-Weight (Kg):1,928
+Weight (Kg):1,290
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -5743,7 +5743,7 @@
       <c r="B335" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 6.00 x 1500.0 x 3000.0 mm
-Weight (Kg):1,290
+Weight (Kg):1,698
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -5759,7 +5759,7 @@
       <c r="B336" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 6.00 x 1500.0 x 3000.0 mm
-Weight (Kg):1,698
+Weight (Kg):1,754
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -5775,7 +5775,7 @@
       <c r="B337" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 6.00 x 1500.0 x 3000.0 mm
-Weight (Kg):1,754
+Weight (Kg):1,716
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -5791,7 +5791,7 @@
       <c r="B338" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 6.00 x 1500.0 x 3000.0 mm
-Weight (Kg):1,716
+Weight (Kg):1,548
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -5807,7 +5807,7 @@
       <c r="B339" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 6.00 x 1500.0 x 3000.0 mm
-Weight (Kg):1,548
+Weight (Kg):1,916
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -5823,7 +5823,7 @@
       <c r="B340" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 6.00 x 1500.0 x 3000.0 mm
-Weight (Kg):1,916
+Weight (Kg):1,485
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -5839,7 +5839,7 @@
       <c r="B341" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 6.00 x 1500.0 x 3000.0 mm
-Weight (Kg):1,485
+Weight (Kg):1,940
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -5855,7 +5855,7 @@
       <c r="B342" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 6.00 x 1500.0 x 3000.0 mm
-Weight (Kg):1,940
+Weight (Kg):1,762
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -5871,7 +5871,7 @@
       <c r="B343" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 6.00 x 1500.0 x 3000.0 mm
-Weight (Kg):1,762
+Weight (Kg):1,918
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -5887,7 +5887,7 @@
       <c r="B344" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 6.00 x 1500.0 x 3000.0 mm
-Weight (Kg):1,918
+Weight (Kg):1,306
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -5903,7 +5903,7 @@
       <c r="B345" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 6.00 x 1500.0 x 3000.0 mm
-Weight (Kg):1,306
+Weight (Kg):1,066
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -5919,7 +5919,7 @@
       <c r="B346" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 6.00 x 1500.0 x 3000.0 mm
-Weight (Kg):1,066
+Weight (Kg):1,936
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -5935,7 +5935,7 @@
       <c r="B347" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 6.00 x 1500.0 x 3000.0 mm
-Weight (Kg):1,936
+Weight (Kg):2,390
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -5951,7 +5951,7 @@
       <c r="B348" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 6.00 x 1500.0 x 3000.0 mm
-Weight (Kg):2,390
+Weight (Kg):1,728
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -5967,7 +5967,7 @@
       <c r="B349" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 6.00 x 1500.0 x 3000.0 mm
-Weight (Kg):1,728
+Weight (Kg):1,514
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -5983,7 +5983,7 @@
       <c r="B350" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 6.00 x 1500.0 x 3000.0 mm
-Weight (Kg):1,514
+Weight (Kg):1,922
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -5999,7 +5999,7 @@
       <c r="B351" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 6.00 x 1500.0 x 3000.0 mm
-Weight (Kg):1,922
+Weight (Kg):1,942
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -6015,7 +6015,7 @@
       <c r="B352" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 6.00 x 1500.0 x 3000.0 mm
-Weight (Kg):1,942
+Weight (Kg):2,114
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -6031,7 +6031,7 @@
       <c r="B353" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 6.00 x 1500.0 x 3000.0 mm
-Weight (Kg):2,114
+Weight (Kg):1,088
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -6047,7 +6047,7 @@
       <c r="B354" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 6.00 x 1500.0 x 3000.0 mm
-Weight (Kg):1,088
+Weight (Kg):1,274
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -6063,7 +6063,7 @@
       <c r="B355" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 6.00 x 1500.0 x 3000.0 mm
-Weight (Kg):1,274
+Weight (Kg):1,718
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -6079,7 +6079,7 @@
       <c r="B356" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 6.00 x 1500.0 x 3000.0 mm
-Weight (Kg):1,718
+Weight (Kg):1,922
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -6095,7 +6095,7 @@
       <c r="B357" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 6.00 x 1500.0 x 3000.0 mm
-Weight (Kg):1,922
+Weight (Kg):1,878
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -6111,7 +6111,7 @@
       <c r="B358" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 6.00 x 1500.0 x 3000.0 mm
-Weight (Kg):1,878
+Weight (Kg):1,714
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -6127,7 +6127,7 @@
       <c r="B359" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 6.00 x 1500.0 x 3000.0 mm
-Weight (Kg):1,714
+Weight (Kg):1,918
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -6143,7 +6143,7 @@
       <c r="B360" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 6.00 x 1500.0 x 3000.0 mm
-Weight (Kg):1,918
+Weight (Kg):1,754
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -6159,7 +6159,7 @@
       <c r="B361" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 6.00 x 1500.0 x 3000.0 mm
-Weight (Kg):1,754
+Weight (Kg):1,528
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -6175,7 +6175,7 @@
       <c r="B362" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 6.00 x 1500.0 x 3000.0 mm
-Weight (Kg):1,528
+Weight (Kg):2,136
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -6191,7 +6191,7 @@
       <c r="B363" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 6.00 x 1500.0 x 3000.0 mm
-Weight (Kg):2,136
+Weight (Kg):1,946
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -6201,13 +6201,13 @@
     </row>
     <row r="364" xml:space="preserve">
       <c r="A364" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
-6.00 x 1500.0 x 3000.0 mm</v>
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, BA,
+0.80 x 1000.0 x 2000.0 mm</v>
       </c>
       <c r="B364" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
-6.00 x 1500.0 x 3000.0 mm
-Weight (Kg):1,946
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, BA,
+0.80 x 1000.0 x 2000.0 mm
+Weight (Kg):1,633
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -6223,7 +6223,7 @@
       <c r="B365" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, BA,
 0.80 x 1000.0 x 2000.0 mm
-Weight (Kg):1,633
+Weight (Kg):1,286
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -6239,7 +6239,7 @@
       <c r="B366" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, BA,
 0.80 x 1000.0 x 2000.0 mm
-Weight (Kg):1,286
+Weight (Kg):727
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -6250,12 +6250,12 @@
     <row r="367" xml:space="preserve">
       <c r="A367" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, BA,
-0.80 x 1000.0 x 2000.0 mm</v>
+1.00 x 1000.0 x 2000.0 mm</v>
       </c>
       <c r="B367" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, BA,
-0.80 x 1000.0 x 2000.0 mm
-Weight (Kg):727
+1.00 x 1000.0 x 2000.0 mm
+Weight (Kg):650
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -6271,7 +6271,7 @@
       <c r="B368" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, BA,
 1.00 x 1000.0 x 2000.0 mm
-Weight (Kg):650
+Weight (Kg):869
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -6287,7 +6287,7 @@
       <c r="B369" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, BA,
 1.00 x 1000.0 x 2000.0 mm
-Weight (Kg):869
+Weight (Kg):885
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -6303,7 +6303,7 @@
       <c r="B370" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, BA,
 1.00 x 1000.0 x 2000.0 mm
-Weight (Kg):885
+Weight (Kg):931
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -6314,12 +6314,12 @@
     <row r="371" xml:space="preserve">
       <c r="A371" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, BA,
-1.00 x 1000.0 x 2000.0 mm</v>
+1.00 x 1250.0 x 3000.0 mm</v>
       </c>
       <c r="B371" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, BA,
-1.00 x 1000.0 x 2000.0 mm
-Weight (Kg):931
+1.00 x 1250.0 x 3000.0 mm
+Weight (Kg):766
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -6335,7 +6335,7 @@
       <c r="B372" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, BA,
 1.00 x 1250.0 x 3000.0 mm
-Weight (Kg):766
+Weight (Kg):1,417
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -6346,12 +6346,12 @@
     <row r="373" xml:space="preserve">
       <c r="A373" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, BA,
-1.00 x 1250.0 x 3000.0 mm</v>
+1.50 x 1000.0 x 2000.0 mm</v>
       </c>
       <c r="B373" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, BA,
-1.00 x 1250.0 x 3000.0 mm
-Weight (Kg):1,417
+1.50 x 1000.0 x 2000.0 mm
+Weight (Kg):1,459
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -6367,7 +6367,7 @@
       <c r="B374" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, BA,
 1.50 x 1000.0 x 2000.0 mm
-Weight (Kg):1,459
+Weight (Kg):825
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -6383,7 +6383,7 @@
       <c r="B375" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, BA,
 1.50 x 1000.0 x 2000.0 mm
-Weight (Kg):825
+Weight (Kg):738
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -6399,7 +6399,7 @@
       <c r="B376" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, BA,
 1.50 x 1000.0 x 2000.0 mm
-Weight (Kg):738
+Weight (Kg):886
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -6415,7 +6415,7 @@
       <c r="B377" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, BA,
 1.50 x 1000.0 x 2000.0 mm
-Weight (Kg):886
+Weight (Kg):1,116
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -6431,7 +6431,7 @@
       <c r="B378" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, BA,
 1.50 x 1000.0 x 2000.0 mm
-Weight (Kg):1,116
+Weight (Kg):692
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -6447,7 +6447,7 @@
       <c r="B379" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, BA,
 1.50 x 1000.0 x 2000.0 mm
-Weight (Kg):692
+Weight (Kg):1,613
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -6463,7 +6463,7 @@
       <c r="B380" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, BA,
 1.50 x 1000.0 x 2000.0 mm
-Weight (Kg):1,613
+Weight (Kg):946
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -6474,12 +6474,12 @@
     <row r="381" xml:space="preserve">
       <c r="A381" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, BA,
-1.50 x 1000.0 x 2000.0 mm</v>
+1.50 x 1250.0 x 2500.0 mm</v>
       </c>
       <c r="B381" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, BA,
-1.50 x 1000.0 x 2000.0 mm
-Weight (Kg):946
+1.50 x 1250.0 x 2500.0 mm
+Weight (Kg):1,628
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -6490,25 +6490,9 @@
     <row r="382" xml:space="preserve">
       <c r="A382" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, BA,
-1.50 x 1250.0 x 2500.0 mm</v>
+1.80 x 1000.0 x 2000.0 mm</v>
       </c>
       <c r="B382" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, BA,
-1.50 x 1250.0 x 2500.0 mm
-Weight (Kg):1,628
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-2,225.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="383" xml:space="preserve">
-      <c r="A383" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, BA,
-1.80 x 1000.0 x 2000.0 mm</v>
-      </c>
-      <c r="B383" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, BA,
 1.80 x 1000.0 x 2000.0 mm
 Weight (Kg):1,405
@@ -6519,12 +6503,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="384" xml:space="preserve">
-      <c r="A384" t="str" xml:space="preserve">
+    <row r="383" xml:space="preserve">
+      <c r="A383" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, Nb. 1,
 3.00 x 1500.0 x 3000.0 mm</v>
       </c>
-      <c r="B384" t="str" xml:space="preserve">
+      <c r="B383" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, Nb. 1,
 3.00 x 1500.0 x 3000.0 mm
 Weight (Kg):1,728
@@ -6532,6 +6516,22 @@
 Help
 Location:FABRICA ALGECIRAS
 2,125.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="384" xml:space="preserve">
+      <c r="A384" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, Nb. 3 Chequered,
+4.50 x 1250.0 x 3000.0 mm</v>
+      </c>
+      <c r="B384" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, Nb. 3 Chequered,
+4.50 x 1250.0 x 3000.0 mm
+Weight (Kg):1,046
+Quality:Prime
+Help
+Location:FABRICA ALGECIRAS
+2,900.00 €/ton
 Add to cart</v>
       </c>
     </row>
@@ -6543,7 +6543,7 @@
       <c r="B385" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, Nb. 3 Chequered,
 4.50 x 1250.0 x 3000.0 mm
-Weight (Kg):1,046
+Weight (Kg):1,316
 Quality:Prime
 Help
 Location:FABRICA ALGECIRAS
@@ -6553,29 +6553,29 @@
     </row>
     <row r="386" xml:space="preserve">
       <c r="A386" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, Nb. 3 Chequered,
-4.50 x 1250.0 x 3000.0 mm</v>
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, Polished N4-G-240,
+0.80 x 1500.0 x 3000.0 mm</v>
       </c>
       <c r="B386" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, Nb. 3 Chequered,
-4.50 x 1250.0 x 3000.0 mm
-Weight (Kg):1,316
-Quality:Prime
-Help
-Location:FABRICA ALGECIRAS
-2,900.00 €/ton
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, Polished N4-G-240,
+0.80 x 1500.0 x 3000.0 mm
+Weight (Kg):630
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,225.00 €/ton
 Add to cart</v>
       </c>
     </row>
     <row r="387" xml:space="preserve">
       <c r="A387" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, Polished N4-G-240,
-0.80 x 1500.0 x 3000.0 mm</v>
+0.90 x 1500.0 x 3000.0 mm</v>
       </c>
       <c r="B387" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, Polished N4-G-240,
-0.80 x 1500.0 x 3000.0 mm
-Weight (Kg):630
+0.90 x 1500.0 x 3000.0 mm
+Weight (Kg):807
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -6591,7 +6591,7 @@
       <c r="B388" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, Polished N4-G-240,
 0.90 x 1500.0 x 3000.0 mm
-Weight (Kg):807
+Weight (Kg):622
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -6601,13 +6601,13 @@
     </row>
     <row r="389" xml:space="preserve">
       <c r="A389" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, Polished N4-G-240,
-0.90 x 1500.0 x 3000.0 mm</v>
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, SB-G-400,
+1.50 x 1000.0 x 2000.0 mm</v>
       </c>
       <c r="B389" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, Polished N4-G-240,
-0.90 x 1500.0 x 3000.0 mm
-Weight (Kg):622
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, SB-G-400,
+1.50 x 1000.0 x 2000.0 mm
+Weight (Kg):674
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -6623,7 +6623,7 @@
       <c r="B390" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, SB-G-400,
 1.50 x 1000.0 x 2000.0 mm
-Weight (Kg):674
+Weight (Kg):535
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -6634,12 +6634,12 @@
     <row r="391" xml:space="preserve">
       <c r="A391" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, SB-G-400,
-1.50 x 1000.0 x 2000.0 mm</v>
+3.00 x 1500.0 x 3000.0 mm</v>
       </c>
       <c r="B391" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, SB-G-400,
-1.50 x 1000.0 x 2000.0 mm
-Weight (Kg):535
+3.00 x 1500.0 x 3000.0 mm
+Weight (Kg):1,877
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -6655,7 +6655,7 @@
       <c r="B392" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, SB-G-400,
 3.00 x 1500.0 x 3000.0 mm
-Weight (Kg):1,877
+Weight (Kg):629
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -6671,7 +6671,7 @@
       <c r="B393" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, SB-G-400,
 3.00 x 1500.0 x 3000.0 mm
-Weight (Kg):629
+Weight (Kg):1,887
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -6681,13 +6681,13 @@
     </row>
     <row r="394" xml:space="preserve">
       <c r="A394" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, SB-G-400,
-3.00 x 1500.0 x 3000.0 mm</v>
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, SB-G-500,
+0.70 x 1500.0 x 3000.0 mm</v>
       </c>
       <c r="B394" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, SB-G-400,
-3.00 x 1500.0 x 3000.0 mm
-Weight (Kg):1,887
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, SB-G-500,
+0.70 x 1500.0 x 3000.0 mm
+Weight (Kg):1,226
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -6703,7 +6703,7 @@
       <c r="B395" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, SB-G-500,
 0.70 x 1500.0 x 3000.0 mm
-Weight (Kg):1,226
+Weight (Kg):1,001
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -6719,7 +6719,7 @@
       <c r="B396" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, SB-G-500,
 0.70 x 1500.0 x 3000.0 mm
-Weight (Kg):1,001
+Weight (Kg):681
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -6735,7 +6735,7 @@
       <c r="B397" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, SB-G-500,
 0.70 x 1500.0 x 3000.0 mm
-Weight (Kg):681
+Weight (Kg):673
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -6751,7 +6751,7 @@
       <c r="B398" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, SB-G-500,
 0.70 x 1500.0 x 3000.0 mm
-Weight (Kg):673
+Weight (Kg):722
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -6762,12 +6762,12 @@
     <row r="399" xml:space="preserve">
       <c r="A399" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, SB-G-500,
-0.70 x 1500.0 x 3000.0 mm</v>
+0.80 x 1000.0 x 2000.0 mm</v>
       </c>
       <c r="B399" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, SB-G-500,
-0.70 x 1500.0 x 3000.0 mm
-Weight (Kg):722
+0.80 x 1000.0 x 2000.0 mm
+Weight (Kg):1,256
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -6778,12 +6778,12 @@
     <row r="400" xml:space="preserve">
       <c r="A400" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, SB-G-500,
-0.80 x 1000.0 x 2000.0 mm</v>
+0.80 x 1250.0 x 3000.0 mm</v>
       </c>
       <c r="B400" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, SB-G-500,
-0.80 x 1000.0 x 2000.0 mm
-Weight (Kg):1,256
+0.80 x 1250.0 x 3000.0 mm
+Weight (Kg):535
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -6810,25 +6810,9 @@
     <row r="402" xml:space="preserve">
       <c r="A402" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, SB-G-500,
-0.80 x 1250.0 x 3000.0 mm</v>
+3.00 x 1500.0 x 3000.0 mm</v>
       </c>
       <c r="B402" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, SB-G-500,
-0.80 x 1250.0 x 3000.0 mm
-Weight (Kg):535
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-2,225.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="403" xml:space="preserve">
-      <c r="A403" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, SB-G-500,
-3.00 x 1500.0 x 3000.0 mm</v>
-      </c>
-      <c r="B403" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, SB-G-500,
 3.00 x 1500.0 x 3000.0 mm
 Weight (Kg):839
@@ -6839,12 +6823,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="404" xml:space="preserve">
-      <c r="A404" t="str" xml:space="preserve">
+    <row r="403" xml:space="preserve">
+      <c r="A403" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Untrimmed, Coil,
 0.80 x 1271.0 x coil mm</v>
       </c>
-      <c r="B404" t="str" xml:space="preserve">
+      <c r="B403" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Untrimmed, Coil,
 0.80 x 1271.0 x coil mm
 Weight (Kg):2,950
@@ -6855,15 +6839,31 @@
 Add to cart</v>
       </c>
     </row>
+    <row r="404" xml:space="preserve">
+      <c r="A404" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Untrimmed, Coil, 2B,
+1.20 x 1277.0 x coil mm</v>
+      </c>
+      <c r="B404" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Untrimmed, Coil, 2B,
+1.20 x 1277.0 x coil mm
+Weight (Kg):2,230
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,225.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
     <row r="405" xml:space="preserve">
       <c r="A405" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Untrimmed, Coil, 2B,
-1.20 x 1277.0 x coil mm</v>
+2.00 x 1275.0 x coil mm</v>
       </c>
       <c r="B405" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Untrimmed, Coil, 2B,
-1.20 x 1277.0 x coil mm
-Weight (Kg):2,230
+2.00 x 1275.0 x coil mm
+Weight (Kg):2,619
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -6874,12 +6874,12 @@
     <row r="406" xml:space="preserve">
       <c r="A406" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Untrimmed, Coil, 2B,
-2.00 x 1275.0 x coil mm</v>
+5.00 x 1540.0 x coil mm</v>
       </c>
       <c r="B406" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Untrimmed, Coil, 2B,
-2.00 x 1275.0 x coil mm
-Weight (Kg):2,619
+5.00 x 1540.0 x coil mm
+Weight (Kg):7,140
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -6895,7 +6895,7 @@
       <c r="B407" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Untrimmed, Coil, 2B,
 5.00 x 1540.0 x coil mm
-Weight (Kg):7,140
+Weight (Kg):13,250
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -6905,26 +6905,10 @@
     </row>
     <row r="408" xml:space="preserve">
       <c r="A408" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Untrimmed, Coil, 2B,
-5.00 x 1540.0 x coil mm</v>
-      </c>
-      <c r="B408" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Untrimmed, Coil, 2B,
-5.00 x 1540.0 x coil mm
-Weight (Kg):13,250
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-2,225.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="409" xml:space="preserve">
-      <c r="A409" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Untrimmed, Coil, 2D,
 1.00 x 1027.0 x coil mm</v>
       </c>
-      <c r="B409" t="str" xml:space="preserve">
+      <c r="B408" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Untrimmed, Coil, 2D,
 1.00 x 1027.0 x coil mm
 Weight (Kg):2,410
@@ -6935,44 +6919,44 @@
 Add to cart</v>
       </c>
     </row>
+    <row r="409" xml:space="preserve">
+      <c r="A409" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Untrimmed, Coil, BA,
+0.40 x 1017.0 x coil mm</v>
+      </c>
+      <c r="B409" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Untrimmed, Coil, BA,
+0.40 x 1017.0 x coil mm
+Weight (Kg):5,705
+Quality:Prime
+Help
+Location:FABRICA ALGECIRAS
+2,425.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
     <row r="410" xml:space="preserve">
       <c r="A410" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Untrimmed, Coil, BA,
-0.40 x 1017.0 x coil mm</v>
+0.90 x 1275.0 x coil mm</v>
       </c>
       <c r="B410" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Untrimmed, Coil, BA,
-0.40 x 1017.0 x coil mm
-Weight (Kg):5,705
-Quality:Prime
-Help
-Location:FABRICA ALGECIRAS
-2,425.00 €/ton
+0.90 x 1275.0 x coil mm
+Weight (Kg):2,500
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,225.00 €/ton
 Add to cart</v>
       </c>
     </row>
     <row r="411" xml:space="preserve">
       <c r="A411" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Untrimmed, Coil, BA,
-0.90 x 1275.0 x coil mm</v>
+0.90 x 1288.0 x coil mm</v>
       </c>
       <c r="B411" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Untrimmed, Coil, BA,
-0.90 x 1275.0 x coil mm
-Weight (Kg):2,500
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-2,225.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="412" xml:space="preserve">
-      <c r="A412" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Untrimmed, Coil, BA,
-0.90 x 1288.0 x coil mm</v>
-      </c>
-      <c r="B412" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Untrimmed, Coil, BA,
 0.90 x 1288.0 x coil mm
 Weight (Kg):7,960
@@ -6983,12 +6967,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="413" xml:space="preserve">
-      <c r="A413" t="str" xml:space="preserve">
+    <row r="412" xml:space="preserve">
+      <c r="A412" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Untrimmed, Coil, SB-G-400,
 1.20 x 1500.0 x coil mm</v>
       </c>
-      <c r="B413" t="str" xml:space="preserve">
+      <c r="B412" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Untrimmed, Coil, SB-G-400,
 1.20 x 1500.0 x coil mm
 Weight (Kg):2,640
@@ -6999,32 +6983,48 @@
 Add to cart</v>
       </c>
     </row>
+    <row r="413" xml:space="preserve">
+      <c r="A413" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Coil, 2B,
+1.20 x 1536.0 x coil mm</v>
+      </c>
+      <c r="B413" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Coil, 2B,
+1.20 x 1536.0 x coil mm
+Weight (Kg):1,260
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+3,395.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
     <row r="414" xml:space="preserve">
       <c r="A414" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Coil, 2B,
-1.20 x 1536.0 x coil mm</v>
+1.50 x 140.0 x coil mm</v>
       </c>
       <c r="B414" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Coil, 2B,
-1.20 x 1536.0 x coil mm
-Weight (Kg):1,260
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-3,395.00 €/ton
+1.50 x 140.0 x coil mm
+Weight (Kg):758
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+3,270.00 €/ton
 Add to cart</v>
       </c>
     </row>
     <row r="415" xml:space="preserve">
       <c r="A415" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Coil, 2B,
-1.50 x 140.0 x coil mm</v>
+1.50 x 160.9 x coil mm</v>
       </c>
       <c r="B415" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Coil, 2B,
-1.50 x 140.0 x coil mm
-Weight (Kg):758
-Quality:Prime-2
+1.50 x 160.9 x coil mm
+Weight (Kg):848
+Quality:Prime
 Help
 Location:FABRICA ALGECIRAS
 3,270.00 €/ton
@@ -7034,13 +7034,13 @@
     <row r="416" xml:space="preserve">
       <c r="A416" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Coil, 2B,
-1.50 x 160.9 x coil mm</v>
+1.50 x 230.9 x coil mm</v>
       </c>
       <c r="B416" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Coil, 2B,
-1.50 x 160.9 x coil mm
-Weight (Kg):848
-Quality:Prime
+1.50 x 230.9 x coil mm
+Weight (Kg):1,044
+Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
 3,270.00 €/ton
@@ -7050,48 +7050,48 @@
     <row r="417" xml:space="preserve">
       <c r="A417" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Coil, 2B,
-1.50 x 230.9 x coil mm</v>
+2.00 x 1498.0 x coil mm</v>
       </c>
       <c r="B417" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Coil, 2B,
-1.50 x 230.9 x coil mm
-Weight (Kg):1,044
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-3,270.00 €/ton
+2.00 x 1498.0 x coil mm
+Weight (Kg):2,770
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+3,395.00 €/ton
 Add to cart</v>
       </c>
     </row>
     <row r="418" xml:space="preserve">
       <c r="A418" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Coil, 2B,
-2.00 x 1498.0 x coil mm</v>
+5.00 x 1250.0 x coil mm</v>
       </c>
       <c r="B418" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Coil, 2B,
-2.00 x 1498.0 x coil mm
-Weight (Kg):2,770
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-3,395.00 €/ton
+5.00 x 1250.0 x coil mm
+Weight (Kg):12,055
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+3,375.00 €/ton
 Add to cart</v>
       </c>
     </row>
     <row r="419" xml:space="preserve">
       <c r="A419" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Coil, 2B,
-5.00 x 1250.0 x coil mm</v>
+5.00 x 240.0 x coil mm</v>
       </c>
       <c r="B419" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Coil, 2B,
-5.00 x 1250.0 x coil mm
-Weight (Kg):12,055
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-3,375.00 €/ton
+5.00 x 240.0 x coil mm
+Weight (Kg):2,314
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+3,270.00 €/ton
 Add to cart</v>
       </c>
     </row>
@@ -7135,7 +7135,7 @@
       <c r="B422" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Coil, 2B,
 5.00 x 240.0 x coil mm
-Weight (Kg):2,314
+Weight (Kg):2,237
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -7146,32 +7146,32 @@
     <row r="423" xml:space="preserve">
       <c r="A423" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Coil, 2B,
-5.00 x 240.0 x coil mm</v>
+6.00 x 1500.0 x coil mm</v>
       </c>
       <c r="B423" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Coil, 2B,
-5.00 x 240.0 x coil mm
-Weight (Kg):2,237
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-3,270.00 €/ton
+6.00 x 1500.0 x coil mm
+Weight (Kg):2,016
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+3,395.00 €/ton
 Add to cart</v>
       </c>
     </row>
     <row r="424" xml:space="preserve">
       <c r="A424" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Coil, 2B,
-6.00 x 1500.0 x coil mm</v>
+6.00 x 250.9 x coil mm</v>
       </c>
       <c r="B424" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Coil, 2B,
-6.00 x 1500.0 x coil mm
-Weight (Kg):2,016
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-3,395.00 €/ton
+6.00 x 250.9 x coil mm
+Weight (Kg):548
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+3,270.00 €/ton
 Add to cart</v>
       </c>
     </row>
@@ -7183,7 +7183,7 @@
       <c r="B425" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Coil, 2B,
 6.00 x 250.9 x coil mm
-Weight (Kg):548
+Weight (Kg):1,880
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -7193,13 +7193,13 @@
     </row>
     <row r="426" xml:space="preserve">
       <c r="A426" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Coil, 2B,
-6.00 x 250.9 x coil mm</v>
+        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Coil, 2D,
+3.30 x 112.0 x coil mm</v>
       </c>
       <c r="B426" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Coil, 2B,
-6.00 x 250.9 x coil mm
-Weight (Kg):1,880
+        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Coil, 2D,
+3.30 x 112.0 x coil mm
+Weight (Kg):1,017
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -7215,8 +7215,8 @@
       <c r="B427" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Coil, 2D,
 3.30 x 112.0 x coil mm
-Weight (Kg):1,017
-Quality:Prime-2
+Weight (Kg):878
+Quality:Prime
 Help
 Location:FABRICA ALGECIRAS
 3,270.00 €/ton
@@ -7226,13 +7226,13 @@
     <row r="428" xml:space="preserve">
       <c r="A428" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Coil, 2D,
-3.30 x 112.0 x coil mm</v>
+3.30 x 449.0 x coil mm</v>
       </c>
       <c r="B428" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Coil, 2D,
-3.30 x 112.0 x coil mm
-Weight (Kg):878
-Quality:Prime
+3.30 x 449.0 x coil mm
+Weight (Kg):1,850
+Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
 3,270.00 €/ton
@@ -7247,7 +7247,7 @@
       <c r="B429" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Coil, 2D,
 3.30 x 449.0 x coil mm
-Weight (Kg):1,850
+Weight (Kg):1,854
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -7257,14 +7257,14 @@
     </row>
     <row r="430" xml:space="preserve">
       <c r="A430" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Coil, 2D,
-3.30 x 449.0 x coil mm</v>
+        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Coil, BA,
+0.40 x 295.9 x coil mm</v>
       </c>
       <c r="B430" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Coil, 2D,
-3.30 x 449.0 x coil mm
-Weight (Kg):1,854
-Quality:Prime-2
+        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Coil, BA,
+0.40 x 295.9 x coil mm
+Weight (Kg):662
+Quality:Prime
 Help
 Location:FABRICA ALGECIRAS
 3,270.00 €/ton
@@ -7279,7 +7279,7 @@
       <c r="B431" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Coil, BA,
 0.40 x 295.9 x coil mm
-Weight (Kg):662
+Weight (Kg):650
 Quality:Prime
 Help
 Location:FABRICA ALGECIRAS
@@ -7290,25 +7290,9 @@
     <row r="432" xml:space="preserve">
       <c r="A432" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Coil, BA,
-0.40 x 295.9 x coil mm</v>
+0.50 x 160.0 x coil mm</v>
       </c>
       <c r="B432" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Coil, BA,
-0.40 x 295.9 x coil mm
-Weight (Kg):650
-Quality:Prime
-Help
-Location:FABRICA ALGECIRAS
-3,270.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="433" xml:space="preserve">
-      <c r="A433" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Coil, BA,
-0.50 x 160.0 x coil mm</v>
-      </c>
-      <c r="B433" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Coil, BA,
 0.50 x 160.0 x coil mm
 Weight (Kg):1,066
@@ -7319,16 +7303,32 @@
 Add to cart</v>
       </c>
     </row>
+    <row r="433" xml:space="preserve">
+      <c r="A433" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Coil, Nb. 1,
+3.70 x 310.0 x coil mm</v>
+      </c>
+      <c r="B433" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Coil, Nb. 1,
+3.70 x 310.0 x coil mm
+Weight (Kg):5,921
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+3,170.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
     <row r="434" xml:space="preserve">
       <c r="A434" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Coil, Nb. 1,
-3.70 x 310.0 x coil mm</v>
+4.10 x 150.0 x coil mm</v>
       </c>
       <c r="B434" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Coil, Nb. 1,
-3.70 x 310.0 x coil mm
-Weight (Kg):5,921
-Quality:Prime-2
+4.10 x 150.0 x coil mm
+Weight (Kg):1,593
+Quality:Prime
 Help
 Location:FABRICA ALGECIRAS
 3,170.00 €/ton
@@ -7343,7 +7343,7 @@
       <c r="B435" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Coil, Nb. 1,
 4.10 x 150.0 x coil mm
-Weight (Kg):1,593
+Weight (Kg):1,438
 Quality:Prime
 Help
 Location:FABRICA ALGECIRAS
@@ -7354,25 +7354,9 @@
     <row r="436" xml:space="preserve">
       <c r="A436" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Coil, Nb. 1,
-4.10 x 150.0 x coil mm</v>
+4.50 x 220.0 x coil mm</v>
       </c>
       <c r="B436" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Coil, Nb. 1,
-4.10 x 150.0 x coil mm
-Weight (Kg):1,438
-Quality:Prime
-Help
-Location:FABRICA ALGECIRAS
-3,170.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="437" xml:space="preserve">
-      <c r="A437" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Coil, Nb. 1,
-4.50 x 220.0 x coil mm</v>
-      </c>
-      <c r="B437" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Coil, Nb. 1,
 4.50 x 220.0 x coil mm
 Weight (Kg):3,869
@@ -7383,12 +7367,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="438" xml:space="preserve">
-      <c r="A438" t="str" xml:space="preserve">
+    <row r="437" xml:space="preserve">
+      <c r="A437" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Coil, SB-G-400,
 1.00 x 250.9 x coil mm</v>
       </c>
-      <c r="B438" t="str" xml:space="preserve">
+      <c r="B437" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Coil, SB-G-400,
 1.00 x 250.9 x coil mm
 Weight (Kg):1,428
@@ -7399,15 +7383,31 @@
 Add to cart</v>
       </c>
     </row>
+    <row r="438" xml:space="preserve">
+      <c r="A438" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
+0.70 x 1250.0 x 2500.0 mm</v>
+      </c>
+      <c r="B438" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
+0.70 x 1250.0 x 2500.0 mm
+Weight (Kg):1,756
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+3,395.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
     <row r="439" xml:space="preserve">
       <c r="A439" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
-0.70 x 1250.0 x 2500.0 mm</v>
+0.80 x 1250.0 x 3000.0 mm</v>
       </c>
       <c r="B439" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
-0.70 x 1250.0 x 2500.0 mm
-Weight (Kg):1,756
+0.80 x 1250.0 x 3000.0 mm
+Weight (Kg):695
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -7418,12 +7418,12 @@
     <row r="440" xml:space="preserve">
       <c r="A440" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
-0.80 x 1250.0 x 3000.0 mm</v>
+0.80 x 1500.0 x 3000.0 mm</v>
       </c>
       <c r="B440" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
-0.80 x 1250.0 x 3000.0 mm
-Weight (Kg):695
+0.80 x 1500.0 x 3000.0 mm
+Weight (Kg):978
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -7439,7 +7439,7 @@
       <c r="B441" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
 0.80 x 1500.0 x 3000.0 mm
-Weight (Kg):978
+Weight (Kg):1,741
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -7455,7 +7455,7 @@
       <c r="B442" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
 0.80 x 1500.0 x 3000.0 mm
-Weight (Kg):1,741
+Weight (Kg):803
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -7471,7 +7471,7 @@
       <c r="B443" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
 0.80 x 1500.0 x 3000.0 mm
-Weight (Kg):803
+Weight (Kg):1,136
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -7482,12 +7482,12 @@
     <row r="444" xml:space="preserve">
       <c r="A444" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
-0.80 x 1500.0 x 3000.0 mm</v>
+0.90 x 1000.0 x 2000.0 mm</v>
       </c>
       <c r="B444" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
-0.80 x 1500.0 x 3000.0 mm
-Weight (Kg):1,136
+0.90 x 1000.0 x 2000.0 mm
+Weight (Kg):576
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -7498,12 +7498,12 @@
     <row r="445" xml:space="preserve">
       <c r="A445" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
-0.90 x 1000.0 x 2000.0 mm</v>
+0.90 x 1500.0 x 3000.0 mm</v>
       </c>
       <c r="B445" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
-0.90 x 1000.0 x 2000.0 mm
-Weight (Kg):576
+0.90 x 1500.0 x 3000.0 mm
+Weight (Kg):553
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -7514,12 +7514,12 @@
     <row r="446" xml:space="preserve">
       <c r="A446" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
-0.90 x 1500.0 x 3000.0 mm</v>
+1.10 x 1500.0 x 3000.0 mm</v>
       </c>
       <c r="B446" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
-0.90 x 1500.0 x 3000.0 mm
-Weight (Kg):553
+1.10 x 1500.0 x 3000.0 mm
+Weight (Kg):1,233
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -7530,12 +7530,12 @@
     <row r="447" xml:space="preserve">
       <c r="A447" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
-1.10 x 1500.0 x 3000.0 mm</v>
+1.20 x 1250.0 x 2500.0 mm</v>
       </c>
       <c r="B447" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
-1.10 x 1500.0 x 3000.0 mm
-Weight (Kg):1,233
+1.20 x 1250.0 x 2500.0 mm
+Weight (Kg):685
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -7546,12 +7546,12 @@
     <row r="448" xml:space="preserve">
       <c r="A448" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
-1.20 x 1250.0 x 2500.0 mm</v>
+1.50 x 1000.0 x 2000.0 mm</v>
       </c>
       <c r="B448" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
-1.20 x 1250.0 x 2500.0 mm
-Weight (Kg):685
+1.50 x 1000.0 x 2000.0 mm
+Weight (Kg):598
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -7562,12 +7562,12 @@
     <row r="449" xml:space="preserve">
       <c r="A449" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
-1.50 x 1000.0 x 2000.0 mm</v>
+1.50 x 1250.0 x 2500.0 mm</v>
       </c>
       <c r="B449" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
-1.50 x 1000.0 x 2000.0 mm
-Weight (Kg):598
+1.50 x 1250.0 x 2500.0 mm
+Weight (Kg):681
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -7578,12 +7578,12 @@
     <row r="450" xml:space="preserve">
       <c r="A450" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
-1.50 x 1250.0 x 2500.0 mm</v>
+2.00 x 1000.0 x 2000.0 mm</v>
       </c>
       <c r="B450" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
-1.50 x 1250.0 x 2500.0 mm
-Weight (Kg):681
+2.00 x 1000.0 x 2000.0 mm
+Weight (Kg):2,359
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -7599,7 +7599,7 @@
       <c r="B451" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
 2.00 x 1000.0 x 2000.0 mm
-Weight (Kg):2,359
+Weight (Kg):529
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -7615,7 +7615,7 @@
       <c r="B452" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
 2.00 x 1000.0 x 2000.0 mm
-Weight (Kg):529
+Weight (Kg):889
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -7631,7 +7631,7 @@
       <c r="B453" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
 2.00 x 1000.0 x 2000.0 mm
-Weight (Kg):889
+Weight (Kg):628
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -7647,7 +7647,7 @@
       <c r="B454" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
 2.00 x 1000.0 x 2000.0 mm
-Weight (Kg):628
+Weight (Kg):1,968
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -7658,12 +7658,12 @@
     <row r="455" xml:space="preserve">
       <c r="A455" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
-2.00 x 1000.0 x 2000.0 mm</v>
+2.00 x 1250.0 x 2500.0 mm</v>
       </c>
       <c r="B455" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
-2.00 x 1000.0 x 2000.0 mm
-Weight (Kg):1,968
+2.00 x 1250.0 x 2500.0 mm
+Weight (Kg):585
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -7674,12 +7674,12 @@
     <row r="456" xml:space="preserve">
       <c r="A456" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
-2.00 x 1250.0 x 2500.0 mm</v>
+2.00 x 1500.0 x 3000.0 mm</v>
       </c>
       <c r="B456" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
-2.00 x 1250.0 x 2500.0 mm
-Weight (Kg):585
+2.00 x 1500.0 x 3000.0 mm
+Weight (Kg):693
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -7695,7 +7695,7 @@
       <c r="B457" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
 2.00 x 1500.0 x 3000.0 mm
-Weight (Kg):693
+Weight (Kg):1,122
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -7711,7 +7711,7 @@
       <c r="B458" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
 2.00 x 1500.0 x 3000.0 mm
-Weight (Kg):1,122
+Weight (Kg):1,108
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -7727,7 +7727,7 @@
       <c r="B459" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
 2.00 x 1500.0 x 3000.0 mm
-Weight (Kg):1,108
+Weight (Kg):1,836
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -7743,7 +7743,7 @@
       <c r="B460" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
 2.00 x 1500.0 x 3000.0 mm
-Weight (Kg):1,836
+Weight (Kg):630
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -7759,7 +7759,7 @@
       <c r="B461" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
 2.00 x 1500.0 x 3000.0 mm
-Weight (Kg):630
+Weight (Kg):726
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -7775,7 +7775,7 @@
       <c r="B462" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
 2.00 x 1500.0 x 3000.0 mm
-Weight (Kg):726
+Weight (Kg):565
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -7791,7 +7791,7 @@
       <c r="B463" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
 2.00 x 1500.0 x 3000.0 mm
-Weight (Kg):565
+Weight (Kg):729
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -7807,7 +7807,7 @@
       <c r="B464" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
 2.00 x 1500.0 x 3000.0 mm
-Weight (Kg):729
+Weight (Kg):792
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -7823,7 +7823,7 @@
       <c r="B465" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
 2.00 x 1500.0 x 3000.0 mm
-Weight (Kg):792
+Weight (Kg):637
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -7839,7 +7839,7 @@
       <c r="B466" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
 2.00 x 1500.0 x 3000.0 mm
-Weight (Kg):637
+Weight (Kg):1,289
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -7850,12 +7850,12 @@
     <row r="467" xml:space="preserve">
       <c r="A467" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
-2.00 x 1500.0 x 3000.0 mm</v>
+2.50 x 1500.0 x 3000.0 mm</v>
       </c>
       <c r="B467" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
-2.00 x 1500.0 x 3000.0 mm
-Weight (Kg):1,289
+2.50 x 1500.0 x 3000.0 mm
+Weight (Kg):1,826
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -7871,7 +7871,7 @@
       <c r="B468" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
 2.50 x 1500.0 x 3000.0 mm
-Weight (Kg):1,826
+Weight (Kg):1,040
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -7887,7 +7887,7 @@
       <c r="B469" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
 2.50 x 1500.0 x 3000.0 mm
-Weight (Kg):1,040
+Weight (Kg):1,328
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -7898,12 +7898,12 @@
     <row r="470" xml:space="preserve">
       <c r="A470" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
-2.50 x 1500.0 x 3000.0 mm</v>
+3.00 x 1000.0 x 2000.0 mm</v>
       </c>
       <c r="B470" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
-2.50 x 1500.0 x 3000.0 mm
-Weight (Kg):1,328
+3.00 x 1000.0 x 2000.0 mm
+Weight (Kg):940
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -7914,12 +7914,12 @@
     <row r="471" xml:space="preserve">
       <c r="A471" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
-3.00 x 1000.0 x 2000.0 mm</v>
+3.00 x 1250.0 x 2500.0 mm</v>
       </c>
       <c r="B471" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
-3.00 x 1000.0 x 2000.0 mm
-Weight (Kg):940
+3.00 x 1250.0 x 2500.0 mm
+Weight (Kg):1,396
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -7935,7 +7935,7 @@
       <c r="B472" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
 3.00 x 1250.0 x 2500.0 mm
-Weight (Kg):1,396
+Weight (Kg):2,318
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -7951,7 +7951,7 @@
       <c r="B473" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
 3.00 x 1250.0 x 2500.0 mm
-Weight (Kg):2,318
+Weight (Kg):1,074
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -7967,7 +7967,7 @@
       <c r="B474" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
 3.00 x 1250.0 x 2500.0 mm
-Weight (Kg):1,074
+Weight (Kg):1,584
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -7983,7 +7983,7 @@
       <c r="B475" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
 3.00 x 1250.0 x 2500.0 mm
-Weight (Kg):1,584
+Weight (Kg):1,028
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -7999,7 +7999,7 @@
       <c r="B476" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
 3.00 x 1250.0 x 2500.0 mm
-Weight (Kg):1,028
+Weight (Kg):598
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -8010,12 +8010,12 @@
     <row r="477" xml:space="preserve">
       <c r="A477" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
-3.00 x 1250.0 x 2500.0 mm</v>
+3.00 x 1340.0 x 2480.0 mm</v>
       </c>
       <c r="B477" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
-3.00 x 1250.0 x 2500.0 mm
-Weight (Kg):598
+3.00 x 1340.0 x 2480.0 mm
+Weight (Kg):1,174
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -8031,7 +8031,7 @@
       <c r="B478" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
 3.00 x 1340.0 x 2480.0 mm
-Weight (Kg):1,174
+Weight (Kg):1,020
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -8047,7 +8047,7 @@
       <c r="B479" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
 3.00 x 1340.0 x 2480.0 mm
-Weight (Kg):1,020
+Weight (Kg):1,169
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -8063,7 +8063,7 @@
       <c r="B480" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
 3.00 x 1340.0 x 2480.0 mm
-Weight (Kg):1,169
+Weight (Kg):1,951
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -8074,12 +8074,12 @@
     <row r="481" xml:space="preserve">
       <c r="A481" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
-3.00 x 1340.0 x 2480.0 mm</v>
+5.00 x 1000.0 x 2000.0 mm</v>
       </c>
       <c r="B481" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
-3.00 x 1340.0 x 2480.0 mm
-Weight (Kg):1,951
+5.00 x 1000.0 x 2000.0 mm
+Weight (Kg):943
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -8095,7 +8095,7 @@
       <c r="B482" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
 5.00 x 1000.0 x 2000.0 mm
-Weight (Kg):943
+Weight (Kg):947
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -8111,7 +8111,7 @@
       <c r="B483" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
 5.00 x 1000.0 x 2000.0 mm
-Weight (Kg):947
+Weight (Kg):1,588
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -8122,12 +8122,12 @@
     <row r="484" xml:space="preserve">
       <c r="A484" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
-5.00 x 1000.0 x 2000.0 mm</v>
+5.00 x 1250.0 x 2500.0 mm</v>
       </c>
       <c r="B484" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
-5.00 x 1000.0 x 2000.0 mm
-Weight (Kg):1,588
+5.00 x 1250.0 x 2500.0 mm
+Weight (Kg):742
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -8138,12 +8138,12 @@
     <row r="485" xml:space="preserve">
       <c r="A485" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
-5.00 x 1250.0 x 2500.0 mm</v>
+6.00 x 1000.0 x 2000.0 mm</v>
       </c>
       <c r="B485" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
-5.00 x 1250.0 x 2500.0 mm
-Weight (Kg):742
+6.00 x 1000.0 x 2000.0 mm
+Weight (Kg):1,452
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -8159,7 +8159,7 @@
       <c r="B486" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
 6.00 x 1000.0 x 2000.0 mm
-Weight (Kg):1,452
+Weight (Kg):1,624
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -8175,7 +8175,7 @@
       <c r="B487" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
 6.00 x 1000.0 x 2000.0 mm
-Weight (Kg):1,624
+Weight (Kg):1,434
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -8191,7 +8191,7 @@
       <c r="B488" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
 6.00 x 1000.0 x 2000.0 mm
-Weight (Kg):1,434
+Weight (Kg):580
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -8207,7 +8207,7 @@
       <c r="B489" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
 6.00 x 1000.0 x 2000.0 mm
-Weight (Kg):580
+Weight (Kg):1,054
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -8223,7 +8223,7 @@
       <c r="B490" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
 6.00 x 1000.0 x 2000.0 mm
-Weight (Kg):1,054
+Weight (Kg):1,716
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -8239,7 +8239,7 @@
       <c r="B491" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
 6.00 x 1000.0 x 2000.0 mm
-Weight (Kg):1,716
+Weight (Kg):1,148
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -8255,7 +8255,7 @@
       <c r="B492" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
 6.00 x 1000.0 x 2000.0 mm
-Weight (Kg):1,148
+Weight (Kg):960
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -8271,7 +8271,7 @@
       <c r="B493" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
 6.00 x 1000.0 x 2000.0 mm
-Weight (Kg):960
+Weight (Kg):772
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -8282,12 +8282,12 @@
     <row r="494" xml:space="preserve">
       <c r="A494" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
-6.00 x 1000.0 x 2000.0 mm</v>
+6.00 x 1500.0 x 3000.0 mm</v>
       </c>
       <c r="B494" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
-6.00 x 1000.0 x 2000.0 mm
-Weight (Kg):772
+6.00 x 1500.0 x 3000.0 mm
+Weight (Kg):2,146
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -8303,7 +8303,7 @@
       <c r="B495" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
 6.00 x 1500.0 x 3000.0 mm
-Weight (Kg):2,146
+Weight (Kg):1,994
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -8319,7 +8319,7 @@
       <c r="B496" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
 6.00 x 1500.0 x 3000.0 mm
-Weight (Kg):1,994
+Weight (Kg):1,488
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -8335,7 +8335,7 @@
       <c r="B497" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
 6.00 x 1500.0 x 3000.0 mm
-Weight (Kg):1,488
+Weight (Kg):1,278
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -8351,7 +8351,7 @@
       <c r="B498" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
 6.00 x 1500.0 x 3000.0 mm
-Weight (Kg):1,278
+Weight (Kg):1,062
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -8367,7 +8367,7 @@
       <c r="B499" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
 6.00 x 1500.0 x 3000.0 mm
-Weight (Kg):1,062
+Weight (Kg):1,526
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -8383,7 +8383,7 @@
       <c r="B500" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
 6.00 x 1500.0 x 3000.0 mm
-Weight (Kg):1,526
+Weight (Kg):1,280
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -8394,12 +8394,12 @@
     <row r="501" xml:space="preserve">
       <c r="A501" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
-6.00 x 1500.0 x 3000.0 mm</v>
+6.00 x 1510.0 x 3010.0 mm</v>
       </c>
       <c r="B501" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
-6.00 x 1500.0 x 3000.0 mm
-Weight (Kg):1,280
+6.00 x 1510.0 x 3010.0 mm
+Weight (Kg):1,986
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -8415,7 +8415,7 @@
       <c r="B502" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
 6.00 x 1510.0 x 3010.0 mm
-Weight (Kg):1,986
+Weight (Kg):1,784
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -8425,26 +8425,10 @@
     </row>
     <row r="503" xml:space="preserve">
       <c r="A503" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
-6.00 x 1510.0 x 3010.0 mm</v>
-      </c>
-      <c r="B503" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, 2B,
-6.00 x 1510.0 x 3010.0 mm
-Weight (Kg):1,784
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-3,395.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="504" xml:space="preserve">
-      <c r="A504" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, Nb. 1,
 6.00 x 1000.0 x 2000.0 mm</v>
       </c>
-      <c r="B504" t="str" xml:space="preserve">
+      <c r="B503" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, Nb. 1,
 6.00 x 1000.0 x 2000.0 mm
 Weight (Kg):570
@@ -8455,15 +8439,31 @@
 Add to cart</v>
       </c>
     </row>
+    <row r="504" xml:space="preserve">
+      <c r="A504" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, SB-G-400,
+1.50 x 1500.0 x 3000.0 mm</v>
+      </c>
+      <c r="B504" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, SB-G-400,
+1.50 x 1500.0 x 3000.0 mm
+Weight (Kg):723
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+3,395.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
     <row r="505" xml:space="preserve">
       <c r="A505" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, SB-G-400,
-1.50 x 1500.0 x 3000.0 mm</v>
+2.00 x 1500.0 x 3000.0 mm</v>
       </c>
       <c r="B505" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, SB-G-400,
-1.50 x 1500.0 x 3000.0 mm
-Weight (Kg):723
+2.00 x 1500.0 x 3000.0 mm
+Weight (Kg):819
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -8479,7 +8479,7 @@
       <c r="B506" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, SB-G-400,
 2.00 x 1500.0 x 3000.0 mm
-Weight (Kg):819
+Weight (Kg):1,935
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -8489,13 +8489,13 @@
     </row>
     <row r="507" xml:space="preserve">
       <c r="A507" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, SB-G-400,
-2.00 x 1500.0 x 3000.0 mm</v>
+        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Untrimmed, Coil, 2B,
+1.20 x 1537.0 x coil mm</v>
       </c>
       <c r="B507" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Sheet, SB-G-400,
-2.00 x 1500.0 x 3000.0 mm
-Weight (Kg):1,935
+        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Untrimmed, Coil, 2B,
+1.20 x 1537.0 x coil mm
+Weight (Kg):2,125
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -8506,12 +8506,12 @@
     <row r="508" xml:space="preserve">
       <c r="A508" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Untrimmed, Coil, 2B,
-1.20 x 1537.0 x coil mm</v>
+1.80 x 1530.0 x coil mm</v>
       </c>
       <c r="B508" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Untrimmed, Coil, 2B,
-1.20 x 1537.0 x coil mm
-Weight (Kg):2,125
+1.80 x 1530.0 x coil mm
+Weight (Kg):5,263
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -8522,12 +8522,12 @@
     <row r="509" xml:space="preserve">
       <c r="A509" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Untrimmed, Coil, 2B,
-1.80 x 1530.0 x coil mm</v>
+1.80 x 1535.0 x coil mm</v>
       </c>
       <c r="B509" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Untrimmed, Coil, 2B,
-1.80 x 1530.0 x coil mm
-Weight (Kg):5,263
+1.80 x 1535.0 x coil mm
+Weight (Kg):2,726
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -8538,57 +8538,41 @@
     <row r="510" xml:space="preserve">
       <c r="A510" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Untrimmed, Coil, 2B,
-1.80 x 1535.0 x coil mm</v>
+2.00 x 1023.0 x coil mm</v>
       </c>
       <c r="B510" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Untrimmed, Coil, 2B,
-1.80 x 1535.0 x coil mm
-Weight (Kg):2,726
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-3,395.00 €/ton
+2.00 x 1023.0 x coil mm
+Weight (Kg):1,825
+Quality:Prime
+Help
+Location:FABRICA ALGECIRAS
+3,595.00 €/ton
 Add to cart</v>
       </c>
     </row>
     <row r="511" xml:space="preserve">
       <c r="A511" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Untrimmed, Coil, 2B,
-2.00 x 1023.0 x coil mm</v>
+3.00 x 1552.0 x coil mm</v>
       </c>
       <c r="B511" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Untrimmed, Coil, 2B,
-2.00 x 1023.0 x coil mm
-Weight (Kg):1,825
-Quality:Prime
-Help
-Location:FABRICA ALGECIRAS
-3,595.00 €/ton
+3.00 x 1552.0 x coil mm
+Weight (Kg):2,868
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+3,395.00 €/ton
 Add to cart</v>
       </c>
     </row>
     <row r="512" xml:space="preserve">
       <c r="A512" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Untrimmed, Coil, 2B,
-3.00 x 1552.0 x coil mm</v>
+6.00 x 1030.0 x coil mm</v>
       </c>
       <c r="B512" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Untrimmed, Coil, 2B,
-3.00 x 1552.0 x coil mm
-Weight (Kg):2,868
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-3,395.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="513" xml:space="preserve">
-      <c r="A513" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Untrimmed, Coil, 2B,
-6.00 x 1030.0 x coil mm</v>
-      </c>
-      <c r="B513" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4404 316L-Untrimmed, Coil, 2B,
 6.00 x 1030.0 x coil mm
 Weight (Kg):2,225
@@ -8599,12 +8583,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="514" xml:space="preserve">
-      <c r="A514" t="str" xml:space="preserve">
+    <row r="513" xml:space="preserve">
+      <c r="A513" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4571 316Ti-Coil, 2B,
 4.00 x 210.0 x coil mm</v>
       </c>
-      <c r="B514" t="str" xml:space="preserve">
+      <c r="B513" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4571 316Ti-Coil, 2B,
 4.00 x 210.0 x coil mm
 Weight (Kg):3,817
@@ -8612,6 +8596,22 @@
 Help
 Location:FABRICA ALGECIRAS
 3,370.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="514" xml:space="preserve">
+      <c r="A514" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4571 316Ti-Coil, Nb. 1,
+3.00 x 184.0 x coil mm</v>
+      </c>
+      <c r="B514" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4571 316Ti-Coil, Nb. 1,
+3.00 x 184.0 x coil mm
+Weight (Kg):1,794
+Quality:Prime
+Help
+Location:FABRICA ALGECIRAS
+3,270.00 €/ton
 Add to cart</v>
       </c>
     </row>
@@ -8623,7 +8623,7 @@
       <c r="B515" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4571 316Ti-Coil, Nb. 1,
 3.00 x 184.0 x coil mm
-Weight (Kg):1,794
+Weight (Kg):1,806
 Quality:Prime
 Help
 Location:FABRICA ALGECIRAS
@@ -8639,7 +8639,7 @@
       <c r="B516" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4571 316Ti-Coil, Nb. 1,
 3.00 x 184.0 x coil mm
-Weight (Kg):1,806
+Weight (Kg):1,808
 Quality:Prime
 Help
 Location:FABRICA ALGECIRAS
@@ -8650,25 +8650,9 @@
     <row r="517" xml:space="preserve">
       <c r="A517" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4571 316Ti-Coil, Nb. 1,
-3.00 x 184.0 x coil mm</v>
+4.00 x 200.0 x coil mm</v>
       </c>
       <c r="B517" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4571 316Ti-Coil, Nb. 1,
-3.00 x 184.0 x coil mm
-Weight (Kg):1,808
-Quality:Prime
-Help
-Location:FABRICA ALGECIRAS
-3,270.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="518" xml:space="preserve">
-      <c r="A518" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4571 316Ti-Coil, Nb. 1,
-4.00 x 200.0 x coil mm</v>
-      </c>
-      <c r="B518" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4571 316Ti-Coil, Nb. 1,
 4.00 x 200.0 x coil mm
 Weight (Kg):1,918
@@ -8679,12 +8663,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="519" xml:space="preserve">
-      <c r="A519" t="str" xml:space="preserve">
+    <row r="518" xml:space="preserve">
+      <c r="A518" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4571 316Ti-Plate, Nb. 1,
 45.00 x 1500.0 x 3000.0 mm</v>
       </c>
-      <c r="B519" t="str" xml:space="preserve">
+      <c r="B518" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4571 316Ti-Plate, Nb. 1,
 45.00 x 1500.0 x 3000.0 mm
 Weight (Kg):1,640
@@ -8692,6 +8676,22 @@
 Help
 Location:FABRICA ALGECIRAS
 4,600.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="519" xml:space="preserve">
+      <c r="A519" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4571 316Ti-Sheet, 2B,
+3.00 x 1000.0 x 2000.0 mm</v>
+      </c>
+      <c r="B519" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4571 316Ti-Sheet, 2B,
+3.00 x 1000.0 x 2000.0 mm
+Weight (Kg):918
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+3,495.00 €/ton
 Add to cart</v>
       </c>
     </row>
@@ -8703,7 +8703,7 @@
       <c r="B520" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4571 316Ti-Sheet, 2B,
 3.00 x 1000.0 x 2000.0 mm
-Weight (Kg):918
+Weight (Kg):518
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -8735,7 +8735,7 @@
       <c r="B522" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4571 316Ti-Sheet, 2B,
 3.00 x 1000.0 x 2000.0 mm
-Weight (Kg):518
+Weight (Kg):848
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -8746,12 +8746,12 @@
     <row r="523" xml:space="preserve">
       <c r="A523" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4571 316Ti-Sheet, 2B,
-3.00 x 1000.0 x 2000.0 mm</v>
+5.00 x 1000.0 x 2000.0 mm</v>
       </c>
       <c r="B523" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4571 316Ti-Sheet, 2B,
-3.00 x 1000.0 x 2000.0 mm
-Weight (Kg):848
+5.00 x 1000.0 x 2000.0 mm
+Weight (Kg):1,102
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -8762,12 +8762,12 @@
     <row r="524" xml:space="preserve">
       <c r="A524" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4571 316Ti-Sheet, 2B,
-5.00 x 1000.0 x 2000.0 mm</v>
+6.00 x 1000.0 x 2000.0 mm</v>
       </c>
       <c r="B524" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4571 316Ti-Sheet, 2B,
-5.00 x 1000.0 x 2000.0 mm
-Weight (Kg):1,102
+6.00 x 1000.0 x 2000.0 mm
+Weight (Kg):1,050
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -8783,7 +8783,7 @@
       <c r="B525" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4571 316Ti-Sheet, 2B,
 6.00 x 1000.0 x 2000.0 mm
-Weight (Kg):1,050
+Weight (Kg):952
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -8793,26 +8793,10 @@
     </row>
     <row r="526" xml:space="preserve">
       <c r="A526" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4571 316Ti-Sheet, 2B,
-6.00 x 1000.0 x 2000.0 mm</v>
-      </c>
-      <c r="B526" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4571 316Ti-Sheet, 2B,
-6.00 x 1000.0 x 2000.0 mm
-Weight (Kg):952
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-3,495.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="527" xml:space="preserve">
-      <c r="A527" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4571 316Ti-Sheet, Nb. 1,
 8.00 x 1500.0 x 3000.0 mm</v>
       </c>
-      <c r="B527" t="str" xml:space="preserve">
+      <c r="B526" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4571 316Ti-Sheet, Nb. 1,
 8.00 x 1500.0 x 3000.0 mm
 Weight (Kg):1,136
@@ -8820,6 +8804,22 @@
 Help
 Location:FABRICA ALGECIRAS
 3,495.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="527" xml:space="preserve">
+      <c r="A527" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4541 321-Coil, 2B,
+1.90 x 217.0 x coil mm</v>
+      </c>
+      <c r="B527" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4541 321-Coil, 2B,
+1.90 x 217.0 x coil mm
+Weight (Kg):3,537
+Quality:Prime
+Help
+Location:FABRICA ALGECIRAS
+2,235.00 €/ton
 Add to cart</v>
       </c>
     </row>
@@ -8831,7 +8831,7 @@
       <c r="B528" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4541 321-Coil, 2B,
 1.90 x 217.0 x coil mm
-Weight (Kg):3,537
+Weight (Kg):3,484
 Quality:Prime
 Help
 Location:FABRICA ALGECIRAS
@@ -8847,7 +8847,7 @@
       <c r="B529" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4541 321-Coil, 2B,
 1.90 x 217.0 x coil mm
-Weight (Kg):3,484
+Weight (Kg):3,537
 Quality:Prime
 Help
 Location:FABRICA ALGECIRAS
@@ -8863,7 +8863,7 @@
       <c r="B530" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4541 321-Coil, 2B,
 1.90 x 217.0 x coil mm
-Weight (Kg):3,537
+Weight (Kg):3,490
 Quality:Prime
 Help
 Location:FABRICA ALGECIRAS
@@ -8879,7 +8879,7 @@
       <c r="B531" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4541 321-Coil, 2B,
 1.90 x 217.0 x coil mm
-Weight (Kg):3,490
+Weight (Kg):3,537
 Quality:Prime
 Help
 Location:FABRICA ALGECIRAS
@@ -8895,7 +8895,7 @@
       <c r="B532" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4541 321-Coil, 2B,
 1.90 x 217.0 x coil mm
-Weight (Kg):3,537
+Weight (Kg):3,492
 Quality:Prime
 Help
 Location:FABRICA ALGECIRAS
@@ -8911,7 +8911,7 @@
       <c r="B533" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4541 321-Coil, 2B,
 1.90 x 217.0 x coil mm
-Weight (Kg):3,492
+Weight (Kg):3,480
 Quality:Prime
 Help
 Location:FABRICA ALGECIRAS
@@ -8922,25 +8922,9 @@
     <row r="534" xml:space="preserve">
       <c r="A534" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4541 321-Coil, 2B,
-1.90 x 217.0 x coil mm</v>
+4.00 x 520.0 x coil mm</v>
       </c>
       <c r="B534" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4541 321-Coil, 2B,
-1.90 x 217.0 x coil mm
-Weight (Kg):3,480
-Quality:Prime
-Help
-Location:FABRICA ALGECIRAS
-2,235.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="535" xml:space="preserve">
-      <c r="A535" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4541 321-Coil, 2B,
-4.00 x 520.0 x coil mm</v>
-      </c>
-      <c r="B535" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4541 321-Coil, 2B,
 4.00 x 520.0 x coil mm
 Weight (Kg):7,263
@@ -8951,28 +8935,28 @@
 Add to cart</v>
       </c>
     </row>
+    <row r="535" xml:space="preserve">
+      <c r="A535" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4541 321-Coil, Nb. 1,
+5.00 x 1542.0 x coil mm</v>
+      </c>
+      <c r="B535" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4541 321-Coil, Nb. 1,
+5.00 x 1542.0 x coil mm
+Weight (Kg):4,890
+Quality:Prime
+Help
+Location:FABRICA ALGECIRAS
+2,875.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
     <row r="536" xml:space="preserve">
       <c r="A536" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4541 321-Coil, Nb. 1,
-5.00 x 1542.0 x coil mm</v>
+5.00 x 230.9 x coil mm</v>
       </c>
       <c r="B536" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4541 321-Coil, Nb. 1,
-5.00 x 1542.0 x coil mm
-Weight (Kg):4,890
-Quality:Prime
-Help
-Location:FABRICA ALGECIRAS
-2,875.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="537" xml:space="preserve">
-      <c r="A537" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4541 321-Coil, Nb. 1,
-5.00 x 230.9 x coil mm</v>
-      </c>
-      <c r="B537" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4541 321-Coil, Nb. 1,
 5.00 x 230.9 x coil mm
 Weight (Kg):4,198
@@ -8983,15 +8967,31 @@
 Add to cart</v>
       </c>
     </row>
+    <row r="537" xml:space="preserve">
+      <c r="A537" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4541 321-Sheet, 2B,
+3.00 x 1000.0 x 2000.0 mm</v>
+      </c>
+      <c r="B537" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4541 321-Sheet, 2B,
+3.00 x 1000.0 x 2000.0 mm
+Weight (Kg):1,104
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,385.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
     <row r="538" xml:space="preserve">
       <c r="A538" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4541 321-Sheet, 2B,
-3.00 x 1000.0 x 2000.0 mm</v>
+4.00 x 1000.0 x 2000.0 mm</v>
       </c>
       <c r="B538" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4541 321-Sheet, 2B,
-3.00 x 1000.0 x 2000.0 mm
-Weight (Kg):1,104
+4.00 x 1000.0 x 2000.0 mm
+Weight (Kg):1,552
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -9002,25 +9002,9 @@
     <row r="539" xml:space="preserve">
       <c r="A539" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4541 321-Sheet, 2B,
-4.00 x 1000.0 x 2000.0 mm</v>
+6.00 x 1250.0 x 2500.0 mm</v>
       </c>
       <c r="B539" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4541 321-Sheet, 2B,
-4.00 x 1000.0 x 2000.0 mm
-Weight (Kg):1,552
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-2,385.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="540" xml:space="preserve">
-      <c r="A540" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4541 321-Sheet, 2B,
-6.00 x 1250.0 x 2500.0 mm</v>
-      </c>
-      <c r="B540" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4541 321-Sheet, 2B,
 6.00 x 1250.0 x 2500.0 mm
 Weight (Kg):1,296
@@ -9031,12 +9015,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="541" xml:space="preserve">
-      <c r="A541" t="str" xml:space="preserve">
+    <row r="540" xml:space="preserve">
+      <c r="A540" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4541 321-Sheet, Nb. 1,
 8.00 x 1000.0 x 2000.0 mm</v>
       </c>
-      <c r="B541" t="str" xml:space="preserve">
+      <c r="B540" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4541 321-Sheet, Nb. 1,
 8.00 x 1000.0 x 2000.0 mm
 Weight (Kg):640
@@ -9047,28 +9031,28 @@
 Add to cart</v>
       </c>
     </row>
+    <row r="541" xml:space="preserve">
+      <c r="A541" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4512 409L-Coil, 2B,
+1.00 x 1304.0 x coil mm</v>
+      </c>
+      <c r="B541" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4512 409L-Coil, 2B,
+1.00 x 1304.0 x coil mm
+Weight (Kg):10,360
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+1,125.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
     <row r="542" xml:space="preserve">
       <c r="A542" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4512 409L-Coil, 2B,
-1.00 x 1304.0 x coil mm</v>
+1.00 x 625.0 x coil mm</v>
       </c>
       <c r="B542" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4512 409L-Coil, 2B,
-1.00 x 1304.0 x coil mm
-Weight (Kg):10,360
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-1,125.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="543" xml:space="preserve">
-      <c r="A543" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4512 409L-Coil, 2B,
-1.00 x 625.0 x coil mm</v>
-      </c>
-      <c r="B543" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4512 409L-Coil, 2B,
 1.00 x 625.0 x coil mm
 Weight (Kg):6,700
@@ -9079,28 +9063,28 @@
 Add to cart</v>
       </c>
     </row>
+    <row r="543" xml:space="preserve">
+      <c r="A543" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4512 409L-Coil, 2D,
+2.00 x 1291.0 x coil mm</v>
+      </c>
+      <c r="B543" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4512 409L-Coil, 2D,
+2.00 x 1291.0 x coil mm
+Weight (Kg):3,579
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+1,125.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
     <row r="544" xml:space="preserve">
       <c r="A544" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4512 409L-Coil, 2D,
-2.00 x 1291.0 x coil mm</v>
+2.00 x 150.0 x coil mm</v>
       </c>
       <c r="B544" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4512 409L-Coil, 2D,
-2.00 x 1291.0 x coil mm
-Weight (Kg):3,579
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-1,125.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="545" xml:space="preserve">
-      <c r="A545" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4512 409L-Coil, 2D,
-2.00 x 150.0 x coil mm</v>
-      </c>
-      <c r="B545" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4512 409L-Coil, 2D,
 2.00 x 150.0 x coil mm
 Weight (Kg):2,270
@@ -9111,15 +9095,31 @@
 Add to cart</v>
       </c>
     </row>
+    <row r="545" xml:space="preserve">
+      <c r="A545" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4512 409L-Coil, Nb. 1,
+4.00 x 140.0 x coil mm</v>
+      </c>
+      <c r="B545" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4512 409L-Coil, Nb. 1,
+4.00 x 140.0 x coil mm
+Weight (Kg):2,354
+Quality:Prime
+Help
+Location:FABRICA ALGECIRAS
+900.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
     <row r="546" xml:space="preserve">
       <c r="A546" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4512 409L-Coil, Nb. 1,
-4.00 x 140.0 x coil mm</v>
+5.00 x 190.0 x coil mm</v>
       </c>
       <c r="B546" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4512 409L-Coil, Nb. 1,
-4.00 x 140.0 x coil mm
-Weight (Kg):2,354
+5.00 x 190.0 x coil mm
+Weight (Kg):2,447
 Quality:Prime
 Help
 Location:FABRICA ALGECIRAS
@@ -9130,13 +9130,13 @@
     <row r="547" xml:space="preserve">
       <c r="A547" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4512 409L-Coil, Nb. 1,
-5.00 x 190.0 x coil mm</v>
+6.00 x 270.0 x coil mm</v>
       </c>
       <c r="B547" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4512 409L-Coil, Nb. 1,
-5.00 x 190.0 x coil mm
-Weight (Kg):2,447
-Quality:Prime
+6.00 x 270.0 x coil mm
+Weight (Kg):2,116
+Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
 900.00 €/ton
@@ -9151,7 +9151,7 @@
       <c r="B548" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4512 409L-Coil, Nb. 1,
 6.00 x 270.0 x coil mm
-Weight (Kg):2,116
+Weight (Kg):1,780
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -9162,13 +9162,13 @@
     <row r="549" xml:space="preserve">
       <c r="A549" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4512 409L-Coil, Nb. 1,
-6.00 x 270.0 x coil mm</v>
+8.00 x 115.9 x coil mm</v>
       </c>
       <c r="B549" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4512 409L-Coil, Nb. 1,
-6.00 x 270.0 x coil mm
-Weight (Kg):1,780
-Quality:Prime-2
+8.00 x 115.9 x coil mm
+Weight (Kg):1,238
+Quality:Prime
 Help
 Location:FABRICA ALGECIRAS
 900.00 €/ton
@@ -9178,12 +9178,12 @@
     <row r="550" xml:space="preserve">
       <c r="A550" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4512 409L-Coil, Nb. 1,
-8.00 x 115.9 x coil mm</v>
+8.00 x 125.9 x coil mm</v>
       </c>
       <c r="B550" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4512 409L-Coil, Nb. 1,
-8.00 x 115.9 x coil mm
-Weight (Kg):1,238
+8.00 x 125.9 x coil mm
+Weight (Kg):1,214
 Quality:Prime
 Help
 Location:FABRICA ALGECIRAS
@@ -9194,25 +9194,9 @@
     <row r="551" xml:space="preserve">
       <c r="A551" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4512 409L-Coil, Nb. 1,
-8.00 x 125.9 x coil mm</v>
+8.00 x 230.9 x coil mm</v>
       </c>
       <c r="B551" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4512 409L-Coil, Nb. 1,
-8.00 x 125.9 x coil mm
-Weight (Kg):1,214
-Quality:Prime
-Help
-Location:FABRICA ALGECIRAS
-900.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="552" xml:space="preserve">
-      <c r="A552" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4512 409L-Coil, Nb. 1,
-8.00 x 230.9 x coil mm</v>
-      </c>
-      <c r="B552" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4512 409L-Coil, Nb. 1,
 8.00 x 230.9 x coil mm
 Weight (Kg):2,960
@@ -9223,12 +9207,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="553" xml:space="preserve">
-      <c r="A553" t="str" xml:space="preserve">
+    <row r="552" xml:space="preserve">
+      <c r="A552" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4512 409L-Untrimmed, Coil, 2B,
 1.00 x 625.0 x coil mm</v>
       </c>
-      <c r="B553" t="str" xml:space="preserve">
+      <c r="B552" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4512 409L-Untrimmed, Coil, 2B,
 1.00 x 625.0 x coil mm
 Weight (Kg):3,441
@@ -9239,12 +9223,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="554" xml:space="preserve">
-      <c r="A554" t="str" xml:space="preserve">
+    <row r="553" xml:space="preserve">
+      <c r="A553" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4512 409L-Untrimmed, Coil, 2D,
 1.50 x 1295.0 x coil mm</v>
       </c>
-      <c r="B554" t="str" xml:space="preserve">
+      <c r="B553" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4512 409L-Untrimmed, Coil, 2D,
 1.50 x 1295.0 x coil mm
 Weight (Kg):2,445
@@ -9255,28 +9239,28 @@
 Add to cart</v>
       </c>
     </row>
+    <row r="554" xml:space="preserve">
+      <c r="A554" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, 2B,
+0.70 x 299.9 x coil mm</v>
+      </c>
+      <c r="B554" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, 2B,
+0.70 x 299.9 x coil mm
+Weight (Kg):2,518
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+1,000.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
     <row r="555" xml:space="preserve">
       <c r="A555" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, 2B,
-0.70 x 299.9 x coil mm</v>
+2.00 x 220.0 x coil mm</v>
       </c>
       <c r="B555" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, 2B,
-0.70 x 299.9 x coil mm
-Weight (Kg):2,518
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-1,000.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="556" xml:space="preserve">
-      <c r="A556" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, 2B,
-2.00 x 220.0 x coil mm</v>
-      </c>
-      <c r="B556" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, 2B,
 2.00 x 220.0 x coil mm
 Weight (Kg):776
@@ -9287,60 +9271,60 @@
 Add to cart</v>
       </c>
     </row>
+    <row r="556" xml:space="preserve">
+      <c r="A556" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, 2D,
+0.50 x 1518.0 x coil mm</v>
+      </c>
+      <c r="B556" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, 2D,
+0.50 x 1518.0 x coil mm
+Weight (Kg):4,480
+Quality:Prime
+Help
+Location:FABRICA ALGECIRAS
+1,325.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
     <row r="557" xml:space="preserve">
       <c r="A557" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, 2D,
-0.50 x 1518.0 x coil mm</v>
+0.70 x 1007.0 x coil mm</v>
       </c>
       <c r="B557" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, 2D,
-0.50 x 1518.0 x coil mm
-Weight (Kg):4,480
-Quality:Prime
-Help
-Location:FABRICA ALGECIRAS
-1,325.00 €/ton
+0.70 x 1007.0 x coil mm
+Weight (Kg):14,970
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+1,125.00 €/ton
 Add to cart</v>
       </c>
     </row>
     <row r="558" xml:space="preserve">
       <c r="A558" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, 2D,
-0.70 x 1007.0 x coil mm</v>
+0.70 x 1450.0 x coil mm</v>
       </c>
       <c r="B558" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, 2D,
-0.70 x 1007.0 x coil mm
-Weight (Kg):14,970
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-1,125.00 €/ton
+0.70 x 1450.0 x coil mm
+Weight (Kg):4,780
+Quality:Prime
+Help
+Location:FABRICA ALGECIRAS
+1,325.00 €/ton
 Add to cart</v>
       </c>
     </row>
     <row r="559" xml:space="preserve">
       <c r="A559" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, 2D,
-0.70 x 1450.0 x coil mm</v>
+0.70 x 869.0 x coil mm</v>
       </c>
       <c r="B559" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, 2D,
-0.70 x 1450.0 x coil mm
-Weight (Kg):4,780
-Quality:Prime
-Help
-Location:FABRICA ALGECIRAS
-1,325.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="560" xml:space="preserve">
-      <c r="A560" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, 2D,
-0.70 x 869.0 x coil mm</v>
-      </c>
-      <c r="B560" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, 2D,
 0.70 x 869.0 x coil mm
 Weight (Kg):13,570
@@ -9351,20 +9335,36 @@
 Add to cart</v>
       </c>
     </row>
+    <row r="560" xml:space="preserve">
+      <c r="A560" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, BA,
+0.40 x 474.0 x coil mm</v>
+      </c>
+      <c r="B560" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, BA,
+0.40 x 474.0 x coil mm
+Weight (Kg):2,997
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+1,050.00 €/ton
+Out of Stock</v>
+      </c>
+    </row>
     <row r="561" xml:space="preserve">
       <c r="A561" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, BA,
-0.40 x 474.0 x coil mm</v>
+0.50 x 114.0 x coil mm</v>
       </c>
       <c r="B561" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, BA,
-0.40 x 474.0 x coil mm
-Weight (Kg):2,997
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-1,050.00 €/ton
-Out of Stock</v>
+0.50 x 114.0 x coil mm
+Weight (Kg):1,225
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+1,000.00 €/ton
+Reserved</v>
       </c>
     </row>
     <row r="562" xml:space="preserve">
@@ -9626,17 +9626,17 @@
     <row r="578" xml:space="preserve">
       <c r="A578" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, BA,
-0.50 x 114.0 x coil mm</v>
+0.70 x 842.0 x coil mm</v>
       </c>
       <c r="B578" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, BA,
-0.50 x 114.0 x coil mm
-Weight (Kg):1,225
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-1,000.00 €/ton
-Reserved</v>
+0.70 x 842.0 x coil mm
+Weight (Kg):10,370
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+1,125.00 €/ton
+Add to cart</v>
       </c>
     </row>
     <row r="579" xml:space="preserve">
@@ -9690,73 +9690,57 @@
     <row r="582" xml:space="preserve">
       <c r="A582" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, BA,
-0.70 x 842.0 x coil mm</v>
+0.70 x 855.0 x coil mm</v>
       </c>
       <c r="B582" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, BA,
-0.70 x 842.0 x coil mm
-Weight (Kg):10,370
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-1,125.00 €/ton
+0.70 x 855.0 x coil mm
+Weight (Kg):3,990
+Quality:Prime
+Help
+Location:FABRICA ALGECIRAS
+1,325.00 €/ton
 Add to cart</v>
       </c>
     </row>
     <row r="583" xml:space="preserve">
       <c r="A583" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, BA,
-0.70 x 855.0 x coil mm</v>
+0.70 x 870.0 x coil mm</v>
       </c>
       <c r="B583" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, BA,
-0.70 x 855.0 x coil mm
-Weight (Kg):3,990
-Quality:Prime
-Help
-Location:FABRICA ALGECIRAS
-1,325.00 €/ton
+0.70 x 870.0 x coil mm
+Weight (Kg):13,910
+Quality:Prime
+Help
+Location:FABRICA ALGECIRAS
+1,900.00 €/ton
 Add to cart</v>
       </c>
     </row>
     <row r="584" xml:space="preserve">
       <c r="A584" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, BA,
-0.70 x 870.0 x coil mm</v>
+0.70 x 953.0 x coil mm</v>
       </c>
       <c r="B584" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, BA,
-0.70 x 870.0 x coil mm
-Weight (Kg):13,910
-Quality:Prime
-Help
-Location:FABRICA ALGECIRAS
-1,900.00 €/ton
+0.70 x 953.0 x coil mm
+Weight (Kg):6,970
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+1,125.00 €/ton
 Add to cart</v>
       </c>
     </row>
     <row r="585" xml:space="preserve">
       <c r="A585" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, BA,
-0.70 x 953.0 x coil mm</v>
+1.00 x 530.0 x coil mm</v>
       </c>
       <c r="B585" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, BA,
-0.70 x 953.0 x coil mm
-Weight (Kg):6,970
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-1,125.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="586" xml:space="preserve">
-      <c r="A586" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, BA,
-1.00 x 530.0 x coil mm</v>
-      </c>
-      <c r="B586" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, BA,
 1.00 x 530.0 x coil mm
 Weight (Kg):880
@@ -9767,32 +9751,48 @@
 Add to cart</v>
       </c>
     </row>
+    <row r="586" xml:space="preserve">
+      <c r="A586" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, Polished N4-G-180,
+0.90 x 1250.0 x coil mm</v>
+      </c>
+      <c r="B586" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, Polished N4-G-180,
+0.90 x 1250.0 x coil mm
+Weight (Kg):2,218
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+1,125.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
     <row r="587" xml:space="preserve">
       <c r="A587" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, Polished N4-G-180,
-0.90 x 1250.0 x coil mm</v>
+1.20 x 120.0 x coil mm</v>
       </c>
       <c r="B587" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, Polished N4-G-180,
-0.90 x 1250.0 x coil mm
-Weight (Kg):2,218
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-1,125.00 €/ton
+1.20 x 120.0 x coil mm
+Weight (Kg):1,430
+Quality:Prime
+Help
+Location:FABRICA ALGECIRAS
+1,000.00 €/ton
 Add to cart</v>
       </c>
     </row>
     <row r="588" xml:space="preserve">
       <c r="A588" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, Polished N4-G-180,
-1.20 x 120.0 x coil mm</v>
+1.20 x 250.0 x coil mm</v>
       </c>
       <c r="B588" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, Polished N4-G-180,
-1.20 x 120.0 x coil mm
-Weight (Kg):1,430
-Quality:Prime
+1.20 x 250.0 x coil mm
+Weight (Kg):1,902
+Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
 1,000.00 €/ton
@@ -9802,13 +9802,13 @@
     <row r="589" xml:space="preserve">
       <c r="A589" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, Polished N4-G-180,
-1.20 x 250.0 x coil mm</v>
+1.20 x 250.9 x coil mm</v>
       </c>
       <c r="B589" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, Polished N4-G-180,
-1.20 x 250.0 x coil mm
-Weight (Kg):1,902
-Quality:Prime-2
+1.20 x 250.9 x coil mm
+Weight (Kg):1,960
+Quality:Prime
 Help
 Location:FABRICA ALGECIRAS
 1,000.00 €/ton
@@ -9823,8 +9823,8 @@
       <c r="B590" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, Polished N4-G-180,
 1.20 x 250.9 x coil mm
-Weight (Kg):1,960
-Quality:Prime
+Weight (Kg):1,918
+Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
 1,000.00 €/ton
@@ -9834,12 +9834,12 @@
     <row r="591" xml:space="preserve">
       <c r="A591" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, Polished N4-G-180,
-1.20 x 250.9 x coil mm</v>
+1.20 x 260.9 x coil mm</v>
       </c>
       <c r="B591" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, Polished N4-G-180,
-1.20 x 250.9 x coil mm
-Weight (Kg):1,918
+1.20 x 260.9 x coil mm
+Weight (Kg):1,524
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -9855,7 +9855,7 @@
       <c r="B592" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, Polished N4-G-180,
 1.20 x 260.9 x coil mm
-Weight (Kg):1,524
+Weight (Kg):1,934
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -9865,13 +9865,13 @@
     </row>
     <row r="593" xml:space="preserve">
       <c r="A593" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, Polished N4-G-180,
-1.20 x 260.9 x coil mm</v>
+        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, SB-G-400,
+0.60 x 134.9 x coil mm</v>
       </c>
       <c r="B593" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, Polished N4-G-180,
-1.20 x 260.9 x coil mm
-Weight (Kg):1,934
+        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, SB-G-400,
+0.60 x 134.9 x coil mm
+Weight (Kg):1,134
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -9887,7 +9887,7 @@
       <c r="B594" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, SB-G-400,
 0.60 x 134.9 x coil mm
-Weight (Kg):1,134
+Weight (Kg):962
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -9898,12 +9898,12 @@
     <row r="595" xml:space="preserve">
       <c r="A595" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, SB-G-400,
-0.60 x 134.9 x coil mm</v>
+0.60 x 245.9 x coil mm</v>
       </c>
       <c r="B595" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, SB-G-400,
-0.60 x 134.9 x coil mm
-Weight (Kg):962
+0.60 x 245.9 x coil mm
+Weight (Kg):1,778
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -9914,12 +9914,12 @@
     <row r="596" xml:space="preserve">
       <c r="A596" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, SB-G-400,
-0.60 x 245.9 x coil mm</v>
+1.00 x 118.9 x coil mm</v>
       </c>
       <c r="B596" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, SB-G-400,
-0.60 x 245.9 x coil mm
-Weight (Kg):1,778
+1.00 x 118.9 x coil mm
+Weight (Kg):754
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -9935,7 +9935,7 @@
       <c r="B597" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, SB-G-400,
 1.00 x 118.9 x coil mm
-Weight (Kg):754
+Weight (Kg):802
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -9946,25 +9946,9 @@
     <row r="598" xml:space="preserve">
       <c r="A598" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, SB-G-400,
-1.00 x 118.9 x coil mm</v>
+1.00 x 266.9 x coil mm</v>
       </c>
       <c r="B598" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, SB-G-400,
-1.00 x 118.9 x coil mm
-Weight (Kg):802
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-1,000.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="599" xml:space="preserve">
-      <c r="A599" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, SB-G-400,
-1.00 x 266.9 x coil mm</v>
-      </c>
-      <c r="B599" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, SB-G-400,
 1.00 x 266.9 x coil mm
 Weight (Kg):1,322
@@ -9975,12 +9959,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="600" xml:space="preserve">
-      <c r="A600" t="str" xml:space="preserve">
+    <row r="599" xml:space="preserve">
+      <c r="A599" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, SB-G-500,
 0.70 x 245.9 x coil mm</v>
       </c>
-      <c r="B600" t="str" xml:space="preserve">
+      <c r="B599" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, SB-G-500,
 0.70 x 245.9 x coil mm
 Weight (Kg):1,496
@@ -9991,32 +9975,48 @@
 Add to cart</v>
       </c>
     </row>
+    <row r="600" xml:space="preserve">
+      <c r="A600" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, SBA,
+0.70 x 1056.0 x coil mm</v>
+      </c>
+      <c r="B600" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, SBA,
+0.70 x 1056.0 x coil mm
+Weight (Kg):15,197
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+1,125.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
     <row r="601" xml:space="preserve">
       <c r="A601" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, SBA,
-0.70 x 1056.0 x coil mm</v>
+0.70 x 150.9 x coil mm</v>
       </c>
       <c r="B601" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, SBA,
-0.70 x 1056.0 x coil mm
-Weight (Kg):15,197
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-1,125.00 €/ton
+0.70 x 150.9 x coil mm
+Weight (Kg):1,268
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+1,000.00 €/ton
 Add to cart</v>
       </c>
     </row>
     <row r="602" xml:space="preserve">
       <c r="A602" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, SBA,
-0.70 x 150.9 x coil mm</v>
+0.70 x 173.0 x coil mm</v>
       </c>
       <c r="B602" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, SBA,
-0.70 x 150.9 x coil mm
-Weight (Kg):1,268
-Quality:Prime-2
+0.70 x 173.0 x coil mm
+Weight (Kg):890
+Quality:Prime
 Help
 Location:FABRICA ALGECIRAS
 1,000.00 €/ton
@@ -10026,13 +10026,13 @@
     <row r="603" xml:space="preserve">
       <c r="A603" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, SBA,
-0.70 x 173.0 x coil mm</v>
+0.70 x 195.9 x coil mm</v>
       </c>
       <c r="B603" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, SBA,
-0.70 x 173.0 x coil mm
-Weight (Kg):890
-Quality:Prime
+0.70 x 195.9 x coil mm
+Weight (Kg):962
+Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
 1,000.00 €/ton
@@ -10042,44 +10042,44 @@
     <row r="604" xml:space="preserve">
       <c r="A604" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, SBA,
-0.70 x 195.9 x coil mm</v>
+0.70 x 682.0 x coil mm</v>
       </c>
       <c r="B604" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, SBA,
-0.70 x 195.9 x coil mm
-Weight (Kg):962
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-1,000.00 €/ton
+0.70 x 682.0 x coil mm
+Weight (Kg):3,870
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+1,025.00 €/ton
 Add to cart</v>
       </c>
     </row>
     <row r="605" xml:space="preserve">
       <c r="A605" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, SBA,
-0.70 x 682.0 x coil mm</v>
+0.70 x 825.0 x coil mm</v>
       </c>
       <c r="B605" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, SBA,
-0.70 x 682.0 x coil mm
-Weight (Kg):3,870
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-1,025.00 €/ton
+0.70 x 825.0 x coil mm
+Weight (Kg):6,448
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+1,125.00 €/ton
 Add to cart</v>
       </c>
     </row>
     <row r="606" xml:space="preserve">
       <c r="A606" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, SBA,
-0.70 x 825.0 x coil mm</v>
+0.70 x 942.0 x coil mm</v>
       </c>
       <c r="B606" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, SBA,
-0.70 x 825.0 x coil mm
-Weight (Kg):6,448
+0.70 x 942.0 x coil mm
+Weight (Kg):1,810
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -10090,12 +10090,12 @@
     <row r="607" xml:space="preserve">
       <c r="A607" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, SBA,
-0.70 x 942.0 x coil mm</v>
+0.70 x 948.0 x coil mm</v>
       </c>
       <c r="B607" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, SBA,
-0.70 x 942.0 x coil mm
-Weight (Kg):1,810
+0.70 x 948.0 x coil mm
+Weight (Kg):3,410
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -10106,12 +10106,12 @@
     <row r="608" xml:space="preserve">
       <c r="A608" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, SBA,
-0.70 x 948.0 x coil mm</v>
+0.70 x 960.0 x coil mm</v>
       </c>
       <c r="B608" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, SBA,
-0.70 x 948.0 x coil mm
-Weight (Kg):3,410
+0.70 x 960.0 x coil mm
+Weight (Kg):2,780
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -10122,25 +10122,9 @@
     <row r="609" xml:space="preserve">
       <c r="A609" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, SBA,
-0.70 x 960.0 x coil mm</v>
+0.70 x 963.0 x coil mm</v>
       </c>
       <c r="B609" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, SBA,
-0.70 x 960.0 x coil mm
-Weight (Kg):2,780
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-1,125.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="610" xml:space="preserve">
-      <c r="A610" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, SBA,
-0.70 x 963.0 x coil mm</v>
-      </c>
-      <c r="B610" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Coil, SBA,
 0.70 x 963.0 x coil mm
 Weight (Kg):4,570
@@ -10148,6 +10132,22 @@
 Help
 Location:FABRICA ALGECIRAS
 1,325.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="610" xml:space="preserve">
+      <c r="A610" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Disk, BA,
+0.60 x 550.0 x 0.0 mm</v>
+      </c>
+      <c r="B610" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Disk, BA,
+0.60 x 550.0 x 0.0 mm
+Weight (Kg):578
+Quality:Prime
+Help
+Location:FABRICA ALGECIRAS
+1,900.00 €/ton
 Add to cart</v>
       </c>
     </row>
@@ -10159,7 +10159,7 @@
       <c r="B611" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Disk, BA,
 0.60 x 550.0 x 0.0 mm
-Weight (Kg):578
+Weight (Kg):572
 Quality:Prime
 Help
 Location:FABRICA ALGECIRAS
@@ -10175,7 +10175,7 @@
       <c r="B612" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Disk, BA,
 0.60 x 550.0 x 0.0 mm
-Weight (Kg):572
+Weight (Kg):576
 Quality:Prime
 Help
 Location:FABRICA ALGECIRAS
@@ -10191,7 +10191,7 @@
       <c r="B613" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Disk, BA,
 0.60 x 550.0 x 0.0 mm
-Weight (Kg):576
+Weight (Kg):578
 Quality:Prime
 Help
 Location:FABRICA ALGECIRAS
@@ -10207,7 +10207,7 @@
       <c r="B614" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Disk, BA,
 0.60 x 550.0 x 0.0 mm
-Weight (Kg):578
+Weight (Kg):582
 Quality:Prime
 Help
 Location:FABRICA ALGECIRAS
@@ -10217,29 +10217,29 @@
     </row>
     <row r="615" xml:space="preserve">
       <c r="A615" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Disk, BA,
-0.60 x 550.0 x 0.0 mm</v>
+        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Sheet, 2B,
+2.00 x 1250.0 x 2500.0 mm</v>
       </c>
       <c r="B615" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Disk, BA,
-0.60 x 550.0 x 0.0 mm
-Weight (Kg):582
-Quality:Prime
-Help
-Location:FABRICA ALGECIRAS
-1,900.00 €/ton
+        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Sheet, 2B,
+2.00 x 1250.0 x 2500.0 mm
+Weight (Kg):619
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+1,125.00 €/ton
 Add to cart</v>
       </c>
     </row>
     <row r="616" xml:space="preserve">
       <c r="A616" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Sheet, 2B,
-2.00 x 1250.0 x 2500.0 mm</v>
+3.00 x 1250.0 x 2500.0 mm</v>
       </c>
       <c r="B616" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Sheet, 2B,
-2.00 x 1250.0 x 2500.0 mm
-Weight (Kg):619
+3.00 x 1250.0 x 2500.0 mm
+Weight (Kg):566
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -10255,7 +10255,7 @@
       <c r="B617" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Sheet, 2B,
 3.00 x 1250.0 x 2500.0 mm
-Weight (Kg):566
+Weight (Kg):640
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -10265,26 +10265,10 @@
     </row>
     <row r="618" xml:space="preserve">
       <c r="A618" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Sheet, 2B,
-3.00 x 1250.0 x 2500.0 mm</v>
-      </c>
-      <c r="B618" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Sheet, 2B,
-3.00 x 1250.0 x 2500.0 mm
-Weight (Kg):640
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-1,125.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="619" xml:space="preserve">
-      <c r="A619" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Sheet, BA,
 0.70 x 1250.0 x 2500.0 mm</v>
       </c>
-      <c r="B619" t="str" xml:space="preserve">
+      <c r="B618" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Sheet, BA,
 0.70 x 1250.0 x 2500.0 mm
 Weight (Kg):766
@@ -10295,12 +10279,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="620" xml:space="preserve">
-      <c r="A620" t="str" xml:space="preserve">
+    <row r="619" xml:space="preserve">
+      <c r="A619" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Sheet, SB-G-400,
 1.00 x 1500.0 x 3000.0 mm</v>
       </c>
-      <c r="B620" t="str" xml:space="preserve">
+      <c r="B619" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Sheet, SB-G-400,
 1.00 x 1500.0 x 3000.0 mm
 Weight (Kg):1,940
@@ -10311,12 +10295,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="621" xml:space="preserve">
-      <c r="A621" t="str" xml:space="preserve">
+    <row r="620" xml:space="preserve">
+      <c r="A620" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Untrimmed, Coil, 1/4 HT,
 3.00 x 1292.0 x coil mm</v>
       </c>
-      <c r="B621" t="str" xml:space="preserve">
+      <c r="B620" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4016 430-Untrimmed, Coil, 1/4 HT,
 3.00 x 1292.0 x coil mm
 Weight (Kg):3,641
@@ -10325,6 +10309,22 @@
 Location:FABRICA ALGECIRAS
 1,125.00 €/ton
 Add to cart</v>
+      </c>
+    </row>
+    <row r="621" xml:space="preserve">
+      <c r="A621" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Untrimmed, Coil, 2B,
+0.40 x 1273.0 x coil mm</v>
+      </c>
+      <c r="B621" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Untrimmed, Coil, 2B,
+0.40 x 1273.0 x coil mm
+Weight (Kg):5,176
+Quality:Prime
+Help
+Location:FABRICA ALGECIRAS
+1,325.00 €/ton
+Reserved</v>
       </c>
     </row>
     <row r="622" xml:space="preserve">
@@ -10585,18 +10585,18 @@
     </row>
     <row r="638" xml:space="preserve">
       <c r="A638" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Untrimmed, Coil, 2B,
-0.40 x 1273.0 x coil mm</v>
+        <v xml:space="preserve">Acerinox Europa, 1.4510 430Ti-Coil, BA,
+0.70 x 905.0 x coil mm</v>
       </c>
       <c r="B638" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4016 430-Untrimmed, Coil, 2B,
-0.40 x 1273.0 x coil mm
-Weight (Kg):5,176
-Quality:Prime
-Help
-Location:FABRICA ALGECIRAS
-1,325.00 €/ton
-Reserved</v>
+        <v xml:space="preserve">Acerinox Europa, 1.4510 430Ti-Coil, BA,
+0.70 x 905.0 x coil mm
+Weight (Kg):9,410
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+1,125.00 €/ton
+Add to cart</v>
       </c>
     </row>
     <row r="639" xml:space="preserve">
@@ -10650,12 +10650,12 @@
     <row r="642" xml:space="preserve">
       <c r="A642" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4510 430Ti-Coil, BA,
-0.70 x 905.0 x coil mm</v>
+0.70 x 932.0 x coil mm</v>
       </c>
       <c r="B642" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4510 430Ti-Coil, BA,
-0.70 x 905.0 x coil mm
-Weight (Kg):9,410
+0.70 x 932.0 x coil mm
+Weight (Kg):2,270
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -10666,25 +10666,9 @@
     <row r="643" xml:space="preserve">
       <c r="A643" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4510 430Ti-Coil, BA,
-0.70 x 932.0 x coil mm</v>
+0.70 x 940.0 x coil mm</v>
       </c>
       <c r="B643" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4510 430Ti-Coil, BA,
-0.70 x 932.0 x coil mm
-Weight (Kg):2,270
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-1,125.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="644" xml:space="preserve">
-      <c r="A644" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4510 430Ti-Coil, BA,
-0.70 x 940.0 x coil mm</v>
-      </c>
-      <c r="B644" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4510 430Ti-Coil, BA,
 0.70 x 940.0 x coil mm
 Weight (Kg):14,920
@@ -10695,28 +10679,28 @@
 Add to cart</v>
       </c>
     </row>
+    <row r="644" xml:space="preserve">
+      <c r="A644" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4510 430Ti-Untrimmed, Coil, BA,
+0.50 x 1275.0 x coil mm</v>
+      </c>
+      <c r="B644" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4510 430Ti-Untrimmed, Coil, BA,
+0.50 x 1275.0 x coil mm
+Weight (Kg):2,258
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+1,125.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
     <row r="645" xml:space="preserve">
       <c r="A645" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4510 430Ti-Untrimmed, Coil, BA,
-0.50 x 1275.0 x coil mm</v>
+0.70 x 928.0 x coil mm</v>
       </c>
       <c r="B645" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4510 430Ti-Untrimmed, Coil, BA,
-0.50 x 1275.0 x coil mm
-Weight (Kg):2,258
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-1,125.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="646" xml:space="preserve">
-      <c r="A646" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4510 430Ti-Untrimmed, Coil, BA,
-0.70 x 928.0 x coil mm</v>
-      </c>
-      <c r="B646" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4510 430Ti-Untrimmed, Coil, BA,
 0.70 x 928.0 x coil mm
 Weight (Kg):4,257
@@ -10727,12 +10711,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="647" xml:space="preserve">
-      <c r="A647" t="str" xml:space="preserve">
+    <row r="646" xml:space="preserve">
+      <c r="A646" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4509 441-Coil, 2B,
 1.20 x 275.9 x coil mm</v>
       </c>
-      <c r="B647" t="str" xml:space="preserve">
+      <c r="B646" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4509 441-Coil, 2B,
 1.20 x 275.9 x coil mm
 Weight (Kg):2,416
@@ -10743,15 +10727,31 @@
 Add to cart</v>
       </c>
     </row>
+    <row r="647" xml:space="preserve">
+      <c r="A647" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4509 441-Coil, 2D,
+1.20 x 196.0 x coil mm</v>
+      </c>
+      <c r="B647" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4509 441-Coil, 2D,
+1.20 x 196.0 x coil mm
+Weight (Kg):2,970
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+1,100.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
     <row r="648" xml:space="preserve">
       <c r="A648" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4509 441-Coil, 2D,
-1.20 x 196.0 x coil mm</v>
+1.20 x 200.0 x coil mm</v>
       </c>
       <c r="B648" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4509 441-Coil, 2D,
-1.20 x 196.0 x coil mm
-Weight (Kg):2,970
+1.20 x 200.0 x coil mm
+Weight (Kg):3,310
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -10762,12 +10762,12 @@
     <row r="649" xml:space="preserve">
       <c r="A649" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4509 441-Coil, 2D,
-1.20 x 200.0 x coil mm</v>
+1.20 x 214.9 x coil mm</v>
       </c>
       <c r="B649" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4509 441-Coil, 2D,
-1.20 x 200.0 x coil mm
-Weight (Kg):3,310
+1.20 x 214.9 x coil mm
+Weight (Kg):3,220
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -10778,12 +10778,12 @@
     <row r="650" xml:space="preserve">
       <c r="A650" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4509 441-Coil, 2D,
-1.20 x 214.9 x coil mm</v>
+1.20 x 223.9 x coil mm</v>
       </c>
       <c r="B650" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4509 441-Coil, 2D,
-1.20 x 214.9 x coil mm
-Weight (Kg):3,220
+1.20 x 223.9 x coil mm
+Weight (Kg):3,798
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -10794,28 +10794,28 @@
     <row r="651" xml:space="preserve">
       <c r="A651" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4509 441-Coil, 2D,
-1.20 x 223.9 x coil mm</v>
+1.20 x 224.0 x coil mm</v>
       </c>
       <c r="B651" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4509 441-Coil, 2D,
-1.20 x 223.9 x coil mm
-Weight (Kg):3,798
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-1,100.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="652" xml:space="preserve">
-      <c r="A652" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4509 441-Coil, 2D,
-1.20 x 224.0 x coil mm</v>
-      </c>
-      <c r="B652" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4509 441-Coil, 2D,
 1.20 x 224.0 x coil mm
 Weight (Kg):3,808
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+1,100.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="652" xml:space="preserve">
+      <c r="A652" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4509 441-Coil, BA,
+0.80 x 130.9 x coil mm</v>
+      </c>
+      <c r="B652" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 1.4509 441-Coil, BA,
+0.80 x 130.9 x coil mm
+Weight (Kg):245
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -10847,7 +10847,7 @@
       <c r="B654" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4509 441-Coil, BA,
 0.80 x 130.9 x coil mm
-Weight (Kg):245
+Weight (Kg):213
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -10863,7 +10863,7 @@
       <c r="B655" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4509 441-Coil, BA,
 0.80 x 130.9 x coil mm
-Weight (Kg):213
+Weight (Kg):244
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -10873,45 +10873,45 @@
     </row>
     <row r="656" xml:space="preserve">
       <c r="A656" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4509 441-Coil, BA,
-0.80 x 130.9 x coil mm</v>
+        <v xml:space="preserve">Acerinox Europa, 1.4509 441-Coil, SB-G-400,
+1.00 x 1000.0 x coil mm</v>
       </c>
       <c r="B656" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4509 441-Coil, BA,
-0.80 x 130.9 x coil mm
-Weight (Kg):244
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-1,100.00 €/ton
+        <v xml:space="preserve">Acerinox Europa, 1.4509 441-Coil, SB-G-400,
+1.00 x 1000.0 x coil mm
+Weight (Kg):7,550
+Quality:Prime
+Help
+Location:FABRICA ALGECIRAS
+1,625.00 €/ton
 Add to cart</v>
       </c>
     </row>
     <row r="657" xml:space="preserve">
       <c r="A657" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4509 441-Coil, SB-G-400,
-1.00 x 1000.0 x coil mm</v>
+1.00 x 255.0 x coil mm</v>
       </c>
       <c r="B657" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4509 441-Coil, SB-G-400,
-1.00 x 1000.0 x coil mm
-Weight (Kg):7,550
-Quality:Prime
-Help
-Location:FABRICA ALGECIRAS
-1,625.00 €/ton
+1.00 x 255.0 x coil mm
+Weight (Kg):2,182
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+1,100.00 €/ton
 Add to cart</v>
       </c>
     </row>
     <row r="658" xml:space="preserve">
       <c r="A658" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4509 441-Coil, SB-G-400,
-1.00 x 255.0 x coil mm</v>
+1.00 x 290.9 x coil mm</v>
       </c>
       <c r="B658" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4509 441-Coil, SB-G-400,
-1.00 x 255.0 x coil mm
-Weight (Kg):2,182
+1.00 x 290.9 x coil mm
+Weight (Kg):2,370
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -10922,12 +10922,12 @@
     <row r="659" xml:space="preserve">
       <c r="A659" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4509 441-Coil, SB-G-400,
-1.00 x 290.9 x coil mm</v>
+1.20 x 110.9 x coil mm</v>
       </c>
       <c r="B659" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4509 441-Coil, SB-G-400,
-1.00 x 290.9 x coil mm
-Weight (Kg):2,370
+1.20 x 110.9 x coil mm
+Weight (Kg):856
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -10938,12 +10938,12 @@
     <row r="660" xml:space="preserve">
       <c r="A660" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4509 441-Coil, SB-G-400,
-1.20 x 110.9 x coil mm</v>
+1.20 x 130.9 x coil mm</v>
       </c>
       <c r="B660" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4509 441-Coil, SB-G-400,
-1.20 x 110.9 x coil mm
-Weight (Kg):856
+1.20 x 130.9 x coil mm
+Weight (Kg):564
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -10959,8 +10959,8 @@
       <c r="B661" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4509 441-Coil, SB-G-400,
 1.20 x 130.9 x coil mm
-Weight (Kg):564
-Quality:Prime-2
+Weight (Kg):532
+Quality:Prime
 Help
 Location:FABRICA ALGECIRAS
 1,100.00 €/ton
@@ -10970,13 +10970,13 @@
     <row r="662" xml:space="preserve">
       <c r="A662" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4509 441-Coil, SB-G-400,
-1.20 x 130.9 x coil mm</v>
+1.50 x 130.9 x coil mm</v>
       </c>
       <c r="B662" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4509 441-Coil, SB-G-400,
-1.20 x 130.9 x coil mm
-Weight (Kg):532
-Quality:Prime
+1.50 x 130.9 x coil mm
+Weight (Kg):640
+Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
 1,100.00 €/ton
@@ -10986,25 +10986,9 @@
     <row r="663" xml:space="preserve">
       <c r="A663" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4509 441-Coil, SB-G-400,
-1.50 x 130.9 x coil mm</v>
+1.50 x 360.0 x coil mm</v>
       </c>
       <c r="B663" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4509 441-Coil, SB-G-400,
-1.50 x 130.9 x coil mm
-Weight (Kg):640
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-1,100.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="664" xml:space="preserve">
-      <c r="A664" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 1.4509 441-Coil, SB-G-400,
-1.50 x 360.0 x coil mm</v>
-      </c>
-      <c r="B664" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4509 441-Coil, SB-G-400,
 1.50 x 360.0 x coil mm
 Weight (Kg):1,488
@@ -11015,12 +10999,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="665" xml:space="preserve">
-      <c r="A665" t="str" xml:space="preserve">
+    <row r="664" xml:space="preserve">
+      <c r="A664" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4509 441-Untrimmed, Coil, 2B,
 1.50 x 1539.0 x coil mm</v>
       </c>
-      <c r="B665" t="str" xml:space="preserve">
+      <c r="B664" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4509 441-Untrimmed, Coil, 2B,
 1.50 x 1539.0 x coil mm
 Weight (Kg):14,230
@@ -11031,12 +11015,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="666" xml:space="preserve">
-      <c r="A666" t="str" xml:space="preserve">
+    <row r="665" xml:space="preserve">
+      <c r="A665" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4509 441-Untrimmed, Coil, BA,
 0.40 x 1075.0 x coil mm</v>
       </c>
-      <c r="B666" t="str" xml:space="preserve">
+      <c r="B665" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4509 441-Untrimmed, Coil, BA,
 0.40 x 1075.0 x coil mm
 Weight (Kg):9,750
@@ -11047,12 +11031,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="667" xml:space="preserve">
-      <c r="A667" t="str" xml:space="preserve">
+    <row r="666" xml:space="preserve">
+      <c r="A666" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4509 441-Untrimmed, Coil, Nb. 1,
 5.00 x 1045.0 x coil mm</v>
       </c>
-      <c r="B667" t="str" xml:space="preserve">
+      <c r="B666" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 1.4509 441-Untrimmed, Coil, Nb. 1,
 5.00 x 1045.0 x coil mm
 Weight (Kg):7,880
@@ -11063,12 +11047,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="668" xml:space="preserve">
-      <c r="A668" t="str" xml:space="preserve">
+    <row r="667" xml:space="preserve">
+      <c r="A667" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 441-1.4509 Coil, 2B,
 1.20 x 240.9 x coil mm</v>
       </c>
-      <c r="B668" t="str" xml:space="preserve">
+      <c r="B667" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 441-1.4509 Coil, 2B,
 1.20 x 240.9 x coil mm
 Weight (Kg):3,882
@@ -11079,12 +11063,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="669" xml:space="preserve">
-      <c r="A669" t="str" xml:space="preserve">
+    <row r="668" xml:space="preserve">
+      <c r="A668" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 304-1.4301 Coil,
 0.70 x 270.9 x coil mm</v>
       </c>
-      <c r="B669" t="str" xml:space="preserve">
+      <c r="B668" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 304-1.4301 Coil,
 0.70 x 270.9 x coil mm
 Weight (Kg):2,704
@@ -11095,12 +11079,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="670" xml:space="preserve">
-      <c r="A670" t="str" xml:space="preserve">
+    <row r="669" xml:space="preserve">
+      <c r="A669" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 316L-1.4404 Coil,
 1.20 x 136.0 x coil mm</v>
       </c>
-      <c r="B670" t="str" xml:space="preserve">
+      <c r="B669" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 316L-1.4404 Coil,
 1.20 x 136.0 x coil mm
 Weight (Kg):2,300
@@ -11111,12 +11095,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="671" xml:space="preserve">
-      <c r="A671" t="str" xml:space="preserve">
+    <row r="670" xml:space="preserve">
+      <c r="A670" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 304L/304-4301/4307 Coil, 2B,
 6.00 x 245.0 x coil mm</v>
       </c>
-      <c r="B671" t="str" xml:space="preserve">
+      <c r="B670" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 304L/304-4301/4307 Coil, 2B,
 6.00 x 245.0 x coil mm
 Weight (Kg):2,394
@@ -11127,12 +11111,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="672" xml:space="preserve">
-      <c r="A672" t="str" xml:space="preserve">
+    <row r="671" xml:space="preserve">
+      <c r="A671" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, 2B,
 0.70 x 197.5 x coil mm</v>
       </c>
-      <c r="B672" t="str" xml:space="preserve">
+      <c r="B671" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, 2B,
 0.70 x 197.5 x coil mm
 Weight (Kg):2,442
@@ -11143,12 +11127,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="673" xml:space="preserve">
-      <c r="A673" t="str" xml:space="preserve">
+    <row r="672" xml:space="preserve">
+      <c r="A672" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 441-1.4509 Coil, 2B,
 2.00 x 120.9 x coil mm</v>
       </c>
-      <c r="B673" t="str" xml:space="preserve">
+      <c r="B672" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 441-1.4509 Coil, 2B,
 2.00 x 120.9 x coil mm
 Weight (Kg):1,956
@@ -11156,6 +11140,22 @@
 Help
 Location:FABRICA ALGECIRAS
 1,100.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="673" xml:space="preserve">
+      <c r="A673" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 304-1.4301 Coil, 2B,
+1.20 x 119.9 x coil mm</v>
+      </c>
+      <c r="B673" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 304-1.4301 Coil, 2B,
+1.20 x 119.9 x coil mm
+Weight (Kg):1,500
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,075.00 €/ton
 Add to cart</v>
       </c>
     </row>
@@ -11167,7 +11167,7 @@
       <c r="B674" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 304-1.4301 Coil, 2B,
 1.20 x 119.9 x coil mm
-Weight (Kg):1,500
+Weight (Kg):1,400
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -11177,29 +11177,29 @@
     </row>
     <row r="675" xml:space="preserve">
       <c r="A675" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 304-1.4301 Coil, 2B,
-1.20 x 119.9 x coil mm</v>
+        <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, BA,
+0.70 x 125.0 x coil mm</v>
       </c>
       <c r="B675" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 304-1.4301 Coil, 2B,
-1.20 x 119.9 x coil mm
-Weight (Kg):1,400
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-2,075.00 €/ton
+        <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, BA,
+0.70 x 125.0 x coil mm
+Weight (Kg):1,764
+Quality:Prime
+Help
+Location:FABRICA ALGECIRAS
+1,000.00 €/ton
 Add to cart</v>
       </c>
     </row>
     <row r="676" xml:space="preserve">
       <c r="A676" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, BA,
-0.70 x 125.0 x coil mm</v>
+0.70 x 104.9 x coil mm</v>
       </c>
       <c r="B676" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, BA,
-0.70 x 125.0 x coil mm
-Weight (Kg):1,764
+0.70 x 104.9 x coil mm
+Weight (Kg):1,240
 Quality:Prime
 Help
 Location:FABRICA ALGECIRAS
@@ -11210,12 +11210,12 @@
     <row r="677" xml:space="preserve">
       <c r="A677" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, BA,
-0.70 x 104.9 x coil mm</v>
+0.70 x 118.9 x coil mm</v>
       </c>
       <c r="B677" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, BA,
-0.70 x 104.9 x coil mm
-Weight (Kg):1,240
+0.70 x 118.9 x coil mm
+Weight (Kg):1,802
 Quality:Prime
 Help
 Location:FABRICA ALGECIRAS
@@ -11226,12 +11226,12 @@
     <row r="678" xml:space="preserve">
       <c r="A678" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, BA,
-0.70 x 118.9 x coil mm</v>
+0.70 x 115.9 x coil mm</v>
       </c>
       <c r="B678" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, BA,
-0.70 x 118.9 x coil mm
-Weight (Kg):1,802
+0.70 x 115.9 x coil mm
+Weight (Kg):1,368
 Quality:Prime
 Help
 Location:FABRICA ALGECIRAS
@@ -11242,25 +11242,9 @@
     <row r="679" xml:space="preserve">
       <c r="A679" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, BA,
-0.70 x 115.9 x coil mm</v>
+0.70 x 119.0 x coil mm</v>
       </c>
       <c r="B679" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, BA,
-0.70 x 115.9 x coil mm
-Weight (Kg):1,368
-Quality:Prime
-Help
-Location:FABRICA ALGECIRAS
-1,000.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="680" xml:space="preserve">
-      <c r="A680" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, BA,
-0.70 x 119.0 x coil mm</v>
-      </c>
-      <c r="B680" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, BA,
 0.70 x 119.0 x coil mm
 Weight (Kg):1,622
@@ -11271,12 +11255,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="681" xml:space="preserve">
-      <c r="A681" t="str" xml:space="preserve">
+    <row r="680" xml:space="preserve">
+      <c r="A680" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 304L/304-4301/4307 Coil, 2B,
 1.40 x 110.9 x coil mm</v>
       </c>
-      <c r="B681" t="str" xml:space="preserve">
+      <c r="B680" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 304L/304-4301/4307 Coil, 2B,
 1.40 x 110.9 x coil mm
 Weight (Kg):1,240
@@ -11284,6 +11268,22 @@
 Help
 Location:FABRICA ALGECIRAS
 2,075.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="681" xml:space="preserve">
+      <c r="A681" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, BA,
+0.70 x 104.0 x coil mm</v>
+      </c>
+      <c r="B681" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, BA,
+0.70 x 104.0 x coil mm
+Weight (Kg):1,622
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+1,000.00 €/ton
 Add to cart</v>
       </c>
     </row>
@@ -11295,7 +11295,7 @@
       <c r="B682" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, BA,
 0.70 x 104.0 x coil mm
-Weight (Kg):1,622
+Weight (Kg):1,688
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -11305,26 +11305,10 @@
     </row>
     <row r="683" xml:space="preserve">
       <c r="A683" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, BA,
-0.70 x 104.0 x coil mm</v>
-      </c>
-      <c r="B683" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, BA,
-0.70 x 104.0 x coil mm
-Weight (Kg):1,688
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-1,000.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="684" xml:space="preserve">
-      <c r="A684" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 304L/304-4301/4307 Coil, 2B,
 1.40 x 110.9 x coil mm</v>
       </c>
-      <c r="B684" t="str" xml:space="preserve">
+      <c r="B683" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 304L/304-4301/4307 Coil, 2B,
 1.40 x 110.9 x coil mm
 Weight (Kg):1,162
@@ -11332,6 +11316,22 @@
 Help
 Location:FABRICA ALGECIRAS
 2,075.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="684" xml:space="preserve">
+      <c r="A684" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 430Ti-1.4510 Coil, BA,
+0.70 x 165.9 x coil mm</v>
+      </c>
+      <c r="B684" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 430Ti-1.4510 Coil, BA,
+0.70 x 165.9 x coil mm
+Weight (Kg):2,692
+Quality:Prime
+Help
+Location:FABRICA ALGECIRAS
+1,000.00 €/ton
 Add to cart</v>
       </c>
     </row>
@@ -11343,8 +11343,8 @@
       <c r="B685" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 430Ti-1.4510 Coil, BA,
 0.70 x 165.9 x coil mm
-Weight (Kg):2,692
-Quality:Prime
+Weight (Kg):2,756
+Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
 1,000.00 €/ton
@@ -11353,13 +11353,13 @@
     </row>
     <row r="686" xml:space="preserve">
       <c r="A686" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 430Ti-1.4510 Coil, BA,
-0.70 x 165.9 x coil mm</v>
+        <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, BA,
+0.70 x 140.9 x coil mm</v>
       </c>
       <c r="B686" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 430Ti-1.4510 Coil, BA,
-0.70 x 165.9 x coil mm
-Weight (Kg):2,756
+        <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, BA,
+0.70 x 140.9 x coil mm
+Weight (Kg):1,676
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -11370,12 +11370,12 @@
     <row r="687" xml:space="preserve">
       <c r="A687" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, BA,
-0.70 x 140.9 x coil mm</v>
+0.70 x 100.9 x coil mm</v>
       </c>
       <c r="B687" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, BA,
-0.70 x 140.9 x coil mm
-Weight (Kg):1,676
+0.70 x 100.9 x coil mm
+Weight (Kg):1,340
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -11386,12 +11386,12 @@
     <row r="688" xml:space="preserve">
       <c r="A688" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, BA,
-0.70 x 100.9 x coil mm</v>
+0.70 x 125.0 x coil mm</v>
       </c>
       <c r="B688" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, BA,
-0.70 x 100.9 x coil mm
-Weight (Kg):1,340
+0.70 x 125.0 x coil mm
+Weight (Kg):1,550
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -11407,7 +11407,7 @@
       <c r="B689" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, BA,
 0.70 x 125.0 x coil mm
-Weight (Kg):1,550
+Weight (Kg):1,414
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -11418,25 +11418,9 @@
     <row r="690" xml:space="preserve">
       <c r="A690" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, BA,
-0.70 x 125.0 x coil mm</v>
+0.70 x 100.9 x coil mm</v>
       </c>
       <c r="B690" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, BA,
-0.70 x 125.0 x coil mm
-Weight (Kg):1,414
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-1,000.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="691" xml:space="preserve">
-      <c r="A691" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, BA,
-0.70 x 100.9 x coil mm</v>
-      </c>
-      <c r="B691" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, BA,
 0.70 x 100.9 x coil mm
 Weight (Kg):2,188
@@ -11444,6 +11428,22 @@
 Help
 Location:FABRICA ALGECIRAS
 1,000.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="691" xml:space="preserve">
+      <c r="A691" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 304L/304-4301/4307 Coil, Nb. 1,
+4.70 x 110.0 x coil mm</v>
+      </c>
+      <c r="B691" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 304L/304-4301/4307 Coil, Nb. 1,
+4.70 x 110.0 x coil mm
+Weight (Kg):1,796
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+1,975.00 €/ton
 Add to cart</v>
       </c>
     </row>
@@ -11455,7 +11455,7 @@
       <c r="B692" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 304L/304-4301/4307 Coil, Nb. 1,
 4.70 x 110.0 x coil mm
-Weight (Kg):1,796
+Weight (Kg):2,038
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -11465,26 +11465,10 @@
     </row>
     <row r="693" xml:space="preserve">
       <c r="A693" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 304L/304-4301/4307 Coil, Nb. 1,
-4.70 x 110.0 x coil mm</v>
-      </c>
-      <c r="B693" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 304L/304-4301/4307 Coil, Nb. 1,
-4.70 x 110.0 x coil mm
-Weight (Kg):2,038
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-1,975.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="694" xml:space="preserve">
-      <c r="A694" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, BA,
 0.70 x 165.9 x coil mm</v>
       </c>
-      <c r="B694" t="str" xml:space="preserve">
+      <c r="B693" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, BA,
 0.70 x 165.9 x coil mm
 Weight (Kg):2,620
@@ -11492,6 +11476,22 @@
 Help
 Location:FABRICA ALGECIRAS
 1,000.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="694" xml:space="preserve">
+      <c r="A694" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 304-1.4301 Coil,
+0.70 x 260.9 x coil mm</v>
+      </c>
+      <c r="B694" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 304-1.4301 Coil,
+0.70 x 260.9 x coil mm
+Weight (Kg):1,330
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,075.00 €/ton
 Add to cart</v>
       </c>
     </row>
@@ -11503,7 +11503,7 @@
       <c r="B695" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 304-1.4301 Coil,
 0.70 x 260.9 x coil mm
-Weight (Kg):1,330
+Weight (Kg):1,264
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -11513,42 +11513,26 @@
     </row>
     <row r="696" xml:space="preserve">
       <c r="A696" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 304-1.4301 Coil,
-0.70 x 260.9 x coil mm</v>
+        <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, BA,
+0.70 x 110.0 x coil mm</v>
       </c>
       <c r="B696" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 304-1.4301 Coil,
-0.70 x 260.9 x coil mm
-Weight (Kg):1,264
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-2,075.00 €/ton
+        <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, BA,
+0.70 x 110.0 x coil mm
+Weight (Kg):1,250
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+1,000.00 €/ton
 Add to cart</v>
       </c>
     </row>
     <row r="697" xml:space="preserve">
       <c r="A697" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, BA,
-0.70 x 110.0 x coil mm</v>
+0.70 x 122.9 x coil mm</v>
       </c>
       <c r="B697" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, BA,
-0.70 x 110.0 x coil mm
-Weight (Kg):1,250
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-1,000.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="698" xml:space="preserve">
-      <c r="A698" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, BA,
-0.70 x 122.9 x coil mm</v>
-      </c>
-      <c r="B698" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, BA,
 0.70 x 122.9 x coil mm
 Weight (Kg):1,460
@@ -11556,6 +11540,22 @@
 Help
 Location:FABRICA ALGECIRAS
 1,000.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="698" xml:space="preserve">
+      <c r="A698" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 304L/304-4301/4307 Coil, 2B,
+1.40 x 110.0 x coil mm</v>
+      </c>
+      <c r="B698" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 304L/304-4301/4307 Coil, 2B,
+1.40 x 110.0 x coil mm
+Weight (Kg):1,554
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,075.00 €/ton
 Add to cart</v>
       </c>
     </row>
@@ -11567,7 +11567,7 @@
       <c r="B699" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 304L/304-4301/4307 Coil, 2B,
 1.40 x 110.0 x coil mm
-Weight (Kg):1,554
+Weight (Kg):1,586
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -11578,25 +11578,9 @@
     <row r="700" xml:space="preserve">
       <c r="A700" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 304L/304-4301/4307 Coil, 2B,
-1.40 x 110.0 x coil mm</v>
+1.40 x 104.0 x coil mm</v>
       </c>
       <c r="B700" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 304L/304-4301/4307 Coil, 2B,
-1.40 x 110.0 x coil mm
-Weight (Kg):1,586
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-2,075.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="701" xml:space="preserve">
-      <c r="A701" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 304L/304-4301/4307 Coil, 2B,
-1.40 x 104.0 x coil mm</v>
-      </c>
-      <c r="B701" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 304L/304-4301/4307 Coil, 2B,
 1.40 x 104.0 x coil mm
 Weight (Kg):1,030
@@ -11607,12 +11591,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="702" xml:space="preserve">
-      <c r="A702" t="str" xml:space="preserve">
+    <row r="701" xml:space="preserve">
+      <c r="A701" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 304DDQ-1.4301 Coil, BA,
 0.70 x 181.9 x coil mm</v>
       </c>
-      <c r="B702" t="str" xml:space="preserve">
+      <c r="B701" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 304DDQ-1.4301 Coil, BA,
 0.70 x 181.9 x coil mm
 Weight (Kg):2,912
@@ -11623,12 +11607,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="703" xml:space="preserve">
-      <c r="A703" t="str" xml:space="preserve">
+    <row r="702" xml:space="preserve">
+      <c r="A702" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 304-1.4301 Coil,
 1.50 x 136.0 x coil mm</v>
       </c>
-      <c r="B703" t="str" xml:space="preserve">
+      <c r="B702" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 304-1.4301 Coil,
 1.50 x 136.0 x coil mm
 Weight (Kg):3,450
@@ -11639,12 +11623,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="704" xml:space="preserve">
-      <c r="A704" t="str" xml:space="preserve">
+    <row r="703" xml:space="preserve">
+      <c r="A703" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 304-1.4301 Coil, BA,
 0.40 x 200.0 x coil mm</v>
       </c>
-      <c r="B704" t="str" xml:space="preserve">
+      <c r="B703" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 304-1.4301 Coil, BA,
 0.40 x 200.0 x coil mm
 Weight (Kg):1,964
@@ -11655,12 +11639,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="705" xml:space="preserve">
-      <c r="A705" t="str" xml:space="preserve">
+    <row r="704" xml:space="preserve">
+      <c r="A704" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 304-1.4301 Coil, BA, ET-60
 0.60 x 120.0 x coil mm</v>
       </c>
-      <c r="B705" t="str" xml:space="preserve">
+      <c r="B704" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 304-1.4301 Coil, BA, ET-60
 0.60 x 120.0 x coil mm
 Weight (Kg):1,302
@@ -11668,6 +11652,22 @@
 Help
 Location:FABRICA ALGECIRAS
 2,075.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="705" xml:space="preserve">
+      <c r="A705" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, ET-100
+0.70 x 124.9 x coil mm</v>
+      </c>
+      <c r="B705" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, ET-100
+0.70 x 124.9 x coil mm
+Weight (Kg):2,106
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+1,000.00 €/ton
 Add to cart</v>
       </c>
     </row>
@@ -11679,7 +11679,7 @@
       <c r="B706" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, ET-100
 0.70 x 124.9 x coil mm
-Weight (Kg):2,106
+Weight (Kg):1,972
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -11689,26 +11689,10 @@
     </row>
     <row r="707" xml:space="preserve">
       <c r="A707" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, ET-100
-0.70 x 124.9 x coil mm</v>
-      </c>
-      <c r="B707" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, ET-100
-0.70 x 124.9 x coil mm
-Weight (Kg):1,972
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-1,000.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="708" xml:space="preserve">
-      <c r="A708" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 430Ti-1.4510 Coil, 2B,
 0.80 x 155.9 x coil mm</v>
       </c>
-      <c r="B708" t="str" xml:space="preserve">
+      <c r="B707" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 430Ti-1.4510 Coil, 2B,
 0.80 x 155.9 x coil mm
 Weight (Kg):1,586
@@ -11719,12 +11703,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="709" xml:space="preserve">
-      <c r="A709" t="str" xml:space="preserve">
+    <row r="708" xml:space="preserve">
+      <c r="A708" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 304-1.4301 Coil, BA,
 0.40 x 270.0 x coil mm</v>
       </c>
-      <c r="B709" t="str" xml:space="preserve">
+      <c r="B708" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 304-1.4301 Coil, BA,
 0.40 x 270.0 x coil mm
 Weight (Kg):2,572
@@ -11735,12 +11719,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="710" xml:space="preserve">
-      <c r="A710" t="str" xml:space="preserve">
+    <row r="709" xml:space="preserve">
+      <c r="A709" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, BA,
 0.60 x 130.0 x coil mm</v>
       </c>
-      <c r="B710" t="str" xml:space="preserve">
+      <c r="B709" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, BA,
 0.60 x 130.0 x coil mm
 Weight (Kg):1,490
@@ -11748,6 +11732,22 @@
 Help
 Location:FABRICA ALGECIRAS
 1,000.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="710" xml:space="preserve">
+      <c r="A710" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 441-1.4509 Coil, BA,
+0.40 x 110.0 x coil mm</v>
+      </c>
+      <c r="B710" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 441-1.4509 Coil, BA,
+0.40 x 110.0 x coil mm
+Weight (Kg):1,870
+Quality:Prime
+Help
+Location:FABRICA ALGECIRAS
+1,100.00 €/ton
 Add to cart</v>
       </c>
     </row>
@@ -11759,7 +11759,7 @@
       <c r="B711" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 441-1.4509 Coil, BA,
 0.40 x 110.0 x coil mm
-Weight (Kg):1,870
+Weight (Kg):1,882
 Quality:Prime
 Help
 Location:FABRICA ALGECIRAS
@@ -11769,17 +11769,17 @@
     </row>
     <row r="712" xml:space="preserve">
       <c r="A712" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 441-1.4509 Coil, BA,
+        <v xml:space="preserve">Acerinox Europa, 301-1.4310 Coil, BA,
 0.40 x 110.0 x coil mm</v>
       </c>
       <c r="B712" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 441-1.4509 Coil, BA,
+        <v xml:space="preserve">Acerinox Europa, 301-1.4310 Coil, BA,
 0.40 x 110.0 x coil mm
-Weight (Kg):1,882
-Quality:Prime
-Help
-Location:FABRICA ALGECIRAS
-1,100.00 €/ton
+Weight (Kg):1,934
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+1,925.00 €/ton
 Add to cart</v>
       </c>
     </row>
@@ -11791,7 +11791,7 @@
       <c r="B713" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 301-1.4310 Coil, BA,
 0.40 x 110.0 x coil mm
-Weight (Kg):1,934
+Weight (Kg):1,860
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -11801,26 +11801,10 @@
     </row>
     <row r="714" xml:space="preserve">
       <c r="A714" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 301-1.4310 Coil, BA,
-0.40 x 110.0 x coil mm</v>
-      </c>
-      <c r="B714" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 301-1.4310 Coil, BA,
-0.40 x 110.0 x coil mm
-Weight (Kg):1,860
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-1,925.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="715" xml:space="preserve">
-      <c r="A715" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 321-1.4541 Coil, 2B,
 1.90 x 104.5 x coil mm</v>
       </c>
-      <c r="B715" t="str" xml:space="preserve">
+      <c r="B714" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 321-1.4541 Coil, 2B,
 1.90 x 104.5 x coil mm
 Weight (Kg):2,304
@@ -11831,12 +11815,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="716" xml:space="preserve">
-      <c r="A716" t="str" xml:space="preserve">
+    <row r="715" xml:space="preserve">
+      <c r="A715" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 304L/304-4301/4307 Coil, Polished N4-G-180,
 1.20 x 255.9 x coil mm</v>
       </c>
-      <c r="B716" t="str" xml:space="preserve">
+      <c r="B715" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 304L/304-4301/4307 Coil, Polished N4-G-180,
 1.20 x 255.9 x coil mm
 Weight (Kg):4,298
@@ -11847,12 +11831,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="717" xml:space="preserve">
-      <c r="A717" t="str" xml:space="preserve">
+    <row r="716" xml:space="preserve">
+      <c r="A716" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 301-1.4310 Coil, BA,
 0.40 x 110.0 x coil mm</v>
       </c>
-      <c r="B717" t="str" xml:space="preserve">
+      <c r="B716" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 301-1.4310 Coil, BA,
 0.40 x 110.0 x coil mm
 Weight (Kg):1,698
@@ -11863,15 +11847,31 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="718" xml:space="preserve">
-      <c r="A718" t="str" xml:space="preserve">
+    <row r="717" xml:space="preserve">
+      <c r="A717" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, BA,
 0.40 x 130.0 x coil mm</v>
       </c>
-      <c r="B718" t="str" xml:space="preserve">
+      <c r="B717" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, BA,
 0.40 x 130.0 x coil mm
 Weight (Kg):1,916
+Quality:Prime
+Help
+Location:FABRICA ALGECIRAS
+1,000.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
+    <row r="718" xml:space="preserve">
+      <c r="A718" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 430Ti-1.4510 Coil, BA,
+0.50 x 140.0 x coil mm</v>
+      </c>
+      <c r="B718" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 430Ti-1.4510 Coil, BA,
+0.50 x 140.0 x coil mm
+Weight (Kg):3,054
 Quality:Prime
 Help
 Location:FABRICA ALGECIRAS
@@ -11887,7 +11887,7 @@
       <c r="B719" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 430Ti-1.4510 Coil, BA,
 0.50 x 140.0 x coil mm
-Weight (Kg):3,054
+Weight (Kg):3,060
 Quality:Prime
 Help
 Location:FABRICA ALGECIRAS
@@ -11903,7 +11903,7 @@
       <c r="B720" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 430Ti-1.4510 Coil, BA,
 0.50 x 140.0 x coil mm
-Weight (Kg):3,060
+Weight (Kg):2,220
 Quality:Prime
 Help
 Location:FABRICA ALGECIRAS
@@ -11919,7 +11919,7 @@
       <c r="B721" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 430Ti-1.4510 Coil, BA,
 0.50 x 140.0 x coil mm
-Weight (Kg):2,220
+Weight (Kg):2,224
 Quality:Prime
 Help
 Location:FABRICA ALGECIRAS
@@ -11929,17 +11929,17 @@
     </row>
     <row r="722" xml:space="preserve">
       <c r="A722" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 430Ti-1.4510 Coil, BA,
-0.50 x 140.0 x coil mm</v>
+        <v xml:space="preserve">Acerinox Europa, 304L/304-4301/4307 Coil, 2B,
+1.40 x 100.9 x coil mm</v>
       </c>
       <c r="B722" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 430Ti-1.4510 Coil, BA,
-0.50 x 140.0 x coil mm
-Weight (Kg):2,224
-Quality:Prime
-Help
-Location:FABRICA ALGECIRAS
-1,000.00 €/ton
+        <v xml:space="preserve">Acerinox Europa, 304L/304-4301/4307 Coil, 2B,
+1.40 x 100.9 x coil mm
+Weight (Kg):1,612
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,075.00 €/ton
 Add to cart</v>
       </c>
     </row>
@@ -11951,7 +11951,7 @@
       <c r="B723" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 304L/304-4301/4307 Coil, 2B,
 1.40 x 100.9 x coil mm
-Weight (Kg):1,612
+Weight (Kg):1,600
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -11961,14 +11961,14 @@
     </row>
     <row r="724" xml:space="preserve">
       <c r="A724" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 304L/304-4301/4307 Coil, 2B,
-1.40 x 100.9 x coil mm</v>
+        <v xml:space="preserve">Acerinox Europa, 304-1.4301 Coil, Emboss Chequered,
+0.70 x 174.9 x coil mm</v>
       </c>
       <c r="B724" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 304L/304-4301/4307 Coil, 2B,
-1.40 x 100.9 x coil mm
-Weight (Kg):1,600
-Quality:Prime-2
+        <v xml:space="preserve">Acerinox Europa, 304-1.4301 Coil, Emboss Chequered,
+0.70 x 174.9 x coil mm
+Weight (Kg):1,494
+Quality:Prime
 Help
 Location:FABRICA ALGECIRAS
 2,075.00 €/ton
@@ -11983,7 +11983,7 @@
       <c r="B725" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 304-1.4301 Coil, Emboss Chequered,
 0.70 x 174.9 x coil mm
-Weight (Kg):1,494
+Weight (Kg):1,472
 Quality:Prime
 Help
 Location:FABRICA ALGECIRAS
@@ -11993,26 +11993,10 @@
     </row>
     <row r="726" xml:space="preserve">
       <c r="A726" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 304-1.4301 Coil, Emboss Chequered,
-0.70 x 174.9 x coil mm</v>
-      </c>
-      <c r="B726" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 304-1.4301 Coil, Emboss Chequered,
-0.70 x 174.9 x coil mm
-Weight (Kg):1,472
-Quality:Prime
-Help
-Location:FABRICA ALGECIRAS
-2,075.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="727" xml:space="preserve">
-      <c r="A727" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, SB-G-240,
 0.50 x 290.9 x coil mm</v>
       </c>
-      <c r="B727" t="str" xml:space="preserve">
+      <c r="B726" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, SB-G-240,
 0.50 x 290.9 x coil mm
 Weight (Kg):4,408
@@ -12023,15 +12007,31 @@
 Add to cart</v>
       </c>
     </row>
+    <row r="727" xml:space="preserve">
+      <c r="A727" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 304-1.4301 Coil, BA,
+0.60 x 110.0 x coil mm</v>
+      </c>
+      <c r="B727" t="str" xml:space="preserve">
+        <v xml:space="preserve">Acerinox Europa, 304-1.4301 Coil, BA,
+0.60 x 110.0 x coil mm
+Weight (Kg):1,032
+Quality:Prime-2
+Help
+Location:FABRICA ALGECIRAS
+2,075.00 €/ton
+Add to cart</v>
+      </c>
+    </row>
     <row r="728" xml:space="preserve">
       <c r="A728" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 304-1.4301 Coil, BA,
-0.60 x 110.0 x coil mm</v>
+0.40 x 270.0 x coil mm</v>
       </c>
       <c r="B728" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 304-1.4301 Coil, BA,
-0.60 x 110.0 x coil mm
-Weight (Kg):1,032
+0.40 x 270.0 x coil mm
+Weight (Kg):3,124
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -12042,25 +12042,9 @@
     <row r="729" xml:space="preserve">
       <c r="A729" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 304-1.4301 Coil, BA,
-0.40 x 270.0 x coil mm</v>
+0.60 x 135.0 x coil mm</v>
       </c>
       <c r="B729" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 304-1.4301 Coil, BA,
-0.40 x 270.0 x coil mm
-Weight (Kg):3,124
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-2,075.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="730" xml:space="preserve">
-      <c r="A730" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 304-1.4301 Coil, BA,
-0.60 x 135.0 x coil mm</v>
-      </c>
-      <c r="B730" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 304-1.4301 Coil, BA,
 0.60 x 135.0 x coil mm
 Weight (Kg):2,078
@@ -12071,12 +12055,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="731" xml:space="preserve">
-      <c r="A731" t="str" xml:space="preserve">
+    <row r="730" xml:space="preserve">
+      <c r="A730" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 441-1.4509 Coil, 2B,
 2.00 x 245.9 x coil mm</v>
       </c>
-      <c r="B731" t="str" xml:space="preserve">
+      <c r="B730" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 441-1.4509 Coil, 2B,
 2.00 x 245.9 x coil mm
 Weight (Kg):3,492
@@ -12087,12 +12071,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="732" xml:space="preserve">
-      <c r="A732" t="str" xml:space="preserve">
+    <row r="731" xml:space="preserve">
+      <c r="A731" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 304-1.4301 Coil, 2B,
 0.60 x 101.9 x coil mm</v>
       </c>
-      <c r="B732" t="str" xml:space="preserve">
+      <c r="B731" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 304-1.4301 Coil, 2B,
 0.60 x 101.9 x coil mm
 Weight (Kg):1,350
@@ -12103,12 +12087,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="733" xml:space="preserve">
-      <c r="A733" t="str" xml:space="preserve">
+    <row r="732" xml:space="preserve">
+      <c r="A732" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 430Ti-1.4510 Coil, BA,
 0.70 x 118.9 x coil mm</v>
       </c>
-      <c r="B733" t="str" xml:space="preserve">
+      <c r="B732" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 430Ti-1.4510 Coil, BA,
 0.70 x 118.9 x coil mm
 Weight (Kg):1,768
@@ -12119,12 +12103,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="734" xml:space="preserve">
-      <c r="A734" t="str" xml:space="preserve">
+    <row r="733" xml:space="preserve">
+      <c r="A733" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 304L/304-4301/4307 Coil, 2B,
 1.00 x 135.9 x coil mm</v>
       </c>
-      <c r="B734" t="str" xml:space="preserve">
+      <c r="B733" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 304L/304-4301/4307 Coil, 2B,
 1.00 x 135.9 x coil mm
 Weight (Kg):1,056
@@ -12135,28 +12119,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="735" xml:space="preserve">
-      <c r="A735" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 304L/304-4301/4307 Coil, 2B,
-2.00 x 250.0 x coil mm</v>
-      </c>
-      <c r="B735" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 304L/304-4301/4307 Coil, 2B,
-2.00 x 250.0 x coil mm
-Weight (Kg):2,388
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-2,075.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="736" xml:space="preserve">
-      <c r="A736" t="str" xml:space="preserve">
+    <row r="734" xml:space="preserve">
+      <c r="A734" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, BA,
 0.70 x 125.9 x coil mm</v>
       </c>
-      <c r="B736" t="str" xml:space="preserve">
+      <c r="B734" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, BA,
 0.70 x 125.9 x coil mm
 Weight (Kg):1,788
@@ -12167,12 +12135,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="737" xml:space="preserve">
-      <c r="A737" t="str" xml:space="preserve">
+    <row r="735" xml:space="preserve">
+      <c r="A735" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, BA,
 0.70 x 125.9 x coil mm</v>
       </c>
-      <c r="B737" t="str" xml:space="preserve">
+      <c r="B735" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, BA,
 0.70 x 125.9 x coil mm
 Weight (Kg):1,794
@@ -12183,12 +12151,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="738" xml:space="preserve">
-      <c r="A738" t="str" xml:space="preserve">
+    <row r="736" xml:space="preserve">
+      <c r="A736" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 430Ti-1.4510 Coil, BA,
 0.70 x 112.0 x coil mm</v>
       </c>
-      <c r="B738" t="str" xml:space="preserve">
+      <c r="B736" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 430Ti-1.4510 Coil, BA,
 0.70 x 112.0 x coil mm
 Weight (Kg):1,550
@@ -12199,12 +12167,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="739" xml:space="preserve">
-      <c r="A739" t="str" xml:space="preserve">
+    <row r="737" xml:space="preserve">
+      <c r="A737" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 304-1.4301 Coil, BA,
 0.60 x 320.0 x coil mm</v>
       </c>
-      <c r="B739" t="str" xml:space="preserve">
+      <c r="B737" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 304-1.4301 Coil, BA,
 0.60 x 320.0 x coil mm
 Weight (Kg):2,534
@@ -12215,12 +12183,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="740" xml:space="preserve">
-      <c r="A740" t="str" xml:space="preserve">
+    <row r="738" xml:space="preserve">
+      <c r="A738" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 304-1.4301 Coil, BA,
 0.60 x 320.0 x coil mm</v>
       </c>
-      <c r="B740" t="str" xml:space="preserve">
+      <c r="B738" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 304-1.4301 Coil, BA,
 0.60 x 320.0 x coil mm
 Weight (Kg):3,148
@@ -12231,28 +12199,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="741" xml:space="preserve">
-      <c r="A741" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 304-1.4301 Coil, 2B,
-0.80 x 199.9 x coil mm</v>
-      </c>
-      <c r="B741" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 304-1.4301 Coil, 2B,
-0.80 x 199.9 x coil mm
-Weight (Kg):2,602
-Quality:Prime-2
-Help
-Location:FABRICA ALGECIRAS
-2,075.00 €/ton
-Add to cart</v>
-      </c>
-    </row>
-    <row r="742" xml:space="preserve">
-      <c r="A742" t="str" xml:space="preserve">
+    <row r="739" xml:space="preserve">
+      <c r="A739" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 304L/304-4301/4307 Coil, 2B,
 1.00 x 125.9 x coil mm</v>
       </c>
-      <c r="B742" t="str" xml:space="preserve">
+      <c r="B739" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 304L/304-4301/4307 Coil, 2B,
 1.00 x 125.9 x coil mm
 Weight (Kg):1,726
@@ -12263,12 +12215,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="743" xml:space="preserve">
-      <c r="A743" t="str" xml:space="preserve">
+    <row r="740" xml:space="preserve">
+      <c r="A740" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 316L-1.4404 Coil, 2B,
 1.50 x 230.9 x coil mm</v>
       </c>
-      <c r="B743" t="str" xml:space="preserve">
+      <c r="B740" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 316L-1.4404 Coil, 2B,
 1.50 x 230.9 x coil mm
 Weight (Kg):1,956
@@ -12279,12 +12231,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="744" xml:space="preserve">
-      <c r="A744" t="str" xml:space="preserve">
+    <row r="741" xml:space="preserve">
+      <c r="A741" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, SBA,
 0.70 x 180.9 x coil mm</v>
       </c>
-      <c r="B744" t="str" xml:space="preserve">
+      <c r="B741" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 430-1.4016 Coil, SBA,
 0.70 x 180.9 x coil mm
 Weight (Kg):2,402
@@ -12295,12 +12247,12 @@
 Add to cart</v>
       </c>
     </row>
-    <row r="745" xml:space="preserve">
-      <c r="A745" t="str" xml:space="preserve">
+    <row r="742" xml:space="preserve">
+      <c r="A742" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 301-1.4310 Coil, BA,
 0.40 x 110.0 x coil mm</v>
       </c>
-      <c r="B745" t="str" xml:space="preserve">
+      <c r="B742" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 301-1.4310 Coil, BA,
 0.40 x 110.0 x coil mm
 Weight (Kg):1,734
@@ -12313,7 +12265,7 @@
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B745"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B742"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/scraped_data.xlsx
+++ b/scraped_data.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B742"/>
+  <dimension ref="A1:B734"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -3519,7 +3519,7 @@
       <c r="B196" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 1.00 x 1500.0 x 3000.0 mm
-Weight (Kg):959
+Weight (Kg):1,921
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -3530,12 +3530,12 @@
     <row r="197" xml:space="preserve">
       <c r="A197" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
-1.00 x 1500.0 x 3000.0 mm</v>
+2.00 x 1000.0 x 2000.0 mm</v>
       </c>
       <c r="B197" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
-1.00 x 1500.0 x 3000.0 mm
-Weight (Kg):794
+2.00 x 1000.0 x 2000.0 mm
+Weight (Kg):512
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -3546,12 +3546,12 @@
     <row r="198" xml:space="preserve">
       <c r="A198" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
-1.00 x 1500.0 x 3000.0 mm</v>
+2.00 x 1000.0 x 2000.0 mm</v>
       </c>
       <c r="B198" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
-1.00 x 1500.0 x 3000.0 mm
-Weight (Kg):659
+2.00 x 1000.0 x 2000.0 mm
+Weight (Kg):949
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -3610,12 +3610,12 @@
     <row r="202" xml:space="preserve">
       <c r="A202" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
-1.00 x 1500.0 x 3000.0 mm</v>
+2.00 x 1250.0 x 2500.0 mm</v>
       </c>
       <c r="B202" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
-1.00 x 1500.0 x 3000.0 mm
-Weight (Kg):1,508
+2.00 x 1250.0 x 2500.0 mm
+Weight (Kg):735
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -3626,12 +3626,12 @@
     <row r="203" xml:space="preserve">
       <c r="A203" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
-1.00 x 1500.0 x 3000.0 mm</v>
+2.00 x 1250.0 x 2500.0 mm</v>
       </c>
       <c r="B203" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
-1.00 x 1500.0 x 3000.0 mm
-Weight (Kg):1,921
+2.00 x 1250.0 x 2500.0 mm
+Weight (Kg):805
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -3642,12 +3642,12 @@
     <row r="204" xml:space="preserve">
       <c r="A204" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
-1.00 x 1500.0 x 3000.0 mm</v>
+2.00 x 1250.0 x 2500.0 mm</v>
       </c>
       <c r="B204" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
-1.00 x 1500.0 x 3000.0 mm
-Weight (Kg):894
+2.00 x 1250.0 x 2500.0 mm
+Weight (Kg):777
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -3658,12 +3658,12 @@
     <row r="205" xml:space="preserve">
       <c r="A205" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
-1.00 x 1500.0 x 3000.0 mm</v>
+2.00 x 1250.0 x 2500.0 mm</v>
       </c>
       <c r="B205" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
-1.00 x 1500.0 x 3000.0 mm
-Weight (Kg):700
+2.00 x 1250.0 x 2500.0 mm
+Weight (Kg):576
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -3674,12 +3674,12 @@
     <row r="206" xml:space="preserve">
       <c r="A206" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
-1.00 x 1500.0 x 3000.0 mm</v>
+2.00 x 1250.0 x 2500.0 mm</v>
       </c>
       <c r="B206" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
-1.00 x 1500.0 x 3000.0 mm
-Weight (Kg):842
+2.00 x 1250.0 x 2500.0 mm
+Weight (Kg):622
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -3690,12 +3690,12 @@
     <row r="207" xml:space="preserve">
       <c r="A207" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
-2.00 x 1000.0 x 2000.0 mm</v>
+2.00 x 1250.0 x 2500.0 mm</v>
       </c>
       <c r="B207" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
-2.00 x 1000.0 x 2000.0 mm
-Weight (Kg):512
+2.00 x 1250.0 x 2500.0 mm
+Weight (Kg):862
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -3706,12 +3706,12 @@
     <row r="208" xml:space="preserve">
       <c r="A208" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
-2.00 x 1000.0 x 2000.0 mm</v>
+2.00 x 1250.0 x 2500.0 mm</v>
       </c>
       <c r="B208" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
-2.00 x 1000.0 x 2000.0 mm
-Weight (Kg):949
+2.00 x 1250.0 x 2500.0 mm
+Weight (Kg):619
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -3727,7 +3727,7 @@
       <c r="B209" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 2.00 x 1250.0 x 2500.0 mm
-Weight (Kg):735
+Weight (Kg):867
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -3743,7 +3743,7 @@
       <c r="B210" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 2.00 x 1250.0 x 2500.0 mm
-Weight (Kg):805
+Weight (Kg):774
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -3754,12 +3754,12 @@
     <row r="211" xml:space="preserve">
       <c r="A211" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
-2.00 x 1250.0 x 2500.0 mm</v>
+2.00 x 1250.0 x 3000.0 mm</v>
       </c>
       <c r="B211" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
-2.00 x 1250.0 x 2500.0 mm
-Weight (Kg):777
+2.00 x 1250.0 x 3000.0 mm
+Weight (Kg):877
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -3770,12 +3770,12 @@
     <row r="212" xml:space="preserve">
       <c r="A212" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
-2.00 x 1250.0 x 2500.0 mm</v>
+2.50 x 1000.0 x 2000.0 mm</v>
       </c>
       <c r="B212" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
-2.00 x 1250.0 x 2500.0 mm
-Weight (Kg):576
+2.50 x 1000.0 x 2000.0 mm
+Weight (Kg):781
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -3786,12 +3786,12 @@
     <row r="213" xml:space="preserve">
       <c r="A213" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
-2.00 x 1250.0 x 2500.0 mm</v>
+2.50 x 1000.0 x 2000.0 mm</v>
       </c>
       <c r="B213" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
-2.00 x 1250.0 x 2500.0 mm
-Weight (Kg):622
+2.50 x 1000.0 x 2000.0 mm
+Weight (Kg):590
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -3802,12 +3802,12 @@
     <row r="214" xml:space="preserve">
       <c r="A214" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
-2.00 x 1250.0 x 2500.0 mm</v>
+2.50 x 1250.0 x 2500.0 mm</v>
       </c>
       <c r="B214" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
-2.00 x 1250.0 x 2500.0 mm
-Weight (Kg):862
+2.50 x 1250.0 x 2500.0 mm
+Weight (Kg):660
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -3818,12 +3818,12 @@
     <row r="215" xml:space="preserve">
       <c r="A215" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
-2.00 x 1250.0 x 2500.0 mm</v>
+2.50 x 1250.0 x 2500.0 mm</v>
       </c>
       <c r="B215" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
-2.00 x 1250.0 x 2500.0 mm
-Weight (Kg):619
+2.50 x 1250.0 x 2500.0 mm
+Weight (Kg):852
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -3834,12 +3834,12 @@
     <row r="216" xml:space="preserve">
       <c r="A216" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
-2.00 x 1250.0 x 2500.0 mm</v>
+2.50 x 1500.0 x 3000.0 mm</v>
       </c>
       <c r="B216" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
-2.00 x 1250.0 x 2500.0 mm
-Weight (Kg):867
+2.50 x 1500.0 x 3000.0 mm
+Weight (Kg):792
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -3850,12 +3850,12 @@
     <row r="217" xml:space="preserve">
       <c r="A217" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
-2.00 x 1250.0 x 2500.0 mm</v>
+2.50 x 1500.0 x 3000.0 mm</v>
       </c>
       <c r="B217" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
-2.00 x 1250.0 x 2500.0 mm
-Weight (Kg):774
+2.50 x 1500.0 x 3000.0 mm
+Weight (Kg):1,390
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -3866,12 +3866,12 @@
     <row r="218" xml:space="preserve">
       <c r="A218" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
-2.00 x 1250.0 x 3000.0 mm</v>
+2.50 x 1500.0 x 3000.0 mm</v>
       </c>
       <c r="B218" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
-2.00 x 1250.0 x 3000.0 mm
-Weight (Kg):877
+2.50 x 1500.0 x 3000.0 mm
+Weight (Kg):1,224
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -3882,12 +3882,12 @@
     <row r="219" xml:space="preserve">
       <c r="A219" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
-2.50 x 1000.0 x 2000.0 mm</v>
+2.50 x 1500.0 x 3000.0 mm</v>
       </c>
       <c r="B219" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
-2.50 x 1000.0 x 2000.0 mm
-Weight (Kg):781
+2.50 x 1500.0 x 3000.0 mm
+Weight (Kg):2,098
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -3898,12 +3898,12 @@
     <row r="220" xml:space="preserve">
       <c r="A220" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
-2.50 x 1000.0 x 2000.0 mm</v>
+2.50 x 1500.0 x 3000.0 mm</v>
       </c>
       <c r="B220" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
-2.50 x 1000.0 x 2000.0 mm
-Weight (Kg):590
+2.50 x 1500.0 x 3000.0 mm
+Weight (Kg):1,238
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -3914,12 +3914,12 @@
     <row r="221" xml:space="preserve">
       <c r="A221" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
-2.50 x 1250.0 x 2500.0 mm</v>
+2.50 x 1500.0 x 3000.0 mm</v>
       </c>
       <c r="B221" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
-2.50 x 1250.0 x 2500.0 mm
-Weight (Kg):660
+2.50 x 1500.0 x 3000.0 mm
+Weight (Kg):856
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -3930,12 +3930,12 @@
     <row r="222" xml:space="preserve">
       <c r="A222" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
-2.50 x 1250.0 x 2500.0 mm</v>
+2.50 x 1500.0 x 3000.0 mm</v>
       </c>
       <c r="B222" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
-2.50 x 1250.0 x 2500.0 mm
-Weight (Kg):852
+2.50 x 1500.0 x 3000.0 mm
+Weight (Kg):605
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -3951,7 +3951,7 @@
       <c r="B223" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 2.50 x 1500.0 x 3000.0 mm
-Weight (Kg):792
+Weight (Kg):521
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -3967,7 +3967,7 @@
       <c r="B224" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 2.50 x 1500.0 x 3000.0 mm
-Weight (Kg):1,390
+Weight (Kg):527
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -3983,7 +3983,7 @@
       <c r="B225" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 2.50 x 1500.0 x 3000.0 mm
-Weight (Kg):1,224
+Weight (Kg):862
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -3994,12 +3994,12 @@
     <row r="226" xml:space="preserve">
       <c r="A226" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
-2.50 x 1500.0 x 3000.0 mm</v>
+3.00 x 1000.0 x 2000.0 mm</v>
       </c>
       <c r="B226" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
-2.50 x 1500.0 x 3000.0 mm
-Weight (Kg):2,098
+3.00 x 1000.0 x 2000.0 mm
+Weight (Kg):992
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -4010,12 +4010,12 @@
     <row r="227" xml:space="preserve">
       <c r="A227" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
-2.50 x 1500.0 x 3000.0 mm</v>
+3.00 x 1000.0 x 2000.0 mm</v>
       </c>
       <c r="B227" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
-2.50 x 1500.0 x 3000.0 mm
-Weight (Kg):1,238
+3.00 x 1000.0 x 2000.0 mm
+Weight (Kg):1,038
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -4026,12 +4026,12 @@
     <row r="228" xml:space="preserve">
       <c r="A228" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
-2.50 x 1500.0 x 3000.0 mm</v>
+3.00 x 1000.0 x 2000.0 mm</v>
       </c>
       <c r="B228" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
-2.50 x 1500.0 x 3000.0 mm
-Weight (Kg):856
+3.00 x 1000.0 x 2000.0 mm
+Weight (Kg):946
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -4042,12 +4042,12 @@
     <row r="229" xml:space="preserve">
       <c r="A229" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
-2.50 x 1500.0 x 3000.0 mm</v>
+3.00 x 1000.0 x 2000.0 mm</v>
       </c>
       <c r="B229" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
-2.50 x 1500.0 x 3000.0 mm
-Weight (Kg):605
+3.00 x 1000.0 x 2000.0 mm
+Weight (Kg):503
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -4058,12 +4058,12 @@
     <row r="230" xml:space="preserve">
       <c r="A230" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
-2.50 x 1500.0 x 3000.0 mm</v>
+3.00 x 1000.0 x 2000.0 mm</v>
       </c>
       <c r="B230" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
-2.50 x 1500.0 x 3000.0 mm
-Weight (Kg):521
+3.00 x 1000.0 x 2000.0 mm
+Weight (Kg):880
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -4074,12 +4074,12 @@
     <row r="231" xml:space="preserve">
       <c r="A231" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
-2.50 x 1500.0 x 3000.0 mm</v>
+3.00 x 1000.0 x 2000.0 mm</v>
       </c>
       <c r="B231" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
-2.50 x 1500.0 x 3000.0 mm
-Weight (Kg):527
+3.00 x 1000.0 x 2000.0 mm
+Weight (Kg):796
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -4090,12 +4090,12 @@
     <row r="232" xml:space="preserve">
       <c r="A232" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
-2.50 x 1500.0 x 3000.0 mm</v>
+3.00 x 1000.0 x 2000.0 mm</v>
       </c>
       <c r="B232" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
-2.50 x 1500.0 x 3000.0 mm
-Weight (Kg):862
+3.00 x 1000.0 x 2000.0 mm
+Weight (Kg):578
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -4111,7 +4111,7 @@
       <c r="B233" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 3.00 x 1000.0 x 2000.0 mm
-Weight (Kg):992
+Weight (Kg):1,506
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -4127,7 +4127,7 @@
       <c r="B234" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 3.00 x 1000.0 x 2000.0 mm
-Weight (Kg):1,038
+Weight (Kg):1,538
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -4143,7 +4143,7 @@
       <c r="B235" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 3.00 x 1000.0 x 2000.0 mm
-Weight (Kg):946
+Weight (Kg):520
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -4154,12 +4154,12 @@
     <row r="236" xml:space="preserve">
       <c r="A236" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
-3.00 x 1000.0 x 2000.0 mm</v>
+3.00 x 1250.0 x 2500.0 mm</v>
       </c>
       <c r="B236" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
-3.00 x 1000.0 x 2000.0 mm
-Weight (Kg):503
+3.00 x 1250.0 x 2500.0 mm
+Weight (Kg):886
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -4170,12 +4170,12 @@
     <row r="237" xml:space="preserve">
       <c r="A237" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
-3.00 x 1000.0 x 2000.0 mm</v>
+3.00 x 1250.0 x 2500.0 mm</v>
       </c>
       <c r="B237" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
-3.00 x 1000.0 x 2000.0 mm
-Weight (Kg):880
+3.00 x 1250.0 x 2500.0 mm
+Weight (Kg):1,233
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -4186,12 +4186,12 @@
     <row r="238" xml:space="preserve">
       <c r="A238" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
-3.00 x 1000.0 x 2000.0 mm</v>
+3.00 x 1250.0 x 2500.0 mm</v>
       </c>
       <c r="B238" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
-3.00 x 1000.0 x 2000.0 mm
-Weight (Kg):796
+3.00 x 1250.0 x 2500.0 mm
+Weight (Kg):742
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -4202,12 +4202,12 @@
     <row r="239" xml:space="preserve">
       <c r="A239" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
-3.00 x 1000.0 x 2000.0 mm</v>
+3.00 x 1250.0 x 2500.0 mm</v>
       </c>
       <c r="B239" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
-3.00 x 1000.0 x 2000.0 mm
-Weight (Kg):578
+3.00 x 1250.0 x 2500.0 mm
+Weight (Kg):858
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -4218,12 +4218,12 @@
     <row r="240" xml:space="preserve">
       <c r="A240" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
-3.00 x 1000.0 x 2000.0 mm</v>
+3.00 x 1250.0 x 2500.0 mm</v>
       </c>
       <c r="B240" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
-3.00 x 1000.0 x 2000.0 mm
-Weight (Kg):1,506
+3.00 x 1250.0 x 2500.0 mm
+Weight (Kg):1,450
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -4234,12 +4234,12 @@
     <row r="241" xml:space="preserve">
       <c r="A241" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
-3.00 x 1000.0 x 2000.0 mm</v>
+3.00 x 1250.0 x 2500.0 mm</v>
       </c>
       <c r="B241" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
-3.00 x 1000.0 x 2000.0 mm
-Weight (Kg):1,538
+3.00 x 1250.0 x 2500.0 mm
+Weight (Kg):1,818
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -4250,12 +4250,12 @@
     <row r="242" xml:space="preserve">
       <c r="A242" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
-3.00 x 1000.0 x 2000.0 mm</v>
+3.00 x 1250.0 x 2500.0 mm</v>
       </c>
       <c r="B242" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
-3.00 x 1000.0 x 2000.0 mm
-Weight (Kg):520
+3.00 x 1250.0 x 2500.0 mm
+Weight (Kg):1,220
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -4271,7 +4271,7 @@
       <c r="B243" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 3.00 x 1250.0 x 2500.0 mm
-Weight (Kg):886
+Weight (Kg):812
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -4287,7 +4287,7 @@
       <c r="B244" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 3.00 x 1250.0 x 2500.0 mm
-Weight (Kg):1,233
+Weight (Kg):816
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -4303,7 +4303,7 @@
       <c r="B245" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 3.00 x 1250.0 x 2500.0 mm
-Weight (Kg):742
+Weight (Kg):1,320
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -4319,7 +4319,7 @@
       <c r="B246" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 3.00 x 1250.0 x 2500.0 mm
-Weight (Kg):858
+Weight (Kg):830
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -4335,7 +4335,7 @@
       <c r="B247" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 3.00 x 1250.0 x 2500.0 mm
-Weight (Kg):1,450
+Weight (Kg):1,446
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -4351,7 +4351,7 @@
       <c r="B248" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 3.00 x 1250.0 x 2500.0 mm
-Weight (Kg):1,818
+Weight (Kg):670
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -4367,7 +4367,7 @@
       <c r="B249" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 3.00 x 1250.0 x 2500.0 mm
-Weight (Kg):1,220
+Weight (Kg):884
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -4383,7 +4383,7 @@
       <c r="B250" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 3.00 x 1250.0 x 2500.0 mm
-Weight (Kg):812
+Weight (Kg):762
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -4394,12 +4394,12 @@
     <row r="251" xml:space="preserve">
       <c r="A251" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
-3.00 x 1250.0 x 2500.0 mm</v>
+3.00 x 1500.0 x 3000.0 mm</v>
       </c>
       <c r="B251" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
-3.00 x 1250.0 x 2500.0 mm
-Weight (Kg):816
+3.00 x 1500.0 x 3000.0 mm
+Weight (Kg):744
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -4410,12 +4410,12 @@
     <row r="252" xml:space="preserve">
       <c r="A252" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
-3.00 x 1250.0 x 2500.0 mm</v>
+3.00 x 1500.0 x 3000.0 mm</v>
       </c>
       <c r="B252" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
-3.00 x 1250.0 x 2500.0 mm
-Weight (Kg):1,320
+3.00 x 1500.0 x 3000.0 mm
+Weight (Kg):1,394
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -4426,12 +4426,12 @@
     <row r="253" xml:space="preserve">
       <c r="A253" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
-3.00 x 1250.0 x 2500.0 mm</v>
+3.00 x 1500.0 x 3000.0 mm</v>
       </c>
       <c r="B253" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
-3.00 x 1250.0 x 2500.0 mm
-Weight (Kg):830
+3.00 x 1500.0 x 3000.0 mm
+Weight (Kg):2,224
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -4442,12 +4442,12 @@
     <row r="254" xml:space="preserve">
       <c r="A254" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
-3.00 x 1250.0 x 2500.0 mm</v>
+3.00 x 1500.0 x 3000.0 mm</v>
       </c>
       <c r="B254" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
-3.00 x 1250.0 x 2500.0 mm
-Weight (Kg):1,446
+3.00 x 1500.0 x 3000.0 mm
+Weight (Kg):1,156
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -4458,12 +4458,12 @@
     <row r="255" xml:space="preserve">
       <c r="A255" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
-3.00 x 1250.0 x 2500.0 mm</v>
+3.00 x 1500.0 x 3000.0 mm</v>
       </c>
       <c r="B255" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
-3.00 x 1250.0 x 2500.0 mm
-Weight (Kg):670
+3.00 x 1500.0 x 3000.0 mm
+Weight (Kg):632
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -4474,12 +4474,12 @@
     <row r="256" xml:space="preserve">
       <c r="A256" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
-3.00 x 1250.0 x 2500.0 mm</v>
+3.00 x 1500.0 x 3000.0 mm</v>
       </c>
       <c r="B256" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
-3.00 x 1250.0 x 2500.0 mm
-Weight (Kg):884
+3.00 x 1500.0 x 3000.0 mm
+Weight (Kg):950
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -4490,12 +4490,12 @@
     <row r="257" xml:space="preserve">
       <c r="A257" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
-3.00 x 1250.0 x 2500.0 mm</v>
+3.00 x 1500.0 x 3000.0 mm</v>
       </c>
       <c r="B257" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
-3.00 x 1250.0 x 2500.0 mm
-Weight (Kg):762
+3.00 x 1500.0 x 3000.0 mm
+Weight (Kg):750
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -4511,7 +4511,7 @@
       <c r="B258" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 3.00 x 1500.0 x 3000.0 mm
-Weight (Kg):744
+Weight (Kg):1,906
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -4527,7 +4527,7 @@
       <c r="B259" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 3.00 x 1500.0 x 3000.0 mm
-Weight (Kg):1,394
+Weight (Kg):640
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -4543,7 +4543,7 @@
       <c r="B260" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 3.00 x 1500.0 x 3000.0 mm
-Weight (Kg):2,224
+Weight (Kg):1,496
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -4554,12 +4554,12 @@
     <row r="261" xml:space="preserve">
       <c r="A261" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
-3.00 x 1500.0 x 3000.0 mm</v>
+4.00 x 1000.0 x 2000.0 mm</v>
       </c>
       <c r="B261" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
-3.00 x 1500.0 x 3000.0 mm
-Weight (Kg):1,156
+4.00 x 1000.0 x 2000.0 mm
+Weight (Kg):1,348
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -4570,12 +4570,12 @@
     <row r="262" xml:space="preserve">
       <c r="A262" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
-3.00 x 1500.0 x 3000.0 mm</v>
+4.00 x 1500.0 x 3000.0 mm</v>
       </c>
       <c r="B262" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
-3.00 x 1500.0 x 3000.0 mm
-Weight (Kg):632
+4.00 x 1500.0 x 3000.0 mm
+Weight (Kg):1,574
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -4586,12 +4586,12 @@
     <row r="263" xml:space="preserve">
       <c r="A263" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
-3.00 x 1500.0 x 3000.0 mm</v>
+4.00 x 1500.0 x 3000.0 mm</v>
       </c>
       <c r="B263" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
-3.00 x 1500.0 x 3000.0 mm
-Weight (Kg):950
+4.00 x 1500.0 x 3000.0 mm
+Weight (Kg):1,861
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -4602,12 +4602,12 @@
     <row r="264" xml:space="preserve">
       <c r="A264" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
-3.00 x 1500.0 x 3000.0 mm</v>
+4.00 x 1500.0 x 3000.0 mm</v>
       </c>
       <c r="B264" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
-3.00 x 1500.0 x 3000.0 mm
-Weight (Kg):750
+4.00 x 1500.0 x 3000.0 mm
+Weight (Kg):1,722
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -4618,12 +4618,12 @@
     <row r="265" xml:space="preserve">
       <c r="A265" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
-3.00 x 1500.0 x 3000.0 mm</v>
+4.00 x 1500.0 x 3000.0 mm</v>
       </c>
       <c r="B265" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
-3.00 x 1500.0 x 3000.0 mm
-Weight (Kg):1,906
+4.00 x 1500.0 x 3000.0 mm
+Weight (Kg):1,726
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -4634,12 +4634,12 @@
     <row r="266" xml:space="preserve">
       <c r="A266" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
-3.00 x 1500.0 x 3000.0 mm</v>
+4.00 x 1500.0 x 3000.0 mm</v>
       </c>
       <c r="B266" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
-3.00 x 1500.0 x 3000.0 mm
-Weight (Kg):640
+4.00 x 1500.0 x 3000.0 mm
+Weight (Kg):999
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -4650,12 +4650,12 @@
     <row r="267" xml:space="preserve">
       <c r="A267" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
-3.00 x 1500.0 x 3000.0 mm</v>
+4.00 x 1500.0 x 3000.0 mm</v>
       </c>
       <c r="B267" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
-3.00 x 1500.0 x 3000.0 mm
-Weight (Kg):1,496
+4.00 x 1500.0 x 3000.0 mm
+Weight (Kg):724
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -4666,12 +4666,12 @@
     <row r="268" xml:space="preserve">
       <c r="A268" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
-4.00 x 1000.0 x 2000.0 mm</v>
+4.00 x 1500.0 x 3000.0 mm</v>
       </c>
       <c r="B268" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
-4.00 x 1000.0 x 2000.0 mm
-Weight (Kg):1,348
+4.00 x 1500.0 x 3000.0 mm
+Weight (Kg):854
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -4687,7 +4687,7 @@
       <c r="B269" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 4.00 x 1500.0 x 3000.0 mm
-Weight (Kg):1,574
+Weight (Kg):1,987
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -4703,7 +4703,7 @@
       <c r="B270" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 4.00 x 1500.0 x 3000.0 mm
-Weight (Kg):1,861
+Weight (Kg):1,708
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -4719,7 +4719,7 @@
       <c r="B271" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 4.00 x 1500.0 x 3000.0 mm
-Weight (Kg):1,722
+Weight (Kg):1,562
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -4730,12 +4730,12 @@
     <row r="272" xml:space="preserve">
       <c r="A272" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
-4.00 x 1500.0 x 3000.0 mm</v>
+5.00 x 1250.0 x 2500.0 mm</v>
       </c>
       <c r="B272" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
-4.00 x 1500.0 x 3000.0 mm
-Weight (Kg):1,726
+5.00 x 1250.0 x 2500.0 mm
+Weight (Kg):2,220
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -4746,12 +4746,12 @@
     <row r="273" xml:space="preserve">
       <c r="A273" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
-4.00 x 1500.0 x 3000.0 mm</v>
+5.00 x 1250.0 x 2500.0 mm</v>
       </c>
       <c r="B273" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
-4.00 x 1500.0 x 3000.0 mm
-Weight (Kg):999
+5.00 x 1250.0 x 2500.0 mm
+Weight (Kg):1,580
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -4762,12 +4762,12 @@
     <row r="274" xml:space="preserve">
       <c r="A274" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
-4.00 x 1500.0 x 3000.0 mm</v>
+5.00 x 1250.0 x 2500.0 mm</v>
       </c>
       <c r="B274" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
-4.00 x 1500.0 x 3000.0 mm
-Weight (Kg):724
+5.00 x 1250.0 x 2500.0 mm
+Weight (Kg):750
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -4778,12 +4778,12 @@
     <row r="275" xml:space="preserve">
       <c r="A275" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
-4.00 x 1500.0 x 3000.0 mm</v>
+5.00 x 1500.0 x 3000.0 mm</v>
       </c>
       <c r="B275" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
-4.00 x 1500.0 x 3000.0 mm
-Weight (Kg):854
+5.00 x 1500.0 x 3000.0 mm
+Weight (Kg):1,777
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -4794,12 +4794,12 @@
     <row r="276" xml:space="preserve">
       <c r="A276" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
-4.00 x 1500.0 x 3000.0 mm</v>
+5.00 x 1500.0 x 3000.0 mm</v>
       </c>
       <c r="B276" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
-4.00 x 1500.0 x 3000.0 mm
-Weight (Kg):1,987
+5.00 x 1500.0 x 3000.0 mm
+Weight (Kg):1,436
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -4810,12 +4810,12 @@
     <row r="277" xml:space="preserve">
       <c r="A277" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
-4.00 x 1500.0 x 3000.0 mm</v>
+5.00 x 1500.0 x 3000.0 mm</v>
       </c>
       <c r="B277" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
-4.00 x 1500.0 x 3000.0 mm
-Weight (Kg):1,708
+5.00 x 1500.0 x 3000.0 mm
+Weight (Kg):890
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -4826,12 +4826,12 @@
     <row r="278" xml:space="preserve">
       <c r="A278" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
-4.00 x 1500.0 x 3000.0 mm</v>
+5.00 x 1500.0 x 3000.0 mm</v>
       </c>
       <c r="B278" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
-4.00 x 1500.0 x 3000.0 mm
-Weight (Kg):1,562
+5.00 x 1500.0 x 3000.0 mm
+Weight (Kg):1,252
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -4842,12 +4842,12 @@
     <row r="279" xml:space="preserve">
       <c r="A279" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
-5.00 x 1250.0 x 2500.0 mm</v>
+5.00 x 1500.0 x 3000.0 mm</v>
       </c>
       <c r="B279" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
-5.00 x 1250.0 x 2500.0 mm
-Weight (Kg):2,220
+5.00 x 1500.0 x 3000.0 mm
+Weight (Kg):1,646
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -4858,12 +4858,12 @@
     <row r="280" xml:space="preserve">
       <c r="A280" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
-5.00 x 1250.0 x 2500.0 mm</v>
+5.00 x 1500.0 x 3000.0 mm</v>
       </c>
       <c r="B280" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
-5.00 x 1250.0 x 2500.0 mm
-Weight (Kg):1,580
+5.00 x 1500.0 x 3000.0 mm
+Weight (Kg):1,434
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -4874,12 +4874,12 @@
     <row r="281" xml:space="preserve">
       <c r="A281" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
-5.00 x 1250.0 x 2500.0 mm</v>
+5.00 x 1500.0 x 3000.0 mm</v>
       </c>
       <c r="B281" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
-5.00 x 1250.0 x 2500.0 mm
-Weight (Kg):750
+5.00 x 1500.0 x 3000.0 mm
+Weight (Kg):1,778
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -4895,7 +4895,7 @@
       <c r="B282" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 5.00 x 1500.0 x 3000.0 mm
-Weight (Kg):1,777
+Weight (Kg):1,818
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -4911,7 +4911,7 @@
       <c r="B283" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 5.00 x 1500.0 x 3000.0 mm
-Weight (Kg):1,436
+Weight (Kg):1,807
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -4927,7 +4927,7 @@
       <c r="B284" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 5.00 x 1500.0 x 3000.0 mm
-Weight (Kg):890
+Weight (Kg):1,978
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -4943,7 +4943,7 @@
       <c r="B285" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 5.00 x 1500.0 x 3000.0 mm
-Weight (Kg):1,252
+Weight (Kg):1,760
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -4959,7 +4959,7 @@
       <c r="B286" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 5.00 x 1500.0 x 3000.0 mm
-Weight (Kg):1,646
+Weight (Kg):1,976
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -4975,7 +4975,7 @@
       <c r="B287" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 5.00 x 1500.0 x 3000.0 mm
-Weight (Kg):1,434
+Weight (Kg):1,236
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -4991,7 +4991,7 @@
       <c r="B288" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 5.00 x 1500.0 x 3000.0 mm
-Weight (Kg):1,778
+Weight (Kg):1,968
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -5007,7 +5007,7 @@
       <c r="B289" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 5.00 x 1500.0 x 3000.0 mm
-Weight (Kg):1,818
+Weight (Kg):1,240
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -5023,7 +5023,7 @@
       <c r="B290" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 5.00 x 1500.0 x 3000.0 mm
-Weight (Kg):1,807
+Weight (Kg):1,070
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -5039,7 +5039,7 @@
       <c r="B291" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 5.00 x 1500.0 x 3000.0 mm
-Weight (Kg):1,978
+Weight (Kg):1,960
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -5055,7 +5055,7 @@
       <c r="B292" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 5.00 x 1500.0 x 3000.0 mm
-Weight (Kg):1,760
+Weight (Kg):1,734
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -5071,7 +5071,7 @@
       <c r="B293" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 5.00 x 1500.0 x 3000.0 mm
-Weight (Kg):1,976
+Weight (Kg):1,874
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -5087,7 +5087,7 @@
       <c r="B294" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 5.00 x 1500.0 x 3000.0 mm
-Weight (Kg):1,236
+Weight (Kg):884
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -5103,7 +5103,7 @@
       <c r="B295" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 5.00 x 1500.0 x 3000.0 mm
-Weight (Kg):1,968
+Weight (Kg):1,578
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -5119,7 +5119,7 @@
       <c r="B296" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 5.00 x 1500.0 x 3000.0 mm
-Weight (Kg):1,240
+Weight (Kg):852
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -5135,7 +5135,7 @@
       <c r="B297" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 5.00 x 1500.0 x 3000.0 mm
-Weight (Kg):1,070
+Weight (Kg):1,942
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -5146,12 +5146,12 @@
     <row r="298" xml:space="preserve">
       <c r="A298" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
-5.00 x 1500.0 x 3000.0 mm</v>
+6.00 x 1000.0 x 2000.0 mm</v>
       </c>
       <c r="B298" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
-5.00 x 1500.0 x 3000.0 mm
-Weight (Kg):1,960
+6.00 x 1000.0 x 2000.0 mm
+Weight (Kg):1,906
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -5162,12 +5162,12 @@
     <row r="299" xml:space="preserve">
       <c r="A299" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
-5.00 x 1500.0 x 3000.0 mm</v>
+6.00 x 1000.0 x 2000.0 mm</v>
       </c>
       <c r="B299" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
-5.00 x 1500.0 x 3000.0 mm
-Weight (Kg):1,734
+6.00 x 1000.0 x 2000.0 mm
+Weight (Kg):1,886
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -5178,12 +5178,12 @@
     <row r="300" xml:space="preserve">
       <c r="A300" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
-5.00 x 1500.0 x 3000.0 mm</v>
+6.00 x 1000.0 x 2000.0 mm</v>
       </c>
       <c r="B300" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
-5.00 x 1500.0 x 3000.0 mm
-Weight (Kg):1,874
+6.00 x 1000.0 x 2000.0 mm
+Weight (Kg):1,414
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -5194,12 +5194,12 @@
     <row r="301" xml:space="preserve">
       <c r="A301" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
-5.00 x 1500.0 x 3000.0 mm</v>
+6.00 x 1000.0 x 2000.0 mm</v>
       </c>
       <c r="B301" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
-5.00 x 1500.0 x 3000.0 mm
-Weight (Kg):884
+6.00 x 1000.0 x 2000.0 mm
+Weight (Kg):1,620
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -5210,12 +5210,12 @@
     <row r="302" xml:space="preserve">
       <c r="A302" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
-5.00 x 1500.0 x 3000.0 mm</v>
+6.00 x 1000.0 x 2000.0 mm</v>
       </c>
       <c r="B302" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
-5.00 x 1500.0 x 3000.0 mm
-Weight (Kg):1,578
+6.00 x 1000.0 x 2000.0 mm
+Weight (Kg):938
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -5226,12 +5226,12 @@
     <row r="303" xml:space="preserve">
       <c r="A303" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
-5.00 x 1500.0 x 3000.0 mm</v>
+6.00 x 1000.0 x 2000.0 mm</v>
       </c>
       <c r="B303" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
-5.00 x 1500.0 x 3000.0 mm
-Weight (Kg):852
+6.00 x 1000.0 x 2000.0 mm
+Weight (Kg):1,406
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -5242,12 +5242,12 @@
     <row r="304" xml:space="preserve">
       <c r="A304" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
-5.00 x 1500.0 x 3000.0 mm</v>
+6.00 x 1000.0 x 2000.0 mm</v>
       </c>
       <c r="B304" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
-5.00 x 1500.0 x 3000.0 mm
-Weight (Kg):1,942
+6.00 x 1000.0 x 2000.0 mm
+Weight (Kg):1,140
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -5258,12 +5258,12 @@
     <row r="305" xml:space="preserve">
       <c r="A305" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
-6.00 x 1000.0 x 2000.0 mm</v>
+6.00 x 1250.0 x 2500.0 mm</v>
       </c>
       <c r="B305" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
-6.00 x 1000.0 x 2000.0 mm
-Weight (Kg):1,906
+6.00 x 1250.0 x 2500.0 mm
+Weight (Kg):1,494
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -5274,12 +5274,12 @@
     <row r="306" xml:space="preserve">
       <c r="A306" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
-6.00 x 1000.0 x 2000.0 mm</v>
+6.00 x 1250.0 x 2500.0 mm</v>
       </c>
       <c r="B306" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
-6.00 x 1000.0 x 2000.0 mm
-Weight (Kg):1,886
+6.00 x 1250.0 x 2500.0 mm
+Weight (Kg):1,652
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -5290,12 +5290,12 @@
     <row r="307" xml:space="preserve">
       <c r="A307" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
-6.00 x 1000.0 x 2000.0 mm</v>
+6.00 x 1250.0 x 2500.0 mm</v>
       </c>
       <c r="B307" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
-6.00 x 1000.0 x 2000.0 mm
-Weight (Kg):1,414
+6.00 x 1250.0 x 2500.0 mm
+Weight (Kg):1,610
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -5306,12 +5306,12 @@
     <row r="308" xml:space="preserve">
       <c r="A308" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
-6.00 x 1000.0 x 2000.0 mm</v>
+6.00 x 1250.0 x 2500.0 mm</v>
       </c>
       <c r="B308" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
-6.00 x 1000.0 x 2000.0 mm
-Weight (Kg):1,620
+6.00 x 1250.0 x 2500.0 mm
+Weight (Kg):1,900
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -5322,12 +5322,12 @@
     <row r="309" xml:space="preserve">
       <c r="A309" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
-6.00 x 1000.0 x 2000.0 mm</v>
+6.00 x 1250.0 x 2500.0 mm</v>
       </c>
       <c r="B309" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
-6.00 x 1000.0 x 2000.0 mm
-Weight (Kg):938
+6.00 x 1250.0 x 2500.0 mm
+Weight (Kg):2,346
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -5338,12 +5338,12 @@
     <row r="310" xml:space="preserve">
       <c r="A310" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
-6.00 x 1000.0 x 2000.0 mm</v>
+6.00 x 1250.0 x 2500.0 mm</v>
       </c>
       <c r="B310" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
-6.00 x 1000.0 x 2000.0 mm
-Weight (Kg):1,406
+6.00 x 1250.0 x 2500.0 mm
+Weight (Kg):1,624
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -5354,12 +5354,12 @@
     <row r="311" xml:space="preserve">
       <c r="A311" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
-6.00 x 1000.0 x 2000.0 mm</v>
+6.00 x 1500.0 x 3000.0 mm</v>
       </c>
       <c r="B311" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
-6.00 x 1000.0 x 2000.0 mm
-Weight (Kg):1,140
+6.00 x 1500.0 x 3000.0 mm
+Weight (Kg):1,296
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -5370,12 +5370,12 @@
     <row r="312" xml:space="preserve">
       <c r="A312" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
-6.00 x 1250.0 x 2500.0 mm</v>
+6.00 x 1500.0 x 3000.0 mm</v>
       </c>
       <c r="B312" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
-6.00 x 1250.0 x 2500.0 mm
-Weight (Kg):1,494
+6.00 x 1500.0 x 3000.0 mm
+Weight (Kg):1,716
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -5386,12 +5386,12 @@
     <row r="313" xml:space="preserve">
       <c r="A313" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
-6.00 x 1250.0 x 2500.0 mm</v>
+6.00 x 1500.0 x 3000.0 mm</v>
       </c>
       <c r="B313" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
-6.00 x 1250.0 x 2500.0 mm
-Weight (Kg):1,652
+6.00 x 1500.0 x 3000.0 mm
+Weight (Kg):1,917
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -5402,12 +5402,12 @@
     <row r="314" xml:space="preserve">
       <c r="A314" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
-6.00 x 1250.0 x 2500.0 mm</v>
+6.00 x 1500.0 x 3000.0 mm</v>
       </c>
       <c r="B314" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
-6.00 x 1250.0 x 2500.0 mm
-Weight (Kg):1,610
+6.00 x 1500.0 x 3000.0 mm
+Weight (Kg):1,922
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -5418,12 +5418,12 @@
     <row r="315" xml:space="preserve">
       <c r="A315" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
-6.00 x 1250.0 x 2500.0 mm</v>
+6.00 x 1500.0 x 3000.0 mm</v>
       </c>
       <c r="B315" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
-6.00 x 1250.0 x 2500.0 mm
-Weight (Kg):1,900
+6.00 x 1500.0 x 3000.0 mm
+Weight (Kg):1,728
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -5434,12 +5434,12 @@
     <row r="316" xml:space="preserve">
       <c r="A316" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
-6.00 x 1250.0 x 2500.0 mm</v>
+6.00 x 1500.0 x 3000.0 mm</v>
       </c>
       <c r="B316" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
-6.00 x 1250.0 x 2500.0 mm
-Weight (Kg):2,346
+6.00 x 1500.0 x 3000.0 mm
+Weight (Kg):864
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -5450,12 +5450,12 @@
     <row r="317" xml:space="preserve">
       <c r="A317" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
-6.00 x 1250.0 x 2500.0 mm</v>
+6.00 x 1500.0 x 3000.0 mm</v>
       </c>
       <c r="B317" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
-6.00 x 1250.0 x 2500.0 mm
-Weight (Kg):1,624
+6.00 x 1500.0 x 3000.0 mm
+Weight (Kg):1,302
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -5471,7 +5471,7 @@
       <c r="B318" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 6.00 x 1500.0 x 3000.0 mm
-Weight (Kg):1,296
+Weight (Kg):1,062
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -5487,7 +5487,7 @@
       <c r="B319" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 6.00 x 1500.0 x 3000.0 mm
-Weight (Kg):1,716
+Weight (Kg):1,966
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -5503,7 +5503,7 @@
       <c r="B320" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 6.00 x 1500.0 x 3000.0 mm
-Weight (Kg):1,917
+Weight (Kg):1,496
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -5519,7 +5519,7 @@
       <c r="B321" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 6.00 x 1500.0 x 3000.0 mm
-Weight (Kg):1,922
+Weight (Kg):1,320
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -5535,7 +5535,7 @@
       <c r="B322" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 6.00 x 1500.0 x 3000.0 mm
-Weight (Kg):1,728
+Weight (Kg):1,071
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -5551,7 +5551,7 @@
       <c r="B323" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 6.00 x 1500.0 x 3000.0 mm
-Weight (Kg):864
+Weight (Kg):1,264
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -5567,7 +5567,7 @@
       <c r="B324" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 6.00 x 1500.0 x 3000.0 mm
-Weight (Kg):1,302
+Weight (Kg):1,916
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -5583,7 +5583,7 @@
       <c r="B325" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 6.00 x 1500.0 x 3000.0 mm
-Weight (Kg):1,062
+Weight (Kg):1,908
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -5599,7 +5599,7 @@
       <c r="B326" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 6.00 x 1500.0 x 3000.0 mm
-Weight (Kg):1,966
+Weight (Kg):1,928
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -5615,7 +5615,7 @@
       <c r="B327" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 6.00 x 1500.0 x 3000.0 mm
-Weight (Kg):1,496
+Weight (Kg):1,290
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -5631,7 +5631,7 @@
       <c r="B328" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 6.00 x 1500.0 x 3000.0 mm
-Weight (Kg):1,320
+Weight (Kg):1,698
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -5647,7 +5647,7 @@
       <c r="B329" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 6.00 x 1500.0 x 3000.0 mm
-Weight (Kg):1,071
+Weight (Kg):1,754
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -5663,7 +5663,7 @@
       <c r="B330" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 6.00 x 1500.0 x 3000.0 mm
-Weight (Kg):1,264
+Weight (Kg):1,716
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -5679,7 +5679,7 @@
       <c r="B331" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 6.00 x 1500.0 x 3000.0 mm
-Weight (Kg):1,916
+Weight (Kg):1,548
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -5695,7 +5695,7 @@
       <c r="B332" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 6.00 x 1500.0 x 3000.0 mm
-Weight (Kg):1,908
+Weight (Kg):1,916
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -5711,7 +5711,7 @@
       <c r="B333" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 6.00 x 1500.0 x 3000.0 mm
-Weight (Kg):1,928
+Weight (Kg):1,485
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -5727,7 +5727,7 @@
       <c r="B334" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 6.00 x 1500.0 x 3000.0 mm
-Weight (Kg):1,290
+Weight (Kg):1,940
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -5743,7 +5743,7 @@
       <c r="B335" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 6.00 x 1500.0 x 3000.0 mm
-Weight (Kg):1,698
+Weight (Kg):1,762
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -5759,7 +5759,7 @@
       <c r="B336" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 6.00 x 1500.0 x 3000.0 mm
-Weight (Kg):1,754
+Weight (Kg):1,918
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -5775,7 +5775,7 @@
       <c r="B337" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 6.00 x 1500.0 x 3000.0 mm
-Weight (Kg):1,716
+Weight (Kg):1,306
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -5791,7 +5791,7 @@
       <c r="B338" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 6.00 x 1500.0 x 3000.0 mm
-Weight (Kg):1,548
+Weight (Kg):1,066
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -5807,7 +5807,7 @@
       <c r="B339" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 6.00 x 1500.0 x 3000.0 mm
-Weight (Kg):1,916
+Weight (Kg):1,936
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -5823,7 +5823,7 @@
       <c r="B340" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 6.00 x 1500.0 x 3000.0 mm
-Weight (Kg):1,485
+Weight (Kg):2,390
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -5839,7 +5839,7 @@
       <c r="B341" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 6.00 x 1500.0 x 3000.0 mm
-Weight (Kg):1,940
+Weight (Kg):1,728
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -5855,7 +5855,7 @@
       <c r="B342" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 6.00 x 1500.0 x 3000.0 mm
-Weight (Kg):1,762
+Weight (Kg):1,514
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -5871,7 +5871,7 @@
       <c r="B343" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 6.00 x 1500.0 x 3000.0 mm
-Weight (Kg):1,918
+Weight (Kg):1,922
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -5887,7 +5887,7 @@
       <c r="B344" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 6.00 x 1500.0 x 3000.0 mm
-Weight (Kg):1,306
+Weight (Kg):1,942
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -5903,7 +5903,7 @@
       <c r="B345" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 6.00 x 1500.0 x 3000.0 mm
-Weight (Kg):1,066
+Weight (Kg):2,114
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -5919,7 +5919,7 @@
       <c r="B346" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 6.00 x 1500.0 x 3000.0 mm
-Weight (Kg):1,936
+Weight (Kg):1,088
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -5935,7 +5935,7 @@
       <c r="B347" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 6.00 x 1500.0 x 3000.0 mm
-Weight (Kg):2,390
+Weight (Kg):1,274
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -5951,7 +5951,7 @@
       <c r="B348" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 6.00 x 1500.0 x 3000.0 mm
-Weight (Kg):1,728
+Weight (Kg):1,718
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -5967,7 +5967,7 @@
       <c r="B349" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 6.00 x 1500.0 x 3000.0 mm
-Weight (Kg):1,514
+Weight (Kg):1,922
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -5983,7 +5983,7 @@
       <c r="B350" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 6.00 x 1500.0 x 3000.0 mm
-Weight (Kg):1,922
+Weight (Kg):1,878
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -5999,7 +5999,7 @@
       <c r="B351" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 6.00 x 1500.0 x 3000.0 mm
-Weight (Kg):1,942
+Weight (Kg):1,714
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -6015,7 +6015,7 @@
       <c r="B352" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 6.00 x 1500.0 x 3000.0 mm
-Weight (Kg):2,114
+Weight (Kg):1,918
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -6031,7 +6031,7 @@
       <c r="B353" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 6.00 x 1500.0 x 3000.0 mm
-Weight (Kg):1,088
+Weight (Kg):1,754
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -6047,7 +6047,7 @@
       <c r="B354" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 6.00 x 1500.0 x 3000.0 mm
-Weight (Kg):1,274
+Weight (Kg):1,528
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -6063,7 +6063,7 @@
       <c r="B355" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 6.00 x 1500.0 x 3000.0 mm
-Weight (Kg):1,718
+Weight (Kg):2,136
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -6079,7 +6079,7 @@
       <c r="B356" t="str" xml:space="preserve">
         <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
 6.00 x 1500.0 x 3000.0 mm
-Weight (Kg):1,922
+Weight (Kg):1,946
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -6089,13 +6089,13 @@
     </row>
     <row r="357" xml:space="preserve">
       <c r="A357" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
-6.00 x 1500.0 x 3000.0 mm</v>
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, BA,
+0.80 x 1000.0 x 2000.0 mm</v>
       </c>
       <c r="B357" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
-6.00 x 1500.0 x 3000.0 mm
-Weight (Kg):1,878
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, BA,
+0.80 x 1000.0 x 2000.0 mm
+Weight (Kg):1,633
 Quality:Prime-2
 Help
 Location:FABRICA ALGECIRAS
@@ -6105,13 +6105,13 @@
     </row>
     <row r="358" xml:space="preserve">
       <c r="A358" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, 2B,
-6.00 x 1500.0 x 3000.0 mm</v>
+        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304-Sheet, BA,
+0.80 x 1000.0 x 2000.0 mm</v>
       </c>
       <c r="B358" t="str" xml:space="preserve">
-        <v xml:space="preserve">Acerinox Europa, 4301/4307 304L/304